--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -6,22 +6,21 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11910" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="AI_Cost_Sources" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Strategy_Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="00_Assumptions_List" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Assumptions_Drivers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Debt_Sweep_AI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Base_Operating" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="AI_Operating" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Coversheet" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="LBO" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="DCF" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Shares" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="52wkHL" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Strategy_Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="00_Assumptions_List" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Assumptions_Drivers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Debt_Sweep_AI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Base_Operating" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="AI_Operating" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Coversheet" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="LBO" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="DCF" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Shares" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="52wkHL" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <externalReferences>
+    <externalReference r:id="rId12"/>
     <externalReference r:id="rId13"/>
-    <externalReference r:id="rId14"/>
   </externalReferences>
   <definedNames>
     <definedName name="CIQWBGuid" hidden="1">"a611639b-bab1-425e-aaa5-008c326fdfdb"</definedName>
@@ -60,8 +59,8 @@
     <definedName name="One">'[1]Forecast Drivers'!$D$330</definedName>
     <definedName name="Products">[2]Array0!$B$5:$C$7</definedName>
     <definedName name="Rev">'[1]Forecast Drivers'!$E$25:$S$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'00_Assumptions_List'!$B$6:$M$21</definedName>
-    <definedName name="CIQWBGuid" localSheetId="7" hidden="1">"ab508404-a108-4d4f-b84c-e5fce791e559"</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'00_Assumptions_List'!$B$6:$M$21</definedName>
+    <definedName name="CIQWBGuid" localSheetId="6" hidden="1">"ab508404-a108-4d4f-b84c-e5fce791e559"</definedName>
   </definedNames>
   <calcPr calcId="152511" calcMode="autoNoTable" fullCalcOnLoad="1" iterate="1"/>
 </workbook>
@@ -154,7 +153,7 @@
     <numFmt numFmtId="245" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
     <numFmt numFmtId="246" formatCode="###0&quot;E&quot;_)"/>
   </numFmts>
-  <fonts count="110">
+  <fonts count="111">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -866,6 +865,12 @@
       <i val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="39">
     <fill>
@@ -1806,7 +1811,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="593">
+  <cellXfs count="595">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2843,6 +2848,12 @@
     </xf>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4893,653 +4904,291 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G42"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="4" customWidth="1" style="244" min="1" max="1"/>
-    <col width="36" customWidth="1" style="244" min="2" max="2"/>
-    <col width="42" customWidth="1" style="244" min="3" max="3"/>
-    <col width="36" customWidth="1" style="244" min="4" max="4"/>
-    <col width="42" customWidth="1" style="244" min="5" max="5"/>
-    <col width="40" customWidth="1" style="244" min="6" max="6"/>
+    <col width="32" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="14" customWidth="1" style="244" min="4" max="4"/>
+    <col width="14" customWidth="1" style="244" min="5" max="5"/>
+    <col width="70" customWidth="1" style="244" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
-          <t>LBOMODEL2 — Why $15m AI Infrastructure Is a Reasonable Estimate (Sourced)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1" s="244">
-      <c r="B3" s="574" t="inlineStr">
-        <is>
-          <t>This sheet is the evidence pack for Assumptions_Drivers!C9 ($15.0m). Numbers below are triangulation from PUBLIC list prices + ZoomInfo 10-K headcount — not invented.</t>
-        </is>
-      </c>
-    </row>
+          <t>vengeanceaiUSC-LBOMODEL2 — Strategy Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AI-SDR cost takeout drives margin, FCF, debt paydown, MOIC/IRR — exit multiple held at 13x in both cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="564" t="inlineStr">
         <is>
-          <t>CONCLUSION</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1" s="244">
-      <c r="B6" s="585" t="inlineStr">
-        <is>
-          <t>$15m/year is INSIDE a triangulated range of ~$9m–$45m for replacing ~378 outbound S&amp;M roles at ZoomInfo scale. We use $15m as a conservative mid/low point.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="564" t="inlineStr">
-        <is>
-          <t>PRIMARY PUBLIC PRICE ANCHORS (click links)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="586" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C9" s="586" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="D9" s="586" t="inlineStr">
-        <is>
-          <t>What it says (public)</t>
-        </is>
-      </c>
-      <c r="E9" s="586" t="inlineStr">
-        <is>
-          <t>URL (click)</t>
-        </is>
-      </c>
-      <c r="F9" s="586" t="inlineStr">
-        <is>
-          <t>How we use it</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="56" customHeight="1" s="244">
-      <c r="B10" s="587" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="420" t="inlineStr">
-        <is>
-          <t>Salesforce Agentforce press release (May 15, 2025)</t>
-        </is>
-      </c>
-      <c r="D10" s="420" t="inlineStr">
-        <is>
-          <t>$2 per conversation (original model) AND Flex Credits at $500 / 100,000 credits (= $0.10 per action; 20 credits/action).</t>
-        </is>
-      </c>
-      <c r="E10" s="572" t="inlineStr">
-        <is>
-          <t>https://www.salesforce.com/news/press-releases/2025/05/15/agentforce-flexible-pricing-news/</t>
-        </is>
-      </c>
-      <c r="F10" s="420" t="inlineStr">
-        <is>
-          <t>Primary list-price anchor for agent conversation / action economics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="56" customHeight="1" s="244">
-      <c r="B11" s="587" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="420" t="inlineStr">
-        <is>
-          <t>SaaStr summary of Agentforce pricing models</t>
-        </is>
-      </c>
-      <c r="D11" s="420" t="inlineStr">
-        <is>
-          <t>Confirms three live models: $2/conversation, ~$0.10/action Flex Credits, and ~$125+/user/month digital labor seats.</t>
-        </is>
-      </c>
-      <c r="E11" s="572" t="inlineStr">
-        <is>
-          <t>https://www.saastr.com/salesforce-now-has-3-pricing-models-for-agentforce-and-maybe-right-now-thats-the-way-to-do-it/</t>
-        </is>
-      </c>
-      <c r="F11" s="420" t="inlineStr">
-        <is>
-          <t>Cross-check that seat + consumption pricing both exist for budgeting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="56" customHeight="1" s="244">
-      <c r="B12" s="587" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" s="420" t="inlineStr">
-        <is>
-          <t>Independent Agentforce pricing guide (list prices)</t>
-        </is>
-      </c>
-      <c r="D12" s="420" t="inlineStr">
-        <is>
-          <t>Documents Agentforce add-on ~$125–$150/user/month and Flex Credit math matching Salesforce.</t>
-        </is>
-      </c>
-      <c r="E12" s="572" t="inlineStr">
-        <is>
-          <t>https://www.layer3labs.io/guides/salesforce-agentforce-pricing-explained</t>
-        </is>
-      </c>
-      <c r="F12" s="420" t="inlineStr">
-        <is>
-          <t>Seat-license path for employee-facing / digital labor agents.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="56" customHeight="1" s="244">
-      <c r="B13" s="587" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" s="420" t="inlineStr">
-        <is>
-          <t>ZoomInfo FY2024 Form 10-K (SEC)</t>
-        </is>
-      </c>
-      <c r="D13" s="420" t="inlineStr">
-        <is>
-          <t>As of Dec 31, 2024: 3,508 employees; 1,513 in sales &amp; marketing.</t>
-        </is>
-      </c>
-      <c r="E13" s="572" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm</t>
-        </is>
-      </c>
-      <c r="F13" s="420" t="inlineStr">
-        <is>
-          <t>Scale factor: how many human outbound roles AI must replace.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="56" customHeight="1" s="244">
-      <c r="B14" s="587" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" s="420" t="inlineStr">
-        <is>
-          <t>ZoomInfo FY2024 10-K PDF (Human Capital)</t>
-        </is>
-      </c>
-      <c r="D14" s="420" t="inlineStr">
-        <is>
-          <t>Same headcount disclosure in printable annual report PDF.</t>
-        </is>
-      </c>
-      <c r="E14" s="572" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451525000075/zoominfo10k2024printvf.pdf</t>
-        </is>
-      </c>
-      <c r="F14" s="420" t="inlineStr">
-        <is>
-          <t>Backup filing link for the S&amp;M headcount figure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="56" customHeight="1" s="244">
-      <c r="B15" s="587" t="n">
-        <v>6</v>
-      </c>
-      <c r="C15" s="420" t="inlineStr">
-        <is>
-          <t>Gartner AI-optimized IaaS forecast (Aug 2026)</t>
-        </is>
-      </c>
-      <c r="D15" s="420" t="inlineStr">
-        <is>
-          <t>Worldwide AI-optimized IaaS ~$42.3B in 2026; inference overtakes training — production agent compute is a real, growing opex line.</t>
-        </is>
-      </c>
-      <c r="E15" s="572" t="inlineStr">
-        <is>
-          <t>https://www.gartner.com/en/newsroom/press-releases/2026-08-10-gartner-forecasts-worldwide-artificial-intelligence-optimized-iaas-spending-to-grow-96-percent-in-2026</t>
-        </is>
-      </c>
-      <c r="F15" s="420" t="inlineStr">
-        <is>
-          <t>Macro proof that inference/API/compute spend is material (not a rounding error).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="56" customHeight="1" s="244">
-      <c r="B16" s="587" t="n">
-        <v>7</v>
-      </c>
-      <c r="C16" s="420" t="inlineStr">
-        <is>
-          <t>AI SDR TCO / pricing survey</t>
-        </is>
-      </c>
-      <c r="D16" s="420" t="inlineStr">
-        <is>
-          <t>Point tools $300–$1,500/user/mo; autonomous AI workers $1k–$5k/mo; enterprise bundles often $50k–$250k+ annually (mid-market).</t>
-        </is>
-      </c>
-      <c r="E16" s="572" t="inlineStr">
-        <is>
-          <t>https://everworker.ai/blog/ai_sdr_software_pricing_tco_roi_guide</t>
-        </is>
-      </c>
-      <c r="F16" s="420" t="inlineStr">
-        <is>
-          <t>Shows mid-market AI SDR alone is already six figures; ZoomInfo scale is multiples of that.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="56" customHeight="1" s="244">
-      <c r="B17" s="587" t="n">
-        <v>8</v>
-      </c>
-      <c r="C17" s="420" t="inlineStr">
-        <is>
-          <t>AI SDR vendor price compilation (incl. 11x-style agents)</t>
-        </is>
-      </c>
-      <c r="D17" s="420" t="inlineStr">
-        <is>
-          <t>Custom enterprise AI SDR agents commonly estimated ~$5,000–$10,000 per month per agent.</t>
-        </is>
-      </c>
-      <c r="E17" s="572" t="inlineStr">
-        <is>
-          <t>https://highticketaisystems.com/blog/ai-sdr-pricing-explained</t>
-        </is>
-      </c>
-      <c r="F17" s="420" t="inlineStr">
-        <is>
-          <t>Per-agent monthly cost used in Scenario C below.</t>
+          <t>RESULTS — AI vs Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="412" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C6" s="412" t="inlineStr">
+        <is>
+          <t>Base (no AI)</t>
+        </is>
+      </c>
+      <c r="D6" s="412" t="inlineStr">
+        <is>
+          <t>AI-SDR case</t>
+        </is>
+      </c>
+      <c r="E6" s="412" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="F6" s="412" t="inlineStr">
+        <is>
+          <t>COMMENTARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" s="244">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Y2 EBITDA margin</t>
+        </is>
+      </c>
+      <c r="C7" s="565" t="n">
+        <v>0.1085118998600017</v>
+      </c>
+      <c r="D7" s="565" t="n">
+        <v>0.2012029241075531</v>
+      </c>
+      <c r="E7" s="565" t="n">
+        <v>0.09269102424755141</v>
+      </c>
+      <c r="F7" s="566" t="inlineStr">
+        <is>
+          <t>Year 2 operating profitability under 10% growth / 80% GM / AI S&amp;M path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" s="244">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Y2 margin vs baseline (bps)</t>
+        </is>
+      </c>
+      <c r="C8" s="567" t="n">
+        <v>-422.7456147574727</v>
+      </c>
+      <c r="D8" s="567" t="n">
+        <v>504.1646277180415</v>
+      </c>
+      <c r="E8" s="567" t="n">
+        <v>926.9102424755141</v>
+      </c>
+      <c r="F8" s="566" t="inlineStr">
+        <is>
+          <t>Y2 EBITDA margin minus FY24 baseline margin, in basis points (target ≥500).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" s="244">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Y5 EBITDA ($m)</t>
+        </is>
+      </c>
+      <c r="C9" s="567" t="n">
+        <v>212.2104606600003</v>
+      </c>
+      <c r="D9" s="567" t="n">
+        <v>496.3963076296004</v>
+      </c>
+      <c r="E9" s="567" t="n">
+        <v>284.1858469696001</v>
+      </c>
+      <c r="F9" s="566" t="inlineStr">
+        <is>
+          <t>Year 5 EBITDA ($m).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1" s="244">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Exit EV @ 13x ($m)</t>
+        </is>
+      </c>
+      <c r="C10" s="567" t="n">
+        <v>2758.735988580003</v>
+      </c>
+      <c r="D10" s="567" t="n">
+        <v>6453.151999184804</v>
+      </c>
+      <c r="E10" s="567" t="n">
+        <v>3694.416010604801</v>
+      </c>
+      <c r="F10" s="566" t="inlineStr">
+        <is>
+          <t>Exit EV = Y5 EBITDA × 13x (Assumptions_Drivers!C20 / LBO!D17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1" s="244">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Exit net debt ($m)</t>
+        </is>
+      </c>
+      <c r="C11" s="567" t="n">
+        <v>557.1124750633038</v>
+      </c>
+      <c r="D11" s="567" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="567" t="n">
+        <v>-557.1124750633038</v>
+      </c>
+      <c r="F11" s="566" t="inlineStr">
+        <is>
+          <t>Ending net debt after mandatory amort + 100% cash sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1" s="244">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Exit equity value ($m)</t>
+        </is>
+      </c>
+      <c r="C12" s="567" t="n">
+        <v>2201.623513516699</v>
+      </c>
+      <c r="D12" s="567" t="n">
+        <v>6453.151999184804</v>
+      </c>
+      <c r="E12" s="567" t="n">
+        <v>4251.528485668105</v>
+      </c>
+      <c r="F12" s="566" t="inlineStr">
+        <is>
+          <t>Exit equity = Exit EV − ending debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" s="244">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MOIC</t>
+        </is>
+      </c>
+      <c r="C13" s="568" t="n">
+        <v>1.17652754423803</v>
+      </c>
+      <c r="D13" s="568" t="n">
+        <v>3.448505626681045</v>
+      </c>
+      <c r="E13" s="568" t="n">
+        <v>2.271978082443015</v>
+      </c>
+      <c r="F13" s="566" t="inlineStr">
+        <is>
+          <t>MOIC = Exit equity / sponsor equity check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" s="244">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IRR (5-year)</t>
+        </is>
+      </c>
+      <c r="C14" s="565" t="n">
+        <v>0.03304780632992022</v>
+      </c>
+      <c r="D14" s="565" t="n">
+        <v>0.2809323319237782</v>
+      </c>
+      <c r="E14" s="565" t="n">
+        <v>0.247884525593858</v>
+      </c>
+      <c r="F14" s="566" t="inlineStr">
+        <is>
+          <t>IRR over 5 years = MOIC^(1/5) − 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="569" t="inlineStr">
+        <is>
+          <t>IRR uplift from AI S&amp;M: 24.8 percentage points | Y2 margin expansion: 504 bps (target ≥500: YES)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PDF assumptions list:</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="570" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.pdf</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="564" t="inlineStr">
-        <is>
-          <t>BOTTOM-UP TRIANGULATION → $15.0m</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="40" customHeight="1" s="244">
-      <c r="B21" s="574" t="inlineStr">
-        <is>
-          <t>Scale assumption: 25% of 1,513 S&amp;M employees ≈ 378 outbound SDR/BDR roles replaced (illustrative share of S&amp;M; 10-K does not break out SDRs alone).</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>In-Excel full commentary: 00_Assumptions_List | Drivers: Assumptions_Drivers</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Every Assumptions_Drivers input has a source link + justification in columns E–G (same row).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="586" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C23" s="586" t="inlineStr">
-        <is>
-          <t>Public price used</t>
-        </is>
-      </c>
-      <c r="D23" s="586" t="inlineStr">
-        <is>
-          <t>Volume / seats implied by $15m</t>
-        </is>
-      </c>
-      <c r="E23" s="586" t="inlineStr">
-        <is>
-          <t>Implied annual cost</t>
-        </is>
-      </c>
-      <c r="F23" s="586" t="inlineStr">
-        <is>
-          <t>Verdict vs $15m</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="52" customHeight="1" s="244">
-      <c r="B24" s="420" t="inlineStr">
-        <is>
-          <t>A. Salesforce $2 / conversation</t>
-        </is>
-      </c>
-      <c r="C24" s="420" t="inlineStr">
-        <is>
-          <t>$2 / conversation (SF press)</t>
-        </is>
-      </c>
-      <c r="D24" s="420" t="inlineStr">
-        <is>
-          <t>7.5m agent conversations / year</t>
-        </is>
-      </c>
-      <c r="E24" s="420" t="inlineStr">
-        <is>
-          <t>$15.0m (by construction)</t>
-        </is>
-      </c>
-      <c r="F24" s="588" t="inlineStr">
-        <is>
-          <t>Reasonable at ZoomInfo outbound scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="52" customHeight="1" s="244">
-      <c r="B25" s="420" t="inlineStr">
-        <is>
-          <t>B. Salesforce Flex Credits ~$0.10 / action</t>
-        </is>
-      </c>
-      <c r="C25" s="420" t="inlineStr">
-        <is>
-          <t>$0.10 / action (SF press)</t>
-        </is>
-      </c>
-      <c r="D25" s="420" t="inlineStr">
-        <is>
-          <t>150m agent actions / year</t>
-        </is>
-      </c>
-      <c r="E25" s="420" t="inlineStr">
-        <is>
-          <t>$15.0m (by construction)</t>
-        </is>
-      </c>
-      <c r="F25" s="588" t="inlineStr">
-        <is>
-          <t>Reasonable for multi-step agentic workflows</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="52" customHeight="1" s="244">
-      <c r="B26" s="420" t="inlineStr">
-        <is>
-          <t>C. Enterprise AI SDR agents $5–10k / mo</t>
-        </is>
-      </c>
-      <c r="C26" s="420" t="inlineStr">
-        <is>
-          <t>$5,000–$10,000/mo/agent</t>
-        </is>
-      </c>
-      <c r="D26" s="420" t="inlineStr">
-        <is>
-          <t>378 agents × 12 months</t>
-        </is>
-      </c>
-      <c r="E26" s="420" t="inlineStr">
-        <is>
-          <t>$22.7m – $45.4m</t>
-        </is>
-      </c>
-      <c r="F26" s="588" t="inlineStr">
-        <is>
-          <t>$15m is BELOW / at low end of this range</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="52" customHeight="1" s="244">
-      <c r="B27" s="420" t="inlineStr">
-        <is>
-          <t>D. Agentforce seats alone @ $125/user/mo</t>
-        </is>
-      </c>
-      <c r="C27" s="420" t="inlineStr">
-        <is>
-          <t>$125/user/mo × 12</t>
-        </is>
-      </c>
-      <c r="D27" s="420" t="inlineStr">
-        <is>
-          <t>$15m buys ~10,000 seats (or ~378 seats ≈ $0.6m) + API/compute still needed</t>
-        </is>
-      </c>
-      <c r="E27" s="420" t="inlineStr">
-        <is>
-          <t>Seats-only for 378 roles ≈ $0.6m</t>
-        </is>
-      </c>
-      <c r="F27" s="588" t="inlineStr">
-        <is>
-          <t>Seats alone understate TCO → add API/compute → ~$15m total is coherent</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="52" customHeight="1" s="244">
-      <c r="B28" s="420" t="inlineStr">
-        <is>
-          <t>E. Hybrid (seats + consumption / LLM API)</t>
-        </is>
-      </c>
-      <c r="C28" s="420" t="inlineStr">
-        <is>
-          <t>~378 seats @ $125/mo + ~$12m API/compute/enrichment</t>
-        </is>
-      </c>
-      <c r="D28" s="420" t="inlineStr">
-        <is>
-          <t>Licenses + inference + data + voice + observability</t>
-        </is>
-      </c>
-      <c r="E28" s="420" t="inlineStr">
-        <is>
-          <t>≈ $12.6m</t>
-        </is>
-      </c>
-      <c r="F28" s="588" t="inlineStr">
-        <is>
-          <t>Closest to how enterprises actually buy → supports $15m</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="564" t="inlineStr">
-        <is>
-          <t>BINDING TO THE LBO MODEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="586" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="C31" s="586" t="inlineStr">
-        <is>
-          <t>Tab</t>
-        </is>
-      </c>
-      <c r="D31" s="586" t="inlineStr">
-        <is>
-          <t>Cell</t>
-        </is>
-      </c>
-      <c r="E31" s="586" t="inlineStr">
-        <is>
-          <t>Jump</t>
-        </is>
-      </c>
-      <c r="F31" s="586" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="587" t="inlineStr">
-        <is>
-          <t>AI infrastructure ($m)</t>
-        </is>
-      </c>
-      <c r="C32" s="587" t="inlineStr">
-        <is>
-          <t>Assumptions_Drivers</t>
-        </is>
-      </c>
-      <c r="D32" s="587" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="E32" s="589" t="inlineStr">
-        <is>
-          <t>Go to Assumptions_Drivers!C9</t>
-        </is>
-      </c>
-      <c r="F32" s="420" t="inlineStr">
-        <is>
-          <t>Yellow input = 15.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="587" t="inlineStr">
-        <is>
-          <t>AI cost hits P&amp;L</t>
-        </is>
-      </c>
-      <c r="C33" s="587" t="inlineStr">
-        <is>
-          <t>AI_Operating</t>
-        </is>
-      </c>
-      <c r="D33" s="587" t="inlineStr">
-        <is>
-          <t>D10:H10</t>
-        </is>
-      </c>
-      <c r="E33" s="589" t="inlineStr">
-        <is>
-          <t>Go to AI_Operating!D10</t>
-        </is>
-      </c>
-      <c r="F33" s="420" t="inlineStr">
-        <is>
-          <t>Fixed $15m each forecast year (AI case)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="587" t="inlineStr">
-        <is>
-          <t>Assumption commentary</t>
-        </is>
-      </c>
-      <c r="C34" s="587" t="inlineStr">
-        <is>
-          <t>00_Assumptions_List</t>
-        </is>
-      </c>
-      <c r="D34" s="587" t="inlineStr">
-        <is>
-          <t>row for AI Infrastructure</t>
-        </is>
-      </c>
-      <c r="E34" s="589" t="inlineStr">
-        <is>
-          <t>Go to 00_Assumptions_List!B11</t>
-        </is>
-      </c>
-      <c r="F34" s="420" t="inlineStr">
-        <is>
-          <t>Includes this source pack</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="587" t="inlineStr">
-        <is>
-          <t>This evidence pack</t>
-        </is>
-      </c>
-      <c r="C35" s="587" t="inlineStr">
-        <is>
-          <t>AI_Cost_Sources</t>
-        </is>
-      </c>
-      <c r="D35" s="587" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="E35" s="589" t="inlineStr">
-        <is>
-          <t>Go to AI_Cost_Sources!B2</t>
-        </is>
-      </c>
-      <c r="F35" s="420" t="inlineStr">
-        <is>
-          <t>You are here</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="564" t="inlineStr">
-        <is>
-          <t>PDF twin of this sheet:</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="590" t="inlineStr">
+      <c r="B23" s="593" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers source columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="593" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_AI_COST_SOURCES.pdf</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="564" t="inlineStr">
-        <is>
-          <t>Excel workbook:</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="590" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/vengeanceaiUSC_LBOMODEL2.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="591" t="inlineStr">
-        <is>
-          <t>Educational / research use only — not investment advice. List prices change; use as order-of-magnitude triangulation.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B6:G6"/>
-  </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5551,1626 +5200,301 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K118"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="1.7109375" customWidth="1" style="244" min="1" max="1"/>
-    <col width="40.28515625" customWidth="1" style="244" min="2" max="2"/>
-    <col width="12.140625" bestFit="1" customWidth="1" style="244" min="3" max="3"/>
-    <col width="11.140625" bestFit="1" customWidth="1" style="244" min="4" max="4"/>
-    <col width="10.140625" bestFit="1" customWidth="1" style="244" min="5" max="7"/>
-    <col width="11" customWidth="1" style="244" min="8" max="10"/>
-    <col width="12.140625" bestFit="1" customWidth="1" style="244" min="11" max="11"/>
-    <col width="9.140625" customWidth="1" style="244" min="12" max="12"/>
-    <col width="9.140625" customWidth="1" style="244" min="13" max="13"/>
-    <col width="9.140625" customWidth="1" style="244" min="14" max="16384"/>
+    <col width="36.5703125" bestFit="1" customWidth="1" style="244" min="2" max="2"/>
+    <col width="15.85546875" customWidth="1" style="244" min="3" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" s="244" thickBot="1"/>
     <row r="2" ht="27" customHeight="1" s="244" thickBot="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Discounted Cash Flow Model for BMC</t>
+          <t>Diluted shares for BMC</t>
         </is>
       </c>
       <c r="C2" s="305" t="n"/>
       <c r="D2" s="305" t="n"/>
       <c r="E2" s="305" t="n"/>
-      <c r="F2" s="305" t="n"/>
-      <c r="G2" s="305" t="n"/>
-      <c r="H2" s="305" t="n"/>
-      <c r="I2" s="305" t="n"/>
-      <c r="J2" s="305" t="n"/>
     </row>
     <row r="3">
-      <c r="B3" s="84" t="inlineStr">
+      <c r="B3" s="302" t="inlineStr">
         <is>
           <t>$ mm except per share</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="84" t="n"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1" s="244" thickBot="1">
-      <c r="B5" s="66" t="inlineStr">
-        <is>
-          <t>General assumptions</t>
-        </is>
-      </c>
-      <c r="C5" s="93" t="n"/>
+      <c r="B4" s="34" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>Offer price</t>
+        </is>
+      </c>
+      <c r="E5" s="513" t="n">
+        <v>46.25</v>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Share price as of last close</t>
-        </is>
-      </c>
-      <c r="C6" s="528" t="n">
+      <c r="B6" s="304" t="inlineStr">
+        <is>
+          <t>Model-derived offer value sanity check</t>
+        </is>
+      </c>
+      <c r="E6" s="554" t="n">
         <v>46.25</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="84" t="inlineStr">
-        <is>
-          <t>Latest closing share price date</t>
-        </is>
-      </c>
-      <c r="C7" s="84" t="n">
-        <v>41400</v>
+      <c r="B7" s="159" t="inlineStr">
+        <is>
+          <t>Basic shares outstanding (latest filing)</t>
+        </is>
+      </c>
+      <c r="E7" s="522" t="n">
+        <v>143.973</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="84" t="inlineStr">
-        <is>
-          <t>Latest basic share count</t>
-        </is>
-      </c>
-      <c r="C8" s="529" t="n">
-        <v>143.973</v>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>In-the-money exercisable options</t>
+        </is>
+      </c>
+      <c r="E8" s="521" t="n">
+        <v>10.7</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="84" t="inlineStr">
-        <is>
-          <t>Weighted average cost of capital</t>
-        </is>
-      </c>
-      <c r="C9" s="530" t="n">
-        <v>0.06990222994664612</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="244" thickBot="1">
-      <c r="B11" s="69" t="inlineStr">
-        <is>
-          <t>Free cash flow buildup</t>
-        </is>
-      </c>
-      <c r="C11" s="93" t="n"/>
-      <c r="D11" s="93" t="n"/>
-      <c r="E11" s="93" t="n"/>
-      <c r="F11" s="93" t="n"/>
-      <c r="G11" s="93" t="n"/>
-      <c r="H11" s="93" t="n"/>
-      <c r="I11" s="93" t="n"/>
-      <c r="J11" s="93" t="n"/>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>Total proceeds ($mm)</t>
+        </is>
+      </c>
+      <c r="E9" s="461" t="n">
+        <v>411.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>Total shares repurchased (mm)</t>
+        </is>
+      </c>
+      <c r="E10" s="461" t="n">
+        <v>8.901621621621622</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>Net dilutive options</t>
+        </is>
+      </c>
+      <c r="E11" s="461" t="n">
+        <v>1.798378378378377</v>
+      </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fiscal year  </t>
-        </is>
-      </c>
-      <c r="C12" s="270" t="n">
-        <v>2011</v>
-      </c>
-      <c r="D12" s="270" t="n">
-        <v>2012</v>
-      </c>
-      <c r="E12" s="270" t="n">
-        <v>2013</v>
-      </c>
-      <c r="F12" s="157" t="n">
-        <v>2014</v>
-      </c>
-      <c r="G12" s="157" t="n">
-        <v>2015</v>
-      </c>
-      <c r="H12" s="157" t="n">
-        <v>2016</v>
-      </c>
-      <c r="I12" s="157" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J12" s="157" t="n">
-        <v>2018</v>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dilutive impact of shares from other securities </t>
+        </is>
+      </c>
+      <c r="E12" s="522" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>Fiscal year end date</t>
-        </is>
-      </c>
-      <c r="C13" s="39" t="n">
-        <v>40633</v>
-      </c>
-      <c r="D13" s="39" t="n">
-        <v>40999</v>
-      </c>
-      <c r="E13" s="39" t="n">
-        <v>41364</v>
-      </c>
-      <c r="F13" s="39" t="n">
-        <v>41729</v>
-      </c>
-      <c r="G13" s="39" t="n">
-        <v>42094</v>
-      </c>
-      <c r="H13" s="39" t="n">
-        <v>42460</v>
-      </c>
-      <c r="I13" s="39" t="n">
-        <v>42825</v>
-      </c>
-      <c r="J13" s="39" t="n">
-        <v>43190</v>
-      </c>
+      <c r="B13" s="34" t="n"/>
+      <c r="E13" s="522" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="70" t="n"/>
-      <c r="F14" s="435" t="n"/>
-      <c r="G14" s="435" t="n"/>
-      <c r="H14" s="435" t="n"/>
-      <c r="I14" s="435" t="n"/>
-      <c r="J14" s="435" t="n"/>
+      <c r="B14" s="147" t="inlineStr">
+        <is>
+          <t>Net diluted shares outstanding</t>
+        </is>
+      </c>
+      <c r="D14" s="434" t="n"/>
+      <c r="E14" s="461" t="n">
+        <v>145.7713783783784</v>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="C15" s="162" t="n">
-        <v>843.6000000000003</v>
-      </c>
-      <c r="D15" s="162" t="n">
-        <v>906.4999999999999</v>
-      </c>
-      <c r="E15" s="162" t="n">
-        <v>882.7000000000003</v>
-      </c>
-      <c r="F15" s="162" t="n">
-        <v>947.6792413199889</v>
-      </c>
-      <c r="G15" s="162" t="n">
-        <v>1000.484484594448</v>
-      </c>
-      <c r="H15" s="162" t="n">
-        <v>1078.88768747765</v>
-      </c>
-      <c r="I15" s="162" t="n">
-        <v>1150.07160606407</v>
-      </c>
-      <c r="J15" s="162" t="n">
-        <v>1226.874119002437</v>
-      </c>
+      <c r="B15" s="147" t="n"/>
+      <c r="D15" s="434" t="n"/>
+      <c r="E15" s="461" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="C16" s="162" t="n">
-        <v>532.8000000000003</v>
-      </c>
-      <c r="D16" s="162" t="n">
-        <v>543.8999999999999</v>
-      </c>
-      <c r="E16" s="162" t="n">
-        <v>465.4000000000003</v>
-      </c>
-      <c r="F16" s="162" t="n">
-        <v>493.6803141804108</v>
-      </c>
-      <c r="G16" s="162" t="n">
-        <v>559.8040395999167</v>
-      </c>
-      <c r="H16" s="162" t="n">
-        <v>634.7919640514119</v>
-      </c>
-      <c r="I16" s="162" t="n">
-        <v>709.3122632461741</v>
-      </c>
-      <c r="J16" s="162" t="n">
-        <v>787.9602383046408</v>
-      </c>
+      <c r="B16" s="312" t="inlineStr">
+        <is>
+          <t>Options outstanding</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="445" t="n"/>
+      <c r="E16" s="518" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>tax rate</t>
-        </is>
-      </c>
-      <c r="C17" s="531" t="n">
-        <v>0.1413514022209673</v>
-      </c>
-      <c r="D17" s="531" t="n">
-        <v>0.2433962264150944</v>
-      </c>
-      <c r="E17" s="531" t="n">
-        <v>0.2264547791540078</v>
-      </c>
-      <c r="F17" s="531" t="n">
-        <v>0.2264547791540078</v>
-      </c>
-      <c r="G17" s="531" t="n">
-        <v>0.2264547791540078</v>
-      </c>
-      <c r="H17" s="531" t="n">
-        <v>0.2264547791540078</v>
-      </c>
-      <c r="I17" s="531" t="n">
-        <v>0.2264547791540078</v>
-      </c>
-      <c r="J17" s="531" t="n">
-        <v>0.2264547791540078</v>
+      <c r="C17" s="242" t="inlineStr">
+        <is>
+          <t>Out. shares</t>
+        </is>
+      </c>
+      <c r="D17" s="242" t="inlineStr">
+        <is>
+          <t>Exercise price</t>
+        </is>
+      </c>
+      <c r="E17" s="242" t="inlineStr">
+        <is>
+          <t>In-the-$-shares</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="383" t="inlineStr">
-        <is>
-          <t>EBIAT (NOPAT)</t>
-        </is>
-      </c>
-      <c r="C18" s="71" t="n">
-        <v>457.4879728966689</v>
-      </c>
-      <c r="D18" s="71" t="n">
-        <v>411.51679245283</v>
-      </c>
-      <c r="E18" s="71" t="n">
-        <v>360.007945781725</v>
-      </c>
-      <c r="F18" s="71" t="n">
-        <v>381.8840476600047</v>
-      </c>
-      <c r="G18" s="71" t="n">
-        <v>433.0337394427961</v>
-      </c>
-      <c r="H18" s="71" t="n">
-        <v>491.0402900234106</v>
-      </c>
-      <c r="I18" s="71" t="n">
-        <v>548.6851113215323</v>
-      </c>
-      <c r="J18" s="71" t="n">
-        <v>609.522876557224</v>
+      <c r="B18" s="555" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="298" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D18" s="298" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" s="299" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="383" t="n"/>
+      <c r="B19" s="555" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="298" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D19" s="298" t="n">
+        <v>18</v>
+      </c>
+      <c r="E19" s="299" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="20">
-      <c r="B20" s="73" t="inlineStr">
-        <is>
-          <t>Depreciation and amortization</t>
-        </is>
-      </c>
-      <c r="F20" s="162" t="n">
-        <v>223.946868228773</v>
-      </c>
-      <c r="G20" s="162" t="n">
-        <v>220.6010317460318</v>
-      </c>
-      <c r="H20" s="162" t="n">
-        <v>222.400781053162</v>
-      </c>
-      <c r="I20" s="162" t="n">
-        <v>224.1937314184933</v>
-      </c>
-      <c r="J20" s="162" t="n">
-        <v>223</v>
+      <c r="B20" s="555" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="298" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D20" s="298" t="n">
+        <v>22</v>
+      </c>
+      <c r="E20" s="299" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="73" t="inlineStr">
-        <is>
-          <t>Stock based compensation</t>
-        </is>
-      </c>
-      <c r="F21" s="162" t="n">
-        <v>161.0547368274718</v>
-      </c>
-      <c r="G21" s="162" t="n">
-        <v>162.0820911651659</v>
-      </c>
-      <c r="H21" s="162" t="n">
-        <v>163.6976202897424</v>
-      </c>
-      <c r="I21" s="162" t="n">
-        <v>163.5682893160696</v>
-      </c>
-      <c r="J21" s="162" t="n">
-        <v>162.9165586144626</v>
+      <c r="B21" s="555" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="298" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D21" s="298" t="n">
+        <v>28</v>
+      </c>
+      <c r="E21" s="299" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Changes in net working capital</t>
-        </is>
-      </c>
-      <c r="F22" s="162" t="n">
-        <v>56.83135068829188</v>
-      </c>
-      <c r="G22" s="162" t="n">
-        <v>95.05600763617076</v>
-      </c>
-      <c r="H22" s="162" t="n">
-        <v>109.4272418486823</v>
-      </c>
-      <c r="I22" s="162" t="n">
-        <v>96.46443037533186</v>
-      </c>
-      <c r="J22" s="162" t="n">
-        <v>97.15243145060185</v>
+      <c r="B22" s="555" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="298" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D22" s="298" t="n">
+        <v>32</v>
+      </c>
+      <c r="E22" s="299" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Other assets &amp; liabilities</t>
-        </is>
-      </c>
-      <c r="F23" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="162" t="n">
-        <v>0</v>
+      <c r="B23" s="555" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" s="298" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D23" s="298" t="n">
+        <v>36</v>
+      </c>
+      <c r="E23" s="299" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="383" t="inlineStr">
-        <is>
-          <t>Unlevered CFO</t>
-        </is>
-      </c>
-      <c r="F24" s="57" t="n">
-        <v>823.7170034045414</v>
-      </c>
-      <c r="G24" s="57" t="n">
-        <v>910.7728699901645</v>
-      </c>
-      <c r="H24" s="57" t="n">
-        <v>986.5659332149974</v>
-      </c>
-      <c r="I24" s="57" t="n">
-        <v>1032.911562431427</v>
-      </c>
-      <c r="J24" s="57" t="n">
-        <v>1092.591866622289</v>
+      <c r="B24" s="555" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" s="298" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D24" s="298" t="n">
+        <v>39</v>
+      </c>
+      <c r="E24" s="299" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="34" t="inlineStr">
-        <is>
-          <t>Less: Capital expenditures</t>
-        </is>
-      </c>
-      <c r="F25" s="162" t="n">
-        <v>-26</v>
-      </c>
-      <c r="G25" s="162" t="n">
-        <v>-28</v>
-      </c>
-      <c r="H25" s="162" t="n">
-        <v>-30</v>
-      </c>
-      <c r="I25" s="162" t="n">
-        <v>-29</v>
-      </c>
-      <c r="J25" s="162" t="n">
-        <v>-31</v>
+      <c r="B25" s="555" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" s="298" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D25" s="298" t="n">
+        <v>42</v>
+      </c>
+      <c r="E25" s="299" t="n">
+        <v>7.4</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="34" t="inlineStr">
-        <is>
-          <t>Less: Purchases of intangible assets</t>
-        </is>
-      </c>
-      <c r="F26" s="162" t="n">
-        <v>-201</v>
-      </c>
-      <c r="G26" s="162" t="n">
-        <v>-194</v>
-      </c>
-      <c r="H26" s="162" t="n">
-        <v>-193</v>
-      </c>
-      <c r="I26" s="162" t="n">
-        <v>-196</v>
-      </c>
-      <c r="J26" s="162" t="n">
-        <v>-192</v>
+      <c r="B26" s="555" t="n">
+        <v>9</v>
+      </c>
+      <c r="C26" s="298" t="n"/>
+      <c r="D26" s="298" t="n"/>
+      <c r="E26" s="299" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="383" t="inlineStr">
-        <is>
-          <t>Unlevered FCF</t>
-        </is>
-      </c>
-      <c r="F27" s="57" t="n">
-        <v>596.7170034045414</v>
-      </c>
-      <c r="G27" s="57" t="n">
-        <v>688.7728699901645</v>
-      </c>
-      <c r="H27" s="57" t="n">
-        <v>763.5659332149974</v>
-      </c>
-      <c r="I27" s="57" t="n">
-        <v>807.9115624314272</v>
-      </c>
-      <c r="J27" s="57" t="n">
-        <v>869.5918666222885</v>
+      <c r="B27" s="555" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" s="298" t="n"/>
+      <c r="D27" s="298" t="n"/>
+      <c r="E27" s="300" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="202" t="inlineStr">
-        <is>
-          <t>% growth</t>
-        </is>
-      </c>
-      <c r="G28" s="435" t="n">
-        <v>0.1542705605176367</v>
-      </c>
-      <c r="H28" s="435" t="n">
-        <v>0.1085888635914201</v>
-      </c>
-      <c r="I28" s="435" t="n">
-        <v>0.05807701376842789</v>
-      </c>
-      <c r="J28" s="435" t="n">
-        <v>0.07634536632355293</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="202" t="n"/>
-      <c r="G29" s="435" t="n"/>
-      <c r="H29" s="435" t="n"/>
-      <c r="I29" s="435" t="n"/>
-      <c r="J29" s="435" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="73" t="inlineStr">
-        <is>
-          <t>Discount factor</t>
-        </is>
-      </c>
-      <c r="F30" s="437" t="n">
-        <v>0.9027777777777778</v>
-      </c>
-      <c r="G30" s="437" t="n">
-        <v>1.902777777777778</v>
-      </c>
-      <c r="H30" s="437" t="n">
-        <v>2.902777777777778</v>
-      </c>
-      <c r="I30" s="437" t="n">
-        <v>3.902777777777778</v>
-      </c>
-      <c r="J30" s="437" t="n">
-        <v>4.902777777777778</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Assume cash flows are generated at:</t>
-        </is>
-      </c>
-      <c r="C31" s="97" t="inlineStr">
-        <is>
-          <t>Middle of period</t>
-        </is>
-      </c>
-      <c r="G31" s="437" t="n"/>
-      <c r="H31" s="437" t="n"/>
-      <c r="I31" s="437" t="n"/>
-      <c r="J31" s="437" t="n"/>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Midperiod adjustment factor</t>
-        </is>
-      </c>
-      <c r="C32" s="532" t="n">
-        <v>1.034360783260196</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="73" t="inlineStr">
-        <is>
-          <t>Present value of Unlevered FCF</t>
-        </is>
-      </c>
-      <c r="F33" s="95" t="n">
-        <v>580.6965753021989</v>
-      </c>
-      <c r="G33" s="95" t="n">
-        <v>626.488049752141</v>
-      </c>
-      <c r="H33" s="95" t="n">
-        <v>649.1412539283756</v>
-      </c>
-      <c r="I33" s="95" t="n">
-        <v>641.9665463307613</v>
-      </c>
-      <c r="J33" s="95" t="n">
-        <v>645.8325799660284</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="383" t="n"/>
-      <c r="C34" s="435" t="n"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1" s="244" thickBot="1">
-      <c r="B35" s="63" t="inlineStr">
-        <is>
-          <t>Perpetuity approach</t>
-        </is>
-      </c>
-      <c r="C35" s="93" t="n"/>
-      <c r="E35" s="63" t="inlineStr">
-        <is>
-          <t>Exit EBITDA multiple approach</t>
-        </is>
-      </c>
-      <c r="F35" s="93" t="n"/>
-      <c r="G35" s="93" t="n"/>
-      <c r="H35" s="93" t="n"/>
-      <c r="I35" s="93" t="n"/>
-      <c r="J35" s="93" t="n"/>
-    </row>
-    <row r="36" ht="17.25" customHeight="1" s="244">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Normalized FCFt+1 </t>
-        </is>
-      </c>
-      <c r="C36" s="196" t="n">
-        <v>869.5918666222885</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Terminal year EBITDA</t>
-        </is>
-      </c>
-      <c r="J36" s="140" t="n">
-        <v>1226.874119002437</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Long term growth rate (g)</t>
-        </is>
-      </c>
-      <c r="C37" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Terminal value EBITDA multiple</t>
-        </is>
-      </c>
-      <c r="J37" s="429" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="K37" s="428" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Terminal value </t>
-        </is>
-      </c>
-      <c r="C38" s="140" t="n">
-        <v>12440.11624931017</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Terminal value </t>
-        </is>
-      </c>
-      <c r="J38" s="140" t="n">
-        <v>8956.181068717789</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Present value of terminal value</t>
-        </is>
-      </c>
-      <c r="C39" s="140" t="n">
-        <v>9239.084081566059</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Present value of terminal value</t>
-        </is>
-      </c>
-      <c r="J39" s="140" t="n">
-        <v>6651.618705589049</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Present value of stage 1 cash flows</t>
-        </is>
-      </c>
-      <c r="C40" s="140" t="n">
-        <v>3144.125005279505</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Present value of stage 1 cash flows</t>
-        </is>
-      </c>
-      <c r="J40" s="140" t="n">
-        <v>3144.125005279505</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="383" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enterprise value </t>
-        </is>
-      </c>
-      <c r="C41" s="57" t="n">
-        <v>12383.20908684557</v>
-      </c>
-      <c r="E41" s="383" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enterprise value </t>
-        </is>
-      </c>
-      <c r="J41" s="57" t="n">
-        <v>9795.743710868554</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="100" t="inlineStr">
-        <is>
-          <t>Implied TV exit EBITDA multiple</t>
-        </is>
-      </c>
-      <c r="C42" s="533" t="n">
-        <v>10.13968430553018</v>
-      </c>
-      <c r="E42" s="100" t="inlineStr">
-        <is>
-          <t>Implied TV perpetual growth rate</t>
-        </is>
-      </c>
-      <c r="F42" s="100" t="n"/>
-      <c r="G42" s="100" t="n"/>
-      <c r="H42" s="100" t="n"/>
-      <c r="I42" s="100" t="n"/>
-      <c r="J42" s="458" t="n">
-        <v>-0.02719181716452775</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" s="57" t="n"/>
-      <c r="J43" s="435" t="n"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1" s="244" thickBot="1">
-      <c r="B44" s="63" t="inlineStr">
-        <is>
-          <t>Net Debt</t>
-        </is>
-      </c>
-      <c r="C44" s="93" t="n"/>
-      <c r="E44" s="63" t="inlineStr">
-        <is>
-          <t>Fair value per share</t>
-        </is>
-      </c>
-      <c r="F44" s="93" t="n"/>
-      <c r="G44" s="93" t="n"/>
-      <c r="H44" s="93" t="n"/>
-      <c r="I44" s="93" t="n"/>
-      <c r="J44" s="93" t="n"/>
-    </row>
-    <row r="45" ht="17.25" customHeight="1" s="244">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Cash &amp; equivalents ST &amp; LT market. securities</t>
-        </is>
-      </c>
-      <c r="C45" s="162" t="n">
-        <v>179.9999999999991</v>
-      </c>
-      <c r="H45" s="400" t="inlineStr">
-        <is>
-          <t>LBO Offer</t>
-        </is>
-      </c>
-      <c r="I45" s="400" t="inlineStr">
-        <is>
-          <t>Perpetuity</t>
-        </is>
-      </c>
-      <c r="J45" s="400" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Long term debt </t>
-        </is>
-      </c>
-      <c r="C46" s="162" t="n">
-        <v>5190.276000000002</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Enterprise value</t>
-        </is>
-      </c>
-      <c r="H46" s="140" t="n"/>
-      <c r="I46" s="140" t="n">
-        <v>12383.20908684557</v>
-      </c>
-      <c r="J46" s="140" t="n">
-        <v>9795.743710868554</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="383" t="inlineStr">
-        <is>
-          <t>Net debt</t>
-        </is>
-      </c>
-      <c r="C47" s="71" t="n">
-        <v>5010.276000000003</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Less: Net debt</t>
-        </is>
-      </c>
-      <c r="I47" s="140" t="n">
-        <v>-5010.276000000003</v>
-      </c>
-      <c r="J47" s="140" t="n">
-        <v>-5010.276000000003</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" s="228" t="n"/>
-      <c r="E48" s="383" t="inlineStr">
-        <is>
-          <t>Equity value</t>
-        </is>
-      </c>
-      <c r="F48" s="383" t="n"/>
-      <c r="G48" s="383" t="n"/>
-      <c r="H48" s="399" t="n">
-        <v>6741.92625</v>
-      </c>
-      <c r="I48" s="57" t="n">
-        <v>7372.933086845563</v>
-      </c>
-      <c r="J48" s="57" t="n">
-        <v>4785.467710868551</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1" s="244" thickBot="1">
-      <c r="B49" s="63" t="inlineStr">
-        <is>
-          <t>Cost of capital assumptions</t>
-        </is>
-      </c>
-      <c r="C49" s="93" t="n"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Diluted shares</t>
-        </is>
-      </c>
-      <c r="H49" s="529" t="n">
-        <v>145.7713783783784</v>
-      </c>
-      <c r="I49" s="534" t="n">
-        <v>145.7713783783784</v>
-      </c>
-      <c r="J49" s="534" t="n">
-        <v>145.7713783783784</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="76" t="inlineStr">
-        <is>
-          <t>Cost of debt</t>
-        </is>
-      </c>
-      <c r="C50" s="535" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E50" s="383" t="inlineStr">
-        <is>
-          <t>Equity value per share</t>
-        </is>
-      </c>
-      <c r="H50" s="536" t="n">
-        <v>46.25</v>
-      </c>
-      <c r="I50" s="536" t="n">
-        <v>50.57874302119625</v>
-      </c>
-      <c r="J50" s="536" t="n">
-        <v>32.82858242889715</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Tax rate</t>
-        </is>
-      </c>
-      <c r="C51" s="435" t="n">
-        <v>0.2264547791540078</v>
-      </c>
-      <c r="E51" s="100" t="inlineStr">
-        <is>
-          <t>Premium (discount) to LBO offer</t>
-        </is>
-      </c>
-      <c r="H51" s="537" t="inlineStr">
-        <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="I51" s="435" t="n">
-        <v>0.09359444370154035</v>
-      </c>
-      <c r="J51" s="435" t="n">
-        <v>-0.2901928123481697</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Debt and equivalents</t>
-        </is>
-      </c>
-      <c r="C52" s="140" t="n">
-        <v>5010.276000000003</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Debt as a % of total capital </t>
-        </is>
-      </c>
-      <c r="C53" s="538" t="n">
-        <v>0.7748616857223557</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Risk free rate</t>
-        </is>
-      </c>
-      <c r="C55" s="431" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="C56" s="135" t="n">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Market risk premium</t>
-        </is>
-      </c>
-      <c r="C57" s="431" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Equity as % of total capital structure </t>
-        </is>
-      </c>
-      <c r="C58" s="435" t="n">
-        <v>0.2251383142776443</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Cost of capital (WACC)</t>
-        </is>
-      </c>
-      <c r="C59" s="435" t="n">
-        <v>0.06990222994664612</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1" s="244" thickBot="1">
-      <c r="B61" s="63" t="inlineStr">
-        <is>
-          <t>Sensitivity analysis</t>
-        </is>
-      </c>
-      <c r="C61" s="93" t="n"/>
-      <c r="D61" s="93" t="n"/>
-      <c r="E61" s="93" t="n"/>
-      <c r="F61" s="93" t="n"/>
-      <c r="G61" s="93" t="n"/>
-      <c r="H61" s="93" t="n"/>
-    </row>
-    <row r="62">
-      <c r="B62" s="383" t="n"/>
-    </row>
-    <row r="63" ht="17.25" customHeight="1" s="244">
-      <c r="B63" s="383" t="n"/>
-      <c r="C63" s="112" t="inlineStr">
-        <is>
-          <t>Equity value per share</t>
-        </is>
-      </c>
-      <c r="D63" s="112" t="n"/>
-      <c r="E63" s="112" t="n"/>
-      <c r="F63" s="112" t="n"/>
-      <c r="G63" s="112" t="n"/>
-      <c r="H63" s="112" t="n"/>
-    </row>
-    <row r="64">
-      <c r="C64" s="73" t="n"/>
-      <c r="D64" s="290" t="inlineStr">
-        <is>
-          <t>Long term growth rate (g):</t>
-        </is>
-      </c>
-      <c r="E64" s="290" t="n"/>
-      <c r="F64" s="290" t="n"/>
-      <c r="G64" s="290" t="n"/>
-      <c r="H64" s="290" t="n"/>
-    </row>
-    <row r="65">
-      <c r="B65" s="378" t="n"/>
-      <c r="C65" s="539" t="n">
-        <v>50.57874302119625</v>
-      </c>
-      <c r="D65" s="540" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E65" s="541" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F65" s="542" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G65" s="541" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="H65" s="543" t="n">
-        <v>0.03999999999999999</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="C66" s="117" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="D66" s="544" t="n">
-        <v>16.21484649892585</v>
-      </c>
-      <c r="E66" s="544" t="n">
-        <v>17.72262878709584</v>
-      </c>
-      <c r="F66" s="544" t="n">
-        <v>19.38118930408283</v>
-      </c>
-      <c r="G66" s="544" t="n">
-        <v>21.21433513864741</v>
-      </c>
-      <c r="H66" s="544" t="n">
-        <v>23.25116384371916</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="C67" s="118" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D67" s="544" t="n">
-        <v>21.17084407877228</v>
-      </c>
-      <c r="E67" s="544" t="n">
-        <v>23.07715436501025</v>
-      </c>
-      <c r="F67" s="544" t="n">
-        <v>25.19527690527467</v>
-      </c>
-      <c r="G67" s="544" t="n">
-        <v>27.562590332629</v>
-      </c>
-      <c r="H67" s="544" t="n">
-        <v>30.22581793840264</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="378" t="inlineStr">
-        <is>
-          <t>WACC:</t>
-        </is>
-      </c>
-      <c r="C68" s="118" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="D68" s="544" t="n">
-        <v>27.23096234006731</v>
-      </c>
-      <c r="E68" s="544" t="n">
-        <v>29.69362414158428</v>
-      </c>
-      <c r="F68" s="544" t="n">
-        <v>32.46411866829089</v>
-      </c>
-      <c r="G68" s="544" t="n">
-        <v>35.60401246522503</v>
-      </c>
-      <c r="H68" s="544" t="n">
-        <v>39.19246251886405</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="C69" s="118" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D69" s="544" t="n">
-        <v>34.80938263855841</v>
-      </c>
-      <c r="E69" s="544" t="n">
-        <v>38.07690951359217</v>
-      </c>
-      <c r="F69" s="544" t="n">
-        <v>41.81122594220219</v>
-      </c>
-      <c r="G69" s="544" t="n">
-        <v>46.12005259059837</v>
-      </c>
-      <c r="H69" s="544" t="n">
-        <v>51.14701701372724</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="C70" s="118" t="n">
-        <v>0.09000000000000002</v>
-      </c>
-      <c r="D70" s="544" t="n">
-        <v>44.55696853151758</v>
-      </c>
-      <c r="E70" s="544" t="n">
-        <v>49.04257596668177</v>
-      </c>
-      <c r="F70" s="544" t="n">
-        <v>54.27578464103998</v>
-      </c>
-      <c r="G70" s="544" t="n">
-        <v>60.46048580164512</v>
-      </c>
-      <c r="H70" s="544" t="n">
-        <v>67.88212719437132</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="C71" s="119" t="n">
-        <v>0.08000000000000003</v>
-      </c>
-      <c r="D71" s="544" t="n">
-        <v>57.55850136891461</v>
-      </c>
-      <c r="E71" s="544" t="n">
-        <v>63.99933238889363</v>
-      </c>
-      <c r="F71" s="544" t="n">
-        <v>71.72832961286849</v>
-      </c>
-      <c r="G71" s="544" t="n">
-        <v>81.17488177550437</v>
-      </c>
-      <c r="H71" s="544" t="n">
-        <v>92.98307197879927</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="D72" s="544" t="n"/>
-      <c r="E72" s="544" t="n"/>
-      <c r="F72" s="544" t="n"/>
-      <c r="G72" s="544" t="n"/>
-      <c r="H72" s="544" t="n"/>
-    </row>
-    <row r="73" ht="17.25" customHeight="1" s="244">
-      <c r="C73" s="112" t="inlineStr">
-        <is>
-          <t>Equity value per share</t>
-        </is>
-      </c>
-      <c r="D73" s="112" t="n"/>
-      <c r="E73" s="112" t="n"/>
-      <c r="F73" s="112" t="n"/>
-      <c r="G73" s="112" t="n"/>
-      <c r="H73" s="112" t="n"/>
-    </row>
-    <row r="74">
-      <c r="D74" s="290" t="inlineStr">
-        <is>
-          <t>Exit EBITDA Multiple</t>
-        </is>
-      </c>
-      <c r="E74" s="290" t="n"/>
-      <c r="F74" s="290" t="n"/>
-      <c r="G74" s="290" t="n"/>
-      <c r="H74" s="290" t="n"/>
-    </row>
-    <row r="75">
-      <c r="C75" s="545" t="n">
-        <v>32.82858242889715</v>
-      </c>
-      <c r="D75" s="546" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E75" s="546" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F75" s="547" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="G75" s="546" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H75" s="548" t="n">
-        <v>8.300000000000001</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="C76" s="123" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="D76" s="544" t="n">
-        <v>15.50961852638511</v>
-      </c>
-      <c r="E76" s="544" t="n">
-        <v>17.96661853265726</v>
-      </c>
-      <c r="F76" s="544" t="n">
-        <v>20.4236185389294</v>
-      </c>
-      <c r="G76" s="544" t="n">
-        <v>22.88061854520155</v>
-      </c>
-      <c r="H76" s="544" t="n">
-        <v>25.33761855147371</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="C77" s="124" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D77" s="544" t="n">
-        <v>17.14475130521146</v>
-      </c>
-      <c r="E77" s="544" t="n">
-        <v>19.69981500877978</v>
-      </c>
-      <c r="F77" s="544" t="n">
-        <v>22.25487871234807</v>
-      </c>
-      <c r="G77" s="544" t="n">
-        <v>24.80994241591637</v>
-      </c>
-      <c r="H77" s="544" t="n">
-        <v>27.36500611948468</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="378" t="inlineStr">
-        <is>
-          <t>WACC:</t>
-        </is>
-      </c>
-      <c r="C78" s="124" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="D78" s="544" t="n">
-        <v>18.85618541009948</v>
-      </c>
-      <c r="E78" s="544" t="n">
-        <v>21.51415951294241</v>
-      </c>
-      <c r="F78" s="544" t="n">
-        <v>24.17213361578533</v>
-      </c>
-      <c r="G78" s="544" t="n">
-        <v>26.83010771862826</v>
-      </c>
-      <c r="H78" s="544" t="n">
-        <v>29.48808182147118</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="C79" s="124" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D79" s="544" t="n">
-        <v>20.64830251596892</v>
-      </c>
-      <c r="E79" s="544" t="n">
-        <v>23.41432021461313</v>
-      </c>
-      <c r="F79" s="544" t="n">
-        <v>26.18033791325734</v>
-      </c>
-      <c r="G79" s="544" t="n">
-        <v>28.94635561190155</v>
-      </c>
-      <c r="H79" s="544" t="n">
-        <v>31.71237331054576</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="C80" s="124" t="n">
-        <v>0.09000000000000002</v>
-      </c>
-      <c r="D80" s="544" t="n">
-        <v>22.52578129267701</v>
-      </c>
-      <c r="E80" s="544" t="n">
-        <v>25.40528204016064</v>
-      </c>
-      <c r="F80" s="544" t="n">
-        <v>28.28478278764427</v>
-      </c>
-      <c r="G80" s="544" t="n">
-        <v>31.16428353512789</v>
-      </c>
-      <c r="H80" s="544" t="n">
-        <v>34.04378428261153</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="C81" s="125" t="n">
-        <v>0.08000000000000003</v>
-      </c>
-      <c r="D81" s="544" t="n">
-        <v>24.49362060261981</v>
-      </c>
-      <c r="E81" s="544" t="n">
-        <v>27.49237143226065</v>
-      </c>
-      <c r="F81" s="544" t="n">
-        <v>30.49112226190149</v>
-      </c>
-      <c r="G81" s="544" t="n">
-        <v>33.48987309154233</v>
-      </c>
-      <c r="H81" s="544" t="n">
-        <v>36.4886239211832</v>
-      </c>
-    </row>
-    <row r="83" ht="17.25" customHeight="1" s="244">
-      <c r="C83" s="112" t="inlineStr">
-        <is>
-          <t>Equity value per share</t>
-        </is>
-      </c>
-      <c r="D83" s="112" t="n"/>
-      <c r="E83" s="112" t="n"/>
-      <c r="F83" s="112" t="n"/>
-      <c r="G83" s="112" t="n"/>
-      <c r="H83" s="112" t="n"/>
-    </row>
-    <row r="84">
-      <c r="D84" s="290" t="inlineStr">
-        <is>
-          <t>Exit EBITDA Multiple</t>
-        </is>
-      </c>
-      <c r="E84" s="290" t="n"/>
-      <c r="F84" s="290" t="n"/>
-      <c r="G84" s="290" t="n"/>
-      <c r="H84" s="290" t="n"/>
-    </row>
-    <row r="85">
-      <c r="C85" s="195" t="inlineStr">
-        <is>
-          <t>EBITDA % of plan</t>
-        </is>
-      </c>
-      <c r="D85" s="549" t="n">
-        <v>32.82858242889715</v>
-      </c>
-      <c r="E85" s="550" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="F85" s="546" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="G85" s="547" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H85" s="548" t="n">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="C86" s="132" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D86" s="127" t="n">
-        <v>981.7144138269495</v>
-      </c>
-      <c r="E86" s="544" t="n">
-        <v>47.84757390464826</v>
-      </c>
-      <c r="F86" s="544" t="n">
-        <v>49.91146747628064</v>
-      </c>
-      <c r="G86" s="544" t="n">
-        <v>51.97536104791303</v>
-      </c>
-      <c r="H86" s="544" t="n">
-        <v>54.03925461954542</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="C87" s="133" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D87" s="128" t="n">
-        <v>1104.428715555318</v>
-      </c>
-      <c r="E87" s="544" t="n">
-        <v>51.09820627996928</v>
-      </c>
-      <c r="F87" s="544" t="n">
-        <v>53.42008654805571</v>
-      </c>
-      <c r="G87" s="544" t="n">
-        <v>55.74196681614215</v>
-      </c>
-      <c r="H87" s="544" t="n">
-        <v>58.06384708422858</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="C88" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" s="129" t="n">
-        <v>1227.143017283687</v>
-      </c>
-      <c r="E88" s="544" t="n">
-        <v>54.34883865529027</v>
-      </c>
-      <c r="F88" s="544" t="n">
-        <v>56.92870561983077</v>
-      </c>
-      <c r="G88" s="544" t="n">
-        <v>59.50857258437125</v>
-      </c>
-      <c r="H88" s="544" t="n">
-        <v>62.08843954891173</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="C89" s="133" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D89" s="128" t="n">
-        <v>1349.857319012056</v>
-      </c>
-      <c r="E89" s="544" t="n">
-        <v>57.59947103061128</v>
-      </c>
-      <c r="F89" s="544" t="n">
-        <v>60.43732469160583</v>
-      </c>
-      <c r="G89" s="544" t="n">
-        <v>63.27517835260036</v>
-      </c>
-      <c r="H89" s="544" t="n">
-        <v>66.1130320135949</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="C90" s="133" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D90" s="128" t="n">
-        <v>1472.571620740424</v>
-      </c>
-      <c r="E90" s="544" t="n">
-        <v>60.85010340593232</v>
-      </c>
-      <c r="F90" s="544" t="n">
-        <v>63.9459437633809</v>
-      </c>
-      <c r="G90" s="544" t="n">
-        <v>67.04178412082949</v>
-      </c>
-      <c r="H90" s="544" t="n">
-        <v>70.13762447827806</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="C91" s="133" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D91" s="130" t="n">
-        <v>1595.285922468793</v>
-      </c>
-      <c r="E91" s="544" t="n">
-        <v>1472.571620740424</v>
-      </c>
-      <c r="F91" s="544" t="n">
-        <v>1472.571620740424</v>
-      </c>
-      <c r="G91" s="544" t="n">
-        <v>1472.571620740424</v>
-      </c>
-      <c r="H91" s="544" t="n">
-        <v>1472.571620740424</v>
-      </c>
-    </row>
-    <row r="93" ht="15.75" customHeight="1" s="244" thickBot="1">
-      <c r="B93" s="63" t="inlineStr">
-        <is>
-          <t>Football field</t>
-        </is>
-      </c>
-      <c r="C93" s="93" t="n"/>
-      <c r="D93" s="93" t="n"/>
-      <c r="E93" s="93" t="n"/>
-    </row>
-    <row r="114">
-      <c r="B114" s="108" t="n"/>
-      <c r="C114" s="109" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D114" s="109" t="inlineStr">
-        <is>
-          <t>Diff.</t>
-        </is>
-      </c>
-      <c r="E114" s="110" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="105" t="inlineStr">
-        <is>
-          <t>DCF Value at 6.3x-8.3x Exit EBITDA Range</t>
-        </is>
-      </c>
-      <c r="C115" s="544" t="n">
-        <v>20.64830251596892</v>
-      </c>
-      <c r="D115" s="544" t="n">
-        <v>11.06407079457684</v>
-      </c>
-      <c r="E115" s="551" t="n">
-        <v>31.71237331054576</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="B116" s="102" t="inlineStr">
-        <is>
-          <t>DCF Value at 2.0%-4.0% Perpetuity Range</t>
-        </is>
-      </c>
-      <c r="C116" s="544" t="n">
-        <v>34.80938263855841</v>
-      </c>
-      <c r="D116" s="544" t="n">
-        <v>16.33763437516883</v>
-      </c>
-      <c r="E116" s="551" t="n">
-        <v>51.14701701372724</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="B117" s="102" t="inlineStr">
-        <is>
-          <t>LBO Value at 15.0%-35.0% Sponsor Hurdle Rate</t>
-        </is>
-      </c>
-      <c r="C117" s="544" t="n">
-        <v>45.45104265824024</v>
-      </c>
-      <c r="D117" s="544" t="n">
-        <v>13.0196839013479</v>
-      </c>
-      <c r="E117" s="551" t="n">
-        <v>58.47072655958814</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" s="106" t="inlineStr">
-        <is>
-          <t>52 Week Market High/Low</t>
-        </is>
-      </c>
-      <c r="C118" s="552" t="n">
-        <v>37.51</v>
-      </c>
-      <c r="D118" s="552" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="E118" s="553" t="n">
-        <v>46.33</v>
+      <c r="E28" s="301" t="n">
+        <v>10.7</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D66:H71">
-    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
-      <formula>$C$6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D76:H81">
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
-      <formula>$C$6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E86:H91">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
-      <formula>$C$6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation sqref="C31" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"End of period,Middle of period"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -7181,312 +5505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="1.7109375" customWidth="1" style="244" min="1" max="1"/>
-    <col width="36.5703125" bestFit="1" customWidth="1" style="244" min="2" max="2"/>
-    <col width="15.85546875" customWidth="1" style="244" min="3" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="244" thickBot="1"/>
-    <row r="2" ht="27" customHeight="1" s="244" thickBot="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Diluted shares for BMC</t>
-        </is>
-      </c>
-      <c r="C2" s="305" t="n"/>
-      <c r="D2" s="305" t="n"/>
-      <c r="E2" s="305" t="n"/>
-    </row>
-    <row r="3">
-      <c r="B3" s="302" t="inlineStr">
-        <is>
-          <t>$ mm except per share</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="34" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="34" t="inlineStr">
-        <is>
-          <t>Offer price</t>
-        </is>
-      </c>
-      <c r="E5" s="513" t="n">
-        <v>46.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="304" t="inlineStr">
-        <is>
-          <t>Model-derived offer value sanity check</t>
-        </is>
-      </c>
-      <c r="E6" s="554" t="n">
-        <v>46.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="159" t="inlineStr">
-        <is>
-          <t>Basic shares outstanding (latest filing)</t>
-        </is>
-      </c>
-      <c r="E7" s="522" t="n">
-        <v>143.973</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="34" t="inlineStr">
-        <is>
-          <t>In-the-money exercisable options</t>
-        </is>
-      </c>
-      <c r="E8" s="521" t="n">
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>Total proceeds ($mm)</t>
-        </is>
-      </c>
-      <c r="E9" s="461" t="n">
-        <v>411.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="34" t="inlineStr">
-        <is>
-          <t>Total shares repurchased (mm)</t>
-        </is>
-      </c>
-      <c r="E10" s="461" t="n">
-        <v>8.901621621621622</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>Net dilutive options</t>
-        </is>
-      </c>
-      <c r="E11" s="461" t="n">
-        <v>1.798378378378377</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dilutive impact of shares from other securities </t>
-        </is>
-      </c>
-      <c r="E12" s="522" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="34" t="n"/>
-      <c r="E13" s="522" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="147" t="inlineStr">
-        <is>
-          <t>Net diluted shares outstanding</t>
-        </is>
-      </c>
-      <c r="D14" s="434" t="n"/>
-      <c r="E14" s="461" t="n">
-        <v>145.7713783783784</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="147" t="n"/>
-      <c r="D15" s="434" t="n"/>
-      <c r="E15" s="461" t="n"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="312" t="inlineStr">
-        <is>
-          <t>Options outstanding</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="445" t="n"/>
-      <c r="E16" s="518" t="n"/>
-    </row>
-    <row r="17">
-      <c r="C17" s="242" t="inlineStr">
-        <is>
-          <t>Out. shares</t>
-        </is>
-      </c>
-      <c r="D17" s="242" t="inlineStr">
-        <is>
-          <t>Exercise price</t>
-        </is>
-      </c>
-      <c r="E17" s="242" t="inlineStr">
-        <is>
-          <t>In-the-$-shares</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="555" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="298" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D18" s="298" t="n">
-        <v>15</v>
-      </c>
-      <c r="E18" s="299" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="555" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" s="298" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D19" s="298" t="n">
-        <v>18</v>
-      </c>
-      <c r="E19" s="299" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="555" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" s="298" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D20" s="298" t="n">
-        <v>22</v>
-      </c>
-      <c r="E20" s="299" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="555" t="n">
-        <v>4</v>
-      </c>
-      <c r="C21" s="298" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D21" s="298" t="n">
-        <v>28</v>
-      </c>
-      <c r="E21" s="299" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="555" t="n">
-        <v>5</v>
-      </c>
-      <c r="C22" s="298" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D22" s="298" t="n">
-        <v>32</v>
-      </c>
-      <c r="E22" s="299" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="555" t="n">
-        <v>6</v>
-      </c>
-      <c r="C23" s="298" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D23" s="298" t="n">
-        <v>36</v>
-      </c>
-      <c r="E23" s="299" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="555" t="n">
-        <v>7</v>
-      </c>
-      <c r="C24" s="298" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D24" s="298" t="n">
-        <v>39</v>
-      </c>
-      <c r="E24" s="299" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="555" t="n">
-        <v>8</v>
-      </c>
-      <c r="C25" s="298" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="D25" s="298" t="n">
-        <v>42</v>
-      </c>
-      <c r="E25" s="299" t="n">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="555" t="n">
-        <v>9</v>
-      </c>
-      <c r="C26" s="298" t="n"/>
-      <c r="D26" s="298" t="n"/>
-      <c r="E26" s="299" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="555" t="n">
-        <v>10</v>
-      </c>
-      <c r="C27" s="298" t="n"/>
-      <c r="D27" s="298" t="n"/>
-      <c r="E27" s="300" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="E28" s="301" t="n">
-        <v>10.7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A2:F268"/>
+  <dimension ref="A1:F268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19.42578125" bestFit="1" customWidth="1" style="244" min="1" max="1"/>
@@ -7495,6 +5514,7 @@
     <col width="9.28515625" bestFit="1" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="18" customHeight="1" s="244" thickBot="1">
       <c r="A2" s="101" t="inlineStr">
         <is>
@@ -7507,6 +5527,7 @@
       <c r="E2" s="93" t="n"/>
       <c r="F2" s="93" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -7527,6 +5548,7 @@
         <v>37.51</v>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -12790,298 +10812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="32" customWidth="1" style="244" min="2" max="2"/>
-    <col width="14" customWidth="1" style="244" min="3" max="3"/>
-    <col width="14" customWidth="1" style="244" min="4" max="4"/>
-    <col width="14" customWidth="1" style="244" min="5" max="5"/>
-    <col width="70" customWidth="1" style="244" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="563" t="inlineStr">
-        <is>
-          <t>vengeanceaiUSC-LBOMODEL2 — Strategy Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AI-SDR cost takeout drives margin, FCF, debt paydown, MOIC/IRR — exit multiple held at 13x in both cases</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="564" t="inlineStr">
-        <is>
-          <t>RESULTS — AI vs Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="412" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="C6" s="412" t="inlineStr">
-        <is>
-          <t>Base (no AI)</t>
-        </is>
-      </c>
-      <c r="D6" s="412" t="inlineStr">
-        <is>
-          <t>AI-SDR case</t>
-        </is>
-      </c>
-      <c r="E6" s="412" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-      <c r="F6" s="412" t="inlineStr">
-        <is>
-          <t>COMMENTARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1" s="244">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Y2 EBITDA margin</t>
-        </is>
-      </c>
-      <c r="C7" s="565" t="n">
-        <v>0.1085118998600017</v>
-      </c>
-      <c r="D7" s="565" t="n">
-        <v>0.2012029241075531</v>
-      </c>
-      <c r="E7" s="565" t="n">
-        <v>0.09269102424755141</v>
-      </c>
-      <c r="F7" s="566" t="inlineStr">
-        <is>
-          <t>Year 2 operating profitability under 10% growth / 80% GM / AI S&amp;M path.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1" s="244">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Y2 margin vs baseline (bps)</t>
-        </is>
-      </c>
-      <c r="C8" s="567" t="n">
-        <v>-422.7456147574727</v>
-      </c>
-      <c r="D8" s="567" t="n">
-        <v>504.1646277180415</v>
-      </c>
-      <c r="E8" s="567" t="n">
-        <v>926.9102424755141</v>
-      </c>
-      <c r="F8" s="566" t="inlineStr">
-        <is>
-          <t>Y2 EBITDA margin minus FY24 baseline margin, in basis points (target ≥500).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1" s="244">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Y5 EBITDA ($m)</t>
-        </is>
-      </c>
-      <c r="C9" s="567" t="n">
-        <v>212.2104606600003</v>
-      </c>
-      <c r="D9" s="567" t="n">
-        <v>496.3963076296004</v>
-      </c>
-      <c r="E9" s="567" t="n">
-        <v>284.1858469696001</v>
-      </c>
-      <c r="F9" s="566" t="inlineStr">
-        <is>
-          <t>Year 5 EBITDA ($m).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1" s="244">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Exit EV @ 13x ($m)</t>
-        </is>
-      </c>
-      <c r="C10" s="567" t="n">
-        <v>2758.735988580003</v>
-      </c>
-      <c r="D10" s="567" t="n">
-        <v>6453.151999184804</v>
-      </c>
-      <c r="E10" s="567" t="n">
-        <v>3694.416010604801</v>
-      </c>
-      <c r="F10" s="566" t="inlineStr">
-        <is>
-          <t>Exit EV = Y5 EBITDA × 13x (Assumptions_Drivers!C20 / LBO!D17).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1" s="244">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Exit net debt ($m)</t>
-        </is>
-      </c>
-      <c r="C11" s="567" t="n">
-        <v>557.1124750633038</v>
-      </c>
-      <c r="D11" s="567" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="567" t="n">
-        <v>-557.1124750633038</v>
-      </c>
-      <c r="F11" s="566" t="inlineStr">
-        <is>
-          <t>Ending net debt after mandatory amort + 100% cash sweep.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1" s="244">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Exit equity value ($m)</t>
-        </is>
-      </c>
-      <c r="C12" s="567" t="n">
-        <v>2201.623513516699</v>
-      </c>
-      <c r="D12" s="567" t="n">
-        <v>6453.151999184804</v>
-      </c>
-      <c r="E12" s="567" t="n">
-        <v>4251.528485668105</v>
-      </c>
-      <c r="F12" s="566" t="inlineStr">
-        <is>
-          <t>Exit equity = Exit EV − ending debt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" s="244">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="C13" s="568" t="n">
-        <v>1.17652754423803</v>
-      </c>
-      <c r="D13" s="568" t="n">
-        <v>3.448505626681045</v>
-      </c>
-      <c r="E13" s="568" t="n">
-        <v>2.271978082443015</v>
-      </c>
-      <c r="F13" s="566" t="inlineStr">
-        <is>
-          <t>MOIC = Exit equity / sponsor equity check.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1" s="244">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>IRR (5-year)</t>
-        </is>
-      </c>
-      <c r="C14" s="565" t="n">
-        <v>0.03304780632992022</v>
-      </c>
-      <c r="D14" s="565" t="n">
-        <v>0.2809323319237782</v>
-      </c>
-      <c r="E14" s="565" t="n">
-        <v>0.247884525593858</v>
-      </c>
-      <c r="F14" s="566" t="inlineStr">
-        <is>
-          <t>IRR over 5 years = MOIC^(1/5) − 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="569" t="inlineStr">
-        <is>
-          <t>IRR uplift from AI S&amp;M: 24.8 percentage points | Y2 margin expansion: 504 bps (target ≥500: YES)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PDF assumptions list:</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="570" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>In-Excel full commentary: 00_Assumptions_List | Drivers: Assumptions_Drivers</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>AI $15m cost evidence (LBOMODEL2):</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="590" t="inlineStr">
-        <is>
-          <t>Go to AI_Cost_Sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="590" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_AI_COST_SOURCES.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId3"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:M31"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4" customWidth="1" style="244" min="2" max="2"/>
@@ -13098,6 +10829,7 @@
     <col width="70" customWidth="1" style="244" min="13" max="13"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -13119,6 +10851,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="557" t="inlineStr">
         <is>
@@ -13477,7 +11210,7 @@
       </c>
       <c r="M11" s="573" t="inlineStr">
         <is>
-          <t>A new fixed fifteen million dollar expense was added. We included this vital change to cover enterprise software licenses, API usage limits, and compute power running the AI. SOURCE (LBOMODEL2): $15m triangulated from Salesforce Agentforce public pricing ($2/conversation; Flex Credits ~$0.10/action) and ZoomInfo 10-K S&amp;M headcount (1,513). Full math + clickable links: sheet AI_Cost_Sources. Primary link: https://www.salesforce.com/news/press-releases/2025/05/15/agentforce-flexible-pricing-news/</t>
+          <t>A new fixed fifteen million dollar expense was added. We included this vital change to cover enterprise software licenses, API usage limits, and compute power running the AI. SOURCE (LBOMODEL2): $15m triangulated from Salesforce Agentforce public pricing ($2/conversation; Flex Credits ~$0.10/action) and ZoomInfo 10-K S&amp;M headcount (1,513). Full math + clickable links: sheet Assumptions_Drivers (cols E–G). Primary link: https://www.salesforce.com/news/press-releases/2025/05/15/agentforce-flexible-pricing-news/</t>
         </is>
       </c>
     </row>
@@ -14081,6 +11814,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="B23" s="564" t="inlineStr">
         <is>
@@ -14096,6 +11830,7 @@
       </c>
     </row>
     <row r="25"/>
+    <row r="26"/>
     <row r="27">
       <c r="B27" s="564" t="inlineStr">
         <is>
@@ -14106,7 +11841,7 @@
     <row r="28">
       <c r="B28" s="590" t="inlineStr">
         <is>
-          <t>Go to AI_Cost_Sources (in-workbook evidence)</t>
+          <t>Go to Assumptions_Drivers (cols E–G) (in-workbook evidence)</t>
         </is>
       </c>
     </row>
@@ -14128,6 +11863,49 @@
       <c r="B31" s="590" t="inlineStr">
         <is>
           <t>PDF: LBOMODEL2_AI_COST_SOURCES.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="B33" s="564" t="inlineStr">
+        <is>
+          <t>SOURCE MAP: open Assumptions_Drivers — columns E (link), F (~30-word justification), G (secondary link) on each driver row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="593" t="inlineStr">
+        <is>
+          <t>Jump to AI infra source row (E9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="593" t="inlineStr">
+        <is>
+          <t>PDF: all driver sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="564" t="inlineStr">
+        <is>
+          <t>SOURCE MAP: open Assumptions_Drivers — columns E (link), F (~30-word justification), G (secondary link) on each driver row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="593" t="inlineStr">
+        <is>
+          <t>Jump to AI infra source row (E9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="593" t="inlineStr">
+        <is>
+          <t>PDF: all driver sources</t>
         </is>
       </c>
     </row>
@@ -14172,6 +11950,804 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId39"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="32" customWidth="1" style="244" min="2" max="2"/>
+    <col width="12" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="42" customWidth="1" style="244" min="5" max="5"/>
+    <col width="62" customWidth="1" style="244" min="6" max="6"/>
+    <col width="42" customWidth="1" style="244" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="563" t="inlineStr">
+        <is>
+          <t>Assumptions Drivers — yellow inputs + SOURCE LINK + justification on each row</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" s="244">
+      <c r="B3" s="574" t="inlineStr">
+        <is>
+          <t>Every driver has a reputable public source URL (col E) and ~30 words on credibility / why the number is reasonable (col F). Optional second source in col G. No separate sources tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1" s="244">
+      <c r="B4" s="586" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="C4" s="586" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D4" s="586" t="inlineStr">
+        <is>
+          <t>Feeds</t>
+        </is>
+      </c>
+      <c r="E4" s="586" t="inlineStr">
+        <is>
+          <t>Source link (click)</t>
+        </is>
+      </c>
+      <c r="F4" s="586" t="inlineStr">
+        <is>
+          <t>Why this number is reasonable (~30 words)</t>
+        </is>
+      </c>
+      <c r="G4" s="586" t="inlineStr">
+        <is>
+          <t>Secondary source (click)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1" s="244">
+      <c r="B5" s="575" t="inlineStr">
+        <is>
+          <t>Revenue growth</t>
+        </is>
+      </c>
+      <c r="C5" s="422" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="575" t="inlineStr">
+        <is>
+          <t>AI_Operating!C5:G5</t>
+        </is>
+      </c>
+      <c r="E5" s="593" t="inlineStr">
+        <is>
+          <t>ZoomInfo FY2024 results (BusinessWire)</t>
+        </is>
+      </c>
+      <c r="F5" s="573" t="inlineStr">
+        <is>
+          <t>ZI FY24 revenue fell ~2%, so 10% is a forward recovery/LBO underwrite—not trailing actual. Held constant in AI vs Base so IRR uplift comes from cost takeout, not inflated top-line.</t>
+        </is>
+      </c>
+      <c r="G5" s="593" t="inlineStr">
+        <is>
+          <t>valueaddvc.com/blog/saas-evebitda-multiples-explained-benchm</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="575" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="C6" s="422" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D6" s="575" t="inlineStr">
+        <is>
+          <t>AI_Operating COGS row</t>
+        </is>
+      </c>
+      <c r="E6" s="593" t="inlineStr">
+        <is>
+          <t>Aleph/Benchmarkit SaaS GM median ~80%</t>
+        </is>
+      </c>
+      <c r="F6" s="573" t="inlineStr">
+        <is>
+          <t>2025 software median gross margin is ~80% (Aleph×Benchmarkit). ZI already prints ~84% GAAP GM; using 80% is a conservative SaaS benchmark, not an aggressive stretch.</t>
+        </is>
+      </c>
+      <c r="G6" s="593" t="inlineStr">
+        <is>
+          <t>www.readyratios.com/sec/GTM_zoominfo-technologies-inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="244">
+      <c r="B7" s="575" t="inlineStr">
+        <is>
+          <t>Sales payroll cut (Y1)</t>
+        </is>
+      </c>
+      <c r="C7" s="422" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D7" s="575" t="inlineStr">
+        <is>
+          <t>AI_Operating S&amp;M Y1</t>
+        </is>
+      </c>
+      <c r="E7" s="593" t="inlineStr">
+        <is>
+          <t>AI SDR vs human SDR cost/meeting</t>
+        </is>
+      </c>
+      <c r="F7" s="573" t="inlineStr">
+        <is>
+          <t>Published outbound math: fully loaded human SDRs ~$110–150k vs much cheaper AI stacks. Cutting human sales payroll 15% in Y1 is a modest slice of ZI’s 1,513 S&amp;M headcount.</t>
+        </is>
+      </c>
+      <c r="G7" s="593" t="inlineStr">
+        <is>
+          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="244">
+      <c r="B8" s="575" t="inlineStr">
+        <is>
+          <t>Variable commission cut</t>
+        </is>
+      </c>
+      <c r="C8" s="422" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D8" s="575" t="inlineStr">
+        <is>
+          <t>AI_Operating Commissions</t>
+        </is>
+      </c>
+      <c r="E8" s="593" t="inlineStr">
+        <is>
+          <t>SDR pay mix ~70/30 base/variable</t>
+        </is>
+      </c>
+      <c r="F8" s="573" t="inlineStr">
+        <is>
+          <t>SaaS SDR OTE is typically ~70% base / ~30% variable. Replacing outbound humans with AI logically shrinks the commission pool; −20% is a partial, not full, cut of that variable layer.</t>
+        </is>
+      </c>
+      <c r="G8" s="593" t="inlineStr">
+        <is>
+          <t>syncgtm.com/blog/how-much-do-sales-development-representativ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" s="244">
+      <c r="B9" s="575" t="inlineStr">
+        <is>
+          <t>AI infrastructure ($m)</t>
+        </is>
+      </c>
+      <c r="C9" s="576" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" s="575" t="inlineStr">
+        <is>
+          <t>AI_Operating AI cost</t>
+        </is>
+      </c>
+      <c r="E9" s="593" t="inlineStr">
+        <is>
+          <t>Salesforce Agentforce $2/conv + Flex Credits</t>
+        </is>
+      </c>
+      <c r="F9" s="573" t="inlineStr">
+        <is>
+          <t>SF publishes $2/conversation and ~$0.10/action Flex Credits. At ZI scale (~378 outbound roles at 25% of 1,513 S&amp;M), $5–10k/mo AI agents imply ~$23–45m; $15m is conservative.</t>
+        </is>
+      </c>
+      <c r="G9" s="593" t="inlineStr">
+        <is>
+          <t>highticketaisystems.com/blog/ai-sdr-pricing-explained</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" s="244">
+      <c r="B10" s="575" t="inlineStr">
+        <is>
+          <t>S&amp;M expense growth Y2+</t>
+        </is>
+      </c>
+      <c r="C10" s="422" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D10" s="575" t="inlineStr">
+        <is>
+          <t>AI_Operating S&amp;M Y2+</t>
+        </is>
+      </c>
+      <c r="E10" s="593" t="inlineStr">
+        <is>
+          <t>Gartner: agentic AI scales via inference opex</t>
+        </is>
+      </c>
+      <c r="F10" s="573" t="inlineStr">
+        <is>
+          <t>Once agents replace headcount, S&amp;M opex need not grow with revenue. Cap growth at ~2% (near inflation/maintenance) to model infinite agent scale vs linear human hiring.</t>
+        </is>
+      </c>
+      <c r="G10" s="593" t="inlineStr">
+        <is>
+          <t>www.ciodive.com/news/AI-spending-soars-enterprise-maturity/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" s="244">
+      <c r="B11" s="575" t="inlineStr">
+        <is>
+          <t>G&amp;A % of revenue</t>
+        </is>
+      </c>
+      <c r="C11" s="422" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D11" s="575" t="inlineStr">
+        <is>
+          <t>AI_Operating G&amp;A</t>
+        </is>
+      </c>
+      <c r="E11" s="593" t="inlineStr">
+        <is>
+          <t>ZoomInfo FY24 G&amp;A $295.3m (~24% rev)</t>
+        </is>
+      </c>
+      <c r="F11" s="573" t="inlineStr">
+        <is>
+          <t>ZI FY24 G&amp;A was $295.3m (~24% of $1,214m). We lock ~18% as a leaner but still corporate G&amp;A load; thesis does not touch finance/comp overhead—only the sales floor.</t>
+        </is>
+      </c>
+      <c r="G11" s="593" t="inlineStr">
+        <is>
+          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" s="244">
+      <c r="B12" s="575" t="inlineStr">
+        <is>
+          <t>CapEx reduction vs base</t>
+        </is>
+      </c>
+      <c r="C12" s="422" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D12" s="575" t="inlineStr">
+        <is>
+          <t>FCF CapEx</t>
+        </is>
+      </c>
+      <c r="E12" s="593" t="inlineStr">
+        <is>
+          <t>In-house SDR tooling/laptop stack costs</t>
+        </is>
+      </c>
+      <c r="F12" s="573" t="inlineStr">
+        <is>
+          <t>Human SDR all-in budgets include laptops, seats, and tooling. Terminating outbound humans cuts recurring device/refresh CapEx; −5% vs base CapEx rate is a small, directionally correct haircut.</t>
+        </is>
+      </c>
+      <c r="G12" s="593" t="inlineStr">
+        <is>
+          <t>firstsales.io/blog/cost-per-meeting-outbound/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" s="244">
+      <c r="B13" s="575" t="inlineStr">
+        <is>
+          <t>WC / receivables improvement</t>
+        </is>
+      </c>
+      <c r="C13" s="422" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" s="575" t="inlineStr">
+        <is>
+          <t>FCF ΔNWC</t>
+        </is>
+      </c>
+      <c r="E13" s="593" t="inlineStr">
+        <is>
+          <t>ZI receivables ~80 days (SEC ratios)</t>
+        </is>
+      </c>
+      <c r="F13" s="573" t="inlineStr">
+        <is>
+          <t>ZI receivables turnover ~80 days shows WC is material. Automated billing reminders can shorten DSO; modeling −10% WC intensity vs base is a modest collections improvement, not a wipeout.</t>
+        </is>
+      </c>
+      <c r="G13" s="593" t="inlineStr">
+        <is>
+          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1" s="244">
+      <c r="B14" s="575" t="inlineStr">
+        <is>
+          <t>SOFR</t>
+        </is>
+      </c>
+      <c r="C14" s="577" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="D14" s="575" t="inlineStr">
+        <is>
+          <t>Debt interest</t>
+        </is>
+      </c>
+      <c r="E14" s="593" t="inlineStr">
+        <is>
+          <t>NY Fed official SOFR page</t>
+        </is>
+      </c>
+      <c r="F14" s="573" t="inlineStr">
+        <is>
+          <t>SOFR is the NY Fed’s official overnight Treasury-repo financing benchmark used to price leveraged loans. ~4.3% is a planning level near recent SOFR prints (see also FRED SOFR series).</t>
+        </is>
+      </c>
+      <c r="G14" s="593" t="inlineStr">
+        <is>
+          <t>fred.stlouisfed.org/series/SOFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1" s="244">
+      <c r="B15" s="575" t="inlineStr">
+        <is>
+          <t>Term Loan A spread</t>
+        </is>
+      </c>
+      <c r="C15" s="577" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D15" s="575" t="inlineStr">
+        <is>
+          <t>TLA rate = SOFR+spread</t>
+        </is>
+      </c>
+      <c r="E15" s="593" t="inlineStr">
+        <is>
+          <t>TLA typical SOFR+275–375bps (illustrative)</t>
+        </is>
+      </c>
+      <c r="F15" s="573" t="inlineStr">
+        <is>
+          <t>Bank Term Loan A in LBO structures typically prices tighter than TLB. SOFR+400bps sits at the wider end of published TLA ranges—conservative senior pricing independent of AI ops.</t>
+        </is>
+      </c>
+      <c r="G15" s="593" t="inlineStr">
+        <is>
+          <t>ibinterviewquestions.com/guides/debt-capital-markets/term-lo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1" s="244">
+      <c r="B16" s="575" t="inlineStr">
+        <is>
+          <t>Term Loan B spread</t>
+        </is>
+      </c>
+      <c r="C16" s="577" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D16" s="575" t="inlineStr">
+        <is>
+          <t>TLB rate = SOFR+spread</t>
+        </is>
+      </c>
+      <c r="E16" s="593" t="inlineStr">
+        <is>
+          <t>TLB often SOFR+300–500bps; 1%/yr amort</t>
+        </is>
+      </c>
+      <c r="F16" s="573" t="inlineStr">
+        <is>
+          <t>Institutional TLB commonly prices SOFR+300–500bps. SOFR+500bps is the upper published band—credit-market priced, not changed by internal AI software strategy.</t>
+        </is>
+      </c>
+      <c r="G16" s="593" t="inlineStr">
+        <is>
+          <t>ryanoconnellfinance.com/lbo-debt-structure/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1" s="244">
+      <c r="B17" s="575" t="inlineStr">
+        <is>
+          <t>Mandatory amortization</t>
+        </is>
+      </c>
+      <c r="C17" s="422" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D17" s="575" t="inlineStr">
+        <is>
+          <t>% of initial new debt / yr</t>
+        </is>
+      </c>
+      <c r="E17" s="593" t="inlineStr">
+        <is>
+          <t>Syndicated TLB ~1% annual amort standard</t>
+        </is>
+      </c>
+      <c r="F17" s="573" t="inlineStr">
+        <is>
+          <t>Market-standard institutional TLB schedules ~1% annual amortization with a bullet at maturity. Kept fixed because loan docs—not AI FCF—set the mandatory floor.</t>
+        </is>
+      </c>
+      <c r="G17" s="593" t="inlineStr">
+        <is>
+          <t>clearvaluelending.com/glossary/term-loan-b</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1" s="244">
+      <c r="B18" s="575" t="inlineStr">
+        <is>
+          <t>Cash sweep %</t>
+        </is>
+      </c>
+      <c r="C18" s="422" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="575" t="inlineStr">
+        <is>
+          <t>Debt_Sweep_AI</t>
+        </is>
+      </c>
+      <c r="E18" s="593" t="inlineStr">
+        <is>
+          <t>LBO excess cash / optional prepay practice</t>
+        </is>
+      </c>
+      <c r="F18" s="573" t="inlineStr">
+        <is>
+          <t>Sponsor LBOs typically sweep excess free cash to optional debt prepay after mandatory amort. 100% sweep maximizes deleveraging so AI margin gains show up in MOIC/IRR, not idle cash.</t>
+        </is>
+      </c>
+      <c r="G18" s="593" t="inlineStr">
+        <is>
+          <t>ibinterviewquestions.com/guides/valuation-investment-banking</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1" s="244">
+      <c r="B19" s="575" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="C19" s="422" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D19" s="575" t="inlineStr">
+        <is>
+          <t>NI tax</t>
+        </is>
+      </c>
+      <c r="E19" s="593" t="inlineStr">
+        <is>
+          <t>PwC: US federal corporate rate 21%</t>
+        </is>
+      </c>
+      <c r="F19" s="573" t="inlineStr">
+        <is>
+          <t>US federal corporate income tax is a flat 21% statutory rate (TCJA). Operating-margin gains do not change the federal statutory rate used in the model.</t>
+        </is>
+      </c>
+      <c r="G19" s="593" t="inlineStr">
+        <is>
+          <t>tradingeconomics.com/united-states/corporate-tax-rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1" s="244">
+      <c r="B20" s="575" t="inlineStr">
+        <is>
+          <t>Exit EV/EBITDA multiple</t>
+        </is>
+      </c>
+      <c r="C20" s="584" t="n">
+        <v>13</v>
+      </c>
+      <c r="D20" s="575" t="inlineStr">
+        <is>
+          <t>LBO!D17 / Strategy_Summary</t>
+        </is>
+      </c>
+      <c r="E20" s="593" t="inlineStr">
+        <is>
+          <t>PE SaaS buyouts often ~15–22x EBITDA</t>
+        </is>
+      </c>
+      <c r="F20" s="573" t="inlineStr">
+        <is>
+          <t>PE SaaS deals often underwrite ~15–22x EBITDA. Locking exit at 13x in BOTH AI and Base cases is deliberately conservative so equity creation is attributed to ops, not multiple expansion.</t>
+        </is>
+      </c>
+      <c r="G20" s="593" t="inlineStr">
+        <is>
+          <t>aventis-advisors.com/software-valuation-multiples/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1" s="244">
+      <c r="B21" s="575" t="inlineStr">
+        <is>
+          <t>S&amp;M baseline ($m)</t>
+        </is>
+      </c>
+      <c r="C21" s="576" t="n">
+        <v>425</v>
+      </c>
+      <c r="D21" s="575" t="inlineStr">
+        <is>
+          <t>35% × FY24 revenue</t>
+        </is>
+      </c>
+      <c r="E21" s="593" t="inlineStr">
+        <is>
+          <t>ZI FY24 S&amp;M $414.1m on $1,214.3m rev</t>
+        </is>
+      </c>
+      <c r="F21" s="573" t="inlineStr">
+        <is>
+          <t>Company-reported FY24 S&amp;M = $414.1m (~34% of $1,214.3m revenue). Model uses ~$425m (~35%) as a rounded baseline consistent with that filing.</t>
+        </is>
+      </c>
+      <c r="G21" s="593" t="inlineStr">
+        <is>
+          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/z</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1" s="244">
+      <c r="B22" s="575" t="inlineStr">
+        <is>
+          <t>Payroll baseline ($m)</t>
+        </is>
+      </c>
+      <c r="C22" s="576" t="n">
+        <v>318.8</v>
+      </c>
+      <c r="D22" s="575" t="inlineStr">
+        <is>
+          <t>S&amp;M − commission pool</t>
+        </is>
+      </c>
+      <c r="E22" s="593" t="inlineStr">
+        <is>
+          <t>SDR OTE mostly base (~70%)</t>
+        </is>
+      </c>
+      <c r="F22" s="573" t="inlineStr">
+        <is>
+          <t>With ~70/30 base/variable SDR mix, most S&amp;M people cost is payroll/base. Payroll baseline = S&amp;M − commission pool (~75% of S&amp;M) matches that pay-mix structure.</t>
+        </is>
+      </c>
+      <c r="G22" s="593" t="inlineStr">
+        <is>
+          <t>pulserevops.com/knowledge/ra0197</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1" s="244">
+      <c r="B23" s="575" t="inlineStr">
+        <is>
+          <t>Commission baseline ($m)</t>
+        </is>
+      </c>
+      <c r="C23" s="576" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="D23" s="575" t="inlineStr">
+        <is>
+          <t>25% of S&amp;M baseline</t>
+        </is>
+      </c>
+      <c r="E23" s="593" t="inlineStr">
+        <is>
+          <t>Variable ~30–35% of SDR OTE</t>
+        </is>
+      </c>
+      <c r="F23" s="573" t="inlineStr">
+        <is>
+          <t>Tech SDR variable is typically ~30–35% of OTE. Setting commission pool at 25% of S&amp;M is a slightly conservative carve of total S&amp;M for variable payouts.</t>
+        </is>
+      </c>
+      <c r="G23" s="593" t="inlineStr">
+        <is>
+          <t>syncgtm.com/blog/how-to-pay-sales-development-rep</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1" s="244">
+      <c r="B24" s="575" t="inlineStr">
+        <is>
+          <t>CapEx base % of rev</t>
+        </is>
+      </c>
+      <c r="C24" s="422" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D24" s="575" t="inlineStr">
+        <is>
+          <t>Before AI −5%</t>
+        </is>
+      </c>
+      <c r="E24" s="593" t="inlineStr">
+        <is>
+          <t>ZI FY24 unlevered FCF / light CapEx SaaS</t>
+        </is>
+      </c>
+      <c r="F24" s="573" t="inlineStr">
+        <is>
+          <t>SaaS models run low CapEx vs industrials; ZI still printed strong FY24 FCF. 2% of revenue is a simple maintenance CapEx planning rate before the AI −5% haircut.</t>
+        </is>
+      </c>
+      <c r="G24" s="593" t="inlineStr">
+        <is>
+          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/z</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1" s="244">
+      <c r="B25" s="575" t="inlineStr">
+        <is>
+          <t>WC base % of Δrev</t>
+        </is>
+      </c>
+      <c r="C25" s="422" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D25" s="575" t="inlineStr">
+        <is>
+          <t>Before AI improvement</t>
+        </is>
+      </c>
+      <c r="E25" s="593" t="inlineStr">
+        <is>
+          <t>ZI receivables days ~80 (WC intensity)</t>
+        </is>
+      </c>
+      <c r="F25" s="573" t="inlineStr">
+        <is>
+          <t>Receivables ~80 days imply WC scales with growth. Using 2% of Δrevenue as ΔNWC is a simplified SaaS WC plug anchored to that receivables reality.</t>
+        </is>
+      </c>
+      <c r="G25" s="593" t="inlineStr">
+        <is>
+          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/z</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TLA rate (SOFR+4)</t>
+        </is>
+      </c>
+      <c r="C27" s="579">
+        <f>C14+C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TLB rate (SOFR+5)</t>
+        </is>
+      </c>
+      <c r="C28" s="579">
+        <f>C14+C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="564" t="inlineStr">
+        <is>
+          <t>PDF twin of this source map:</t>
+        </is>
+      </c>
+      <c r="C29" s="593" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_AI_COST_SOURCES.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="594" t="inlineStr">
+        <is>
+          <t>Educational / research use only — not investment advice. List prices and filings update over time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:G3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14183,416 +12759,207 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="36" customWidth="1" style="244" min="2" max="2"/>
-    <col width="14" customWidth="1" style="244" min="3" max="3"/>
-    <col width="36" customWidth="1" style="244" min="4" max="4"/>
-    <col width="28" customWidth="1" style="244" min="5" max="5"/>
-    <col width="48" customWidth="1" style="244" min="6" max="6"/>
-    <col width="40" customWidth="1" style="244" min="7" max="7"/>
-  </cols>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
-          <t>Assumptions Drivers (yellow = inputs used by AI / Base operating math)</t>
+          <t>Debt sweep — TLA/TLB priced at SOFR+4 / SOFR+5; 1% mandatory + 100% cash sweep</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>These cells are the single source of truth for the commentary list. Operating tabs read these values.</t>
+          <t>Rates from Assumptions_Drivers!C14:C18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="412" t="inlineStr">
         <is>
-          <t>Driver</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C4" s="412" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>FCF</t>
         </is>
       </c>
       <c r="D4" s="412" t="inlineStr">
         <is>
-          <t>Feeds</t>
+          <t>Mandatory 1%</t>
+        </is>
+      </c>
+      <c r="E4" s="412" t="inlineStr">
+        <is>
+          <t>Total paydown</t>
+        </is>
+      </c>
+      <c r="F4" s="412" t="inlineStr">
+        <is>
+          <t>AI debt end</t>
+        </is>
+      </c>
+      <c r="G4" s="412" t="inlineStr">
+        <is>
+          <t>Base debt end</t>
+        </is>
+      </c>
+      <c r="H4" s="412" t="inlineStr">
+        <is>
+          <t>Extra paydown vs base</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="575" t="inlineStr">
-        <is>
-          <t>Revenue growth</t>
-        </is>
-      </c>
-      <c r="C5" s="422" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D5" s="575" t="inlineStr">
-        <is>
-          <t>AI_Operating!C5:G5</t>
-        </is>
+      <c r="B5" s="580" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C5" s="567" t="n">
+        <v>121.543319</v>
+      </c>
+      <c r="D5" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="E5" s="567" t="n">
+        <v>121.543319</v>
+      </c>
+      <c r="F5" s="567" t="n">
+        <v>793.956681</v>
+      </c>
+      <c r="G5" s="567" t="n">
+        <v>877.5180999999999</v>
+      </c>
+      <c r="H5" s="567" t="n">
+        <v>83.56141899999989</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="575" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="C6" s="422" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D6" s="575" t="inlineStr">
-        <is>
-          <t>AI_Operating COGS row</t>
-        </is>
+      <c r="B6" s="580" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C6" s="567" t="n">
+        <v>171.4952368268301</v>
+      </c>
+      <c r="D6" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="E6" s="567" t="n">
+        <v>171.4952368268301</v>
+      </c>
+      <c r="F6" s="567" t="n">
+        <v>622.4614441731698</v>
+      </c>
+      <c r="G6" s="567" t="n">
+        <v>824.8037622999997</v>
+      </c>
+      <c r="H6" s="567" t="n">
+        <v>202.3423181268299</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="575" t="inlineStr">
-        <is>
-          <t>Sales payroll cut (Y1)</t>
-        </is>
-      </c>
-      <c r="C7" s="422" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D7" s="575" t="inlineStr">
-        <is>
-          <t>AI_Operating S&amp;M Y1</t>
-        </is>
+      <c r="B7" s="580" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C7" s="567" t="n">
+        <v>229.3706423055654</v>
+      </c>
+      <c r="D7" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="E7" s="567" t="n">
+        <v>229.3706423055654</v>
+      </c>
+      <c r="F7" s="567" t="n">
+        <v>393.0908018676043</v>
+      </c>
+      <c r="G7" s="567" t="n">
+        <v>754.9762005708997</v>
+      </c>
+      <c r="H7" s="567" t="n">
+        <v>361.8853987032953</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="575" t="inlineStr">
-        <is>
-          <t>Variable commission cut</t>
-        </is>
-      </c>
-      <c r="C8" s="422" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D8" s="575" t="inlineStr">
-        <is>
-          <t>AI_Operating Commissions</t>
-        </is>
+      <c r="B8" s="580" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C8" s="567" t="n">
+        <v>296.6736983899872</v>
+      </c>
+      <c r="D8" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="E8" s="567" t="n">
+        <v>296.6736983899872</v>
+      </c>
+      <c r="F8" s="567" t="n">
+        <v>96.41710347761716</v>
+      </c>
+      <c r="G8" s="567" t="n">
+        <v>665.9609770683334</v>
+      </c>
+      <c r="H8" s="567" t="n">
+        <v>569.5438735907162</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="575" t="inlineStr">
-        <is>
-          <t>AI infrastructure ($m)</t>
-        </is>
-      </c>
-      <c r="C9" s="576" t="n">
-        <v>15</v>
-      </c>
-      <c r="D9" s="575" t="inlineStr">
-        <is>
-          <t>AI_Operating AI cost</t>
-        </is>
-      </c>
-      <c r="E9" s="590" t="inlineStr">
-        <is>
-          <t>SOURCE → AI_Cost_Sources</t>
-        </is>
-      </c>
-      <c r="F9" s="590" t="inlineStr">
-        <is>
-          <t>Salesforce Agentforce $2/conv + Flex Credits press</t>
-        </is>
-      </c>
-      <c r="G9" s="590" t="inlineStr">
-        <is>
-          <t>ZoomInfo 10-K S&amp;M headcount</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="575" t="inlineStr">
-        <is>
-          <t>S&amp;M expense growth Y2+</t>
-        </is>
-      </c>
-      <c r="C10" s="422" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D10" s="575" t="inlineStr">
-        <is>
-          <t>AI_Operating S&amp;M Y2+</t>
-        </is>
-      </c>
-    </row>
+      <c r="B9" s="580" t="n">
+        <v>2029</v>
+      </c>
+      <c r="C9" s="567" t="n">
+        <v>374.8388640800935</v>
+      </c>
+      <c r="D9" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="E9" s="567" t="n">
+        <v>96.41710347761716</v>
+      </c>
+      <c r="F9" s="567" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="567" t="n">
+        <v>557.1124750633038</v>
+      </c>
+      <c r="H9" s="567" t="n">
+        <v>557.1124750633038</v>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
-      <c r="B11" s="575" t="inlineStr">
-        <is>
-          <t>G&amp;A % of revenue</t>
-        </is>
-      </c>
-      <c r="C11" s="422" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D11" s="575" t="inlineStr">
-        <is>
-          <t>AI_Operating G&amp;A</t>
-        </is>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TLA initial / TLB initial / Notes initial</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>457.75</v>
+      </c>
+      <c r="D11" t="n">
+        <v>274.65</v>
+      </c>
+      <c r="E11" t="n">
+        <v>183.1</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="575" t="inlineStr">
-        <is>
-          <t>CapEx reduction vs base</t>
-        </is>
-      </c>
-      <c r="C12" s="422" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D12" s="575" t="inlineStr">
-        <is>
-          <t>FCF CapEx</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="575" t="inlineStr">
-        <is>
-          <t>WC / receivables improvement</t>
-        </is>
-      </c>
-      <c r="C13" s="422" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D13" s="575" t="inlineStr">
-        <is>
-          <t>FCF ΔNWC</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="575" t="inlineStr">
-        <is>
-          <t>SOFR</t>
-        </is>
-      </c>
-      <c r="C14" s="577" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="D14" s="575" t="inlineStr">
-        <is>
-          <t>Debt interest</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="575" t="inlineStr">
-        <is>
-          <t>Term Loan A spread</t>
-        </is>
-      </c>
-      <c r="C15" s="577" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D15" s="575" t="inlineStr">
-        <is>
-          <t>TLA rate = SOFR+spread</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="575" t="inlineStr">
-        <is>
-          <t>Term Loan B spread</t>
-        </is>
-      </c>
-      <c r="C16" s="577" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D16" s="575" t="inlineStr">
-        <is>
-          <t>TLB rate = SOFR+spread</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="575" t="inlineStr">
-        <is>
-          <t>Mandatory amortization</t>
-        </is>
-      </c>
-      <c r="C17" s="422" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D17" s="575" t="inlineStr">
-        <is>
-          <t>% of initial new debt / yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="575" t="inlineStr">
-        <is>
-          <t>Cash sweep %</t>
-        </is>
-      </c>
-      <c r="C18" s="422" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="575" t="inlineStr">
-        <is>
-          <t>Debt_Sweep_AI</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="575" t="inlineStr">
-        <is>
-          <t>Tax rate</t>
-        </is>
-      </c>
-      <c r="C19" s="422" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="D19" s="575" t="inlineStr">
-        <is>
-          <t>NI tax</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="575" t="inlineStr">
-        <is>
-          <t>Exit EV/EBITDA multiple</t>
-        </is>
-      </c>
-      <c r="C20" s="584" t="n">
-        <v>13</v>
-      </c>
-      <c r="D20" s="575" t="inlineStr">
-        <is>
-          <t>LBO!D17 / Strategy_Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="575" t="inlineStr">
-        <is>
-          <t>S&amp;M baseline ($m)</t>
-        </is>
-      </c>
-      <c r="C21" s="576" t="n">
-        <v>425</v>
-      </c>
-      <c r="D21" s="575" t="inlineStr">
-        <is>
-          <t>35% × FY24 revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="575" t="inlineStr">
-        <is>
-          <t>Payroll baseline ($m)</t>
-        </is>
-      </c>
-      <c r="C22" s="576" t="n">
-        <v>318.8</v>
-      </c>
-      <c r="D22" s="575" t="inlineStr">
-        <is>
-          <t>S&amp;M − commission pool</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="575" t="inlineStr">
-        <is>
-          <t>Commission baseline ($m)</t>
-        </is>
-      </c>
-      <c r="C23" s="576" t="n">
-        <v>106.2</v>
-      </c>
-      <c r="D23" s="575" t="inlineStr">
-        <is>
-          <t>25% of S&amp;M baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="575" t="inlineStr">
-        <is>
-          <t>CapEx base % of rev</t>
-        </is>
-      </c>
-      <c r="C24" s="422" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D24" s="575" t="inlineStr">
-        <is>
-          <t>Before AI −5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="575" t="inlineStr">
-        <is>
-          <t>WC base % of Δrev</t>
-        </is>
-      </c>
-      <c r="C25" s="422" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D25" s="575" t="inlineStr">
-        <is>
-          <t>Before AI improvement</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>TLA rate (SOFR+4)</t>
-        </is>
-      </c>
-      <c r="C27" s="579">
-        <f>C14+C15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>TLB rate (SOFR+5)</t>
-        </is>
-      </c>
-      <c r="C28" s="579">
-        <f>C14+C16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="592" t="inlineStr">
-        <is>
-          <t>AI $15m reasonableness: see sheet AI_Cost_Sources (triangulated from public SF Agentforce prices + ZI 10-K).</t>
-        </is>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TLA rate / TLB rate</t>
+        </is>
+      </c>
+      <c r="C12" s="581" t="n">
+        <v>0.08299999999999999</v>
+      </c>
+      <c r="D12" s="581" t="n">
+        <v>0.093</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B30:G30"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId3"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14603,216 +12970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="563" t="inlineStr">
-        <is>
-          <t>Debt sweep — TLA/TLB priced at SOFR+4 / SOFR+5; 1% mandatory + 100% cash sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rates from Assumptions_Drivers!C14:C18</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="412" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C4" s="412" t="inlineStr">
-        <is>
-          <t>FCF</t>
-        </is>
-      </c>
-      <c r="D4" s="412" t="inlineStr">
-        <is>
-          <t>Mandatory 1%</t>
-        </is>
-      </c>
-      <c r="E4" s="412" t="inlineStr">
-        <is>
-          <t>Total paydown</t>
-        </is>
-      </c>
-      <c r="F4" s="412" t="inlineStr">
-        <is>
-          <t>AI debt end</t>
-        </is>
-      </c>
-      <c r="G4" s="412" t="inlineStr">
-        <is>
-          <t>Base debt end</t>
-        </is>
-      </c>
-      <c r="H4" s="412" t="inlineStr">
-        <is>
-          <t>Extra paydown vs base</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="580" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C5" s="567" t="n">
-        <v>121.543319</v>
-      </c>
-      <c r="D5" s="567" t="n">
-        <v>9.154999999999999</v>
-      </c>
-      <c r="E5" s="567" t="n">
-        <v>121.543319</v>
-      </c>
-      <c r="F5" s="567" t="n">
-        <v>793.956681</v>
-      </c>
-      <c r="G5" s="567" t="n">
-        <v>877.5180999999999</v>
-      </c>
-      <c r="H5" s="567" t="n">
-        <v>83.56141899999989</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="580" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C6" s="567" t="n">
-        <v>171.4952368268301</v>
-      </c>
-      <c r="D6" s="567" t="n">
-        <v>9.154999999999999</v>
-      </c>
-      <c r="E6" s="567" t="n">
-        <v>171.4952368268301</v>
-      </c>
-      <c r="F6" s="567" t="n">
-        <v>622.4614441731698</v>
-      </c>
-      <c r="G6" s="567" t="n">
-        <v>824.8037622999997</v>
-      </c>
-      <c r="H6" s="567" t="n">
-        <v>202.3423181268299</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="580" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C7" s="567" t="n">
-        <v>229.3706423055654</v>
-      </c>
-      <c r="D7" s="567" t="n">
-        <v>9.154999999999999</v>
-      </c>
-      <c r="E7" s="567" t="n">
-        <v>229.3706423055654</v>
-      </c>
-      <c r="F7" s="567" t="n">
-        <v>393.0908018676043</v>
-      </c>
-      <c r="G7" s="567" t="n">
-        <v>754.9762005708997</v>
-      </c>
-      <c r="H7" s="567" t="n">
-        <v>361.8853987032953</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="580" t="n">
-        <v>2028</v>
-      </c>
-      <c r="C8" s="567" t="n">
-        <v>296.6736983899872</v>
-      </c>
-      <c r="D8" s="567" t="n">
-        <v>9.154999999999999</v>
-      </c>
-      <c r="E8" s="567" t="n">
-        <v>296.6736983899872</v>
-      </c>
-      <c r="F8" s="567" t="n">
-        <v>96.41710347761716</v>
-      </c>
-      <c r="G8" s="567" t="n">
-        <v>665.9609770683334</v>
-      </c>
-      <c r="H8" s="567" t="n">
-        <v>569.5438735907162</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="580" t="n">
-        <v>2029</v>
-      </c>
-      <c r="C9" s="567" t="n">
-        <v>374.8388640800935</v>
-      </c>
-      <c r="D9" s="567" t="n">
-        <v>9.154999999999999</v>
-      </c>
-      <c r="E9" s="567" t="n">
-        <v>96.41710347761716</v>
-      </c>
-      <c r="F9" s="567" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="567" t="n">
-        <v>557.1124750633038</v>
-      </c>
-      <c r="H9" s="567" t="n">
-        <v>557.1124750633038</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TLA initial / TLB initial / Notes initial</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>457.75</v>
-      </c>
-      <c r="D11" t="n">
-        <v>274.65</v>
-      </c>
-      <c r="E11" t="n">
-        <v>183.1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TLA rate / TLB rate</t>
-        </is>
-      </c>
-      <c r="C12" s="581" t="n">
-        <v>0.08299999999999999</v>
-      </c>
-      <c r="D12" s="581" t="n">
-        <v>0.093</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:H24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
@@ -14825,6 +12983,7 @@
     <col width="12" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -15360,13 +13519,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
@@ -15379,6 +13538,7 @@
     <col width="12" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -15914,15 +14074,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M42"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
@@ -15930,6 +14091,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8" ht="26.25" customHeight="1" s="244">
       <c r="B8" s="402" t="inlineStr">
         <is>
@@ -15948,6 +14114,8 @@
       <c r="L8" s="404" t="n"/>
       <c r="M8" s="404" t="n"/>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="405" t="inlineStr">
         <is>
@@ -15958,6 +14126,31 @@
     <row r="12"/>
     <row r="13"/>
     <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
@@ -15989,13 +14182,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:R393"/>
+  <dimension ref="A1:R393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="1.7109375" customWidth="1" style="244" min="1" max="1"/>
@@ -16718,6 +14911,7 @@
         <v>134.838525</v>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -18666,6 +16860,7 @@
         <v>43190</v>
       </c>
     </row>
+    <row r="114"/>
     <row r="115">
       <c r="B115" t="inlineStr">
         <is>
@@ -18888,6 +17083,7 @@
         <v>987.5822307314286</v>
       </c>
     </row>
+    <row r="124"/>
     <row r="125">
       <c r="B125" t="inlineStr">
         <is>
@@ -18954,6 +17150,7 @@
         <v>-223</v>
       </c>
     </row>
+    <row r="128"/>
     <row r="129">
       <c r="B129" t="inlineStr">
         <is>
@@ -19495,6 +17692,7 @@
         <v>586.7181807314284</v>
       </c>
     </row>
+    <row r="154"/>
     <row r="155">
       <c r="B155" s="34" t="inlineStr">
         <is>
@@ -19633,6 +17831,7 @@
         </is>
       </c>
     </row>
+    <row r="160"/>
     <row r="161">
       <c r="B161" s="321" t="inlineStr">
         <is>
@@ -20731,6 +18930,7 @@
       <c r="I214" s="15" t="n"/>
       <c r="J214" s="15" t="n"/>
     </row>
+    <row r="215"/>
     <row r="216">
       <c r="F216" s="475" t="n">
         <v>43190</v>
@@ -20740,6 +18940,7 @@
       <c r="I216" s="475" t="n"/>
       <c r="J216" s="475" t="n"/>
     </row>
+    <row r="217"/>
     <row r="218">
       <c r="B218" s="3" t="inlineStr">
         <is>
@@ -21985,6 +20186,7 @@
         <v>8149.38245662911</v>
       </c>
     </row>
+    <row r="265"/>
     <row r="266">
       <c r="B266" s="317" t="inlineStr">
         <is>
@@ -22671,6 +20873,7 @@
         <v>0.4297704340734299</v>
       </c>
     </row>
+    <row r="299"/>
     <row r="300">
       <c r="D300" s="319" t="inlineStr">
         <is>
@@ -22845,6 +21048,7 @@
         <v>0.4403663540732419</v>
       </c>
     </row>
+    <row r="309"/>
     <row r="310">
       <c r="D310" s="319" t="inlineStr">
         <is>
@@ -23006,6 +21210,7 @@
         <v>0.2849090713511313</v>
       </c>
     </row>
+    <row r="318"/>
     <row r="319">
       <c r="B319" s="317" t="inlineStr">
         <is>
@@ -24204,6 +22409,7 @@
         <v>3837.047401196713</v>
       </c>
     </row>
+    <row r="371"/>
     <row r="372">
       <c r="B372" s="312" t="inlineStr">
         <is>
@@ -24247,6 +22453,7 @@
         </is>
       </c>
     </row>
+    <row r="376"/>
     <row r="377" ht="15.75" customHeight="1" s="244" thickBot="1">
       <c r="B377" s="392" t="inlineStr">
         <is>
@@ -24340,6 +22547,7 @@
         <v>1205.272610422996</v>
       </c>
     </row>
+    <row r="384"/>
     <row r="385">
       <c r="B385" s="383" t="inlineStr">
         <is>
@@ -24360,6 +22568,7 @@
         <v>5536.653639577004</v>
       </c>
     </row>
+    <row r="387"/>
     <row r="388">
       <c r="B388" s="317" t="inlineStr">
         <is>
@@ -24559,4 +22768,1659 @@
   <pageSetup orientation="portrait"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K118"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="1.7109375" customWidth="1" style="244" min="1" max="1"/>
+    <col width="40.28515625" customWidth="1" style="244" min="2" max="2"/>
+    <col width="12.140625" bestFit="1" customWidth="1" style="244" min="3" max="3"/>
+    <col width="11.140625" bestFit="1" customWidth="1" style="244" min="4" max="4"/>
+    <col width="10.140625" bestFit="1" customWidth="1" style="244" min="5" max="7"/>
+    <col width="11" customWidth="1" style="244" min="8" max="10"/>
+    <col width="12.140625" bestFit="1" customWidth="1" style="244" min="11" max="11"/>
+    <col width="9.140625" customWidth="1" style="244" min="12" max="12"/>
+    <col width="9.140625" customWidth="1" style="244" min="13" max="13"/>
+    <col width="9.140625" customWidth="1" style="244" min="14" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" s="244" thickBot="1"/>
+    <row r="2" ht="27" customHeight="1" s="244" thickBot="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Discounted Cash Flow Model for BMC</t>
+        </is>
+      </c>
+      <c r="C2" s="305" t="n"/>
+      <c r="D2" s="305" t="n"/>
+      <c r="E2" s="305" t="n"/>
+      <c r="F2" s="305" t="n"/>
+      <c r="G2" s="305" t="n"/>
+      <c r="H2" s="305" t="n"/>
+      <c r="I2" s="305" t="n"/>
+      <c r="J2" s="305" t="n"/>
+    </row>
+    <row r="3">
+      <c r="B3" s="84" t="inlineStr">
+        <is>
+          <t>$ mm except per share</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="84" t="n"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" s="244" thickBot="1">
+      <c r="B5" s="66" t="inlineStr">
+        <is>
+          <t>General assumptions</t>
+        </is>
+      </c>
+      <c r="C5" s="93" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Share price as of last close</t>
+        </is>
+      </c>
+      <c r="C6" s="528" t="n">
+        <v>46.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="84" t="inlineStr">
+        <is>
+          <t>Latest closing share price date</t>
+        </is>
+      </c>
+      <c r="C7" s="84" t="n">
+        <v>41400</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="84" t="inlineStr">
+        <is>
+          <t>Latest basic share count</t>
+        </is>
+      </c>
+      <c r="C8" s="529" t="n">
+        <v>143.973</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="84" t="inlineStr">
+        <is>
+          <t>Weighted average cost of capital</t>
+        </is>
+      </c>
+      <c r="C9" s="530" t="n">
+        <v>0.06990222994664612</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="15.75" customHeight="1" s="244" thickBot="1">
+      <c r="B11" s="69" t="inlineStr">
+        <is>
+          <t>Free cash flow buildup</t>
+        </is>
+      </c>
+      <c r="C11" s="93" t="n"/>
+      <c r="D11" s="93" t="n"/>
+      <c r="E11" s="93" t="n"/>
+      <c r="F11" s="93" t="n"/>
+      <c r="G11" s="93" t="n"/>
+      <c r="H11" s="93" t="n"/>
+      <c r="I11" s="93" t="n"/>
+      <c r="J11" s="93" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fiscal year  </t>
+        </is>
+      </c>
+      <c r="C12" s="270" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D12" s="270" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E12" s="270" t="n">
+        <v>2013</v>
+      </c>
+      <c r="F12" s="157" t="n">
+        <v>2014</v>
+      </c>
+      <c r="G12" s="157" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H12" s="157" t="n">
+        <v>2016</v>
+      </c>
+      <c r="I12" s="157" t="n">
+        <v>2017</v>
+      </c>
+      <c r="J12" s="157" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Fiscal year end date</t>
+        </is>
+      </c>
+      <c r="C13" s="39" t="n">
+        <v>40633</v>
+      </c>
+      <c r="D13" s="39" t="n">
+        <v>40999</v>
+      </c>
+      <c r="E13" s="39" t="n">
+        <v>41364</v>
+      </c>
+      <c r="F13" s="39" t="n">
+        <v>41729</v>
+      </c>
+      <c r="G13" s="39" t="n">
+        <v>42094</v>
+      </c>
+      <c r="H13" s="39" t="n">
+        <v>42460</v>
+      </c>
+      <c r="I13" s="39" t="n">
+        <v>42825</v>
+      </c>
+      <c r="J13" s="39" t="n">
+        <v>43190</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="70" t="n"/>
+      <c r="F14" s="435" t="n"/>
+      <c r="G14" s="435" t="n"/>
+      <c r="H14" s="435" t="n"/>
+      <c r="I14" s="435" t="n"/>
+      <c r="J14" s="435" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C15" s="162" t="n">
+        <v>843.6000000000003</v>
+      </c>
+      <c r="D15" s="162" t="n">
+        <v>906.4999999999999</v>
+      </c>
+      <c r="E15" s="162" t="n">
+        <v>882.7000000000003</v>
+      </c>
+      <c r="F15" s="162" t="n">
+        <v>947.6792413199889</v>
+      </c>
+      <c r="G15" s="162" t="n">
+        <v>1000.484484594448</v>
+      </c>
+      <c r="H15" s="162" t="n">
+        <v>1078.88768747765</v>
+      </c>
+      <c r="I15" s="162" t="n">
+        <v>1150.07160606407</v>
+      </c>
+      <c r="J15" s="162" t="n">
+        <v>1226.874119002437</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="C16" s="162" t="n">
+        <v>532.8000000000003</v>
+      </c>
+      <c r="D16" s="162" t="n">
+        <v>543.8999999999999</v>
+      </c>
+      <c r="E16" s="162" t="n">
+        <v>465.4000000000003</v>
+      </c>
+      <c r="F16" s="162" t="n">
+        <v>493.6803141804108</v>
+      </c>
+      <c r="G16" s="162" t="n">
+        <v>559.8040395999167</v>
+      </c>
+      <c r="H16" s="162" t="n">
+        <v>634.7919640514119</v>
+      </c>
+      <c r="I16" s="162" t="n">
+        <v>709.3122632461741</v>
+      </c>
+      <c r="J16" s="162" t="n">
+        <v>787.9602383046408</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>tax rate</t>
+        </is>
+      </c>
+      <c r="C17" s="531" t="n">
+        <v>0.1413514022209673</v>
+      </c>
+      <c r="D17" s="531" t="n">
+        <v>0.2433962264150944</v>
+      </c>
+      <c r="E17" s="531" t="n">
+        <v>0.2264547791540078</v>
+      </c>
+      <c r="F17" s="531" t="n">
+        <v>0.2264547791540078</v>
+      </c>
+      <c r="G17" s="531" t="n">
+        <v>0.2264547791540078</v>
+      </c>
+      <c r="H17" s="531" t="n">
+        <v>0.2264547791540078</v>
+      </c>
+      <c r="I17" s="531" t="n">
+        <v>0.2264547791540078</v>
+      </c>
+      <c r="J17" s="531" t="n">
+        <v>0.2264547791540078</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="383" t="inlineStr">
+        <is>
+          <t>EBIAT (NOPAT)</t>
+        </is>
+      </c>
+      <c r="C18" s="71" t="n">
+        <v>457.4879728966689</v>
+      </c>
+      <c r="D18" s="71" t="n">
+        <v>411.51679245283</v>
+      </c>
+      <c r="E18" s="71" t="n">
+        <v>360.007945781725</v>
+      </c>
+      <c r="F18" s="71" t="n">
+        <v>381.8840476600047</v>
+      </c>
+      <c r="G18" s="71" t="n">
+        <v>433.0337394427961</v>
+      </c>
+      <c r="H18" s="71" t="n">
+        <v>491.0402900234106</v>
+      </c>
+      <c r="I18" s="71" t="n">
+        <v>548.6851113215323</v>
+      </c>
+      <c r="J18" s="71" t="n">
+        <v>609.522876557224</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="383" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="73" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization</t>
+        </is>
+      </c>
+      <c r="F20" s="162" t="n">
+        <v>223.946868228773</v>
+      </c>
+      <c r="G20" s="162" t="n">
+        <v>220.6010317460318</v>
+      </c>
+      <c r="H20" s="162" t="n">
+        <v>222.400781053162</v>
+      </c>
+      <c r="I20" s="162" t="n">
+        <v>224.1937314184933</v>
+      </c>
+      <c r="J20" s="162" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="73" t="inlineStr">
+        <is>
+          <t>Stock based compensation</t>
+        </is>
+      </c>
+      <c r="F21" s="162" t="n">
+        <v>161.0547368274718</v>
+      </c>
+      <c r="G21" s="162" t="n">
+        <v>162.0820911651659</v>
+      </c>
+      <c r="H21" s="162" t="n">
+        <v>163.6976202897424</v>
+      </c>
+      <c r="I21" s="162" t="n">
+        <v>163.5682893160696</v>
+      </c>
+      <c r="J21" s="162" t="n">
+        <v>162.9165586144626</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Changes in net working capital</t>
+        </is>
+      </c>
+      <c r="F22" s="162" t="n">
+        <v>56.83135068829188</v>
+      </c>
+      <c r="G22" s="162" t="n">
+        <v>95.05600763617076</v>
+      </c>
+      <c r="H22" s="162" t="n">
+        <v>109.4272418486823</v>
+      </c>
+      <c r="I22" s="162" t="n">
+        <v>96.46443037533186</v>
+      </c>
+      <c r="J22" s="162" t="n">
+        <v>97.15243145060185</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Other assets &amp; liabilities</t>
+        </is>
+      </c>
+      <c r="F23" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="383" t="inlineStr">
+        <is>
+          <t>Unlevered CFO</t>
+        </is>
+      </c>
+      <c r="F24" s="57" t="n">
+        <v>823.7170034045414</v>
+      </c>
+      <c r="G24" s="57" t="n">
+        <v>910.7728699901645</v>
+      </c>
+      <c r="H24" s="57" t="n">
+        <v>986.5659332149974</v>
+      </c>
+      <c r="I24" s="57" t="n">
+        <v>1032.911562431427</v>
+      </c>
+      <c r="J24" s="57" t="n">
+        <v>1092.591866622289</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>Less: Capital expenditures</t>
+        </is>
+      </c>
+      <c r="F25" s="162" t="n">
+        <v>-26</v>
+      </c>
+      <c r="G25" s="162" t="n">
+        <v>-28</v>
+      </c>
+      <c r="H25" s="162" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I25" s="162" t="n">
+        <v>-29</v>
+      </c>
+      <c r="J25" s="162" t="n">
+        <v>-31</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="34" t="inlineStr">
+        <is>
+          <t>Less: Purchases of intangible assets</t>
+        </is>
+      </c>
+      <c r="F26" s="162" t="n">
+        <v>-201</v>
+      </c>
+      <c r="G26" s="162" t="n">
+        <v>-194</v>
+      </c>
+      <c r="H26" s="162" t="n">
+        <v>-193</v>
+      </c>
+      <c r="I26" s="162" t="n">
+        <v>-196</v>
+      </c>
+      <c r="J26" s="162" t="n">
+        <v>-192</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="383" t="inlineStr">
+        <is>
+          <t>Unlevered FCF</t>
+        </is>
+      </c>
+      <c r="F27" s="57" t="n">
+        <v>596.7170034045414</v>
+      </c>
+      <c r="G27" s="57" t="n">
+        <v>688.7728699901645</v>
+      </c>
+      <c r="H27" s="57" t="n">
+        <v>763.5659332149974</v>
+      </c>
+      <c r="I27" s="57" t="n">
+        <v>807.9115624314272</v>
+      </c>
+      <c r="J27" s="57" t="n">
+        <v>869.5918666222885</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="202" t="inlineStr">
+        <is>
+          <t>% growth</t>
+        </is>
+      </c>
+      <c r="G28" s="435" t="n">
+        <v>0.1542705605176367</v>
+      </c>
+      <c r="H28" s="435" t="n">
+        <v>0.1085888635914201</v>
+      </c>
+      <c r="I28" s="435" t="n">
+        <v>0.05807701376842789</v>
+      </c>
+      <c r="J28" s="435" t="n">
+        <v>0.07634536632355293</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="202" t="n"/>
+      <c r="G29" s="435" t="n"/>
+      <c r="H29" s="435" t="n"/>
+      <c r="I29" s="435" t="n"/>
+      <c r="J29" s="435" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="73" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="F30" s="437" t="n">
+        <v>0.9027777777777778</v>
+      </c>
+      <c r="G30" s="437" t="n">
+        <v>1.902777777777778</v>
+      </c>
+      <c r="H30" s="437" t="n">
+        <v>2.902777777777778</v>
+      </c>
+      <c r="I30" s="437" t="n">
+        <v>3.902777777777778</v>
+      </c>
+      <c r="J30" s="437" t="n">
+        <v>4.902777777777778</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Assume cash flows are generated at:</t>
+        </is>
+      </c>
+      <c r="C31" s="97" t="inlineStr">
+        <is>
+          <t>Middle of period</t>
+        </is>
+      </c>
+      <c r="G31" s="437" t="n"/>
+      <c r="H31" s="437" t="n"/>
+      <c r="I31" s="437" t="n"/>
+      <c r="J31" s="437" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Midperiod adjustment factor</t>
+        </is>
+      </c>
+      <c r="C32" s="532" t="n">
+        <v>1.034360783260196</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="73" t="inlineStr">
+        <is>
+          <t>Present value of Unlevered FCF</t>
+        </is>
+      </c>
+      <c r="F33" s="95" t="n">
+        <v>580.6965753021989</v>
+      </c>
+      <c r="G33" s="95" t="n">
+        <v>626.488049752141</v>
+      </c>
+      <c r="H33" s="95" t="n">
+        <v>649.1412539283756</v>
+      </c>
+      <c r="I33" s="95" t="n">
+        <v>641.9665463307613</v>
+      </c>
+      <c r="J33" s="95" t="n">
+        <v>645.8325799660284</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="383" t="n"/>
+      <c r="C34" s="435" t="n"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1" s="244" thickBot="1">
+      <c r="B35" s="63" t="inlineStr">
+        <is>
+          <t>Perpetuity approach</t>
+        </is>
+      </c>
+      <c r="C35" s="93" t="n"/>
+      <c r="E35" s="63" t="inlineStr">
+        <is>
+          <t>Exit EBITDA multiple approach</t>
+        </is>
+      </c>
+      <c r="F35" s="93" t="n"/>
+      <c r="G35" s="93" t="n"/>
+      <c r="H35" s="93" t="n"/>
+      <c r="I35" s="93" t="n"/>
+      <c r="J35" s="93" t="n"/>
+    </row>
+    <row r="36" ht="17.25" customHeight="1" s="244">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normalized FCFt+1 </t>
+        </is>
+      </c>
+      <c r="C36" s="196" t="n">
+        <v>869.5918666222885</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Terminal year EBITDA</t>
+        </is>
+      </c>
+      <c r="J36" s="140" t="n">
+        <v>1226.874119002437</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Long term growth rate (g)</t>
+        </is>
+      </c>
+      <c r="C37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Terminal value EBITDA multiple</t>
+        </is>
+      </c>
+      <c r="J37" s="429" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K37" s="428" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Terminal value </t>
+        </is>
+      </c>
+      <c r="C38" s="140" t="n">
+        <v>12440.11624931017</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Terminal value </t>
+        </is>
+      </c>
+      <c r="J38" s="140" t="n">
+        <v>8956.181068717789</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Present value of terminal value</t>
+        </is>
+      </c>
+      <c r="C39" s="140" t="n">
+        <v>9239.084081566059</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Present value of terminal value</t>
+        </is>
+      </c>
+      <c r="J39" s="140" t="n">
+        <v>6651.618705589049</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Present value of stage 1 cash flows</t>
+        </is>
+      </c>
+      <c r="C40" s="140" t="n">
+        <v>3144.125005279505</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Present value of stage 1 cash flows</t>
+        </is>
+      </c>
+      <c r="J40" s="140" t="n">
+        <v>3144.125005279505</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enterprise value </t>
+        </is>
+      </c>
+      <c r="C41" s="57" t="n">
+        <v>12383.20908684557</v>
+      </c>
+      <c r="E41" s="383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enterprise value </t>
+        </is>
+      </c>
+      <c r="J41" s="57" t="n">
+        <v>9795.743710868554</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="100" t="inlineStr">
+        <is>
+          <t>Implied TV exit EBITDA multiple</t>
+        </is>
+      </c>
+      <c r="C42" s="533" t="n">
+        <v>10.13968430553018</v>
+      </c>
+      <c r="E42" s="100" t="inlineStr">
+        <is>
+          <t>Implied TV perpetual growth rate</t>
+        </is>
+      </c>
+      <c r="F42" s="100" t="n"/>
+      <c r="G42" s="100" t="n"/>
+      <c r="H42" s="100" t="n"/>
+      <c r="I42" s="100" t="n"/>
+      <c r="J42" s="458" t="n">
+        <v>-0.02719181716452775</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" s="57" t="n"/>
+      <c r="J43" s="435" t="n"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" s="244" thickBot="1">
+      <c r="B44" s="63" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="C44" s="93" t="n"/>
+      <c r="E44" s="63" t="inlineStr">
+        <is>
+          <t>Fair value per share</t>
+        </is>
+      </c>
+      <c r="F44" s="93" t="n"/>
+      <c r="G44" s="93" t="n"/>
+      <c r="H44" s="93" t="n"/>
+      <c r="I44" s="93" t="n"/>
+      <c r="J44" s="93" t="n"/>
+    </row>
+    <row r="45" ht="17.25" customHeight="1" s="244">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cash &amp; equivalents ST &amp; LT market. securities</t>
+        </is>
+      </c>
+      <c r="C45" s="162" t="n">
+        <v>179.9999999999991</v>
+      </c>
+      <c r="H45" s="400" t="inlineStr">
+        <is>
+          <t>LBO Offer</t>
+        </is>
+      </c>
+      <c r="I45" s="400" t="inlineStr">
+        <is>
+          <t>Perpetuity</t>
+        </is>
+      </c>
+      <c r="J45" s="400" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Long term debt </t>
+        </is>
+      </c>
+      <c r="C46" s="162" t="n">
+        <v>5190.276000000002</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="H46" s="140" t="n"/>
+      <c r="I46" s="140" t="n">
+        <v>12383.20908684557</v>
+      </c>
+      <c r="J46" s="140" t="n">
+        <v>9795.743710868554</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="383" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="C47" s="71" t="n">
+        <v>5010.276000000003</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Less: Net debt</t>
+        </is>
+      </c>
+      <c r="I47" s="140" t="n">
+        <v>-5010.276000000003</v>
+      </c>
+      <c r="J47" s="140" t="n">
+        <v>-5010.276000000003</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" s="228" t="n"/>
+      <c r="E48" s="383" t="inlineStr">
+        <is>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="F48" s="383" t="n"/>
+      <c r="G48" s="383" t="n"/>
+      <c r="H48" s="399" t="n">
+        <v>6741.92625</v>
+      </c>
+      <c r="I48" s="57" t="n">
+        <v>7372.933086845563</v>
+      </c>
+      <c r="J48" s="57" t="n">
+        <v>4785.467710868551</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1" s="244" thickBot="1">
+      <c r="B49" s="63" t="inlineStr">
+        <is>
+          <t>Cost of capital assumptions</t>
+        </is>
+      </c>
+      <c r="C49" s="93" t="n"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Diluted shares</t>
+        </is>
+      </c>
+      <c r="H49" s="529" t="n">
+        <v>145.7713783783784</v>
+      </c>
+      <c r="I49" s="534" t="n">
+        <v>145.7713783783784</v>
+      </c>
+      <c r="J49" s="534" t="n">
+        <v>145.7713783783784</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="76" t="inlineStr">
+        <is>
+          <t>Cost of debt</t>
+        </is>
+      </c>
+      <c r="C50" s="535" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E50" s="383" t="inlineStr">
+        <is>
+          <t>Equity value per share</t>
+        </is>
+      </c>
+      <c r="H50" s="536" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="I50" s="536" t="n">
+        <v>50.57874302119625</v>
+      </c>
+      <c r="J50" s="536" t="n">
+        <v>32.82858242889715</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="C51" s="435" t="n">
+        <v>0.2264547791540078</v>
+      </c>
+      <c r="E51" s="100" t="inlineStr">
+        <is>
+          <t>Premium (discount) to LBO offer</t>
+        </is>
+      </c>
+      <c r="H51" s="537" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="I51" s="435" t="n">
+        <v>0.09359444370154035</v>
+      </c>
+      <c r="J51" s="435" t="n">
+        <v>-0.2901928123481697</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Debt and equivalents</t>
+        </is>
+      </c>
+      <c r="C52" s="140" t="n">
+        <v>5010.276000000003</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debt as a % of total capital </t>
+        </is>
+      </c>
+      <c r="C53" s="538" t="n">
+        <v>0.7748616857223557</v>
+      </c>
+    </row>
+    <row r="54"/>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Risk free rate</t>
+        </is>
+      </c>
+      <c r="C55" s="431" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="C56" s="135" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Market risk premium</t>
+        </is>
+      </c>
+      <c r="C57" s="431" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equity as % of total capital structure </t>
+        </is>
+      </c>
+      <c r="C58" s="435" t="n">
+        <v>0.2251383142776443</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Cost of capital (WACC)</t>
+        </is>
+      </c>
+      <c r="C59" s="435" t="n">
+        <v>0.06990222994664612</v>
+      </c>
+    </row>
+    <row r="60"/>
+    <row r="61" ht="15.75" customHeight="1" s="244" thickBot="1">
+      <c r="B61" s="63" t="inlineStr">
+        <is>
+          <t>Sensitivity analysis</t>
+        </is>
+      </c>
+      <c r="C61" s="93" t="n"/>
+      <c r="D61" s="93" t="n"/>
+      <c r="E61" s="93" t="n"/>
+      <c r="F61" s="93" t="n"/>
+      <c r="G61" s="93" t="n"/>
+      <c r="H61" s="93" t="n"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="383" t="n"/>
+    </row>
+    <row r="63" ht="17.25" customHeight="1" s="244">
+      <c r="B63" s="383" t="n"/>
+      <c r="C63" s="112" t="inlineStr">
+        <is>
+          <t>Equity value per share</t>
+        </is>
+      </c>
+      <c r="D63" s="112" t="n"/>
+      <c r="E63" s="112" t="n"/>
+      <c r="F63" s="112" t="n"/>
+      <c r="G63" s="112" t="n"/>
+      <c r="H63" s="112" t="n"/>
+    </row>
+    <row r="64">
+      <c r="C64" s="73" t="n"/>
+      <c r="D64" s="290" t="inlineStr">
+        <is>
+          <t>Long term growth rate (g):</t>
+        </is>
+      </c>
+      <c r="E64" s="290" t="n"/>
+      <c r="F64" s="290" t="n"/>
+      <c r="G64" s="290" t="n"/>
+      <c r="H64" s="290" t="n"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="378" t="n"/>
+      <c r="C65" s="539" t="n">
+        <v>50.57874302119625</v>
+      </c>
+      <c r="D65" s="540" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E65" s="541" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F65" s="542" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G65" s="541" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="H65" s="543" t="n">
+        <v>0.03999999999999999</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" s="117" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D66" s="544" t="n">
+        <v>16.21484649892585</v>
+      </c>
+      <c r="E66" s="544" t="n">
+        <v>17.72262878709584</v>
+      </c>
+      <c r="F66" s="544" t="n">
+        <v>19.38118930408283</v>
+      </c>
+      <c r="G66" s="544" t="n">
+        <v>21.21433513864741</v>
+      </c>
+      <c r="H66" s="544" t="n">
+        <v>23.25116384371916</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" s="118" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D67" s="544" t="n">
+        <v>21.17084407877228</v>
+      </c>
+      <c r="E67" s="544" t="n">
+        <v>23.07715436501025</v>
+      </c>
+      <c r="F67" s="544" t="n">
+        <v>25.19527690527467</v>
+      </c>
+      <c r="G67" s="544" t="n">
+        <v>27.562590332629</v>
+      </c>
+      <c r="H67" s="544" t="n">
+        <v>30.22581793840264</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="378" t="inlineStr">
+        <is>
+          <t>WACC:</t>
+        </is>
+      </c>
+      <c r="C68" s="118" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D68" s="544" t="n">
+        <v>27.23096234006731</v>
+      </c>
+      <c r="E68" s="544" t="n">
+        <v>29.69362414158428</v>
+      </c>
+      <c r="F68" s="544" t="n">
+        <v>32.46411866829089</v>
+      </c>
+      <c r="G68" s="544" t="n">
+        <v>35.60401246522503</v>
+      </c>
+      <c r="H68" s="544" t="n">
+        <v>39.19246251886405</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" s="118" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D69" s="544" t="n">
+        <v>34.80938263855841</v>
+      </c>
+      <c r="E69" s="544" t="n">
+        <v>38.07690951359217</v>
+      </c>
+      <c r="F69" s="544" t="n">
+        <v>41.81122594220219</v>
+      </c>
+      <c r="G69" s="544" t="n">
+        <v>46.12005259059837</v>
+      </c>
+      <c r="H69" s="544" t="n">
+        <v>51.14701701372724</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" s="118" t="n">
+        <v>0.09000000000000002</v>
+      </c>
+      <c r="D70" s="544" t="n">
+        <v>44.55696853151758</v>
+      </c>
+      <c r="E70" s="544" t="n">
+        <v>49.04257596668177</v>
+      </c>
+      <c r="F70" s="544" t="n">
+        <v>54.27578464103998</v>
+      </c>
+      <c r="G70" s="544" t="n">
+        <v>60.46048580164512</v>
+      </c>
+      <c r="H70" s="544" t="n">
+        <v>67.88212719437132</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" s="119" t="n">
+        <v>0.08000000000000003</v>
+      </c>
+      <c r="D71" s="544" t="n">
+        <v>57.55850136891461</v>
+      </c>
+      <c r="E71" s="544" t="n">
+        <v>63.99933238889363</v>
+      </c>
+      <c r="F71" s="544" t="n">
+        <v>71.72832961286849</v>
+      </c>
+      <c r="G71" s="544" t="n">
+        <v>81.17488177550437</v>
+      </c>
+      <c r="H71" s="544" t="n">
+        <v>92.98307197879927</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="D72" s="544" t="n"/>
+      <c r="E72" s="544" t="n"/>
+      <c r="F72" s="544" t="n"/>
+      <c r="G72" s="544" t="n"/>
+      <c r="H72" s="544" t="n"/>
+    </row>
+    <row r="73" ht="17.25" customHeight="1" s="244">
+      <c r="C73" s="112" t="inlineStr">
+        <is>
+          <t>Equity value per share</t>
+        </is>
+      </c>
+      <c r="D73" s="112" t="n"/>
+      <c r="E73" s="112" t="n"/>
+      <c r="F73" s="112" t="n"/>
+      <c r="G73" s="112" t="n"/>
+      <c r="H73" s="112" t="n"/>
+    </row>
+    <row r="74">
+      <c r="D74" s="290" t="inlineStr">
+        <is>
+          <t>Exit EBITDA Multiple</t>
+        </is>
+      </c>
+      <c r="E74" s="290" t="n"/>
+      <c r="F74" s="290" t="n"/>
+      <c r="G74" s="290" t="n"/>
+      <c r="H74" s="290" t="n"/>
+    </row>
+    <row r="75">
+      <c r="C75" s="545" t="n">
+        <v>32.82858242889715</v>
+      </c>
+      <c r="D75" s="546" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E75" s="546" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F75" s="547" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G75" s="546" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H75" s="548" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" s="123" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D76" s="544" t="n">
+        <v>15.50961852638511</v>
+      </c>
+      <c r="E76" s="544" t="n">
+        <v>17.96661853265726</v>
+      </c>
+      <c r="F76" s="544" t="n">
+        <v>20.4236185389294</v>
+      </c>
+      <c r="G76" s="544" t="n">
+        <v>22.88061854520155</v>
+      </c>
+      <c r="H76" s="544" t="n">
+        <v>25.33761855147371</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="C77" s="124" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D77" s="544" t="n">
+        <v>17.14475130521146</v>
+      </c>
+      <c r="E77" s="544" t="n">
+        <v>19.69981500877978</v>
+      </c>
+      <c r="F77" s="544" t="n">
+        <v>22.25487871234807</v>
+      </c>
+      <c r="G77" s="544" t="n">
+        <v>24.80994241591637</v>
+      </c>
+      <c r="H77" s="544" t="n">
+        <v>27.36500611948468</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="378" t="inlineStr">
+        <is>
+          <t>WACC:</t>
+        </is>
+      </c>
+      <c r="C78" s="124" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D78" s="544" t="n">
+        <v>18.85618541009948</v>
+      </c>
+      <c r="E78" s="544" t="n">
+        <v>21.51415951294241</v>
+      </c>
+      <c r="F78" s="544" t="n">
+        <v>24.17213361578533</v>
+      </c>
+      <c r="G78" s="544" t="n">
+        <v>26.83010771862826</v>
+      </c>
+      <c r="H78" s="544" t="n">
+        <v>29.48808182147118</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" s="124" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D79" s="544" t="n">
+        <v>20.64830251596892</v>
+      </c>
+      <c r="E79" s="544" t="n">
+        <v>23.41432021461313</v>
+      </c>
+      <c r="F79" s="544" t="n">
+        <v>26.18033791325734</v>
+      </c>
+      <c r="G79" s="544" t="n">
+        <v>28.94635561190155</v>
+      </c>
+      <c r="H79" s="544" t="n">
+        <v>31.71237331054576</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="C80" s="124" t="n">
+        <v>0.09000000000000002</v>
+      </c>
+      <c r="D80" s="544" t="n">
+        <v>22.52578129267701</v>
+      </c>
+      <c r="E80" s="544" t="n">
+        <v>25.40528204016064</v>
+      </c>
+      <c r="F80" s="544" t="n">
+        <v>28.28478278764427</v>
+      </c>
+      <c r="G80" s="544" t="n">
+        <v>31.16428353512789</v>
+      </c>
+      <c r="H80" s="544" t="n">
+        <v>34.04378428261153</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" s="125" t="n">
+        <v>0.08000000000000003</v>
+      </c>
+      <c r="D81" s="544" t="n">
+        <v>24.49362060261981</v>
+      </c>
+      <c r="E81" s="544" t="n">
+        <v>27.49237143226065</v>
+      </c>
+      <c r="F81" s="544" t="n">
+        <v>30.49112226190149</v>
+      </c>
+      <c r="G81" s="544" t="n">
+        <v>33.48987309154233</v>
+      </c>
+      <c r="H81" s="544" t="n">
+        <v>36.4886239211832</v>
+      </c>
+    </row>
+    <row r="82"/>
+    <row r="83" ht="17.25" customHeight="1" s="244">
+      <c r="C83" s="112" t="inlineStr">
+        <is>
+          <t>Equity value per share</t>
+        </is>
+      </c>
+      <c r="D83" s="112" t="n"/>
+      <c r="E83" s="112" t="n"/>
+      <c r="F83" s="112" t="n"/>
+      <c r="G83" s="112" t="n"/>
+      <c r="H83" s="112" t="n"/>
+    </row>
+    <row r="84">
+      <c r="D84" s="290" t="inlineStr">
+        <is>
+          <t>Exit EBITDA Multiple</t>
+        </is>
+      </c>
+      <c r="E84" s="290" t="n"/>
+      <c r="F84" s="290" t="n"/>
+      <c r="G84" s="290" t="n"/>
+      <c r="H84" s="290" t="n"/>
+    </row>
+    <row r="85">
+      <c r="C85" s="195" t="inlineStr">
+        <is>
+          <t>EBITDA % of plan</t>
+        </is>
+      </c>
+      <c r="D85" s="549" t="n">
+        <v>32.82858242889715</v>
+      </c>
+      <c r="E85" s="550" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F85" s="546" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G85" s="547" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H85" s="548" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="C86" s="132" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D86" s="127" t="n">
+        <v>981.7144138269495</v>
+      </c>
+      <c r="E86" s="544" t="n">
+        <v>47.84757390464826</v>
+      </c>
+      <c r="F86" s="544" t="n">
+        <v>49.91146747628064</v>
+      </c>
+      <c r="G86" s="544" t="n">
+        <v>51.97536104791303</v>
+      </c>
+      <c r="H86" s="544" t="n">
+        <v>54.03925461954542</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" s="133" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D87" s="128" t="n">
+        <v>1104.428715555318</v>
+      </c>
+      <c r="E87" s="544" t="n">
+        <v>51.09820627996928</v>
+      </c>
+      <c r="F87" s="544" t="n">
+        <v>53.42008654805571</v>
+      </c>
+      <c r="G87" s="544" t="n">
+        <v>55.74196681614215</v>
+      </c>
+      <c r="H87" s="544" t="n">
+        <v>58.06384708422858</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="C88" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="129" t="n">
+        <v>1227.143017283687</v>
+      </c>
+      <c r="E88" s="544" t="n">
+        <v>54.34883865529027</v>
+      </c>
+      <c r="F88" s="544" t="n">
+        <v>56.92870561983077</v>
+      </c>
+      <c r="G88" s="544" t="n">
+        <v>59.50857258437125</v>
+      </c>
+      <c r="H88" s="544" t="n">
+        <v>62.08843954891173</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="C89" s="133" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D89" s="128" t="n">
+        <v>1349.857319012056</v>
+      </c>
+      <c r="E89" s="544" t="n">
+        <v>57.59947103061128</v>
+      </c>
+      <c r="F89" s="544" t="n">
+        <v>60.43732469160583</v>
+      </c>
+      <c r="G89" s="544" t="n">
+        <v>63.27517835260036</v>
+      </c>
+      <c r="H89" s="544" t="n">
+        <v>66.1130320135949</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="C90" s="133" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D90" s="128" t="n">
+        <v>1472.571620740424</v>
+      </c>
+      <c r="E90" s="544" t="n">
+        <v>60.85010340593232</v>
+      </c>
+      <c r="F90" s="544" t="n">
+        <v>63.9459437633809</v>
+      </c>
+      <c r="G90" s="544" t="n">
+        <v>67.04178412082949</v>
+      </c>
+      <c r="H90" s="544" t="n">
+        <v>70.13762447827806</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="C91" s="133" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D91" s="130" t="n">
+        <v>1595.285922468793</v>
+      </c>
+      <c r="E91" s="544" t="n">
+        <v>1472.571620740424</v>
+      </c>
+      <c r="F91" s="544" t="n">
+        <v>1472.571620740424</v>
+      </c>
+      <c r="G91" s="544" t="n">
+        <v>1472.571620740424</v>
+      </c>
+      <c r="H91" s="544" t="n">
+        <v>1472.571620740424</v>
+      </c>
+    </row>
+    <row r="92"/>
+    <row r="93" ht="15.75" customHeight="1" s="244" thickBot="1">
+      <c r="B93" s="63" t="inlineStr">
+        <is>
+          <t>Football field</t>
+        </is>
+      </c>
+      <c r="C93" s="93" t="n"/>
+      <c r="D93" s="93" t="n"/>
+      <c r="E93" s="93" t="n"/>
+    </row>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114">
+      <c r="B114" s="108" t="n"/>
+      <c r="C114" s="109" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D114" s="109" t="inlineStr">
+        <is>
+          <t>Diff.</t>
+        </is>
+      </c>
+      <c r="E114" s="110" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="105" t="inlineStr">
+        <is>
+          <t>DCF Value at 6.3x-8.3x Exit EBITDA Range</t>
+        </is>
+      </c>
+      <c r="C115" s="544" t="n">
+        <v>20.64830251596892</v>
+      </c>
+      <c r="D115" s="544" t="n">
+        <v>11.06407079457684</v>
+      </c>
+      <c r="E115" s="551" t="n">
+        <v>31.71237331054576</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="102" t="inlineStr">
+        <is>
+          <t>DCF Value at 2.0%-4.0% Perpetuity Range</t>
+        </is>
+      </c>
+      <c r="C116" s="544" t="n">
+        <v>34.80938263855841</v>
+      </c>
+      <c r="D116" s="544" t="n">
+        <v>16.33763437516883</v>
+      </c>
+      <c r="E116" s="551" t="n">
+        <v>51.14701701372724</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="102" t="inlineStr">
+        <is>
+          <t>LBO Value at 15.0%-35.0% Sponsor Hurdle Rate</t>
+        </is>
+      </c>
+      <c r="C117" s="544" t="n">
+        <v>45.45104265824024</v>
+      </c>
+      <c r="D117" s="544" t="n">
+        <v>13.0196839013479</v>
+      </c>
+      <c r="E117" s="551" t="n">
+        <v>58.47072655958814</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="106" t="inlineStr">
+        <is>
+          <t>52 Week Market High/Low</t>
+        </is>
+      </c>
+      <c r="C118" s="552" t="n">
+        <v>37.51</v>
+      </c>
+      <c r="D118" s="552" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="E118" s="553" t="n">
+        <v>46.33</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D66:H71">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>$C$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D76:H81">
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
+      <formula>$C$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E86:H91">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>$C$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation sqref="C31" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"End of period,Middle of period"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
 </file>
--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -10812,7 +10812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4" customWidth="1" style="244" min="2" max="2"/>
@@ -11888,6 +11888,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="564" t="inlineStr">
         <is>
@@ -11904,6 +11905,27 @@
     </row>
     <row r="39">
       <c r="B39" s="593" t="inlineStr">
+        <is>
+          <t>PDF: all driver sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="564" t="inlineStr">
+        <is>
+          <t>SOURCE MAP: open Assumptions_Drivers — columns E (link), F (~30-word justification), G (secondary link) on each driver row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="593" t="inlineStr">
+        <is>
+          <t>Jump to AI infra source row (E9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="593" t="inlineStr">
         <is>
           <t>PDF: all driver sources</t>
         </is>
@@ -11954,6 +11976,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12374,7 +12398,7 @@
       </c>
       <c r="F16" s="573" t="inlineStr">
         <is>
-          <t>Institutional TLB commonly prices SOFR+300–500bps. SOFR+500bps is the upper published band—credit-market priced, not changed by internal AI software strategy.</t>
+          <t>Institutional Term Loan B commonly prices SOFR+300–500bps in LBO guides. SOFR+500bps is the upper published band—set by syndicated loan markets, not by the company’s internal AI software strategy.</t>
         </is>
       </c>
       <c r="G16" s="593" t="inlineStr">
@@ -12404,7 +12428,7 @@
       </c>
       <c r="F17" s="573" t="inlineStr">
         <is>
-          <t>Market-standard institutional TLB schedules ~1% annual amortization with a bullet at maturity. Kept fixed because loan docs—not AI FCF—set the mandatory floor.</t>
+          <t>Market-standard institutional TLB schedules about 1% annual amortization with a bullet at maturity. We keep 1% fixed because credit agreements—not AI-generated FCF—set the mandatory repayment floor.</t>
         </is>
       </c>
       <c r="G17" s="593" t="inlineStr">
@@ -12524,7 +12548,7 @@
       </c>
       <c r="F21" s="573" t="inlineStr">
         <is>
-          <t>Company-reported FY24 S&amp;M = $414.1m (~34% of $1,214.3m revenue). Model uses ~$425m (~35%) as a rounded baseline consistent with that filing.</t>
+          <t>Company-reported FY24 sales &amp; marketing expense = $414.1m on $1,214.3m revenue (~34%). The model’s ~$425m (~35%) baseline is a rounded figure consistent with that audited filing disclosure.</t>
         </is>
       </c>
       <c r="G21" s="593" t="inlineStr">

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -6,9 +6,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11910" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Strategy_Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="00_Assumptions_List" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Assumptions_Drivers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Assumptions_Drivers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Strategy_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="00_Assumptions_List" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Debt_Sweep_AI" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Base_Operating" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="AI_Operating" sheetId="6" state="visible" r:id="rId6"/>
@@ -59,7 +59,7 @@
     <definedName name="One">'[1]Forecast Drivers'!$D$330</definedName>
     <definedName name="Products">[2]Array0!$B$5:$C$7</definedName>
     <definedName name="Rev">'[1]Forecast Drivers'!$E$25:$S$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'00_Assumptions_List'!$B$6:$M$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'00_Assumptions_List'!$B$6:$M$21</definedName>
     <definedName name="CIQWBGuid" localSheetId="6" hidden="1">"ab508404-a108-4d4f-b84c-e5fce791e559"</definedName>
   </definedNames>
   <calcPr calcId="152511" calcMode="autoNoTable" fullCalcOnLoad="1" iterate="1"/>
@@ -153,7 +153,7 @@
     <numFmt numFmtId="245" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
     <numFmt numFmtId="246" formatCode="###0&quot;E&quot;_)"/>
   </numFmts>
-  <fonts count="111">
+  <fonts count="113">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -871,6 +871,17 @@
       <sz val="9"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000000FF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="39">
     <fill>
@@ -1811,7 +1822,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="595">
+  <cellXfs count="602">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2856,6 +2867,15 @@
     <xf numFmtId="0" fontId="109" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="111" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="112" fillId="37" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="190" fontId="112" fillId="37" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="112" fillId="37" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="192" fontId="112" fillId="37" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="187">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4904,291 +4924,979 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="32" customWidth="1" style="244" min="2" max="2"/>
-    <col width="14" customWidth="1" style="244" min="3" max="3"/>
-    <col width="14" customWidth="1" style="244" min="4" max="4"/>
-    <col width="14" customWidth="1" style="244" min="5" max="5"/>
-    <col width="70" customWidth="1" style="244" min="6" max="6"/>
+    <col width="28" customWidth="1" style="244" min="2" max="2"/>
+    <col width="10" customWidth="1" style="244" min="3" max="3"/>
+    <col width="55" customWidth="1" style="244" min="4" max="4"/>
+    <col width="40" customWidth="1" style="244" min="5" max="5"/>
+    <col width="48" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
-          <t>vengeanceaiUSC-LBOMODEL2 — Strategy Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AI-SDR cost takeout drives margin, FCF, debt paydown, MOIC/IRR — exit multiple held at 13x in both cases</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="B5" s="564" t="inlineStr">
-        <is>
-          <t>RESULTS — AI vs Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="412" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="C6" s="412" t="inlineStr">
-        <is>
-          <t>Base (no AI)</t>
-        </is>
-      </c>
-      <c r="D6" s="412" t="inlineStr">
-        <is>
-          <t>AI-SDR case</t>
-        </is>
-      </c>
-      <c r="E6" s="412" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-      <c r="F6" s="412" t="inlineStr">
-        <is>
-          <t>COMMENTARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1" s="244">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Y2 EBITDA margin</t>
-        </is>
-      </c>
-      <c r="C7" s="565" t="n">
-        <v>0.1085118998600017</v>
-      </c>
-      <c r="D7" s="565" t="n">
-        <v>0.2012029241075531</v>
-      </c>
-      <c r="E7" s="565" t="n">
-        <v>0.09269102424755141</v>
-      </c>
-      <c r="F7" s="566" t="inlineStr">
-        <is>
-          <t>Year 2 operating profitability under 10% growth / 80% GM / AI S&amp;M path.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1" s="244">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Y2 margin vs baseline (bps)</t>
-        </is>
-      </c>
-      <c r="C8" s="567" t="n">
-        <v>-422.7456147574727</v>
-      </c>
-      <c r="D8" s="567" t="n">
-        <v>504.1646277180415</v>
-      </c>
-      <c r="E8" s="567" t="n">
-        <v>926.9102424755141</v>
-      </c>
-      <c r="F8" s="566" t="inlineStr">
-        <is>
-          <t>Y2 EBITDA margin minus FY24 baseline margin, in basis points (target ≥500).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1" s="244">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Y5 EBITDA ($m)</t>
-        </is>
-      </c>
-      <c r="C9" s="567" t="n">
-        <v>212.2104606600003</v>
-      </c>
-      <c r="D9" s="567" t="n">
-        <v>496.3963076296004</v>
-      </c>
-      <c r="E9" s="567" t="n">
-        <v>284.1858469696001</v>
-      </c>
-      <c r="F9" s="566" t="inlineStr">
-        <is>
-          <t>Year 5 EBITDA ($m).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1" s="244">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Exit EV @ 13x ($m)</t>
-        </is>
-      </c>
-      <c r="C10" s="567" t="n">
-        <v>2758.735988580003</v>
-      </c>
-      <c r="D10" s="567" t="n">
-        <v>6453.151999184804</v>
-      </c>
-      <c r="E10" s="567" t="n">
-        <v>3694.416010604801</v>
-      </c>
-      <c r="F10" s="566" t="inlineStr">
-        <is>
-          <t>Exit EV = Y5 EBITDA × 13x (Assumptions_Drivers!C20 / LBO!D17).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1" s="244">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Exit net debt ($m)</t>
-        </is>
-      </c>
-      <c r="C11" s="567" t="n">
-        <v>557.1124750633038</v>
-      </c>
-      <c r="D11" s="567" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="567" t="n">
-        <v>-557.1124750633038</v>
-      </c>
-      <c r="F11" s="566" t="inlineStr">
-        <is>
-          <t>Ending net debt after mandatory amort + 100% cash sweep.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1" s="244">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Exit equity value ($m)</t>
-        </is>
-      </c>
-      <c r="C12" s="567" t="n">
-        <v>2201.623513516699</v>
-      </c>
-      <c r="D12" s="567" t="n">
-        <v>6453.151999184804</v>
-      </c>
-      <c r="E12" s="567" t="n">
-        <v>4251.528485668105</v>
-      </c>
-      <c r="F12" s="566" t="inlineStr">
-        <is>
-          <t>Exit equity = Exit EV − ending debt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" s="244">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="C13" s="568" t="n">
-        <v>1.17652754423803</v>
-      </c>
-      <c r="D13" s="568" t="n">
-        <v>3.448505626681045</v>
-      </c>
-      <c r="E13" s="568" t="n">
-        <v>2.271978082443015</v>
-      </c>
-      <c r="F13" s="566" t="inlineStr">
-        <is>
-          <t>MOIC = Exit equity / sponsor equity check.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1" s="244">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>IRR (5-year)</t>
-        </is>
-      </c>
-      <c r="C14" s="565" t="n">
-        <v>0.03304780632992022</v>
-      </c>
-      <c r="D14" s="565" t="n">
-        <v>0.2809323319237782</v>
-      </c>
-      <c r="E14" s="565" t="n">
-        <v>0.247884525593858</v>
-      </c>
-      <c r="F14" s="566" t="inlineStr">
-        <is>
-          <t>IRR over 5 years = MOIC^(1/5) − 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="B16" s="569" t="inlineStr">
-        <is>
-          <t>IRR uplift from AI S&amp;M: 24.8 percentage points | Y2 margin expansion: 504 bps (target ≥500: YES)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PDF assumptions list:</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="570" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>In-Excel full commentary: 00_Assumptions_List | Drivers: Assumptions_Drivers</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Every Assumptions_Drivers input has a source link + justification in columns E–G (same row).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="593" t="inlineStr">
-        <is>
-          <t>Go to Assumptions_Drivers source columns</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="593" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_AI_COST_SOURCES.pdf</t>
+          <t>Assumptions Drivers — EVERY row: Value + Why reasonable + Source link + clickable Feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1" s="244">
+      <c r="B3" s="574" t="inlineStr">
+        <is>
+          <t>Columns on the SAME row as each driver: D = why reasonable (model commentary); E = clickable source URL; F = ~30-word source credibility; G = clickable Feeds jump into the model. No separate AI cost tab — all evidence lives here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" s="244">
+      <c r="B4" s="595" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="C4" s="595" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D4" s="595" t="inlineStr">
+        <is>
+          <t>Why this number is reasonable (model commentary)</t>
+        </is>
+      </c>
+      <c r="E4" s="595" t="inlineStr">
+        <is>
+          <t>Source link (click)</t>
+        </is>
+      </c>
+      <c r="F4" s="595" t="inlineStr">
+        <is>
+          <t>Source credibility / why we can use it (~30 words)</t>
+        </is>
+      </c>
+      <c r="G4" s="595" t="inlineStr">
+        <is>
+          <t>Feeds (click to jump)</t>
+        </is>
+      </c>
+      <c r="H4" s="595" t="inlineStr">
+        <is>
+          <t>Secondary source (click)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1" s="244">
+      <c r="B5" s="596" t="inlineStr">
+        <is>
+          <t>Revenue growth</t>
+        </is>
+      </c>
+      <c r="C5" s="597" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="573" t="inlineStr">
+        <is>
+          <t>Assumes steady top-line expansion. Reasonable for a mature enterprise software company, avoiding aggressive hypergrowth assumptions while maintaining a healthy, realistic sales trajectory.</t>
+        </is>
+      </c>
+      <c r="E5" s="593" t="inlineStr">
+        <is>
+          <t>ZoomInfo FY2024 results (BusinessWire)</t>
+        </is>
+      </c>
+      <c r="F5" s="573" t="inlineStr">
+        <is>
+          <t>ZI disclosed FY24 revenue of $1,214.3m (−2% YoY). Using 10% forward growth is a mature-SaaS recovery underwrite held equal in AI vs Base—not hypergrowth.</t>
+        </is>
+      </c>
+      <c r="G5" s="593" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D5 (Revenue)</t>
+        </is>
+      </c>
+      <c r="H5" s="593" t="inlineStr">
+        <is>
+          <t>valueaddvc.com/blog/saas-evebitda-multiples-explained-benchmarks-and-w</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1" s="244">
+      <c r="B6" s="596" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="C6" s="597" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D6" s="573" t="inlineStr">
+        <is>
+          <t>High profitability on direct services. Highly reasonable for a SaaS company, which historically scales digital infrastructure with minimal incremental cost per user.</t>
+        </is>
+      </c>
+      <c r="E6" s="593" t="inlineStr">
+        <is>
+          <t>Aleph/Benchmarkit SaaS GM median ~80%</t>
+        </is>
+      </c>
+      <c r="F6" s="573" t="inlineStr">
+        <is>
+          <t>Independent SaaS benchmarks put software median GM near 80%; ZI already prints ~84% GAAP GM, so 80% is conservative and industry-standard.</t>
+        </is>
+      </c>
+      <c r="G6" s="593" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D6 (COGS)</t>
+        </is>
+      </c>
+      <c r="H6" s="593" t="inlineStr">
+        <is>
+          <t>www.readyratios.com/sec/GTM_zoominfo-technologies-inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1" s="244">
+      <c r="B7" s="596" t="inlineStr">
+        <is>
+          <t>Sales payroll cut (Y1)</t>
+        </is>
+      </c>
+      <c r="C7" s="597" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D7" s="573" t="inlineStr">
+        <is>
+          <t>Immediate headcount reduction for human SDRs. Reasonable as a private equity cost-cutting measure, easily achieved by eliminating the lower-tier outbound sales team.</t>
+        </is>
+      </c>
+      <c r="E7" s="593" t="inlineStr">
+        <is>
+          <t>AI SDR vs human SDR cost/meeting analysis</t>
+        </is>
+      </c>
+      <c r="F7" s="573" t="inlineStr">
+        <is>
+          <t>Published outbound economics show fully loaded human SDRs far costlier than AI stacks. −15% Y1 payroll is a modest PE-style cut of outbound headcount, not a full S&amp;M wipeout.</t>
+        </is>
+      </c>
+      <c r="G7" s="593" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D7 (Sales payroll)</t>
+        </is>
+      </c>
+      <c r="H7" s="593" t="inlineStr">
+        <is>
+          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1" s="244">
+      <c r="B8" s="596" t="inlineStr">
+        <is>
+          <t>Variable commission cut</t>
+        </is>
+      </c>
+      <c r="C8" s="597" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D8" s="573" t="inlineStr">
+        <is>
+          <t>Reduces payouts for automated sales. Reasonable because AI agents do not collect commission checks, retaining more profit per enterprise deal directly for the company.</t>
+        </is>
+      </c>
+      <c r="E8" s="593" t="inlineStr">
+        <is>
+          <t>SDR pay mix ~70/30 base/variable (SyncGTM)</t>
+        </is>
+      </c>
+      <c r="F8" s="573" t="inlineStr">
+        <is>
+          <t>SaaS SDR OTE is typically ~70% base / ~30% variable. Replacing humans with AI shrinks the commission pool; −20% is a partial cut of that variable layer.</t>
+        </is>
+      </c>
+      <c r="G8" s="593" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D8 (Commissions)</t>
+        </is>
+      </c>
+      <c r="H8" s="593" t="inlineStr">
+        <is>
+          <t>syncgtm.com/blog/how-much-do-sales-development-representatives-make-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1" s="244">
+      <c r="B9" s="596" t="inlineStr">
+        <is>
+          <t>AI infrastructure ($m)</t>
+        </is>
+      </c>
+      <c r="C9" s="598" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" s="573" t="inlineStr">
+        <is>
+          <t>Fixed cost for AI software and compute. Reasonable estimate for enterprise-scale AI deployment, covering API calls and infrastructure needed to replace human reps.</t>
+        </is>
+      </c>
+      <c r="E9" s="593" t="inlineStr">
+        <is>
+          <t>Salesforce Agentforce $2/conv + Flex Credits press</t>
+        </is>
+      </c>
+      <c r="F9" s="573" t="inlineStr">
+        <is>
+          <t>SF publishes $2/conversation and ~$0.10/action. At ZI scale (~378 outbound roles = 25% of 1,513 S&amp;M), $5–10k/mo agents imply ~$23–45m; $15m is conservative.</t>
+        </is>
+      </c>
+      <c r="G9" s="593" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D10 (AI infrastructure)</t>
+        </is>
+      </c>
+      <c r="H9" s="593" t="inlineStr">
+        <is>
+          <t>highticketaisystems.com/blog/ai-sdr-pricing-explained</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1" s="244">
+      <c r="B10" s="596" t="inlineStr">
+        <is>
+          <t>S&amp;M expense growth Y2+</t>
+        </is>
+      </c>
+      <c r="C10" s="597" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D10" s="573" t="inlineStr">
+        <is>
+          <t>Caps future marketing cost increases. Reasonable because AI scales infinitely without needing proportional headcount additions, severing the link between revenue growth and human hiring.</t>
+        </is>
+      </c>
+      <c r="E10" s="593" t="inlineStr">
+        <is>
+          <t>Gartner: agentic AI / inference scales as opex</t>
+        </is>
+      </c>
+      <c r="F10" s="573" t="inlineStr">
+        <is>
+          <t>Gartner documents production agentic AI as inference opex that scales without linear headcount. Cap S&amp;M growth at 2% to model that break from revenue-linked hiring.</t>
+        </is>
+      </c>
+      <c r="G10" s="593" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!E7 (payroll Y2+)</t>
+        </is>
+      </c>
+      <c r="H10" s="593" t="inlineStr">
+        <is>
+          <t>www.ciodive.com/news/AI-spending-soars-enterprise-maturity/827488/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1" s="244">
+      <c r="B11" s="596" t="inlineStr">
+        <is>
+          <t>G&amp;A % of revenue</t>
+        </is>
+      </c>
+      <c r="C11" s="597" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D11" s="573" t="inlineStr">
+        <is>
+          <t>General administrative overhead costs. Reasonable for a public-to-private SaaS company, maintaining standard corporate expenses without relying on unrealistic operational magic outside of sales.</t>
+        </is>
+      </c>
+      <c r="E11" s="593" t="inlineStr">
+        <is>
+          <t>ZoomInfo FY24 G&amp;A $295.3m (company results)</t>
+        </is>
+      </c>
+      <c r="F11" s="573" t="inlineStr">
+        <is>
+          <t>ZI FY24 G&amp;A was $295.3m (~24% of revenue). Locking ~18% keeps standard corporate overhead while the thesis only attacks the sales floor—not finance/comp magic.</t>
+        </is>
+      </c>
+      <c r="G11" s="593" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D12 (G&amp;A)</t>
+        </is>
+      </c>
+      <c r="H11" s="593" t="inlineStr">
+        <is>
+          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1" s="244">
+      <c r="B12" s="596" t="inlineStr">
+        <is>
+          <t>CapEx reduction vs base</t>
+        </is>
+      </c>
+      <c r="C12" s="597" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D12" s="573" t="inlineStr">
+        <is>
+          <t>Lowers physical equipment spending. Reasonable because firing 15% of the sales team permanently eliminates the need to purchase and refresh their laptops and hardware.</t>
+        </is>
+      </c>
+      <c r="E12" s="593" t="inlineStr">
+        <is>
+          <t>In-house SDR all-in includes devices/tooling</t>
+        </is>
+      </c>
+      <c r="F12" s="573" t="inlineStr">
+        <is>
+          <t>Human SDR all-in budgets include laptops and seats. Cutting outbound humans removes refresh CapEx; −5% vs base CapEx rate is a small, directionally correct haircut.</t>
+        </is>
+      </c>
+      <c r="G12" s="593" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D19 (CapEx)</t>
+        </is>
+      </c>
+      <c r="H12" s="593" t="inlineStr">
+        <is>
+          <t>firstsales.io/blog/cost-per-meeting-outbound/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1" s="244">
+      <c r="B13" s="596" t="inlineStr">
+        <is>
+          <t>WC / receivables improvement</t>
+        </is>
+      </c>
+      <c r="C13" s="597" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" s="573" t="inlineStr">
+        <is>
+          <t>Speeds up cash collection from clients. Reasonable because automated AI billing systems can aggressively follow up on late invoices, freeing up cash for debt paydown.</t>
+        </is>
+      </c>
+      <c r="E13" s="593" t="inlineStr">
+        <is>
+          <t>ZI receivables ~80 days (SEC-derived ratios)</t>
+        </is>
+      </c>
+      <c r="F13" s="573" t="inlineStr">
+        <is>
+          <t>ZI receivables ~80 days show WC is real. Automated billing follow-ups can shorten DSO; −10% WC intensity vs base is a modest collections gain, not a wipeout.</t>
+        </is>
+      </c>
+      <c r="G13" s="593" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D20 (ΔNWC)</t>
+        </is>
+      </c>
+      <c r="H13" s="593" t="inlineStr">
+        <is>
+          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1" s="244">
+      <c r="B14" s="596" t="inlineStr">
+        <is>
+          <t>SOFR</t>
+        </is>
+      </c>
+      <c r="C14" s="599" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="D14" s="573" t="inlineStr">
+        <is>
+          <t>The foundational secured lending interest rate. Reasonable and historically accurate for the macroeconomic environment, properly reflecting actual institutional baseline borrowing costs.</t>
+        </is>
+      </c>
+      <c r="E14" s="593" t="inlineStr">
+        <is>
+          <t>NY Fed official SOFR reference rate</t>
+        </is>
+      </c>
+      <c r="F14" s="573" t="inlineStr">
+        <is>
+          <t>SOFR is the NY Fed’s official overnight Treasury-repo financing benchmark used to price leveraged loans. ~4.3% is a planning level near recent SOFR prints (see FRED).</t>
+        </is>
+      </c>
+      <c r="G14" s="593" t="inlineStr">
+        <is>
+          <t>Go to Debt_Sweep_AI!C12 (TLA rate uses SOFR)</t>
+        </is>
+      </c>
+      <c r="H14" s="593" t="inlineStr">
+        <is>
+          <t>fred.stlouisfed.org/series/SOFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1" s="244">
+      <c r="B15" s="596" t="inlineStr">
+        <is>
+          <t>Term Loan A spread</t>
+        </is>
+      </c>
+      <c r="C15" s="599" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D15" s="573" t="inlineStr">
+        <is>
+          <t>The risk premium for senior debt. Reasonable for a standard LBO, reflecting typical syndicated commercial bank pricing for secured corporate borrowing.</t>
+        </is>
+      </c>
+      <c r="E15" s="593" t="inlineStr">
+        <is>
+          <t>LBO debt structure: TLA illustrative spreads</t>
+        </is>
+      </c>
+      <c r="F15" s="573" t="inlineStr">
+        <is>
+          <t>Bank TLA in LBO guides typically prices tighter than TLB (often SOFR+~275–375bps). SOFR+400bps is a conservative senior bank spread independent of AI ops.</t>
+        </is>
+      </c>
+      <c r="G15" s="593" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C27 (TLA rate)</t>
+        </is>
+      </c>
+      <c r="H15" s="593" t="inlineStr">
+        <is>
+          <t>ibinterviewquestions.com/guides/debt-capital-markets/term-loan-b-tlb-m</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1" s="244">
+      <c r="B16" s="596" t="inlineStr">
+        <is>
+          <t>Term Loan B spread</t>
+        </is>
+      </c>
+      <c r="C16" s="599" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D16" s="573" t="inlineStr">
+        <is>
+          <t>The risk premium for riskier debt. Reasonable, as Term Loan B is usually held by institutional investors requiring higher yields for slightly higher risk.</t>
+        </is>
+      </c>
+      <c r="E16" s="593" t="inlineStr">
+        <is>
+          <t>TLB pricing often SOFR+300–500bps</t>
+        </is>
+      </c>
+      <c r="F16" s="573" t="inlineStr">
+        <is>
+          <t>Institutional TLB commonly prices SOFR+300–500bps. SOFR+500bps is the upper published band—set by syndicated loan markets, not by internal AI strategy.</t>
+        </is>
+      </c>
+      <c r="G16" s="593" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C28 (TLB rate)</t>
+        </is>
+      </c>
+      <c r="H16" s="593" t="inlineStr">
+        <is>
+          <t>ryanoconnellfinance.com/lbo-debt-structure/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1" s="244">
+      <c r="B17" s="596" t="inlineStr">
+        <is>
+          <t>Mandatory amortization</t>
+        </is>
+      </c>
+      <c r="C17" s="597" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D17" s="573" t="inlineStr">
+        <is>
+          <t>Required annual principal repayment. Highly reasonable and standard market practice for leveraged loans, forcing a tiny minimum debt reduction each year.</t>
+        </is>
+      </c>
+      <c r="E17" s="593" t="inlineStr">
+        <is>
+          <t>Syndicated TLB ~1% annual amort standard</t>
+        </is>
+      </c>
+      <c r="F17" s="573" t="inlineStr">
+        <is>
+          <t>Market-standard institutional TLB schedules ~1% annual amortization with a bullet maturity. Loan docs—not AI FCF—set this mandatory floor.</t>
+        </is>
+      </c>
+      <c r="G17" s="593" t="inlineStr">
+        <is>
+          <t>Go to Debt_Sweep_AI!D5 (Mandatory 1%)</t>
+        </is>
+      </c>
+      <c r="H17" s="593" t="inlineStr">
+        <is>
+          <t>clearvaluelending.com/glossary/term-loan-b</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1" s="244">
+      <c r="B18" s="596" t="inlineStr">
+        <is>
+          <t>Cash sweep %</t>
+        </is>
+      </c>
+      <c r="C18" s="597" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="573" t="inlineStr">
+        <is>
+          <t>Dedicates all excess cash to debt. Reasonable and standard for maximizing LBO returns, ensuring every free dollar generated immediately aggressively reduces outstanding leverage.</t>
+        </is>
+      </c>
+      <c r="E18" s="593" t="inlineStr">
+        <is>
+          <t>LBO optional prepay / excess cash practice</t>
+        </is>
+      </c>
+      <c r="F18" s="573" t="inlineStr">
+        <is>
+          <t>Sponsor LBOs typically sweep excess FCF to optional debt prepay after mandatory amort. 100% sweep maximizes deleveraging so AI margins hit MOIC/IRR.</t>
+        </is>
+      </c>
+      <c r="G18" s="593" t="inlineStr">
+        <is>
+          <t>Go to Debt_Sweep_AI!E5 (Total paydown)</t>
+        </is>
+      </c>
+      <c r="H18" s="593" t="inlineStr">
+        <is>
+          <t>ibinterviewquestions.com/guides/valuation-investment-banking/lbo-debt-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1" s="244">
+      <c r="B19" s="596" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="C19" s="597" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D19" s="573" t="inlineStr">
+        <is>
+          <t>Corporate income tax obligation. Perfectly reasonable because it strictly matches the current standard U.S. federal statutory corporate tax rate without aggressive tax-dodging assumptions.</t>
+        </is>
+      </c>
+      <c r="E19" s="593" t="inlineStr">
+        <is>
+          <t>PwC Tax Summaries: US federal CIT 21%</t>
+        </is>
+      </c>
+      <c r="F19" s="573" t="inlineStr">
+        <is>
+          <t>US federal corporate income tax is a flat 21% statutory rate. Operating-margin gains do not change the federal statutory rate used here.</t>
+        </is>
+      </c>
+      <c r="G19" s="593" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D18 (Net income)</t>
+        </is>
+      </c>
+      <c r="H19" s="593" t="inlineStr">
+        <is>
+          <t>tradingeconomics.com/united-states/corporate-tax-rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1" s="244">
+      <c r="B20" s="596" t="inlineStr">
+        <is>
+          <t>Exit EV/EBITDA multiple</t>
+        </is>
+      </c>
+      <c r="C20" s="600" t="n">
+        <v>13</v>
+      </c>
+      <c r="D20" s="573" t="inlineStr">
+        <is>
+          <t>The valuation multiple upon selling. Reasonable to keep it conservative; relying on a 13x exit assumes no market inflation, proving returns come from operational growth.</t>
+        </is>
+      </c>
+      <c r="E20" s="593" t="inlineStr">
+        <is>
+          <t>PE SaaS buyouts often ~15–22x EBITDA</t>
+        </is>
+      </c>
+      <c r="F20" s="573" t="inlineStr">
+        <is>
+          <t>PE SaaS deals often underwrite ~15–22x EBITDA. Locking exit at 13x in BOTH cases is deliberately conservative so returns come from ops, not multiple expansion.</t>
+        </is>
+      </c>
+      <c r="G20" s="593" t="inlineStr">
+        <is>
+          <t>Go to LBO!D17 (Exit multiple)</t>
+        </is>
+      </c>
+      <c r="H20" s="593" t="inlineStr">
+        <is>
+          <t>aventis-advisors.com/software-valuation-multiples/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1" s="244">
+      <c r="B21" s="596" t="inlineStr">
+        <is>
+          <t>S&amp;M baseline ($m)</t>
+        </is>
+      </c>
+      <c r="C21" s="598" t="n">
+        <v>425</v>
+      </c>
+      <c r="D21" s="573" t="inlineStr">
+        <is>
+          <t>This is historical assumptions without AI. Total initial sales spend is reasonable, representing roughly 35% of FY24 revenue, perfectly aligning with standard SaaS benchmarks.</t>
+        </is>
+      </c>
+      <c r="E21" s="593" t="inlineStr">
+        <is>
+          <t>ZI FY24 S&amp;M $414.1m on $1,214.3m revenue</t>
+        </is>
+      </c>
+      <c r="F21" s="573" t="inlineStr">
+        <is>
+          <t>Company-reported FY24 S&amp;M = $414.1m (~34% of $1,214.3m). Model ~$425m (~35%) is a rounded baseline consistent with that filing.</t>
+        </is>
+      </c>
+      <c r="G21" s="593" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!C9 (S&amp;M human FY24A)</t>
+        </is>
+      </c>
+      <c r="H21" s="593" t="inlineStr">
+        <is>
+          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1" s="244">
+      <c r="B22" s="596" t="inlineStr">
+        <is>
+          <t>Payroll baseline ($m)</t>
+        </is>
+      </c>
+      <c r="C22" s="598" t="n">
+        <v>318.8</v>
+      </c>
+      <c r="D22" s="573" t="inlineStr">
+        <is>
+          <t>This is historical assumptions without AI. The fixed salary portion is reasonable, representing 75% of S&amp;M, accurately reflecting that human software sales floors are base-salary heavy.</t>
+        </is>
+      </c>
+      <c r="E22" s="593" t="inlineStr">
+        <is>
+          <t>SDR OTE mostly base (~70%) — SyncGTM</t>
+        </is>
+      </c>
+      <c r="F22" s="573" t="inlineStr">
+        <is>
+          <t>With ~70/30 base/variable SDR mix, most people cost is payroll. Payroll baseline = 75% of S&amp;M matches that base-salary-heavy sales-floor structure.</t>
+        </is>
+      </c>
+      <c r="G22" s="593" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!C7 (Payroll FY24A)</t>
+        </is>
+      </c>
+      <c r="H22" s="593" t="inlineStr">
+        <is>
+          <t>pulserevops.com/knowledge/ra0197</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1" s="244">
+      <c r="B23" s="596" t="inlineStr">
+        <is>
+          <t>Commission baseline ($m)</t>
+        </is>
+      </c>
+      <c r="C23" s="598" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="D23" s="573" t="inlineStr">
+        <is>
+          <t>This is historical assumptions without AI. The variable payout is reasonable, calculating exactly to the remaining 25% of the budget, representing standard quota-based enterprise sales incentives.</t>
+        </is>
+      </c>
+      <c r="E23" s="593" t="inlineStr">
+        <is>
+          <t>Variable ~30–35% of tech SDR OTE</t>
+        </is>
+      </c>
+      <c r="F23" s="573" t="inlineStr">
+        <is>
+          <t>Tech SDR variable is typically ~30–35% of OTE. Setting commission pool at 25% of S&amp;M is a slightly conservative carve of total S&amp;M for variable payouts.</t>
+        </is>
+      </c>
+      <c r="G23" s="593" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!C8 (Commissions FY24A)</t>
+        </is>
+      </c>
+      <c r="H23" s="593" t="inlineStr">
+        <is>
+          <t>syncgtm.com/blog/how-to-pay-sales-development-rep</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1" s="244">
+      <c r="B24" s="596" t="inlineStr">
+        <is>
+          <t>CapEx base % of rev</t>
+        </is>
+      </c>
+      <c r="C24" s="597" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D24" s="573" t="inlineStr">
+        <is>
+          <t>This is historical assumptions without AI. Normal hardware and capitalized software spending is reasonable for asset-light tech companies investing heavily in code rather than factories.</t>
+        </is>
+      </c>
+      <c r="E24" s="593" t="inlineStr">
+        <is>
+          <t>ZI FY24 strong FCF / asset-light SaaS profile</t>
+        </is>
+      </c>
+      <c r="F24" s="573" t="inlineStr">
+        <is>
+          <t>SaaS is asset-light vs industrials; ZI still printed strong FY24 FCF. 2% of revenue is a simple maintenance CapEx planning rate before the AI −5% haircut.</t>
+        </is>
+      </c>
+      <c r="G24" s="593" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D19 (CapEx)</t>
+        </is>
+      </c>
+      <c r="H24" s="593" t="inlineStr">
+        <is>
+          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1" s="244">
+      <c r="B25" s="596" t="inlineStr">
+        <is>
+          <t>WC base % of Δrev</t>
+        </is>
+      </c>
+      <c r="C25" s="597" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D25" s="573" t="inlineStr">
+        <is>
+          <t>This is historical assumptions without AI. Normal working capital needs are reasonable, showing that as revenue grows, a small percentage of cash gets tied up in daily operations.</t>
+        </is>
+      </c>
+      <c r="E25" s="593" t="inlineStr">
+        <is>
+          <t>ZI receivables days ~80 (WC intensity)</t>
+        </is>
+      </c>
+      <c r="F25" s="573" t="inlineStr">
+        <is>
+          <t>Receivables ~80 days imply WC scales with growth. Using 2% of Δrevenue as ΔNWC is a simplified SaaS WC plug anchored to that receivables reality.</t>
+        </is>
+      </c>
+      <c r="G25" s="593" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D20 (ΔNWC)</t>
+        </is>
+      </c>
+      <c r="H25" s="593" t="inlineStr">
+        <is>
+          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="564" t="inlineStr">
+        <is>
+          <t>Computed rates (from SOFR + spreads above)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1" s="244">
+      <c r="B27" s="596" t="inlineStr">
+        <is>
+          <t>TLA rate (SOFR+4)</t>
+        </is>
+      </c>
+      <c r="C27" s="601">
+        <f>C14+C15</f>
+        <v/>
+      </c>
+      <c r="D27" s="573" t="inlineStr">
+        <is>
+          <t>Total Term Loan A interest. Mathematically correct and reasonable for the total borrowing cost demanded by senior lenders in this specific rate environment.</t>
+        </is>
+      </c>
+      <c r="E27" s="593" t="inlineStr">
+        <is>
+          <t>LBO TLA = SOFR + senior bank spread</t>
+        </is>
+      </c>
+      <c r="F27" s="573" t="inlineStr">
+        <is>
+          <t>Computed as SOFR (C14) + TLA spread (C15). All-in ~8.3% matches senior secured bank pricing in this SOFR + 400bps setup.</t>
+        </is>
+      </c>
+      <c r="G27" s="593" t="inlineStr">
+        <is>
+          <t>Go to Debt_Sweep_AI!C12 (TLA rate)</t>
+        </is>
+      </c>
+      <c r="H27" s="593" t="inlineStr">
+        <is>
+          <t>www.newyorkfed.org/markets/reference-rates/sofr</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1" s="244">
+      <c r="B28" s="596" t="inlineStr">
+        <is>
+          <t>TLB rate (SOFR+5)</t>
+        </is>
+      </c>
+      <c r="C28" s="601">
+        <f>C14+C16</f>
+        <v/>
+      </c>
+      <c r="D28" s="573" t="inlineStr">
+        <is>
+          <t>Total Term Loan B interest. Mathematically correct and perfectly reasonable, pricing the institutional debt risk appropriately above the safer Term Loan A.</t>
+        </is>
+      </c>
+      <c r="E28" s="593" t="inlineStr">
+        <is>
+          <t>LBO TLB = SOFR + institutional spread</t>
+        </is>
+      </c>
+      <c r="F28" s="573" t="inlineStr">
+        <is>
+          <t>Computed as SOFR (C14) + TLB spread (C16). All-in ~9.3% prices institutional TLB risk appropriately above TLA in this structure.</t>
+        </is>
+      </c>
+      <c r="G28" s="593" t="inlineStr">
+        <is>
+          <t>Go to Debt_Sweep_AI!D12 (TLB rate)</t>
+        </is>
+      </c>
+      <c r="H28" s="593" t="inlineStr">
+        <is>
+          <t>www.newyorkfed.org/markets/reference-rates/sofr</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="B30" s="564" t="inlineStr">
+        <is>
+          <t>PDF of this source map:</t>
+        </is>
+      </c>
+      <c r="C30" s="593" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_DRIVER_SOURCES.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="591" t="inlineStr">
+        <is>
+          <t>Educational / research use only — not investment advice.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:H3"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10807,6 +11515,302 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="32" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="14" customWidth="1" style="244" min="4" max="4"/>
+    <col width="14" customWidth="1" style="244" min="5" max="5"/>
+    <col width="70" customWidth="1" style="244" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="563" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSC-LBOMODEL2 — Strategy Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AI-SDR cost takeout drives margin, FCF, debt paydown, MOIC/IRR — exit multiple held at 13x in both cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="B5" s="564" t="inlineStr">
+        <is>
+          <t>RESULTS — AI vs Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="412" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C6" s="412" t="inlineStr">
+        <is>
+          <t>Base (no AI)</t>
+        </is>
+      </c>
+      <c r="D6" s="412" t="inlineStr">
+        <is>
+          <t>AI-SDR case</t>
+        </is>
+      </c>
+      <c r="E6" s="412" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="F6" s="412" t="inlineStr">
+        <is>
+          <t>COMMENTARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" s="244">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Y2 EBITDA margin</t>
+        </is>
+      </c>
+      <c r="C7" s="565" t="n">
+        <v>0.1085118998600017</v>
+      </c>
+      <c r="D7" s="565" t="n">
+        <v>0.2012029241075531</v>
+      </c>
+      <c r="E7" s="565" t="n">
+        <v>0.09269102424755141</v>
+      </c>
+      <c r="F7" s="566" t="inlineStr">
+        <is>
+          <t>Year 2 operating profitability under 10% growth / 80% GM / AI S&amp;M path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" s="244">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Y2 margin vs baseline (bps)</t>
+        </is>
+      </c>
+      <c r="C8" s="567" t="n">
+        <v>-422.7456147574727</v>
+      </c>
+      <c r="D8" s="567" t="n">
+        <v>504.1646277180415</v>
+      </c>
+      <c r="E8" s="567" t="n">
+        <v>926.9102424755141</v>
+      </c>
+      <c r="F8" s="566" t="inlineStr">
+        <is>
+          <t>Y2 EBITDA margin minus FY24 baseline margin, in basis points (target ≥500).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" s="244">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Y5 EBITDA ($m)</t>
+        </is>
+      </c>
+      <c r="C9" s="567" t="n">
+        <v>212.2104606600003</v>
+      </c>
+      <c r="D9" s="567" t="n">
+        <v>496.3963076296004</v>
+      </c>
+      <c r="E9" s="567" t="n">
+        <v>284.1858469696001</v>
+      </c>
+      <c r="F9" s="566" t="inlineStr">
+        <is>
+          <t>Year 5 EBITDA ($m).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1" s="244">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Exit EV @ 13x ($m)</t>
+        </is>
+      </c>
+      <c r="C10" s="567" t="n">
+        <v>2758.735988580003</v>
+      </c>
+      <c r="D10" s="567" t="n">
+        <v>6453.151999184804</v>
+      </c>
+      <c r="E10" s="567" t="n">
+        <v>3694.416010604801</v>
+      </c>
+      <c r="F10" s="566" t="inlineStr">
+        <is>
+          <t>Exit EV = Y5 EBITDA × 13x (Assumptions_Drivers!C20 / LBO!D17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1" s="244">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Exit net debt ($m)</t>
+        </is>
+      </c>
+      <c r="C11" s="567" t="n">
+        <v>557.1124750633038</v>
+      </c>
+      <c r="D11" s="567" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="567" t="n">
+        <v>-557.1124750633038</v>
+      </c>
+      <c r="F11" s="566" t="inlineStr">
+        <is>
+          <t>Ending net debt after mandatory amort + 100% cash sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1" s="244">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Exit equity value ($m)</t>
+        </is>
+      </c>
+      <c r="C12" s="567" t="n">
+        <v>2201.623513516699</v>
+      </c>
+      <c r="D12" s="567" t="n">
+        <v>6453.151999184804</v>
+      </c>
+      <c r="E12" s="567" t="n">
+        <v>4251.528485668105</v>
+      </c>
+      <c r="F12" s="566" t="inlineStr">
+        <is>
+          <t>Exit equity = Exit EV − ending debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" s="244">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MOIC</t>
+        </is>
+      </c>
+      <c r="C13" s="568" t="n">
+        <v>1.17652754423803</v>
+      </c>
+      <c r="D13" s="568" t="n">
+        <v>3.448505626681045</v>
+      </c>
+      <c r="E13" s="568" t="n">
+        <v>2.271978082443015</v>
+      </c>
+      <c r="F13" s="566" t="inlineStr">
+        <is>
+          <t>MOIC = Exit equity / sponsor equity check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" s="244">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IRR (5-year)</t>
+        </is>
+      </c>
+      <c r="C14" s="565" t="n">
+        <v>0.03304780632992022</v>
+      </c>
+      <c r="D14" s="565" t="n">
+        <v>0.2809323319237782</v>
+      </c>
+      <c r="E14" s="565" t="n">
+        <v>0.247884525593858</v>
+      </c>
+      <c r="F14" s="566" t="inlineStr">
+        <is>
+          <t>IRR over 5 years = MOIC^(1/5) − 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="569" t="inlineStr">
+        <is>
+          <t>IRR uplift from AI S&amp;M: 24.8 percentage points | Y2 margin expansion: 504 bps (target ≥500: YES)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PDF assumptions list:</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="570" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>In-Excel full commentary: 00_Assumptions_List | Drivers: Assumptions_Drivers</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ALL driver sources + commentary live on Assumptions_Drivers (cols D–H, same row). No separate AI cost tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="593" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers (start at Revenue growth)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="593" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_DRIVER_SOURCES.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11910,6 +12914,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="B41" s="564" t="inlineStr">
         <is>
@@ -11978,800 +12983,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId41"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="32" customWidth="1" style="244" min="2" max="2"/>
-    <col width="12" customWidth="1" style="244" min="3" max="3"/>
-    <col width="28" customWidth="1" style="244" min="4" max="4"/>
-    <col width="42" customWidth="1" style="244" min="5" max="5"/>
-    <col width="62" customWidth="1" style="244" min="6" max="6"/>
-    <col width="42" customWidth="1" style="244" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1"/>
-    <row r="2">
-      <c r="B2" s="563" t="inlineStr">
-        <is>
-          <t>Assumptions Drivers — yellow inputs + SOURCE LINK + justification on each row</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1" s="244">
-      <c r="B3" s="574" t="inlineStr">
-        <is>
-          <t>Every driver has a reputable public source URL (col E) and ~30 words on credibility / why the number is reasonable (col F). Optional second source in col G. No separate sources tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1" s="244">
-      <c r="B4" s="586" t="inlineStr">
-        <is>
-          <t>Driver</t>
-        </is>
-      </c>
-      <c r="C4" s="586" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="D4" s="586" t="inlineStr">
-        <is>
-          <t>Feeds</t>
-        </is>
-      </c>
-      <c r="E4" s="586" t="inlineStr">
-        <is>
-          <t>Source link (click)</t>
-        </is>
-      </c>
-      <c r="F4" s="586" t="inlineStr">
-        <is>
-          <t>Why this number is reasonable (~30 words)</t>
-        </is>
-      </c>
-      <c r="G4" s="586" t="inlineStr">
-        <is>
-          <t>Secondary source (click)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1" s="244">
-      <c r="B5" s="575" t="inlineStr">
-        <is>
-          <t>Revenue growth</t>
-        </is>
-      </c>
-      <c r="C5" s="422" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D5" s="575" t="inlineStr">
-        <is>
-          <t>AI_Operating!C5:G5</t>
-        </is>
-      </c>
-      <c r="E5" s="593" t="inlineStr">
-        <is>
-          <t>ZoomInfo FY2024 results (BusinessWire)</t>
-        </is>
-      </c>
-      <c r="F5" s="573" t="inlineStr">
-        <is>
-          <t>ZI FY24 revenue fell ~2%, so 10% is a forward recovery/LBO underwrite—not trailing actual. Held constant in AI vs Base so IRR uplift comes from cost takeout, not inflated top-line.</t>
-        </is>
-      </c>
-      <c r="G5" s="593" t="inlineStr">
-        <is>
-          <t>valueaddvc.com/blog/saas-evebitda-multiples-explained-benchm</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1" s="244">
-      <c r="B6" s="575" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="C6" s="422" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D6" s="575" t="inlineStr">
-        <is>
-          <t>AI_Operating COGS row</t>
-        </is>
-      </c>
-      <c r="E6" s="593" t="inlineStr">
-        <is>
-          <t>Aleph/Benchmarkit SaaS GM median ~80%</t>
-        </is>
-      </c>
-      <c r="F6" s="573" t="inlineStr">
-        <is>
-          <t>2025 software median gross margin is ~80% (Aleph×Benchmarkit). ZI already prints ~84% GAAP GM; using 80% is a conservative SaaS benchmark, not an aggressive stretch.</t>
-        </is>
-      </c>
-      <c r="G6" s="593" t="inlineStr">
-        <is>
-          <t>www.readyratios.com/sec/GTM_zoominfo-technologies-inc</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1" s="244">
-      <c r="B7" s="575" t="inlineStr">
-        <is>
-          <t>Sales payroll cut (Y1)</t>
-        </is>
-      </c>
-      <c r="C7" s="422" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D7" s="575" t="inlineStr">
-        <is>
-          <t>AI_Operating S&amp;M Y1</t>
-        </is>
-      </c>
-      <c r="E7" s="593" t="inlineStr">
-        <is>
-          <t>AI SDR vs human SDR cost/meeting</t>
-        </is>
-      </c>
-      <c r="F7" s="573" t="inlineStr">
-        <is>
-          <t>Published outbound math: fully loaded human SDRs ~$110–150k vs much cheaper AI stacks. Cutting human sales payroll 15% in Y1 is a modest slice of ZI’s 1,513 S&amp;M headcount.</t>
-        </is>
-      </c>
-      <c r="G7" s="593" t="inlineStr">
-        <is>
-          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1" s="244">
-      <c r="B8" s="575" t="inlineStr">
-        <is>
-          <t>Variable commission cut</t>
-        </is>
-      </c>
-      <c r="C8" s="422" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D8" s="575" t="inlineStr">
-        <is>
-          <t>AI_Operating Commissions</t>
-        </is>
-      </c>
-      <c r="E8" s="593" t="inlineStr">
-        <is>
-          <t>SDR pay mix ~70/30 base/variable</t>
-        </is>
-      </c>
-      <c r="F8" s="573" t="inlineStr">
-        <is>
-          <t>SaaS SDR OTE is typically ~70% base / ~30% variable. Replacing outbound humans with AI logically shrinks the commission pool; −20% is a partial, not full, cut of that variable layer.</t>
-        </is>
-      </c>
-      <c r="G8" s="593" t="inlineStr">
-        <is>
-          <t>syncgtm.com/blog/how-much-do-sales-development-representativ</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1" s="244">
-      <c r="B9" s="575" t="inlineStr">
-        <is>
-          <t>AI infrastructure ($m)</t>
-        </is>
-      </c>
-      <c r="C9" s="576" t="n">
-        <v>15</v>
-      </c>
-      <c r="D9" s="575" t="inlineStr">
-        <is>
-          <t>AI_Operating AI cost</t>
-        </is>
-      </c>
-      <c r="E9" s="593" t="inlineStr">
-        <is>
-          <t>Salesforce Agentforce $2/conv + Flex Credits</t>
-        </is>
-      </c>
-      <c r="F9" s="573" t="inlineStr">
-        <is>
-          <t>SF publishes $2/conversation and ~$0.10/action Flex Credits. At ZI scale (~378 outbound roles at 25% of 1,513 S&amp;M), $5–10k/mo AI agents imply ~$23–45m; $15m is conservative.</t>
-        </is>
-      </c>
-      <c r="G9" s="593" t="inlineStr">
-        <is>
-          <t>highticketaisystems.com/blog/ai-sdr-pricing-explained</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1" s="244">
-      <c r="B10" s="575" t="inlineStr">
-        <is>
-          <t>S&amp;M expense growth Y2+</t>
-        </is>
-      </c>
-      <c r="C10" s="422" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D10" s="575" t="inlineStr">
-        <is>
-          <t>AI_Operating S&amp;M Y2+</t>
-        </is>
-      </c>
-      <c r="E10" s="593" t="inlineStr">
-        <is>
-          <t>Gartner: agentic AI scales via inference opex</t>
-        </is>
-      </c>
-      <c r="F10" s="573" t="inlineStr">
-        <is>
-          <t>Once agents replace headcount, S&amp;M opex need not grow with revenue. Cap growth at ~2% (near inflation/maintenance) to model infinite agent scale vs linear human hiring.</t>
-        </is>
-      </c>
-      <c r="G10" s="593" t="inlineStr">
-        <is>
-          <t>www.ciodive.com/news/AI-spending-soars-enterprise-maturity/8</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1" s="244">
-      <c r="B11" s="575" t="inlineStr">
-        <is>
-          <t>G&amp;A % of revenue</t>
-        </is>
-      </c>
-      <c r="C11" s="422" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D11" s="575" t="inlineStr">
-        <is>
-          <t>AI_Operating G&amp;A</t>
-        </is>
-      </c>
-      <c r="E11" s="593" t="inlineStr">
-        <is>
-          <t>ZoomInfo FY24 G&amp;A $295.3m (~24% rev)</t>
-        </is>
-      </c>
-      <c r="F11" s="573" t="inlineStr">
-        <is>
-          <t>ZI FY24 G&amp;A was $295.3m (~24% of $1,214m). We lock ~18% as a leaner but still corporate G&amp;A load; thesis does not touch finance/comp overhead—only the sales floor.</t>
-        </is>
-      </c>
-      <c r="G11" s="593" t="inlineStr">
-        <is>
-          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1" s="244">
-      <c r="B12" s="575" t="inlineStr">
-        <is>
-          <t>CapEx reduction vs base</t>
-        </is>
-      </c>
-      <c r="C12" s="422" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D12" s="575" t="inlineStr">
-        <is>
-          <t>FCF CapEx</t>
-        </is>
-      </c>
-      <c r="E12" s="593" t="inlineStr">
-        <is>
-          <t>In-house SDR tooling/laptop stack costs</t>
-        </is>
-      </c>
-      <c r="F12" s="573" t="inlineStr">
-        <is>
-          <t>Human SDR all-in budgets include laptops, seats, and tooling. Terminating outbound humans cuts recurring device/refresh CapEx; −5% vs base CapEx rate is a small, directionally correct haircut.</t>
-        </is>
-      </c>
-      <c r="G12" s="593" t="inlineStr">
-        <is>
-          <t>firstsales.io/blog/cost-per-meeting-outbound/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1" s="244">
-      <c r="B13" s="575" t="inlineStr">
-        <is>
-          <t>WC / receivables improvement</t>
-        </is>
-      </c>
-      <c r="C13" s="422" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D13" s="575" t="inlineStr">
-        <is>
-          <t>FCF ΔNWC</t>
-        </is>
-      </c>
-      <c r="E13" s="593" t="inlineStr">
-        <is>
-          <t>ZI receivables ~80 days (SEC ratios)</t>
-        </is>
-      </c>
-      <c r="F13" s="573" t="inlineStr">
-        <is>
-          <t>ZI receivables turnover ~80 days shows WC is material. Automated billing reminders can shorten DSO; modeling −10% WC intensity vs base is a modest collections improvement, not a wipeout.</t>
-        </is>
-      </c>
-      <c r="G13" s="593" t="inlineStr">
-        <is>
-          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1" s="244">
-      <c r="B14" s="575" t="inlineStr">
-        <is>
-          <t>SOFR</t>
-        </is>
-      </c>
-      <c r="C14" s="577" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="D14" s="575" t="inlineStr">
-        <is>
-          <t>Debt interest</t>
-        </is>
-      </c>
-      <c r="E14" s="593" t="inlineStr">
-        <is>
-          <t>NY Fed official SOFR page</t>
-        </is>
-      </c>
-      <c r="F14" s="573" t="inlineStr">
-        <is>
-          <t>SOFR is the NY Fed’s official overnight Treasury-repo financing benchmark used to price leveraged loans. ~4.3% is a planning level near recent SOFR prints (see also FRED SOFR series).</t>
-        </is>
-      </c>
-      <c r="G14" s="593" t="inlineStr">
-        <is>
-          <t>fred.stlouisfed.org/series/SOFR</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1" s="244">
-      <c r="B15" s="575" t="inlineStr">
-        <is>
-          <t>Term Loan A spread</t>
-        </is>
-      </c>
-      <c r="C15" s="577" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D15" s="575" t="inlineStr">
-        <is>
-          <t>TLA rate = SOFR+spread</t>
-        </is>
-      </c>
-      <c r="E15" s="593" t="inlineStr">
-        <is>
-          <t>TLA typical SOFR+275–375bps (illustrative)</t>
-        </is>
-      </c>
-      <c r="F15" s="573" t="inlineStr">
-        <is>
-          <t>Bank Term Loan A in LBO structures typically prices tighter than TLB. SOFR+400bps sits at the wider end of published TLA ranges—conservative senior pricing independent of AI ops.</t>
-        </is>
-      </c>
-      <c r="G15" s="593" t="inlineStr">
-        <is>
-          <t>ibinterviewquestions.com/guides/debt-capital-markets/term-lo</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="48" customHeight="1" s="244">
-      <c r="B16" s="575" t="inlineStr">
-        <is>
-          <t>Term Loan B spread</t>
-        </is>
-      </c>
-      <c r="C16" s="577" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D16" s="575" t="inlineStr">
-        <is>
-          <t>TLB rate = SOFR+spread</t>
-        </is>
-      </c>
-      <c r="E16" s="593" t="inlineStr">
-        <is>
-          <t>TLB often SOFR+300–500bps; 1%/yr amort</t>
-        </is>
-      </c>
-      <c r="F16" s="573" t="inlineStr">
-        <is>
-          <t>Institutional Term Loan B commonly prices SOFR+300–500bps in LBO guides. SOFR+500bps is the upper published band—set by syndicated loan markets, not by the company’s internal AI software strategy.</t>
-        </is>
-      </c>
-      <c r="G16" s="593" t="inlineStr">
-        <is>
-          <t>ryanoconnellfinance.com/lbo-debt-structure/</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="48" customHeight="1" s="244">
-      <c r="B17" s="575" t="inlineStr">
-        <is>
-          <t>Mandatory amortization</t>
-        </is>
-      </c>
-      <c r="C17" s="422" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D17" s="575" t="inlineStr">
-        <is>
-          <t>% of initial new debt / yr</t>
-        </is>
-      </c>
-      <c r="E17" s="593" t="inlineStr">
-        <is>
-          <t>Syndicated TLB ~1% annual amort standard</t>
-        </is>
-      </c>
-      <c r="F17" s="573" t="inlineStr">
-        <is>
-          <t>Market-standard institutional TLB schedules about 1% annual amortization with a bullet at maturity. We keep 1% fixed because credit agreements—not AI-generated FCF—set the mandatory repayment floor.</t>
-        </is>
-      </c>
-      <c r="G17" s="593" t="inlineStr">
-        <is>
-          <t>clearvaluelending.com/glossary/term-loan-b</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="48" customHeight="1" s="244">
-      <c r="B18" s="575" t="inlineStr">
-        <is>
-          <t>Cash sweep %</t>
-        </is>
-      </c>
-      <c r="C18" s="422" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="575" t="inlineStr">
-        <is>
-          <t>Debt_Sweep_AI</t>
-        </is>
-      </c>
-      <c r="E18" s="593" t="inlineStr">
-        <is>
-          <t>LBO excess cash / optional prepay practice</t>
-        </is>
-      </c>
-      <c r="F18" s="573" t="inlineStr">
-        <is>
-          <t>Sponsor LBOs typically sweep excess free cash to optional debt prepay after mandatory amort. 100% sweep maximizes deleveraging so AI margin gains show up in MOIC/IRR, not idle cash.</t>
-        </is>
-      </c>
-      <c r="G18" s="593" t="inlineStr">
-        <is>
-          <t>ibinterviewquestions.com/guides/valuation-investment-banking</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="48" customHeight="1" s="244">
-      <c r="B19" s="575" t="inlineStr">
-        <is>
-          <t>Tax rate</t>
-        </is>
-      </c>
-      <c r="C19" s="422" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="D19" s="575" t="inlineStr">
-        <is>
-          <t>NI tax</t>
-        </is>
-      </c>
-      <c r="E19" s="593" t="inlineStr">
-        <is>
-          <t>PwC: US federal corporate rate 21%</t>
-        </is>
-      </c>
-      <c r="F19" s="573" t="inlineStr">
-        <is>
-          <t>US federal corporate income tax is a flat 21% statutory rate (TCJA). Operating-margin gains do not change the federal statutory rate used in the model.</t>
-        </is>
-      </c>
-      <c r="G19" s="593" t="inlineStr">
-        <is>
-          <t>tradingeconomics.com/united-states/corporate-tax-rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="48" customHeight="1" s="244">
-      <c r="B20" s="575" t="inlineStr">
-        <is>
-          <t>Exit EV/EBITDA multiple</t>
-        </is>
-      </c>
-      <c r="C20" s="584" t="n">
-        <v>13</v>
-      </c>
-      <c r="D20" s="575" t="inlineStr">
-        <is>
-          <t>LBO!D17 / Strategy_Summary</t>
-        </is>
-      </c>
-      <c r="E20" s="593" t="inlineStr">
-        <is>
-          <t>PE SaaS buyouts often ~15–22x EBITDA</t>
-        </is>
-      </c>
-      <c r="F20" s="573" t="inlineStr">
-        <is>
-          <t>PE SaaS deals often underwrite ~15–22x EBITDA. Locking exit at 13x in BOTH AI and Base cases is deliberately conservative so equity creation is attributed to ops, not multiple expansion.</t>
-        </is>
-      </c>
-      <c r="G20" s="593" t="inlineStr">
-        <is>
-          <t>aventis-advisors.com/software-valuation-multiples/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="48" customHeight="1" s="244">
-      <c r="B21" s="575" t="inlineStr">
-        <is>
-          <t>S&amp;M baseline ($m)</t>
-        </is>
-      </c>
-      <c r="C21" s="576" t="n">
-        <v>425</v>
-      </c>
-      <c r="D21" s="575" t="inlineStr">
-        <is>
-          <t>35% × FY24 revenue</t>
-        </is>
-      </c>
-      <c r="E21" s="593" t="inlineStr">
-        <is>
-          <t>ZI FY24 S&amp;M $414.1m on $1,214.3m rev</t>
-        </is>
-      </c>
-      <c r="F21" s="573" t="inlineStr">
-        <is>
-          <t>Company-reported FY24 sales &amp; marketing expense = $414.1m on $1,214.3m revenue (~34%). The model’s ~$425m (~35%) baseline is a rounded figure consistent with that audited filing disclosure.</t>
-        </is>
-      </c>
-      <c r="G21" s="593" t="inlineStr">
-        <is>
-          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="48" customHeight="1" s="244">
-      <c r="B22" s="575" t="inlineStr">
-        <is>
-          <t>Payroll baseline ($m)</t>
-        </is>
-      </c>
-      <c r="C22" s="576" t="n">
-        <v>318.8</v>
-      </c>
-      <c r="D22" s="575" t="inlineStr">
-        <is>
-          <t>S&amp;M − commission pool</t>
-        </is>
-      </c>
-      <c r="E22" s="593" t="inlineStr">
-        <is>
-          <t>SDR OTE mostly base (~70%)</t>
-        </is>
-      </c>
-      <c r="F22" s="573" t="inlineStr">
-        <is>
-          <t>With ~70/30 base/variable SDR mix, most S&amp;M people cost is payroll/base. Payroll baseline = S&amp;M − commission pool (~75% of S&amp;M) matches that pay-mix structure.</t>
-        </is>
-      </c>
-      <c r="G22" s="593" t="inlineStr">
-        <is>
-          <t>pulserevops.com/knowledge/ra0197</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="48" customHeight="1" s="244">
-      <c r="B23" s="575" t="inlineStr">
-        <is>
-          <t>Commission baseline ($m)</t>
-        </is>
-      </c>
-      <c r="C23" s="576" t="n">
-        <v>106.2</v>
-      </c>
-      <c r="D23" s="575" t="inlineStr">
-        <is>
-          <t>25% of S&amp;M baseline</t>
-        </is>
-      </c>
-      <c r="E23" s="593" t="inlineStr">
-        <is>
-          <t>Variable ~30–35% of SDR OTE</t>
-        </is>
-      </c>
-      <c r="F23" s="573" t="inlineStr">
-        <is>
-          <t>Tech SDR variable is typically ~30–35% of OTE. Setting commission pool at 25% of S&amp;M is a slightly conservative carve of total S&amp;M for variable payouts.</t>
-        </is>
-      </c>
-      <c r="G23" s="593" t="inlineStr">
-        <is>
-          <t>syncgtm.com/blog/how-to-pay-sales-development-rep</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="48" customHeight="1" s="244">
-      <c r="B24" s="575" t="inlineStr">
-        <is>
-          <t>CapEx base % of rev</t>
-        </is>
-      </c>
-      <c r="C24" s="422" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D24" s="575" t="inlineStr">
-        <is>
-          <t>Before AI −5%</t>
-        </is>
-      </c>
-      <c r="E24" s="593" t="inlineStr">
-        <is>
-          <t>ZI FY24 unlevered FCF / light CapEx SaaS</t>
-        </is>
-      </c>
-      <c r="F24" s="573" t="inlineStr">
-        <is>
-          <t>SaaS models run low CapEx vs industrials; ZI still printed strong FY24 FCF. 2% of revenue is a simple maintenance CapEx planning rate before the AI −5% haircut.</t>
-        </is>
-      </c>
-      <c r="G24" s="593" t="inlineStr">
-        <is>
-          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="48" customHeight="1" s="244">
-      <c r="B25" s="575" t="inlineStr">
-        <is>
-          <t>WC base % of Δrev</t>
-        </is>
-      </c>
-      <c r="C25" s="422" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D25" s="575" t="inlineStr">
-        <is>
-          <t>Before AI improvement</t>
-        </is>
-      </c>
-      <c r="E25" s="593" t="inlineStr">
-        <is>
-          <t>ZI receivables days ~80 (WC intensity)</t>
-        </is>
-      </c>
-      <c r="F25" s="573" t="inlineStr">
-        <is>
-          <t>Receivables ~80 days imply WC scales with growth. Using 2% of Δrevenue as ΔNWC is a simplified SaaS WC plug anchored to that receivables reality.</t>
-        </is>
-      </c>
-      <c r="G25" s="593" t="inlineStr">
-        <is>
-          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>TLA rate (SOFR+4)</t>
-        </is>
-      </c>
-      <c r="C27" s="579">
-        <f>C14+C15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>TLB rate (SOFR+5)</t>
-        </is>
-      </c>
-      <c r="C28" s="579">
-        <f>C14+C16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="564" t="inlineStr">
-        <is>
-          <t>PDF twin of this source map:</t>
-        </is>
-      </c>
-      <c r="C29" s="593" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_AI_COST_SOURCES.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="594" t="inlineStr">
-        <is>
-          <t>Educational / research use only — not investment advice. List prices and filings update over time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B3:G3"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -1822,7 +1822,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="602">
+  <cellXfs count="604">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2876,6 +2876,10 @@
     <xf numFmtId="10" fontId="112" fillId="37" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="192" fontId="112" fillId="37" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="187">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3224,6 +3228,112 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ZoomInfo LBOMODEL2 — Base vs AI-SDR Strategy</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Strategy_Summary'!C49</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Strategy_Summary'!$B$50:$B$55</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Strategy_Summary'!$C$50:$C$55</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Strategy_Summary'!D49</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Strategy_Summary'!$B$50:$B$55</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Strategy_Summary'!$D$50:$D$55</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -4292,6 +4402,33 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>1</col>
@@ -4924,8 +5061,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="B2:H31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="244" min="2" max="2"/>
     <col width="10" customWidth="1" style="244" min="3" max="3"/>
@@ -4936,7 +5073,6 @@
     <col width="40" customWidth="1" style="244" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -5802,7 +5938,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="B30" s="564" t="inlineStr">
         <is>
@@ -5908,8 +6043,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="B2:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.7109375" customWidth="1" style="244" min="1" max="1"/>
     <col width="36.5703125" bestFit="1" customWidth="1" style="244" min="2" max="2"/>
@@ -6213,8 +6348,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F268"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A2:F268"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19.42578125" bestFit="1" customWidth="1" style="244" min="1" max="1"/>
     <col width="9.28515625" bestFit="1" customWidth="1" style="244" min="2" max="5"/>
@@ -6222,7 +6357,6 @@
     <col width="9.28515625" bestFit="1" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="18" customHeight="1" s="244" thickBot="1">
       <c r="A2" s="101" t="inlineStr">
         <is>
@@ -6235,7 +6369,6 @@
       <c r="E2" s="93" t="n"/>
       <c r="F2" s="93" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -6256,7 +6389,6 @@
         <v>37.51</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -11520,293 +11652,636 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="B2:F55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="244" min="2" max="2"/>
+    <col width="34" customWidth="1" style="244" min="2" max="2"/>
     <col width="14" customWidth="1" style="244" min="3" max="3"/>
     <col width="14" customWidth="1" style="244" min="4" max="4"/>
     <col width="14" customWidth="1" style="244" min="5" max="5"/>
-    <col width="70" customWidth="1" style="244" min="6" max="6"/>
+    <col width="78" customWidth="1" style="244" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
-          <t>vengeanceaiUSC-LBOMODEL2 — Strategy Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AI-SDR cost takeout drives margin, FCF, debt paydown, MOIC/IRR — exit multiple held at 13x in both cases</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>vengeanceaiUSC-LBOMODEL2 — ZoomInfo AI-SDR LBO Strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1" s="244">
+      <c r="B3" s="574" t="inlineStr">
+        <is>
+          <t>Take-private LBO: slash outbound SDR S&amp;M, replace with AI agents, ≥500 bps EBITDA margin → higher FCF → faster debt paydown → higher IRR</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="B5" s="564" t="inlineStr">
         <is>
-          <t>RESULTS — AI vs Base</t>
+          <t>THESIS</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="412" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Replacing human SDRs with AI agents to drive 500+ bps EBITDA margin expansion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>S&amp;M is the largest SaaS opex lever → lower CAC → higher FCF → sweep debt → juice LBO IRR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="564" t="inlineStr">
+        <is>
+          <t>ENTRY (ZoomInfo FY2024 10-K baseline + latest BS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="575" t="inlineStr">
+        <is>
+          <t>Revenue (FY2024)</t>
+        </is>
+      </c>
+      <c r="C10" s="567" t="n">
+        <v>1214.3</v>
+      </c>
+      <c r="D10" s="591" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="575" t="inlineStr">
+        <is>
+          <t>Gross Profit / GM</t>
+        </is>
+      </c>
+      <c r="C11" s="602" t="inlineStr">
+        <is>
+          <t>1024.5 / 84.4%</t>
+        </is>
+      </c>
+      <c r="D11" s="591" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="575" t="inlineStr">
+        <is>
+          <t>GAAP Operating Income</t>
+        </is>
+      </c>
+      <c r="C12" s="567" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="D12" s="591" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="575" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="C13" s="567" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="D13" s="591" t="inlineStr">
+        <is>
+          <t>XBRL OtherDepreciationAndAmortization</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="575" t="inlineStr">
+        <is>
+          <t>Baseline EBITDA (OpInc+D&amp;A)</t>
+        </is>
+      </c>
+      <c r="C14" s="567" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="D14" s="591" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="575" t="inlineStr">
+        <is>
+          <t>Baseline EBITDA margin</t>
+        </is>
+      </c>
+      <c r="C15" s="565" t="n">
+        <v>0.1508</v>
+      </c>
+      <c r="D15" s="591" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="575" t="inlineStr">
+        <is>
+          <t>S&amp;M baseline (35% of rev)</t>
+        </is>
+      </c>
+      <c r="C16" s="567" t="n">
+        <v>425</v>
+      </c>
+      <c r="D16" s="591" t="inlineStr">
+        <is>
+          <t>Prompt: ~35% / ~$425m</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="575" t="inlineStr">
+        <is>
+          <t>Share price / shares (m)</t>
+        </is>
+      </c>
+      <c r="C17" s="602" t="inlineStr">
+        <is>
+          <t>$4.05 / 307.294</t>
+        </is>
+      </c>
+      <c r="D17" s="591" t="inlineStr">
+        <is>
+          <t>Market + 10-K shares</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="575" t="inlineStr">
+        <is>
+          <t>Offer (25% premium)</t>
+        </is>
+      </c>
+      <c r="C18" s="602" t="inlineStr">
+        <is>
+          <t>$5.0625</t>
+        </is>
+      </c>
+      <c r="D18" s="591" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="575" t="inlineStr">
+        <is>
+          <t>Gross debt / cash</t>
+        </is>
+      </c>
+      <c r="C19" s="602" t="inlineStr">
+        <is>
+          <t>1329.9 / 179.9</t>
+        </is>
+      </c>
+      <c r="D19" s="591" t="inlineStr">
+        <is>
+          <t>YE2025 10-K/Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="575" t="inlineStr">
+        <is>
+          <t>Sponsor equity check</t>
+        </is>
+      </c>
+      <c r="C20" s="567" t="n">
+        <v>1871.3</v>
+      </c>
+      <c r="D20" s="591" t="inlineStr">
+        <is>
+          <t>Uses − excess cash − new debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="575" t="inlineStr">
+        <is>
+          <t>New debt (5.0x EBITDA)</t>
+        </is>
+      </c>
+      <c r="C21" s="567" t="n">
+        <v>915.5</v>
+      </c>
+      <c r="D21" s="591" t="inlineStr">
+        <is>
+          <t>TLA 2.5x + TLB 1.5x + Notes 1.0x</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="575" t="inlineStr">
+        <is>
+          <t>Exit multiple</t>
+        </is>
+      </c>
+      <c r="C22" s="602" t="inlineStr">
+        <is>
+          <t>13.0x</t>
+        </is>
+      </c>
+      <c r="D22" s="591" t="inlineStr">
+        <is>
+          <t>Mid of 12–14x software band</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="564" t="inlineStr">
+        <is>
+          <t>AI STRATEGY RULES (as specified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Y1: cut S&amp;M 15% vs baseline $425m; add $15m AI software/compute cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Y2–Y5: S&amp;M grows only 2%/yr (AI scales without headcount)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Target: ≥500 bps EBITDA margin expansion by Year 2 vs baseline year</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="564" t="inlineStr">
+        <is>
+          <t>RESULTS — AI case vs Base (no AI) case</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="412" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C6" s="412" t="inlineStr">
+      <c r="C30" s="412" t="inlineStr">
         <is>
           <t>Base (no AI)</t>
         </is>
       </c>
-      <c r="D6" s="412" t="inlineStr">
+      <c r="D30" s="412" t="inlineStr">
         <is>
           <t>AI-SDR case</t>
         </is>
       </c>
-      <c r="E6" s="412" t="inlineStr">
+      <c r="E30" s="412" t="inlineStr">
         <is>
           <t>Delta</t>
         </is>
       </c>
-      <c r="F6" s="412" t="inlineStr">
+      <c r="F30" s="412" t="inlineStr">
         <is>
           <t>COMMENTARY</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1" s="244">
-      <c r="B7" t="inlineStr">
+    <row r="31" ht="42" customHeight="1" s="244">
+      <c r="B31" s="575" t="inlineStr">
         <is>
           <t>Y2 EBITDA margin</t>
         </is>
       </c>
-      <c r="C7" s="565" t="n">
+      <c r="C31" s="565" t="n">
         <v>0.1085118998600017</v>
       </c>
-      <c r="D7" s="565" t="n">
+      <c r="D31" s="565" t="n">
         <v>0.2012029241075531</v>
       </c>
-      <c r="E7" s="565" t="n">
+      <c r="E31" s="565" t="n">
         <v>0.09269102424755141</v>
       </c>
-      <c r="F7" s="566" t="inlineStr">
-        <is>
-          <t>Year 2 operating profitability under 10% growth / 80% GM / AI S&amp;M path.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1" s="244">
-      <c r="B8" t="inlineStr">
+      <c r="F31" s="603" t="inlineStr">
+        <is>
+          <t>Year 2 operating profitability; the AI strategy drove this from 10.9% to 20.1%, expanding the margin by 9.3%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1" s="244">
+      <c r="B32" s="575" t="inlineStr">
         <is>
           <t>Y2 margin vs baseline (bps)</t>
         </is>
       </c>
-      <c r="C8" s="567" t="n">
+      <c r="C32" s="567" t="n">
         <v>-422.7456147574727</v>
       </c>
-      <c r="D8" s="567" t="n">
+      <c r="D32" s="567" t="n">
         <v>504.1646277180415</v>
       </c>
-      <c r="E8" s="567" t="n">
+      <c r="E32" s="567" t="n">
         <v>926.9102424755141</v>
       </c>
-      <c r="F8" s="566" t="inlineStr">
-        <is>
-          <t>Y2 EBITDA margin minus FY24 baseline margin, in basis points (target ≥500).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1" s="244">
-      <c r="B9" t="inlineStr">
+      <c r="F32" s="603" t="inlineStr">
+        <is>
+          <t>The difference from baseline margin; AI implementation increased this metric by 926.9 basis points to reach 504.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1" s="244">
+      <c r="B33" s="575" t="inlineStr">
         <is>
           <t>Y5 EBITDA ($m)</t>
         </is>
       </c>
-      <c r="C9" s="567" t="n">
+      <c r="C33" s="567" t="n">
         <v>212.2104606600003</v>
       </c>
-      <c r="D9" s="567" t="n">
+      <c r="D33" s="567" t="n">
         <v>496.3963076296004</v>
       </c>
-      <c r="E9" s="567" t="n">
+      <c r="E33" s="567" t="n">
         <v>284.1858469696001</v>
       </c>
-      <c r="F9" s="566" t="inlineStr">
-        <is>
-          <t>Year 5 EBITDA ($m).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1" s="244">
-      <c r="B10" t="inlineStr">
+      <c r="F33" s="603" t="inlineStr">
+        <is>
+          <t>Year 5 operating cash flow proxy; AI-driven cost savings boosted this figure by $284.2 million to $496.4 million.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1" s="244">
+      <c r="B34" s="575" t="inlineStr">
         <is>
           <t>Exit EV @ 13x ($m)</t>
         </is>
       </c>
-      <c r="C10" s="567" t="n">
+      <c r="C34" s="567" t="n">
         <v>2758.735988580003</v>
       </c>
-      <c r="D10" s="567" t="n">
+      <c r="D34" s="567" t="n">
         <v>6453.151999184804</v>
       </c>
-      <c r="E10" s="567" t="n">
+      <c r="E34" s="567" t="n">
         <v>3694.416010604801</v>
       </c>
-      <c r="F10" s="566" t="inlineStr">
-        <is>
-          <t>Exit EV = Y5 EBITDA × 13x (Assumptions_Drivers!C20 / LBO!D17).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1" s="244">
-      <c r="B11" t="inlineStr">
+      <c r="F34" s="603" t="inlineStr">
+        <is>
+          <t>Projected exit Enterprise Value; higher EBITDA from AI increased this valuation by $3,694.4 million to $6,453.2 million.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1" s="244">
+      <c r="B35" s="575" t="inlineStr">
         <is>
           <t>Exit net debt ($m)</t>
         </is>
       </c>
-      <c r="C11" s="567" t="n">
+      <c r="C35" s="567" t="n">
         <v>557.1124750633038</v>
       </c>
-      <c r="D11" s="567" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="567" t="n">
+      <c r="D35" s="567" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="567" t="n">
         <v>-557.1124750633038</v>
       </c>
-      <c r="F11" s="566" t="inlineStr">
-        <is>
-          <t>Ending net debt after mandatory amort + 100% cash sweep.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1" s="244">
-      <c r="B12" t="inlineStr">
+      <c r="F35" s="603" t="inlineStr">
+        <is>
+          <t>Remaining debt balance at exit; higher cash flow from the AI strategy paid down an extra $557.1 million vs Base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1" s="244">
+      <c r="B36" s="575" t="inlineStr">
         <is>
           <t>Exit equity value ($m)</t>
         </is>
       </c>
-      <c r="C12" s="567" t="n">
+      <c r="C36" s="567" t="n">
         <v>2201.623513516699</v>
       </c>
-      <c r="D12" s="567" t="n">
+      <c r="D36" s="567" t="n">
         <v>6453.151999184804</v>
       </c>
-      <c r="E12" s="567" t="n">
+      <c r="E36" s="567" t="n">
         <v>4251.528485668105</v>
       </c>
-      <c r="F12" s="566" t="inlineStr">
-        <is>
-          <t>Exit equity = Exit EV − ending debt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" s="244">
-      <c r="B13" t="inlineStr">
+      <c r="F36" s="603" t="inlineStr">
+        <is>
+          <t>Total payout to equity holders; the AI strategy increased this final payout by $4,251.5 million to $6,453.2 million.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1" s="244">
+      <c r="B37" s="575" t="inlineStr">
         <is>
           <t>MOIC</t>
         </is>
       </c>
-      <c r="C13" s="568" t="n">
+      <c r="C37" s="568" t="n">
         <v>1.17652754423803</v>
       </c>
-      <c r="D13" s="568" t="n">
+      <c r="D37" s="568" t="n">
         <v>3.448505626681045</v>
       </c>
-      <c r="E13" s="568" t="n">
+      <c r="E37" s="568" t="n">
         <v>2.271978082443015</v>
       </c>
-      <c r="F13" s="566" t="inlineStr">
-        <is>
-          <t>MOIC = Exit equity / sponsor equity check.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1" s="244">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>IRR (5-year)</t>
-        </is>
-      </c>
-      <c r="C14" s="565" t="n">
+      <c r="F37" s="603" t="inlineStr">
+        <is>
+          <t>Multiple on Invested Capital; the AI strategy significantly improved the total gross cash return from 1.18x to 3.45x.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1" s="244">
+      <c r="B38" s="575" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="C38" s="565" t="n">
         <v>0.03304780632992022</v>
       </c>
-      <c r="D14" s="565" t="n">
+      <c r="D38" s="565" t="n">
         <v>0.2809323319237782</v>
       </c>
-      <c r="E14" s="565" t="n">
+      <c r="E38" s="565" t="n">
         <v>0.247884525593858</v>
       </c>
-      <c r="F14" s="566" t="inlineStr">
-        <is>
-          <t>IRR over 5 years = MOIC^(1/5) − 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="B16" s="569" t="inlineStr">
-        <is>
-          <t>IRR uplift from AI S&amp;M: 24.8 percentage points | Y2 margin expansion: 504 bps (target ≥500: YES)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PDF assumptions list:</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="570" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>In-Excel full commentary: 00_Assumptions_List | Drivers: Assumptions_Drivers</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ALL driver sources + commentary live on Assumptions_Drivers (cols D–H, same row). No separate AI cost tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="593" t="inlineStr">
-        <is>
-          <t>Go to Assumptions_Drivers (start at Revenue growth)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="593" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_DRIVER_SOURCES.pdf</t>
-        </is>
+      <c r="F38" s="603" t="inlineStr">
+        <is>
+          <t>Annualized compound return rate over a 5-year period; replacing human SDRs with AI boosted this return by 24.8 percentage points to 28.1%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>The IRR is calculated over a 5-year period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="564" t="inlineStr">
+        <is>
+          <t>IRR POINTS FROM AI-DRIVEN S&amp;M REDUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="569" t="inlineStr">
+        <is>
+          <t>AI case IRR 28.1% − Base IRR 3.3% = 24.8 percentage points of IRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="569" t="inlineStr">
+        <is>
+          <t>Y2 AI EBITDA margin 20.1% vs baseline 15.1% = 504 bps (target ≥500: YES)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>See AI_Operating, Base_Operating, Debt_Sweep_AI, LBO, Assumptions_Drivers, 00_Assumptions_List</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="564" t="inlineStr">
+        <is>
+          <t>CHART DATA (Base vs AI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="412" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C49" s="412" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D49" s="412" t="inlineStr">
+        <is>
+          <t>AI-SDR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Y2 EBITDA margin %</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="D50" t="n">
+        <v>20.12</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Y2 margin bps vs base</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-422.75</v>
+      </c>
+      <c r="D51" t="n">
+        <v>504.16</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Y5 EBITDA ($m)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>212.21</v>
+      </c>
+      <c r="D52" t="n">
+        <v>496.4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Exit equity ($m)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2201.62</v>
+      </c>
+      <c r="D53" t="n">
+        <v>6453.15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MOIC (x)</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>IRR (%)</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>28.09</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId3"/>
-  </hyperlinks>
+  <mergeCells count="1">
+    <mergeCell ref="B3:F3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11816,8 +12291,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="B2:M43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" style="244" min="2" max="2"/>
     <col width="22" customWidth="1" style="244" min="3" max="3"/>
@@ -11833,7 +12308,6 @@
     <col width="70" customWidth="1" style="244" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -11855,7 +12329,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" s="557" t="inlineStr">
         <is>
@@ -12818,7 +13291,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="B23" s="564" t="inlineStr">
         <is>
@@ -12834,7 +13306,6 @@
       </c>
     </row>
     <row r="25"/>
-    <row r="26"/>
     <row r="27">
       <c r="B27" s="564" t="inlineStr">
         <is>
@@ -12870,7 +13341,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="B33" s="564" t="inlineStr">
         <is>
@@ -12892,7 +13362,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="B37" s="564" t="inlineStr">
         <is>
@@ -12914,7 +13383,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="B41" s="564" t="inlineStr">
         <is>
@@ -12994,10 +13462,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="B2:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -13164,7 +13631,6 @@
         <v>557.1124750633038</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
@@ -13205,8 +13671,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="B2:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
     <col width="12" customWidth="1" style="244" min="3" max="3"/>
@@ -13218,7 +13684,6 @@
     <col width="12" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -13760,8 +14225,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="B2:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
     <col width="12" customWidth="1" style="244" min="3" max="3"/>
@@ -13773,7 +14238,6 @@
     <col width="12" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -14315,10 +14779,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="B2:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
@@ -14326,11 +14789,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8" ht="26.25" customHeight="1" s="244">
       <c r="B8" s="402" t="inlineStr">
         <is>
@@ -14349,8 +14807,6 @@
       <c r="L8" s="404" t="n"/>
       <c r="M8" s="404" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="B11" s="405" t="inlineStr">
         <is>
@@ -14361,31 +14817,6 @@
     <row r="12"/>
     <row r="13"/>
     <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
@@ -14423,8 +14854,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R393"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A2:R393"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.7109375" customWidth="1" style="244" min="1" max="1"/>
     <col width="44.140625" customWidth="1" style="244" min="2" max="2"/>
@@ -15146,7 +15577,6 @@
         <v>134.838525</v>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -17095,7 +17525,6 @@
         <v>43190</v>
       </c>
     </row>
-    <row r="114"/>
     <row r="115">
       <c r="B115" t="inlineStr">
         <is>
@@ -17318,7 +17747,6 @@
         <v>987.5822307314286</v>
       </c>
     </row>
-    <row r="124"/>
     <row r="125">
       <c r="B125" t="inlineStr">
         <is>
@@ -17385,7 +17813,6 @@
         <v>-223</v>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="B129" t="inlineStr">
         <is>
@@ -17927,7 +18354,6 @@
         <v>586.7181807314284</v>
       </c>
     </row>
-    <row r="154"/>
     <row r="155">
       <c r="B155" s="34" t="inlineStr">
         <is>
@@ -18066,7 +18492,6 @@
         </is>
       </c>
     </row>
-    <row r="160"/>
     <row r="161">
       <c r="B161" s="321" t="inlineStr">
         <is>
@@ -19165,7 +19590,6 @@
       <c r="I214" s="15" t="n"/>
       <c r="J214" s="15" t="n"/>
     </row>
-    <row r="215"/>
     <row r="216">
       <c r="F216" s="475" t="n">
         <v>43190</v>
@@ -19175,7 +19599,6 @@
       <c r="I216" s="475" t="n"/>
       <c r="J216" s="475" t="n"/>
     </row>
-    <row r="217"/>
     <row r="218">
       <c r="B218" s="3" t="inlineStr">
         <is>
@@ -20421,7 +20844,6 @@
         <v>8149.38245662911</v>
       </c>
     </row>
-    <row r="265"/>
     <row r="266">
       <c r="B266" s="317" t="inlineStr">
         <is>
@@ -21108,7 +21530,6 @@
         <v>0.4297704340734299</v>
       </c>
     </row>
-    <row r="299"/>
     <row r="300">
       <c r="D300" s="319" t="inlineStr">
         <is>
@@ -21283,7 +21704,6 @@
         <v>0.4403663540732419</v>
       </c>
     </row>
-    <row r="309"/>
     <row r="310">
       <c r="D310" s="319" t="inlineStr">
         <is>
@@ -21445,7 +21865,6 @@
         <v>0.2849090713511313</v>
       </c>
     </row>
-    <row r="318"/>
     <row r="319">
       <c r="B319" s="317" t="inlineStr">
         <is>
@@ -22644,7 +23063,6 @@
         <v>3837.047401196713</v>
       </c>
     </row>
-    <row r="371"/>
     <row r="372">
       <c r="B372" s="312" t="inlineStr">
         <is>
@@ -22688,7 +23106,6 @@
         </is>
       </c>
     </row>
-    <row r="376"/>
     <row r="377" ht="15.75" customHeight="1" s="244" thickBot="1">
       <c r="B377" s="392" t="inlineStr">
         <is>
@@ -22782,7 +23199,6 @@
         <v>1205.272610422996</v>
       </c>
     </row>
-    <row r="384"/>
     <row r="385">
       <c r="B385" s="383" t="inlineStr">
         <is>
@@ -22803,7 +23219,6 @@
         <v>5536.653639577004</v>
       </c>
     </row>
-    <row r="387"/>
     <row r="388">
       <c r="B388" s="317" t="inlineStr">
         <is>
@@ -23011,8 +23426,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K118"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="B2:K118"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.7109375" customWidth="1" style="244" min="1" max="1"/>
     <col width="40.28515625" customWidth="1" style="244" min="2" max="2"/>
@@ -23100,7 +23515,6 @@
         <v>0.06990222994664612</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="15.75" customHeight="1" s="244" thickBot="1">
       <c r="B11" s="69" t="inlineStr">
         <is>
@@ -23939,7 +24353,6 @@
         <v>0.7748616857223557</v>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
@@ -23990,7 +24403,6 @@
         <v>0.06990222994664612</v>
       </c>
     </row>
-    <row r="60"/>
     <row r="61" ht="15.75" customHeight="1" s="244" thickBot="1">
       <c r="B61" s="63" t="inlineStr">
         <is>
@@ -24353,7 +24765,6 @@
         <v>36.4886239211832</v>
       </c>
     </row>
-    <row r="82"/>
     <row r="83" ht="17.25" customHeight="1" s="244">
       <c r="C83" s="112" t="inlineStr">
         <is>
@@ -24519,7 +24930,6 @@
         <v>1472.571620740424</v>
       </c>
     </row>
-    <row r="92"/>
     <row r="93" ht="15.75" customHeight="1" s="244" thickBot="1">
       <c r="B93" s="63" t="inlineStr">
         <is>
@@ -24530,26 +24940,6 @@
       <c r="D93" s="93" t="n"/>
       <c r="E93" s="93" t="n"/>
     </row>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
     <row r="114">
       <c r="B114" s="108" t="n"/>
       <c r="C114" s="109" t="inlineStr">

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -153,7 +153,7 @@
     <numFmt numFmtId="245" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
     <numFmt numFmtId="246" formatCode="###0&quot;E&quot;_)"/>
   </numFmts>
-  <fonts count="113">
+  <fonts count="118">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -882,8 +882,36 @@
       <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000B3D5C"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00334455"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00556677"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="39">
+  <fills count="45">
     <fill>
       <patternFill/>
     </fill>
@@ -1083,8 +1111,38 @@
         <fgColor rgb="00E7F3FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000B3D5C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F1F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFCF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE8A3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="36">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1490,6 +1548,64 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D0DA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D0DA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D0DA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D0DA"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D0DA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D0DA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D0DA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D0DA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D0DA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D0DA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D0DA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D0DA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1822,7 +1938,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="604">
+  <cellXfs count="624">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2880,6 +2996,56 @@
     <xf numFmtId="0" fontId="0" fillId="38" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="39" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="116" fillId="37" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="40" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="41" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="42" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="43" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="116" fillId="37" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="44" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="116" fillId="37" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="192" fontId="116" fillId="37" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="105" fillId="34" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="187">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5064,884 +5230,899 @@
   <dimension ref="B2:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" style="244" min="2" max="2"/>
-    <col width="10" customWidth="1" style="244" min="3" max="3"/>
-    <col width="55" customWidth="1" style="244" min="4" max="4"/>
-    <col width="40" customWidth="1" style="244" min="5" max="5"/>
-    <col width="48" customWidth="1" style="244" min="6" max="6"/>
-    <col width="36" customWidth="1" style="244" min="7" max="7"/>
-    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="26" customWidth="1" style="244" min="2" max="2"/>
+    <col width="11" customWidth="1" style="244" min="3" max="3"/>
+    <col width="52" customWidth="1" style="244" min="4" max="4"/>
+    <col width="42" customWidth="1" style="244" min="5" max="5"/>
+    <col width="55" customWidth="1" style="244" min="6" max="6"/>
+    <col width="34" customWidth="1" style="244" min="7" max="7"/>
+    <col width="38" customWidth="1" style="244" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="563" t="inlineStr">
-        <is>
-          <t>Assumptions Drivers — EVERY row: Value + Why reasonable + Source link + clickable Feeds</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1" s="244">
-      <c r="B3" s="574" t="inlineStr">
-        <is>
-          <t>Columns on the SAME row as each driver: D = why reasonable (model commentary); E = clickable source URL; F = ~30-word source credibility; G = clickable Feeds jump into the model. No separate AI cost tab — all evidence lives here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1" s="244">
-      <c r="B4" s="595" t="inlineStr">
+      <c r="B2" s="604" t="inlineStr">
+        <is>
+          <t>Assumptions Drivers — value, justification, source link, and Feeds on every row</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1" s="244">
+      <c r="B3" s="605" t="inlineStr">
+        <is>
+          <t>Same-row evidence for every yellow input. Col D = why the assumption is reasonable for this LBO. Col E = clickable source. Col F = source math / credibility (e.g. SF Agentforce list prices → $15m). Col G = click into the model. No separate AI-cost tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" s="244">
+      <c r="B4" s="606" t="inlineStr">
         <is>
           <t>Driver</t>
         </is>
       </c>
-      <c r="C4" s="595" t="inlineStr">
+      <c r="C4" s="606" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D4" s="595" t="inlineStr">
-        <is>
-          <t>Why this number is reasonable (model commentary)</t>
-        </is>
-      </c>
-      <c r="E4" s="595" t="inlineStr">
+      <c r="D4" s="606" t="inlineStr">
+        <is>
+          <t>Why reasonable (model justification)</t>
+        </is>
+      </c>
+      <c r="E4" s="606" t="inlineStr">
         <is>
           <t>Source link (click)</t>
         </is>
       </c>
-      <c r="F4" s="595" t="inlineStr">
-        <is>
-          <t>Source credibility / why we can use it (~30 words)</t>
-        </is>
-      </c>
-      <c r="G4" s="595" t="inlineStr">
+      <c r="F4" s="606" t="inlineStr">
+        <is>
+          <t>Source math / credibility</t>
+        </is>
+      </c>
+      <c r="G4" s="606" t="inlineStr">
         <is>
           <t>Feeds (click to jump)</t>
         </is>
       </c>
-      <c r="H4" s="595" t="inlineStr">
+      <c r="H4" s="606" t="inlineStr">
         <is>
           <t>Secondary source (click)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="58" customHeight="1" s="244">
-      <c r="B5" s="596" t="inlineStr">
+    <row r="5" ht="62" customHeight="1" s="244">
+      <c r="B5" s="607" t="inlineStr">
         <is>
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="C5" s="597" t="n">
+      <c r="C5" s="608" t="n">
         <v>0.1</v>
       </c>
-      <c r="D5" s="573" t="inlineStr">
+      <c r="D5" s="609" t="inlineStr">
         <is>
           <t>Assumes steady top-line expansion. Reasonable for a mature enterprise software company, avoiding aggressive hypergrowth assumptions while maintaining a healthy, realistic sales trajectory.</t>
         </is>
       </c>
-      <c r="E5" s="593" t="inlineStr">
+      <c r="E5" s="610" t="inlineStr">
         <is>
           <t>ZoomInfo FY2024 results (BusinessWire)</t>
         </is>
       </c>
-      <c r="F5" s="573" t="inlineStr">
+      <c r="F5" s="611" t="inlineStr">
         <is>
           <t>ZI disclosed FY24 revenue of $1,214.3m (−2% YoY). Using 10% forward growth is a mature-SaaS recovery underwrite held equal in AI vs Base—not hypergrowth.</t>
         </is>
       </c>
-      <c r="G5" s="593" t="inlineStr">
+      <c r="G5" s="612" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D5 (Revenue)</t>
         </is>
       </c>
-      <c r="H5" s="593" t="inlineStr">
+      <c r="H5" s="612" t="inlineStr">
         <is>
           <t>valueaddvc.com/blog/saas-evebitda-multiples-explained-benchmarks-and-w</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1" s="244">
-      <c r="B6" s="596" t="inlineStr">
+    <row r="6" ht="62" customHeight="1" s="244">
+      <c r="B6" s="613" t="inlineStr">
         <is>
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="C6" s="597" t="n">
+      <c r="C6" s="608" t="n">
         <v>0.8</v>
       </c>
-      <c r="D6" s="573" t="inlineStr">
+      <c r="D6" s="609" t="inlineStr">
         <is>
           <t>High profitability on direct services. Highly reasonable for a SaaS company, which historically scales digital infrastructure with minimal incremental cost per user.</t>
         </is>
       </c>
-      <c r="E6" s="593" t="inlineStr">
+      <c r="E6" s="610" t="inlineStr">
         <is>
           <t>Aleph/Benchmarkit SaaS GM median ~80%</t>
         </is>
       </c>
-      <c r="F6" s="573" t="inlineStr">
+      <c r="F6" s="611" t="inlineStr">
         <is>
           <t>Independent SaaS benchmarks put software median GM near 80%; ZI already prints ~84% GAAP GM, so 80% is conservative and industry-standard.</t>
         </is>
       </c>
-      <c r="G6" s="593" t="inlineStr">
+      <c r="G6" s="612" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D6 (COGS)</t>
         </is>
       </c>
-      <c r="H6" s="593" t="inlineStr">
+      <c r="H6" s="612" t="inlineStr">
         <is>
           <t>www.readyratios.com/sec/GTM_zoominfo-technologies-inc</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1" s="244">
-      <c r="B7" s="596" t="inlineStr">
+    <row r="7" ht="62" customHeight="1" s="244">
+      <c r="B7" s="607" t="inlineStr">
         <is>
           <t>Sales payroll cut (Y1)</t>
         </is>
       </c>
-      <c r="C7" s="597" t="n">
+      <c r="C7" s="608" t="n">
         <v>0.15</v>
       </c>
-      <c r="D7" s="573" t="inlineStr">
+      <c r="D7" s="609" t="inlineStr">
         <is>
           <t>Immediate headcount reduction for human SDRs. Reasonable as a private equity cost-cutting measure, easily achieved by eliminating the lower-tier outbound sales team.</t>
         </is>
       </c>
-      <c r="E7" s="593" t="inlineStr">
+      <c r="E7" s="610" t="inlineStr">
         <is>
           <t>AI SDR vs human SDR cost/meeting analysis</t>
         </is>
       </c>
-      <c r="F7" s="573" t="inlineStr">
+      <c r="F7" s="611" t="inlineStr">
         <is>
           <t>Published outbound economics show fully loaded human SDRs far costlier than AI stacks. −15% Y1 payroll is a modest PE-style cut of outbound headcount, not a full S&amp;M wipeout.</t>
         </is>
       </c>
-      <c r="G7" s="593" t="inlineStr">
+      <c r="G7" s="612" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D7 (Sales payroll)</t>
         </is>
       </c>
-      <c r="H7" s="593" t="inlineStr">
+      <c r="H7" s="612" t="inlineStr">
         <is>
           <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1" s="244">
-      <c r="B8" s="596" t="inlineStr">
+    <row r="8" ht="62" customHeight="1" s="244">
+      <c r="B8" s="613" t="inlineStr">
         <is>
           <t>Variable commission cut</t>
         </is>
       </c>
-      <c r="C8" s="597" t="n">
+      <c r="C8" s="608" t="n">
         <v>0.2</v>
       </c>
-      <c r="D8" s="573" t="inlineStr">
+      <c r="D8" s="609" t="inlineStr">
         <is>
           <t>Reduces payouts for automated sales. Reasonable because AI agents do not collect commission checks, retaining more profit per enterprise deal directly for the company.</t>
         </is>
       </c>
-      <c r="E8" s="593" t="inlineStr">
+      <c r="E8" s="610" t="inlineStr">
         <is>
           <t>SDR pay mix ~70/30 base/variable (SyncGTM)</t>
         </is>
       </c>
-      <c r="F8" s="573" t="inlineStr">
+      <c r="F8" s="611" t="inlineStr">
         <is>
           <t>SaaS SDR OTE is typically ~70% base / ~30% variable. Replacing humans with AI shrinks the commission pool; −20% is a partial cut of that variable layer.</t>
         </is>
       </c>
-      <c r="G8" s="593" t="inlineStr">
+      <c r="G8" s="612" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D8 (Commissions)</t>
         </is>
       </c>
-      <c r="H8" s="593" t="inlineStr">
+      <c r="H8" s="612" t="inlineStr">
         <is>
           <t>syncgtm.com/blog/how-much-do-sales-development-representatives-make-at</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="58" customHeight="1" s="244">
-      <c r="B9" s="596" t="inlineStr">
+    <row r="9" ht="62" customHeight="1" s="244">
+      <c r="B9" s="607" t="inlineStr">
         <is>
           <t>AI infrastructure ($m)</t>
         </is>
       </c>
-      <c r="C9" s="598" t="n">
+      <c r="C9" s="614" t="n">
         <v>15</v>
       </c>
-      <c r="D9" s="573" t="inlineStr">
+      <c r="D9" s="609" t="inlineStr">
         <is>
           <t>Fixed cost for AI software and compute. Reasonable estimate for enterprise-scale AI deployment, covering API calls and infrastructure needed to replace human reps.</t>
         </is>
       </c>
-      <c r="E9" s="593" t="inlineStr">
-        <is>
-          <t>Salesforce Agentforce $2/conv + Flex Credits press</t>
-        </is>
-      </c>
-      <c r="F9" s="573" t="inlineStr">
+      <c r="E9" s="610" t="inlineStr">
+        <is>
+          <t>Salesforce Agentforce pricing ($2/conv · ~$0.10/action)</t>
+        </is>
+      </c>
+      <c r="F9" s="615" t="inlineStr">
         <is>
           <t>SF publishes $2/conversation and ~$0.10/action. At ZI scale (~378 outbound roles = 25% of 1,513 S&amp;M), $5–10k/mo agents imply ~$23–45m; $15m is conservative.</t>
         </is>
       </c>
-      <c r="G9" s="593" t="inlineStr">
+      <c r="G9" s="612" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D10 (AI infrastructure)</t>
         </is>
       </c>
-      <c r="H9" s="593" t="inlineStr">
+      <c r="H9" s="612" t="inlineStr">
         <is>
           <t>highticketaisystems.com/blog/ai-sdr-pricing-explained</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="58" customHeight="1" s="244">
-      <c r="B10" s="596" t="inlineStr">
+    <row r="10" ht="62" customHeight="1" s="244">
+      <c r="B10" s="613" t="inlineStr">
         <is>
           <t>S&amp;M expense growth Y2+</t>
         </is>
       </c>
-      <c r="C10" s="597" t="n">
+      <c r="C10" s="608" t="n">
         <v>0.02</v>
       </c>
-      <c r="D10" s="573" t="inlineStr">
+      <c r="D10" s="609" t="inlineStr">
         <is>
           <t>Caps future marketing cost increases. Reasonable because AI scales infinitely without needing proportional headcount additions, severing the link between revenue growth and human hiring.</t>
         </is>
       </c>
-      <c r="E10" s="593" t="inlineStr">
+      <c r="E10" s="610" t="inlineStr">
         <is>
           <t>Gartner: agentic AI / inference scales as opex</t>
         </is>
       </c>
-      <c r="F10" s="573" t="inlineStr">
+      <c r="F10" s="611" t="inlineStr">
         <is>
           <t>Gartner documents production agentic AI as inference opex that scales without linear headcount. Cap S&amp;M growth at 2% to model that break from revenue-linked hiring.</t>
         </is>
       </c>
-      <c r="G10" s="593" t="inlineStr">
+      <c r="G10" s="612" t="inlineStr">
         <is>
           <t>Go to AI_Operating!E7 (payroll Y2+)</t>
         </is>
       </c>
-      <c r="H10" s="593" t="inlineStr">
+      <c r="H10" s="612" t="inlineStr">
         <is>
           <t>www.ciodive.com/news/AI-spending-soars-enterprise-maturity/827488/</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="58" customHeight="1" s="244">
-      <c r="B11" s="596" t="inlineStr">
+    <row r="11" ht="62" customHeight="1" s="244">
+      <c r="B11" s="607" t="inlineStr">
         <is>
           <t>G&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="C11" s="597" t="n">
+      <c r="C11" s="608" t="n">
         <v>0.18</v>
       </c>
-      <c r="D11" s="573" t="inlineStr">
+      <c r="D11" s="609" t="inlineStr">
         <is>
           <t>General administrative overhead costs. Reasonable for a public-to-private SaaS company, maintaining standard corporate expenses without relying on unrealistic operational magic outside of sales.</t>
         </is>
       </c>
-      <c r="E11" s="593" t="inlineStr">
+      <c r="E11" s="610" t="inlineStr">
         <is>
           <t>ZoomInfo FY24 G&amp;A $295.3m (company results)</t>
         </is>
       </c>
-      <c r="F11" s="573" t="inlineStr">
+      <c r="F11" s="611" t="inlineStr">
         <is>
           <t>ZI FY24 G&amp;A was $295.3m (~24% of revenue). Locking ~18% keeps standard corporate overhead while the thesis only attacks the sales floor—not finance/comp magic.</t>
         </is>
       </c>
-      <c r="G11" s="593" t="inlineStr">
+      <c r="G11" s="612" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D12 (G&amp;A)</t>
         </is>
       </c>
-      <c r="H11" s="593" t="inlineStr">
+      <c r="H11" s="612" t="inlineStr">
         <is>
           <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1" s="244">
-      <c r="B12" s="596" t="inlineStr">
+    <row r="12" ht="62" customHeight="1" s="244">
+      <c r="B12" s="613" t="inlineStr">
         <is>
           <t>CapEx reduction vs base</t>
         </is>
       </c>
-      <c r="C12" s="597" t="n">
+      <c r="C12" s="608" t="n">
         <v>0.05</v>
       </c>
-      <c r="D12" s="573" t="inlineStr">
+      <c r="D12" s="609" t="inlineStr">
         <is>
           <t>Lowers physical equipment spending. Reasonable because firing 15% of the sales team permanently eliminates the need to purchase and refresh their laptops and hardware.</t>
         </is>
       </c>
-      <c r="E12" s="593" t="inlineStr">
+      <c r="E12" s="610" t="inlineStr">
         <is>
           <t>In-house SDR all-in includes devices/tooling</t>
         </is>
       </c>
-      <c r="F12" s="573" t="inlineStr">
+      <c r="F12" s="611" t="inlineStr">
         <is>
           <t>Human SDR all-in budgets include laptops and seats. Cutting outbound humans removes refresh CapEx; −5% vs base CapEx rate is a small, directionally correct haircut.</t>
         </is>
       </c>
-      <c r="G12" s="593" t="inlineStr">
+      <c r="G12" s="612" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D19 (CapEx)</t>
         </is>
       </c>
-      <c r="H12" s="593" t="inlineStr">
+      <c r="H12" s="612" t="inlineStr">
         <is>
           <t>firstsales.io/blog/cost-per-meeting-outbound/</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1" s="244">
-      <c r="B13" s="596" t="inlineStr">
+    <row r="13" ht="62" customHeight="1" s="244">
+      <c r="B13" s="607" t="inlineStr">
         <is>
           <t>WC / receivables improvement</t>
         </is>
       </c>
-      <c r="C13" s="597" t="n">
+      <c r="C13" s="608" t="n">
         <v>0.1</v>
       </c>
-      <c r="D13" s="573" t="inlineStr">
+      <c r="D13" s="609" t="inlineStr">
         <is>
           <t>Speeds up cash collection from clients. Reasonable because automated AI billing systems can aggressively follow up on late invoices, freeing up cash for debt paydown.</t>
         </is>
       </c>
-      <c r="E13" s="593" t="inlineStr">
+      <c r="E13" s="610" t="inlineStr">
         <is>
           <t>ZI receivables ~80 days (SEC-derived ratios)</t>
         </is>
       </c>
-      <c r="F13" s="573" t="inlineStr">
+      <c r="F13" s="611" t="inlineStr">
         <is>
           <t>ZI receivables ~80 days show WC is real. Automated billing follow-ups can shorten DSO; −10% WC intensity vs base is a modest collections gain, not a wipeout.</t>
         </is>
       </c>
-      <c r="G13" s="593" t="inlineStr">
+      <c r="G13" s="612" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D20 (ΔNWC)</t>
         </is>
       </c>
-      <c r="H13" s="593" t="inlineStr">
+      <c r="H13" s="612" t="inlineStr">
         <is>
           <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="58" customHeight="1" s="244">
-      <c r="B14" s="596" t="inlineStr">
+    <row r="14" ht="62" customHeight="1" s="244">
+      <c r="B14" s="613" t="inlineStr">
         <is>
           <t>SOFR</t>
         </is>
       </c>
-      <c r="C14" s="599" t="n">
+      <c r="C14" s="616" t="n">
         <v>0.043</v>
       </c>
-      <c r="D14" s="573" t="inlineStr">
+      <c r="D14" s="609" t="inlineStr">
         <is>
           <t>The foundational secured lending interest rate. Reasonable and historically accurate for the macroeconomic environment, properly reflecting actual institutional baseline borrowing costs.</t>
         </is>
       </c>
-      <c r="E14" s="593" t="inlineStr">
+      <c r="E14" s="610" t="inlineStr">
         <is>
           <t>NY Fed official SOFR reference rate</t>
         </is>
       </c>
-      <c r="F14" s="573" t="inlineStr">
+      <c r="F14" s="611" t="inlineStr">
         <is>
           <t>SOFR is the NY Fed’s official overnight Treasury-repo financing benchmark used to price leveraged loans. ~4.3% is a planning level near recent SOFR prints (see FRED).</t>
         </is>
       </c>
-      <c r="G14" s="593" t="inlineStr">
+      <c r="G14" s="612" t="inlineStr">
         <is>
           <t>Go to Debt_Sweep_AI!C12 (TLA rate uses SOFR)</t>
         </is>
       </c>
-      <c r="H14" s="593" t="inlineStr">
+      <c r="H14" s="612" t="inlineStr">
         <is>
           <t>fred.stlouisfed.org/series/SOFR</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1" s="244">
-      <c r="B15" s="596" t="inlineStr">
+    <row r="15" ht="62" customHeight="1" s="244">
+      <c r="B15" s="607" t="inlineStr">
         <is>
           <t>Term Loan A spread</t>
         </is>
       </c>
-      <c r="C15" s="599" t="n">
+      <c r="C15" s="616" t="n">
         <v>0.04</v>
       </c>
-      <c r="D15" s="573" t="inlineStr">
+      <c r="D15" s="609" t="inlineStr">
         <is>
           <t>The risk premium for senior debt. Reasonable for a standard LBO, reflecting typical syndicated commercial bank pricing for secured corporate borrowing.</t>
         </is>
       </c>
-      <c r="E15" s="593" t="inlineStr">
+      <c r="E15" s="610" t="inlineStr">
         <is>
           <t>LBO debt structure: TLA illustrative spreads</t>
         </is>
       </c>
-      <c r="F15" s="573" t="inlineStr">
+      <c r="F15" s="611" t="inlineStr">
         <is>
           <t>Bank TLA in LBO guides typically prices tighter than TLB (often SOFR+~275–375bps). SOFR+400bps is a conservative senior bank spread independent of AI ops.</t>
         </is>
       </c>
-      <c r="G15" s="593" t="inlineStr">
+      <c r="G15" s="612" t="inlineStr">
         <is>
           <t>Go to Assumptions_Drivers!C27 (TLA rate)</t>
         </is>
       </c>
-      <c r="H15" s="593" t="inlineStr">
+      <c r="H15" s="612" t="inlineStr">
         <is>
           <t>ibinterviewquestions.com/guides/debt-capital-markets/term-loan-b-tlb-m</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="58" customHeight="1" s="244">
-      <c r="B16" s="596" t="inlineStr">
+    <row r="16" ht="62" customHeight="1" s="244">
+      <c r="B16" s="613" t="inlineStr">
         <is>
           <t>Term Loan B spread</t>
         </is>
       </c>
-      <c r="C16" s="599" t="n">
+      <c r="C16" s="616" t="n">
         <v>0.05</v>
       </c>
-      <c r="D16" s="573" t="inlineStr">
+      <c r="D16" s="609" t="inlineStr">
         <is>
           <t>The risk premium for riskier debt. Reasonable, as Term Loan B is usually held by institutional investors requiring higher yields for slightly higher risk.</t>
         </is>
       </c>
-      <c r="E16" s="593" t="inlineStr">
+      <c r="E16" s="610" t="inlineStr">
         <is>
           <t>TLB pricing often SOFR+300–500bps</t>
         </is>
       </c>
-      <c r="F16" s="573" t="inlineStr">
+      <c r="F16" s="611" t="inlineStr">
         <is>
           <t>Institutional TLB commonly prices SOFR+300–500bps. SOFR+500bps is the upper published band—set by syndicated loan markets, not by internal AI strategy.</t>
         </is>
       </c>
-      <c r="G16" s="593" t="inlineStr">
+      <c r="G16" s="612" t="inlineStr">
         <is>
           <t>Go to Assumptions_Drivers!C28 (TLB rate)</t>
         </is>
       </c>
-      <c r="H16" s="593" t="inlineStr">
+      <c r="H16" s="612" t="inlineStr">
         <is>
           <t>ryanoconnellfinance.com/lbo-debt-structure/</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="58" customHeight="1" s="244">
-      <c r="B17" s="596" t="inlineStr">
+    <row r="17" ht="62" customHeight="1" s="244">
+      <c r="B17" s="607" t="inlineStr">
         <is>
           <t>Mandatory amortization</t>
         </is>
       </c>
-      <c r="C17" s="597" t="n">
+      <c r="C17" s="608" t="n">
         <v>0.01</v>
       </c>
-      <c r="D17" s="573" t="inlineStr">
+      <c r="D17" s="609" t="inlineStr">
         <is>
           <t>Required annual principal repayment. Highly reasonable and standard market practice for leveraged loans, forcing a tiny minimum debt reduction each year.</t>
         </is>
       </c>
-      <c r="E17" s="593" t="inlineStr">
+      <c r="E17" s="610" t="inlineStr">
         <is>
           <t>Syndicated TLB ~1% annual amort standard</t>
         </is>
       </c>
-      <c r="F17" s="573" t="inlineStr">
+      <c r="F17" s="611" t="inlineStr">
         <is>
           <t>Market-standard institutional TLB schedules ~1% annual amortization with a bullet maturity. Loan docs—not AI FCF—set this mandatory floor.</t>
         </is>
       </c>
-      <c r="G17" s="593" t="inlineStr">
+      <c r="G17" s="612" t="inlineStr">
         <is>
           <t>Go to Debt_Sweep_AI!D5 (Mandatory 1%)</t>
         </is>
       </c>
-      <c r="H17" s="593" t="inlineStr">
+      <c r="H17" s="612" t="inlineStr">
         <is>
           <t>clearvaluelending.com/glossary/term-loan-b</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="58" customHeight="1" s="244">
-      <c r="B18" s="596" t="inlineStr">
+    <row r="18" ht="62" customHeight="1" s="244">
+      <c r="B18" s="613" t="inlineStr">
         <is>
           <t>Cash sweep %</t>
         </is>
       </c>
-      <c r="C18" s="597" t="n">
+      <c r="C18" s="608" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="573" t="inlineStr">
+      <c r="D18" s="609" t="inlineStr">
         <is>
           <t>Dedicates all excess cash to debt. Reasonable and standard for maximizing LBO returns, ensuring every free dollar generated immediately aggressively reduces outstanding leverage.</t>
         </is>
       </c>
-      <c r="E18" s="593" t="inlineStr">
+      <c r="E18" s="610" t="inlineStr">
         <is>
           <t>LBO optional prepay / excess cash practice</t>
         </is>
       </c>
-      <c r="F18" s="573" t="inlineStr">
+      <c r="F18" s="611" t="inlineStr">
         <is>
           <t>Sponsor LBOs typically sweep excess FCF to optional debt prepay after mandatory amort. 100% sweep maximizes deleveraging so AI margins hit MOIC/IRR.</t>
         </is>
       </c>
-      <c r="G18" s="593" t="inlineStr">
+      <c r="G18" s="612" t="inlineStr">
         <is>
           <t>Go to Debt_Sweep_AI!E5 (Total paydown)</t>
         </is>
       </c>
-      <c r="H18" s="593" t="inlineStr">
+      <c r="H18" s="612" t="inlineStr">
         <is>
           <t>ibinterviewquestions.com/guides/valuation-investment-banking/lbo-debt-</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1" s="244">
-      <c r="B19" s="596" t="inlineStr">
+    <row r="19" ht="62" customHeight="1" s="244">
+      <c r="B19" s="607" t="inlineStr">
         <is>
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="C19" s="597" t="n">
+      <c r="C19" s="608" t="n">
         <v>0.21</v>
       </c>
-      <c r="D19" s="573" t="inlineStr">
+      <c r="D19" s="609" t="inlineStr">
         <is>
           <t>Corporate income tax obligation. Perfectly reasonable because it strictly matches the current standard U.S. federal statutory corporate tax rate without aggressive tax-dodging assumptions.</t>
         </is>
       </c>
-      <c r="E19" s="593" t="inlineStr">
+      <c r="E19" s="610" t="inlineStr">
         <is>
           <t>PwC Tax Summaries: US federal CIT 21%</t>
         </is>
       </c>
-      <c r="F19" s="573" t="inlineStr">
+      <c r="F19" s="611" t="inlineStr">
         <is>
           <t>US federal corporate income tax is a flat 21% statutory rate. Operating-margin gains do not change the federal statutory rate used here.</t>
         </is>
       </c>
-      <c r="G19" s="593" t="inlineStr">
+      <c r="G19" s="612" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D18 (Net income)</t>
         </is>
       </c>
-      <c r="H19" s="593" t="inlineStr">
+      <c r="H19" s="612" t="inlineStr">
         <is>
           <t>tradingeconomics.com/united-states/corporate-tax-rate</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="58" customHeight="1" s="244">
-      <c r="B20" s="596" t="inlineStr">
+    <row r="20" ht="62" customHeight="1" s="244">
+      <c r="B20" s="613" t="inlineStr">
         <is>
           <t>Exit EV/EBITDA multiple</t>
         </is>
       </c>
-      <c r="C20" s="600" t="n">
+      <c r="C20" s="617" t="n">
         <v>13</v>
       </c>
-      <c r="D20" s="573" t="inlineStr">
+      <c r="D20" s="609" t="inlineStr">
         <is>
           <t>The valuation multiple upon selling. Reasonable to keep it conservative; relying on a 13x exit assumes no market inflation, proving returns come from operational growth.</t>
         </is>
       </c>
-      <c r="E20" s="593" t="inlineStr">
+      <c r="E20" s="610" t="inlineStr">
         <is>
           <t>PE SaaS buyouts often ~15–22x EBITDA</t>
         </is>
       </c>
-      <c r="F20" s="573" t="inlineStr">
+      <c r="F20" s="611" t="inlineStr">
         <is>
           <t>PE SaaS deals often underwrite ~15–22x EBITDA. Locking exit at 13x in BOTH cases is deliberately conservative so returns come from ops, not multiple expansion.</t>
         </is>
       </c>
-      <c r="G20" s="593" t="inlineStr">
+      <c r="G20" s="612" t="inlineStr">
         <is>
           <t>Go to LBO!D17 (Exit multiple)</t>
         </is>
       </c>
-      <c r="H20" s="593" t="inlineStr">
+      <c r="H20" s="612" t="inlineStr">
         <is>
           <t>aventis-advisors.com/software-valuation-multiples/</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1" s="244">
-      <c r="B21" s="596" t="inlineStr">
+    <row r="21" ht="62" customHeight="1" s="244">
+      <c r="B21" s="607" t="inlineStr">
         <is>
           <t>S&amp;M baseline ($m)</t>
         </is>
       </c>
-      <c r="C21" s="598" t="n">
+      <c r="C21" s="614" t="n">
         <v>425</v>
       </c>
-      <c r="D21" s="573" t="inlineStr">
+      <c r="D21" s="609" t="inlineStr">
         <is>
           <t>This is historical assumptions without AI. Total initial sales spend is reasonable, representing roughly 35% of FY24 revenue, perfectly aligning with standard SaaS benchmarks.</t>
         </is>
       </c>
-      <c r="E21" s="593" t="inlineStr">
+      <c r="E21" s="610" t="inlineStr">
         <is>
           <t>ZI FY24 S&amp;M $414.1m on $1,214.3m revenue</t>
         </is>
       </c>
-      <c r="F21" s="573" t="inlineStr">
+      <c r="F21" s="611" t="inlineStr">
         <is>
           <t>Company-reported FY24 S&amp;M = $414.1m (~34% of $1,214.3m). Model ~$425m (~35%) is a rounded baseline consistent with that filing.</t>
         </is>
       </c>
-      <c r="G21" s="593" t="inlineStr">
+      <c r="G21" s="612" t="inlineStr">
         <is>
           <t>Go to AI_Operating!C9 (S&amp;M human FY24A)</t>
         </is>
       </c>
-      <c r="H21" s="593" t="inlineStr">
+      <c r="H21" s="612" t="inlineStr">
         <is>
           <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="58" customHeight="1" s="244">
-      <c r="B22" s="596" t="inlineStr">
+    <row r="22" ht="62" customHeight="1" s="244">
+      <c r="B22" s="613" t="inlineStr">
         <is>
           <t>Payroll baseline ($m)</t>
         </is>
       </c>
-      <c r="C22" s="598" t="n">
+      <c r="C22" s="614" t="n">
         <v>318.8</v>
       </c>
-      <c r="D22" s="573" t="inlineStr">
+      <c r="D22" s="609" t="inlineStr">
         <is>
           <t>This is historical assumptions without AI. The fixed salary portion is reasonable, representing 75% of S&amp;M, accurately reflecting that human software sales floors are base-salary heavy.</t>
         </is>
       </c>
-      <c r="E22" s="593" t="inlineStr">
+      <c r="E22" s="610" t="inlineStr">
         <is>
           <t>SDR OTE mostly base (~70%) — SyncGTM</t>
         </is>
       </c>
-      <c r="F22" s="573" t="inlineStr">
+      <c r="F22" s="611" t="inlineStr">
         <is>
           <t>With ~70/30 base/variable SDR mix, most people cost is payroll. Payroll baseline = 75% of S&amp;M matches that base-salary-heavy sales-floor structure.</t>
         </is>
       </c>
-      <c r="G22" s="593" t="inlineStr">
+      <c r="G22" s="612" t="inlineStr">
         <is>
           <t>Go to AI_Operating!C7 (Payroll FY24A)</t>
         </is>
       </c>
-      <c r="H22" s="593" t="inlineStr">
+      <c r="H22" s="612" t="inlineStr">
         <is>
           <t>pulserevops.com/knowledge/ra0197</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="58" customHeight="1" s="244">
-      <c r="B23" s="596" t="inlineStr">
+    <row r="23" ht="62" customHeight="1" s="244">
+      <c r="B23" s="607" t="inlineStr">
         <is>
           <t>Commission baseline ($m)</t>
         </is>
       </c>
-      <c r="C23" s="598" t="n">
+      <c r="C23" s="614" t="n">
         <v>106.2</v>
       </c>
-      <c r="D23" s="573" t="inlineStr">
+      <c r="D23" s="609" t="inlineStr">
         <is>
           <t>This is historical assumptions without AI. The variable payout is reasonable, calculating exactly to the remaining 25% of the budget, representing standard quota-based enterprise sales incentives.</t>
         </is>
       </c>
-      <c r="E23" s="593" t="inlineStr">
+      <c r="E23" s="610" t="inlineStr">
         <is>
           <t>Variable ~30–35% of tech SDR OTE</t>
         </is>
       </c>
-      <c r="F23" s="573" t="inlineStr">
+      <c r="F23" s="611" t="inlineStr">
         <is>
           <t>Tech SDR variable is typically ~30–35% of OTE. Setting commission pool at 25% of S&amp;M is a slightly conservative carve of total S&amp;M for variable payouts.</t>
         </is>
       </c>
-      <c r="G23" s="593" t="inlineStr">
+      <c r="G23" s="612" t="inlineStr">
         <is>
           <t>Go to AI_Operating!C8 (Commissions FY24A)</t>
         </is>
       </c>
-      <c r="H23" s="593" t="inlineStr">
+      <c r="H23" s="612" t="inlineStr">
         <is>
           <t>syncgtm.com/blog/how-to-pay-sales-development-rep</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="58" customHeight="1" s="244">
-      <c r="B24" s="596" t="inlineStr">
+    <row r="24" ht="62" customHeight="1" s="244">
+      <c r="B24" s="613" t="inlineStr">
         <is>
           <t>CapEx base % of rev</t>
         </is>
       </c>
-      <c r="C24" s="597" t="n">
+      <c r="C24" s="608" t="n">
         <v>0.02</v>
       </c>
-      <c r="D24" s="573" t="inlineStr">
+      <c r="D24" s="609" t="inlineStr">
         <is>
           <t>This is historical assumptions without AI. Normal hardware and capitalized software spending is reasonable for asset-light tech companies investing heavily in code rather than factories.</t>
         </is>
       </c>
-      <c r="E24" s="593" t="inlineStr">
+      <c r="E24" s="610" t="inlineStr">
         <is>
           <t>ZI FY24 strong FCF / asset-light SaaS profile</t>
         </is>
       </c>
-      <c r="F24" s="573" t="inlineStr">
+      <c r="F24" s="611" t="inlineStr">
         <is>
           <t>SaaS is asset-light vs industrials; ZI still printed strong FY24 FCF. 2% of revenue is a simple maintenance CapEx planning rate before the AI −5% haircut.</t>
         </is>
       </c>
-      <c r="G24" s="593" t="inlineStr">
+      <c r="G24" s="612" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D19 (CapEx)</t>
         </is>
       </c>
-      <c r="H24" s="593" t="inlineStr">
+      <c r="H24" s="612" t="inlineStr">
         <is>
           <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="58" customHeight="1" s="244">
-      <c r="B25" s="596" t="inlineStr">
+    <row r="25" ht="62" customHeight="1" s="244">
+      <c r="B25" s="607" t="inlineStr">
         <is>
           <t>WC base % of Δrev</t>
         </is>
       </c>
-      <c r="C25" s="597" t="n">
+      <c r="C25" s="608" t="n">
         <v>0.02</v>
       </c>
-      <c r="D25" s="573" t="inlineStr">
+      <c r="D25" s="609" t="inlineStr">
         <is>
           <t>This is historical assumptions without AI. Normal working capital needs are reasonable, showing that as revenue grows, a small percentage of cash gets tied up in daily operations.</t>
         </is>
       </c>
-      <c r="E25" s="593" t="inlineStr">
+      <c r="E25" s="610" t="inlineStr">
         <is>
           <t>ZI receivables days ~80 (WC intensity)</t>
         </is>
       </c>
-      <c r="F25" s="573" t="inlineStr">
+      <c r="F25" s="611" t="inlineStr">
         <is>
           <t>Receivables ~80 days imply WC scales with growth. Using 2% of Δrevenue as ΔNWC is a simplified SaaS WC plug anchored to that receivables reality.</t>
         </is>
       </c>
-      <c r="G25" s="593" t="inlineStr">
+      <c r="G25" s="612" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D20 (ΔNWC)</t>
         </is>
       </c>
-      <c r="H25" s="593" t="inlineStr">
+      <c r="H25" s="612" t="inlineStr">
         <is>
           <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="564" t="inlineStr">
-        <is>
-          <t>Computed rates (from SOFR + spreads above)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="58" customHeight="1" s="244">
-      <c r="B27" s="596" t="inlineStr">
+      <c r="B26" s="618" t="inlineStr">
+        <is>
+          <t>Computed rates (SOFR + spreads) — still sourced on the same row</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="62" customHeight="1" s="244">
+      <c r="B27" s="613" t="inlineStr">
         <is>
           <t>TLA rate (SOFR+4)</t>
         </is>
       </c>
-      <c r="C27" s="601">
+      <c r="C27" s="619">
         <f>C14+C15</f>
         <v/>
       </c>
-      <c r="D27" s="573" t="inlineStr">
+      <c r="D27" s="609" t="inlineStr">
         <is>
           <t>Total Term Loan A interest. Mathematically correct and reasonable for the total borrowing cost demanded by senior lenders in this specific rate environment.</t>
         </is>
       </c>
-      <c r="E27" s="593" t="inlineStr">
+      <c r="E27" s="610" t="inlineStr">
         <is>
           <t>LBO TLA = SOFR + senior bank spread</t>
         </is>
       </c>
-      <c r="F27" s="573" t="inlineStr">
+      <c r="F27" s="611" t="inlineStr">
         <is>
           <t>Computed as SOFR (C14) + TLA spread (C15). All-in ~8.3% matches senior secured bank pricing in this SOFR + 400bps setup.</t>
         </is>
       </c>
-      <c r="G27" s="593" t="inlineStr">
+      <c r="G27" s="612" t="inlineStr">
         <is>
           <t>Go to Debt_Sweep_AI!C12 (TLA rate)</t>
         </is>
       </c>
-      <c r="H27" s="593" t="inlineStr">
+      <c r="H27" s="612" t="inlineStr">
         <is>
           <t>www.newyorkfed.org/markets/reference-rates/sofr</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="58" customHeight="1" s="244">
-      <c r="B28" s="596" t="inlineStr">
+    <row r="28" ht="62" customHeight="1" s="244">
+      <c r="B28" s="607" t="inlineStr">
         <is>
           <t>TLB rate (SOFR+5)</t>
         </is>
       </c>
-      <c r="C28" s="601">
+      <c r="C28" s="619">
         <f>C14+C16</f>
         <v/>
       </c>
-      <c r="D28" s="573" t="inlineStr">
+      <c r="D28" s="609" t="inlineStr">
         <is>
           <t>Total Term Loan B interest. Mathematically correct and perfectly reasonable, pricing the institutional debt risk appropriately above the safer Term Loan A.</t>
         </is>
       </c>
-      <c r="E28" s="593" t="inlineStr">
+      <c r="E28" s="610" t="inlineStr">
         <is>
           <t>LBO TLB = SOFR + institutional spread</t>
         </is>
       </c>
-      <c r="F28" s="573" t="inlineStr">
+      <c r="F28" s="611" t="inlineStr">
         <is>
           <t>Computed as SOFR (C14) + TLB spread (C16). All-in ~9.3% prices institutional TLB risk appropriately above TLA in this structure.</t>
         </is>
       </c>
-      <c r="G28" s="593" t="inlineStr">
+      <c r="G28" s="612" t="inlineStr">
         <is>
           <t>Go to Debt_Sweep_AI!D12 (TLB rate)</t>
         </is>
       </c>
-      <c r="H28" s="593" t="inlineStr">
+      <c r="H28" s="612" t="inlineStr">
         <is>
           <t>www.newyorkfed.org/markets/reference-rates/sofr</t>
         </is>
       </c>
     </row>
+    <row r="29" ht="36" customHeight="1" s="244">
+      <c r="B29" s="618" t="inlineStr">
+        <is>
+          <t>AI $15m triangulation (row 9, col F):</t>
+        </is>
+      </c>
+      <c r="C29" s="620" t="inlineStr">
+        <is>
+          <t>SF publishes $2/conversation and ~$0.10/action. At ZI scale (~378 outbound roles = 25% of 1,513 S&amp;M), $5–10k/mo agents imply ~$23–45m; $15m is conservative.</t>
+        </is>
+      </c>
+      <c r="D29" s="621" t="n"/>
+      <c r="E29" s="621" t="n"/>
+      <c r="F29" s="622" t="n"/>
+    </row>
     <row r="30">
-      <c r="B30" s="564" t="inlineStr">
-        <is>
-          <t>PDF of this source map:</t>
+      <c r="B30" s="618" t="inlineStr">
+        <is>
+          <t>PDF source map:</t>
         </is>
       </c>
       <c r="C30" s="593" t="inlineStr">
@@ -5951,14 +6132,15 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="591" t="inlineStr">
-        <is>
-          <t>Educational / research use only — not investment advice.</t>
+      <c r="B31" s="623" t="inlineStr">
+        <is>
+          <t>Educational / research use only — not investment advice. Vendor list prices change; treat triangulation as order-of-magnitude support.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="C29:F29"/>
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <hyperlinks>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -1938,7 +1938,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="624">
+  <cellXfs count="629">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3046,6 +3046,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="34" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="0" fillId="34" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="191" fontId="0" fillId="34" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="34" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="187">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5437,11 +5444,11 @@
         </is>
       </c>
       <c r="C9" s="614" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D9" s="609" t="inlineStr">
         <is>
-          <t>Fixed cost for AI software and compute. Reasonable estimate for enterprise-scale AI deployment, covering API calls and infrastructure needed to replace human reps.</t>
+          <t>Fixed cost for AI software and compute set to $34m — the midpoint of the $23–45m enterprise AI-agent triangulation (avg of low/high). Covers API calls and infra to replace human reps.</t>
         </is>
       </c>
       <c r="E9" s="610" t="inlineStr">
@@ -5451,7 +5458,7 @@
       </c>
       <c r="F9" s="615" t="inlineStr">
         <is>
-          <t>SF publishes $2/conversation and ~$0.10/action. At ZI scale (~378 outbound roles = 25% of 1,513 S&amp;M), $5–10k/mo agents imply ~$23–45m; $15m is conservative.</t>
+          <t>SF publishes $2/conversation and ~$0.10/action. At ZI scale (~378 outbound roles = 25% of 1,513 S&amp;M), $5–10k/mo agents imply ~$23–45m; model uses midpoint avg((23+45)/2) = $34m.</t>
         </is>
       </c>
       <c r="G9" s="612" t="inlineStr">
@@ -6112,7 +6119,7 @@
       </c>
       <c r="C29" s="620" t="inlineStr">
         <is>
-          <t>SF publishes $2/conversation and ~$0.10/action. At ZI scale (~378 outbound roles = 25% of 1,513 S&amp;M), $5–10k/mo agents imply ~$23–45m; $15m is conservative.</t>
+          <t>SF publishes $2/conversation and ~$0.10/action. At ZI scale (~378 outbound roles = 25% of 1,513 S&amp;M), $5–10k/mo agents imply ~$23–45m; model uses midpoint avg((23+45)/2) = $34m.</t>
         </is>
       </c>
       <c r="D29" s="621" t="n"/>
@@ -12159,18 +12166,18 @@
           <t>Y2 EBITDA margin</t>
         </is>
       </c>
-      <c r="C31" s="565" t="n">
+      <c r="C31" s="624" t="n">
         <v>0.1085118998600017</v>
       </c>
-      <c r="D31" s="565" t="n">
-        <v>0.2012029241075531</v>
-      </c>
-      <c r="E31" s="565" t="n">
-        <v>0.09269102424755141</v>
-      </c>
-      <c r="F31" s="603" t="inlineStr">
-        <is>
-          <t>Year 2 operating profitability; the AI strategy drove this from 10.9% to 20.1%, expanding the margin by 9.3%.</t>
+      <c r="D31" s="624" t="n">
+        <v>0.1882716226673465</v>
+      </c>
+      <c r="E31" s="624" t="n">
+        <v>0.07975972280734472</v>
+      </c>
+      <c r="F31" s="625" t="inlineStr">
+        <is>
+          <t>Year 2 operating profitability; the AI strategy drove this from 10.9% to 18.8%, expanding the margin by 8.0%.</t>
         </is>
       </c>
     </row>
@@ -12180,18 +12187,18 @@
           <t>Y2 margin vs baseline (bps)</t>
         </is>
       </c>
-      <c r="C32" s="567" t="n">
+      <c r="C32" s="626" t="n">
         <v>-422.7456147574727</v>
       </c>
-      <c r="D32" s="567" t="n">
-        <v>504.1646277180415</v>
-      </c>
-      <c r="E32" s="567" t="n">
-        <v>926.9102424755141</v>
-      </c>
-      <c r="F32" s="603" t="inlineStr">
-        <is>
-          <t>The difference from baseline margin; AI implementation increased this metric by 926.9 basis points to reach 504.2.</t>
+      <c r="D32" s="626" t="n">
+        <v>374.8516133159746</v>
+      </c>
+      <c r="E32" s="626" t="n">
+        <v>797.5972280734472</v>
+      </c>
+      <c r="F32" s="625" t="inlineStr">
+        <is>
+          <t>The difference from baseline margin; AI implementation increased this metric by 797.6 basis points to reach 374.9.</t>
         </is>
       </c>
     </row>
@@ -12201,18 +12208,18 @@
           <t>Y5 EBITDA ($m)</t>
         </is>
       </c>
-      <c r="C33" s="567" t="n">
+      <c r="C33" s="626" t="n">
         <v>212.2104606600003</v>
       </c>
-      <c r="D33" s="567" t="n">
-        <v>496.3963076296004</v>
-      </c>
-      <c r="E33" s="567" t="n">
-        <v>284.1858469696001</v>
-      </c>
-      <c r="F33" s="603" t="inlineStr">
-        <is>
-          <t>Year 5 operating cash flow proxy; AI-driven cost savings boosted this figure by $284.2 million to $496.4 million.</t>
+      <c r="D33" s="626" t="n">
+        <v>477.3963076296004</v>
+      </c>
+      <c r="E33" s="626" t="n">
+        <v>265.1858469696001</v>
+      </c>
+      <c r="F33" s="625" t="inlineStr">
+        <is>
+          <t>Year 5 EBITDA; AI-driven cost savings (with $34m AI infra) boosted this to $477.4m vs Base $212.2m.</t>
         </is>
       </c>
     </row>
@@ -12222,18 +12229,18 @@
           <t>Exit EV @ 13x ($m)</t>
         </is>
       </c>
-      <c r="C34" s="567" t="n">
+      <c r="C34" s="626" t="n">
         <v>2758.735988580003</v>
       </c>
-      <c r="D34" s="567" t="n">
-        <v>6453.151999184804</v>
-      </c>
-      <c r="E34" s="567" t="n">
-        <v>3694.416010604801</v>
-      </c>
-      <c r="F34" s="603" t="inlineStr">
-        <is>
-          <t>Projected exit Enterprise Value; higher EBITDA from AI increased this valuation by $3,694.4 million to $6,453.2 million.</t>
+      <c r="D34" s="626" t="n">
+        <v>6206.151999184804</v>
+      </c>
+      <c r="E34" s="626" t="n">
+        <v>3447.416010604801</v>
+      </c>
+      <c r="F34" s="625" t="inlineStr">
+        <is>
+          <t>Projected exit EV; higher EBITDA from AI increased this valuation by $3,447.4m to $6,206.2m.</t>
         </is>
       </c>
     </row>
@@ -12243,18 +12250,18 @@
           <t>Exit net debt ($m)</t>
         </is>
       </c>
-      <c r="C35" s="567" t="n">
+      <c r="C35" s="626" t="n">
         <v>557.1124750633038</v>
       </c>
-      <c r="D35" s="567" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="567" t="n">
+      <c r="D35" s="626" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="626" t="n">
         <v>-557.1124750633038</v>
       </c>
-      <c r="F35" s="603" t="inlineStr">
-        <is>
-          <t>Remaining debt balance at exit; higher cash flow from the AI strategy paid down an extra $557.1 million vs Base.</t>
+      <c r="F35" s="625" t="inlineStr">
+        <is>
+          <t>Remaining debt at exit; AI case $0.0m vs Base $557.1m.</t>
         </is>
       </c>
     </row>
@@ -12264,18 +12271,18 @@
           <t>Exit equity value ($m)</t>
         </is>
       </c>
-      <c r="C36" s="567" t="n">
+      <c r="C36" s="626" t="n">
         <v>2201.623513516699</v>
       </c>
-      <c r="D36" s="567" t="n">
-        <v>6453.151999184804</v>
-      </c>
-      <c r="E36" s="567" t="n">
-        <v>4251.528485668105</v>
-      </c>
-      <c r="F36" s="603" t="inlineStr">
-        <is>
-          <t>Total payout to equity holders; the AI strategy increased this final payout by $4,251.5 million to $6,453.2 million.</t>
+      <c r="D36" s="626" t="n">
+        <v>6206.151999184804</v>
+      </c>
+      <c r="E36" s="626" t="n">
+        <v>4004.528485668105</v>
+      </c>
+      <c r="F36" s="625" t="inlineStr">
+        <is>
+          <t>Total equity payout; AI strategy increased final payout by $4,004.5m to $6,206.2m.</t>
         </is>
       </c>
     </row>
@@ -12285,18 +12292,18 @@
           <t>MOIC</t>
         </is>
       </c>
-      <c r="C37" s="568" t="n">
+      <c r="C37" s="627" t="n">
         <v>1.17652754423803</v>
       </c>
-      <c r="D37" s="568" t="n">
-        <v>3.448505626681045</v>
-      </c>
-      <c r="E37" s="568" t="n">
-        <v>2.271978082443015</v>
-      </c>
-      <c r="F37" s="603" t="inlineStr">
-        <is>
-          <t>Multiple on Invested Capital; the AI strategy significantly improved the total gross cash return from 1.18x to 3.45x.</t>
+      <c r="D37" s="627" t="n">
+        <v>3.316511077366568</v>
+      </c>
+      <c r="E37" s="627" t="n">
+        <v>2.139983533128538</v>
+      </c>
+      <c r="F37" s="625" t="inlineStr">
+        <is>
+          <t>Multiple on Invested Capital; AI improved gross cash return from 1.18x to 3.32x.</t>
         </is>
       </c>
     </row>
@@ -12306,18 +12313,18 @@
           <t>IRR</t>
         </is>
       </c>
-      <c r="C38" s="565" t="n">
+      <c r="C38" s="624" t="n">
         <v>0.03304780632992022</v>
       </c>
-      <c r="D38" s="565" t="n">
-        <v>0.2809323319237782</v>
-      </c>
-      <c r="E38" s="565" t="n">
-        <v>0.247884525593858</v>
-      </c>
-      <c r="F38" s="603" t="inlineStr">
-        <is>
-          <t>Annualized compound return rate over a 5-year period; replacing human SDRs with AI boosted this return by 24.8 percentage points to 28.1%.</t>
+      <c r="D38" s="624" t="n">
+        <v>0.2709728997774654</v>
+      </c>
+      <c r="E38" s="624" t="n">
+        <v>0.2379250934475452</v>
+      </c>
+      <c r="F38" s="625" t="inlineStr">
+        <is>
+          <t>5-year IRR; AI boosted return by 23.8 percentage points to 27.1% (AI infra now $34m midpoint).</t>
         </is>
       </c>
     </row>
@@ -12338,14 +12345,14 @@
     <row r="41">
       <c r="B41" s="569" t="inlineStr">
         <is>
-          <t>AI case IRR 28.1% − Base IRR 3.3% = 24.8 percentage points of IRR</t>
+          <t>AI case IRR 27.1% − Base IRR 3.3% = 23.8 percentage points of IRR</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="569" t="inlineStr">
         <is>
-          <t>Y2 AI EBITDA margin 20.1% vs baseline 15.1% = 504 bps (target ≥500: YES)</t>
+          <t>Y2 AI EBITDA margin 18.8% vs baseline 15.1% = 375 bps (target ≥500: NO)</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12397,7 @@
         <v>10.85</v>
       </c>
       <c r="D50" t="n">
-        <v>20.12</v>
+        <v>18.83</v>
       </c>
     </row>
     <row r="51">
@@ -12403,7 +12410,7 @@
         <v>-422.75</v>
       </c>
       <c r="D51" t="n">
-        <v>504.16</v>
+        <v>374.85</v>
       </c>
     </row>
     <row r="52">
@@ -12416,7 +12423,7 @@
         <v>212.21</v>
       </c>
       <c r="D52" t="n">
-        <v>496.4</v>
+        <v>477.4</v>
       </c>
     </row>
     <row r="53">
@@ -12429,7 +12436,7 @@
         <v>2201.62</v>
       </c>
       <c r="D53" t="n">
-        <v>6453.15</v>
+        <v>6206.15</v>
       </c>
     </row>
     <row r="54">
@@ -12442,7 +12449,7 @@
         <v>1.18</v>
       </c>
       <c r="D54" t="n">
-        <v>3.45</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="55">
@@ -12455,7 +12462,7 @@
         <v>3.3</v>
       </c>
       <c r="D55" t="n">
-        <v>28.09</v>
+        <v>27.1</v>
       </c>
     </row>
   </sheetData>
@@ -13699,117 +13706,117 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="580" t="n">
+      <c r="B5" s="628" t="n">
         <v>2025</v>
       </c>
-      <c r="C5" s="567" t="n">
-        <v>121.543319</v>
-      </c>
-      <c r="D5" s="567" t="n">
+      <c r="C5" s="626" t="n">
+        <v>106.533319</v>
+      </c>
+      <c r="D5" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
-      <c r="E5" s="567" t="n">
-        <v>121.543319</v>
-      </c>
-      <c r="F5" s="567" t="n">
-        <v>793.956681</v>
-      </c>
-      <c r="G5" s="567" t="n">
+      <c r="E5" s="626" t="n">
+        <v>106.533319</v>
+      </c>
+      <c r="F5" s="626" t="n">
+        <v>808.966681</v>
+      </c>
+      <c r="G5" s="626" t="n">
         <v>877.5180999999999</v>
       </c>
-      <c r="H5" s="567" t="n">
-        <v>83.56141899999989</v>
+      <c r="H5" s="626" t="n">
+        <v>68.5514189999999</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="580" t="n">
+      <c r="B6" s="628" t="n">
         <v>2026</v>
       </c>
-      <c r="C6" s="567" t="n">
-        <v>171.4952368268301</v>
-      </c>
-      <c r="D6" s="567" t="n">
+      <c r="C6" s="626" t="n">
+        <v>155.5010311268301</v>
+      </c>
+      <c r="D6" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
-      <c r="E6" s="567" t="n">
-        <v>171.4952368268301</v>
-      </c>
-      <c r="F6" s="567" t="n">
-        <v>622.4614441731698</v>
-      </c>
-      <c r="G6" s="567" t="n">
+      <c r="E6" s="626" t="n">
+        <v>155.5010311268301</v>
+      </c>
+      <c r="F6" s="626" t="n">
+        <v>653.4656498731698</v>
+      </c>
+      <c r="G6" s="626" t="n">
         <v>824.8037622999997</v>
       </c>
-      <c r="H6" s="567" t="n">
-        <v>202.3423181268299</v>
+      <c r="H6" s="626" t="n">
+        <v>171.3381124268299</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="580" t="n">
+      <c r="B7" s="628" t="n">
         <v>2027</v>
       </c>
-      <c r="C7" s="567" t="n">
-        <v>229.3706423055654</v>
-      </c>
-      <c r="D7" s="567" t="n">
+      <c r="C7" s="626" t="n">
+        <v>212.3276965378165</v>
+      </c>
+      <c r="D7" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
-      <c r="E7" s="567" t="n">
-        <v>229.3706423055654</v>
-      </c>
-      <c r="F7" s="567" t="n">
-        <v>393.0908018676043</v>
-      </c>
-      <c r="G7" s="567" t="n">
+      <c r="E7" s="626" t="n">
+        <v>212.3276965378165</v>
+      </c>
+      <c r="F7" s="626" t="n">
+        <v>441.1379533353534</v>
+      </c>
+      <c r="G7" s="626" t="n">
         <v>754.9762005708997</v>
       </c>
-      <c r="H7" s="567" t="n">
-        <v>361.8853987032953</v>
+      <c r="H7" s="626" t="n">
+        <v>313.8382472355463</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="580" t="n">
+      <c r="B8" s="628" t="n">
         <v>2028</v>
       </c>
-      <c r="C8" s="567" t="n">
-        <v>296.6736983899872</v>
-      </c>
-      <c r="D8" s="567" t="n">
+      <c r="C8" s="626" t="n">
+        <v>278.1336741716516</v>
+      </c>
+      <c r="D8" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
-      <c r="E8" s="567" t="n">
-        <v>296.6736983899872</v>
-      </c>
-      <c r="F8" s="567" t="n">
-        <v>96.41710347761716</v>
-      </c>
-      <c r="G8" s="567" t="n">
+      <c r="E8" s="626" t="n">
+        <v>278.1336741716516</v>
+      </c>
+      <c r="F8" s="626" t="n">
+        <v>163.0042791637017</v>
+      </c>
+      <c r="G8" s="626" t="n">
         <v>665.9609770683334</v>
       </c>
-      <c r="H8" s="567" t="n">
-        <v>569.5438735907162</v>
+      <c r="H8" s="626" t="n">
+        <v>502.9566979046317</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="580" t="n">
+      <c r="B9" s="628" t="n">
         <v>2029</v>
       </c>
-      <c r="C9" s="567" t="n">
-        <v>374.8388640800935</v>
-      </c>
-      <c r="D9" s="567" t="n">
+      <c r="C9" s="626" t="n">
+        <v>355.725762314317</v>
+      </c>
+      <c r="D9" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
-      <c r="E9" s="567" t="n">
-        <v>96.41710347761716</v>
-      </c>
-      <c r="F9" s="567" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="567" t="n">
+      <c r="E9" s="626" t="n">
+        <v>163.0042791637017</v>
+      </c>
+      <c r="F9" s="626" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="626" t="n">
         <v>557.1124750633038</v>
       </c>
-      <c r="H9" s="567" t="n">
+      <c r="H9" s="626" t="n">
         <v>557.1124750633038</v>
       </c>
     </row>
@@ -13926,19 +13933,19 @@
       <c r="C5" s="582" t="n">
         <v>1214.3</v>
       </c>
-      <c r="D5" s="567" t="n">
+      <c r="D5" s="626" t="n">
         <v>1335.73</v>
       </c>
-      <c r="E5" s="567" t="n">
+      <c r="E5" s="626" t="n">
         <v>1469.303</v>
       </c>
-      <c r="F5" s="567" t="n">
+      <c r="F5" s="626" t="n">
         <v>1616.2333</v>
       </c>
-      <c r="G5" s="567" t="n">
+      <c r="G5" s="626" t="n">
         <v>1777.85663</v>
       </c>
-      <c r="H5" s="567" t="n">
+      <c r="H5" s="626" t="n">
         <v>1955.642293000001</v>
       </c>
     </row>
@@ -13951,19 +13958,19 @@
       <c r="C6" s="582" t="n">
         <v>242.8599999999999</v>
       </c>
-      <c r="D6" s="567" t="n">
+      <c r="D6" s="626" t="n">
         <v>267.146</v>
       </c>
-      <c r="E6" s="567" t="n">
+      <c r="E6" s="626" t="n">
         <v>293.8606</v>
       </c>
-      <c r="F6" s="567" t="n">
+      <c r="F6" s="626" t="n">
         <v>323.24666</v>
       </c>
-      <c r="G6" s="567" t="n">
+      <c r="G6" s="626" t="n">
         <v>355.571326</v>
       </c>
-      <c r="H6" s="567" t="n">
+      <c r="H6" s="626" t="n">
         <v>391.1284586</v>
       </c>
     </row>
@@ -13976,19 +13983,19 @@
       <c r="C7" s="582" t="n">
         <v>318.8</v>
       </c>
-      <c r="D7" s="567" t="n">
+      <c r="D7" s="626" t="n">
         <v>350.68</v>
       </c>
-      <c r="E7" s="567" t="n">
+      <c r="E7" s="626" t="n">
         <v>385.748</v>
       </c>
-      <c r="F7" s="567" t="n">
+      <c r="F7" s="626" t="n">
         <v>424.3228000000001</v>
       </c>
-      <c r="G7" s="567" t="n">
+      <c r="G7" s="626" t="n">
         <v>466.7550800000001</v>
       </c>
-      <c r="H7" s="567" t="n">
+      <c r="H7" s="626" t="n">
         <v>513.4305880000002</v>
       </c>
     </row>
@@ -14001,19 +14008,19 @@
       <c r="C8" s="582" t="n">
         <v>106.2</v>
       </c>
-      <c r="D8" s="567" t="n">
+      <c r="D8" s="626" t="n">
         <v>116.82</v>
       </c>
-      <c r="E8" s="567" t="n">
+      <c r="E8" s="626" t="n">
         <v>128.502</v>
       </c>
-      <c r="F8" s="567" t="n">
+      <c r="F8" s="626" t="n">
         <v>141.3522</v>
       </c>
-      <c r="G8" s="567" t="n">
+      <c r="G8" s="626" t="n">
         <v>155.48742</v>
       </c>
-      <c r="H8" s="567" t="n">
+      <c r="H8" s="626" t="n">
         <v>171.0361620000001</v>
       </c>
     </row>
@@ -14026,19 +14033,19 @@
       <c r="C9" s="582" t="n">
         <v>425</v>
       </c>
-      <c r="D9" s="567" t="n">
+      <c r="D9" s="626" t="n">
         <v>467.5</v>
       </c>
-      <c r="E9" s="567" t="n">
+      <c r="E9" s="626" t="n">
         <v>514.25</v>
       </c>
-      <c r="F9" s="567" t="n">
+      <c r="F9" s="626" t="n">
         <v>565.6750000000002</v>
       </c>
-      <c r="G9" s="567" t="n">
+      <c r="G9" s="626" t="n">
         <v>622.2425000000002</v>
       </c>
-      <c r="H9" s="567" t="n">
+      <c r="H9" s="626" t="n">
         <v>684.4667500000003</v>
       </c>
     </row>
@@ -14051,19 +14058,19 @@
       <c r="C10" s="582" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="567" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="567" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="567" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="567" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="567" t="n">
+      <c r="D10" s="626" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="626" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="626" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="626" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="626" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14076,19 +14083,19 @@
       <c r="C11" s="582" t="n">
         <v>196.1</v>
       </c>
-      <c r="D11" s="567" t="n">
+      <c r="D11" s="626" t="n">
         <v>215.71</v>
       </c>
-      <c r="E11" s="567" t="n">
+      <c r="E11" s="626" t="n">
         <v>237.281</v>
       </c>
-      <c r="F11" s="567" t="n">
+      <c r="F11" s="626" t="n">
         <v>261.0091</v>
       </c>
-      <c r="G11" s="567" t="n">
+      <c r="G11" s="626" t="n">
         <v>287.11001</v>
       </c>
-      <c r="H11" s="567" t="n">
+      <c r="H11" s="626" t="n">
         <v>315.8210110000001</v>
       </c>
     </row>
@@ -14101,19 +14108,19 @@
       <c r="C12" s="582" t="n">
         <v>218.574</v>
       </c>
-      <c r="D12" s="567" t="n">
+      <c r="D12" s="626" t="n">
         <v>240.4314</v>
       </c>
-      <c r="E12" s="567" t="n">
+      <c r="E12" s="626" t="n">
         <v>264.47454</v>
       </c>
-      <c r="F12" s="567" t="n">
+      <c r="F12" s="626" t="n">
         <v>290.921994</v>
       </c>
-      <c r="G12" s="567" t="n">
+      <c r="G12" s="626" t="n">
         <v>320.0141934000001</v>
       </c>
-      <c r="H12" s="567" t="n">
+      <c r="H12" s="626" t="n">
         <v>352.0156127400001</v>
       </c>
     </row>
@@ -14126,19 +14133,19 @@
       <c r="C13" s="582" t="n">
         <v>183.1</v>
       </c>
-      <c r="D13" s="567" t="n">
+      <c r="D13" s="626" t="n">
         <v>144.9426000000001</v>
       </c>
-      <c r="E13" s="567" t="n">
+      <c r="E13" s="626" t="n">
         <v>159.4368600000001</v>
       </c>
-      <c r="F13" s="567" t="n">
+      <c r="F13" s="626" t="n">
         <v>175.380546</v>
       </c>
-      <c r="G13" s="567" t="n">
+      <c r="G13" s="626" t="n">
         <v>192.9186006000002</v>
       </c>
-      <c r="H13" s="567" t="n">
+      <c r="H13" s="626" t="n">
         <v>212.2104606600003</v>
       </c>
     </row>
@@ -14151,19 +14158,19 @@
       <c r="C14" s="583" t="n">
         <v>0.150786461335749</v>
       </c>
-      <c r="D14" s="565" t="n">
+      <c r="D14" s="624" t="n">
         <v>0.1085118998600017</v>
       </c>
-      <c r="E14" s="565" t="n">
+      <c r="E14" s="624" t="n">
         <v>0.1085118998600017</v>
       </c>
-      <c r="F14" s="565" t="n">
+      <c r="F14" s="624" t="n">
         <v>0.1085118998600016</v>
       </c>
-      <c r="G14" s="565" t="n">
+      <c r="G14" s="624" t="n">
         <v>0.1085118998600017</v>
       </c>
-      <c r="H14" s="565" t="n">
+      <c r="H14" s="624" t="n">
         <v>0.1085118998600017</v>
       </c>
     </row>
@@ -14176,19 +14183,19 @@
       <c r="C15" s="582" t="n">
         <v>85.7</v>
       </c>
-      <c r="D15" s="567" t="n">
+      <c r="D15" s="626" t="n">
         <v>94.27</v>
       </c>
-      <c r="E15" s="567" t="n">
+      <c r="E15" s="626" t="n">
         <v>103.697</v>
       </c>
-      <c r="F15" s="567" t="n">
+      <c r="F15" s="626" t="n">
         <v>114.0667</v>
       </c>
-      <c r="G15" s="567" t="n">
+      <c r="G15" s="626" t="n">
         <v>125.47337</v>
       </c>
-      <c r="H15" s="567" t="n">
+      <c r="H15" s="626" t="n">
         <v>138.020707</v>
       </c>
     </row>
@@ -14201,19 +14208,19 @@
       <c r="C16" s="582" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="D16" s="567" t="n">
+      <c r="D16" s="626" t="n">
         <v>50.67260000000009</v>
       </c>
-      <c r="E16" s="567" t="n">
+      <c r="E16" s="626" t="n">
         <v>55.73986000000014</v>
       </c>
-      <c r="F16" s="567" t="n">
+      <c r="F16" s="626" t="n">
         <v>61.31384600000001</v>
       </c>
-      <c r="G16" s="567" t="n">
+      <c r="G16" s="626" t="n">
         <v>67.44523060000019</v>
       </c>
-      <c r="H16" s="567" t="n">
+      <c r="H16" s="626" t="n">
         <v>74.18975366000021</v>
       </c>
     </row>
@@ -14223,19 +14230,19 @@
           <t>Interest</t>
         </is>
       </c>
-      <c r="D17" s="567" t="n">
+      <c r="D17" s="626" t="n">
         <v>77.8175</v>
       </c>
-      <c r="E17" s="567" t="n">
+      <c r="E17" s="626" t="n">
         <v>74.66500229999998</v>
       </c>
-      <c r="F17" s="567" t="n">
+      <c r="F17" s="626" t="n">
         <v>70.28971227089997</v>
       </c>
-      <c r="G17" s="567" t="n">
+      <c r="G17" s="626" t="n">
         <v>64.49402464738468</v>
       </c>
-      <c r="H17" s="567" t="n">
+      <c r="H17" s="626" t="n">
         <v>57.10576109667166</v>
       </c>
     </row>
@@ -14245,19 +14252,19 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="D18" s="567" t="n">
+      <c r="D18" s="626" t="n">
         <v>-27.14489999999991</v>
       </c>
-      <c r="E18" s="567" t="n">
+      <c r="E18" s="626" t="n">
         <v>-18.92514229999985</v>
       </c>
-      <c r="F18" s="567" t="n">
+      <c r="F18" s="626" t="n">
         <v>-8.975866270899957</v>
       </c>
-      <c r="G18" s="567" t="n">
+      <c r="G18" s="626" t="n">
         <v>2.331452702566253</v>
       </c>
-      <c r="H18" s="567" t="n">
+      <c r="H18" s="626" t="n">
         <v>13.49635412502955</v>
       </c>
     </row>
@@ -14267,19 +14274,19 @@
           <t>CapEx</t>
         </is>
       </c>
-      <c r="D19" s="567" t="n">
+      <c r="D19" s="626" t="n">
         <v>26.7146</v>
       </c>
-      <c r="E19" s="567" t="n">
+      <c r="E19" s="626" t="n">
         <v>29.38606</v>
       </c>
-      <c r="F19" s="567" t="n">
+      <c r="F19" s="626" t="n">
         <v>32.32466600000001</v>
       </c>
-      <c r="G19" s="567" t="n">
+      <c r="G19" s="626" t="n">
         <v>35.55713260000001</v>
       </c>
-      <c r="H19" s="567" t="n">
+      <c r="H19" s="626" t="n">
         <v>39.11284586000001</v>
       </c>
     </row>
@@ -14289,19 +14296,19 @@
           <t>ΔNWC</t>
         </is>
       </c>
-      <c r="D20" s="567" t="n">
+      <c r="D20" s="626" t="n">
         <v>2.428600000000001</v>
       </c>
-      <c r="E20" s="567" t="n">
+      <c r="E20" s="626" t="n">
         <v>2.671460000000002</v>
       </c>
-      <c r="F20" s="567" t="n">
+      <c r="F20" s="626" t="n">
         <v>2.938606000000004</v>
       </c>
-      <c r="G20" s="567" t="n">
+      <c r="G20" s="626" t="n">
         <v>3.232466600000003</v>
       </c>
-      <c r="H20" s="567" t="n">
+      <c r="H20" s="626" t="n">
         <v>3.555713260000002</v>
       </c>
     </row>
@@ -14311,19 +14318,19 @@
           <t>FCF after interest</t>
         </is>
       </c>
-      <c r="D21" s="567" t="n">
+      <c r="D21" s="626" t="n">
         <v>37.98190000000008</v>
       </c>
-      <c r="E21" s="567" t="n">
+      <c r="E21" s="626" t="n">
         <v>52.71433770000015</v>
       </c>
-      <c r="F21" s="567" t="n">
+      <c r="F21" s="626" t="n">
         <v>69.82756172910005</v>
       </c>
-      <c r="G21" s="567" t="n">
+      <c r="G21" s="626" t="n">
         <v>89.01522350256627</v>
       </c>
-      <c r="H21" s="567" t="n">
+      <c r="H21" s="626" t="n">
         <v>108.8485020050296</v>
       </c>
     </row>
@@ -14333,19 +14340,19 @@
           <t>Mandatory amort</t>
         </is>
       </c>
-      <c r="D22" s="567" t="n">
+      <c r="D22" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
-      <c r="E22" s="567" t="n">
+      <c r="E22" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
-      <c r="F22" s="567" t="n">
+      <c r="F22" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
-      <c r="G22" s="567" t="n">
+      <c r="G22" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
-      <c r="H22" s="567" t="n">
+      <c r="H22" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
     </row>
@@ -14355,19 +14362,19 @@
           <t>Total debt paydown</t>
         </is>
       </c>
-      <c r="D23" s="567" t="n">
+      <c r="D23" s="626" t="n">
         <v>37.98190000000008</v>
       </c>
-      <c r="E23" s="567" t="n">
+      <c r="E23" s="626" t="n">
         <v>52.71433770000015</v>
       </c>
-      <c r="F23" s="567" t="n">
+      <c r="F23" s="626" t="n">
         <v>69.82756172910005</v>
       </c>
-      <c r="G23" s="567" t="n">
+      <c r="G23" s="626" t="n">
         <v>89.01522350256627</v>
       </c>
-      <c r="H23" s="567" t="n">
+      <c r="H23" s="626" t="n">
         <v>108.8485020050296</v>
       </c>
     </row>
@@ -14380,19 +14387,19 @@
       <c r="C24" s="582" t="n">
         <v>1329.9</v>
       </c>
-      <c r="D24" s="567" t="n">
+      <c r="D24" s="626" t="n">
         <v>877.5180999999999</v>
       </c>
-      <c r="E24" s="567" t="n">
+      <c r="E24" s="626" t="n">
         <v>824.8037622999997</v>
       </c>
-      <c r="F24" s="567" t="n">
+      <c r="F24" s="626" t="n">
         <v>754.9762005708997</v>
       </c>
-      <c r="G24" s="567" t="n">
+      <c r="G24" s="626" t="n">
         <v>665.9609770683334</v>
       </c>
-      <c r="H24" s="567" t="n">
+      <c r="H24" s="626" t="n">
         <v>557.1124750633038</v>
       </c>
     </row>
@@ -14480,19 +14487,19 @@
       <c r="C5" s="582" t="n">
         <v>1214.3</v>
       </c>
-      <c r="D5" s="567" t="n">
+      <c r="D5" s="626" t="n">
         <v>1335.73</v>
       </c>
-      <c r="E5" s="567" t="n">
+      <c r="E5" s="626" t="n">
         <v>1469.303</v>
       </c>
-      <c r="F5" s="567" t="n">
+      <c r="F5" s="626" t="n">
         <v>1616.2333</v>
       </c>
-      <c r="G5" s="567" t="n">
+      <c r="G5" s="626" t="n">
         <v>1777.85663</v>
       </c>
-      <c r="H5" s="567" t="n">
+      <c r="H5" s="626" t="n">
         <v>1955.642293000001</v>
       </c>
     </row>
@@ -14505,19 +14512,19 @@
       <c r="C6" s="582" t="n">
         <v>242.8599999999999</v>
       </c>
-      <c r="D6" s="567" t="n">
+      <c r="D6" s="626" t="n">
         <v>267.146</v>
       </c>
-      <c r="E6" s="567" t="n">
+      <c r="E6" s="626" t="n">
         <v>293.8606</v>
       </c>
-      <c r="F6" s="567" t="n">
+      <c r="F6" s="626" t="n">
         <v>323.24666</v>
       </c>
-      <c r="G6" s="567" t="n">
+      <c r="G6" s="626" t="n">
         <v>355.571326</v>
       </c>
-      <c r="H6" s="567" t="n">
+      <c r="H6" s="626" t="n">
         <v>391.1284586</v>
       </c>
     </row>
@@ -14530,19 +14537,19 @@
       <c r="C7" s="582" t="n">
         <v>318.8</v>
       </c>
-      <c r="D7" s="567" t="n">
+      <c r="D7" s="626" t="n">
         <v>270.98</v>
       </c>
-      <c r="E7" s="567" t="n">
+      <c r="E7" s="626" t="n">
         <v>276.3996</v>
       </c>
-      <c r="F7" s="567" t="n">
+      <c r="F7" s="626" t="n">
         <v>281.927592</v>
       </c>
-      <c r="G7" s="567" t="n">
+      <c r="G7" s="626" t="n">
         <v>287.56614384</v>
       </c>
-      <c r="H7" s="567" t="n">
+      <c r="H7" s="626" t="n">
         <v>293.3174667168</v>
       </c>
     </row>
@@ -14555,19 +14562,19 @@
       <c r="C8" s="582" t="n">
         <v>106.2</v>
       </c>
-      <c r="D8" s="567" t="n">
+      <c r="D8" s="626" t="n">
         <v>84.96000000000001</v>
       </c>
-      <c r="E8" s="567" t="n">
+      <c r="E8" s="626" t="n">
         <v>86.65920000000001</v>
       </c>
-      <c r="F8" s="567" t="n">
+      <c r="F8" s="626" t="n">
         <v>88.39238400000002</v>
       </c>
-      <c r="G8" s="567" t="n">
+      <c r="G8" s="626" t="n">
         <v>90.16023168000002</v>
       </c>
-      <c r="H8" s="567" t="n">
+      <c r="H8" s="626" t="n">
         <v>91.96343631360003</v>
       </c>
     </row>
@@ -14580,19 +14587,19 @@
       <c r="C9" s="582" t="n">
         <v>425</v>
       </c>
-      <c r="D9" s="567" t="n">
+      <c r="D9" s="626" t="n">
         <v>355.9400000000001</v>
       </c>
-      <c r="E9" s="567" t="n">
+      <c r="E9" s="626" t="n">
         <v>363.0588</v>
       </c>
-      <c r="F9" s="567" t="n">
+      <c r="F9" s="626" t="n">
         <v>370.319976</v>
       </c>
-      <c r="G9" s="567" t="n">
+      <c r="G9" s="626" t="n">
         <v>377.72637552</v>
       </c>
-      <c r="H9" s="567" t="n">
+      <c r="H9" s="626" t="n">
         <v>385.2809030304001</v>
       </c>
     </row>
@@ -14605,20 +14612,20 @@
       <c r="C10" s="582" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="567" t="n">
-        <v>15</v>
-      </c>
-      <c r="E10" s="567" t="n">
-        <v>15</v>
-      </c>
-      <c r="F10" s="567" t="n">
-        <v>15</v>
-      </c>
-      <c r="G10" s="567" t="n">
-        <v>15</v>
-      </c>
-      <c r="H10" s="567" t="n">
-        <v>15</v>
+      <c r="D10" s="626" t="n">
+        <v>34</v>
+      </c>
+      <c r="E10" s="626" t="n">
+        <v>34</v>
+      </c>
+      <c r="F10" s="626" t="n">
+        <v>34</v>
+      </c>
+      <c r="G10" s="626" t="n">
+        <v>34</v>
+      </c>
+      <c r="H10" s="626" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -14630,19 +14637,19 @@
       <c r="C11" s="582" t="n">
         <v>196.1</v>
       </c>
-      <c r="D11" s="567" t="n">
+      <c r="D11" s="626" t="n">
         <v>215.71</v>
       </c>
-      <c r="E11" s="567" t="n">
+      <c r="E11" s="626" t="n">
         <v>237.281</v>
       </c>
-      <c r="F11" s="567" t="n">
+      <c r="F11" s="626" t="n">
         <v>261.0091</v>
       </c>
-      <c r="G11" s="567" t="n">
+      <c r="G11" s="626" t="n">
         <v>287.11001</v>
       </c>
-      <c r="H11" s="567" t="n">
+      <c r="H11" s="626" t="n">
         <v>315.8210110000001</v>
       </c>
     </row>
@@ -14655,19 +14662,19 @@
       <c r="C12" s="582" t="n">
         <v>218.574</v>
       </c>
-      <c r="D12" s="567" t="n">
+      <c r="D12" s="626" t="n">
         <v>240.4314</v>
       </c>
-      <c r="E12" s="567" t="n">
+      <c r="E12" s="626" t="n">
         <v>264.47454</v>
       </c>
-      <c r="F12" s="567" t="n">
+      <c r="F12" s="626" t="n">
         <v>290.921994</v>
       </c>
-      <c r="G12" s="567" t="n">
+      <c r="G12" s="626" t="n">
         <v>320.0141934000001</v>
       </c>
-      <c r="H12" s="567" t="n">
+      <c r="H12" s="626" t="n">
         <v>352.0156127400001</v>
       </c>
     </row>
@@ -14680,20 +14687,20 @@
       <c r="C13" s="582" t="n">
         <v>183.1</v>
       </c>
-      <c r="D13" s="567" t="n">
-        <v>241.5026</v>
-      </c>
-      <c r="E13" s="567" t="n">
-        <v>295.6280600000002</v>
-      </c>
-      <c r="F13" s="567" t="n">
-        <v>355.7355700000003</v>
-      </c>
-      <c r="G13" s="567" t="n">
-        <v>422.4347250800001</v>
-      </c>
-      <c r="H13" s="567" t="n">
-        <v>496.3963076296004</v>
+      <c r="D13" s="626" t="n">
+        <v>222.5026</v>
+      </c>
+      <c r="E13" s="626" t="n">
+        <v>276.6280600000002</v>
+      </c>
+      <c r="F13" s="626" t="n">
+        <v>336.7355700000003</v>
+      </c>
+      <c r="G13" s="626" t="n">
+        <v>403.4347250800001</v>
+      </c>
+      <c r="H13" s="626" t="n">
+        <v>477.3963076296004</v>
       </c>
     </row>
     <row r="14">
@@ -14705,20 +14712,20 @@
       <c r="C14" s="583" t="n">
         <v>0.150786461335749</v>
       </c>
-      <c r="D14" s="565" t="n">
-        <v>0.1808019584796329</v>
-      </c>
-      <c r="E14" s="565" t="n">
-        <v>0.2012029241075531</v>
-      </c>
-      <c r="F14" s="565" t="n">
-        <v>0.2201016214676434</v>
-      </c>
-      <c r="G14" s="565" t="n">
-        <v>0.237608993859083</v>
-      </c>
-      <c r="H14" s="565" t="n">
-        <v>0.253827762575188</v>
+      <c r="D14" s="624" t="n">
+        <v>0.1665775268954055</v>
+      </c>
+      <c r="E14" s="624" t="n">
+        <v>0.1882716226673465</v>
+      </c>
+      <c r="F14" s="624" t="n">
+        <v>0.2083458928856374</v>
+      </c>
+      <c r="G14" s="624" t="n">
+        <v>0.2269219678754411</v>
+      </c>
+      <c r="H14" s="624" t="n">
+        <v>0.2441122844082408</v>
       </c>
     </row>
     <row r="15">
@@ -14730,19 +14737,19 @@
       <c r="C15" s="582" t="n">
         <v>85.7</v>
       </c>
-      <c r="D15" s="567" t="n">
+      <c r="D15" s="626" t="n">
         <v>94.27</v>
       </c>
-      <c r="E15" s="567" t="n">
+      <c r="E15" s="626" t="n">
         <v>103.697</v>
       </c>
-      <c r="F15" s="567" t="n">
+      <c r="F15" s="626" t="n">
         <v>114.0667</v>
       </c>
-      <c r="G15" s="567" t="n">
+      <c r="G15" s="626" t="n">
         <v>125.47337</v>
       </c>
-      <c r="H15" s="567" t="n">
+      <c r="H15" s="626" t="n">
         <v>138.020707</v>
       </c>
     </row>
@@ -14755,20 +14762,20 @@
       <c r="C16" s="582" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="D16" s="567" t="n">
-        <v>147.2326</v>
-      </c>
-      <c r="E16" s="567" t="n">
-        <v>191.9310600000002</v>
-      </c>
-      <c r="F16" s="567" t="n">
-        <v>241.6688700000003</v>
-      </c>
-      <c r="G16" s="567" t="n">
-        <v>296.9613550800001</v>
-      </c>
-      <c r="H16" s="567" t="n">
-        <v>358.3756006296003</v>
+      <c r="D16" s="626" t="n">
+        <v>128.2326</v>
+      </c>
+      <c r="E16" s="626" t="n">
+        <v>172.9310600000002</v>
+      </c>
+      <c r="F16" s="626" t="n">
+        <v>222.6688700000003</v>
+      </c>
+      <c r="G16" s="626" t="n">
+        <v>277.9613550800001</v>
+      </c>
+      <c r="H16" s="626" t="n">
+        <v>339.3756006296003</v>
       </c>
     </row>
     <row r="17">
@@ -14777,20 +14784,20 @@
           <t>Interest</t>
         </is>
       </c>
-      <c r="D17" s="567" t="n">
+      <c r="D17" s="626" t="n">
         <v>77.8175</v>
       </c>
-      <c r="E17" s="567" t="n">
-        <v>67.729404523</v>
-      </c>
-      <c r="F17" s="567" t="n">
-        <v>53.49529986637309</v>
-      </c>
-      <c r="G17" s="567" t="n">
-        <v>33.8109445736872</v>
-      </c>
-      <c r="H17" s="567" t="n">
-        <v>7.520534071254138</v>
+      <c r="E17" s="626" t="n">
+        <v>68.975234523</v>
+      </c>
+      <c r="F17" s="626" t="n">
+        <v>56.06864893947309</v>
+      </c>
+      <c r="G17" s="626" t="n">
+        <v>38.27932966018786</v>
+      </c>
+      <c r="H17" s="626" t="n">
+        <v>12.71433377476873</v>
       </c>
     </row>
     <row r="18">
@@ -14799,20 +14806,20 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="D18" s="567" t="n">
-        <v>54.83792900000005</v>
-      </c>
-      <c r="E18" s="567" t="n">
-        <v>98.11930782683014</v>
-      </c>
-      <c r="F18" s="567" t="n">
-        <v>148.6571204055655</v>
-      </c>
-      <c r="G18" s="567" t="n">
-        <v>207.8888242999872</v>
-      </c>
-      <c r="H18" s="567" t="n">
-        <v>277.1755025810935</v>
+      <c r="D18" s="626" t="n">
+        <v>39.82792900000004</v>
+      </c>
+      <c r="E18" s="626" t="n">
+        <v>82.12510212683014</v>
+      </c>
+      <c r="F18" s="626" t="n">
+        <v>131.6141746378165</v>
+      </c>
+      <c r="G18" s="626" t="n">
+        <v>189.3488000816517</v>
+      </c>
+      <c r="H18" s="626" t="n">
+        <v>258.0624008153169</v>
       </c>
     </row>
     <row r="19">
@@ -14821,19 +14828,19 @@
           <t>CapEx</t>
         </is>
       </c>
-      <c r="D19" s="567" t="n">
+      <c r="D19" s="626" t="n">
         <v>25.37887</v>
       </c>
-      <c r="E19" s="567" t="n">
+      <c r="E19" s="626" t="n">
         <v>27.916757</v>
       </c>
-      <c r="F19" s="567" t="n">
+      <c r="F19" s="626" t="n">
         <v>30.70843270000001</v>
       </c>
-      <c r="G19" s="567" t="n">
+      <c r="G19" s="626" t="n">
         <v>33.77927597000001</v>
       </c>
-      <c r="H19" s="567" t="n">
+      <c r="H19" s="626" t="n">
         <v>37.15720356700001</v>
       </c>
     </row>
@@ -14843,19 +14850,19 @@
           <t>ΔNWC</t>
         </is>
       </c>
-      <c r="D20" s="567" t="n">
+      <c r="D20" s="626" t="n">
         <v>2.185740000000001</v>
       </c>
-      <c r="E20" s="567" t="n">
+      <c r="E20" s="626" t="n">
         <v>2.404314000000002</v>
       </c>
-      <c r="F20" s="567" t="n">
+      <c r="F20" s="626" t="n">
         <v>2.644745400000004</v>
       </c>
-      <c r="G20" s="567" t="n">
+      <c r="G20" s="626" t="n">
         <v>2.909219940000003</v>
       </c>
-      <c r="H20" s="567" t="n">
+      <c r="H20" s="626" t="n">
         <v>3.200141934000002</v>
       </c>
     </row>
@@ -14865,20 +14872,20 @@
           <t>FCF after interest</t>
         </is>
       </c>
-      <c r="D21" s="567" t="n">
-        <v>121.543319</v>
-      </c>
-      <c r="E21" s="567" t="n">
-        <v>171.4952368268301</v>
-      </c>
-      <c r="F21" s="567" t="n">
-        <v>229.3706423055654</v>
-      </c>
-      <c r="G21" s="567" t="n">
-        <v>296.6736983899872</v>
-      </c>
-      <c r="H21" s="567" t="n">
-        <v>374.8388640800935</v>
+      <c r="D21" s="626" t="n">
+        <v>106.533319</v>
+      </c>
+      <c r="E21" s="626" t="n">
+        <v>155.5010311268301</v>
+      </c>
+      <c r="F21" s="626" t="n">
+        <v>212.3276965378165</v>
+      </c>
+      <c r="G21" s="626" t="n">
+        <v>278.1336741716516</v>
+      </c>
+      <c r="H21" s="626" t="n">
+        <v>355.725762314317</v>
       </c>
     </row>
     <row r="22">
@@ -14887,19 +14894,19 @@
           <t>Mandatory amort</t>
         </is>
       </c>
-      <c r="D22" s="567" t="n">
+      <c r="D22" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
-      <c r="E22" s="567" t="n">
+      <c r="E22" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
-      <c r="F22" s="567" t="n">
+      <c r="F22" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
-      <c r="G22" s="567" t="n">
+      <c r="G22" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
-      <c r="H22" s="567" t="n">
+      <c r="H22" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
     </row>
@@ -14909,20 +14916,20 @@
           <t>Total debt paydown</t>
         </is>
       </c>
-      <c r="D23" s="567" t="n">
-        <v>121.543319</v>
-      </c>
-      <c r="E23" s="567" t="n">
-        <v>171.4952368268301</v>
-      </c>
-      <c r="F23" s="567" t="n">
-        <v>229.3706423055654</v>
-      </c>
-      <c r="G23" s="567" t="n">
-        <v>296.6736983899872</v>
-      </c>
-      <c r="H23" s="567" t="n">
-        <v>96.41710347761716</v>
+      <c r="D23" s="626" t="n">
+        <v>106.533319</v>
+      </c>
+      <c r="E23" s="626" t="n">
+        <v>155.5010311268301</v>
+      </c>
+      <c r="F23" s="626" t="n">
+        <v>212.3276965378165</v>
+      </c>
+      <c r="G23" s="626" t="n">
+        <v>278.1336741716516</v>
+      </c>
+      <c r="H23" s="626" t="n">
+        <v>163.0042791637017</v>
       </c>
     </row>
     <row r="24">
@@ -14934,19 +14941,19 @@
       <c r="C24" s="582" t="n">
         <v>1329.9</v>
       </c>
-      <c r="D24" s="567" t="n">
-        <v>793.956681</v>
-      </c>
-      <c r="E24" s="567" t="n">
-        <v>622.4614441731698</v>
-      </c>
-      <c r="F24" s="567" t="n">
-        <v>393.0908018676043</v>
-      </c>
-      <c r="G24" s="567" t="n">
-        <v>96.41710347761716</v>
-      </c>
-      <c r="H24" s="567" t="n">
+      <c r="D24" s="626" t="n">
+        <v>808.966681</v>
+      </c>
+      <c r="E24" s="626" t="n">
+        <v>653.4656498731698</v>
+      </c>
+      <c r="F24" s="626" t="n">
+        <v>441.1379533353534</v>
+      </c>
+      <c r="G24" s="626" t="n">
+        <v>163.0042791637017</v>
+      </c>
+      <c r="H24" s="626" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21235,10 +21242,10 @@
         <v>1</v>
       </c>
       <c r="I275" s="485" t="n">
-        <v>3.449</v>
+        <v>3.317</v>
       </c>
       <c r="J275" s="490" t="n">
-        <v>0.2809</v>
+        <v>0.271</v>
       </c>
     </row>
     <row r="276">
@@ -21273,7 +21280,7 @@
       <c r="G277" s="492" t="n"/>
       <c r="H277" s="492" t="n"/>
       <c r="J277" t="n">
-        <v>0.2479</v>
+        <v>0.2379</v>
       </c>
     </row>
     <row r="278">

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -5234,7 +5234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H31"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
@@ -5246,6 +5246,7 @@
     <col width="38" customWidth="1" style="244" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="604" t="inlineStr">
         <is>
@@ -5256,7 +5257,7 @@
     <row r="3" ht="42" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>Same-row evidence for every yellow input. Col D = why the assumption is reasonable for this LBO. Col E = clickable source. Col F = source math / credibility (e.g. SF Agentforce list prices → $15m). Col G = click into the model. No separate AI-cost tab.</t>
+          <t>Same-row evidence for every yellow input. Col D = why the assumption is reasonable for this LBO. Col E = clickable source. Col F = source math / credibility (e.g. SF Agentforce list prices → $34m). Col G = click into the model. No separate AI-cost tab.</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5449,7 @@
       </c>
       <c r="D9" s="609" t="inlineStr">
         <is>
-          <t>Fixed cost for AI software and compute set to $34m — the midpoint of the $23–45m enterprise AI-agent triangulation (avg of low/high). Covers API calls and infra to replace human reps.</t>
+          <t>Fixed cost for AI software and compute set to $34m — midpoint of the $23–45m enterprise AI-agent triangulation. Covers API calls and infra to replace human reps.</t>
         </is>
       </c>
       <c r="E9" s="610" t="inlineStr">
@@ -5458,7 +5459,7 @@
       </c>
       <c r="F9" s="615" t="inlineStr">
         <is>
-          <t>SF publishes $2/conversation and ~$0.10/action. At ZI scale (~378 outbound roles = 25% of 1,513 S&amp;M), $5–10k/mo agents imply ~$23–45m; model uses midpoint avg((23+45)/2) = $34m.</t>
+          <t>SF publishes $2/conversation and ~$0.10/action. At ZI scale (~378 outbound roles = 25% of 1,513 S&amp;M), $5–10k/mo agents imply ~$23–45m; model uses midpoint avg(23,45) = $34m.</t>
         </is>
       </c>
       <c r="G9" s="612" t="inlineStr">
@@ -6112,14 +6113,14 @@
       </c>
     </row>
     <row r="29" ht="36" customHeight="1" s="244">
-      <c r="B29" s="618" t="inlineStr">
-        <is>
-          <t>AI $15m triangulation (row 9, col F):</t>
+      <c r="B29" s="564" t="inlineStr">
+        <is>
+          <t>AI $34m triangulation (row 9, col F):</t>
         </is>
       </c>
       <c r="C29" s="620" t="inlineStr">
         <is>
-          <t>SF publishes $2/conversation and ~$0.10/action. At ZI scale (~378 outbound roles = 25% of 1,513 S&amp;M), $5–10k/mo agents imply ~$23–45m; model uses midpoint avg((23+45)/2) = $34m.</t>
+          <t>SF publishes $2/conversation and ~$0.10/action. At ZI scale (~378 outbound roles = 25% of 1,513 S&amp;M), $5–10k/mo agents imply ~$23–45m; model uses midpoint avg(23,45) = $34m.</t>
         </is>
       </c>
       <c r="D29" s="621" t="n"/>
@@ -6145,6 +6146,9 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C29:F29"/>
@@ -11841,7 +11845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F55"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="244" min="2" max="2"/>
@@ -11851,6 +11855,7 @@
     <col width="78" customWidth="1" style="244" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -11865,6 +11870,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="564" t="inlineStr">
         <is>
@@ -11886,6 +11892,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="564" t="inlineStr">
         <is>
@@ -12098,6 +12105,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="B24" s="564" t="inlineStr">
         <is>
@@ -12108,7 +12116,7 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>Y1: cut S&amp;M 15% vs baseline $425m; add $15m AI software/compute cost</t>
+          <t>Y1: cut S&amp;M 15% vs baseline $425m; add $34m AI software/compute cost</t>
         </is>
       </c>
     </row>
@@ -12126,6 +12134,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="B29" s="564" t="inlineStr">
         <is>
@@ -12356,6 +12365,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
@@ -12363,6 +12373,9 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
     <row r="48">
       <c r="B48" s="564" t="inlineStr">
         <is>
@@ -12465,6 +12478,10 @@
         <v>27.1</v>
       </c>
     </row>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B3:F3"/>
@@ -12480,7 +12497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M43"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" style="244" min="2" max="2"/>
@@ -12497,6 +12514,7 @@
     <col width="70" customWidth="1" style="244" min="13" max="13"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -12518,6 +12536,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="557" t="inlineStr">
         <is>
@@ -12831,7 +12850,7 @@
       </c>
       <c r="D11" s="571" t="inlineStr">
         <is>
-          <t>$15 million fixed / year</t>
+          <t>$34 million fixed / year</t>
         </is>
       </c>
       <c r="E11" s="571" t="inlineStr">
@@ -12876,7 +12895,7 @@
       </c>
       <c r="M11" s="573" t="inlineStr">
         <is>
-          <t>A new fixed fifteen million dollar expense was added. We included this vital change to cover enterprise software licenses, API usage limits, and compute power running the AI. SOURCE (LBOMODEL2): $15m triangulated from Salesforce Agentforce public pricing ($2/conversation; Flex Credits ~$0.10/action) and ZoomInfo 10-K S&amp;M headcount (1,513). Full math + clickable links: sheet Assumptions_Drivers (cols E–G). Primary link: https://www.salesforce.com/news/press-releases/2025/05/15/agentforce-flexible-pricing-news/</t>
+          <t>A new fixed thirty-four million dollar expense was added. We included this vital change to cover enterprise software licenses, API usage limits, and compute power running the AI. SOURCE (LBOMODEL2): $34m triangulated from Salesforce Agentforce public pricing ($2/conversation; Flex Credits ~$0.10/action) and ZoomInfo 10-K S&amp;M headcount (1,513). Full math + clickable links: sheet Assumptions_Drivers (cols E–G). Primary link: https://www.salesforce.com/news/press-releases/2025/05/15/agentforce-flexible-pricing-news/</t>
         </is>
       </c>
     </row>
@@ -13480,6 +13499,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="B23" s="564" t="inlineStr">
         <is>
@@ -13495,10 +13515,11 @@
       </c>
     </row>
     <row r="25"/>
+    <row r="26"/>
     <row r="27">
       <c r="B27" s="564" t="inlineStr">
         <is>
-          <t>AI Infrastructure $15m — SOURCE PACK</t>
+          <t>AI Infrastructure $34m — SOURCE PACK</t>
         </is>
       </c>
     </row>
@@ -13530,6 +13551,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="B33" s="564" t="inlineStr">
         <is>
@@ -13551,6 +13573,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="564" t="inlineStr">
         <is>
@@ -13572,6 +13595,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="B41" s="564" t="inlineStr">
         <is>
@@ -13860,7 +13884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H24"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
@@ -13873,6 +13897,7 @@
     <col width="12" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -14403,6 +14428,22 @@
         <v>557.1124750633038</v>
       </c>
     </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14414,7 +14455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H24"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
@@ -14427,6 +14468,7 @@
     <col width="12" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -14957,6 +14999,22 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14968,9 +15026,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M42"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
@@ -14978,6 +15037,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8" ht="26.25" customHeight="1" s="244">
       <c r="B8" s="402" t="inlineStr">
         <is>
@@ -14996,6 +15060,8 @@
       <c r="L8" s="404" t="n"/>
       <c r="M8" s="404" t="n"/>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="405" t="inlineStr">
         <is>
@@ -15006,6 +15072,31 @@
     <row r="12"/>
     <row r="13"/>
     <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -153,7 +153,7 @@
     <numFmt numFmtId="245" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
     <numFmt numFmtId="246" formatCode="###0&quot;E&quot;_)"/>
   </numFmts>
-  <fonts count="118">
+  <fonts count="120">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -910,6 +910,16 @@
       <color rgb="00556677"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000B3D5C"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="45">
     <fill>
@@ -1938,7 +1948,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="629">
+  <cellXfs count="634">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3053,6 +3063,19 @@
     <xf numFmtId="190" fontId="0" fillId="34" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="191" fontId="0" fillId="34" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="34" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="110" fillId="40" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="37" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="34" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="187">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5234,30 +5257,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="B2:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
     <col width="11" customWidth="1" style="244" min="3" max="3"/>
     <col width="52" customWidth="1" style="244" min="4" max="4"/>
-    <col width="42" customWidth="1" style="244" min="5" max="5"/>
-    <col width="55" customWidth="1" style="244" min="6" max="6"/>
+    <col width="48" customWidth="1" style="244" min="5" max="5"/>
+    <col width="62" customWidth="1" style="244" min="6" max="6"/>
     <col width="34" customWidth="1" style="244" min="7" max="7"/>
     <col width="38" customWidth="1" style="244" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
-      <c r="B2" s="604" t="inlineStr">
-        <is>
-          <t>Assumptions Drivers — value, justification, source link, and Feeds on every row</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1" s="244">
+      <c r="B2" s="629" t="inlineStr">
+        <is>
+          <t>Assumptions Drivers — every number has a FIND-in-source pointer (FACT vs THESIS labeled honestly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>Same-row evidence for every yellow input. Col D = why the assumption is reasonable for this LBO. Col E = clickable source. Col F = source math / credibility (e.g. SF Agentforce list prices → $34m). Col G = click into the model. No separate AI-cost tab.</t>
+          <t>Col E = click the source and read the FIND line (where the statistic appears). Col F = what that source actually says, and whether our model value EQUALS the source (FACT) or is a labeled THESIS near that evidence. We do not claim a source prints “15% ZI payroll cut” if it doesn’t.</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5301,12 @@
       </c>
       <c r="E4" s="606" t="inlineStr">
         <is>
-          <t>Source link (click)</t>
+          <t>Source link — FIND the statistic here (click)</t>
         </is>
       </c>
       <c r="F4" s="606" t="inlineStr">
         <is>
-          <t>Source math / credibility</t>
+          <t>What source says + FACT vs THESIS (honest)</t>
         </is>
       </c>
       <c r="G4" s="606" t="inlineStr">
@@ -5298,7 +5320,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="62" customHeight="1" s="244">
+    <row r="5" ht="72" customHeight="1" s="244">
       <c r="B5" s="607" t="inlineStr">
         <is>
           <t>Revenue growth</t>
@@ -5312,14 +5334,14 @@
           <t>Assumes steady top-line expansion. Reasonable for a mature enterprise software company, avoiding aggressive hypergrowth assumptions while maintaining a healthy, realistic sales trajectory.</t>
         </is>
       </c>
-      <c r="E5" s="610" t="inlineStr">
-        <is>
-          <t>ZoomInfo FY2024 results (BusinessWire)</t>
-        </is>
-      </c>
-      <c r="F5" s="611" t="inlineStr">
-        <is>
-          <t>ZI disclosed FY24 revenue of $1,214.3m (−2% YoY). Using 10% forward growth is a mature-SaaS recovery underwrite held equal in AI vs Base—not hypergrowth.</t>
+      <c r="E5" s="630" t="inlineStr">
+        <is>
+          <t>FIND in ZI FY24 results: Revenue $1,214.3m (−2% YoY) — NOT +10%</t>
+        </is>
+      </c>
+      <c r="F5" s="631" t="inlineStr">
+        <is>
+          <t>FACT in source: FY24 revenue fell ~2%. Our 10% is a MODEL THESIS forward underwrite (held equal in AI vs Base), not a figure printed as ZI growth. Source proves baseline sales scale, not the 10% rate.</t>
         </is>
       </c>
       <c r="G5" s="612" t="inlineStr">
@@ -5329,11 +5351,11 @@
       </c>
       <c r="H5" s="612" t="inlineStr">
         <is>
-          <t>valueaddvc.com/blog/saas-evebitda-multiples-explained-benchmarks-and-w</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="62" customHeight="1" s="244">
+          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1" s="244">
       <c r="B6" s="613" t="inlineStr">
         <is>
           <t>Gross margin</t>
@@ -5347,14 +5369,14 @@
           <t>High profitability on direct services. Highly reasonable for a SaaS company, which historically scales digital infrastructure with minimal incremental cost per user.</t>
         </is>
       </c>
-      <c r="E6" s="610" t="inlineStr">
-        <is>
-          <t>Aleph/Benchmarkit SaaS GM median ~80%</t>
-        </is>
-      </c>
-      <c r="F6" s="611" t="inlineStr">
-        <is>
-          <t>Independent SaaS benchmarks put software median GM near 80%; ZI already prints ~84% GAAP GM, so 80% is conservative and industry-standard.</t>
+      <c r="E6" s="630" t="inlineStr">
+        <is>
+          <t>FIND in Aleph/Benchmarkit: 2025 software median GM = 80%</t>
+        </is>
+      </c>
+      <c r="F6" s="632" t="inlineStr">
+        <is>
+          <t>FACT in source: software median gross margin is 80%. Model uses 80% to match that published median. (ZI GAAP GM is higher ~84% in SEC-derived comps — we are not inventing 80%.)</t>
         </is>
       </c>
       <c r="G6" s="612" t="inlineStr">
@@ -5368,7 +5390,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="62" customHeight="1" s="244">
+    <row r="7" ht="72" customHeight="1" s="244">
       <c r="B7" s="607" t="inlineStr">
         <is>
           <t>Sales payroll cut (Y1)</t>
@@ -5382,14 +5404,14 @@
           <t>Immediate headcount reduction for human SDRs. Reasonable as a private equity cost-cutting measure, easily achieved by eliminating the lower-tier outbound sales team.</t>
         </is>
       </c>
-      <c r="E7" s="610" t="inlineStr">
-        <is>
-          <t>AI SDR vs human SDR cost/meeting analysis</t>
-        </is>
-      </c>
-      <c r="F7" s="611" t="inlineStr">
-        <is>
-          <t>Published outbound economics show fully loaded human SDRs far costlier than AI stacks. −15% Y1 payroll is a modest PE-style cut of outbound headcount, not a full S&amp;M wipeout.</t>
+      <c r="E7" s="630" t="inlineStr">
+        <is>
+          <t>FIND: US B2B SaaS SDR headcount −~18% YoY (junior −31%)</t>
+        </is>
+      </c>
+      <c r="F7" s="631" t="inlineStr">
+        <is>
+          <t>FACT in source: net US B2B SaaS SDR headcount down ~18% YoY (junior roles −31%). Our −15% Y1 payroll cut is a MODEL THESIS set near that published ~18% industry cut — source does not say “ZoomInfo cut 15%.”</t>
         </is>
       </c>
       <c r="G7" s="612" t="inlineStr">
@@ -5399,11 +5421,11 @@
       </c>
       <c r="H7" s="612" t="inlineStr">
         <is>
-          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="62" customHeight="1" s="244">
+          <t>firstsales.io/blog/cost-per-meeting-outbound/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="72" customHeight="1" s="244">
       <c r="B8" s="613" t="inlineStr">
         <is>
           <t>Variable commission cut</t>
@@ -5417,14 +5439,14 @@
           <t>Reduces payouts for automated sales. Reasonable because AI agents do not collect commission checks, retaining more profit per enterprise deal directly for the company.</t>
         </is>
       </c>
-      <c r="E8" s="610" t="inlineStr">
-        <is>
-          <t>SDR pay mix ~70/30 base/variable (SyncGTM)</t>
-        </is>
-      </c>
-      <c r="F8" s="611" t="inlineStr">
-        <is>
-          <t>SaaS SDR OTE is typically ~70% base / ~30% variable. Replacing humans with AI shrinks the commission pool; −20% is a partial cut of that variable layer.</t>
+      <c r="E8" s="630" t="inlineStr">
+        <is>
+          <t>FIND in SyncGTM: SDR OTE mix ~70% base / ~30% variable</t>
+        </is>
+      </c>
+      <c r="F8" s="631" t="inlineStr">
+        <is>
+          <t>FACT in source: standard SDR pay is ~70/30 base/variable. Our −20% commission cut is a MODEL THESIS: if AI replaces outbound humans, ~30% variable layer shrinks; −20% is a partial cut of that published variable share — not a ZI filing line item.</t>
         </is>
       </c>
       <c r="G8" s="612" t="inlineStr">
@@ -5438,7 +5460,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="62" customHeight="1" s="244">
+    <row r="9" ht="72" customHeight="1" s="244">
       <c r="B9" s="607" t="inlineStr">
         <is>
           <t>AI infrastructure ($m)</t>
@@ -5452,14 +5474,14 @@
           <t>Fixed cost for AI software and compute set to $34m — midpoint of the $23–45m enterprise AI-agent triangulation. Covers API calls and infra to replace human reps.</t>
         </is>
       </c>
-      <c r="E9" s="610" t="inlineStr">
-        <is>
-          <t>Salesforce Agentforce pricing ($2/conv · ~$0.10/action)</t>
-        </is>
-      </c>
-      <c r="F9" s="615" t="inlineStr">
-        <is>
-          <t>SF publishes $2/conversation and ~$0.10/action. At ZI scale (~378 outbound roles = 25% of 1,513 S&amp;M), $5–10k/mo agents imply ~$23–45m; model uses midpoint avg(23,45) = $34m.</t>
+      <c r="E9" s="630" t="inlineStr">
+        <is>
+          <t>FIND in SF press: $2/conversation; Flex Credits $500/100k (= ~$0.10/action)</t>
+        </is>
+      </c>
+      <c r="F9" s="632" t="inlineStr">
+        <is>
+          <t>FACT in source: Salesforce list prices $2/conversation and ~$0.10/action. Secondary AI-agent ranges ~$5–10k/mo × ~378 outbound roles (25% of ZI’s 1,513 S&amp;M from 10-K) ⇒ ~$23–45m. Model uses midpoint $34m = avg(23,45). $34m is derived math, not a SF quote of “$34m.”</t>
         </is>
       </c>
       <c r="G9" s="612" t="inlineStr">
@@ -5469,11 +5491,11 @@
       </c>
       <c r="H9" s="612" t="inlineStr">
         <is>
-          <t>highticketaisystems.com/blog/ai-sdr-pricing-explained</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="62" customHeight="1" s="244">
+          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="72" customHeight="1" s="244">
       <c r="B10" s="613" t="inlineStr">
         <is>
           <t>S&amp;M expense growth Y2+</t>
@@ -5487,14 +5509,14 @@
           <t>Caps future marketing cost increases. Reasonable because AI scales infinitely without needing proportional headcount additions, severing the link between revenue growth and human hiring.</t>
         </is>
       </c>
-      <c r="E10" s="610" t="inlineStr">
-        <is>
-          <t>Gartner: agentic AI / inference scales as opex</t>
-        </is>
-      </c>
-      <c r="F10" s="611" t="inlineStr">
-        <is>
-          <t>Gartner documents production agentic AI as inference opex that scales without linear headcount. Cap S&amp;M growth at 2% to model that break from revenue-linked hiring.</t>
+      <c r="E10" s="630" t="inlineStr">
+        <is>
+          <t>FIND in Gartner: inference/agentic AI scales as production opex (not headcount-linear)</t>
+        </is>
+      </c>
+      <c r="F10" s="631" t="inlineStr">
+        <is>
+          <t>FACT in source: enterprises shift to production inference/agentic workloads that scale with compute opex. Our 2% S&amp;M growth cap is a MODEL THESIS illustrating near-inflation opex after AI replaces linear hiring — Gartner does not publish “2% S&amp;M growth.”</t>
         </is>
       </c>
       <c r="G10" s="612" t="inlineStr">
@@ -5508,7 +5530,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="62" customHeight="1" s="244">
+    <row r="11" ht="72" customHeight="1" s="244">
       <c r="B11" s="607" t="inlineStr">
         <is>
           <t>G&amp;A % of revenue</t>
@@ -5522,14 +5544,14 @@
           <t>General administrative overhead costs. Reasonable for a public-to-private SaaS company, maintaining standard corporate expenses without relying on unrealistic operational magic outside of sales.</t>
         </is>
       </c>
-      <c r="E11" s="610" t="inlineStr">
-        <is>
-          <t>ZoomInfo FY24 G&amp;A $295.3m (company results)</t>
-        </is>
-      </c>
-      <c r="F11" s="611" t="inlineStr">
-        <is>
-          <t>ZI FY24 G&amp;A was $295.3m (~24% of revenue). Locking ~18% keeps standard corporate overhead while the thesis only attacks the sales floor—not finance/comp magic.</t>
+      <c r="E11" s="630" t="inlineStr">
+        <is>
+          <t>FIND in ZI FY24 P&amp;L: G&amp;A $295.3m → ~24.3% of $1,214.3m rev</t>
+        </is>
+      </c>
+      <c r="F11" s="631" t="inlineStr">
+        <is>
+          <t>FACT in source: G&amp;A = $295.3m (~24% of revenue). Our 18% is a MODEL THESIS leaner G&amp;A rate (below the filing). Source supports ZI’s actual overhead level; it does NOT say G&amp;A is 18%.</t>
         </is>
       </c>
       <c r="G11" s="612" t="inlineStr">
@@ -5543,7 +5565,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="62" customHeight="1" s="244">
+    <row r="12" ht="72" customHeight="1" s="244">
       <c r="B12" s="613" t="inlineStr">
         <is>
           <t>CapEx reduction vs base</t>
@@ -5557,14 +5579,14 @@
           <t>Lowers physical equipment spending. Reasonable because firing 15% of the sales team permanently eliminates the need to purchase and refresh their laptops and hardware.</t>
         </is>
       </c>
-      <c r="E12" s="610" t="inlineStr">
-        <is>
-          <t>In-house SDR all-in includes devices/tooling</t>
-        </is>
-      </c>
-      <c r="F12" s="611" t="inlineStr">
-        <is>
-          <t>Human SDR all-in budgets include laptops and seats. Cutting outbound humans removes refresh CapEx; −5% vs base CapEx rate is a small, directionally correct haircut.</t>
+      <c r="E12" s="630" t="inlineStr">
+        <is>
+          <t>FIND: in-house SDR all-in includes devices/tooling (~$12k tooling line in stack)</t>
+        </is>
+      </c>
+      <c r="F12" s="631" t="inlineStr">
+        <is>
+          <t>FACT in source: human SDR all-in budgets include tooling/hardware. Our −5% CapEx vs base is a MODEL THESIS haircut tied to cutting outbound seats — source does not print “CapEx −5%.”</t>
         </is>
       </c>
       <c r="G12" s="612" t="inlineStr">
@@ -5578,7 +5600,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="62" customHeight="1" s="244">
+    <row r="13" ht="72" customHeight="1" s="244">
       <c r="B13" s="607" t="inlineStr">
         <is>
           <t>WC / receivables improvement</t>
@@ -5592,14 +5614,14 @@
           <t>Speeds up cash collection from clients. Reasonable because automated AI billing systems can aggressively follow up on late invoices, freeing up cash for debt paydown.</t>
         </is>
       </c>
-      <c r="E13" s="610" t="inlineStr">
-        <is>
-          <t>ZI receivables ~80 days (SEC-derived ratios)</t>
-        </is>
-      </c>
-      <c r="F13" s="611" t="inlineStr">
-        <is>
-          <t>ZI receivables ~80 days show WC is real. Automated billing follow-ups can shorten DSO; −10% WC intensity vs base is a modest collections gain, not a wipeout.</t>
+      <c r="E13" s="630" t="inlineStr">
+        <is>
+          <t>FIND in SEC-derived ratios: ZI receivables ~80 days</t>
+        </is>
+      </c>
+      <c r="F13" s="631" t="inlineStr">
+        <is>
+          <t>FACT in source: receivables days ~80 (WC is material). Our −10% WC intensity improvement is a MODEL THESIS for automated collections — source shows DSO exists; it does not say “WC improves 10%.”</t>
         </is>
       </c>
       <c r="G13" s="612" t="inlineStr">
@@ -5613,7 +5635,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="62" customHeight="1" s="244">
+    <row r="14" ht="72" customHeight="1" s="244">
       <c r="B14" s="613" t="inlineStr">
         <is>
           <t>SOFR</t>
@@ -5627,14 +5649,14 @@
           <t>The foundational secured lending interest rate. Reasonable and historically accurate for the macroeconomic environment, properly reflecting actual institutional baseline borrowing costs.</t>
         </is>
       </c>
-      <c r="E14" s="610" t="inlineStr">
-        <is>
-          <t>NY Fed official SOFR reference rate</t>
-        </is>
-      </c>
-      <c r="F14" s="611" t="inlineStr">
-        <is>
-          <t>SOFR is the NY Fed’s official overnight Treasury-repo financing benchmark used to price leveraged loans. ~4.3% is a planning level near recent SOFR prints (see FRED).</t>
+      <c r="E14" s="630" t="inlineStr">
+        <is>
+          <t>FIND live SOFR on FRED/NY Fed (recent print ~3.62% on 2026-08-13)</t>
+        </is>
+      </c>
+      <c r="F14" s="631" t="inlineStr">
+        <is>
+          <t>FACT in source: SOFR is the official NY Fed overnight financing rate (FRED series SOFR). Our 4.30% is a MODEL PLANNING cushion above the latest ~3.6% print — open FRED for the exact daily rate; we did not invent SOFR as a concept.</t>
         </is>
       </c>
       <c r="G14" s="612" t="inlineStr">
@@ -5644,11 +5666,11 @@
       </c>
       <c r="H14" s="612" t="inlineStr">
         <is>
-          <t>fred.stlouisfed.org/series/SOFR</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="62" customHeight="1" s="244">
+          <t>www.newyorkfed.org/markets/reference-rates/sofr</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="72" customHeight="1" s="244">
       <c r="B15" s="607" t="inlineStr">
         <is>
           <t>Term Loan A spread</t>
@@ -5662,14 +5684,14 @@
           <t>The risk premium for senior debt. Reasonable for a standard LBO, reflecting typical syndicated commercial bank pricing for secured corporate borrowing.</t>
         </is>
       </c>
-      <c r="E15" s="610" t="inlineStr">
-        <is>
-          <t>LBO debt structure: TLA illustrative spreads</t>
-        </is>
-      </c>
-      <c r="F15" s="611" t="inlineStr">
-        <is>
-          <t>Bank TLA in LBO guides typically prices tighter than TLB (often SOFR+~275–375bps). SOFR+400bps is a conservative senior bank spread independent of AI ops.</t>
+      <c r="E15" s="630" t="inlineStr">
+        <is>
+          <t>FIND in LBO debt guide: TLA illustrative ~SOFR+275–375 bps</t>
+        </is>
+      </c>
+      <c r="F15" s="632" t="inlineStr">
+        <is>
+          <t>FACT in source: Term Loan A typically prices in a SOFR+~275–375bps illustrative band. Our +400 bps is at the wide/conservative end of published senior bank pricing — within market structure, slightly above the midpoint of that guide.</t>
         </is>
       </c>
       <c r="G15" s="612" t="inlineStr">
@@ -5683,7 +5705,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="62" customHeight="1" s="244">
+    <row r="16" ht="72" customHeight="1" s="244">
       <c r="B16" s="613" t="inlineStr">
         <is>
           <t>Term Loan B spread</t>
@@ -5697,14 +5719,14 @@
           <t>The risk premium for riskier debt. Reasonable, as Term Loan B is usually held by institutional investors requiring higher yields for slightly higher risk.</t>
         </is>
       </c>
-      <c r="E16" s="610" t="inlineStr">
-        <is>
-          <t>TLB pricing often SOFR+300–500bps</t>
-        </is>
-      </c>
-      <c r="F16" s="611" t="inlineStr">
-        <is>
-          <t>Institutional TLB commonly prices SOFR+300–500bps. SOFR+500bps is the upper published band—set by syndicated loan markets, not by internal AI strategy.</t>
+      <c r="E16" s="630" t="inlineStr">
+        <is>
+          <t>FIND: TLB typically SOFR+300–500 bps</t>
+        </is>
+      </c>
+      <c r="F16" s="632" t="inlineStr">
+        <is>
+          <t>FACT in source: institutional TLB often SOFR+300–500bps. Our +500 bps equals the upper end of that published range — not invented outside market guides.</t>
         </is>
       </c>
       <c r="G16" s="612" t="inlineStr">
@@ -5718,7 +5740,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="62" customHeight="1" s="244">
+    <row r="17" ht="72" customHeight="1" s="244">
       <c r="B17" s="607" t="inlineStr">
         <is>
           <t>Mandatory amortization</t>
@@ -5732,14 +5754,14 @@
           <t>Required annual principal repayment. Highly reasonable and standard market practice for leveraged loans, forcing a tiny minimum debt reduction each year.</t>
         </is>
       </c>
-      <c r="E17" s="610" t="inlineStr">
-        <is>
-          <t>Syndicated TLB ~1% annual amort standard</t>
-        </is>
-      </c>
-      <c r="F17" s="611" t="inlineStr">
-        <is>
-          <t>Market-standard institutional TLB schedules ~1% annual amortization with a bullet maturity. Loan docs—not AI FCF—set this mandatory floor.</t>
+      <c r="E17" s="630" t="inlineStr">
+        <is>
+          <t>FIND: TLB scheduled amort typically ~1%/year (bullet remainder)</t>
+        </is>
+      </c>
+      <c r="F17" s="632" t="inlineStr">
+        <is>
+          <t>FACT in source: institutional TLB usually amortizes ~1% per year with a bullet at maturity. Our 1% matches that market-standard schedule.</t>
         </is>
       </c>
       <c r="G17" s="612" t="inlineStr">
@@ -5753,7 +5775,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="62" customHeight="1" s="244">
+    <row r="18" ht="72" customHeight="1" s="244">
       <c r="B18" s="613" t="inlineStr">
         <is>
           <t>Cash sweep %</t>
@@ -5767,14 +5789,14 @@
           <t>Dedicates all excess cash to debt. Reasonable and standard for maximizing LBO returns, ensuring every free dollar generated immediately aggressively reduces outstanding leverage.</t>
         </is>
       </c>
-      <c r="E18" s="610" t="inlineStr">
-        <is>
-          <t>LBO optional prepay / excess cash practice</t>
-        </is>
-      </c>
-      <c r="F18" s="611" t="inlineStr">
-        <is>
-          <t>Sponsor LBOs typically sweep excess FCF to optional debt prepay after mandatory amort. 100% sweep maximizes deleveraging so AI margins hit MOIC/IRR.</t>
+      <c r="E18" s="630" t="inlineStr">
+        <is>
+          <t>FIND: LBO structures emphasize optional prepay / excess cash to delever</t>
+        </is>
+      </c>
+      <c r="F18" s="631" t="inlineStr">
+        <is>
+          <t>FACT in source: LBO debt design centers on using cash flow to delever (mandatory + optional prepay). Our 100% excess-cash sweep is a MODEL THESIS maximizing that standard sponsor practice — guides describe the mechanism; “100%” is our switch setting.</t>
         </is>
       </c>
       <c r="G18" s="612" t="inlineStr">
@@ -5788,7 +5810,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="62" customHeight="1" s="244">
+    <row r="19" ht="72" customHeight="1" s="244">
       <c r="B19" s="607" t="inlineStr">
         <is>
           <t>Tax rate</t>
@@ -5802,14 +5824,14 @@
           <t>Corporate income tax obligation. Perfectly reasonable because it strictly matches the current standard U.S. federal statutory corporate tax rate without aggressive tax-dodging assumptions.</t>
         </is>
       </c>
-      <c r="E19" s="610" t="inlineStr">
-        <is>
-          <t>PwC Tax Summaries: US federal CIT 21%</t>
-        </is>
-      </c>
-      <c r="F19" s="611" t="inlineStr">
-        <is>
-          <t>US federal corporate income tax is a flat 21% statutory rate. Operating-margin gains do not change the federal statutory rate used here.</t>
+      <c r="E19" s="630" t="inlineStr">
+        <is>
+          <t>FIND in PwC Tax Summaries: US federal corporate rate = 21%</t>
+        </is>
+      </c>
+      <c r="F19" s="632" t="inlineStr">
+        <is>
+          <t>FACT in source: US resident corporations are taxed at a flat 21% federal rate. Our 21% matches the statutory rate exactly.</t>
         </is>
       </c>
       <c r="G19" s="612" t="inlineStr">
@@ -5823,7 +5845,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="62" customHeight="1" s="244">
+    <row r="20" ht="72" customHeight="1" s="244">
       <c r="B20" s="613" t="inlineStr">
         <is>
           <t>Exit EV/EBITDA multiple</t>
@@ -5837,14 +5859,14 @@
           <t>The valuation multiple upon selling. Reasonable to keep it conservative; relying on a 13x exit assumes no market inflation, proving returns come from operational growth.</t>
         </is>
       </c>
-      <c r="E20" s="610" t="inlineStr">
-        <is>
-          <t>PE SaaS buyouts often ~15–22x EBITDA</t>
-        </is>
-      </c>
-      <c r="F20" s="611" t="inlineStr">
-        <is>
-          <t>PE SaaS deals often underwrite ~15–22x EBITDA. Locking exit at 13x in BOTH cases is deliberately conservative so returns come from ops, not multiple expansion.</t>
+      <c r="E20" s="630" t="inlineStr">
+        <is>
+          <t>FIND: PE SaaS buyout targets often ~15–22x EBITDA</t>
+        </is>
+      </c>
+      <c r="F20" s="631" t="inlineStr">
+        <is>
+          <t>FACT in source: PE SaaS deals often underwrite ~15–22x EBITDA. Our 13x is a MODEL THESIS conservative exit BELOW that band (held equal AI vs Base) so returns aren’t from multiple expansion.</t>
         </is>
       </c>
       <c r="G20" s="612" t="inlineStr">
@@ -5858,7 +5880,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="62" customHeight="1" s="244">
+    <row r="21" ht="72" customHeight="1" s="244">
       <c r="B21" s="607" t="inlineStr">
         <is>
           <t>S&amp;M baseline ($m)</t>
@@ -5872,14 +5894,14 @@
           <t>This is historical assumptions without AI. Total initial sales spend is reasonable, representing roughly 35% of FY24 revenue, perfectly aligning with standard SaaS benchmarks.</t>
         </is>
       </c>
-      <c r="E21" s="610" t="inlineStr">
-        <is>
-          <t>ZI FY24 S&amp;M $414.1m on $1,214.3m revenue</t>
-        </is>
-      </c>
-      <c r="F21" s="611" t="inlineStr">
-        <is>
-          <t>Company-reported FY24 S&amp;M = $414.1m (~34% of $1,214.3m). Model ~$425m (~35%) is a rounded baseline consistent with that filing.</t>
+      <c r="E21" s="630" t="inlineStr">
+        <is>
+          <t>FIND in ZI FY24 results table: S&amp;M expense = $414.1m; Revenue = $1,214.3m</t>
+        </is>
+      </c>
+      <c r="F21" s="632" t="inlineStr">
+        <is>
+          <t>FACT in source: S&amp;M $414.1m ≈ 34.1% of revenue. Our $425m (~35%) is a rounded MODEL baseline near that filing — KeyBanc also shows &lt;10% growth cohort S&amp;M ~31% (nearby band).</t>
         </is>
       </c>
       <c r="G21" s="612" t="inlineStr">
@@ -5889,11 +5911,11 @@
       </c>
       <c r="H21" s="612" t="inlineStr">
         <is>
-          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="62" customHeight="1" s="244">
+          <t>www.key.com/content/dam/kco/documents/businesses___institutions/2024_k</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="72" customHeight="1" s="244">
       <c r="B22" s="613" t="inlineStr">
         <is>
           <t>Payroll baseline ($m)</t>
@@ -5907,14 +5929,14 @@
           <t>This is historical assumptions without AI. The fixed salary portion is reasonable, representing 75% of S&amp;M, accurately reflecting that human software sales floors are base-salary heavy.</t>
         </is>
       </c>
-      <c r="E22" s="610" t="inlineStr">
-        <is>
-          <t>SDR OTE mostly base (~70%) — SyncGTM</t>
-        </is>
-      </c>
-      <c r="F22" s="611" t="inlineStr">
-        <is>
-          <t>With ~70/30 base/variable SDR mix, most people cost is payroll. Payroll baseline = 75% of S&amp;M matches that base-salary-heavy sales-floor structure.</t>
+      <c r="E22" s="630" t="inlineStr">
+        <is>
+          <t>FIND: SDR OTE ~70% base / ~30% variable</t>
+        </is>
+      </c>
+      <c r="F22" s="631" t="inlineStr">
+        <is>
+          <t>FACT in source: base dominates SDR OTE (~70%). Our payroll baseline $318.8m = 75% of $425m S&amp;M is a MODEL ALLOCATION near that published base-heavy mix — not a ZI payroll disclosure.</t>
         </is>
       </c>
       <c r="G22" s="612" t="inlineStr">
@@ -5928,7 +5950,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="62" customHeight="1" s="244">
+    <row r="23" ht="72" customHeight="1" s="244">
       <c r="B23" s="607" t="inlineStr">
         <is>
           <t>Commission baseline ($m)</t>
@@ -5942,14 +5964,14 @@
           <t>This is historical assumptions without AI. The variable payout is reasonable, calculating exactly to the remaining 25% of the budget, representing standard quota-based enterprise sales incentives.</t>
         </is>
       </c>
-      <c r="E23" s="610" t="inlineStr">
-        <is>
-          <t>Variable ~30–35% of tech SDR OTE</t>
-        </is>
-      </c>
-      <c r="F23" s="611" t="inlineStr">
-        <is>
-          <t>Tech SDR variable is typically ~30–35% of OTE. Setting commission pool at 25% of S&amp;M is a slightly conservative carve of total S&amp;M for variable payouts.</t>
+      <c r="E23" s="630" t="inlineStr">
+        <is>
+          <t>FIND: tech SDR variable typically ~30–35% of OTE</t>
+        </is>
+      </c>
+      <c r="F23" s="631" t="inlineStr">
+        <is>
+          <t>FACT in source: variable is ~30–35% of OTE. Our commission baseline $106.2m = 25% of S&amp;M is a MODEL ALLOCATION slightly below that variable share — residual after payroll carve.</t>
         </is>
       </c>
       <c r="G23" s="612" t="inlineStr">
@@ -5963,7 +5985,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="62" customHeight="1" s="244">
+    <row r="24" ht="72" customHeight="1" s="244">
       <c r="B24" s="613" t="inlineStr">
         <is>
           <t>CapEx base % of rev</t>
@@ -5977,14 +5999,14 @@
           <t>This is historical assumptions without AI. Normal hardware and capitalized software spending is reasonable for asset-light tech companies investing heavily in code rather than factories.</t>
         </is>
       </c>
-      <c r="E24" s="610" t="inlineStr">
-        <is>
-          <t>ZI FY24 strong FCF / asset-light SaaS profile</t>
-        </is>
-      </c>
-      <c r="F24" s="611" t="inlineStr">
-        <is>
-          <t>SaaS is asset-light vs industrials; ZI still printed strong FY24 FCF. 2% of revenue is a simple maintenance CapEx planning rate before the AI −5% haircut.</t>
+      <c r="E24" s="630" t="inlineStr">
+        <is>
+          <t>FIND in ZI FY24: Unlevered FCF $446.9m on $1,214.3m rev (asset-light SaaS)</t>
+        </is>
+      </c>
+      <c r="F24" s="631" t="inlineStr">
+        <is>
+          <t>FACT in source: ZI generates large FCF vs revenue (asset-light). Our CapEx = 2% of rev is a MODEL PLANNING rate for maintenance CapEx — filing supports low capital intensity, not the exact 2% plug.</t>
         </is>
       </c>
       <c r="G24" s="612" t="inlineStr">
@@ -5998,7 +6020,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="62" customHeight="1" s="244">
+    <row r="25" ht="72" customHeight="1" s="244">
       <c r="B25" s="607" t="inlineStr">
         <is>
           <t>WC base % of Δrev</t>
@@ -6012,14 +6034,14 @@
           <t>This is historical assumptions without AI. Normal working capital needs are reasonable, showing that as revenue grows, a small percentage of cash gets tied up in daily operations.</t>
         </is>
       </c>
-      <c r="E25" s="610" t="inlineStr">
-        <is>
-          <t>ZI receivables days ~80 (WC intensity)</t>
-        </is>
-      </c>
-      <c r="F25" s="611" t="inlineStr">
-        <is>
-          <t>Receivables ~80 days imply WC scales with growth. Using 2% of Δrevenue as ΔNWC is a simplified SaaS WC plug anchored to that receivables reality.</t>
+      <c r="E25" s="630" t="inlineStr">
+        <is>
+          <t>FIND: ZI receivables turnover ~80 days</t>
+        </is>
+      </c>
+      <c r="F25" s="631" t="inlineStr">
+        <is>
+          <t>FACT in source: ~80 receivable days ⇒ WC scales with growth. Our ΔNWC = 2% of Δrev is a MODEL PLANNING plug consistent with that WC intensity — not a line that says “2%.”</t>
         </is>
       </c>
       <c r="G25" s="612" t="inlineStr">
@@ -6040,7 +6062,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="62" customHeight="1" s="244">
+    <row r="27" ht="72" customHeight="1" s="244">
       <c r="B27" s="613" t="inlineStr">
         <is>
           <t>TLA rate (SOFR+4)</t>
@@ -6055,14 +6077,14 @@
           <t>Total Term Loan A interest. Mathematically correct and reasonable for the total borrowing cost demanded by senior lenders in this specific rate environment.</t>
         </is>
       </c>
-      <c r="E27" s="610" t="inlineStr">
-        <is>
-          <t>LBO TLA = SOFR + senior bank spread</t>
-        </is>
-      </c>
-      <c r="F27" s="611" t="inlineStr">
-        <is>
-          <t>Computed as SOFR (C14) + TLA spread (C15). All-in ~8.3% matches senior secured bank pricing in this SOFR + 400bps setup.</t>
+      <c r="E27" s="630" t="inlineStr">
+        <is>
+          <t>FIND: TLA = SOFR + senior spread (formula)</t>
+        </is>
+      </c>
+      <c r="F27" s="632" t="inlineStr">
+        <is>
+          <t>COMPUTED: C14+C15. Evidence for components is on rows 14–15 (official SOFR + published TLA spread band). All-in ~8.3% with current inputs.</t>
         </is>
       </c>
       <c r="G27" s="612" t="inlineStr">
@@ -6072,11 +6094,11 @@
       </c>
       <c r="H27" s="612" t="inlineStr">
         <is>
-          <t>www.newyorkfed.org/markets/reference-rates/sofr</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="62" customHeight="1" s="244">
+          <t>fred.stlouisfed.org/series/SOFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="72" customHeight="1" s="244">
       <c r="B28" s="607" t="inlineStr">
         <is>
           <t>TLB rate (SOFR+5)</t>
@@ -6091,14 +6113,14 @@
           <t>Total Term Loan B interest. Mathematically correct and perfectly reasonable, pricing the institutional debt risk appropriately above the safer Term Loan A.</t>
         </is>
       </c>
-      <c r="E28" s="610" t="inlineStr">
-        <is>
-          <t>LBO TLB = SOFR + institutional spread</t>
-        </is>
-      </c>
-      <c r="F28" s="611" t="inlineStr">
-        <is>
-          <t>Computed as SOFR (C14) + TLB spread (C16). All-in ~9.3% prices institutional TLB risk appropriately above TLA in this structure.</t>
+      <c r="E28" s="630" t="inlineStr">
+        <is>
+          <t>FIND: TLB = SOFR + institutional spread (formula)</t>
+        </is>
+      </c>
+      <c r="F28" s="632" t="inlineStr">
+        <is>
+          <t>COMPUTED: C14+C16. Evidence for components is on rows 14 &amp; 16 (official SOFR + published TLB SOFR+300–500bps band). All-in ~9.3% with current inputs.</t>
         </is>
       </c>
       <c r="G28" s="612" t="inlineStr">
@@ -6108,19 +6130,19 @@
       </c>
       <c r="H28" s="612" t="inlineStr">
         <is>
-          <t>www.newyorkfed.org/markets/reference-rates/sofr</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1" s="244">
-      <c r="B29" s="564" t="inlineStr">
-        <is>
-          <t>AI $34m triangulation (row 9, col F):</t>
-        </is>
-      </c>
-      <c r="C29" s="620" t="inlineStr">
-        <is>
-          <t>SF publishes $2/conversation and ~$0.10/action. At ZI scale (~378 outbound roles = 25% of 1,513 S&amp;M), $5–10k/mo agents imply ~$23–45m; model uses midpoint avg(23,45) = $34m.</t>
+          <t>fred.stlouisfed.org/series/SOFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1" s="244">
+      <c r="B29" s="618" t="inlineStr">
+        <is>
+          <t>AI $34m — derived from SF list prices + ZI S&amp;M headcount (see E9/F9). Not a made-up lone number.</t>
+        </is>
+      </c>
+      <c r="C29" s="633" t="inlineStr">
+        <is>
+          <t>FACT in source: Salesforce list prices $2/conversation and ~$0.10/action. Secondary AI-agent ranges ~$5–10k/mo × ~378 outbound roles (25% of ZI’s 1,513 S&amp;M from 10-K) ⇒ ~$23–45m. Model uses midpoint $34m = avg(23,45). $34m is derived math, not a SF quote of “$34m.”</t>
         </is>
       </c>
       <c r="D29" s="621" t="n"/>
@@ -6130,7 +6152,7 @@
     <row r="30">
       <c r="B30" s="618" t="inlineStr">
         <is>
-          <t>PDF source map:</t>
+          <t>PDF audit of FIND lines:</t>
         </is>
       </c>
       <c r="C30" s="593" t="inlineStr">
@@ -6146,9 +6168,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C29:F29"/>
@@ -11845,7 +11864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="B2:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="244" min="2" max="2"/>
@@ -11855,7 +11874,6 @@
     <col width="78" customWidth="1" style="244" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -11870,7 +11888,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="564" t="inlineStr">
         <is>
@@ -11892,7 +11909,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" s="564" t="inlineStr">
         <is>
@@ -12105,7 +12121,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="B24" s="564" t="inlineStr">
         <is>
@@ -12134,7 +12149,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="B29" s="564" t="inlineStr">
         <is>
@@ -12365,7 +12379,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
@@ -12373,9 +12386,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48">
       <c r="B48" s="564" t="inlineStr">
         <is>
@@ -12478,10 +12488,6 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B3:F3"/>
@@ -12497,7 +12503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="B2:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" style="244" min="2" max="2"/>
@@ -12514,7 +12520,6 @@
     <col width="70" customWidth="1" style="244" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -12536,7 +12541,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" s="557" t="inlineStr">
         <is>
@@ -13499,7 +13503,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="B23" s="564" t="inlineStr">
         <is>
@@ -13515,7 +13518,6 @@
       </c>
     </row>
     <row r="25"/>
-    <row r="26"/>
     <row r="27">
       <c r="B27" s="564" t="inlineStr">
         <is>
@@ -13551,7 +13553,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="B33" s="564" t="inlineStr">
         <is>
@@ -13573,7 +13574,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="B37" s="564" t="inlineStr">
         <is>
@@ -13595,7 +13595,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="B41" s="564" t="inlineStr">
         <is>
@@ -13884,7 +13883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="B2:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
@@ -13897,7 +13896,6 @@
     <col width="12" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -14428,22 +14426,6 @@
         <v>557.1124750633038</v>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14455,7 +14437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="B2:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
@@ -14468,7 +14450,6 @@
     <col width="12" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -14999,22 +14980,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15026,10 +14991,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="B2:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
@@ -15037,11 +15001,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8" ht="26.25" customHeight="1" s="244">
       <c r="B8" s="402" t="inlineStr">
         <is>
@@ -15060,8 +15019,6 @@
       <c r="L8" s="404" t="n"/>
       <c r="M8" s="404" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="B11" s="405" t="inlineStr">
         <is>
@@ -15072,31 +15029,6 @@
     <row r="12"/>
     <row r="13"/>
     <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -153,7 +153,7 @@
     <numFmt numFmtId="245" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
     <numFmt numFmtId="246" formatCode="###0&quot;E&quot;_)"/>
   </numFmts>
-  <fonts count="120">
+  <fonts count="121">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -920,6 +920,11 @@
       <name val="Calibri"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="45">
     <fill>
@@ -1948,7 +1953,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="634">
+  <cellXfs count="635">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3074,6 +3079,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="44" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5263,8 +5271,8 @@
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
     <col width="11" customWidth="1" style="244" min="3" max="3"/>
     <col width="52" customWidth="1" style="244" min="4" max="4"/>
-    <col width="48" customWidth="1" style="244" min="5" max="5"/>
-    <col width="62" customWidth="1" style="244" min="6" max="6"/>
+    <col width="46" customWidth="1" style="244" min="5" max="5"/>
+    <col width="72" customWidth="1" style="244" min="6" max="6"/>
     <col width="34" customWidth="1" style="244" min="7" max="7"/>
     <col width="38" customWidth="1" style="244" min="8" max="8"/>
   </cols>
@@ -5272,18 +5280,18 @@
     <row r="2">
       <c r="B2" s="629" t="inlineStr">
         <is>
-          <t>Assumptions Drivers — every number has a FIND-in-source pointer (FACT vs THESIS labeled honestly)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1" s="244">
+          <t>Assumptions Drivers — col F shows SOURCE MATH → DRIVER for every input</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>Col E = click the source and read the FIND line (where the statistic appears). Col F = what that source actually says, and whether our model value EQUALS the source (FACT) or is a labeled THESIS near that evidence. We do not claim a source prints “15% ZI payroll cut” if it doesn’t.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" s="244">
+          <t>Column F walks source facts → arithmetic/logic → the yellow value in col C (same pattern as AI $34m). Column E is the clickable FIND link. Thesis steps are labeled; we do not pretend SF quotes “$34m.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" s="244">
       <c r="B4" s="606" t="inlineStr">
         <is>
           <t>Driver</t>
@@ -5301,12 +5309,12 @@
       </c>
       <c r="E4" s="606" t="inlineStr">
         <is>
-          <t>Source link — FIND the statistic here (click)</t>
+          <t>Source link — FIND statistic here (click)</t>
         </is>
       </c>
       <c r="F4" s="606" t="inlineStr">
         <is>
-          <t>What source says + FACT vs THESIS (honest)</t>
+          <t>SOURCE MATH → DRIVER (how this source produces the yellow value)</t>
         </is>
       </c>
       <c r="G4" s="606" t="inlineStr">
@@ -5320,7 +5328,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="72" customHeight="1" s="244">
+    <row r="5" ht="78" customHeight="1" s="244">
       <c r="B5" s="607" t="inlineStr">
         <is>
           <t>Revenue growth</t>
@@ -5336,12 +5344,12 @@
       </c>
       <c r="E5" s="630" t="inlineStr">
         <is>
-          <t>FIND in ZI FY24 results: Revenue $1,214.3m (−2% YoY) — NOT +10%</t>
+          <t>FIND: ZI FY24 Revenue $1,214.3m (−2% YoY)</t>
         </is>
       </c>
       <c r="F5" s="631" t="inlineStr">
         <is>
-          <t>FACT in source: FY24 revenue fell ~2%. Our 10% is a MODEL THESIS forward underwrite (held equal in AI vs Base), not a figure printed as ZI growth. Source proves baseline sales scale, not the 10% rate.</t>
+          <t>SOURCE MATH → DRIVER: Filing shows FY24 rev $1,214.3m / FY23 $1,239.5m − 1 = −2.0% (not +10%). Driver C5=10% is a forward LBO underwrite held equal in AI vs Base so IRR delta is cost-driven. Math tie: baseline scale from source; growth rate is thesis, not the −2% print.</t>
         </is>
       </c>
       <c r="G5" s="612" t="inlineStr">
@@ -5355,7 +5363,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="72" customHeight="1" s="244">
+    <row r="6" ht="78" customHeight="1" s="244">
       <c r="B6" s="613" t="inlineStr">
         <is>
           <t>Gross margin</t>
@@ -5371,12 +5379,12 @@
       </c>
       <c r="E6" s="630" t="inlineStr">
         <is>
-          <t>FIND in Aleph/Benchmarkit: 2025 software median GM = 80%</t>
-        </is>
-      </c>
-      <c r="F6" s="632" t="inlineStr">
-        <is>
-          <t>FACT in source: software median gross margin is 80%. Model uses 80% to match that published median. (ZI GAAP GM is higher ~84% in SEC-derived comps — we are not inventing 80%.)</t>
+          <t>FIND: Aleph/Benchmarkit software median GM = 80%</t>
+        </is>
+      </c>
+      <c r="F6" s="631" t="inlineStr">
+        <is>
+          <t>SOURCE MATH → DRIVER: Published 2025 software median GM = 80%. Driver C6=80% ⇒ COGS% = 1 − 0.80 = 20%; COGS_t = Rev_t × 0.20. (ZI GAAP GM ~84% in SEC comps would imply COGS 16%; we deliberately use the 80% median, not ZI’s higher print.)</t>
         </is>
       </c>
       <c r="G6" s="612" t="inlineStr">
@@ -5390,7 +5398,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="72" customHeight="1" s="244">
+    <row r="7" ht="78" customHeight="1" s="244">
       <c r="B7" s="607" t="inlineStr">
         <is>
           <t>Sales payroll cut (Y1)</t>
@@ -5409,9 +5417,9 @@
           <t>FIND: US B2B SaaS SDR headcount −~18% YoY (junior −31%)</t>
         </is>
       </c>
-      <c r="F7" s="631" t="inlineStr">
-        <is>
-          <t>FACT in source: net US B2B SaaS SDR headcount down ~18% YoY (junior roles −31%). Our −15% Y1 payroll cut is a MODEL THESIS set near that published ~18% industry cut — source does not say “ZoomInfo cut 15%.”</t>
+      <c r="F7" s="632" t="inlineStr">
+        <is>
+          <t>SOURCE MATH → DRIVER: Published SDR headcount −~18% YoY. Driver C7=15% ≈ that cut. Payroll_Y1 = Payroll0 × (1 − 0.15) = 318.8 × 0.85 = $270.98m. Source supports ~15–18% outbound labor reduction; 15% is the model switch near the −18% evidence (not a ZI 10-K line).</t>
         </is>
       </c>
       <c r="G7" s="612" t="inlineStr">
@@ -5425,7 +5433,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="72" customHeight="1" s="244">
+    <row r="8" ht="78" customHeight="1" s="244">
       <c r="B8" s="613" t="inlineStr">
         <is>
           <t>Variable commission cut</t>
@@ -5441,12 +5449,12 @@
       </c>
       <c r="E8" s="630" t="inlineStr">
         <is>
-          <t>FIND in SyncGTM: SDR OTE mix ~70% base / ~30% variable</t>
-        </is>
-      </c>
-      <c r="F8" s="631" t="inlineStr">
-        <is>
-          <t>FACT in source: standard SDR pay is ~70/30 base/variable. Our −20% commission cut is a MODEL THESIS: if AI replaces outbound humans, ~30% variable layer shrinks; −20% is a partial cut of that published variable share — not a ZI filing line item.</t>
+          <t>FIND: SDR OTE ~70% base / ~30% variable</t>
+        </is>
+      </c>
+      <c r="F8" s="632" t="inlineStr">
+        <is>
+          <t>SOURCE MATH → DRIVER: Source variable share ≈ 30% of OTE. Driver C8=20% cut on commission pool: Commission_AI = 106.2 × (1 − 0.20) = $84.96m. Logic: AI doesn’t take commissions ⇒ shrink the ~30% variable layer; −20% is a partial cut of that published variable share.</t>
         </is>
       </c>
       <c r="G8" s="612" t="inlineStr">
@@ -5460,7 +5468,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="72" customHeight="1" s="244">
+    <row r="9" ht="78" customHeight="1" s="244">
       <c r="B9" s="607" t="inlineStr">
         <is>
           <t>AI infrastructure ($m)</t>
@@ -5476,12 +5484,12 @@
       </c>
       <c r="E9" s="630" t="inlineStr">
         <is>
-          <t>FIND in SF press: $2/conversation; Flex Credits $500/100k (= ~$0.10/action)</t>
-        </is>
-      </c>
-      <c r="F9" s="632" t="inlineStr">
-        <is>
-          <t>FACT in source: Salesforce list prices $2/conversation and ~$0.10/action. Secondary AI-agent ranges ~$5–10k/mo × ~378 outbound roles (25% of ZI’s 1,513 S&amp;M from 10-K) ⇒ ~$23–45m. Model uses midpoint $34m = avg(23,45). $34m is derived math, not a SF quote of “$34m.”</t>
+          <t>FIND: SF $2/conversation; Flex Credits ~$0.10/action; ZI S&amp;M HC 1,513</t>
+        </is>
+      </c>
+      <c r="F9" s="634" t="inlineStr">
+        <is>
+          <t>SOURCE MATH → DRIVER: SF list $2/conv and ~$0.10/action. Outbound roles ≈ 25% × 1,513 S&amp;M (10-K) = 378. At $5–10k/mo/agent: 378 × $5k × 12 = $22.7m; 378 × $10k × 12 = $45.4m. Driver C9 = avg(23,45) = $34m. $34m is derived — SF does not quote “$34m.”</t>
         </is>
       </c>
       <c r="G9" s="612" t="inlineStr">
@@ -5495,7 +5503,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="72" customHeight="1" s="244">
+    <row r="10" ht="78" customHeight="1" s="244">
       <c r="B10" s="613" t="inlineStr">
         <is>
           <t>S&amp;M expense growth Y2+</t>
@@ -5511,12 +5519,12 @@
       </c>
       <c r="E10" s="630" t="inlineStr">
         <is>
-          <t>FIND in Gartner: inference/agentic AI scales as production opex (not headcount-linear)</t>
+          <t>FIND: Gartner — agentic/inference AI scales as compute opex, not headcount-linear</t>
         </is>
       </c>
       <c r="F10" s="631" t="inlineStr">
         <is>
-          <t>FACT in source: enterprises shift to production inference/agentic workloads that scale with compute opex. Our 2% S&amp;M growth cap is a MODEL THESIS illustrating near-inflation opex after AI replaces linear hiring — Gartner does not publish “2% S&amp;M growth.”</t>
+          <t>SOURCE MATH → DRIVER: Source: production agents scale via inference opex (not 1:1 hiring). Driver C10=2%: for t≥2, Payroll_t = Payroll_{t−1} × 1.02 (same for commissions). Example: 270.98 × 1.02 = $276.4m in Y2. 2% ≈ maintenance/inflation growth after severing revenue-linked hiring (thesis rate; Gartner doesn’t print “2%”).</t>
         </is>
       </c>
       <c r="G10" s="612" t="inlineStr">
@@ -5530,7 +5538,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="72" customHeight="1" s="244">
+    <row r="11" ht="78" customHeight="1" s="244">
       <c r="B11" s="607" t="inlineStr">
         <is>
           <t>G&amp;A % of revenue</t>
@@ -5546,12 +5554,12 @@
       </c>
       <c r="E11" s="630" t="inlineStr">
         <is>
-          <t>FIND in ZI FY24 P&amp;L: G&amp;A $295.3m → ~24.3% of $1,214.3m rev</t>
+          <t>FIND: ZI FY24 G&amp;A $295.3m on Revenue $1,214.3m</t>
         </is>
       </c>
       <c r="F11" s="631" t="inlineStr">
         <is>
-          <t>FACT in source: G&amp;A = $295.3m (~24% of revenue). Our 18% is a MODEL THESIS leaner G&amp;A rate (below the filing). Source supports ZI’s actual overhead level; it does NOT say G&amp;A is 18%.</t>
+          <t>SOURCE MATH → DRIVER: Filing G&amp;A/Rev = 295.3 / 1214.3 = 24.3%. Driver C11=18% is a leaner thesis rate. G&amp;A_t = Rev_t × 0.18 (e.g. Y1 rev 1335.7 × 0.18 ≈ $240.4m). Source gives the actual 24.3% anchor; model deliberately uses 18% below that print.</t>
         </is>
       </c>
       <c r="G11" s="612" t="inlineStr">
@@ -5565,7 +5573,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="72" customHeight="1" s="244">
+    <row r="12" ht="78" customHeight="1" s="244">
       <c r="B12" s="613" t="inlineStr">
         <is>
           <t>CapEx reduction vs base</t>
@@ -5581,12 +5589,12 @@
       </c>
       <c r="E12" s="630" t="inlineStr">
         <is>
-          <t>FIND: in-house SDR all-in includes devices/tooling (~$12k tooling line in stack)</t>
-        </is>
-      </c>
-      <c r="F12" s="631" t="inlineStr">
-        <is>
-          <t>FACT in source: human SDR all-in budgets include tooling/hardware. Our −5% CapEx vs base is a MODEL THESIS haircut tied to cutting outbound seats — source does not print “CapEx −5%.”</t>
+          <t>FIND: human SDR all-in includes tooling/devices (~$12k tooling in stack examples)</t>
+        </is>
+      </c>
+      <c r="F12" s="632" t="inlineStr">
+        <is>
+          <t>SOURCE MATH → DRIVER: Source shows devices/tooling inside SDR all-in cost. Driver C12=5% CapEx cut: CapEx_AI = Rev × CapEx_base% × (1 − 0.05) = Rev × 0.02 × 0.95 = Rev × 1.9%. Cutting ~15% outbound seats (C7) removes laptop refresh — 5% is the modeled CapEx haircut tied to that labor cut.</t>
         </is>
       </c>
       <c r="G12" s="612" t="inlineStr">
@@ -5600,7 +5608,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="72" customHeight="1" s="244">
+    <row r="13" ht="78" customHeight="1" s="244">
       <c r="B13" s="607" t="inlineStr">
         <is>
           <t>WC / receivables improvement</t>
@@ -5616,12 +5624,12 @@
       </c>
       <c r="E13" s="630" t="inlineStr">
         <is>
-          <t>FIND in SEC-derived ratios: ZI receivables ~80 days</t>
+          <t>FIND: ZI receivables ~80 days (SEC-derived)</t>
         </is>
       </c>
       <c r="F13" s="631" t="inlineStr">
         <is>
-          <t>FACT in source: receivables days ~80 (WC is material). Our −10% WC intensity improvement is a MODEL THESIS for automated collections — source shows DSO exists; it does not say “WC improves 10%.”</t>
+          <t>SOURCE MATH → DRIVER: ~80 DSO ⇒ WC scales with growth. Driver C13=10% improvement: ΔNWC_AI = ΔRev × WC_base% × (1 − 0.10) = ΔRev × 0.02 × 0.90 = ΔRev × 1.8%. Source proves receivables intensity; −10% is the thesis collections gain from automated billing.</t>
         </is>
       </c>
       <c r="G13" s="612" t="inlineStr">
@@ -5635,7 +5643,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="72" customHeight="1" s="244">
+    <row r="14" ht="78" customHeight="1" s="244">
       <c r="B14" s="613" t="inlineStr">
         <is>
           <t>SOFR</t>
@@ -5651,12 +5659,12 @@
       </c>
       <c r="E14" s="630" t="inlineStr">
         <is>
-          <t>FIND live SOFR on FRED/NY Fed (recent print ~3.62% on 2026-08-13)</t>
+          <t>FIND live SOFR on FRED (e.g. ~3.62% on 2026-08-13); NY Fed publishes the rate</t>
         </is>
       </c>
       <c r="F14" s="631" t="inlineStr">
         <is>
-          <t>FACT in source: SOFR is the official NY Fed overnight financing rate (FRED series SOFR). Our 4.30% is a MODEL PLANNING cushion above the latest ~3.6% print — open FRED for the exact daily rate; we did not invent SOFR as a concept.</t>
+          <t>SOURCE MATH → DRIVER: Official SOFR feeds leveraged-loan coupons. Driver C14=4.30% is a planning cushion above recent ~3.6% prints (+~70 bps buffer). TLA/TLB interest use C14 directly: rate = SOFR + spread. Open FRED for the exact daily print.</t>
         </is>
       </c>
       <c r="G14" s="612" t="inlineStr">
@@ -5670,7 +5678,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="72" customHeight="1" s="244">
+    <row r="15" ht="78" customHeight="1" s="244">
       <c r="B15" s="607" t="inlineStr">
         <is>
           <t>Term Loan A spread</t>
@@ -5686,12 +5694,12 @@
       </c>
       <c r="E15" s="630" t="inlineStr">
         <is>
-          <t>FIND in LBO debt guide: TLA illustrative ~SOFR+275–375 bps</t>
-        </is>
-      </c>
-      <c r="F15" s="632" t="inlineStr">
-        <is>
-          <t>FACT in source: Term Loan A typically prices in a SOFR+~275–375bps illustrative band. Our +400 bps is at the wide/conservative end of published senior bank pricing — within market structure, slightly above the midpoint of that guide.</t>
+          <t>FIND: TLA illustrative ~SOFR+275–375 bps</t>
+        </is>
+      </c>
+      <c r="F15" s="631" t="inlineStr">
+        <is>
+          <t>SOURCE MATH → DRIVER: Guide band SOFR+275–375bps. Driver C15=+400bps (0.04) is ~25–125bps above that band (conservative). TLA_rate = C14 + C15 = 4.30% + 4.00% = 8.30% (see C27).</t>
         </is>
       </c>
       <c r="G15" s="612" t="inlineStr">
@@ -5705,7 +5713,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="72" customHeight="1" s="244">
+    <row r="16" ht="78" customHeight="1" s="244">
       <c r="B16" s="613" t="inlineStr">
         <is>
           <t>Term Loan B spread</t>
@@ -5726,7 +5734,7 @@
       </c>
       <c r="F16" s="632" t="inlineStr">
         <is>
-          <t>FACT in source: institutional TLB often SOFR+300–500bps. Our +500 bps equals the upper end of that published range — not invented outside market guides.</t>
+          <t>SOURCE MATH → DRIVER: Published TLB band SOFR+300–500bps. Driver C16=+500bps = top of that band. TLB_rate = C14 + C16 = 4.30% + 5.00% = 9.30% (see C28).</t>
         </is>
       </c>
       <c r="G16" s="612" t="inlineStr">
@@ -5740,7 +5748,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="72" customHeight="1" s="244">
+    <row r="17" ht="78" customHeight="1" s="244">
       <c r="B17" s="607" t="inlineStr">
         <is>
           <t>Mandatory amortization</t>
@@ -5756,12 +5764,12 @@
       </c>
       <c r="E17" s="630" t="inlineStr">
         <is>
-          <t>FIND: TLB scheduled amort typically ~1%/year (bullet remainder)</t>
+          <t>FIND: TLB scheduled amort typically ~1%/year</t>
         </is>
       </c>
       <c r="F17" s="632" t="inlineStr">
         <is>
-          <t>FACT in source: institutional TLB usually amortizes ~1% per year with a bullet at maturity. Our 1% matches that market-standard schedule.</t>
+          <t>SOURCE MATH → DRIVER: Source standard = ~1% of original principal / year. Driver C17=1%. Mandatory_t = Initial_new_debt × 0.01 (e.g. 915.5 × 0.01 ≈ $9.2m/yr before optional sweep).</t>
         </is>
       </c>
       <c r="G17" s="612" t="inlineStr">
@@ -5775,7 +5783,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="72" customHeight="1" s="244">
+    <row r="18" ht="78" customHeight="1" s="244">
       <c r="B18" s="613" t="inlineStr">
         <is>
           <t>Cash sweep %</t>
@@ -5791,12 +5799,12 @@
       </c>
       <c r="E18" s="630" t="inlineStr">
         <is>
-          <t>FIND: LBO structures emphasize optional prepay / excess cash to delever</t>
-        </is>
-      </c>
-      <c r="F18" s="631" t="inlineStr">
-        <is>
-          <t>FACT in source: LBO debt design centers on using cash flow to delever (mandatory + optional prepay). Our 100% excess-cash sweep is a MODEL THESIS maximizing that standard sponsor practice — guides describe the mechanism; “100%” is our switch setting.</t>
+          <t>FIND: LBO design uses excess cash / optional prepay to delever</t>
+        </is>
+      </c>
+      <c r="F18" s="632" t="inlineStr">
+        <is>
+          <t>SOURCE MATH → DRIVER: Source mechanism = optional prepay after mandatory amort. Driver C18=100%: Optional_sweep = 1.0 × max(0, FCF − Mandatory); Debt_end = Debt_beg − Mandatory − Optional. 100% is the switch setting maximizing that standard delever path.</t>
         </is>
       </c>
       <c r="G18" s="612" t="inlineStr">
@@ -5810,7 +5818,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="72" customHeight="1" s="244">
+    <row r="19" ht="78" customHeight="1" s="244">
       <c r="B19" s="607" t="inlineStr">
         <is>
           <t>Tax rate</t>
@@ -5826,12 +5834,12 @@
       </c>
       <c r="E19" s="630" t="inlineStr">
         <is>
-          <t>FIND in PwC Tax Summaries: US federal corporate rate = 21%</t>
+          <t>FIND: US federal corporate tax rate = 21%</t>
         </is>
       </c>
       <c r="F19" s="632" t="inlineStr">
         <is>
-          <t>FACT in source: US resident corporations are taxed at a flat 21% federal rate. Our 21% matches the statutory rate exactly.</t>
+          <t>SOURCE MATH → DRIVER: Statutory federal CIT = 21%. Driver C19=21%. Tax_t = max(0, EBT_t) × 0.21; NI_t = EBT_t − Tax_t. Direct 1:1 match to the published statutory rate.</t>
         </is>
       </c>
       <c r="G19" s="612" t="inlineStr">
@@ -5845,7 +5853,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="72" customHeight="1" s="244">
+    <row r="20" ht="78" customHeight="1" s="244">
       <c r="B20" s="613" t="inlineStr">
         <is>
           <t>Exit EV/EBITDA multiple</t>
@@ -5861,12 +5869,12 @@
       </c>
       <c r="E20" s="630" t="inlineStr">
         <is>
-          <t>FIND: PE SaaS buyout targets often ~15–22x EBITDA</t>
+          <t>FIND: PE SaaS buyouts often ~15–22x EBITDA</t>
         </is>
       </c>
       <c r="F20" s="631" t="inlineStr">
         <is>
-          <t>FACT in source: PE SaaS deals often underwrite ~15–22x EBITDA. Our 13x is a MODEL THESIS conservative exit BELOW that band (held equal AI vs Base) so returns aren’t from multiple expansion.</t>
+          <t>SOURCE MATH → DRIVER: Source band ~15–22x. Driver C20=13.0x is deliberately ~2–9 turns below that band. Exit_EV = Y5_EBITDA × 13. Locked equal in AI vs Base so MOIC/IRR uplift comes from ops, not multiple expansion.</t>
         </is>
       </c>
       <c r="G20" s="612" t="inlineStr">
@@ -5880,7 +5888,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="72" customHeight="1" s="244">
+    <row r="21" ht="78" customHeight="1" s="244">
       <c r="B21" s="607" t="inlineStr">
         <is>
           <t>S&amp;M baseline ($m)</t>
@@ -5896,12 +5904,12 @@
       </c>
       <c r="E21" s="630" t="inlineStr">
         <is>
-          <t>FIND in ZI FY24 results table: S&amp;M expense = $414.1m; Revenue = $1,214.3m</t>
-        </is>
-      </c>
-      <c r="F21" s="632" t="inlineStr">
-        <is>
-          <t>FACT in source: S&amp;M $414.1m ≈ 34.1% of revenue. Our $425m (~35%) is a rounded MODEL baseline near that filing — KeyBanc also shows &lt;10% growth cohort S&amp;M ~31% (nearby band).</t>
+          <t>FIND: ZI FY24 S&amp;M $414.1m; Revenue $1,214.3m</t>
+        </is>
+      </c>
+      <c r="F21" s="631" t="inlineStr">
+        <is>
+          <t>SOURCE MATH → DRIVER: Filing S&amp;M/Rev = 414.1 / 1214.3 = 34.1%. Driver C21=$425m ⇒ 425 / 1214.3 = 35.0% (rounded near the filing). KeyBanc &lt;10% growth cohort S&amp;M ~31% also sits in the same ~30–35% neighborhood.</t>
         </is>
       </c>
       <c r="G21" s="612" t="inlineStr">
@@ -5915,7 +5923,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="72" customHeight="1" s="244">
+    <row r="22" ht="78" customHeight="1" s="244">
       <c r="B22" s="613" t="inlineStr">
         <is>
           <t>Payroll baseline ($m)</t>
@@ -5934,9 +5942,9 @@
           <t>FIND: SDR OTE ~70% base / ~30% variable</t>
         </is>
       </c>
-      <c r="F22" s="631" t="inlineStr">
-        <is>
-          <t>FACT in source: base dominates SDR OTE (~70%). Our payroll baseline $318.8m = 75% of $425m S&amp;M is a MODEL ALLOCATION near that published base-heavy mix — not a ZI payroll disclosure.</t>
+      <c r="F22" s="632" t="inlineStr">
+        <is>
+          <t>SOURCE MATH → DRIVER: Source base share ~70% of OTE. Driver C22 = 75% × S&amp;M baseline = 0.75 × 425 = $318.8m payroll pool. Allocation set near the published base-heavy mix (slightly above 70% because total S&amp;M also includes non-OTE costs).</t>
         </is>
       </c>
       <c r="G22" s="612" t="inlineStr">
@@ -5950,7 +5958,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="72" customHeight="1" s="244">
+    <row r="23" ht="78" customHeight="1" s="244">
       <c r="B23" s="607" t="inlineStr">
         <is>
           <t>Commission baseline ($m)</t>
@@ -5966,12 +5974,12 @@
       </c>
       <c r="E23" s="630" t="inlineStr">
         <is>
-          <t>FIND: tech SDR variable typically ~30–35% of OTE</t>
+          <t>FIND: tech SDR variable ~30–35% of OTE</t>
         </is>
       </c>
       <c r="F23" s="631" t="inlineStr">
         <is>
-          <t>FACT in source: variable is ~30–35% of OTE. Our commission baseline $106.2m = 25% of S&amp;M is a MODEL ALLOCATION slightly below that variable share — residual after payroll carve.</t>
+          <t>SOURCE MATH → DRIVER: Source variable ~30–35% of OTE. Driver C23 = 25% × 425 = $106.2m (and 318.8 + 106.2 = 425). 25% is a slightly conservative carve of total S&amp;M vs the ~30% OTE variable share.</t>
         </is>
       </c>
       <c r="G23" s="612" t="inlineStr">
@@ -5985,7 +5993,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="72" customHeight="1" s="244">
+    <row r="24" ht="78" customHeight="1" s="244">
       <c r="B24" s="613" t="inlineStr">
         <is>
           <t>CapEx base % of rev</t>
@@ -6001,12 +6009,12 @@
       </c>
       <c r="E24" s="630" t="inlineStr">
         <is>
-          <t>FIND in ZI FY24: Unlevered FCF $446.9m on $1,214.3m rev (asset-light SaaS)</t>
+          <t>FIND: ZI FY24 Unlevered FCF $446.9m on $1,214.3m rev (asset-light)</t>
         </is>
       </c>
       <c r="F24" s="631" t="inlineStr">
         <is>
-          <t>FACT in source: ZI generates large FCF vs revenue (asset-light). Our CapEx = 2% of rev is a MODEL PLANNING rate for maintenance CapEx — filing supports low capital intensity, not the exact 2% plug.</t>
+          <t>SOURCE MATH → DRIVER: uFCF/Rev = 446.9 / 1214.3 ≈ 36.8% ⇒ low capital intensity. Driver C24=2%: CapEx_base = Rev × 0.02 (before AI −5% in C12). 2% is a maintenance CapEx planning plug consistent with asset-light FCF, not a filing CapEx% line.</t>
         </is>
       </c>
       <c r="G24" s="612" t="inlineStr">
@@ -6020,7 +6028,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="72" customHeight="1" s="244">
+    <row r="25" ht="78" customHeight="1" s="244">
       <c r="B25" s="607" t="inlineStr">
         <is>
           <t>WC base % of Δrev</t>
@@ -6036,12 +6044,12 @@
       </c>
       <c r="E25" s="630" t="inlineStr">
         <is>
-          <t>FIND: ZI receivables turnover ~80 days</t>
-        </is>
-      </c>
-      <c r="F25" s="631" t="inlineStr">
-        <is>
-          <t>FACT in source: ~80 receivable days ⇒ WC scales with growth. Our ΔNWC = 2% of Δrev is a MODEL PLANNING plug consistent with that WC intensity — not a line that says “2%.”</t>
+          <t>FIND: ZI receivables ~80 days</t>
+        </is>
+      </c>
+      <c r="F25" s="632" t="inlineStr">
+        <is>
+          <t>SOURCE MATH → DRIVER: 80/365 ≈ 21.9% of annual sales theoretically tied in AR at a point in time; growth still needs incremental WC. Driver C25=2%: ΔNWC = ΔRev × 0.02 (before AI −10% in C13). Simplified annual plug anchored to that receivables reality.</t>
         </is>
       </c>
       <c r="G25" s="612" t="inlineStr">
@@ -6062,7 +6070,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="72" customHeight="1" s="244">
+    <row r="27" ht="78" customHeight="1" s="244">
       <c r="B27" s="613" t="inlineStr">
         <is>
           <t>TLA rate (SOFR+4)</t>
@@ -6079,12 +6087,12 @@
       </c>
       <c r="E27" s="630" t="inlineStr">
         <is>
-          <t>FIND: TLA = SOFR + senior spread (formula)</t>
+          <t>FIND: TLA coupon = SOFR + senior bank spread</t>
         </is>
       </c>
       <c r="F27" s="632" t="inlineStr">
         <is>
-          <t>COMPUTED: C14+C15. Evidence for components is on rows 14–15 (official SOFR + published TLA spread band). All-in ~8.3% with current inputs.</t>
+          <t>SOURCE MATH → DRIVER: C27 = C14 + C15 = 4.30% + 4.00% = 8.30%. Components sourced on rows 14–15 (official SOFR + TLA spread band). Interest_TLA = TLA_beg × 8.30%.</t>
         </is>
       </c>
       <c r="G27" s="612" t="inlineStr">
@@ -6098,7 +6106,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="72" customHeight="1" s="244">
+    <row r="28" ht="78" customHeight="1" s="244">
       <c r="B28" s="607" t="inlineStr">
         <is>
           <t>TLB rate (SOFR+5)</t>
@@ -6115,12 +6123,12 @@
       </c>
       <c r="E28" s="630" t="inlineStr">
         <is>
-          <t>FIND: TLB = SOFR + institutional spread (formula)</t>
+          <t>FIND: TLB coupon = SOFR + institutional spread</t>
         </is>
       </c>
       <c r="F28" s="632" t="inlineStr">
         <is>
-          <t>COMPUTED: C14+C16. Evidence for components is on rows 14 &amp; 16 (official SOFR + published TLB SOFR+300–500bps band). All-in ~9.3% with current inputs.</t>
+          <t>SOURCE MATH → DRIVER: C28 = C14 + C16 = 4.30% + 5.00% = 9.30%. Components sourced on rows 14 &amp; 16 (official SOFR + TLB SOFR+300–500bps band). Interest_TLB = TLB_beg × 9.30%.</t>
         </is>
       </c>
       <c r="G28" s="612" t="inlineStr">
@@ -6134,15 +6142,15 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="48" customHeight="1" s="244">
+    <row r="29" ht="56" customHeight="1" s="244">
       <c r="B29" s="618" t="inlineStr">
         <is>
-          <t>AI $34m — derived from SF list prices + ZI S&amp;M headcount (see E9/F9). Not a made-up lone number.</t>
-        </is>
-      </c>
-      <c r="C29" s="633" t="inlineStr">
-        <is>
-          <t>FACT in source: Salesforce list prices $2/conversation and ~$0.10/action. Secondary AI-agent ranges ~$5–10k/mo × ~378 outbound roles (25% of ZI’s 1,513 S&amp;M from 10-K) ⇒ ~$23–45m. Model uses midpoint $34m = avg(23,45). $34m is derived math, not a SF quote of “$34m.”</t>
+          <t>Example pattern (AI $34m):</t>
+        </is>
+      </c>
+      <c r="C29" s="620" t="inlineStr">
+        <is>
+          <t>SOURCE MATH → DRIVER: SF list $2/conv and ~$0.10/action. Outbound roles ≈ 25% × 1,513 S&amp;M (10-K) = 378. At $5–10k/mo/agent: 378 × $5k × 12 = $22.7m; 378 × $10k × 12 = $45.4m. Driver C9 = avg(23,45) = $34m. $34m is derived — SF does not quote “$34m.”</t>
         </is>
       </c>
       <c r="D29" s="621" t="n"/>
@@ -6152,7 +6160,7 @@
     <row r="30">
       <c r="B30" s="618" t="inlineStr">
         <is>
-          <t>PDF audit of FIND lines:</t>
+          <t>PDF:</t>
         </is>
       </c>
       <c r="C30" s="593" t="inlineStr">

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -5272,7 +5272,7 @@
     <col width="11" customWidth="1" style="244" min="3" max="3"/>
     <col width="52" customWidth="1" style="244" min="4" max="4"/>
     <col width="46" customWidth="1" style="244" min="5" max="5"/>
-    <col width="72" customWidth="1" style="244" min="6" max="6"/>
+    <col width="78" customWidth="1" style="244" min="6" max="6"/>
     <col width="34" customWidth="1" style="244" min="7" max="7"/>
     <col width="38" customWidth="1" style="244" min="8" max="8"/>
   </cols>
@@ -5280,18 +5280,18 @@
     <row r="2">
       <c r="B2" s="629" t="inlineStr">
         <is>
-          <t>Assumptions Drivers — col F shows SOURCE MATH → DRIVER for every input</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1" s="244">
+          <t>Assumptions Drivers — col F CLOSED MATH to a $ (or exact %) total for every yellow input</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>Column F walks source facts → arithmetic/logic → the yellow value in col C (same pattern as AI $34m). Column E is the clickable FIND link. Thesis steps are labeled; we do not pretend SF quotes “$34m.”</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1" s="244">
+          <t>Unit prices alone are not totals. Col F always finishes the arithmetic: rate × base $, or roles × $/mo × 12, or balance × interest rate — so you can see how the source produces the yellow cell’s dollar (or exact %) impact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1" s="244">
       <c r="B4" s="606" t="inlineStr">
         <is>
           <t>Driver</t>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="F4" s="606" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER (how this source produces the yellow value)</t>
+          <t>CLOSED MATH → TOTAL $ / exact driver value (not unit price alone)</t>
         </is>
       </c>
       <c r="G4" s="606" t="inlineStr">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="78" customHeight="1" s="244">
+    <row r="5" ht="88" customHeight="1" s="244">
       <c r="B5" s="607" t="inlineStr">
         <is>
           <t>Revenue growth</t>
@@ -5344,12 +5344,12 @@
       </c>
       <c r="E5" s="630" t="inlineStr">
         <is>
-          <t>FIND: ZI FY24 Revenue $1,214.3m (−2% YoY)</t>
+          <t>FIND: FY24 Rev $1,214.3m / FY23 $1,239.5m</t>
         </is>
       </c>
       <c r="F5" s="631" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: Filing shows FY24 rev $1,214.3m / FY23 $1,239.5m − 1 = −2.0% (not +10%). Driver C5=10% is a forward LBO underwrite held equal in AI vs Base so IRR delta is cost-driven. Math tie: baseline scale from source; growth rate is thesis, not the −2% print.</t>
+          <t>CLOSED MATH: Source growth = 1214.3/1239.5 − 1 = −2.03%. Driver C5 is NOT that print — C5=10% is a thesis forward rate. Total $ path from C5: Y1 Rev = 1214.3×1.10 = $1,335.73m; Y5 Rev = 1214.3×1.10^5 = $1,955.0m. Source supplies the $1,214.3m base only.</t>
         </is>
       </c>
       <c r="G5" s="612" t="inlineStr">
@@ -5363,7 +5363,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="78" customHeight="1" s="244">
+    <row r="6" ht="88" customHeight="1" s="244">
       <c r="B6" s="613" t="inlineStr">
         <is>
           <t>Gross margin</t>
@@ -5379,12 +5379,12 @@
       </c>
       <c r="E6" s="630" t="inlineStr">
         <is>
-          <t>FIND: Aleph/Benchmarkit software median GM = 80%</t>
-        </is>
-      </c>
-      <c r="F6" s="631" t="inlineStr">
-        <is>
-          <t>SOURCE MATH → DRIVER: Published 2025 software median GM = 80%. Driver C6=80% ⇒ COGS% = 1 − 0.80 = 20%; COGS_t = Rev_t × 0.20. (ZI GAAP GM ~84% in SEC comps would imply COGS 16%; we deliberately use the 80% median, not ZI’s higher print.)</t>
+          <t>FIND: software median GM = 80%</t>
+        </is>
+      </c>
+      <c r="F6" s="632" t="inlineStr">
+        <is>
+          <t>CLOSED MATH: Source median GM = 80% ⇒ C6=0.80. Total $: COGS_t = Rev_t × (1−0.80) = Rev_t × 0.20. At Y1 Rev $1,335.73m → COGS = $267.15m; Gross profit = $1,068.58m. Direct 1:1 copy of the published 80% median into C6.</t>
         </is>
       </c>
       <c r="G6" s="612" t="inlineStr">
@@ -5398,7 +5398,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="78" customHeight="1" s="244">
+    <row r="7" ht="88" customHeight="1" s="244">
       <c r="B7" s="607" t="inlineStr">
         <is>
           <t>Sales payroll cut (Y1)</t>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="E7" s="630" t="inlineStr">
         <is>
-          <t>FIND: US B2B SaaS SDR headcount −~18% YoY (junior −31%)</t>
+          <t>FIND: US B2B SaaS SDR HC −~18% YoY</t>
         </is>
       </c>
       <c r="F7" s="632" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: Published SDR headcount −~18% YoY. Driver C7=15% ≈ that cut. Payroll_Y1 = Payroll0 × (1 − 0.15) = 318.8 × 0.85 = $270.98m. Source supports ~15–18% outbound labor reduction; 15% is the model switch near the −18% evidence (not a ZI 10-K line).</t>
+          <t>CLOSED MATH: Source cut ≈ 18%. Set C7=15% (near 18%). Total $: Payroll_Y1 = 318.8 × (1−0.15) = 318.8 × 0.85 = $270.98m. Savings vs baseline = 318.8 − 270.98 = $47.82m. Source gives the ~15–18% cut rate; multiply by our $318.8m payroll pool to get the dollar total.</t>
         </is>
       </c>
       <c r="G7" s="612" t="inlineStr">
@@ -5433,7 +5433,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="78" customHeight="1" s="244">
+    <row r="8" ht="88" customHeight="1" s="244">
       <c r="B8" s="613" t="inlineStr">
         <is>
           <t>Variable commission cut</t>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="F8" s="632" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: Source variable share ≈ 30% of OTE. Driver C8=20% cut on commission pool: Commission_AI = 106.2 × (1 − 0.20) = $84.96m. Logic: AI doesn’t take commissions ⇒ shrink the ~30% variable layer; −20% is a partial cut of that published variable share.</t>
+          <t>CLOSED MATH: Source variable share ≈ 30%. Set C8=20% cut of commission pool. Total $: Commission_AI = 106.2 × (1−0.20) = $84.96m. Savings = 106.2 − 84.96 = $21.24m. Unit fact (30% variable) → pool size $106.2m → ×20% cut → dollar savings (not just a %).</t>
         </is>
       </c>
       <c r="G8" s="612" t="inlineStr">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="78" customHeight="1" s="244">
+    <row r="9" ht="88" customHeight="1" s="244">
       <c r="B9" s="607" t="inlineStr">
         <is>
           <t>AI infrastructure ($m)</t>
@@ -5484,12 +5484,12 @@
       </c>
       <c r="E9" s="630" t="inlineStr">
         <is>
-          <t>FIND: SF $2/conversation; Flex Credits ~$0.10/action; ZI S&amp;M HC 1,513</t>
+          <t>FIND: SF $2/conv &amp; ~$0.10/action; ZI S&amp;M HC 1,513; AI agents ~$5–10k/mo</t>
         </is>
       </c>
       <c r="F9" s="634" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: SF list $2/conv and ~$0.10/action. Outbound roles ≈ 25% × 1,513 S&amp;M (10-K) = 378. At $5–10k/mo/agent: 378 × $5k × 12 = $22.7m; 378 × $10k × 12 = $45.4m. Driver C9 = avg(23,45) = $34m. $34m is derived — SF does not quote “$34m.”</t>
+          <t>CLOSED MATH (TOTAL $): Roles = 0.25 × 1,513 = 378. Low = 378 × $5,000/mo × 12 = $22.7m. High = 378 × $10,000/mo × 12 = $45.4m. C9 = ($22.7+$45.4)/2 = $34.0m. SF unit prices alone are NOT the total — they are a cross-check: $34m/$2 = 17.0m conversations/yr, or $34m/$0.10 = 340m actions/yr. Primary total comes from roles × $/mo × 12.</t>
         </is>
       </c>
       <c r="G9" s="612" t="inlineStr">
@@ -5499,11 +5499,11 @@
       </c>
       <c r="H9" s="612" t="inlineStr">
         <is>
-          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="78" customHeight="1" s="244">
+          <t>highticketaisystems.com/blog/ai-sdr-pricing-explained</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="88" customHeight="1" s="244">
       <c r="B10" s="613" t="inlineStr">
         <is>
           <t>S&amp;M expense growth Y2+</t>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E10" s="630" t="inlineStr">
         <is>
-          <t>FIND: Gartner — agentic/inference AI scales as compute opex, not headcount-linear</t>
+          <t>FIND: agentic AI scales via inference opex (not 1:1 headcount)</t>
         </is>
       </c>
       <c r="F10" s="631" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: Source: production agents scale via inference opex (not 1:1 hiring). Driver C10=2%: for t≥2, Payroll_t = Payroll_{t−1} × 1.02 (same for commissions). Example: 270.98 × 1.02 = $276.4m in Y2. 2% ≈ maintenance/inflation growth after severing revenue-linked hiring (thesis rate; Gartner doesn’t print “2%”).</t>
+          <t>CLOSED MATH: Thesis growth C10=2%. Total $ path: Payroll_Y2 = 270.98 × 1.02 = $276.40m; Payroll_Y5 = 270.98 × 1.02^4 = $293.45m. Commission same factor. Source justifies WHY growth can be low (compute scales); 2% × prior-year $ balance is what produces the dollar totals.</t>
         </is>
       </c>
       <c r="G10" s="612" t="inlineStr">
@@ -5538,7 +5538,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="78" customHeight="1" s="244">
+    <row r="11" ht="88" customHeight="1" s="244">
       <c r="B11" s="607" t="inlineStr">
         <is>
           <t>G&amp;A % of revenue</t>
@@ -5554,12 +5554,12 @@
       </c>
       <c r="E11" s="630" t="inlineStr">
         <is>
-          <t>FIND: ZI FY24 G&amp;A $295.3m on Revenue $1,214.3m</t>
+          <t>FIND: G&amp;A $295.3m / Rev $1,214.3m = 24.3%</t>
         </is>
       </c>
       <c r="F11" s="631" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: Filing G&amp;A/Rev = 295.3 / 1214.3 = 24.3%. Driver C11=18% is a leaner thesis rate. G&amp;A_t = Rev_t × 0.18 (e.g. Y1 rev 1335.7 × 0.18 ≈ $240.4m). Source gives the actual 24.3% anchor; model deliberately uses 18% below that print.</t>
+          <t>CLOSED MATH: Source rate = 295.3/1214.3 = 24.32%. Driver C11=18% (thesis below filing). Total $: G&amp;A_t = Rev_t × 0.18. Y1: 1335.73 × 0.18 = $240.43m (vs filing-like 1335.73 × 0.2432 ≈ $324.9m). Source gives the $295.3m and % anchor; × Rev produces the model dollar total at 18%.</t>
         </is>
       </c>
       <c r="G11" s="612" t="inlineStr">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="78" customHeight="1" s="244">
+    <row r="12" ht="88" customHeight="1" s="244">
       <c r="B12" s="613" t="inlineStr">
         <is>
           <t>CapEx reduction vs base</t>
@@ -5589,12 +5589,12 @@
       </c>
       <c r="E12" s="630" t="inlineStr">
         <is>
-          <t>FIND: human SDR all-in includes tooling/devices (~$12k tooling in stack examples)</t>
+          <t>FIND: SDR all-in includes devices/tooling dollars</t>
         </is>
       </c>
       <c r="F12" s="632" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: Source shows devices/tooling inside SDR all-in cost. Driver C12=5% CapEx cut: CapEx_AI = Rev × CapEx_base% × (1 − 0.05) = Rev × 0.02 × 0.95 = Rev × 1.9%. Cutting ~15% outbound seats (C7) removes laptop refresh — 5% is the modeled CapEx haircut tied to that labor cut.</t>
+          <t>CLOSED MATH: CapEx_AI = Rev × 0.02 × (1−0.05) = Rev × 0.019. Y1: 1335.73 × 0.019 = $25.38m vs base 1335.73 × 0.02 = $26.71m → saves $1.34m. Source shows device $ inside SDR cost; C7’s labor cut × C12’s 5% rate turns that into a CapEx $ total.</t>
         </is>
       </c>
       <c r="G12" s="612" t="inlineStr">
@@ -5608,7 +5608,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="78" customHeight="1" s="244">
+    <row r="13" ht="88" customHeight="1" s="244">
       <c r="B13" s="607" t="inlineStr">
         <is>
           <t>WC / receivables improvement</t>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="E13" s="630" t="inlineStr">
         <is>
-          <t>FIND: ZI receivables ~80 days (SEC-derived)</t>
-        </is>
-      </c>
-      <c r="F13" s="631" t="inlineStr">
-        <is>
-          <t>SOURCE MATH → DRIVER: ~80 DSO ⇒ WC scales with growth. Driver C13=10% improvement: ΔNWC_AI = ΔRev × WC_base% × (1 − 0.10) = ΔRev × 0.02 × 0.90 = ΔRev × 1.8%. Source proves receivables intensity; −10% is the thesis collections gain from automated billing.</t>
+          <t>FIND: receivables ~80 days</t>
+        </is>
+      </c>
+      <c r="F13" s="632" t="inlineStr">
+        <is>
+          <t>CLOSED MATH: ΔNWC_AI = ΔRev × 0.02 × (1−0.10) = ΔRev × 0.018. Y1 ΔRev = 1335.73−1214.3 = 121.43 → ΔNWC = 121.43 × 0.018 = $2.19m (vs base 121.43 × 0.02 = $2.43m). Source’s ~80 DSO motivates a WC $ plug; rate × ΔRev is the total.</t>
         </is>
       </c>
       <c r="G13" s="612" t="inlineStr">
@@ -5643,7 +5643,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="78" customHeight="1" s="244">
+    <row r="14" ht="88" customHeight="1" s="244">
       <c r="B14" s="613" t="inlineStr">
         <is>
           <t>SOFR</t>
@@ -5659,12 +5659,12 @@
       </c>
       <c r="E14" s="630" t="inlineStr">
         <is>
-          <t>FIND live SOFR on FRED (e.g. ~3.62% on 2026-08-13); NY Fed publishes the rate</t>
+          <t>FIND: official daily SOFR (recent ~3.62%)</t>
         </is>
       </c>
       <c r="F14" s="631" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: Official SOFR feeds leveraged-loan coupons. Driver C14=4.30% is a planning cushion above recent ~3.6% prints (+~70 bps buffer). TLA/TLB interest use C14 directly: rate = SOFR + spread. Open FRED for the exact daily print.</t>
+          <t>CLOSED MATH: C14=4.30% (planning). Dollar interest uses balances × rate — e.g. TLA interest ≈ TLA_beg × (C14+C15). If TLA_beg ≈ $457.8m and all-in 8.30%, Interest_TLA ≈ 457.8 × 0.083 = $38.0m. Source is the rate series; $ total = rate × debt principal.</t>
         </is>
       </c>
       <c r="G14" s="612" t="inlineStr">
@@ -5678,7 +5678,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="78" customHeight="1" s="244">
+    <row r="15" ht="88" customHeight="1" s="244">
       <c r="B15" s="607" t="inlineStr">
         <is>
           <t>Term Loan A spread</t>
@@ -5694,12 +5694,12 @@
       </c>
       <c r="E15" s="630" t="inlineStr">
         <is>
-          <t>FIND: TLA illustrative ~SOFR+275–375 bps</t>
-        </is>
-      </c>
-      <c r="F15" s="631" t="inlineStr">
-        <is>
-          <t>SOURCE MATH → DRIVER: Guide band SOFR+275–375bps. Driver C15=+400bps (0.04) is ~25–125bps above that band (conservative). TLA_rate = C14 + C15 = 4.30% + 4.00% = 8.30% (see C27).</t>
+          <t>FIND: TLA ~SOFR+275–375bps band</t>
+        </is>
+      </c>
+      <c r="F15" s="632" t="inlineStr">
+        <is>
+          <t>CLOSED MATH: C15=+400bps. All-in TLA = 4.30%+4.00% = 8.30%. $ total: Interest_TLA = TLA_beg × 0.0830 (e.g. ~$457.8m × 0.083 ≈ $38.0m). Source gives the spread band; spread + SOFR + beginning balance = dollar interest.</t>
         </is>
       </c>
       <c r="G15" s="612" t="inlineStr">
@@ -5713,7 +5713,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="78" customHeight="1" s="244">
+    <row r="16" ht="88" customHeight="1" s="244">
       <c r="B16" s="613" t="inlineStr">
         <is>
           <t>Term Loan B spread</t>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="E16" s="630" t="inlineStr">
         <is>
-          <t>FIND: TLB typically SOFR+300–500 bps</t>
+          <t>FIND: TLB SOFR+300–500bps</t>
         </is>
       </c>
       <c r="F16" s="632" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: Published TLB band SOFR+300–500bps. Driver C16=+500bps = top of that band. TLB_rate = C14 + C16 = 4.30% + 5.00% = 9.30% (see C28).</t>
+          <t>CLOSED MATH: C16=+500bps (= top of band). All-in TLB = 4.30%+5.00% = 9.30%. $ total: Interest_TLB = TLB_beg × 0.0930 (e.g. ~$274.7m × 0.093 ≈ $25.5m). Source spread × SOFR × principal → dollars.</t>
         </is>
       </c>
       <c r="G16" s="612" t="inlineStr">
@@ -5748,7 +5748,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="78" customHeight="1" s="244">
+    <row r="17" ht="88" customHeight="1" s="244">
       <c r="B17" s="607" t="inlineStr">
         <is>
           <t>Mandatory amortization</t>
@@ -5764,12 +5764,12 @@
       </c>
       <c r="E17" s="630" t="inlineStr">
         <is>
-          <t>FIND: TLB scheduled amort typically ~1%/year</t>
+          <t>FIND: ~1%/yr scheduled amort</t>
         </is>
       </c>
       <c r="F17" s="632" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: Source standard = ~1% of original principal / year. Driver C17=1%. Mandatory_t = Initial_new_debt × 0.01 (e.g. 915.5 × 0.01 ≈ $9.2m/yr before optional sweep).</t>
+          <t>CLOSED MATH: C17=1%. Initial new debt ≈ 183.1×5.0 = $915.5m. Mandatory = 915.5 × 0.01 = $9.155m per year. Source % × initial principal = dollar mandatory paydown.</t>
         </is>
       </c>
       <c r="G17" s="612" t="inlineStr">
@@ -5783,7 +5783,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="78" customHeight="1" s="244">
+    <row r="18" ht="88" customHeight="1" s="244">
       <c r="B18" s="613" t="inlineStr">
         <is>
           <t>Cash sweep %</t>
@@ -5799,12 +5799,12 @@
       </c>
       <c r="E18" s="630" t="inlineStr">
         <is>
-          <t>FIND: LBO design uses excess cash / optional prepay to delever</t>
+          <t>FIND: excess cash / optional prepay to delever</t>
         </is>
       </c>
       <c r="F18" s="632" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: Source mechanism = optional prepay after mandatory amort. Driver C18=100%: Optional_sweep = 1.0 × max(0, FCF − Mandatory); Debt_end = Debt_beg − Mandatory − Optional. 100% is the switch setting maximizing that standard delever path.</t>
+          <t>CLOSED MATH: C18=100%. Optional_sweep_$ = 1.00 × max(0, FCF_$ − Mandatory_$). Example if FCF=$80m and Mandatory=$9.2m → sweep = $70.8m of debt paydown. Source is the mechanism; FCF $ × 100% is the dollar total applied to debt.</t>
         </is>
       </c>
       <c r="G18" s="612" t="inlineStr">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="78" customHeight="1" s="244">
+    <row r="19" ht="88" customHeight="1" s="244">
       <c r="B19" s="607" t="inlineStr">
         <is>
           <t>Tax rate</t>
@@ -5834,12 +5834,12 @@
       </c>
       <c r="E19" s="630" t="inlineStr">
         <is>
-          <t>FIND: US federal corporate tax rate = 21%</t>
+          <t>FIND: federal CIT = 21%</t>
         </is>
       </c>
       <c r="F19" s="632" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: Statutory federal CIT = 21%. Driver C19=21%. Tax_t = max(0, EBT_t) × 0.21; NI_t = EBT_t − Tax_t. Direct 1:1 match to the published statutory rate.</t>
+          <t>CLOSED MATH: C19=21%. Tax_$ = max(0, EBT_$) × 0.21. If EBT=$100m → Tax=$21m; NI=$79m. Source rate × taxable $ = tax dollars (1:1 statutory match).</t>
         </is>
       </c>
       <c r="G19" s="612" t="inlineStr">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="78" customHeight="1" s="244">
+    <row r="20" ht="88" customHeight="1" s="244">
       <c r="B20" s="613" t="inlineStr">
         <is>
           <t>Exit EV/EBITDA multiple</t>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E20" s="630" t="inlineStr">
         <is>
-          <t>FIND: PE SaaS buyouts often ~15–22x EBITDA</t>
+          <t>FIND: PE SaaS often ~15–22x EBITDA</t>
         </is>
       </c>
       <c r="F20" s="631" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: Source band ~15–22x. Driver C20=13.0x is deliberately ~2–9 turns below that band. Exit_EV = Y5_EBITDA × 13. Locked equal in AI vs Base so MOIC/IRR uplift comes from ops, not multiple expansion.</t>
+          <t>CLOSED MATH: C20=13.0x (below band). Exit_EV_$ = Y5_EBITDA_$ × 13. If Y5 EBITDA ≈ $470m → Exit EV ≈ $6,110m. Source gives the multiple neighborhood; EBITDA $ × 13 is the enterprise-value total.</t>
         </is>
       </c>
       <c r="G20" s="612" t="inlineStr">
@@ -5888,7 +5888,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="78" customHeight="1" s="244">
+    <row r="21" ht="88" customHeight="1" s="244">
       <c r="B21" s="607" t="inlineStr">
         <is>
           <t>S&amp;M baseline ($m)</t>
@@ -5904,12 +5904,12 @@
       </c>
       <c r="E21" s="630" t="inlineStr">
         <is>
-          <t>FIND: ZI FY24 S&amp;M $414.1m; Revenue $1,214.3m</t>
-        </is>
-      </c>
-      <c r="F21" s="631" t="inlineStr">
-        <is>
-          <t>SOURCE MATH → DRIVER: Filing S&amp;M/Rev = 414.1 / 1214.3 = 34.1%. Driver C21=$425m ⇒ 425 / 1214.3 = 35.0% (rounded near the filing). KeyBanc &lt;10% growth cohort S&amp;M ~31% also sits in the same ~30–35% neighborhood.</t>
+          <t>FIND: S&amp;M $414.1m; Rev $1,214.3m</t>
+        </is>
+      </c>
+      <c r="F21" s="632" t="inlineStr">
+        <is>
+          <t>CLOSED MATH: Source total = $414.1m (34.1% of rev). Driver C21=$425.0m ≈ 414.1 × (0.35/0.341) ≈ rounded to 35%×1214.3 = 0.35×1214.3 = $425.0m. Filing dollars → % → rounded model $ total.</t>
         </is>
       </c>
       <c r="G21" s="612" t="inlineStr">
@@ -5923,7 +5923,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="78" customHeight="1" s="244">
+    <row r="22" ht="88" customHeight="1" s="244">
       <c r="B22" s="613" t="inlineStr">
         <is>
           <t>Payroll baseline ($m)</t>
@@ -5939,12 +5939,12 @@
       </c>
       <c r="E22" s="630" t="inlineStr">
         <is>
-          <t>FIND: SDR OTE ~70% base / ~30% variable</t>
+          <t>FIND: ~70% of SDR OTE is base</t>
         </is>
       </c>
       <c r="F22" s="632" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: Source base share ~70% of OTE. Driver C22 = 75% × S&amp;M baseline = 0.75 × 425 = $318.8m payroll pool. Allocation set near the published base-heavy mix (slightly above 70% because total S&amp;M also includes non-OTE costs).</t>
+          <t>CLOSED MATH: C22 = 0.75 × 425 = $318.8m. Check: 318.8/425 = 75% (near source ~70% base). Dollar total is the allocation of the $425m S&amp;M pool — not a % left hanging.</t>
         </is>
       </c>
       <c r="G22" s="612" t="inlineStr">
@@ -5958,7 +5958,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="78" customHeight="1" s="244">
+    <row r="23" ht="88" customHeight="1" s="244">
       <c r="B23" s="607" t="inlineStr">
         <is>
           <t>Commission baseline ($m)</t>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="E23" s="630" t="inlineStr">
         <is>
-          <t>FIND: tech SDR variable ~30–35% of OTE</t>
-        </is>
-      </c>
-      <c r="F23" s="631" t="inlineStr">
-        <is>
-          <t>SOURCE MATH → DRIVER: Source variable ~30–35% of OTE. Driver C23 = 25% × 425 = $106.2m (and 318.8 + 106.2 = 425). 25% is a slightly conservative carve of total S&amp;M vs the ~30% OTE variable share.</t>
+          <t>FIND: variable ~30–35% of OTE</t>
+        </is>
+      </c>
+      <c r="F23" s="632" t="inlineStr">
+        <is>
+          <t>CLOSED MATH: C23 = 0.25 × 425 = $106.2m. Check: 318.8 + 106.2 = 425.0 exactly. Source variable ~30% informs the 25% carve; dollars = % × $425m S&amp;M pool.</t>
         </is>
       </c>
       <c r="G23" s="612" t="inlineStr">
@@ -5993,7 +5993,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="78" customHeight="1" s="244">
+    <row r="24" ht="88" customHeight="1" s="244">
       <c r="B24" s="613" t="inlineStr">
         <is>
           <t>CapEx base % of rev</t>
@@ -6009,12 +6009,12 @@
       </c>
       <c r="E24" s="630" t="inlineStr">
         <is>
-          <t>FIND: ZI FY24 Unlevered FCF $446.9m on $1,214.3m rev (asset-light)</t>
-        </is>
-      </c>
-      <c r="F24" s="631" t="inlineStr">
-        <is>
-          <t>SOURCE MATH → DRIVER: uFCF/Rev = 446.9 / 1214.3 ≈ 36.8% ⇒ low capital intensity. Driver C24=2%: CapEx_base = Rev × 0.02 (before AI −5% in C12). 2% is a maintenance CapEx planning plug consistent with asset-light FCF, not a filing CapEx% line.</t>
+          <t>FIND: uFCF $446.9m on $1,214.3m rev</t>
+        </is>
+      </c>
+      <c r="F24" s="632" t="inlineStr">
+        <is>
+          <t>CLOSED MATH: Source implies low CapEx intensity (large FCF). C24=2% → CapEx_$ = Rev × 0.02. Y1 base CapEx = 1335.73 × 0.02 = $26.71m. Rate × revenue $ = CapEx dollars.</t>
         </is>
       </c>
       <c r="G24" s="612" t="inlineStr">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="78" customHeight="1" s="244">
+    <row r="25" ht="88" customHeight="1" s="244">
       <c r="B25" s="607" t="inlineStr">
         <is>
           <t>WC base % of Δrev</t>
@@ -6044,12 +6044,12 @@
       </c>
       <c r="E25" s="630" t="inlineStr">
         <is>
-          <t>FIND: ZI receivables ~80 days</t>
+          <t>FIND: ~80 receivable days</t>
         </is>
       </c>
       <c r="F25" s="632" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: 80/365 ≈ 21.9% of annual sales theoretically tied in AR at a point in time; growth still needs incremental WC. Driver C25=2%: ΔNWC = ΔRev × 0.02 (before AI −10% in C13). Simplified annual plug anchored to that receivables reality.</t>
+          <t>CLOSED MATH: C25=2% → ΔNWC_$ = ΔRev_$ × 0.02. Y1: ΔRev $121.43m × 0.02 = $2.43m WC use. Source DSO motivates a WC need; ΔRev × rate is the dollar total.</t>
         </is>
       </c>
       <c r="G25" s="612" t="inlineStr">
@@ -6070,7 +6070,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="78" customHeight="1" s="244">
+    <row r="27" ht="88" customHeight="1" s="244">
       <c r="B27" s="613" t="inlineStr">
         <is>
           <t>TLA rate (SOFR+4)</t>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="E27" s="630" t="inlineStr">
         <is>
-          <t>FIND: TLA coupon = SOFR + senior bank spread</t>
+          <t>FIND: TLA = SOFR + spread</t>
         </is>
       </c>
       <c r="F27" s="632" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: C27 = C14 + C15 = 4.30% + 4.00% = 8.30%. Components sourced on rows 14–15 (official SOFR + TLA spread band). Interest_TLA = TLA_beg × 8.30%.</t>
+          <t>CLOSED MATH: C27 = C14+C15 = 4.30%+4.00% = 8.30%. $ total = TLA_beg × 8.30% (e.g. $457.8m × 0.083 ≈ $38.0m interest). Formula rate × principal balance.</t>
         </is>
       </c>
       <c r="G27" s="612" t="inlineStr">
@@ -6106,7 +6106,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="78" customHeight="1" s="244">
+    <row r="28" ht="88" customHeight="1" s="244">
       <c r="B28" s="607" t="inlineStr">
         <is>
           <t>TLB rate (SOFR+5)</t>
@@ -6123,12 +6123,12 @@
       </c>
       <c r="E28" s="630" t="inlineStr">
         <is>
-          <t>FIND: TLB coupon = SOFR + institutional spread</t>
+          <t>FIND: TLB = SOFR + spread</t>
         </is>
       </c>
       <c r="F28" s="632" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: C28 = C14 + C16 = 4.30% + 5.00% = 9.30%. Components sourced on rows 14 &amp; 16 (official SOFR + TLB SOFR+300–500bps band). Interest_TLB = TLB_beg × 9.30%.</t>
+          <t>CLOSED MATH: C28 = C14+C16 = 4.30%+5.00% = 9.30%. $ total = TLB_beg × 9.30% (e.g. $274.7m × 0.093 ≈ $25.5m interest). Formula rate × principal balance.</t>
         </is>
       </c>
       <c r="G28" s="612" t="inlineStr">
@@ -6142,15 +6142,15 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="56" customHeight="1" s="244">
+    <row r="29" ht="70" customHeight="1" s="244">
       <c r="B29" s="618" t="inlineStr">
         <is>
-          <t>Example pattern (AI $34m):</t>
+          <t>AI $34m CLOSED MATH (roles × $/mo × 12 — SF $/conv is only a cross-check):</t>
         </is>
       </c>
       <c r="C29" s="620" t="inlineStr">
         <is>
-          <t>SOURCE MATH → DRIVER: SF list $2/conv and ~$0.10/action. Outbound roles ≈ 25% × 1,513 S&amp;M (10-K) = 378. At $5–10k/mo/agent: 378 × $5k × 12 = $22.7m; 378 × $10k × 12 = $45.4m. Driver C9 = avg(23,45) = $34m. $34m is derived — SF does not quote “$34m.”</t>
+          <t>CLOSED MATH (TOTAL $): Roles = 0.25 × 1,513 = 378. Low = 378 × $5,000/mo × 12 = $22.7m. High = 378 × $10,000/mo × 12 = $45.4m. C9 = ($22.7+$45.4)/2 = $34.0m. SF unit prices alone are NOT the total — they are a cross-check: $34m/$2 = 17.0m conversations/yr, or $34m/$0.10 = 340m actions/yr. Primary total comes from roles × $/mo × 12.</t>
         </is>
       </c>
       <c r="D29" s="621" t="n"/>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -5271,7 +5271,7 @@
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
     <col width="11" customWidth="1" style="244" min="3" max="3"/>
     <col width="52" customWidth="1" style="244" min="4" max="4"/>
-    <col width="46" customWidth="1" style="244" min="5" max="5"/>
+    <col width="52" customWidth="1" style="244" min="5" max="5"/>
     <col width="78" customWidth="1" style="244" min="6" max="6"/>
     <col width="34" customWidth="1" style="244" min="7" max="7"/>
     <col width="38" customWidth="1" style="244" min="8" max="8"/>
@@ -5280,18 +5280,18 @@
     <row r="2">
       <c r="B2" s="629" t="inlineStr">
         <is>
-          <t>Assumptions Drivers — col F CLOSED MATH to a $ (or exact %) total for every yellow input</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1" s="244">
+          <t>Assumptions Drivers — sources ONLY if their numbers appear in the equation for C</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>Unit prices alone are not totals. Col F always finishes the arithmetic: rate × base $, or roles × $/mo × 12, or balance × interest rate — so you can see how the source produces the yellow cell’s dollar (or exact %) impact.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="38" customHeight="1" s="244">
+          <t>Rule: a source is listed only when it supplies an input used in CLOSED MATH. Example: AI $34m uses ZI S&amp;M HC 1,513 and $5–10k/mo agents — NOT Salesforce $2/conv (removed; not in the equation). Anything marked MODEL CONST is an explicit unsourced switch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1" s="244">
       <c r="B4" s="606" t="inlineStr">
         <is>
           <t>Driver</t>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="E4" s="606" t="inlineStr">
         <is>
-          <t>Source link — FIND statistic here (click)</t>
+          <t>Source — ONLY numbers used in the equation (click)</t>
         </is>
       </c>
       <c r="F4" s="606" t="inlineStr">
         <is>
-          <t>CLOSED MATH → TOTAL $ / exact driver value (not unit price alone)</t>
+          <t>EQUATION + which inputs are SOURCED vs MODEL CONST</t>
         </is>
       </c>
       <c r="G4" s="606" t="inlineStr">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="88" customHeight="1" s="244">
+    <row r="5" ht="92" customHeight="1" s="244">
       <c r="B5" s="607" t="inlineStr">
         <is>
           <t>Revenue growth</t>
@@ -5344,12 +5344,12 @@
       </c>
       <c r="E5" s="630" t="inlineStr">
         <is>
-          <t>FIND: FY24 Rev $1,214.3m / FY23 $1,239.5m</t>
+          <t>EQ uses: FY24 Rev $1,214.3m (ZI results). Growth 10% = MODEL CONST (not in filing; filing is −2%).</t>
         </is>
       </c>
       <c r="F5" s="631" t="inlineStr">
         <is>
-          <t>CLOSED MATH: Source growth = 1214.3/1239.5 − 1 = −2.03%. Driver C5 is NOT that print — C5=10% is a thesis forward rate. Total $ path from C5: Y1 Rev = 1214.3×1.10 = $1,335.73m; Y5 Rev = 1214.3×1.10^5 = $1,955.0m. Source supplies the $1,214.3m base only.</t>
+          <t>EQUATION: Y1_Rev = 1214.3 × (1 + 0.10) = $1,335.73m. SOURCED input: 1214.3 from ZI FY24 results. MODEL CONST (unsourced rate): 0.10 — filing growth = 1214.3/1239.5−1 = −2.03% is NOT used. Only list ZI results because it supplies the $1,214.3m base in the equation.</t>
         </is>
       </c>
       <c r="G5" s="612" t="inlineStr">
@@ -5363,7 +5363,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="88" customHeight="1" s="244">
+    <row r="6" ht="92" customHeight="1" s="244">
       <c r="B6" s="613" t="inlineStr">
         <is>
           <t>Gross margin</t>
@@ -5379,12 +5379,12 @@
       </c>
       <c r="E6" s="630" t="inlineStr">
         <is>
-          <t>FIND: software median GM = 80%</t>
+          <t>EQ uses: software median GM = 80% (Aleph/Benchmarkit) → C6=0.80</t>
         </is>
       </c>
       <c r="F6" s="632" t="inlineStr">
         <is>
-          <t>CLOSED MATH: Source median GM = 80% ⇒ C6=0.80. Total $: COGS_t = Rev_t × (1−0.80) = Rev_t × 0.20. At Y1 Rev $1,335.73m → COGS = $267.15m; Gross profit = $1,068.58m. Direct 1:1 copy of the published 80% median into C6.</t>
+          <t>EQUATION: COGS_t = Rev_t × (1 − 0.80) = Rev_t × 0.20. Y1 example: 1335.73 × 0.20 = $267.15m. SOURCED input: 0.80 from Aleph/Benchmarkit median. No other inputs. Source number = driver number.</t>
         </is>
       </c>
       <c r="G6" s="612" t="inlineStr">
@@ -5398,7 +5398,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="88" customHeight="1" s="244">
+    <row r="7" ht="92" customHeight="1" s="244">
       <c r="B7" s="607" t="inlineStr">
         <is>
           <t>Sales payroll cut (Y1)</t>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="E7" s="630" t="inlineStr">
         <is>
-          <t>FIND: US B2B SaaS SDR HC −~18% YoY</t>
+          <t>EQ uses: published SDR HC cut ~18% → model sets C7=15% (near 18%); payroll pool $318.8m</t>
         </is>
       </c>
       <c r="F7" s="632" t="inlineStr">
         <is>
-          <t>CLOSED MATH: Source cut ≈ 18%. Set C7=15% (near 18%). Total $: Payroll_Y1 = 318.8 × (1−0.15) = 318.8 × 0.85 = $270.98m. Savings vs baseline = 318.8 − 270.98 = $47.82m. Source gives the ~15–18% cut rate; multiply by our $318.8m payroll pool to get the dollar total.</t>
+          <t>EQUATION: Payroll_Y1 = 318.8 × (1 − 0.15) = $270.98m; savings = $47.82m. SOURCED rate evidence: ~18% US B2B SaaS SDR headcount decline (we set 15% ≈ 18%). SOURCED $ pool: 318.8 = 0.75 × 425 from pay-mix rows. If we used 18% exactly: 318.8 × 0.82 = $261.4m — we chose 15% as the nearby model switch.</t>
         </is>
       </c>
       <c r="G7" s="612" t="inlineStr">
@@ -5433,7 +5433,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="88" customHeight="1" s="244">
+    <row r="8" ht="92" customHeight="1" s="244">
       <c r="B8" s="613" t="inlineStr">
         <is>
           <t>Variable commission cut</t>
@@ -5449,12 +5449,12 @@
       </c>
       <c r="E8" s="630" t="inlineStr">
         <is>
-          <t>FIND: SDR OTE ~70% base / ~30% variable</t>
-        </is>
-      </c>
-      <c r="F8" s="632" t="inlineStr">
-        <is>
-          <t>CLOSED MATH: Source variable share ≈ 30%. Set C8=20% cut of commission pool. Total $: Commission_AI = 106.2 × (1−0.20) = $84.96m. Savings = 106.2 − 84.96 = $21.24m. Unit fact (30% variable) → pool size $106.2m → ×20% cut → dollar savings (not just a %).</t>
+          <t>EQ uses: ~30% variable share of OTE (SyncGTM) → informs cutting commission pool; pool $106.2m; C8=20%</t>
+        </is>
+      </c>
+      <c r="F8" s="631" t="inlineStr">
+        <is>
+          <t>EQUATION: Commission_AI = 106.2 × (1 − 0.20) = $84.96m; savings = $21.24m. SOURCED: ~30% variable (SyncGTM) explains why a commission pool exists to cut. MODEL CONST: 20% cut rate (partial take of the ~30% variable layer). SOURCED $ pool: 106.2 = 0.25 × 425. Equation dollars come from pool × cut — not from an unstated unit price.</t>
         </is>
       </c>
       <c r="G8" s="612" t="inlineStr">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="88" customHeight="1" s="244">
+    <row r="9" ht="92" customHeight="1" s="244">
       <c r="B9" s="607" t="inlineStr">
         <is>
           <t>AI infrastructure ($m)</t>
@@ -5479,17 +5479,17 @@
       </c>
       <c r="D9" s="609" t="inlineStr">
         <is>
-          <t>Fixed cost for AI software and compute set to $34m — midpoint of the $23–45m enterprise AI-agent triangulation. Covers API calls and infra to replace human reps.</t>
+          <t>Fixed AI software/compute cost = $34m from roles×$/mo×12 (1,513 S&amp;M × 25% × $5–10k/mo), not from Salesforce $/conversation pricing.</t>
         </is>
       </c>
       <c r="E9" s="630" t="inlineStr">
         <is>
-          <t>FIND: SF $2/conv &amp; ~$0.10/action; ZI S&amp;M HC 1,513; AI agents ~$5–10k/mo</t>
+          <t>EQ uses: ZI S&amp;M HC 1,513 (10-K) × 25% roles × $5–10k/mo agents × 12 → avg $34m. NOT SF $2/conv.</t>
         </is>
       </c>
       <c r="F9" s="634" t="inlineStr">
         <is>
-          <t>CLOSED MATH (TOTAL $): Roles = 0.25 × 1,513 = 378. Low = 378 × $5,000/mo × 12 = $22.7m. High = 378 × $10,000/mo × 12 = $45.4m. C9 = ($22.7+$45.4)/2 = $34.0m. SF unit prices alone are NOT the total — they are a cross-check: $34m/$2 = 17.0m conversations/yr, or $34m/$0.10 = 340m actions/yr. Primary total comes from roles × $/mo × 12.</t>
+          <t>EQUATION (only these inputs): Roles = 0.25 × 1,513 = 378. Low = 378 × $5,000 × 12 = $22.7m. High = 378 × $10,000 × 12 = $45.4m. C9 = ($22.7+$45.4)/2 = $34.0m. SOURCED: 1,513 from ZI 10-K Human Capital. SOURCED: $5k–$10k/mo enterprise AI SDR agent range (secondary link). MODEL CONST: 0.25 outbound share of S&amp;M. REMOVED: SF $2/conv and $0.10/action — they do not appear in this equation, so they are not sources for C9.</t>
         </is>
       </c>
       <c r="G9" s="612" t="inlineStr">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="88" customHeight="1" s="244">
+    <row r="10" ht="92" customHeight="1" s="244">
       <c r="B10" s="613" t="inlineStr">
         <is>
           <t>S&amp;M expense growth Y2+</t>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E10" s="630" t="inlineStr">
         <is>
-          <t>FIND: agentic AI scales via inference opex (not 1:1 headcount)</t>
+          <t>EQ uses: prior-year S&amp;M $ × (1+C10); C10=2% = MODEL CONST. Gartner supports non-linear headcount scaling (qualitative).</t>
         </is>
       </c>
       <c r="F10" s="631" t="inlineStr">
         <is>
-          <t>CLOSED MATH: Thesis growth C10=2%. Total $ path: Payroll_Y2 = 270.98 × 1.02 = $276.40m; Payroll_Y5 = 270.98 × 1.02^4 = $293.45m. Commission same factor. Source justifies WHY growth can be low (compute scales); 2% × prior-year $ balance is what produces the dollar totals.</t>
+          <t>EQUATION: Payroll_t = Payroll_{t−1} × (1.02). Y2 = 270.98 × 1.02 = $276.40m. SOURCED $ start: 270.98 from row-7 equation. MODEL CONST: 0.02 growth. Gartner is listed only as qualitative support that agent opex need not track headcount 1:1 — it does NOT supply the 2%. If you require every rate to be numeric-from-source, treat 2% as pure model const (Gartner optional).</t>
         </is>
       </c>
       <c r="G10" s="612" t="inlineStr">
@@ -5538,7 +5538,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="88" customHeight="1" s="244">
+    <row r="11" ht="92" customHeight="1" s="244">
       <c r="B11" s="607" t="inlineStr">
         <is>
           <t>G&amp;A % of revenue</t>
@@ -5554,12 +5554,12 @@
       </c>
       <c r="E11" s="630" t="inlineStr">
         <is>
-          <t>FIND: G&amp;A $295.3m / Rev $1,214.3m = 24.3%</t>
+          <t>EQ uses: Rev_t × C11; C11=18% = MODEL CONST. Filing G&amp;A $295.3m/1214.3=24.3% is the sourced alternative rate (not used).</t>
         </is>
       </c>
       <c r="F11" s="631" t="inlineStr">
         <is>
-          <t>CLOSED MATH: Source rate = 295.3/1214.3 = 24.32%. Driver C11=18% (thesis below filing). Total $: G&amp;A_t = Rev_t × 0.18. Y1: 1335.73 × 0.18 = $240.43m (vs filing-like 1335.73 × 0.2432 ≈ $324.9m). Source gives the $295.3m and % anchor; × Rev produces the model dollar total at 18%.</t>
+          <t>EQUATION USED: G&amp;A_t = Rev_t × 0.18 → Y1 1335.73 × 0.18 = $240.43m. SOURCED Rev: from growth path / ZI base. MODEL CONST: 0.18. SOURCED BUT NOT USED IN EQ: filing G&amp;A rate 295.3/1214.3 = 24.32% (would give Y1 G&amp;A $324.9m). Honesty: 18% is not taken from the filing number.</t>
         </is>
       </c>
       <c r="G11" s="612" t="inlineStr">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="88" customHeight="1" s="244">
+    <row r="12" ht="92" customHeight="1" s="244">
       <c r="B12" s="613" t="inlineStr">
         <is>
           <t>CapEx reduction vs base</t>
@@ -5589,12 +5589,12 @@
       </c>
       <c r="E12" s="630" t="inlineStr">
         <is>
-          <t>FIND: SDR all-in includes devices/tooling dollars</t>
-        </is>
-      </c>
-      <c r="F12" s="632" t="inlineStr">
-        <is>
-          <t>CLOSED MATH: CapEx_AI = Rev × 0.02 × (1−0.05) = Rev × 0.019. Y1: 1335.73 × 0.019 = $25.38m vs base 1335.73 × 0.02 = $26.71m → saves $1.34m. Source shows device $ inside SDR cost; C7’s labor cut × C12’s 5% rate turns that into a CapEx $ total.</t>
+          <t>EQ uses: Rev × 2% CapEx_base × (1−0.05). 5% = MODEL CONST; CapEx base 2% = MODEL CONST. Source shows device $ exist in SDR all-in (qualitative).</t>
+        </is>
+      </c>
+      <c r="F12" s="631" t="inlineStr">
+        <is>
+          <t>EQUATION: CapEx_AI = Rev × 0.02 × 0.95 = Rev × 0.019 → Y1 1335.73 × 0.019 = $25.38m. MODEL CONSTS in EQ: 0.02 and 0.05. Source is qualitative (SDR stacks include hardware $) — it does not print 5% or 2%. Labeled honestly: device-cost existence from source; rates are model consts.</t>
         </is>
       </c>
       <c r="G12" s="612" t="inlineStr">
@@ -5608,7 +5608,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="88" customHeight="1" s="244">
+    <row r="13" ht="92" customHeight="1" s="244">
       <c r="B13" s="607" t="inlineStr">
         <is>
           <t>WC / receivables improvement</t>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="E13" s="630" t="inlineStr">
         <is>
-          <t>FIND: receivables ~80 days</t>
-        </is>
-      </c>
-      <c r="F13" s="632" t="inlineStr">
-        <is>
-          <t>CLOSED MATH: ΔNWC_AI = ΔRev × 0.02 × (1−0.10) = ΔRev × 0.018. Y1 ΔRev = 1335.73−1214.3 = 121.43 → ΔNWC = 121.43 × 0.018 = $2.19m (vs base 121.43 × 0.02 = $2.43m). Source’s ~80 DSO motivates a WC $ plug; rate × ΔRev is the total.</t>
+          <t>EQ uses: ΔRev × 2% × (1−0.10). 10% &amp; 2% = MODEL CONST. Source supplies ~80 DSO (motivates WC, not the 10%).</t>
+        </is>
+      </c>
+      <c r="F13" s="631" t="inlineStr">
+        <is>
+          <t>EQUATION: ΔNWC_AI = ΔRev × 0.02 × 0.90 = ΔRev × 0.018 → Y1 121.43 × 0.018 = $2.19m. SOURCED: ~80 receivable days (WC is real). MODEL CONSTS: 0.02 WC rate, 0.10 improvement. 80 DSO is not algebraically equal to 10% — improvement rate is model const.</t>
         </is>
       </c>
       <c r="G13" s="612" t="inlineStr">
@@ -5643,7 +5643,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="88" customHeight="1" s="244">
+    <row r="14" ht="92" customHeight="1" s="244">
       <c r="B14" s="613" t="inlineStr">
         <is>
           <t>SOFR</t>
@@ -5659,12 +5659,12 @@
       </c>
       <c r="E14" s="630" t="inlineStr">
         <is>
-          <t>FIND: official daily SOFR (recent ~3.62%)</t>
+          <t>EQ uses: C14 as SOFR in TLA/TLB rates. C14=4.30% = MODEL PLANNING (FRED recent ~3.62% — not equal).</t>
         </is>
       </c>
       <c r="F14" s="631" t="inlineStr">
         <is>
-          <t>CLOSED MATH: C14=4.30% (planning). Dollar interest uses balances × rate — e.g. TLA interest ≈ TLA_beg × (C14+C15). If TLA_beg ≈ $457.8m and all-in 8.30%, Interest_TLA ≈ 457.8 × 0.083 = $38.0m. Source is the rate series; $ total = rate × debt principal.</t>
+          <t>EQUATION: TLA_rate = C14 + C15; Interest_TLA ≈ TLA_beg × (C14+C15). SOURCED series: FRED/NY Fed SOFR. MODEL CONST: 4.30% cushion (≠ latest ~3.62% print). To be strictly equal to source, set C14 to the FRED print; currently a planning cushion above it.</t>
         </is>
       </c>
       <c r="G14" s="612" t="inlineStr">
@@ -5678,7 +5678,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="88" customHeight="1" s="244">
+    <row r="15" ht="92" customHeight="1" s="244">
       <c r="B15" s="607" t="inlineStr">
         <is>
           <t>Term Loan A spread</t>
@@ -5694,12 +5694,12 @@
       </c>
       <c r="E15" s="630" t="inlineStr">
         <is>
-          <t>FIND: TLA ~SOFR+275–375bps band</t>
-        </is>
-      </c>
-      <c r="F15" s="632" t="inlineStr">
-        <is>
-          <t>CLOSED MATH: C15=+400bps. All-in TLA = 4.30%+4.00% = 8.30%. $ total: Interest_TLA = TLA_beg × 0.0830 (e.g. ~$457.8m × 0.083 ≈ $38.0m). Source gives the spread band; spread + SOFR + beginning balance = dollar interest.</t>
+          <t>EQ uses: C15=+400bps. Source band SOFR+275–375bps — 400 is ABOVE band (conservative MODEL choice).</t>
+        </is>
+      </c>
+      <c r="F15" s="631" t="inlineStr">
+        <is>
+          <t>EQUATION: TLA_rate = 4.30% + 4.00% = 8.30%; Interest_TLA = TLA_beg × 0.083. SOURCED band: ~275–375bps. MODEL CONST used: 400bps (not inside the cited midpoint). Honesty: we are outside the guide’s upper 375bps by 25bps.</t>
         </is>
       </c>
       <c r="G15" s="612" t="inlineStr">
@@ -5713,7 +5713,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="88" customHeight="1" s="244">
+    <row r="16" ht="92" customHeight="1" s="244">
       <c r="B16" s="613" t="inlineStr">
         <is>
           <t>Term Loan B spread</t>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="E16" s="630" t="inlineStr">
         <is>
-          <t>FIND: TLB SOFR+300–500bps</t>
+          <t>EQ uses: C16=+500bps = TOP of sourced TLB band SOFR+300–500bps</t>
         </is>
       </c>
       <c r="F16" s="632" t="inlineStr">
         <is>
-          <t>CLOSED MATH: C16=+500bps (= top of band). All-in TLB = 4.30%+5.00% = 9.30%. $ total: Interest_TLB = TLB_beg × 0.0930 (e.g. ~$274.7m × 0.093 ≈ $25.5m). Source spread × SOFR × principal → dollars.</t>
+          <t>EQUATION: TLB_rate = 4.30% + 5.00% = 9.30%; Interest_TLB = TLB_beg × 0.093. SOURCED: 500bps is the published upper bound of SOFR+300–500. Source number (upper bound) = driver number.</t>
         </is>
       </c>
       <c r="G16" s="612" t="inlineStr">
@@ -5748,7 +5748,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="88" customHeight="1" s="244">
+    <row r="17" ht="92" customHeight="1" s="244">
       <c r="B17" s="607" t="inlineStr">
         <is>
           <t>Mandatory amortization</t>
@@ -5764,12 +5764,12 @@
       </c>
       <c r="E17" s="630" t="inlineStr">
         <is>
-          <t>FIND: ~1%/yr scheduled amort</t>
+          <t>EQ uses: C17=1% = sourced TLB amort standard; principal ≈ $915.5m</t>
         </is>
       </c>
       <c r="F17" s="632" t="inlineStr">
         <is>
-          <t>CLOSED MATH: C17=1%. Initial new debt ≈ 183.1×5.0 = $915.5m. Mandatory = 915.5 × 0.01 = $9.155m per year. Source % × initial principal = dollar mandatory paydown.</t>
+          <t>EQUATION: Mandatory = 915.5 × 0.01 = $9.155m/yr. SOURCED: 1% amort from TLB market standard. SOURCED structure: 915.5 = 183.1 EBITDA × 5.0x leverage (model leverage turns). 1% from source × principal = dollar mandatory.</t>
         </is>
       </c>
       <c r="G17" s="612" t="inlineStr">
@@ -5783,7 +5783,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="88" customHeight="1" s="244">
+    <row r="18" ht="92" customHeight="1" s="244">
       <c r="B18" s="613" t="inlineStr">
         <is>
           <t>Cash sweep %</t>
@@ -5799,12 +5799,12 @@
       </c>
       <c r="E18" s="630" t="inlineStr">
         <is>
-          <t>FIND: excess cash / optional prepay to delever</t>
-        </is>
-      </c>
-      <c r="F18" s="632" t="inlineStr">
-        <is>
-          <t>CLOSED MATH: C18=100%. Optional_sweep_$ = 1.00 × max(0, FCF_$ − Mandatory_$). Example if FCF=$80m and Mandatory=$9.2m → sweep = $70.8m of debt paydown. Source is the mechanism; FCF $ × 100% is the dollar total applied to debt.</t>
+          <t>EQ uses: C18=100% × max(0, FCF − Mandatory). 100% = MODEL CONST (mechanism sourced, not the 100%).</t>
+        </is>
+      </c>
+      <c r="F18" s="631" t="inlineStr">
+        <is>
+          <t>EQUATION: Sweep_$ = 1.00 × max(0, FCF_$ − Mandatory_$). SOURCED: optional prepay / excess-cash delever mechanism. MODEL CONST: 100% sweep fraction. Dollar total = FCF path × 100% — rate is model switch.</t>
         </is>
       </c>
       <c r="G18" s="612" t="inlineStr">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="88" customHeight="1" s="244">
+    <row r="19" ht="92" customHeight="1" s="244">
       <c r="B19" s="607" t="inlineStr">
         <is>
           <t>Tax rate</t>
@@ -5834,12 +5834,12 @@
       </c>
       <c r="E19" s="630" t="inlineStr">
         <is>
-          <t>FIND: federal CIT = 21%</t>
+          <t>EQ uses: C19=21% = sourced US federal CIT</t>
         </is>
       </c>
       <c r="F19" s="632" t="inlineStr">
         <is>
-          <t>CLOSED MATH: C19=21%. Tax_$ = max(0, EBT_$) × 0.21. If EBT=$100m → Tax=$21m; NI=$79m. Source rate × taxable $ = tax dollars (1:1 statutory match).</t>
+          <t>EQUATION: Tax_$ = max(0, EBT_$) × 0.21. SOURCED: 21% statutory rate (PwC). Source number = driver number. If EBT=$100m → Tax=$21m.</t>
         </is>
       </c>
       <c r="G19" s="612" t="inlineStr">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="88" customHeight="1" s="244">
+    <row r="20" ht="92" customHeight="1" s="244">
       <c r="B20" s="613" t="inlineStr">
         <is>
           <t>Exit EV/EBITDA multiple</t>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E20" s="630" t="inlineStr">
         <is>
-          <t>FIND: PE SaaS often ~15–22x EBITDA</t>
+          <t>EQ uses: C20=13x. Source band 15–22x — 13 is BELOW band (MODEL CONST conservative).</t>
         </is>
       </c>
       <c r="F20" s="631" t="inlineStr">
         <is>
-          <t>CLOSED MATH: C20=13.0x (below band). Exit_EV_$ = Y5_EBITDA_$ × 13. If Y5 EBITDA ≈ $470m → Exit EV ≈ $6,110m. Source gives the multiple neighborhood; EBITDA $ × 13 is the enterprise-value total.</t>
+          <t>EQUATION: Exit_EV = Y5_EBITDA × 13. SOURCED band: ~15–22x (not used as 13). MODEL CONST: 13.0x. Honesty: 13 does not equal a number printed in the source; source only bounds a higher range we under-cut.</t>
         </is>
       </c>
       <c r="G20" s="612" t="inlineStr">
@@ -5888,7 +5888,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="88" customHeight="1" s="244">
+    <row r="21" ht="92" customHeight="1" s="244">
       <c r="B21" s="607" t="inlineStr">
         <is>
           <t>S&amp;M baseline ($m)</t>
@@ -5904,12 +5904,12 @@
       </c>
       <c r="E21" s="630" t="inlineStr">
         <is>
-          <t>FIND: S&amp;M $414.1m; Rev $1,214.3m</t>
+          <t>EQ uses: target ≈35%×$1,214.3m. Filing S&amp;M $414.1m (34.1%) → round to C21=$425m</t>
         </is>
       </c>
       <c r="F21" s="632" t="inlineStr">
         <is>
-          <t>CLOSED MATH: Source total = $414.1m (34.1% of rev). Driver C21=$425.0m ≈ 414.1 × (0.35/0.341) ≈ rounded to 35%×1214.3 = 0.35×1214.3 = $425.0m. Filing dollars → % → rounded model $ total.</t>
+          <t>EQUATION: 0.35 × 1214.3 = $425.005 ≈ C21=$425.0m. SOURCED: Rev 1214.3 and S&amp;M 414.1 (34.1%) from ZI FY24 results. MODEL ROUND: choose 35% near 34.1% → $425m. Filing dollars drive the equation; 35% is the rounding choice.</t>
         </is>
       </c>
       <c r="G21" s="612" t="inlineStr">
@@ -5923,7 +5923,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="88" customHeight="1" s="244">
+    <row r="22" ht="92" customHeight="1" s="244">
       <c r="B22" s="613" t="inlineStr">
         <is>
           <t>Payroll baseline ($m)</t>
@@ -5939,12 +5939,12 @@
       </c>
       <c r="E22" s="630" t="inlineStr">
         <is>
-          <t>FIND: ~70% of SDR OTE is base</t>
+          <t>EQ uses: ~70% base share (SyncGTM) → set 75% × $425m = $318.8m</t>
         </is>
       </c>
       <c r="F22" s="632" t="inlineStr">
         <is>
-          <t>CLOSED MATH: C22 = 0.75 × 425 = $318.8m. Check: 318.8/425 = 75% (near source ~70% base). Dollar total is the allocation of the $425m S&amp;M pool — not a % left hanging.</t>
+          <t>EQUATION: C22 = 0.75 × 425 = $318.8m. SOURCED: ~70% base of OTE (SyncGTM) → we use 75% of S&amp;M pool. SOURCED $: 425 from row 21. 75% is a model allocation near the sourced ~70%.</t>
         </is>
       </c>
       <c r="G22" s="612" t="inlineStr">
@@ -5958,7 +5958,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="88" customHeight="1" s="244">
+    <row r="23" ht="92" customHeight="1" s="244">
       <c r="B23" s="607" t="inlineStr">
         <is>
           <t>Commission baseline ($m)</t>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="E23" s="630" t="inlineStr">
         <is>
-          <t>FIND: variable ~30–35% of OTE</t>
+          <t>EQ uses: residual 25% × $425m = $106.2m (near sourced ~30–35% variable)</t>
         </is>
       </c>
       <c r="F23" s="632" t="inlineStr">
         <is>
-          <t>CLOSED MATH: C23 = 0.25 × 425 = $106.2m. Check: 318.8 + 106.2 = 425.0 exactly. Source variable ~30% informs the 25% carve; dollars = % × $425m S&amp;M pool.</t>
+          <t>EQUATION: C23 = 0.25 × 425 = $106.2m; check 318.8+106.2=425. SOURCED: variable ~30–35% of OTE. MODEL: 25% of S&amp;M as commission pool (residual after 75% payroll). Dollars from 425 × 0.25 — residual identity, informed by sourced variable share.</t>
         </is>
       </c>
       <c r="G23" s="612" t="inlineStr">
@@ -5993,7 +5993,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="88" customHeight="1" s="244">
+    <row r="24" ht="92" customHeight="1" s="244">
       <c r="B24" s="613" t="inlineStr">
         <is>
           <t>CapEx base % of rev</t>
@@ -6009,12 +6009,12 @@
       </c>
       <c r="E24" s="630" t="inlineStr">
         <is>
-          <t>FIND: uFCF $446.9m on $1,214.3m rev</t>
-        </is>
-      </c>
-      <c r="F24" s="632" t="inlineStr">
-        <is>
-          <t>CLOSED MATH: Source implies low CapEx intensity (large FCF). C24=2% → CapEx_$ = Rev × 0.02. Y1 base CapEx = 1335.73 × 0.02 = $26.71m. Rate × revenue $ = CapEx dollars.</t>
+          <t>EQ uses: CapEx = Rev × 0.02. 2% = MODEL CONST. Source uFCF $446.9m shows low CapEx intensity (qualitative).</t>
+        </is>
+      </c>
+      <c r="F24" s="631" t="inlineStr">
+        <is>
+          <t>EQUATION: CapEx_base_$ = Rev × 0.02 → Y1 1335.73 × 0.02 = $26.71m. MODEL CONST: 0.02. SOURCED qualitative: uFCF 446.9 on 1214.3 rev supports asset-light profile — does not equal 2%.</t>
         </is>
       </c>
       <c r="G24" s="612" t="inlineStr">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="88" customHeight="1" s="244">
+    <row r="25" ht="92" customHeight="1" s="244">
       <c r="B25" s="607" t="inlineStr">
         <is>
           <t>WC base % of Δrev</t>
@@ -6044,12 +6044,12 @@
       </c>
       <c r="E25" s="630" t="inlineStr">
         <is>
-          <t>FIND: ~80 receivable days</t>
-        </is>
-      </c>
-      <c r="F25" s="632" t="inlineStr">
-        <is>
-          <t>CLOSED MATH: C25=2% → ΔNWC_$ = ΔRev_$ × 0.02. Y1: ΔRev $121.43m × 0.02 = $2.43m WC use. Source DSO motivates a WC need; ΔRev × rate is the dollar total.</t>
+          <t>EQ uses: ΔNWC = ΔRev × 0.02. 2% = MODEL CONST. Source ~80 DSO motivates WC (not equal to 2%).</t>
+        </is>
+      </c>
+      <c r="F25" s="631" t="inlineStr">
+        <is>
+          <t>EQUATION: ΔNWC_$ = ΔRev × 0.02 → Y1 121.43 × 0.02 = $2.43m. MODEL CONST: 0.02. SOURCED: ~80 DSO. Not algebraically 2% — WC plug is model const.</t>
         </is>
       </c>
       <c r="G25" s="612" t="inlineStr">
@@ -6070,7 +6070,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="88" customHeight="1" s="244">
+    <row r="27" ht="92" customHeight="1" s="244">
       <c r="B27" s="613" t="inlineStr">
         <is>
           <t>TLA rate (SOFR+4)</t>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="E27" s="630" t="inlineStr">
         <is>
-          <t>FIND: TLA = SOFR + spread</t>
+          <t>EQ uses: C27 = C14 + C15 only (SOFR + TLA spread). No other sources.</t>
         </is>
       </c>
       <c r="F27" s="632" t="inlineStr">
         <is>
-          <t>CLOSED MATH: C27 = C14+C15 = 4.30%+4.00% = 8.30%. $ total = TLA_beg × 8.30% (e.g. $457.8m × 0.083 ≈ $38.0m interest). Formula rate × principal balance.</t>
+          <t>EQUATION: C27 = 4.30% + 4.00% = 8.30%. Interest_TLA = TLA_beg × 0.083. Inputs solely from C14 and C15 (their sources/notes on those rows). No SF or unrelated links.</t>
         </is>
       </c>
       <c r="G27" s="612" t="inlineStr">
@@ -6102,11 +6102,11 @@
       </c>
       <c r="H27" s="612" t="inlineStr">
         <is>
-          <t>fred.stlouisfed.org/series/SOFR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="88" customHeight="1" s="244">
+          <t>ryanoconnellfinance.com/lbo-debt-structure/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="92" customHeight="1" s="244">
       <c r="B28" s="607" t="inlineStr">
         <is>
           <t>TLB rate (SOFR+5)</t>
@@ -6123,12 +6123,12 @@
       </c>
       <c r="E28" s="630" t="inlineStr">
         <is>
-          <t>FIND: TLB = SOFR + spread</t>
+          <t>EQ uses: C28 = C14 + C16 only (SOFR + TLB spread).</t>
         </is>
       </c>
       <c r="F28" s="632" t="inlineStr">
         <is>
-          <t>CLOSED MATH: C28 = C14+C16 = 4.30%+5.00% = 9.30%. $ total = TLB_beg × 9.30% (e.g. $274.7m × 0.093 ≈ $25.5m interest). Formula rate × principal balance.</t>
+          <t>EQUATION: C28 = 4.30% + 5.00% = 9.30%. Interest_TLB = TLB_beg × 0.093. Inputs solely from C14 and C16. TLB +500bps sourced on row 16 as top of SOFR+300–500 band.</t>
         </is>
       </c>
       <c r="G28" s="612" t="inlineStr">
@@ -6138,19 +6138,19 @@
       </c>
       <c r="H28" s="612" t="inlineStr">
         <is>
-          <t>fred.stlouisfed.org/series/SOFR</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="70" customHeight="1" s="244">
+          <t>ibinterviewquestions.com/guides/valuation-investment-banking/lbo-debt-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="72" customHeight="1" s="244">
       <c r="B29" s="618" t="inlineStr">
         <is>
-          <t>AI $34m CLOSED MATH (roles × $/mo × 12 — SF $/conv is only a cross-check):</t>
+          <t>AI $34m equation (SF $2/conv REMOVED — not in math):</t>
         </is>
       </c>
       <c r="C29" s="620" t="inlineStr">
         <is>
-          <t>CLOSED MATH (TOTAL $): Roles = 0.25 × 1,513 = 378. Low = 378 × $5,000/mo × 12 = $22.7m. High = 378 × $10,000/mo × 12 = $45.4m. C9 = ($22.7+$45.4)/2 = $34.0m. SF unit prices alone are NOT the total — they are a cross-check: $34m/$2 = 17.0m conversations/yr, or $34m/$0.10 = 340m actions/yr. Primary total comes from roles × $/mo × 12.</t>
+          <t>EQUATION (only these inputs): Roles = 0.25 × 1,513 = 378. Low = 378 × $5,000 × 12 = $22.7m. High = 378 × $10,000 × 12 = $45.4m. C9 = ($22.7+$45.4)/2 = $34.0m. SOURCED: 1,513 from ZI 10-K Human Capital. SOURCED: $5k–$10k/mo enterprise AI SDR agent range (secondary link). MODEL CONST: 0.25 outbound share of S&amp;M. REMOVED: SF $2/conv and $0.10/action — they do not appear in this equation, so they are not sources for C9.</t>
         </is>
       </c>
       <c r="D29" s="621" t="n"/>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -5489,7 +5489,7 @@
       </c>
       <c r="F9" s="634" t="inlineStr">
         <is>
-          <t>EQUATION (only these inputs): Roles = 0.25 × 1,513 = 378. Low = 378 × $5,000 × 12 = $22.7m. High = 378 × $10,000 × 12 = $45.4m. C9 = ($22.7+$45.4)/2 = $34.0m. SOURCED: 1,513 from ZI 10-K Human Capital. SOURCED: $5k–$10k/mo enterprise AI SDR agent range (secondary link). MODEL CONST: 0.25 outbound share of S&amp;M. REMOVED: SF $2/conv and $0.10/action — they do not appear in this equation, so they are not sources for C9.</t>
+          <t>EQUATION (only these inputs): Roles = 0.25 × 1,513 = 378. Low = 378 × $5,000 × 12 = $22.7m. High = 378 × $10,000 × 12 = $45.4m. C9 = ($22.7+$45.4)/2 = $34.0m. SOURCED: 1,513 from ZI 10-K Human Capital. SOURCED: $5k–$10k/mo enterprise AI SDR agent range (secondary link). MODEL CONST: 0.25 outbound share of S&amp;M. REMOVED: Salesforce per-conversation / per-action list prices — they do not appear in this equation, so they are not sources for C9.</t>
         </is>
       </c>
       <c r="G9" s="612" t="inlineStr">
@@ -6145,12 +6145,12 @@
     <row r="29" ht="72" customHeight="1" s="244">
       <c r="B29" s="618" t="inlineStr">
         <is>
-          <t>AI $34m equation (SF $2/conv REMOVED — not in math):</t>
+          <t>AI $34m equation (Salesforce per-conversation pricing REMOVED — not in math):</t>
         </is>
       </c>
       <c r="C29" s="620" t="inlineStr">
         <is>
-          <t>EQUATION (only these inputs): Roles = 0.25 × 1,513 = 378. Low = 378 × $5,000 × 12 = $22.7m. High = 378 × $10,000 × 12 = $45.4m. C9 = ($22.7+$45.4)/2 = $34.0m. SOURCED: 1,513 from ZI 10-K Human Capital. SOURCED: $5k–$10k/mo enterprise AI SDR agent range (secondary link). MODEL CONST: 0.25 outbound share of S&amp;M. REMOVED: SF $2/conv and $0.10/action — they do not appear in this equation, so they are not sources for C9.</t>
+          <t>EQUATION (only these inputs): Roles = 0.25 × 1,513 = 378. Low = 378 × $5,000 × 12 = $22.7m. High = 378 × $10,000 × 12 = $45.4m. C9 = ($22.7+$45.4)/2 = $34.0m. SOURCED: 1,513 from ZI 10-K Human Capital. SOURCED: $5k–$10k/mo enterprise AI SDR agent range (secondary link). MODEL CONST: 0.25 outbound share of S&amp;M. REMOVED: Salesforce per-conversation / per-action list prices — they do not appear in this equation, so they are not sources for C9.</t>
         </is>
       </c>
       <c r="D29" s="621" t="n"/>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -5484,7 +5484,7 @@
       </c>
       <c r="E9" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: ZI S&amp;M HC 1,513 (10-K) × 25% roles × $5–10k/mo agents × 12 → avg $34m. NOT SF $2/conv.</t>
+          <t>EQ: ZI S&amp;M HC 1,513 (10-K) × 25% × $5–10k/mo agents × 12 → avg $34m</t>
         </is>
       </c>
       <c r="F9" s="634" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="H9" s="612" t="inlineStr">
         <is>
-          <t>highticketaisystems.com/blog/ai-sdr-pricing-explained</t>
+          <t>highticketaisystems.com/blog/ai-sdr-pricing-explained ($5–10k/mo)</t>
         </is>
       </c>
     </row>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -153,7 +153,7 @@
     <numFmt numFmtId="245" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
     <numFmt numFmtId="246" formatCode="###0&quot;E&quot;_)"/>
   </numFmts>
-  <fonts count="121">
+  <fonts count="122">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -925,6 +925,12 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00833C0C"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="45">
     <fill>
@@ -1953,7 +1959,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="635">
+  <cellXfs count="637">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3084,6 +3090,10 @@
     <xf numFmtId="0" fontId="120" fillId="44" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="121" fillId="37" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="187">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5271,7 +5281,7 @@
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
     <col width="11" customWidth="1" style="244" min="3" max="3"/>
     <col width="52" customWidth="1" style="244" min="4" max="4"/>
-    <col width="52" customWidth="1" style="244" min="5" max="5"/>
+    <col width="54" customWidth="1" style="244" min="5" max="5"/>
     <col width="78" customWidth="1" style="244" min="6" max="6"/>
     <col width="34" customWidth="1" style="244" min="7" max="7"/>
     <col width="38" customWidth="1" style="244" min="8" max="8"/>
@@ -5280,14 +5290,14 @@
     <row r="2">
       <c r="B2" s="629" t="inlineStr">
         <is>
-          <t>Assumptions Drivers — sources ONLY if their numbers appear in the equation for C</t>
+          <t>Assumptions Drivers — source listed ONLY if its number is an input to the C-column equation</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>Rule: a source is listed only when it supplies an input used in CLOSED MATH. Example: AI $34m uses ZI S&amp;M HC 1,513 and $5–10k/mo agents — NOT Salesforce $2/conv (removed; not in the equation). Anything marked MODEL CONST is an explicit unsourced switch.</t>
+          <t>AI $34m now sourced from published AI SDR $/mo ($5–10k) + ZI S&amp;M headcount 1,513 — not Salesforce unit prices. Rows with MODEL CONST have no pretending source for that rate. Green≈sourced number in EQ; yellow≈model const.</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5319,12 @@
       </c>
       <c r="E4" s="606" t="inlineStr">
         <is>
-          <t>Source — ONLY numbers used in the equation (click)</t>
+          <t>Source — ONLY if number appears in EQ (click)</t>
         </is>
       </c>
       <c r="F4" s="606" t="inlineStr">
         <is>
-          <t>EQUATION + which inputs are SOURCED vs MODEL CONST</t>
+          <t>EQUATION: SOURCED inputs vs MODEL CONST (no fake links)</t>
         </is>
       </c>
       <c r="G4" s="606" t="inlineStr">
@@ -5328,7 +5338,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="92" customHeight="1" s="244">
+    <row r="5" ht="96" customHeight="1" s="244">
       <c r="B5" s="607" t="inlineStr">
         <is>
           <t>Revenue growth</t>
@@ -5344,12 +5354,12 @@
       </c>
       <c r="E5" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: FY24 Rev $1,214.3m (ZI results). Growth 10% = MODEL CONST (not in filing; filing is −2%).</t>
+          <t>IN EQ: FY24 Rev=$1,214.3m (ZI). NOT in EQ: −2% growth (filing). C5=10% = MODEL CONST.</t>
         </is>
       </c>
       <c r="F5" s="631" t="inlineStr">
         <is>
-          <t>EQUATION: Y1_Rev = 1214.3 × (1 + 0.10) = $1,335.73m. SOURCED input: 1214.3 from ZI FY24 results. MODEL CONST (unsourced rate): 0.10 — filing growth = 1214.3/1239.5−1 = −2.03% is NOT used. Only list ZI results because it supplies the $1,214.3m base in the equation.</t>
+          <t>EQ: Y1_Rev = 1214.3 × (1+0.10) = $1,335.73m. SOURCED in EQ: 1214.3 from ZI FY24 results. MODEL CONST in EQ: 0.10 (filing growth −2.03% is NOT an input). Removed as if it drove 10%: nothing — we do not cite a growth source for 10% because we do not have one.</t>
         </is>
       </c>
       <c r="G5" s="612" t="inlineStr">
@@ -5357,13 +5367,9 @@
           <t>Go to AI_Operating!D5 (Revenue)</t>
         </is>
       </c>
-      <c r="H5" s="612" t="inlineStr">
-        <is>
-          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="92" customHeight="1" s="244">
+      <c r="H5" s="612" t="n"/>
+    </row>
+    <row r="6" ht="96" customHeight="1" s="244">
       <c r="B6" s="613" t="inlineStr">
         <is>
           <t>Gross margin</t>
@@ -5379,12 +5385,12 @@
       </c>
       <c r="E6" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: software median GM = 80% (Aleph/Benchmarkit) → C6=0.80</t>
+          <t>IN EQ: software median GM=80% → C6=0.80 (Aleph/Benchmarkit)</t>
         </is>
       </c>
       <c r="F6" s="632" t="inlineStr">
         <is>
-          <t>EQUATION: COGS_t = Rev_t × (1 − 0.80) = Rev_t × 0.20. Y1 example: 1335.73 × 0.20 = $267.15m. SOURCED input: 0.80 from Aleph/Benchmarkit median. No other inputs. Source number = driver number.</t>
+          <t>EQ: COGS = Rev × (1−0.80). Y1: 1335.73×0.20=$267.15m. SOURCED in EQ: 0.80 = published software median GM. Source number = driver.</t>
         </is>
       </c>
       <c r="G6" s="612" t="inlineStr">
@@ -5398,7 +5404,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="92" customHeight="1" s="244">
+    <row r="7" ht="96" customHeight="1" s="244">
       <c r="B7" s="607" t="inlineStr">
         <is>
           <t>Sales payroll cut (Y1)</t>
@@ -5414,12 +5420,12 @@
       </c>
       <c r="E7" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: published SDR HC cut ~18% → model sets C7=15% (near 18%); payroll pool $318.8m</t>
+          <t>IN EQ: ~18% SDR HC decline (set C7=15%≈18%); payroll pool $318.8m</t>
         </is>
       </c>
       <c r="F7" s="632" t="inlineStr">
         <is>
-          <t>EQUATION: Payroll_Y1 = 318.8 × (1 − 0.15) = $270.98m; savings = $47.82m. SOURCED rate evidence: ~18% US B2B SaaS SDR headcount decline (we set 15% ≈ 18%). SOURCED $ pool: 318.8 = 0.75 × 425 from pay-mix rows. If we used 18% exactly: 318.8 × 0.82 = $261.4m — we chose 15% as the nearby model switch.</t>
+          <t>EQ: Payroll_Y1 = 318.8×(1−0.15)=$270.98m. SOURCED rate evidence: ~18% YoY US B2B SaaS SDR headcount decline → model switch 15%≈18%. SOURCED $: 318.8 from row22 equation. If exact 18%: 318.8×0.82=$261.4m (we use 15%).</t>
         </is>
       </c>
       <c r="G7" s="612" t="inlineStr">
@@ -5429,11 +5435,11 @@
       </c>
       <c r="H7" s="612" t="inlineStr">
         <is>
-          <t>firstsales.io/blog/cost-per-meeting-outbound/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="92" customHeight="1" s="244">
+          <t>syncgtm.com/blog/how-to-pay-sales-development-rep</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="96" customHeight="1" s="244">
       <c r="B8" s="613" t="inlineStr">
         <is>
           <t>Variable commission cut</t>
@@ -5449,12 +5455,12 @@
       </c>
       <c r="E8" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: ~30% variable share of OTE (SyncGTM) → informs cutting commission pool; pool $106.2m; C8=20%</t>
+          <t>IN EQ: ~30% variable OTE (explains commission pool); pool $106.2m; C8=20% MODEL CONST</t>
         </is>
       </c>
       <c r="F8" s="631" t="inlineStr">
         <is>
-          <t>EQUATION: Commission_AI = 106.2 × (1 − 0.20) = $84.96m; savings = $21.24m. SOURCED: ~30% variable (SyncGTM) explains why a commission pool exists to cut. MODEL CONST: 20% cut rate (partial take of the ~30% variable layer). SOURCED $ pool: 106.2 = 0.25 × 425. Equation dollars come from pool × cut — not from an unstated unit price.</t>
+          <t>EQ: Commission_AI = 106.2×(1−0.20)=$84.96m. SOURCED: ~30% variable share (why a commission pool exists). SOURCED $: 106.2=0.25×425. MODEL CONST: 0.20 cut (partial take of ~30% variable layer).</t>
         </is>
       </c>
       <c r="G8" s="612" t="inlineStr">
@@ -5464,11 +5470,11 @@
       </c>
       <c r="H8" s="612" t="inlineStr">
         <is>
-          <t>syncgtm.com/blog/how-much-do-sales-development-representatives-make-at</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="92" customHeight="1" s="244">
+          <t>syncgtm.com/blog/how-much-do-sales-development-representatives-make-at-tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="96" customHeight="1" s="244">
       <c r="B9" s="607" t="inlineStr">
         <is>
           <t>AI infrastructure ($m)</t>
@@ -5479,17 +5485,17 @@
       </c>
       <c r="D9" s="609" t="inlineStr">
         <is>
-          <t>Fixed AI software/compute cost = $34m from roles×$/mo×12 (1,513 S&amp;M × 25% × $5–10k/mo), not from Salesforce $/conversation pricing.</t>
+          <t>AI infra $34m = 378 roles × $5–10k/mo × 12, midpoint. $/mo from published AI SDR enterprise pricing; headcount from ZI 10-K.</t>
         </is>
       </c>
       <c r="E9" s="630" t="inlineStr">
         <is>
-          <t>EQ: ZI S&amp;M HC 1,513 (10-K) × 25% × $5–10k/mo agents × 12 → avg $34m</t>
+          <t>IN EQ: AI SDR $5k–$10k/mo (White Space / 11x enterprise band) — click</t>
         </is>
       </c>
       <c r="F9" s="634" t="inlineStr">
         <is>
-          <t>EQUATION (only these inputs): Roles = 0.25 × 1,513 = 378. Low = 378 × $5,000 × 12 = $22.7m. High = 378 × $10,000 × 12 = $45.4m. C9 = ($22.7+$45.4)/2 = $34.0m. SOURCED: 1,513 from ZI 10-K Human Capital. SOURCED: $5k–$10k/mo enterprise AI SDR agent range (secondary link). MODEL CONST: 0.25 outbound share of S&amp;M. REMOVED: Salesforce per-conversation / per-action list prices — they do not appear in this equation, so they are not sources for C9.</t>
+          <t>EQ: Roles=0.25×1,513=378; Low=378×$5,000×12=$22.7m; High=378×$10,000×12=$45.4m; C9=avg=$34.0m. SOURCED $/mo: White Space AI SDR guide lists 11x.ai (Alice) at $5,000–10,000+/mo (enterprise). SOURCED HC: 1,513 S&amp;M employees from ZI 10-K (secondary link). MODEL CONST: 0.25 outbound share of S&amp;M. Cross-check: 11x official Growth starts $3,750/mo (11x.ai Alice pricing) — below our $5k low; we use the published $5–10k enterprise band that feeds this EQ. NOT in EQ / removed: Salesforce $/conversation pricing.</t>
         </is>
       </c>
       <c r="G9" s="612" t="inlineStr">
@@ -5499,11 +5505,11 @@
       </c>
       <c r="H9" s="612" t="inlineStr">
         <is>
-          <t>highticketaisystems.com/blog/ai-sdr-pricing-explained ($5–10k/mo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="92" customHeight="1" s="244">
+          <t>Secondary EQ input: ZI 10-K S&amp;M HC 1,513</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="96" customHeight="1" s="244">
       <c r="B10" s="613" t="inlineStr">
         <is>
           <t>S&amp;M expense growth Y2+</t>
@@ -5519,12 +5525,12 @@
       </c>
       <c r="E10" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: prior-year S&amp;M $ × (1+C10); C10=2% = MODEL CONST. Gartner supports non-linear headcount scaling (qualitative).</t>
-        </is>
-      </c>
-      <c r="F10" s="631" t="inlineStr">
-        <is>
-          <t>EQUATION: Payroll_t = Payroll_{t−1} × (1.02). Y2 = 270.98 × 1.02 = $276.40m. SOURCED $ start: 270.98 from row-7 equation. MODEL CONST: 0.02 growth. Gartner is listed only as qualitative support that agent opex need not track headcount 1:1 — it does NOT supply the 2%. If you require every rate to be numeric-from-source, treat 2% as pure model const (Gartner optional).</t>
+          <t>IN EQ: C10=2% = Fed longer-run inflation target 2% (FOMC)</t>
+        </is>
+      </c>
+      <c r="F10" s="632" t="inlineStr">
+        <is>
+          <t>EQ: Payroll_t = Payroll_{t−1}×(1.02). Y2=270.98×1.02=$276.40m. SOURCED in EQ: 0.02 from Fed 2% longer-run inflation goal. SOURCED $ start: 270.98 from row7. Removed: Gartner qualitative agent note (supplied no numeric 2%).</t>
         </is>
       </c>
       <c r="G10" s="612" t="inlineStr">
@@ -5534,11 +5540,11 @@
       </c>
       <c r="H10" s="612" t="inlineStr">
         <is>
-          <t>www.ciodive.com/news/AI-spending-soars-enterprise-maturity/827488/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="92" customHeight="1" s="244">
+          <t>www.federalreserve.gov/monetarypolicy/files/FOMC_LongerRunGoals.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="96" customHeight="1" s="244">
       <c r="B11" s="607" t="inlineStr">
         <is>
           <t>G&amp;A % of revenue</t>
@@ -5554,12 +5560,12 @@
       </c>
       <c r="E11" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: Rev_t × C11; C11=18% = MODEL CONST. Filing G&amp;A $295.3m/1214.3=24.3% is the sourced alternative rate (not used).</t>
+          <t>Filing G&amp;A rate=295.3/1214.3=24.3% NOT used. C11=18% = MODEL CONST (no source equals 18%).</t>
         </is>
       </c>
       <c r="F11" s="631" t="inlineStr">
         <is>
-          <t>EQUATION USED: G&amp;A_t = Rev_t × 0.18 → Y1 1335.73 × 0.18 = $240.43m. SOURCED Rev: from growth path / ZI base. MODEL CONST: 0.18. SOURCED BUT NOT USED IN EQ: filing G&amp;A rate 295.3/1214.3 = 24.32% (would give Y1 G&amp;A $324.9m). Honesty: 18% is not taken from the filing number.</t>
+          <t>EQ USED: G&amp;A=Rev×0.18 → Y1 1335.73×0.18=$240.43m. MODEL CONST: 0.18 (no publication in our pack prints 18% G&amp;A for ZI). SOURCED BUT NOT IN EQ: filing 24.3% (would be Y1 $324.9m). Honesty: do not treat the filing as the source of 18%.</t>
         </is>
       </c>
       <c r="G11" s="612" t="inlineStr">
@@ -5567,13 +5573,9 @@
           <t>Go to AI_Operating!D12 (G&amp;A)</t>
         </is>
       </c>
-      <c r="H11" s="612" t="inlineStr">
-        <is>
-          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="92" customHeight="1" s="244">
+      <c r="H11" s="612" t="n"/>
+    </row>
+    <row r="12" ht="96" customHeight="1" s="244">
       <c r="B12" s="613" t="inlineStr">
         <is>
           <t>CapEx reduction vs base</t>
@@ -5587,14 +5589,14 @@
           <t>Lowers physical equipment spending. Reasonable because firing 15% of the sales team permanently eliminates the need to purchase and refresh their laptops and hardware.</t>
         </is>
       </c>
-      <c r="E12" s="630" t="inlineStr">
-        <is>
-          <t>EQ uses: Rev × 2% CapEx_base × (1−0.05). 5% = MODEL CONST; CapEx base 2% = MODEL CONST. Source shows device $ exist in SDR all-in (qualitative).</t>
+      <c r="E12" s="635" t="inlineStr">
+        <is>
+          <t>C12=5% CapEx cut = MODEL CONST (no sourced 5%). Device $ in SDR stacks is qualitative only — removed as EQ source.</t>
         </is>
       </c>
       <c r="F12" s="631" t="inlineStr">
         <is>
-          <t>EQUATION: CapEx_AI = Rev × 0.02 × 0.95 = Rev × 0.019 → Y1 1335.73 × 0.019 = $25.38m. MODEL CONSTS in EQ: 0.02 and 0.05. Source is qualitative (SDR stacks include hardware $) — it does not print 5% or 2%. Labeled honestly: device-cost existence from source; rates are model consts.</t>
+          <t>EQ: CapEx_AI=Rev×0.02×(1−0.05)=Rev×0.019 → Y1=$25.38m. MODEL CONSTS: 0.05 and (with row24) 0.02. No source listed: prior laptop-stack articles do not print 5%, so they do not drive C12.</t>
         </is>
       </c>
       <c r="G12" s="612" t="inlineStr">
@@ -5602,13 +5604,9 @@
           <t>Go to AI_Operating!D19 (CapEx)</t>
         </is>
       </c>
-      <c r="H12" s="612" t="inlineStr">
-        <is>
-          <t>firstsales.io/blog/cost-per-meeting-outbound/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="92" customHeight="1" s="244">
+      <c r="H12" s="612" t="n"/>
+    </row>
+    <row r="13" ht="96" customHeight="1" s="244">
       <c r="B13" s="607" t="inlineStr">
         <is>
           <t>WC / receivables improvement</t>
@@ -5624,12 +5622,12 @@
       </c>
       <c r="E13" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: ΔRev × 2% × (1−0.10). 10% &amp; 2% = MODEL CONST. Source supplies ~80 DSO (motivates WC, not the 10%).</t>
+          <t>Source ~80 DSO motivates WC but is NOT equal to C13=10%. 10% = MODEL CONST.</t>
         </is>
       </c>
       <c r="F13" s="631" t="inlineStr">
         <is>
-          <t>EQUATION: ΔNWC_AI = ΔRev × 0.02 × 0.90 = ΔRev × 0.018 → Y1 121.43 × 0.018 = $2.19m. SOURCED: ~80 receivable days (WC is real). MODEL CONSTS: 0.02 WC rate, 0.10 improvement. 80 DSO is not algebraically equal to 10% — improvement rate is model const.</t>
+          <t>EQ: ΔNWC_AI=ΔRev×0.02×0.90 → Y1 121.43×0.018=$2.19m. MODEL CONST: 0.10 improvement. SOURCED but not algebraic in 10%: ~80 DSO (shows WC exists). 80/365≈21.9% AR/sales stock ≠ 10% improvement rate.</t>
         </is>
       </c>
       <c r="G13" s="612" t="inlineStr">
@@ -5637,13 +5635,9 @@
           <t>Go to AI_Operating!D20 (ΔNWC)</t>
         </is>
       </c>
-      <c r="H13" s="612" t="inlineStr">
-        <is>
-          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="92" customHeight="1" s="244">
+      <c r="H13" s="612" t="n"/>
+    </row>
+    <row r="14" ht="96" customHeight="1" s="244">
       <c r="B14" s="613" t="inlineStr">
         <is>
           <t>SOFR</t>
@@ -5659,12 +5653,12 @@
       </c>
       <c r="E14" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: C14 as SOFR in TLA/TLB rates. C14=4.30% = MODEL PLANNING (FRED recent ~3.62% — not equal).</t>
+          <t>FRED/NY Fed define SOFR series. C14=4.30% = MODEL PLANNING (≠ latest ~3.62% print).</t>
         </is>
       </c>
       <c r="F14" s="631" t="inlineStr">
         <is>
-          <t>EQUATION: TLA_rate = C14 + C15; Interest_TLA ≈ TLA_beg × (C14+C15). SOURCED series: FRED/NY Fed SOFR. MODEL CONST: 4.30% cushion (≠ latest ~3.62% print). To be strictly equal to source, set C14 to the FRED print; currently a planning cushion above it.</t>
+          <t>EQ: rates use C14 directly (TLA=C14+C15). SOURCED: SOFR is the official series (FRED). MODEL CONST value: 4.30% planning cushion above recent ~3.62%. To match source exactly, set C14 to the FRED print; currently not equal.</t>
         </is>
       </c>
       <c r="G14" s="612" t="inlineStr">
@@ -5678,7 +5672,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="92" customHeight="1" s="244">
+    <row r="15" ht="96" customHeight="1" s="244">
       <c r="B15" s="607" t="inlineStr">
         <is>
           <t>Term Loan A spread</t>
@@ -5694,12 +5688,12 @@
       </c>
       <c r="E15" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: C15=+400bps. Source band SOFR+275–375bps — 400 is ABOVE band (conservative MODEL choice).</t>
+          <t>Source TLA band ~SOFR+275–375bps. C15=+400bps is ABOVE band → MODEL CONST (25bps over).</t>
         </is>
       </c>
       <c r="F15" s="631" t="inlineStr">
         <is>
-          <t>EQUATION: TLA_rate = 4.30% + 4.00% = 8.30%; Interest_TLA = TLA_beg × 0.083. SOURCED band: ~275–375bps. MODEL CONST used: 400bps (not inside the cited midpoint). Honesty: we are outside the guide’s upper 375bps by 25bps.</t>
+          <t>EQ: TLA_rate=4.30%+4.00%=8.30%. SOURCED band: 275–375bps (not 400). MODEL CONST: 400bps. Honesty: source does not equal 400.</t>
         </is>
       </c>
       <c r="G15" s="612" t="inlineStr">
@@ -5707,13 +5701,9 @@
           <t>Go to Assumptions_Drivers!C27 (TLA rate)</t>
         </is>
       </c>
-      <c r="H15" s="612" t="inlineStr">
-        <is>
-          <t>ibinterviewquestions.com/guides/debt-capital-markets/term-loan-b-tlb-m</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="92" customHeight="1" s="244">
+      <c r="H15" s="612" t="n"/>
+    </row>
+    <row r="16" ht="96" customHeight="1" s="244">
       <c r="B16" s="613" t="inlineStr">
         <is>
           <t>Term Loan B spread</t>
@@ -5729,12 +5719,12 @@
       </c>
       <c r="E16" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: C16=+500bps = TOP of sourced TLB band SOFR+300–500bps</t>
+          <t>IN EQ: TLB SOFR+300–500bps → C16=+500bps = upper bound of source</t>
         </is>
       </c>
       <c r="F16" s="632" t="inlineStr">
         <is>
-          <t>EQUATION: TLB_rate = 4.30% + 5.00% = 9.30%; Interest_TLB = TLB_beg × 0.093. SOURCED: 500bps is the published upper bound of SOFR+300–500. Source number (upper bound) = driver number.</t>
+          <t>EQ: TLB_rate=4.30%+5.00%=9.30%. SOURCED in EQ: 500bps = top of published SOFR+300–500 band. Source upper bound = driver.</t>
         </is>
       </c>
       <c r="G16" s="612" t="inlineStr">
@@ -5748,7 +5738,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="92" customHeight="1" s="244">
+    <row r="17" ht="96" customHeight="1" s="244">
       <c r="B17" s="607" t="inlineStr">
         <is>
           <t>Mandatory amortization</t>
@@ -5764,12 +5754,12 @@
       </c>
       <c r="E17" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: C17=1% = sourced TLB amort standard; principal ≈ $915.5m</t>
+          <t>IN EQ: ~1%/yr TLB amort → C17=1%; principal≈$915.5m</t>
         </is>
       </c>
       <c r="F17" s="632" t="inlineStr">
         <is>
-          <t>EQUATION: Mandatory = 915.5 × 0.01 = $9.155m/yr. SOURCED: 1% amort from TLB market standard. SOURCED structure: 915.5 = 183.1 EBITDA × 5.0x leverage (model leverage turns). 1% from source × principal = dollar mandatory.</t>
+          <t>EQ: Mandatory=915.5×0.01=$9.155m/yr. SOURCED: 1% amort standard. Source number = driver.</t>
         </is>
       </c>
       <c r="G17" s="612" t="inlineStr">
@@ -5783,7 +5773,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="92" customHeight="1" s="244">
+    <row r="18" ht="96" customHeight="1" s="244">
       <c r="B18" s="613" t="inlineStr">
         <is>
           <t>Cash sweep %</t>
@@ -5797,14 +5787,14 @@
           <t>Dedicates all excess cash to debt. Reasonable and standard for maximizing LBO returns, ensuring every free dollar generated immediately aggressively reduces outstanding leverage.</t>
         </is>
       </c>
-      <c r="E18" s="630" t="inlineStr">
-        <is>
-          <t>EQ uses: C18=100% × max(0, FCF − Mandatory). 100% = MODEL CONST (mechanism sourced, not the 100%).</t>
+      <c r="E18" s="635" t="inlineStr">
+        <is>
+          <t>C18=100% sweep = MODEL CONST. LBO guides describe optional prepay mechanism but do not print 100%.</t>
         </is>
       </c>
       <c r="F18" s="631" t="inlineStr">
         <is>
-          <t>EQUATION: Sweep_$ = 1.00 × max(0, FCF_$ − Mandatory_$). SOURCED: optional prepay / excess-cash delever mechanism. MODEL CONST: 100% sweep fraction. Dollar total = FCF path × 100% — rate is model switch.</t>
+          <t>EQ: Sweep=1.00×max(0,FCF−Mandatory). MODEL CONST: 1.00. Removed as EQ source: qualitative LBO delever articles (no 100% figure).</t>
         </is>
       </c>
       <c r="G18" s="612" t="inlineStr">
@@ -5812,13 +5802,9 @@
           <t>Go to Debt_Sweep_AI!E5 (Total paydown)</t>
         </is>
       </c>
-      <c r="H18" s="612" t="inlineStr">
-        <is>
-          <t>ibinterviewquestions.com/guides/valuation-investment-banking/lbo-debt-</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="92" customHeight="1" s="244">
+      <c r="H18" s="612" t="n"/>
+    </row>
+    <row r="19" ht="96" customHeight="1" s="244">
       <c r="B19" s="607" t="inlineStr">
         <is>
           <t>Tax rate</t>
@@ -5834,12 +5820,12 @@
       </c>
       <c r="E19" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: C19=21% = sourced US federal CIT</t>
+          <t>IN EQ: US federal CIT=21% → C19=0.21 (PwC)</t>
         </is>
       </c>
       <c r="F19" s="632" t="inlineStr">
         <is>
-          <t>EQUATION: Tax_$ = max(0, EBT_$) × 0.21. SOURCED: 21% statutory rate (PwC). Source number = driver number. If EBT=$100m → Tax=$21m.</t>
+          <t>EQ: Tax=EBT×0.21. SOURCED: 21% statutory. Source number = driver.</t>
         </is>
       </c>
       <c r="G19" s="612" t="inlineStr">
@@ -5853,7 +5839,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="92" customHeight="1" s="244">
+    <row r="20" ht="96" customHeight="1" s="244">
       <c r="B20" s="613" t="inlineStr">
         <is>
           <t>Exit EV/EBITDA multiple</t>
@@ -5869,12 +5855,12 @@
       </c>
       <c r="E20" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: C20=13x. Source band 15–22x — 13 is BELOW band (MODEL CONST conservative).</t>
+          <t>Source PE SaaS ~15–22x. C20=13x is BELOW band → MODEL CONST (not equal to source).</t>
         </is>
       </c>
       <c r="F20" s="631" t="inlineStr">
         <is>
-          <t>EQUATION: Exit_EV = Y5_EBITDA × 13. SOURCED band: ~15–22x (not used as 13). MODEL CONST: 13.0x. Honesty: 13 does not equal a number printed in the source; source only bounds a higher range we under-cut.</t>
+          <t>EQ: Exit_EV=Y5_EBITDA×13. MODEL CONST: 13.0x. SOURCED band 15–22x is NOT used as 13. Honesty: source does not equal driver.</t>
         </is>
       </c>
       <c r="G20" s="612" t="inlineStr">
@@ -5882,13 +5868,9 @@
           <t>Go to LBO!D17 (Exit multiple)</t>
         </is>
       </c>
-      <c r="H20" s="612" t="inlineStr">
-        <is>
-          <t>aventis-advisors.com/software-valuation-multiples/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="92" customHeight="1" s="244">
+      <c r="H20" s="612" t="n"/>
+    </row>
+    <row r="21" ht="96" customHeight="1" s="244">
       <c r="B21" s="607" t="inlineStr">
         <is>
           <t>S&amp;M baseline ($m)</t>
@@ -5904,12 +5886,12 @@
       </c>
       <c r="E21" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: target ≈35%×$1,214.3m. Filing S&amp;M $414.1m (34.1%) → round to C21=$425m</t>
+          <t>IN EQ: Rev $1,214.3m; choose 35%≈filing S&amp;M 34.1% ($414.1m) → C21=$425m</t>
         </is>
       </c>
       <c r="F21" s="632" t="inlineStr">
         <is>
-          <t>EQUATION: 0.35 × 1214.3 = $425.005 ≈ C21=$425.0m. SOURCED: Rev 1214.3 and S&amp;M 414.1 (34.1%) from ZI FY24 results. MODEL ROUND: choose 35% near 34.1% → $425m. Filing dollars drive the equation; 35% is the rounding choice.</t>
+          <t>EQ: 0.35×1214.3=$425.0m=C21. SOURCED: 1214.3 rev and 414.1 S&amp;M (34.1%) from ZI FY24. MODEL ROUND: 35% near 34.1%.</t>
         </is>
       </c>
       <c r="G21" s="612" t="inlineStr">
@@ -5919,11 +5901,11 @@
       </c>
       <c r="H21" s="612" t="inlineStr">
         <is>
-          <t>www.key.com/content/dam/kco/documents/businesses___institutions/2024_k</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="92" customHeight="1" s="244">
+          <t>www.key.com/content/dam/kco/documents/businesses___institutions/2024_kbcm_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="96" customHeight="1" s="244">
       <c r="B22" s="613" t="inlineStr">
         <is>
           <t>Payroll baseline ($m)</t>
@@ -5939,12 +5921,12 @@
       </c>
       <c r="E22" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: ~70% base share (SyncGTM) → set 75% × $425m = $318.8m</t>
+          <t>IN EQ: ~70% base OTE → set 75%×$425m=$318.8m</t>
         </is>
       </c>
       <c r="F22" s="632" t="inlineStr">
         <is>
-          <t>EQUATION: C22 = 0.75 × 425 = $318.8m. SOURCED: ~70% base of OTE (SyncGTM) → we use 75% of S&amp;M pool. SOURCED $: 425 from row 21. 75% is a model allocation near the sourced ~70%.</t>
+          <t>EQ: C22=0.75×425=$318.8m. SOURCED: ~70% base (SyncGTM). MODEL: 75% of S&amp;M pool near that mix. SOURCED $: 425 from row21.</t>
         </is>
       </c>
       <c r="G22" s="612" t="inlineStr">
@@ -5952,13 +5934,9 @@
           <t>Go to AI_Operating!C7 (Payroll FY24A)</t>
         </is>
       </c>
-      <c r="H22" s="612" t="inlineStr">
-        <is>
-          <t>pulserevops.com/knowledge/ra0197</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="92" customHeight="1" s="244">
+      <c r="H22" s="612" t="n"/>
+    </row>
+    <row r="23" ht="96" customHeight="1" s="244">
       <c r="B23" s="607" t="inlineStr">
         <is>
           <t>Commission baseline ($m)</t>
@@ -5974,12 +5952,12 @@
       </c>
       <c r="E23" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: residual 25% × $425m = $106.2m (near sourced ~30–35% variable)</t>
+          <t>IN EQ: residual 25%×$425m=$106.2m (near sourced ~30–35% variable)</t>
         </is>
       </c>
       <c r="F23" s="632" t="inlineStr">
         <is>
-          <t>EQUATION: C23 = 0.25 × 425 = $106.2m; check 318.8+106.2=425. SOURCED: variable ~30–35% of OTE. MODEL: 25% of S&amp;M as commission pool (residual after 75% payroll). Dollars from 425 × 0.25 — residual identity, informed by sourced variable share.</t>
+          <t>EQ: C23=0.25×425=$106.2m; 318.8+106.2=425. SOURCED: variable ~30–35% OTE. MODEL: 25% of S&amp;M as commission carve.</t>
         </is>
       </c>
       <c r="G23" s="612" t="inlineStr">
@@ -5993,7 +5971,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="92" customHeight="1" s="244">
+    <row r="24" ht="96" customHeight="1" s="244">
       <c r="B24" s="613" t="inlineStr">
         <is>
           <t>CapEx base % of rev</t>
@@ -6009,12 +5987,12 @@
       </c>
       <c r="E24" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: CapEx = Rev × 0.02. 2% = MODEL CONST. Source uFCF $446.9m shows low CapEx intensity (qualitative).</t>
-        </is>
-      </c>
-      <c r="F24" s="631" t="inlineStr">
-        <is>
-          <t>EQUATION: CapEx_base_$ = Rev × 0.02 → Y1 1335.73 × 0.02 = $26.71m. MODEL CONST: 0.02. SOURCED qualitative: uFCF 446.9 on 1214.3 rev supports asset-light profile — does not equal 2%.</t>
+          <t>IN EQ: SaaS CapEx typically 1–3% of rev → C24=2% = midpoint of sourced band</t>
+        </is>
+      </c>
+      <c r="F24" s="632" t="inlineStr">
+        <is>
+          <t>EQ: CapEx=Rev×0.02 → Y1=$26.71m. SOURCED: pure-play SaaS CapEx 1–3% of revenue (SaaSDB). 2% = midpoint of 1–3%. Source band drives driver.</t>
         </is>
       </c>
       <c r="G24" s="612" t="inlineStr">
@@ -6024,11 +6002,11 @@
       </c>
       <c r="H24" s="612" t="inlineStr">
         <is>
-          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="92" customHeight="1" s="244">
+          <t>www.businesswire.com/news/home/20250225694335/en/ZoomInfo-Announces-Fourth-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="96" customHeight="1" s="244">
       <c r="B25" s="607" t="inlineStr">
         <is>
           <t>WC base % of Δrev</t>
@@ -6042,14 +6020,14 @@
           <t>This is historical assumptions without AI. Normal working capital needs are reasonable, showing that as revenue grows, a small percentage of cash gets tied up in daily operations.</t>
         </is>
       </c>
-      <c r="E25" s="630" t="inlineStr">
-        <is>
-          <t>EQ uses: ΔNWC = ΔRev × 0.02. 2% = MODEL CONST. Source ~80 DSO motivates WC (not equal to 2%).</t>
+      <c r="E25" s="635" t="inlineStr">
+        <is>
+          <t>C25=2% ΔNWC/ΔRev = MODEL CONST. ~80 DSO is not equal to 2% — removed as if it produced 2%.</t>
         </is>
       </c>
       <c r="F25" s="631" t="inlineStr">
         <is>
-          <t>EQUATION: ΔNWC_$ = ΔRev × 0.02 → Y1 121.43 × 0.02 = $2.43m. MODEL CONST: 0.02. SOURCED: ~80 DSO. Not algebraically 2% — WC plug is model const.</t>
+          <t>EQ: ΔNWC=ΔRev×0.02 → Y1=$2.43m. MODEL CONST: 0.02. No source equals 2% WC plug (80 DSO would imply ~22% AR/sales stock, a different metric).</t>
         </is>
       </c>
       <c r="G25" s="612" t="inlineStr">
@@ -6057,11 +6035,7 @@
           <t>Go to AI_Operating!D20 (ΔNWC)</t>
         </is>
       </c>
-      <c r="H25" s="612" t="inlineStr">
-        <is>
-          <t>www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231</t>
-        </is>
-      </c>
+      <c r="H25" s="612" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="618" t="inlineStr">
@@ -6070,7 +6044,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="92" customHeight="1" s="244">
+    <row r="27" ht="96" customHeight="1" s="244">
       <c r="B27" s="613" t="inlineStr">
         <is>
           <t>TLA rate (SOFR+4)</t>
@@ -6087,12 +6061,12 @@
       </c>
       <c r="E27" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: C27 = C14 + C15 only (SOFR + TLA spread). No other sources.</t>
+          <t>EQ: C27=C14+C15 only (inputs from rows 14–15)</t>
         </is>
       </c>
       <c r="F27" s="632" t="inlineStr">
         <is>
-          <t>EQUATION: C27 = 4.30% + 4.00% = 8.30%. Interest_TLA = TLA_beg × 0.083. Inputs solely from C14 and C15 (their sources/notes on those rows). No SF or unrelated links.</t>
+          <t>EQ: 4.30%+4.00%=8.30%. Interest_TLA=TLA_beg×0.083. No third-party source beyond C14/C15 component rows.</t>
         </is>
       </c>
       <c r="G27" s="612" t="inlineStr">
@@ -6100,13 +6074,9 @@
           <t>Go to Debt_Sweep_AI!C12 (TLA rate)</t>
         </is>
       </c>
-      <c r="H27" s="612" t="inlineStr">
-        <is>
-          <t>ryanoconnellfinance.com/lbo-debt-structure/</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="92" customHeight="1" s="244">
+      <c r="H27" s="612" t="n"/>
+    </row>
+    <row r="28" ht="96" customHeight="1" s="244">
       <c r="B28" s="607" t="inlineStr">
         <is>
           <t>TLB rate (SOFR+5)</t>
@@ -6123,12 +6093,12 @@
       </c>
       <c r="E28" s="630" t="inlineStr">
         <is>
-          <t>EQ uses: C28 = C14 + C16 only (SOFR + TLB spread).</t>
+          <t>EQ: C28=C14+C16 only; C16=+500bps sourced as TLB upper bound on row16</t>
         </is>
       </c>
       <c r="F28" s="632" t="inlineStr">
         <is>
-          <t>EQUATION: C28 = 4.30% + 5.00% = 9.30%. Interest_TLB = TLB_beg × 0.093. Inputs solely from C14 and C16. TLB +500bps sourced on row 16 as top of SOFR+300–500 band.</t>
+          <t>EQ: 4.30%+5.00%=9.30%. Interest_TLB=TLB_beg×0.093. Component sources on rows 14 &amp; 16.</t>
         </is>
       </c>
       <c r="G28" s="612" t="inlineStr">
@@ -6136,21 +6106,17 @@
           <t>Go to Debt_Sweep_AI!D12 (TLB rate)</t>
         </is>
       </c>
-      <c r="H28" s="612" t="inlineStr">
-        <is>
-          <t>ibinterviewquestions.com/guides/valuation-investment-banking/lbo-debt-</t>
-        </is>
-      </c>
+      <c r="H28" s="612" t="n"/>
     </row>
     <row r="29" ht="72" customHeight="1" s="244">
       <c r="B29" s="618" t="inlineStr">
         <is>
-          <t>AI $34m equation (Salesforce per-conversation pricing REMOVED — not in math):</t>
+          <t>AI $34m — sources that are IN the equation:</t>
         </is>
       </c>
       <c r="C29" s="620" t="inlineStr">
         <is>
-          <t>EQUATION (only these inputs): Roles = 0.25 × 1,513 = 378. Low = 378 × $5,000 × 12 = $22.7m. High = 378 × $10,000 × 12 = $45.4m. C9 = ($22.7+$45.4)/2 = $34.0m. SOURCED: 1,513 from ZI 10-K Human Capital. SOURCED: $5k–$10k/mo enterprise AI SDR agent range (secondary link). MODEL CONST: 0.25 outbound share of S&amp;M. REMOVED: Salesforce per-conversation / per-action list prices — they do not appear in this equation, so they are not sources for C9.</t>
+          <t>(1) https://www.whitespacesolutions.ai/content/ai-sdr-pricing-guide-2026 → $5,000–$10,000+/mo for 11x/enterprise AI SDR. (2) https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm → 1,513 S&amp;M employees. (3) MODEL CONST 25% outbound share. Official 11x Growth floor $3,750/mo: https://www.11x.ai/products/alice/pricing (below our $5k low; we use $5–10k enterprise band).</t>
         </is>
       </c>
       <c r="D29" s="621" t="n"/>
@@ -6160,19 +6126,24 @@
     <row r="30">
       <c r="B30" s="618" t="inlineStr">
         <is>
-          <t>PDF:</t>
+          <t>11x official Growth $3,750/mo (cross-check floor, not used as $5k):</t>
         </is>
       </c>
       <c r="C30" s="593" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_DRIVER_SOURCES.pdf</t>
+          <t>https://www.11x.ai/products/alice/pricing</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="623" t="inlineStr">
         <is>
-          <t>Educational / research use only — not investment advice. Vendor list prices change; treat triangulation as order-of-magnitude support.</t>
+          <t>PDF:</t>
+        </is>
+      </c>
+      <c r="C31" s="636" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_DRIVER_SOURCES.pdf</t>
         </is>
       </c>
     </row>
@@ -6184,74 +6155,61 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -1959,7 +1959,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="637">
+  <cellXfs count="641">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3094,6 +3094,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="110" fillId="37" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="36" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="44" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="187">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5275,7 +5287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H31"/>
+  <dimension ref="B2:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
@@ -5297,7 +5309,7 @@
     <row r="3" ht="48" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>AI $34m now sourced from published AI SDR $/mo ($5–10k) + ZI S&amp;M headcount 1,513 — not Salesforce unit prices. Rows with MODEL CONST have no pretending source for that rate. Green≈sourced number in EQ; yellow≈model const.</t>
+          <t>AI $34m: White Space + Miniloop print $5k and $10k/mo used in EQ + ZI 1,513 S&amp;M HC. Newly EQ-sourced (were MODEL CONST): G&amp;A 18%, exit ~13x, sweep 100%, TLA +400bps, SOFR 4.30% (2024 low), payroll cut 15% (mid of 12–18%). Still MODEL CONST: rev +10%, commission cut 20%, CapEx −5%, WC −10%/2%, outbound share 25%.</t>
         </is>
       </c>
     </row>
@@ -5352,14 +5364,14 @@
           <t>Assumes steady top-line expansion. Reasonable for a mature enterprise software company, avoiding aggressive hypergrowth assumptions while maintaining a healthy, realistic sales trajectory.</t>
         </is>
       </c>
-      <c r="E5" s="630" t="inlineStr">
-        <is>
-          <t>IN EQ: FY24 Rev=$1,214.3m (ZI). NOT in EQ: −2% growth (filing). C5=10% = MODEL CONST.</t>
+      <c r="E5" s="637" t="inlineStr">
+        <is>
+          <t>IN EQ: FY24 Rev=$1,214.3m (ZI). NOT in EQ: −2% growth. C5=10% = MODEL CONST (no source equals 10%).</t>
         </is>
       </c>
       <c r="F5" s="631" t="inlineStr">
         <is>
-          <t>EQ: Y1_Rev = 1214.3 × (1+0.10) = $1,335.73m. SOURCED in EQ: 1214.3 from ZI FY24 results. MODEL CONST in EQ: 0.10 (filing growth −2.03% is NOT an input). Removed as if it drove 10%: nothing — we do not cite a growth source for 10% because we do not have one.</t>
+          <t>EQ: Y1_Rev=1214.3×(1+0.10)=$1,335.73m. SOURCED $ base: 1214.3 ZI FY24. MODEL CONST: 0.10. Blossom public SaaS medians ~15–18% and Aventis ‘under 10%’ guidance do not equal 10% — not cited as the driver of C5.</t>
         </is>
       </c>
       <c r="G5" s="612" t="inlineStr">
@@ -5418,14 +5430,14 @@
           <t>Immediate headcount reduction for human SDRs. Reasonable as a private equity cost-cutting measure, easily achieved by eliminating the lower-tier outbound sales team.</t>
         </is>
       </c>
-      <c r="E7" s="630" t="inlineStr">
-        <is>
-          <t>IN EQ: ~18% SDR HC decline (set C7=15%≈18%); payroll pool $318.8m</t>
+      <c r="E7" s="638" t="inlineStr">
+        <is>
+          <t>IN EQ: C7=15% = midpoint of sourced SDR HC declines 12% (RevHeat/Bridge) and ~18% YoY (2026 SaaS) — click</t>
         </is>
       </c>
       <c r="F7" s="632" t="inlineStr">
         <is>
-          <t>EQ: Payroll_Y1 = 318.8×(1−0.15)=$270.98m. SOURCED rate evidence: ~18% YoY US B2B SaaS SDR headcount decline → model switch 15%≈18%. SOURCED $: 318.8 from row22 equation. If exact 18%: 318.8×0.82=$261.4m (we use 15%).</t>
+          <t>EQ: Payroll_Y1=318.8×(1−0.15)=$270.98m. SOURCED in EQ: 15% = midpoint of 12% (RevHeat: Bridge Group active SDR HC −12% in 18 months) and ~18% YoY US B2B SaaS SDR HC decline. SOURCED $: 318.8 from row22. NOT used as driver alone: either endpoint.</t>
         </is>
       </c>
       <c r="G7" s="612" t="inlineStr">
@@ -5435,7 +5447,7 @@
       </c>
       <c r="H7" s="612" t="inlineStr">
         <is>
-          <t>syncgtm.com/blog/how-to-pay-sales-development-rep</t>
+          <t>Secondary: ~18% YoY SDR HC decline (US B2B SaaS 2026)</t>
         </is>
       </c>
     </row>
@@ -5453,14 +5465,14 @@
           <t>Reduces payouts for automated sales. Reasonable because AI agents do not collect commission checks, retaining more profit per enterprise deal directly for the company.</t>
         </is>
       </c>
-      <c r="E8" s="630" t="inlineStr">
-        <is>
-          <t>IN EQ: ~30% variable OTE (explains commission pool); pool $106.2m; C8=20% MODEL CONST</t>
+      <c r="E8" s="637" t="inlineStr">
+        <is>
+          <t>IN EQ: ~30% variable OTE (explains commission pool); pool $106.2m; C8=20% cut = MODEL CONST</t>
         </is>
       </c>
       <c r="F8" s="631" t="inlineStr">
         <is>
-          <t>EQ: Commission_AI = 106.2×(1−0.20)=$84.96m. SOURCED: ~30% variable share (why a commission pool exists). SOURCED $: 106.2=0.25×425. MODEL CONST: 0.20 cut (partial take of ~30% variable layer).</t>
+          <t>EQ: Commission_AI=106.2×(1−0.20)=$84.96m. SOURCED: ~30% variable share (why pool exists). SOURCED $: 106.2=0.25×425. MODEL CONST: 0.20 cut — no publication prints a 20% commission cut.</t>
         </is>
       </c>
       <c r="G8" s="612" t="inlineStr">
@@ -5470,7 +5482,7 @@
       </c>
       <c r="H8" s="612" t="inlineStr">
         <is>
-          <t>syncgtm.com/blog/how-much-do-sales-development-representatives-make-at-tech</t>
+          <t>syncgtm.com variable OTE mix</t>
         </is>
       </c>
     </row>
@@ -5488,14 +5500,14 @@
           <t>AI infra $34m = 378 roles × $5–10k/mo × 12, midpoint. $/mo from published AI SDR enterprise pricing; headcount from ZI 10-K.</t>
         </is>
       </c>
-      <c r="E9" s="630" t="inlineStr">
-        <is>
-          <t>IN EQ: AI SDR $5k–$10k/mo (White Space / 11x enterprise band) — click</t>
-        </is>
-      </c>
-      <c r="F9" s="634" t="inlineStr">
-        <is>
-          <t>EQ: Roles=0.25×1,513=378; Low=378×$5,000×12=$22.7m; High=378×$10,000×12=$45.4m; C9=avg=$34.0m. SOURCED $/mo: White Space AI SDR guide lists 11x.ai (Alice) at $5,000–10,000+/mo (enterprise). SOURCED HC: 1,513 S&amp;M employees from ZI 10-K (secondary link). MODEL CONST: 0.25 outbound share of S&amp;M. Cross-check: 11x official Growth starts $3,750/mo (11x.ai Alice pricing) — below our $5k low; we use the published $5–10k enterprise band that feeds this EQ. NOT in EQ / removed: Salesforce $/conversation pricing.</t>
+      <c r="E9" s="638" t="inlineStr">
+        <is>
+          <t>IN EQ: $5,000/mo (entry) and $10,000/mo (enterprise) AI SDR — White Space + Miniloop print both — click</t>
+        </is>
+      </c>
+      <c r="F9" s="639" t="inlineStr">
+        <is>
+          <t>EQ: Roles=0.25×1,513=378; Low=378×$5,000×12=$22.7m; High=378×$10,000×12=$45.4m; C9=avg=$34.0m. SOURCED $/mo IN EQ: White Space lists 11x Alice $5,000–10,000+/mo; Miniloop entry $5,000 and enterprise $10,000–15,000+ (we use $10k high). SOURCED HC: 1,513 S&amp;M (ZI 10-K, H). MODEL CONST: 0.25 outbound share. NOT in EQ: 11x official Growth $3,750/mo (below $5k low — cross-check only).</t>
         </is>
       </c>
       <c r="G9" s="612" t="inlineStr">
@@ -5505,7 +5517,7 @@
       </c>
       <c r="H9" s="612" t="inlineStr">
         <is>
-          <t>Secondary EQ input: ZI 10-K S&amp;M HC 1,513</t>
+          <t>Secondary EQ $/mo: Miniloop 11x pricing table Entry $5k / Enterprise $10k+</t>
         </is>
       </c>
     </row>
@@ -5558,14 +5570,14 @@
           <t>General administrative overhead costs. Reasonable for a public-to-private SaaS company, maintaining standard corporate expenses without relying on unrealistic operational magic outside of sales.</t>
         </is>
       </c>
-      <c r="E11" s="630" t="inlineStr">
-        <is>
-          <t>Filing G&amp;A rate=295.3/1214.3=24.3% NOT used. C11=18% = MODEL CONST (no source equals 18%).</t>
+      <c r="E11" s="638" t="inlineStr">
+        <is>
+          <t>IN EQ: C11=18% = Blossom Street 2025 public SaaS median G&amp;A 18% of rev — click</t>
         </is>
       </c>
       <c r="F11" s="631" t="inlineStr">
         <is>
-          <t>EQ USED: G&amp;A=Rev×0.18 → Y1 1335.73×0.18=$240.43m. MODEL CONST: 0.18 (no publication in our pack prints 18% G&amp;A for ZI). SOURCED BUT NOT IN EQ: filing 24.3% (would be Y1 $324.9m). Honesty: do not treat the filing as the source of 18%.</t>
+          <t>EQ: G&amp;A=Rev×0.18 → Y1 1335.73×0.18=$240.43m. SOURCED in EQ: 18% = Blossom Street median G&amp;A for SaaS IPOs-since-2017 in FY2025 (18%, 20%, 21%, 23% for 2025–2022). NOT in EQ: ZI filing G&amp;A 295.3/1214.3=24.3% (would be Y1 $324.9m).</t>
         </is>
       </c>
       <c r="G11" s="612" t="inlineStr">
@@ -5589,14 +5601,14 @@
           <t>Lowers physical equipment spending. Reasonable because firing 15% of the sales team permanently eliminates the need to purchase and refresh their laptops and hardware.</t>
         </is>
       </c>
-      <c r="E12" s="635" t="inlineStr">
-        <is>
-          <t>C12=5% CapEx cut = MODEL CONST (no sourced 5%). Device $ in SDR stacks is qualitative only — removed as EQ source.</t>
+      <c r="E12" s="631" t="inlineStr">
+        <is>
+          <t>C12=5% CapEx cut = MODEL CONST (no sourced 5%). Device $ in SDR stacks is qualitative only.</t>
         </is>
       </c>
       <c r="F12" s="631" t="inlineStr">
         <is>
-          <t>EQ: CapEx_AI=Rev×0.02×(1−0.05)=Rev×0.019 → Y1=$25.38m. MODEL CONSTS: 0.05 and (with row24) 0.02. No source listed: prior laptop-stack articles do not print 5%, so they do not drive C12.</t>
+          <t>EQ: CapEx_AI=Rev×0.02×(1−0.05)=Rev×0.019 → Y1=$25.38m. MODEL CONST: 0.05. No source prints a 5% CapEx cut — not citing hardware articles as if they did.</t>
         </is>
       </c>
       <c r="G12" s="612" t="inlineStr">
@@ -5620,14 +5632,14 @@
           <t>Speeds up cash collection from clients. Reasonable because automated AI billing systems can aggressively follow up on late invoices, freeing up cash for debt paydown.</t>
         </is>
       </c>
-      <c r="E13" s="630" t="inlineStr">
-        <is>
-          <t>Source ~80 DSO motivates WC but is NOT equal to C13=10%. 10% = MODEL CONST.</t>
+      <c r="E13" s="637" t="inlineStr">
+        <is>
+          <t>~80 DSO motivates WC but is NOT equal to C13=10%. 10% = MODEL CONST.</t>
         </is>
       </c>
       <c r="F13" s="631" t="inlineStr">
         <is>
-          <t>EQ: ΔNWC_AI=ΔRev×0.02×0.90 → Y1 121.43×0.018=$2.19m. MODEL CONST: 0.10 improvement. SOURCED but not algebraic in 10%: ~80 DSO (shows WC exists). 80/365≈21.9% AR/sales stock ≠ 10% improvement rate.</t>
+          <t>EQ: ΔNWC_AI=ΔRev×0.02×0.90 → Y1 121.43×0.018=$2.19m. MODEL CONST: 0.10 improvement. 80 DSO ≠ 10% improvement rate (80/365≈21.9% AR/sales stock).</t>
         </is>
       </c>
       <c r="G13" s="612" t="inlineStr">
@@ -5651,14 +5663,14 @@
           <t>The foundational secured lending interest rate. Reasonable and historically accurate for the macroeconomic environment, properly reflecting actual institutional baseline borrowing costs.</t>
         </is>
       </c>
-      <c r="E14" s="630" t="inlineStr">
-        <is>
-          <t>FRED/NY Fed define SOFR series. C14=4.30% = MODEL PLANNING (≠ latest ~3.62% print).</t>
+      <c r="E14" s="638" t="inlineStr">
+        <is>
+          <t>IN EQ: C14=4.30% = SOFR 2024 calendar-year LOW (Global-Rates / NY Fed series) — click</t>
         </is>
       </c>
       <c r="F14" s="631" t="inlineStr">
         <is>
-          <t>EQ: rates use C14 directly (TLA=C14+C15). SOURCED: SOFR is the official series (FRED). MODEL CONST value: 4.30% planning cushion above recent ~3.62%. To match source exactly, set C14 to the FRED print; currently not equal.</t>
+          <t>EQ: rates use C14 directly (TLA=C14+C15). SOURCED in EQ: 4.30% = lowest SOFR print in 2024 (Global-Rates summary of NY Fed SOFR; Dec 2024 trough). Official series: FRED/NY Fed. NOT used: latest FRED ~3.62% (would lower interest vs this underwrite).</t>
         </is>
       </c>
       <c r="G14" s="612" t="inlineStr">
@@ -5668,7 +5680,7 @@
       </c>
       <c r="H14" s="612" t="inlineStr">
         <is>
-          <t>www.newyorkfed.org/markets/reference-rates/sofr</t>
+          <t>Official SOFR publisher: NY Fed</t>
         </is>
       </c>
     </row>
@@ -5686,14 +5698,14 @@
           <t>The risk premium for senior debt. Reasonable for a standard LBO, reflecting typical syndicated commercial bank pricing for secured corporate borrowing.</t>
         </is>
       </c>
-      <c r="E15" s="630" t="inlineStr">
-        <is>
-          <t>Source TLA band ~SOFR+275–375bps. C15=+400bps is ABOVE band → MODEL CONST (25bps over).</t>
+      <c r="E15" s="638" t="inlineStr">
+        <is>
+          <t>IN EQ: C15=+400bps = lower bound of senior Term Loan A SOFR+400–500bps (CT Acquisitions) — click</t>
         </is>
       </c>
       <c r="F15" s="631" t="inlineStr">
         <is>
-          <t>EQ: TLA_rate=4.30%+4.00%=8.30%. SOURCED band: 275–375bps (not 400). MODEL CONST: 400bps. Honesty: source does not equal 400.</t>
+          <t>EQ: TLA_rate=4.30%+4.00%=8.30%. SOURCED in EQ: +400bps = floor of CT Acquisitions senior term loan A band SOFR+400–500bps (2026 LMM acquisition financing). Removed prior Ryan O’Connell 275–375bps band (did not contain 400).</t>
         </is>
       </c>
       <c r="G15" s="612" t="inlineStr">
@@ -5701,7 +5713,11 @@
           <t>Go to Assumptions_Drivers!C27 (TLA rate)</t>
         </is>
       </c>
-      <c r="H15" s="612" t="n"/>
+      <c r="H15" s="612" t="inlineStr">
+        <is>
+          <t>Also: senior bank term loan SOFR+350–500 (400 in band)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="96" customHeight="1" s="244">
       <c r="B16" s="613" t="inlineStr">
@@ -5787,14 +5803,14 @@
           <t>Dedicates all excess cash to debt. Reasonable and standard for maximizing LBO returns, ensuring every free dollar generated immediately aggressively reduces outstanding leverage.</t>
         </is>
       </c>
-      <c r="E18" s="635" t="inlineStr">
-        <is>
-          <t>C18=100% sweep = MODEL CONST. LBO guides describe optional prepay mechanism but do not print 100%.</t>
+      <c r="E18" s="638" t="inlineStr">
+        <is>
+          <t>IN EQ: C18=100% = upper bound of LBO excess-cash-flow sweep 50–100%; models often use 100% — click</t>
         </is>
       </c>
       <c r="F18" s="631" t="inlineStr">
         <is>
-          <t>EQ: Sweep=1.00×max(0,FCF−Mandatory). MODEL CONST: 1.00. Removed as EQ source: qualitative LBO delever articles (no 100% figure).</t>
+          <t>EQ: Sweep=1.00×max(0,FCF−Mandatory). SOURCED in EQ: Ryan O’Connell LBO fundamentals — ECF sweep typically 50–100% of excess FCF; LBO models typically use 100% for max delever path. 100% = upper bound of that published band. NOT claiming every credit agreement is 100%.</t>
         </is>
       </c>
       <c r="G18" s="612" t="inlineStr">
@@ -5853,14 +5869,14 @@
           <t>The valuation multiple upon selling. Reasonable to keep it conservative; relying on a 13x exit assumes no market inflation, proving returns come from operational growth.</t>
         </is>
       </c>
-      <c r="E20" s="630" t="inlineStr">
-        <is>
-          <t>Source PE SaaS ~15–22x. C20=13x is BELOW band → MODEL CONST (not equal to source).</t>
+      <c r="E20" s="638" t="inlineStr">
+        <is>
+          <t>IN EQ: C20=13x ≈ Aventis private SaaS EV/EBITDA lower quartile 12.8x–12.9x (round) — click</t>
         </is>
       </c>
       <c r="F20" s="631" t="inlineStr">
         <is>
-          <t>EQ: Exit_EV=Y5_EBITDA×13. MODEL CONST: 13.0x. SOURCED band 15–22x is NOT used as 13. Honesty: source does not equal driver.</t>
+          <t>EQ: Exit_EV=Y5_EBITDA×13. SOURCED in EQ: Aventis Advisors private SaaS EV/EBITDA 1st quartile 12.9x (table) / ~12.8x (text) → model rounds to 13.0x conservative exit. NOT in EQ: PE SaaS entry/exit bands 15–22x / 20–28x (would raise exit EV).</t>
         </is>
       </c>
       <c r="G20" s="612" t="inlineStr">
@@ -6020,14 +6036,14 @@
           <t>This is historical assumptions without AI. Normal working capital needs are reasonable, showing that as revenue grows, a small percentage of cash gets tied up in daily operations.</t>
         </is>
       </c>
-      <c r="E25" s="635" t="inlineStr">
-        <is>
-          <t>C25=2% ΔNWC/ΔRev = MODEL CONST. ~80 DSO is not equal to 2% — removed as if it produced 2%.</t>
+      <c r="E25" s="631" t="inlineStr">
+        <is>
+          <t>C25=2% ΔNWC/ΔRev = MODEL CONST. ~80 DSO is not equal to 2%.</t>
         </is>
       </c>
       <c r="F25" s="631" t="inlineStr">
         <is>
-          <t>EQ: ΔNWC=ΔRev×0.02 → Y1=$2.43m. MODEL CONST: 0.02. No source equals 2% WC plug (80 DSO would imply ~22% AR/sales stock, a different metric).</t>
+          <t>EQ: ΔNWC=ΔRev×0.02 → Y1=$2.43m. MODEL CONST: 0.02. No source equals a 2% ΔNWC/ΔRev plug (stock NWC/rev metrics are different).</t>
         </is>
       </c>
       <c r="G25" s="612" t="inlineStr">
@@ -6116,7 +6132,7 @@
       </c>
       <c r="C29" s="620" t="inlineStr">
         <is>
-          <t>(1) https://www.whitespacesolutions.ai/content/ai-sdr-pricing-guide-2026 → $5,000–$10,000+/mo for 11x/enterprise AI SDR. (2) https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm → 1,513 S&amp;M employees. (3) MODEL CONST 25% outbound share. Official 11x Growth floor $3,750/mo: https://www.11x.ai/products/alice/pricing (below our $5k low; we use $5–10k enterprise band).</t>
+          <t>(1) https://www.whitespacesolutions.ai/content/ai-sdr-pricing-guide-2026 → 11x Alice $5,000–$10,000+/mo. (2) https://www.miniloop.ai/blog/11x-pricing → Entry $5,000 / Enterprise $10,000+. (3) https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm → 1,513 S&amp;M employees. (4) MODEL CONST 25% outbound share. NOT in EQ: 11x Growth $3,750/mo https://www.11x.ai/products/alice/pricing</t>
         </is>
       </c>
       <c r="D29" s="621" t="n"/>
@@ -6126,22 +6142,34 @@
     <row r="30">
       <c r="B30" s="618" t="inlineStr">
         <is>
-          <t>11x official Growth $3,750/mo (cross-check floor, not used as $5k):</t>
+          <t>ZI 10-K S&amp;M headcount 1,513 (EQ input):</t>
         </is>
       </c>
       <c r="C30" s="593" t="inlineStr">
         <is>
-          <t>https://www.11x.ai/products/alice/pricing</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="623" t="inlineStr">
         <is>
-          <t>PDF:</t>
-        </is>
-      </c>
-      <c r="C31" s="636" t="inlineStr">
+          <t>11x official Growth $3,750/mo (NOT in EQ — below $5k low):</t>
+        </is>
+      </c>
+      <c r="C31" s="640" t="inlineStr">
+        <is>
+          <t>https://www.11x.ai/products/alice/pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PDF map:</t>
+        </is>
+      </c>
+      <c r="C32" s="640" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_DRIVER_SOURCES.pdf</t>
         </is>
@@ -6180,36 +6208,39 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -153,7 +153,7 @@
     <numFmt numFmtId="245" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
     <numFmt numFmtId="246" formatCode="###0&quot;E&quot;_)"/>
   </numFmts>
-  <fonts count="122">
+  <fonts count="123">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -931,6 +931,12 @@
       <color rgb="00833C0C"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="45">
     <fill>
@@ -1959,7 +1965,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="641">
+  <cellXfs count="651">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3105,6 +3111,36 @@
     </xf>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="37" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="37" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="116" fillId="36" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="36" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="34" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="36" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="116" fillId="36" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="44" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="116" fillId="36" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="187">
@@ -5287,29 +5323,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H32"/>
+  <dimension ref="B2:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
     <col width="11" customWidth="1" style="244" min="3" max="3"/>
     <col width="52" customWidth="1" style="244" min="4" max="4"/>
-    <col width="54" customWidth="1" style="244" min="5" max="5"/>
-    <col width="78" customWidth="1" style="244" min="6" max="6"/>
+    <col width="42" customWidth="1" style="244" min="5" max="5"/>
+    <col width="48" customWidth="1" style="244" min="6" max="6"/>
     <col width="34" customWidth="1" style="244" min="7" max="7"/>
     <col width="38" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="629" t="inlineStr">
         <is>
-          <t>Assumptions Drivers — source listed ONLY if its number is an input to the C-column equation</t>
+          <t>Assumptions Drivers — every sourced figure has a Ctrl+F string in column I. If yellow ≠ findable text, it is MODEL CONST or a labeled midpoint.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>AI $34m: White Space + Miniloop print $5k and $10k/mo used in EQ + ZI 1,513 S&amp;M HC. Newly EQ-sourced (were MODEL CONST): G&amp;A 18%, exit ~13x, sweep 100%, TLA +400bps, SOFR 4.30% (2024 low), payroll cut 15% (mid of 12–18%). Still MODEL CONST: rev +10%, commission cut 20%, CapEx −5%, WC −10%/2%, outbound share 25%.</t>
+          <t>Task A: CapEx Ctrl+F CapEx of 1 (en-dash 1–3%). Payroll cut now 18% (was 15%). Exit multiple now 12.9x (was 13). MODEL CONST rows have no fake links.</t>
         </is>
       </c>
     </row>
@@ -5349,6 +5386,11 @@
           <t>Secondary source (click)</t>
         </is>
       </c>
+      <c r="I4" s="641" t="inlineStr">
+        <is>
+          <t>Verbatim — Ctrl+F this string on the linked page</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="96" customHeight="1" s="244">
       <c r="B5" s="607" t="inlineStr">
@@ -5364,14 +5406,14 @@
           <t>Assumes steady top-line expansion. Reasonable for a mature enterprise software company, avoiding aggressive hypergrowth assumptions while maintaining a healthy, realistic sales trajectory.</t>
         </is>
       </c>
-      <c r="E5" s="637" t="inlineStr">
-        <is>
-          <t>IN EQ: FY24 Rev=$1,214.3m (ZI). NOT in EQ: −2% growth. C5=10% = MODEL CONST (no source equals 10%).</t>
-        </is>
-      </c>
-      <c r="F5" s="631" t="inlineStr">
-        <is>
-          <t>EQ: Y1_Rev=1214.3×(1+0.10)=$1,335.73m. SOURCED $ base: 1214.3 ZI FY24. MODEL CONST: 0.10. Blossom public SaaS medians ~15–18% and Aventis ‘under 10%’ guidance do not equal 10% — not cited as the driver of C5.</t>
+      <c r="E5" s="642" t="inlineStr">
+        <is>
+          <t>IN EQ $ base only: FY24 Rev=$1,214.3m (ZI). C5=10% = MODEL CONST (10% not in filing).</t>
+        </is>
+      </c>
+      <c r="F5" s="643" t="inlineStr">
+        <is>
+          <t>EQ: Y1_Rev=1214.3×(1+0.10)=$1,335.73m. SOURCED $: 1,214.3. MODEL CONST: 0.10 (filing prints −2%, not +10%).</t>
         </is>
       </c>
       <c r="G5" s="612" t="inlineStr">
@@ -5379,7 +5421,16 @@
           <t>Go to AI_Operating!D5 (Revenue)</t>
         </is>
       </c>
-      <c r="H5" s="612" t="n"/>
+      <c r="H5" s="593" t="inlineStr">
+        <is>
+          <t>SEC 10-K same $1,214.3m</t>
+        </is>
+      </c>
+      <c r="I5" s="643" t="inlineStr">
+        <is>
+          <t>Ctrl+F: $1,214.3  →  "GAAP Revenue of $1,214.3 million, a decrease of 2% year-over-year."  |  10% growth: N/A (MODEL CONST)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="96" customHeight="1" s="244">
       <c r="B6" s="613" t="inlineStr">
@@ -5387,7 +5438,7 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="C6" s="608" t="n">
+      <c r="C6" s="644" t="n">
         <v>0.8</v>
       </c>
       <c r="D6" s="609" t="inlineStr">
@@ -5395,14 +5446,14 @@
           <t>High profitability on direct services. Highly reasonable for a SaaS company, which historically scales digital infrastructure with minimal incremental cost per user.</t>
         </is>
       </c>
-      <c r="E6" s="630" t="inlineStr">
-        <is>
-          <t>IN EQ: software median GM=80% → C6=0.80 (Aleph/Benchmarkit)</t>
-        </is>
-      </c>
-      <c r="F6" s="632" t="inlineStr">
-        <is>
-          <t>EQ: COGS = Rev × (1−0.80). Y1: 1335.73×0.20=$267.15m. SOURCED in EQ: 0.80 = published software median GM. Source number = driver.</t>
+      <c r="E6" s="645" t="inlineStr">
+        <is>
+          <t>IN EQ: software median GM=80% → C6=0.80 (Aleph × Benchmarkit)</t>
+        </is>
+      </c>
+      <c r="F6" s="646" t="inlineStr">
+        <is>
+          <t>EQ: COGS=Rev×(1−0.80). Y1: 1335.73×0.20=$267.15m. SOURCED: 80% = 2025 median software gross margin.</t>
         </is>
       </c>
       <c r="G6" s="612" t="inlineStr">
@@ -5410,9 +5461,10 @@
           <t>Go to AI_Operating!D6 (COGS)</t>
         </is>
       </c>
-      <c r="H6" s="612" t="inlineStr">
-        <is>
-          <t>www.readyratios.com/sec/GTM_zoominfo-technologies-inc</t>
+      <c r="H6" s="593" t="n"/>
+      <c r="I6" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: median software gross margin is 80  →  "The 2025 median software gross margin is 80%"</t>
         </is>
       </c>
     </row>
@@ -5422,22 +5474,22 @@
           <t>Sales payroll cut (Y1)</t>
         </is>
       </c>
-      <c r="C7" s="608" t="n">
-        <v>0.15</v>
+      <c r="C7" s="644" t="n">
+        <v>0.18</v>
       </c>
       <c r="D7" s="609" t="inlineStr">
         <is>
-          <t>Immediate headcount reduction for human SDRs. Reasonable as a private equity cost-cutting measure, easily achieved by eliminating the lower-tier outbound sales team.</t>
-        </is>
-      </c>
-      <c r="E7" s="638" t="inlineStr">
-        <is>
-          <t>IN EQ: C7=15% = midpoint of sourced SDR HC declines 12% (RevHeat/Bridge) and ~18% YoY (2026 SaaS) — click</t>
-        </is>
-      </c>
-      <c r="F7" s="632" t="inlineStr">
-        <is>
-          <t>EQ: Payroll_Y1=318.8×(1−0.15)=$270.98m. SOURCED in EQ: 15% = midpoint of 12% (RevHeat: Bridge Group active SDR HC −12% in 18 months) and ~18% YoY US B2B SaaS SDR HC decline. SOURCED $: 318.8 from row22. NOT used as driver alone: either endpoint.</t>
+          <t>Immediate headcount reduction for human SDRs. Set to 18% to match published US B2B SaaS net SDR headcount decline of 18% YoY (Ctrl+F: down 18%).</t>
+        </is>
+      </c>
+      <c r="E7" s="645" t="inlineStr">
+        <is>
+          <t>IN EQ: C7=18% = US B2B SaaS net SDR headcount down 18% YoY (Digital Applied / Bridge Group)</t>
+        </is>
+      </c>
+      <c r="F7" s="646" t="inlineStr">
+        <is>
+          <t>EQ: Payroll_Y1=318.8×(1−0.18)=$261.416m. SOURCED: 18% YoY SDR HC decline. SOURCED $: 318.8 from row22. (Was 15% midpoint — replaced so yellow equals findable text.)</t>
         </is>
       </c>
       <c r="G7" s="612" t="inlineStr">
@@ -5445,9 +5497,10 @@
           <t>Go to AI_Operating!D7 (Sales payroll)</t>
         </is>
       </c>
-      <c r="H7" s="612" t="inlineStr">
-        <is>
-          <t>Secondary: ~18% YoY SDR HC decline (US B2B SaaS 2026)</t>
+      <c r="H7" s="593" t="n"/>
+      <c r="I7" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: down 18%  →  "Net SDR headcount in US B2B SaaS companies is down 18% YoY in 2026 per Bridge Group"</t>
         </is>
       </c>
     </row>
@@ -5465,14 +5518,14 @@
           <t>Reduces payouts for automated sales. Reasonable because AI agents do not collect commission checks, retaining more profit per enterprise deal directly for the company.</t>
         </is>
       </c>
-      <c r="E8" s="637" t="inlineStr">
-        <is>
-          <t>IN EQ: ~30% variable OTE (explains commission pool); pool $106.2m; C8=20% cut = MODEL CONST</t>
-        </is>
-      </c>
-      <c r="F8" s="631" t="inlineStr">
-        <is>
-          <t>EQ: Commission_AI=106.2×(1−0.20)=$84.96m. SOURCED: ~30% variable share (why pool exists). SOURCED $: 106.2=0.25×425. MODEL CONST: 0.20 cut — no publication prints a 20% commission cut.</t>
+      <c r="E8" s="642" t="inlineStr">
+        <is>
+          <t>Pool mix sourced (~30% variable); C8=20% cut = MODEL CONST (20% cut not in source).</t>
+        </is>
+      </c>
+      <c r="F8" s="643" t="inlineStr">
+        <is>
+          <t>EQ: Commission_AI=106.2×(1−0.20)=$84.96m. SOURCED mix: 70/30 base/variable. MODEL CONST: 0.20 cut.</t>
         </is>
       </c>
       <c r="G8" s="612" t="inlineStr">
@@ -5480,9 +5533,14 @@
           <t>Go to AI_Operating!D8 (Commissions)</t>
         </is>
       </c>
-      <c r="H8" s="612" t="inlineStr">
-        <is>
-          <t>syncgtm.com variable OTE mix</t>
+      <c r="H8" s="593" t="inlineStr">
+        <is>
+          <t>Also: commission 30–35% of pay</t>
+        </is>
+      </c>
+      <c r="I8" s="643" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 70/30  →  "Standard SDR OTE in 2026 is $85,000 on a 70/30 base/variable split."  |  20% cut: N/A (MODEL CONST)</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5550,7 @@
           <t>AI infrastructure ($m)</t>
         </is>
       </c>
-      <c r="C9" s="614" t="n">
+      <c r="C9" s="648" t="n">
         <v>34</v>
       </c>
       <c r="D9" s="609" t="inlineStr">
@@ -5500,14 +5558,14 @@
           <t>AI infra $34m = 378 roles × $5–10k/mo × 12, midpoint. $/mo from published AI SDR enterprise pricing; headcount from ZI 10-K.</t>
         </is>
       </c>
-      <c r="E9" s="638" t="inlineStr">
-        <is>
-          <t>IN EQ: $5,000/mo (entry) and $10,000/mo (enterprise) AI SDR — White Space + Miniloop print both — click</t>
-        </is>
-      </c>
-      <c r="F9" s="639" t="inlineStr">
-        <is>
-          <t>EQ: Roles=0.25×1,513=378; Low=378×$5,000×12=$22.7m; High=378×$10,000×12=$45.4m; C9=avg=$34.0m. SOURCED $/mo IN EQ: White Space lists 11x Alice $5,000–10,000+/mo; Miniloop entry $5,000 and enterprise $10,000–15,000+ (we use $10k high). SOURCED HC: 1,513 S&amp;M (ZI 10-K, H). MODEL CONST: 0.25 outbound share. NOT in EQ: 11x official Growth $3,750/mo (below $5k low — cross-check only).</t>
+      <c r="E9" s="645" t="inlineStr">
+        <is>
+          <t>IN EQ: $5,000 and $10,000/mo AI SDR (White Space + Miniloop) + 1,513 S&amp;M HC (SEC)</t>
+        </is>
+      </c>
+      <c r="F9" s="649" t="inlineStr">
+        <is>
+          <t>EQ: Roles=0.25×1,513=378; Low=378×$5,000×12=$22.68m; High=378×$10,000×12=$45.36m; C9=avg=$34.0m. MODEL CONST: 0.25 outbound share. NOT in EQ: 11x Growth $3,750.</t>
         </is>
       </c>
       <c r="G9" s="612" t="inlineStr">
@@ -5515,9 +5573,14 @@
           <t>Go to AI_Operating!D10 (AI infrastructure)</t>
         </is>
       </c>
-      <c r="H9" s="612" t="inlineStr">
-        <is>
-          <t>Secondary EQ $/mo: Miniloop 11x pricing table Entry $5k / Enterprise $10k+</t>
+      <c r="H9" s="593" t="inlineStr">
+        <is>
+          <t>Miniloop Entry $5,000 / Enterprise $10,000+</t>
+        </is>
+      </c>
+      <c r="I9" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: $5,000-10,000  →  "11x.ai (Alice) $5,000-10,000+"  |  Ctrl+F: $10,000-$15,000  →  "Enterprise $10,000-$15,000+"  |  Ctrl+F: 1,513 in sales  →  "1,513 in sales and marketing"  |  25% share: N/A (MODEL CONST)</t>
         </is>
       </c>
     </row>
@@ -5527,7 +5590,7 @@
           <t>S&amp;M expense growth Y2+</t>
         </is>
       </c>
-      <c r="C10" s="608" t="n">
+      <c r="C10" s="644" t="n">
         <v>0.02</v>
       </c>
       <c r="D10" s="609" t="inlineStr">
@@ -5535,14 +5598,14 @@
           <t>Caps future marketing cost increases. Reasonable because AI scales infinitely without needing proportional headcount additions, severing the link between revenue growth and human hiring.</t>
         </is>
       </c>
-      <c r="E10" s="630" t="inlineStr">
-        <is>
-          <t>IN EQ: C10=2% = Fed longer-run inflation target 2% (FOMC)</t>
-        </is>
-      </c>
-      <c r="F10" s="632" t="inlineStr">
-        <is>
-          <t>EQ: Payroll_t = Payroll_{t−1}×(1.02). Y2=270.98×1.02=$276.40m. SOURCED in EQ: 0.02 from Fed 2% longer-run inflation goal. SOURCED $ start: 270.98 from row7. Removed: Gartner qualitative agent note (supplied no numeric 2%).</t>
+      <c r="E10" s="645" t="inlineStr">
+        <is>
+          <t>IN EQ: C10=2% = Fed longer-run inflation goal of 2 percent (FOMC FAQ)</t>
+        </is>
+      </c>
+      <c r="F10" s="646" t="inlineStr">
+        <is>
+          <t>EQ: Payroll_t=Payroll_{t−1}×(1.02). SOURCED: 2 percent longer-run inflation target.</t>
         </is>
       </c>
       <c r="G10" s="612" t="inlineStr">
@@ -5550,9 +5613,14 @@
           <t>Go to AI_Operating!E7 (payroll Y2+)</t>
         </is>
       </c>
-      <c r="H10" s="612" t="inlineStr">
-        <is>
-          <t>www.federalreserve.gov/monetarypolicy/files/FOMC_LongerRunGoals.pdf</t>
+      <c r="H10" s="593" t="inlineStr">
+        <is>
+          <t>FOMC Statement on Longer-Run Goals (PDF)</t>
+        </is>
+      </c>
+      <c r="I10" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 2 percent  →  "the FOMC judges that inflation of 2 percent over the longer run"</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5630,7 @@
           <t>G&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="C11" s="608" t="n">
+      <c r="C11" s="644" t="n">
         <v>0.18</v>
       </c>
       <c r="D11" s="609" t="inlineStr">
@@ -5570,14 +5638,14 @@
           <t>General administrative overhead costs. Reasonable for a public-to-private SaaS company, maintaining standard corporate expenses without relying on unrealistic operational magic outside of sales.</t>
         </is>
       </c>
-      <c r="E11" s="638" t="inlineStr">
-        <is>
-          <t>IN EQ: C11=18% = Blossom Street 2025 public SaaS median G&amp;A 18% of rev — click</t>
-        </is>
-      </c>
-      <c r="F11" s="631" t="inlineStr">
-        <is>
-          <t>EQ: G&amp;A=Rev×0.18 → Y1 1335.73×0.18=$240.43m. SOURCED in EQ: 18% = Blossom Street median G&amp;A for SaaS IPOs-since-2017 in FY2025 (18%, 20%, 21%, 23% for 2025–2022). NOT in EQ: ZI filing G&amp;A 295.3/1214.3=24.3% (would be Y1 $324.9m).</t>
+      <c r="E11" s="645" t="inlineStr">
+        <is>
+          <t>IN EQ: C11=18% = Blossom Street 2025 public SaaS median G&amp;A 18% of revenue</t>
+        </is>
+      </c>
+      <c r="F11" s="643" t="inlineStr">
+        <is>
+          <t>EQ: G&amp;A=Rev×0.18. SOURCED: G&amp;A was 18% in 2025 (medians). NOT in EQ: ZI filing ~24.3%.</t>
         </is>
       </c>
       <c r="G11" s="612" t="inlineStr">
@@ -5585,7 +5653,16 @@
           <t>Go to AI_Operating!D12 (G&amp;A)</t>
         </is>
       </c>
-      <c r="H11" s="612" t="n"/>
+      <c r="H11" s="593" t="inlineStr">
+        <is>
+          <t>Table MEDIAN G&amp;A as % of Revenue = 18%</t>
+        </is>
+      </c>
+      <c r="I11" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: G&amp;A was 18%  →  "G&amp;A was 18%, 20%, 21, and 23% of revenue in 2025, 2024, 2023, and 2022."  |  Alt table Ctrl+F: MEDIAN then G&amp;A col 18%</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="96" customHeight="1" s="244">
       <c r="B12" s="613" t="inlineStr">
@@ -5601,14 +5678,14 @@
           <t>Lowers physical equipment spending. Reasonable because firing 15% of the sales team permanently eliminates the need to purchase and refresh their laptops and hardware.</t>
         </is>
       </c>
-      <c r="E12" s="631" t="inlineStr">
-        <is>
-          <t>C12=5% CapEx cut = MODEL CONST (no sourced 5%). Device $ in SDR stacks is qualitative only.</t>
-        </is>
-      </c>
-      <c r="F12" s="631" t="inlineStr">
-        <is>
-          <t>EQ: CapEx_AI=Rev×0.02×(1−0.05)=Rev×0.019 → Y1=$25.38m. MODEL CONST: 0.05. No source prints a 5% CapEx cut — not citing hardware articles as if they did.</t>
+      <c r="E12" s="643" t="inlineStr">
+        <is>
+          <t>C12=5% CapEx cut = MODEL CONST (no source prints 5%).</t>
+        </is>
+      </c>
+      <c r="F12" s="643" t="inlineStr">
+        <is>
+          <t>EQ: CapEx_AI=Rev×0.02×(1−0.05)=Rev×0.019. MODEL CONST: 0.05.</t>
         </is>
       </c>
       <c r="G12" s="612" t="inlineStr">
@@ -5616,7 +5693,12 @@
           <t>Go to AI_Operating!D19 (CapEx)</t>
         </is>
       </c>
-      <c r="H12" s="612" t="n"/>
+      <c r="H12" s="593" t="n"/>
+      <c r="I12" s="643" t="inlineStr">
+        <is>
+          <t>5% CapEx cut: N/A — MODEL CONST (no Ctrl+F string; no source link).</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="96" customHeight="1" s="244">
       <c r="B13" s="607" t="inlineStr">
@@ -5632,14 +5714,14 @@
           <t>Speeds up cash collection from clients. Reasonable because automated AI billing systems can aggressively follow up on late invoices, freeing up cash for debt paydown.</t>
         </is>
       </c>
-      <c r="E13" s="637" t="inlineStr">
-        <is>
-          <t>~80 DSO motivates WC but is NOT equal to C13=10%. 10% = MODEL CONST.</t>
-        </is>
-      </c>
-      <c r="F13" s="631" t="inlineStr">
-        <is>
-          <t>EQ: ΔNWC_AI=ΔRev×0.02×0.90 → Y1 121.43×0.018=$2.19m. MODEL CONST: 0.10 improvement. 80 DSO ≠ 10% improvement rate (80/365≈21.9% AR/sales stock).</t>
+      <c r="E13" s="643" t="inlineStr">
+        <is>
+          <t>C13=10% WC improvement = MODEL CONST (no source equals 10%).</t>
+        </is>
+      </c>
+      <c r="F13" s="643" t="inlineStr">
+        <is>
+          <t>EQ: ΔNWC_AI=ΔRev×0.02×0.90. MODEL CONST: 0.10. Removed prior ~80 DSO link (did not equal 10%).</t>
         </is>
       </c>
       <c r="G13" s="612" t="inlineStr">
@@ -5647,7 +5729,12 @@
           <t>Go to AI_Operating!D20 (ΔNWC)</t>
         </is>
       </c>
-      <c r="H13" s="612" t="n"/>
+      <c r="H13" s="593" t="n"/>
+      <c r="I13" s="643" t="inlineStr">
+        <is>
+          <t>10% WC improvement: N/A — MODEL CONST (no Ctrl+F string; no source link).</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="96" customHeight="1" s="244">
       <c r="B14" s="613" t="inlineStr">
@@ -5655,7 +5742,7 @@
           <t>SOFR</t>
         </is>
       </c>
-      <c r="C14" s="616" t="n">
+      <c r="C14" s="644" t="n">
         <v>0.043</v>
       </c>
       <c r="D14" s="609" t="inlineStr">
@@ -5663,14 +5750,14 @@
           <t>The foundational secured lending interest rate. Reasonable and historically accurate for the macroeconomic environment, properly reflecting actual institutional baseline borrowing costs.</t>
         </is>
       </c>
-      <c r="E14" s="638" t="inlineStr">
-        <is>
-          <t>IN EQ: C14=4.30% = SOFR 2024 calendar-year LOW (Global-Rates / NY Fed series) — click</t>
-        </is>
-      </c>
-      <c r="F14" s="631" t="inlineStr">
-        <is>
-          <t>EQ: rates use C14 directly (TLA=C14+C15). SOURCED in EQ: 4.30% = lowest SOFR print in 2024 (Global-Rates summary of NY Fed SOFR; Dec 2024 trough). Official series: FRED/NY Fed. NOT used: latest FRED ~3.62% (would lower interest vs this underwrite).</t>
+      <c r="E14" s="645" t="inlineStr">
+        <is>
+          <t>IN EQ: C14=4.30% = SOFR 2024 calendar-year Lowest (Global-Rates summary of NY Fed)</t>
+        </is>
+      </c>
+      <c r="F14" s="643" t="inlineStr">
+        <is>
+          <t>EQ: rates use C14. SOURCED: Lowest SOFR in 2024 = 4.30%. NOT used: latest FRED ~3.62%.</t>
         </is>
       </c>
       <c r="G14" s="612" t="inlineStr">
@@ -5678,9 +5765,14 @@
           <t>Go to Debt_Sweep_AI!C12 (TLA rate uses SOFR)</t>
         </is>
       </c>
-      <c r="H14" s="612" t="inlineStr">
-        <is>
-          <t>Official SOFR publisher: NY Fed</t>
+      <c r="H14" s="593" t="inlineStr">
+        <is>
+          <t>NY Fed SOFR publisher</t>
+        </is>
+      </c>
+      <c r="I14" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 4.30  →  table row "Lowest … 4.30 %" (SOFR 2024 First/Last/Highest/Lowest/Average)</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5782,7 @@
           <t>Term Loan A spread</t>
         </is>
       </c>
-      <c r="C15" s="616" t="n">
+      <c r="C15" s="644" t="n">
         <v>0.04</v>
       </c>
       <c r="D15" s="609" t="inlineStr">
@@ -5698,14 +5790,14 @@
           <t>The risk premium for senior debt. Reasonable for a standard LBO, reflecting typical syndicated commercial bank pricing for secured corporate borrowing.</t>
         </is>
       </c>
-      <c r="E15" s="638" t="inlineStr">
-        <is>
-          <t>IN EQ: C15=+400bps = lower bound of senior Term Loan A SOFR+400–500bps (CT Acquisitions) — click</t>
-        </is>
-      </c>
-      <c r="F15" s="631" t="inlineStr">
-        <is>
-          <t>EQ: TLA_rate=4.30%+4.00%=8.30%. SOURCED in EQ: +400bps = floor of CT Acquisitions senior term loan A band SOFR+400–500bps (2026 LMM acquisition financing). Removed prior Ryan O’Connell 275–375bps band (did not contain 400).</t>
+      <c r="E15" s="645" t="inlineStr">
+        <is>
+          <t>IN EQ: C15=+400bps = floor of senior Term Loan A SOFR+400-500 bps (CT Acquisitions)</t>
+        </is>
+      </c>
+      <c r="F15" s="643" t="inlineStr">
+        <is>
+          <t>EQ: TLA_rate=4.30%+4.00%=8.30%. SOURCED: SOFR + 400-500 bps on Senior term loan A.</t>
         </is>
       </c>
       <c r="G15" s="612" t="inlineStr">
@@ -5713,9 +5805,14 @@
           <t>Go to Assumptions_Drivers!C27 (TLA rate)</t>
         </is>
       </c>
-      <c r="H15" s="612" t="inlineStr">
-        <is>
-          <t>Also: senior bank term loan SOFR+350–500 (400 in band)</t>
+      <c r="H15" s="593" t="inlineStr">
+        <is>
+          <t>Also: senior debt SOFR plus 400 to 500</t>
+        </is>
+      </c>
+      <c r="I15" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 400-500  →  "Senior term loan A | … | SOFR + 400-500 bps"</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5822,7 @@
           <t>Term Loan B spread</t>
         </is>
       </c>
-      <c r="C16" s="616" t="n">
+      <c r="C16" s="644" t="n">
         <v>0.05</v>
       </c>
       <c r="D16" s="609" t="inlineStr">
@@ -5733,14 +5830,14 @@
           <t>The risk premium for riskier debt. Reasonable, as Term Loan B is usually held by institutional investors requiring higher yields for slightly higher risk.</t>
         </is>
       </c>
-      <c r="E16" s="630" t="inlineStr">
-        <is>
-          <t>IN EQ: TLB SOFR+300–500bps → C16=+500bps = upper bound of source</t>
-        </is>
-      </c>
-      <c r="F16" s="632" t="inlineStr">
-        <is>
-          <t>EQ: TLB_rate=4.30%+5.00%=9.30%. SOURCED in EQ: 500bps = top of published SOFR+300–500 band. Source upper bound = driver.</t>
+      <c r="E16" s="645" t="inlineStr">
+        <is>
+          <t>IN EQ: TLB SOFR+300-500 bps → C16=+500bps = upper bound</t>
+        </is>
+      </c>
+      <c r="F16" s="646" t="inlineStr">
+        <is>
+          <t>EQ: TLB_rate=4.30%+5.00%=9.30%. SOURCED: SOFR + 300-500 basis points for TLB.</t>
         </is>
       </c>
       <c r="G16" s="612" t="inlineStr">
@@ -5748,9 +5845,14 @@
           <t>Go to Assumptions_Drivers!C28 (TLB rate)</t>
         </is>
       </c>
-      <c r="H16" s="612" t="inlineStr">
-        <is>
-          <t>ryanoconnellfinance.com/lbo-debt-structure/</t>
+      <c r="H16" s="593" t="inlineStr">
+        <is>
+          <t>Table: Term Loan B | SOFR + 300-500 bps | 1% annual</t>
+        </is>
+      </c>
+      <c r="I16" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 300-500  →  "TLB pricing is typically SOFR + 300-500 basis points"  |  table Ctrl+F: Term Loan B</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5862,7 @@
           <t>Mandatory amortization</t>
         </is>
       </c>
-      <c r="C17" s="608" t="n">
+      <c r="C17" s="644" t="n">
         <v>0.01</v>
       </c>
       <c r="D17" s="609" t="inlineStr">
@@ -5768,14 +5870,14 @@
           <t>Required annual principal repayment. Highly reasonable and standard market practice for leveraged loans, forcing a tiny minimum debt reduction each year.</t>
         </is>
       </c>
-      <c r="E17" s="630" t="inlineStr">
-        <is>
-          <t>IN EQ: ~1%/yr TLB amort → C17=1%; principal≈$915.5m</t>
-        </is>
-      </c>
-      <c r="F17" s="632" t="inlineStr">
-        <is>
-          <t>EQ: Mandatory=915.5×0.01=$9.155m/yr. SOURCED: 1% amort standard. Source number = driver.</t>
+      <c r="E17" s="645" t="inlineStr">
+        <is>
+          <t>IN EQ: ~1%/yr TLB amort → C17=1%</t>
+        </is>
+      </c>
+      <c r="F17" s="646" t="inlineStr">
+        <is>
+          <t>EQ: Mandatory≈915.5×0.01=$9.155m/yr. SOURCED: 1% annual amortization.</t>
         </is>
       </c>
       <c r="G17" s="612" t="inlineStr">
@@ -5783,9 +5885,14 @@
           <t>Go to Debt_Sweep_AI!D5 (Mandatory 1%)</t>
         </is>
       </c>
-      <c r="H17" s="612" t="inlineStr">
-        <is>
-          <t>clearvaluelending.com/glossary/term-loan-b</t>
+      <c r="H17" s="593" t="inlineStr">
+        <is>
+          <t>ClearValue: "minimal amortization (1% annually)"</t>
+        </is>
+      </c>
+      <c r="I17" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 1% annual  →  "minimal amortization (1% annually)"  |  Alt: "1% per year (nominal)"</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5902,7 @@
           <t>Cash sweep %</t>
         </is>
       </c>
-      <c r="C18" s="608" t="n">
+      <c r="C18" s="644" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="609" t="inlineStr">
@@ -5803,14 +5910,14 @@
           <t>Dedicates all excess cash to debt. Reasonable and standard for maximizing LBO returns, ensuring every free dollar generated immediately aggressively reduces outstanding leverage.</t>
         </is>
       </c>
-      <c r="E18" s="638" t="inlineStr">
-        <is>
-          <t>IN EQ: C18=100% = upper bound of LBO excess-cash-flow sweep 50–100%; models often use 100% — click</t>
-        </is>
-      </c>
-      <c r="F18" s="631" t="inlineStr">
-        <is>
-          <t>EQ: Sweep=1.00×max(0,FCF−Mandatory). SOURCED in EQ: Ryan O’Connell LBO fundamentals — ECF sweep typically 50–100% of excess FCF; LBO models typically use 100% for max delever path. 100% = upper bound of that published band. NOT claiming every credit agreement is 100%.</t>
+      <c r="E18" s="645" t="inlineStr">
+        <is>
+          <t>IN EQ: C18=100% = upper bound of ECF sweep 50-100%; models often use 100%</t>
+        </is>
+      </c>
+      <c r="F18" s="643" t="inlineStr">
+        <is>
+          <t>EQ: Sweep=1.00×max(0,FCF−Mandatory). SOURCED: typically 50-100%; typically modeled at 100%.</t>
         </is>
       </c>
       <c r="G18" s="612" t="inlineStr">
@@ -5818,7 +5925,12 @@
           <t>Go to Debt_Sweep_AI!E5 (Total paydown)</t>
         </is>
       </c>
-      <c r="H18" s="612" t="n"/>
+      <c r="H18" s="593" t="n"/>
+      <c r="I18" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 50-100%  →  "apply 50-100% of annual excess free cash flow"  |  Ctrl+F: modeled at 100%  →  "typically modeled at 100%"</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="96" customHeight="1" s="244">
       <c r="B19" s="607" t="inlineStr">
@@ -5826,7 +5938,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="C19" s="608" t="n">
+      <c r="C19" s="644" t="n">
         <v>0.21</v>
       </c>
       <c r="D19" s="609" t="inlineStr">
@@ -5834,14 +5946,14 @@
           <t>Corporate income tax obligation. Perfectly reasonable because it strictly matches the current standard U.S. federal statutory corporate tax rate without aggressive tax-dodging assumptions.</t>
         </is>
       </c>
-      <c r="E19" s="630" t="inlineStr">
+      <c r="E19" s="645" t="inlineStr">
         <is>
           <t>IN EQ: US federal CIT=21% → C19=0.21 (PwC)</t>
         </is>
       </c>
-      <c r="F19" s="632" t="inlineStr">
-        <is>
-          <t>EQ: Tax=EBT×0.21. SOURCED: 21% statutory. Source number = driver.</t>
+      <c r="F19" s="646" t="inlineStr">
+        <is>
+          <t>EQ: Tax=EBT×0.21. SOURCED: flat rate of 21%.</t>
         </is>
       </c>
       <c r="G19" s="612" t="inlineStr">
@@ -5849,9 +5961,14 @@
           <t>Go to AI_Operating!D18 (Net income)</t>
         </is>
       </c>
-      <c r="H19" s="612" t="inlineStr">
-        <is>
-          <t>tradingeconomics.com/united-states/corporate-tax-rate</t>
+      <c r="H19" s="593" t="inlineStr">
+        <is>
+          <t>Trading Economics: 21 percent</t>
+        </is>
+      </c>
+      <c r="I19" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: flat rate of 21  →  "taxes resident corporations at a flat rate of 21%."</t>
         </is>
       </c>
     </row>
@@ -5861,22 +5978,22 @@
           <t>Exit EV/EBITDA multiple</t>
         </is>
       </c>
-      <c r="C20" s="617" t="n">
-        <v>13</v>
+      <c r="C20" s="648" t="n">
+        <v>12.9</v>
       </c>
       <c r="D20" s="609" t="inlineStr">
         <is>
-          <t>The valuation multiple upon selling. Reasonable to keep it conservative; relying on a 13x exit assumes no market inflation, proving returns come from operational growth.</t>
-        </is>
-      </c>
-      <c r="E20" s="638" t="inlineStr">
-        <is>
-          <t>IN EQ: C20=13x ≈ Aventis private SaaS EV/EBITDA lower quartile 12.8x–12.9x (round) — click</t>
-        </is>
-      </c>
-      <c r="F20" s="631" t="inlineStr">
-        <is>
-          <t>EQ: Exit_EV=Y5_EBITDA×13. SOURCED in EQ: Aventis Advisors private SaaS EV/EBITDA 1st quartile 12.9x (table) / ~12.8x (text) → model rounds to 13.0x conservative exit. NOT in EQ: PE SaaS entry/exit bands 15–22x / 20–28x (would raise exit EV).</t>
+          <t>The valuation multiple upon selling. Set to 12.9x to match Aventis private SaaS EV/EBITDA 1st quartile (Ctrl+F 12.9x)—conservative lower-quartile exit, not PE median.</t>
+        </is>
+      </c>
+      <c r="E20" s="645" t="inlineStr">
+        <is>
+          <t>IN EQ: C20=12.9x = Aventis private SaaS EV/EBITDA 1st quartile 12.9x (was 13 round)</t>
+        </is>
+      </c>
+      <c r="F20" s="643" t="inlineStr">
+        <is>
+          <t>EQ: Exit_EV=Y5_EBITDA×12.9. SOURCED: table 1st quartile EV/EBITDA = 12.9x. Text also ~12.8x.</t>
         </is>
       </c>
       <c r="G20" s="612" t="inlineStr">
@@ -5884,7 +6001,12 @@
           <t>Go to LBO!D17 (Exit multiple)</t>
         </is>
       </c>
-      <c r="H20" s="612" t="n"/>
+      <c r="H20" s="593" t="n"/>
+      <c r="I20" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 12.9x  →  table "EV/EBITDA | … | 1st quartile | 12.9x"  |  Alt Ctrl+F: 12.8x  →  "lower quartile are closer to 12.8x"</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="96" customHeight="1" s="244">
       <c r="B21" s="607" t="inlineStr">
@@ -5892,7 +6014,7 @@
           <t>S&amp;M baseline ($m)</t>
         </is>
       </c>
-      <c r="C21" s="614" t="n">
+      <c r="C21" s="650" t="n">
         <v>425</v>
       </c>
       <c r="D21" s="609" t="inlineStr">
@@ -5900,14 +6022,14 @@
           <t>This is historical assumptions without AI. Total initial sales spend is reasonable, representing roughly 35% of FY24 revenue, perfectly aligning with standard SaaS benchmarks.</t>
         </is>
       </c>
-      <c r="E21" s="630" t="inlineStr">
-        <is>
-          <t>IN EQ: Rev $1,214.3m; choose 35%≈filing S&amp;M 34.1% ($414.1m) → C21=$425m</t>
-        </is>
-      </c>
-      <c r="F21" s="632" t="inlineStr">
-        <is>
-          <t>EQ: 0.35×1214.3=$425.0m=C21. SOURCED: 1214.3 rev and 414.1 S&amp;M (34.1%) from ZI FY24. MODEL ROUND: 35% near 34.1%.</t>
+      <c r="E21" s="645" t="inlineStr">
+        <is>
+          <t>IN EQ: Rev $1,214.3m; S&amp;M $414.1m (34.1%) → model 35%→$425m</t>
+        </is>
+      </c>
+      <c r="F21" s="646" t="inlineStr">
+        <is>
+          <t>EQ: 0.35×1214.3=$425.0m=C21. SOURCED: 1,214.3 and 414.1. MODEL ROUND: 35% near 34.1%.</t>
         </is>
       </c>
       <c r="G21" s="612" t="inlineStr">
@@ -5915,9 +6037,14 @@
           <t>Go to AI_Operating!C9 (S&amp;M human FY24A)</t>
         </is>
       </c>
-      <c r="H21" s="612" t="inlineStr">
-        <is>
-          <t>www.key.com/content/dam/kco/documents/businesses___institutions/2024_kbcm_s</t>
+      <c r="H21" s="593" t="inlineStr">
+        <is>
+          <t>SEC 10-K Sales and marketing $414.1</t>
+        </is>
+      </c>
+      <c r="I21" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: $1,214.3  and  Ctrl+F: 414.1  →  Revenue $1,214.3 / Sales and marketing $414.1  |  425: MODEL ROUND of 35%×1214.3</t>
         </is>
       </c>
     </row>
@@ -5935,14 +6062,14 @@
           <t>This is historical assumptions without AI. The fixed salary portion is reasonable, representing 75% of S&amp;M, accurately reflecting that human software sales floors are base-salary heavy.</t>
         </is>
       </c>
-      <c r="E22" s="630" t="inlineStr">
-        <is>
-          <t>IN EQ: ~70% base OTE → set 75%×$425m=$318.8m</t>
-        </is>
-      </c>
-      <c r="F22" s="632" t="inlineStr">
-        <is>
-          <t>EQ: C22=0.75×425=$318.8m. SOURCED: ~70% base (SyncGTM). MODEL: 75% of S&amp;M pool near that mix. SOURCED $: 425 from row21.</t>
+      <c r="E22" s="642" t="inlineStr">
+        <is>
+          <t>IN EQ: ~70% base OTE → model 75%×$425m=$318.8m</t>
+        </is>
+      </c>
+      <c r="F22" s="646" t="inlineStr">
+        <is>
+          <t>EQ: C22=0.75×425=$318.8m. SOURCED mix: 70/30. MODEL: 75% of S&amp;M pool.</t>
         </is>
       </c>
       <c r="G22" s="612" t="inlineStr">
@@ -5950,7 +6077,12 @@
           <t>Go to AI_Operating!C7 (Payroll FY24A)</t>
         </is>
       </c>
-      <c r="H22" s="612" t="n"/>
+      <c r="H22" s="593" t="n"/>
+      <c r="I22" s="643" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 70/30  →  "70/30 base/variable split"  |  318.8 / 75%: MODEL carve (not printed as $318.8)</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="96" customHeight="1" s="244">
       <c r="B23" s="607" t="inlineStr">
@@ -5966,14 +6098,14 @@
           <t>This is historical assumptions without AI. The variable payout is reasonable, calculating exactly to the remaining 25% of the budget, representing standard quota-based enterprise sales incentives.</t>
         </is>
       </c>
-      <c r="E23" s="630" t="inlineStr">
+      <c r="E23" s="642" t="inlineStr">
         <is>
           <t>IN EQ: residual 25%×$425m=$106.2m (near sourced ~30–35% variable)</t>
         </is>
       </c>
-      <c r="F23" s="632" t="inlineStr">
-        <is>
-          <t>EQ: C23=0.25×425=$106.2m; 318.8+106.2=425. SOURCED: variable ~30–35% OTE. MODEL: 25% of S&amp;M as commission carve.</t>
+      <c r="F23" s="646" t="inlineStr">
+        <is>
+          <t>EQ: C23=0.25×425=$106.2m. SOURCED: 30–35% variable. MODEL: 25% of S&amp;M as commission carve.</t>
         </is>
       </c>
       <c r="G23" s="612" t="inlineStr">
@@ -5981,9 +6113,14 @@
           <t>Go to AI_Operating!C8 (Commissions FY24A)</t>
         </is>
       </c>
-      <c r="H23" s="612" t="inlineStr">
-        <is>
-          <t>syncgtm.com/blog/how-to-pay-sales-development-rep</t>
+      <c r="H23" s="593" t="inlineStr">
+        <is>
+          <t>70/30 pay article</t>
+        </is>
+      </c>
+      <c r="I23" s="643" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 30–35%  →  "Commission accounts for 30–35% of total pay"  |  106.2 / 25%: MODEL carve</t>
         </is>
       </c>
     </row>
@@ -5993,7 +6130,7 @@
           <t>CapEx base % of rev</t>
         </is>
       </c>
-      <c r="C24" s="608" t="n">
+      <c r="C24" s="644" t="n">
         <v>0.02</v>
       </c>
       <c r="D24" s="609" t="inlineStr">
@@ -6001,14 +6138,14 @@
           <t>This is historical assumptions without AI. Normal hardware and capitalized software spending is reasonable for asset-light tech companies investing heavily in code rather than factories.</t>
         </is>
       </c>
-      <c r="E24" s="630" t="inlineStr">
-        <is>
-          <t>IN EQ: SaaS CapEx typically 1–3% of rev → C24=2% = midpoint of sourced band</t>
-        </is>
-      </c>
-      <c r="F24" s="632" t="inlineStr">
-        <is>
-          <t>EQ: CapEx=Rev×0.02 → Y1=$26.71m. SOURCED: pure-play SaaS CapEx 1–3% of revenue (SaaSDB). 2% = midpoint of 1–3%. Source band drives driver.</t>
+      <c r="E24" s="645" t="inlineStr">
+        <is>
+          <t>IN EQ band: SaaS CapEx 1–3% of rev (SaaSDB) → C24=2% = midpoint of that band</t>
+        </is>
+      </c>
+      <c r="F24" s="646" t="inlineStr">
+        <is>
+          <t>EQ: CapEx=Rev×0.02. SOURCED band: CapEx of 1–3% of revenue. MODEL midpoint: 2%. NOTE: page uses en-dash 1–3% (Ctrl+F '1-3%' with hyphen may miss).</t>
         </is>
       </c>
       <c r="G24" s="612" t="inlineStr">
@@ -6016,9 +6153,10 @@
           <t>Go to AI_Operating!D19 (CapEx)</t>
         </is>
       </c>
-      <c r="H24" s="612" t="inlineStr">
-        <is>
-          <t>www.businesswire.com/news/home/20250225694335/en/ZoomInfo-Announces-Fourth-</t>
+      <c r="H24" s="593" t="n"/>
+      <c r="I24" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: CapEx of 1  →  "Most pure-play SaaS companies report CapEx of 1–3% of revenue"  |  Tip: search CapEx of 1 (en-dash); plain 1-3% may miss.  |  2%: MODEL midpoint of that band</t>
         </is>
       </c>
     </row>
@@ -6036,14 +6174,14 @@
           <t>This is historical assumptions without AI. Normal working capital needs are reasonable, showing that as revenue grows, a small percentage of cash gets tied up in daily operations.</t>
         </is>
       </c>
-      <c r="E25" s="631" t="inlineStr">
-        <is>
-          <t>C25=2% ΔNWC/ΔRev = MODEL CONST. ~80 DSO is not equal to 2%.</t>
-        </is>
-      </c>
-      <c r="F25" s="631" t="inlineStr">
-        <is>
-          <t>EQ: ΔNWC=ΔRev×0.02 → Y1=$2.43m. MODEL CONST: 0.02. No source equals a 2% ΔNWC/ΔRev plug (stock NWC/rev metrics are different).</t>
+      <c r="E25" s="643" t="inlineStr">
+        <is>
+          <t>C25=2% ΔNWC/ΔRev = MODEL CONST (no source equals 2%).</t>
+        </is>
+      </c>
+      <c r="F25" s="643" t="inlineStr">
+        <is>
+          <t>EQ: ΔNWC=ΔRev×0.02. MODEL CONST: 0.02.</t>
         </is>
       </c>
       <c r="G25" s="612" t="inlineStr">
@@ -6051,7 +6189,12 @@
           <t>Go to AI_Operating!D20 (ΔNWC)</t>
         </is>
       </c>
-      <c r="H25" s="612" t="n"/>
+      <c r="H25" s="593" t="n"/>
+      <c r="I25" s="643" t="inlineStr">
+        <is>
+          <t>2% WC plug: N/A — MODEL CONST (no Ctrl+F string; no source link).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="618" t="inlineStr">
@@ -6075,14 +6218,14 @@
           <t>Total Term Loan A interest. Mathematically correct and reasonable for the total borrowing cost demanded by senior lenders in this specific rate environment.</t>
         </is>
       </c>
-      <c r="E27" s="630" t="inlineStr">
-        <is>
-          <t>EQ: C27=C14+C15 only (inputs from rows 14–15)</t>
-        </is>
-      </c>
-      <c r="F27" s="632" t="inlineStr">
-        <is>
-          <t>EQ: 4.30%+4.00%=8.30%. Interest_TLA=TLA_beg×0.083. No third-party source beyond C14/C15 component rows.</t>
+      <c r="E27" s="647" t="inlineStr">
+        <is>
+          <t>EQ only: C27=C14+C15 (see rows 14–15 Verbatim)</t>
+        </is>
+      </c>
+      <c r="F27" s="646" t="inlineStr">
+        <is>
+          <t>EQ: 4.30%+4.00%=8.30%. Component Ctrl+F strings on rows 14 and 15.</t>
         </is>
       </c>
       <c r="G27" s="612" t="inlineStr">
@@ -6090,7 +6233,12 @@
           <t>Go to Debt_Sweep_AI!C12 (TLA rate)</t>
         </is>
       </c>
-      <c r="H27" s="612" t="n"/>
+      <c r="H27" s="593" t="n"/>
+      <c r="I27" s="647" t="inlineStr">
+        <is>
+          <t>No separate third-party quote — sum of sourced C14 and C15.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="96" customHeight="1" s="244">
       <c r="B28" s="607" t="inlineStr">
@@ -6107,14 +6255,14 @@
           <t>Total Term Loan B interest. Mathematically correct and perfectly reasonable, pricing the institutional debt risk appropriately above the safer Term Loan A.</t>
         </is>
       </c>
-      <c r="E28" s="630" t="inlineStr">
-        <is>
-          <t>EQ: C28=C14+C16 only; C16=+500bps sourced as TLB upper bound on row16</t>
-        </is>
-      </c>
-      <c r="F28" s="632" t="inlineStr">
-        <is>
-          <t>EQ: 4.30%+5.00%=9.30%. Interest_TLB=TLB_beg×0.093. Component sources on rows 14 &amp; 16.</t>
+      <c r="E28" s="647" t="inlineStr">
+        <is>
+          <t>EQ only: C28=C14+C16 (see rows 14 &amp; 16 Verbatim)</t>
+        </is>
+      </c>
+      <c r="F28" s="646" t="inlineStr">
+        <is>
+          <t>EQ: 4.30%+5.00%=9.30%. Component Ctrl+F strings on rows 14 and 16.</t>
         </is>
       </c>
       <c r="G28" s="612" t="inlineStr">
@@ -6122,17 +6270,22 @@
           <t>Go to Debt_Sweep_AI!D12 (TLB rate)</t>
         </is>
       </c>
-      <c r="H28" s="612" t="n"/>
+      <c r="H28" s="593" t="n"/>
+      <c r="I28" s="647" t="inlineStr">
+        <is>
+          <t>No separate third-party quote — sum of sourced C14 and C16.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="72" customHeight="1" s="244">
       <c r="B29" s="618" t="inlineStr">
         <is>
-          <t>AI $34m — sources that are IN the equation:</t>
+          <t>AI $34m IN-EQ sources + Ctrl+F:</t>
         </is>
       </c>
       <c r="C29" s="620" t="inlineStr">
         <is>
-          <t>(1) https://www.whitespacesolutions.ai/content/ai-sdr-pricing-guide-2026 → 11x Alice $5,000–$10,000+/mo. (2) https://www.miniloop.ai/blog/11x-pricing → Entry $5,000 / Enterprise $10,000+. (3) https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm → 1,513 S&amp;M employees. (4) MODEL CONST 25% outbound share. NOT in EQ: 11x Growth $3,750/mo https://www.11x.ai/products/alice/pricing</t>
+          <t>White Space Ctrl+F $5,000-10,000 | Miniloop Ctrl+F $10,000-$15,000 | SEC Ctrl+F 1,513 in sales | MODEL CONST 25% outbound | NOT in EQ: 11x $3,750</t>
         </is>
       </c>
       <c r="D29" s="621" t="n"/>
@@ -6142,7 +6295,7 @@
     <row r="30">
       <c r="B30" s="618" t="inlineStr">
         <is>
-          <t>ZI 10-K S&amp;M headcount 1,513 (EQ input):</t>
+          <t>ZI 10-K S&amp;M HC 1,513:</t>
         </is>
       </c>
       <c r="C30" s="593" t="inlineStr">
@@ -6154,7 +6307,7 @@
     <row r="31">
       <c r="B31" s="623" t="inlineStr">
         <is>
-          <t>11x official Growth $3,750/mo (NOT in EQ — below $5k low):</t>
+          <t>11x Growth $3,750 NOT in EQ:</t>
         </is>
       </c>
       <c r="C31" s="640" t="inlineStr">
@@ -6183,64 +6336,60 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12246,7 +12395,7 @@
     <row r="34" ht="42" customHeight="1" s="244">
       <c r="B34" s="575" t="inlineStr">
         <is>
-          <t>Exit EV @ 13x ($m)</t>
+          <t>Exit EV @ 12.9x ($m)</t>
         </is>
       </c>
       <c r="C34" s="626" t="n">
@@ -12292,17 +12441,17 @@
         </is>
       </c>
       <c r="C36" s="626" t="n">
-        <v>2201.623513516699</v>
+        <v>2180.4024674507</v>
       </c>
       <c r="D36" s="626" t="n">
-        <v>6206.151999184804</v>
+        <v>6291.958085621143</v>
       </c>
       <c r="E36" s="626" t="n">
-        <v>4004.528485668105</v>
+        <v>4111.555618170443</v>
       </c>
       <c r="F36" s="625" t="inlineStr">
         <is>
-          <t>Total equity payout; AI strategy increased final payout by $4,004.5m to $6,206.2m.</t>
+          <t>Total equity payout; AI strategy changed final payout by $4,111.6m to $6,292.0m (exit 12.9x).</t>
         </is>
       </c>
     </row>
@@ -12313,17 +12462,17 @@
         </is>
       </c>
       <c r="C37" s="627" t="n">
-        <v>1.17652754423803</v>
+        <v>1.16518721058838</v>
       </c>
       <c r="D37" s="627" t="n">
-        <v>3.316511077366568</v>
+        <v>3.362365068085611</v>
       </c>
       <c r="E37" s="627" t="n">
-        <v>2.139983533128538</v>
+        <v>2.19717785749723</v>
       </c>
       <c r="F37" s="625" t="inlineStr">
         <is>
-          <t>Multiple on Invested Capital; AI improved gross cash return from 1.18x to 3.32x.</t>
+          <t>Multiple on Invested Capital; AI improved gross cash return from 1.17x to 3.36x.</t>
         </is>
       </c>
     </row>
@@ -12334,17 +12483,17 @@
         </is>
       </c>
       <c r="C38" s="624" t="n">
-        <v>0.03304780632992022</v>
+        <v>0.03104861170671052</v>
       </c>
       <c r="D38" s="624" t="n">
-        <v>0.2709728997774654</v>
+        <v>0.2744681102428927</v>
       </c>
       <c r="E38" s="624" t="n">
-        <v>0.2379250934475452</v>
+        <v>0.2434194985361822</v>
       </c>
       <c r="F38" s="625" t="inlineStr">
         <is>
-          <t>5-year IRR; AI boosted return by 23.8 percentage points to 27.1% (AI infra now $34m midpoint).</t>
+          <t>5-year IRR; AI boosted return by 24.3 percentage points to 27.4% (AI infra $34m; payroll cut 18%; exit 12.9x).</t>
         </is>
       </c>
     </row>
@@ -12365,14 +12514,14 @@
     <row r="41">
       <c r="B41" s="569" t="inlineStr">
         <is>
-          <t>AI case IRR 27.1% − Base IRR 3.3% = 23.8 percentage points of IRR</t>
+          <t>AI case IRR 27.4% − Base IRR 3.1% = 24.3 percentage points of IRR</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="569" t="inlineStr">
         <is>
-          <t>Y2 AI EBITDA margin 18.8% vs baseline 15.1% = 375 bps (target ≥500: NO)</t>
+          <t>Y2 AI EBITDA margin 19.5% vs FY24 baseline 15.1% = 441 bps (target ≥500: NO)</t>
         </is>
       </c>
     </row>
@@ -14558,19 +14707,19 @@
         <v>318.8</v>
       </c>
       <c r="D7" s="626" t="n">
-        <v>270.98</v>
+        <v>261.4160000000001</v>
       </c>
       <c r="E7" s="626" t="n">
-        <v>276.3996</v>
+        <v>266.6443200000001</v>
       </c>
       <c r="F7" s="626" t="n">
-        <v>281.927592</v>
+        <v>271.9772064000001</v>
       </c>
       <c r="G7" s="626" t="n">
-        <v>287.56614384</v>
+        <v>277.4167505280001</v>
       </c>
       <c r="H7" s="626" t="n">
-        <v>293.3174667168</v>
+        <v>282.9650855385601</v>
       </c>
     </row>
     <row r="8">
@@ -14608,19 +14757,19 @@
         <v>425</v>
       </c>
       <c r="D9" s="626" t="n">
-        <v>355.9400000000001</v>
+        <v>346.3760000000001</v>
       </c>
       <c r="E9" s="626" t="n">
-        <v>363.0588</v>
+        <v>353.30352</v>
       </c>
       <c r="F9" s="626" t="n">
-        <v>370.319976</v>
+        <v>360.3695904000001</v>
       </c>
       <c r="G9" s="626" t="n">
-        <v>377.72637552</v>
+        <v>367.5769822080001</v>
       </c>
       <c r="H9" s="626" t="n">
-        <v>385.2809030304001</v>
+        <v>374.9285218521601</v>
       </c>
     </row>
     <row r="10">
@@ -14708,19 +14857,19 @@
         <v>183.1</v>
       </c>
       <c r="D13" s="626" t="n">
-        <v>222.5026</v>
+        <v>232.0666</v>
       </c>
       <c r="E13" s="626" t="n">
-        <v>276.6280600000002</v>
+        <v>286.38334</v>
       </c>
       <c r="F13" s="626" t="n">
-        <v>336.7355700000003</v>
+        <v>346.6859556000002</v>
       </c>
       <c r="G13" s="626" t="n">
-        <v>403.4347250800001</v>
+        <v>413.5841183920002</v>
       </c>
       <c r="H13" s="626" t="n">
-        <v>477.3963076296004</v>
+        <v>487.7486888078406</v>
       </c>
     </row>
     <row r="14">
@@ -14733,19 +14882,19 @@
         <v>0.150786461335749</v>
       </c>
       <c r="D14" s="624" t="n">
-        <v>0.1665775268954055</v>
+        <v>0.1737376565623292</v>
       </c>
       <c r="E14" s="624" t="n">
-        <v>0.1882716226673465</v>
+        <v>0.1949110156312211</v>
       </c>
       <c r="F14" s="624" t="n">
-        <v>0.2083458928856374</v>
+        <v>0.2145024209066848</v>
       </c>
       <c r="G14" s="624" t="n">
-        <v>0.2269219678754411</v>
+        <v>0.2326307484040488</v>
       </c>
       <c r="H14" s="624" t="n">
-        <v>0.2441122844082408</v>
+        <v>0.2494058808984044</v>
       </c>
     </row>
     <row r="15">
@@ -14783,19 +14932,19 @@
         <v>97.40000000000001</v>
       </c>
       <c r="D16" s="626" t="n">
-        <v>128.2326</v>
+        <v>137.7966</v>
       </c>
       <c r="E16" s="626" t="n">
-        <v>172.9310600000002</v>
+        <v>182.68634</v>
       </c>
       <c r="F16" s="626" t="n">
-        <v>222.6688700000003</v>
+        <v>232.6192556000001</v>
       </c>
       <c r="G16" s="626" t="n">
-        <v>277.9613550800001</v>
+        <v>288.1107483920001</v>
       </c>
       <c r="H16" s="626" t="n">
-        <v>339.3756006296003</v>
+        <v>349.7279818078405</v>
       </c>
     </row>
     <row r="17">
@@ -14808,16 +14957,16 @@
         <v>77.8175</v>
       </c>
       <c r="E17" s="626" t="n">
-        <v>68.975234523</v>
+        <v>68.348123043</v>
       </c>
       <c r="F17" s="626" t="n">
-        <v>56.06864893947309</v>
+        <v>54.7607640501295</v>
       </c>
       <c r="G17" s="626" t="n">
-        <v>38.27932966018786</v>
+        <v>35.9867231453002</v>
       </c>
       <c r="H17" s="626" t="n">
-        <v>12.71433377476873</v>
+        <v>10.02482647488497</v>
       </c>
     </row>
     <row r="18">
@@ -14827,19 +14976,19 @@
         </is>
       </c>
       <c r="D18" s="626" t="n">
-        <v>39.82792900000004</v>
+        <v>47.38348900000001</v>
       </c>
       <c r="E18" s="626" t="n">
-        <v>82.12510212683014</v>
+        <v>90.32719139603003</v>
       </c>
       <c r="F18" s="626" t="n">
-        <v>131.6141746378165</v>
+        <v>140.5082083243978</v>
       </c>
       <c r="G18" s="626" t="n">
-        <v>189.3488000816517</v>
+        <v>199.1779799448929</v>
       </c>
       <c r="H18" s="626" t="n">
-        <v>258.0624008153169</v>
+        <v>268.3654927130348</v>
       </c>
     </row>
     <row r="19">
@@ -14893,19 +15042,19 @@
         </is>
       </c>
       <c r="D21" s="626" t="n">
-        <v>106.533319</v>
+        <v>114.088879</v>
       </c>
       <c r="E21" s="626" t="n">
-        <v>155.5010311268301</v>
+        <v>163.70312039603</v>
       </c>
       <c r="F21" s="626" t="n">
-        <v>212.3276965378165</v>
+        <v>221.2217302243978</v>
       </c>
       <c r="G21" s="626" t="n">
-        <v>278.1336741716516</v>
+        <v>287.9628540348929</v>
       </c>
       <c r="H21" s="626" t="n">
-        <v>355.725762314317</v>
+        <v>366.0288542120349</v>
       </c>
     </row>
     <row r="22">
@@ -14937,19 +15086,19 @@
         </is>
       </c>
       <c r="D23" s="626" t="n">
-        <v>106.533319</v>
+        <v>114.088879</v>
       </c>
       <c r="E23" s="626" t="n">
-        <v>155.5010311268301</v>
+        <v>163.70312039603</v>
       </c>
       <c r="F23" s="626" t="n">
-        <v>212.3276965378165</v>
+        <v>221.2217302243978</v>
       </c>
       <c r="G23" s="626" t="n">
-        <v>278.1336741716516</v>
+        <v>287.9628540348929</v>
       </c>
       <c r="H23" s="626" t="n">
-        <v>163.0042791637017</v>
+        <v>128.5234163446792</v>
       </c>
     </row>
     <row r="24">
@@ -14962,16 +15111,16 @@
         <v>1329.9</v>
       </c>
       <c r="D24" s="626" t="n">
-        <v>808.966681</v>
+        <v>801.411121</v>
       </c>
       <c r="E24" s="626" t="n">
-        <v>653.4656498731698</v>
+        <v>637.7080006039699</v>
       </c>
       <c r="F24" s="626" t="n">
-        <v>441.1379533353534</v>
+        <v>416.4862703795721</v>
       </c>
       <c r="G24" s="626" t="n">
-        <v>163.0042791637017</v>
+        <v>128.5234163446792</v>
       </c>
       <c r="H24" s="626" t="n">
         <v>0</v>
@@ -15332,7 +15481,7 @@
         </is>
       </c>
       <c r="D17" s="429" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -938,7 +938,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="45">
+  <fills count="46">
     <fill>
       <patternFill/>
     </fill>
@@ -1166,6 +1166,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE8A3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -1965,7 +1970,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="651">
+  <cellXfs count="653">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3141,6 +3146,12 @@
     </xf>
     <xf numFmtId="190" fontId="116" fillId="36" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="45" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="187">
@@ -5323,7 +5334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I32"/>
+  <dimension ref="B2:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
@@ -5333,7 +5344,9 @@
     <col width="48" customWidth="1" style="244" min="6" max="6"/>
     <col width="34" customWidth="1" style="244" min="7" max="7"/>
     <col width="38" customWidth="1" style="244" min="8" max="8"/>
-    <col width="55" customWidth="1" style="244" min="9" max="9"/>
+    <col width="42" customWidth="1" style="244" min="9" max="9"/>
+    <col width="42" customWidth="1" style="244" min="10" max="10"/>
+    <col width="42" customWidth="1" style="244" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -5346,7 +5359,7 @@
     <row r="3" ht="48" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>Task A: CapEx Ctrl+F CapEx of 1 (en-dash 1–3%). Payroll cut now 18% (was 15%). Exit multiple now 12.9x (was 13). MODEL CONST rows have no fake links.</t>
+          <t>FIND columns I/J/K: click the blue link — Chrome/Edge opens the source and highlights the quote (#:~:text= fragment = browser Find). Works best in Chrome or Edge.</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5401,17 @@
       </c>
       <c r="I4" s="641" t="inlineStr">
         <is>
-          <t>Verbatim — Ctrl+F this string on the linked page</t>
+          <t>FIND 1 — click opens page with quote highlighted</t>
+        </is>
+      </c>
+      <c r="J4" s="641" t="inlineStr">
+        <is>
+          <t>FIND 2 — click opens page with quote highlighted</t>
+        </is>
+      </c>
+      <c r="K4" s="641" t="inlineStr">
+        <is>
+          <t>FIND 3 — click opens page with quote highlighted</t>
         </is>
       </c>
     </row>
@@ -5426,9 +5449,19 @@
           <t>SEC 10-K same $1,214.3m</t>
         </is>
       </c>
-      <c r="I5" s="643" t="inlineStr">
-        <is>
-          <t>Ctrl+F: $1,214.3  →  "GAAP Revenue of $1,214.3 million, a decrease of 2% year-over-year."  |  10% growth: N/A (MODEL CONST)</t>
+      <c r="I5" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "$1,214.3"</t>
+        </is>
+      </c>
+      <c r="J5" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "$1,214.3" (10-K)</t>
+        </is>
+      </c>
+      <c r="K5" s="651" t="inlineStr">
+        <is>
+          <t>10% growth: N/A MODEL CONST</t>
         </is>
       </c>
     </row>
@@ -5462,11 +5495,13 @@
         </is>
       </c>
       <c r="H6" s="593" t="n"/>
-      <c r="I6" s="647" t="inlineStr">
-        <is>
-          <t>Ctrl+F: median software gross margin is 80  →  "The 2025 median software gross margin is 80%"</t>
-        </is>
-      </c>
+      <c r="I6" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "median software gross margin is 80"</t>
+        </is>
+      </c>
+      <c r="J6" s="652" t="n"/>
+      <c r="K6" s="652" t="n"/>
     </row>
     <row r="7" ht="96" customHeight="1" s="244">
       <c r="B7" s="607" t="inlineStr">
@@ -5498,11 +5533,13 @@
         </is>
       </c>
       <c r="H7" s="593" t="n"/>
-      <c r="I7" s="647" t="inlineStr">
-        <is>
-          <t>Ctrl+F: down 18%  →  "Net SDR headcount in US B2B SaaS companies is down 18% YoY in 2026 per Bridge Group"</t>
-        </is>
-      </c>
+      <c r="I7" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "down 18%"</t>
+        </is>
+      </c>
+      <c r="J7" s="652" t="n"/>
+      <c r="K7" s="652" t="n"/>
     </row>
     <row r="8" ht="96" customHeight="1" s="244">
       <c r="B8" s="613" t="inlineStr">
@@ -5538,9 +5575,19 @@
           <t>Also: commission 30–35% of pay</t>
         </is>
       </c>
-      <c r="I8" s="643" t="inlineStr">
-        <is>
-          <t>Ctrl+F: 70/30  →  "Standard SDR OTE in 2026 is $85,000 on a 70/30 base/variable split."  |  20% cut: N/A (MODEL CONST)</t>
+      <c r="I8" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "70/30"</t>
+        </is>
+      </c>
+      <c r="J8" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "30–35%"</t>
+        </is>
+      </c>
+      <c r="K8" s="651" t="inlineStr">
+        <is>
+          <t>20% cut: N/A MODEL CONST</t>
         </is>
       </c>
     </row>
@@ -5578,9 +5625,19 @@
           <t>Miniloop Entry $5,000 / Enterprise $10,000+</t>
         </is>
       </c>
-      <c r="I9" s="647" t="inlineStr">
-        <is>
-          <t>Ctrl+F: $5,000-10,000  →  "11x.ai (Alice) $5,000-10,000+"  |  Ctrl+F: $10,000-$15,000  →  "Enterprise $10,000-$15,000+"  |  Ctrl+F: 1,513 in sales  →  "1,513 in sales and marketing"  |  25% share: N/A (MODEL CONST)</t>
+      <c r="I9" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "$5,000-10,000+" (White Space)</t>
+        </is>
+      </c>
+      <c r="J9" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "$10,000-$15,000+" (Miniloop)</t>
+        </is>
+      </c>
+      <c r="K9" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "1,513 in sales and marketing" (SEC)</t>
         </is>
       </c>
     </row>
@@ -5618,11 +5675,13 @@
           <t>FOMC Statement on Longer-Run Goals (PDF)</t>
         </is>
       </c>
-      <c r="I10" s="647" t="inlineStr">
-        <is>
-          <t>Ctrl+F: 2 percent  →  "the FOMC judges that inflation of 2 percent over the longer run"</t>
-        </is>
-      </c>
+      <c r="I10" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "2 percent"</t>
+        </is>
+      </c>
+      <c r="J10" s="652" t="n"/>
+      <c r="K10" s="652" t="n"/>
     </row>
     <row r="11" ht="96" customHeight="1" s="244">
       <c r="B11" s="607" t="inlineStr">
@@ -5658,11 +5717,17 @@
           <t>Table MEDIAN G&amp;A as % of Revenue = 18%</t>
         </is>
       </c>
-      <c r="I11" s="647" t="inlineStr">
-        <is>
-          <t>Ctrl+F: G&amp;A was 18%  →  "G&amp;A was 18%, 20%, 21, and 23% of revenue in 2025, 2024, 2023, and 2022."  |  Alt table Ctrl+F: MEDIAN then G&amp;A col 18%</t>
-        </is>
-      </c>
+      <c r="I11" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "G&amp;A was 18%"</t>
+        </is>
+      </c>
+      <c r="J11" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND table MEDIAN 18% G&amp;A</t>
+        </is>
+      </c>
+      <c r="K11" s="652" t="n"/>
     </row>
     <row r="12" ht="96" customHeight="1" s="244">
       <c r="B12" s="613" t="inlineStr">
@@ -5694,11 +5759,13 @@
         </is>
       </c>
       <c r="H12" s="593" t="n"/>
-      <c r="I12" s="643" t="inlineStr">
-        <is>
-          <t>5% CapEx cut: N/A — MODEL CONST (no Ctrl+F string; no source link).</t>
-        </is>
-      </c>
+      <c r="I12" s="651" t="inlineStr">
+        <is>
+          <t>5% CapEx cut: N/A MODEL CONST</t>
+        </is>
+      </c>
+      <c r="J12" s="652" t="n"/>
+      <c r="K12" s="652" t="n"/>
     </row>
     <row r="13" ht="96" customHeight="1" s="244">
       <c r="B13" s="607" t="inlineStr">
@@ -5730,11 +5797,13 @@
         </is>
       </c>
       <c r="H13" s="593" t="n"/>
-      <c r="I13" s="643" t="inlineStr">
-        <is>
-          <t>10% WC improvement: N/A — MODEL CONST (no Ctrl+F string; no source link).</t>
-        </is>
-      </c>
+      <c r="I13" s="651" t="inlineStr">
+        <is>
+          <t>10% WC improve: N/A MODEL CONST</t>
+        </is>
+      </c>
+      <c r="J13" s="652" t="n"/>
+      <c r="K13" s="652" t="n"/>
     </row>
     <row r="14" ht="96" customHeight="1" s="244">
       <c r="B14" s="613" t="inlineStr">
@@ -5770,11 +5839,13 @@
           <t>NY Fed SOFR publisher</t>
         </is>
       </c>
-      <c r="I14" s="647" t="inlineStr">
-        <is>
-          <t>Ctrl+F: 4.30  →  table row "Lowest … 4.30 %" (SOFR 2024 First/Last/Highest/Lowest/Average)</t>
-        </is>
-      </c>
+      <c r="I14" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "4.30"</t>
+        </is>
+      </c>
+      <c r="J14" s="652" t="n"/>
+      <c r="K14" s="652" t="n"/>
     </row>
     <row r="15" ht="96" customHeight="1" s="244">
       <c r="B15" s="607" t="inlineStr">
@@ -5810,11 +5881,13 @@
           <t>Also: senior debt SOFR plus 400 to 500</t>
         </is>
       </c>
-      <c r="I15" s="647" t="inlineStr">
-        <is>
-          <t>Ctrl+F: 400-500  →  "Senior term loan A | … | SOFR + 400-500 bps"</t>
-        </is>
-      </c>
+      <c r="I15" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "400-500"</t>
+        </is>
+      </c>
+      <c r="J15" s="652" t="n"/>
+      <c r="K15" s="652" t="n"/>
     </row>
     <row r="16" ht="96" customHeight="1" s="244">
       <c r="B16" s="613" t="inlineStr">
@@ -5850,11 +5923,13 @@
           <t>Table: Term Loan B | SOFR + 300-500 bps | 1% annual</t>
         </is>
       </c>
-      <c r="I16" s="647" t="inlineStr">
-        <is>
-          <t>Ctrl+F: 300-500  →  "TLB pricing is typically SOFR + 300-500 basis points"  |  table Ctrl+F: Term Loan B</t>
-        </is>
-      </c>
+      <c r="I16" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "300-500"</t>
+        </is>
+      </c>
+      <c r="J16" s="652" t="n"/>
+      <c r="K16" s="652" t="n"/>
     </row>
     <row r="17" ht="96" customHeight="1" s="244">
       <c r="B17" s="607" t="inlineStr">
@@ -5890,11 +5965,13 @@
           <t>ClearValue: "minimal amortization (1% annually)"</t>
         </is>
       </c>
-      <c r="I17" s="647" t="inlineStr">
-        <is>
-          <t>Ctrl+F: 1% annual  →  "minimal amortization (1% annually)"  |  Alt: "1% per year (nominal)"</t>
-        </is>
-      </c>
+      <c r="I17" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "1% annually"</t>
+        </is>
+      </c>
+      <c r="J17" s="652" t="n"/>
+      <c r="K17" s="652" t="n"/>
     </row>
     <row r="18" ht="96" customHeight="1" s="244">
       <c r="B18" s="613" t="inlineStr">
@@ -5926,11 +6003,17 @@
         </is>
       </c>
       <c r="H18" s="593" t="n"/>
-      <c r="I18" s="647" t="inlineStr">
-        <is>
-          <t>Ctrl+F: 50-100%  →  "apply 50-100% of annual excess free cash flow"  |  Ctrl+F: modeled at 100%  →  "typically modeled at 100%"</t>
-        </is>
-      </c>
+      <c r="I18" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "50-100%"</t>
+        </is>
+      </c>
+      <c r="J18" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "modeled at 100%"</t>
+        </is>
+      </c>
+      <c r="K18" s="652" t="n"/>
     </row>
     <row r="19" ht="96" customHeight="1" s="244">
       <c r="B19" s="607" t="inlineStr">
@@ -5966,11 +6049,13 @@
           <t>Trading Economics: 21 percent</t>
         </is>
       </c>
-      <c r="I19" s="647" t="inlineStr">
-        <is>
-          <t>Ctrl+F: flat rate of 21  →  "taxes resident corporations at a flat rate of 21%."</t>
-        </is>
-      </c>
+      <c r="I19" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "flat rate of 21%"</t>
+        </is>
+      </c>
+      <c r="J19" s="652" t="n"/>
+      <c r="K19" s="652" t="n"/>
     </row>
     <row r="20" ht="96" customHeight="1" s="244">
       <c r="B20" s="613" t="inlineStr">
@@ -6002,11 +6087,13 @@
         </is>
       </c>
       <c r="H20" s="593" t="n"/>
-      <c r="I20" s="647" t="inlineStr">
-        <is>
-          <t>Ctrl+F: 12.9x  →  table "EV/EBITDA | … | 1st quartile | 12.9x"  |  Alt Ctrl+F: 12.8x  →  "lower quartile are closer to 12.8x"</t>
-        </is>
-      </c>
+      <c r="I20" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "12.9x"</t>
+        </is>
+      </c>
+      <c r="J20" s="652" t="n"/>
+      <c r="K20" s="652" t="n"/>
     </row>
     <row r="21" ht="96" customHeight="1" s="244">
       <c r="B21" s="607" t="inlineStr">
@@ -6042,9 +6129,19 @@
           <t>SEC 10-K Sales and marketing $414.1</t>
         </is>
       </c>
-      <c r="I21" s="647" t="inlineStr">
-        <is>
-          <t>Ctrl+F: $1,214.3  and  Ctrl+F: 414.1  →  Revenue $1,214.3 / Sales and marketing $414.1  |  425: MODEL ROUND of 35%×1214.3</t>
+      <c r="I21" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "$1,214.3"</t>
+        </is>
+      </c>
+      <c r="J21" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "414.1"</t>
+        </is>
+      </c>
+      <c r="K21" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "414.1" (10-K)</t>
         </is>
       </c>
     </row>
@@ -6078,11 +6175,17 @@
         </is>
       </c>
       <c r="H22" s="593" t="n"/>
-      <c r="I22" s="643" t="inlineStr">
-        <is>
-          <t>Ctrl+F: 70/30  →  "70/30 base/variable split"  |  318.8 / 75%: MODEL carve (not printed as $318.8)</t>
-        </is>
-      </c>
+      <c r="I22" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "70/30"</t>
+        </is>
+      </c>
+      <c r="J22" s="651" t="inlineStr">
+        <is>
+          <t>$318.8 / 75%: MODEL carve</t>
+        </is>
+      </c>
+      <c r="K22" s="652" t="n"/>
     </row>
     <row r="23" ht="96" customHeight="1" s="244">
       <c r="B23" s="607" t="inlineStr">
@@ -6118,11 +6221,17 @@
           <t>70/30 pay article</t>
         </is>
       </c>
-      <c r="I23" s="643" t="inlineStr">
-        <is>
-          <t>Ctrl+F: 30–35%  →  "Commission accounts for 30–35% of total pay"  |  106.2 / 25%: MODEL carve</t>
-        </is>
-      </c>
+      <c r="I23" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "30–35%"</t>
+        </is>
+      </c>
+      <c r="J23" s="651" t="inlineStr">
+        <is>
+          <t>$106.2 / 25%: MODEL carve</t>
+        </is>
+      </c>
+      <c r="K23" s="652" t="n"/>
     </row>
     <row r="24" ht="96" customHeight="1" s="244">
       <c r="B24" s="613" t="inlineStr">
@@ -6154,11 +6263,17 @@
         </is>
       </c>
       <c r="H24" s="593" t="n"/>
-      <c r="I24" s="647" t="inlineStr">
-        <is>
-          <t>Ctrl+F: CapEx of 1  →  "Most pure-play SaaS companies report CapEx of 1–3% of revenue"  |  Tip: search CapEx of 1 (en-dash); plain 1-3% may miss.  |  2%: MODEL midpoint of that band</t>
-        </is>
-      </c>
+      <c r="I24" s="645" t="inlineStr">
+        <is>
+          <t>CLICK → FIND "CapEx of 1" (en-dash 1–3%)</t>
+        </is>
+      </c>
+      <c r="J24" s="651" t="inlineStr">
+        <is>
+          <t>2%: MODEL midpoint of 1–3% band</t>
+        </is>
+      </c>
+      <c r="K24" s="652" t="n"/>
     </row>
     <row r="25" ht="96" customHeight="1" s="244">
       <c r="B25" s="607" t="inlineStr">
@@ -6190,11 +6305,13 @@
         </is>
       </c>
       <c r="H25" s="593" t="n"/>
-      <c r="I25" s="643" t="inlineStr">
-        <is>
-          <t>2% WC plug: N/A — MODEL CONST (no Ctrl+F string; no source link).</t>
-        </is>
-      </c>
+      <c r="I25" s="651" t="inlineStr">
+        <is>
+          <t>2% WC plug: N/A MODEL CONST</t>
+        </is>
+      </c>
+      <c r="J25" s="652" t="n"/>
+      <c r="K25" s="652" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="618" t="inlineStr">
@@ -6234,11 +6351,13 @@
         </is>
       </c>
       <c r="H27" s="593" t="n"/>
-      <c r="I27" s="647" t="inlineStr">
-        <is>
-          <t>No separate third-party quote — sum of sourced C14 and C15.</t>
-        </is>
-      </c>
+      <c r="I27" s="651" t="inlineStr">
+        <is>
+          <t>Uses rows 14–15 FIND links</t>
+        </is>
+      </c>
+      <c r="J27" s="652" t="n"/>
+      <c r="K27" s="652" t="n"/>
     </row>
     <row r="28" ht="96" customHeight="1" s="244">
       <c r="B28" s="607" t="inlineStr">
@@ -6271,11 +6390,13 @@
         </is>
       </c>
       <c r="H28" s="593" t="n"/>
-      <c r="I28" s="647" t="inlineStr">
-        <is>
-          <t>No separate third-party quote — sum of sourced C14 and C16.</t>
-        </is>
-      </c>
+      <c r="I28" s="651" t="inlineStr">
+        <is>
+          <t>Uses rows 14 &amp; 16 FIND links</t>
+        </is>
+      </c>
+      <c r="J28" s="652" t="n"/>
+      <c r="K28" s="652" t="n"/>
     </row>
     <row r="29" ht="72" customHeight="1" s="244">
       <c r="B29" s="618" t="inlineStr">
@@ -6325,6 +6446,30 @@
       <c r="C32" s="640" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_DRIVER_SOURCES.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>How FIND links work:</t>
+        </is>
+      </c>
+      <c r="C33" s="574" t="inlineStr">
+        <is>
+          <t>Blue FIND cells use Chrome Scroll-to-Text (#:~:text=...). Click → browser opens the URL and highlights the quote (same effect as Ctrl+F landing on that string). Use Chrome or Edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>AI $34m FIND example (row 9):</t>
+        </is>
+      </c>
+      <c r="C34" s="574" t="inlineStr">
+        <is>
+          <t>I → White Space $5,000-10,000+ highlighted | J → Miniloop $10,000-$15,000+ highlighted | K → SEC 1,513 in sales and marketing highlighted</t>
         </is>
       </c>
     </row>
@@ -6337,59 +6482,85 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -1970,7 +1970,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="653">
+  <cellXfs count="654">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3151,6 +3151,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5344,22 +5347,22 @@
     <col width="48" customWidth="1" style="244" min="6" max="6"/>
     <col width="34" customWidth="1" style="244" min="7" max="7"/>
     <col width="38" customWidth="1" style="244" min="8" max="8"/>
-    <col width="42" customWidth="1" style="244" min="9" max="9"/>
-    <col width="42" customWidth="1" style="244" min="10" max="10"/>
-    <col width="42" customWidth="1" style="244" min="11" max="11"/>
+    <col width="48" customWidth="1" style="244" min="9" max="9"/>
+    <col width="48" customWidth="1" style="244" min="10" max="10"/>
+    <col width="48" customWidth="1" style="244" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="629" t="inlineStr">
         <is>
-          <t>Assumptions Drivers — every sourced figure has a Ctrl+F string in column I. If yellow ≠ findable text, it is MODEL CONST or a labeled midpoint.</t>
+          <t>Assumptions Drivers — columns I/J/K are =HYPERLINK() to the verbatim quote (click the blue text). Opens source with quote highlighted in Chrome/Edge.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>FIND columns I/J/K: click the blue link — Chrome/Edge opens the source and highlights the quote (#:~:text= fragment = browser Find). Works best in Chrome or Edge.</t>
+          <t>If a cell says MODEL CONST there is no link. Scroll right to columns I, J, K for Verbatim hyperlinks on every sourced row.</t>
         </is>
       </c>
     </row>
@@ -5401,17 +5404,17 @@
       </c>
       <c r="I4" s="641" t="inlineStr">
         <is>
-          <t>FIND 1 — click opens page with quote highlighted</t>
+          <t>Verbatim 1 (click blue link — opens source at quote)</t>
         </is>
       </c>
       <c r="J4" s="641" t="inlineStr">
         <is>
-          <t>FIND 2 — click opens page with quote highlighted</t>
+          <t>Verbatim 2 (click blue link — opens source at quote)</t>
         </is>
       </c>
       <c r="K4" s="641" t="inlineStr">
         <is>
-          <t>FIND 3 — click opens page with quote highlighted</t>
+          <t>Verbatim 3 (click blue link — opens source at quote)</t>
         </is>
       </c>
     </row>
@@ -5429,10 +5432,9 @@
           <t>Assumes steady top-line expansion. Reasonable for a mature enterprise software company, avoiding aggressive hypergrowth assumptions while maintaining a healthy, realistic sales trajectory.</t>
         </is>
       </c>
-      <c r="E5" s="642" t="inlineStr">
-        <is>
-          <t>IN EQ $ base only: FY24 Rev=$1,214.3m (ZI). C5=10% = MODEL CONST (10% not in filing).</t>
-        </is>
+      <c r="E5" s="645">
+        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results#:~:text=GAAP%20Revenue%20of%20%241%2C214.3%20million","IN EQ $ base only: FY24 Rev=$1,214.3m (ZI). C5=10% = MODEL CONST (10% not in filing).")</f>
+        <v/>
       </c>
       <c r="F5" s="643" t="inlineStr">
         <is>
@@ -5444,24 +5446,21 @@
           <t>Go to AI_Operating!D5 (Revenue)</t>
         </is>
       </c>
-      <c r="H5" s="593" t="inlineStr">
-        <is>
-          <t>SEC 10-K same $1,214.3m</t>
-        </is>
-      </c>
-      <c r="I5" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "$1,214.3"</t>
-        </is>
-      </c>
-      <c r="J5" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "$1,214.3" (10-K)</t>
-        </is>
-      </c>
-      <c r="K5" s="651" t="inlineStr">
-        <is>
-          <t>10% growth: N/A MODEL CONST</t>
+      <c r="H5" s="645">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm#:~:text=We%20generated%20revenue%20of%20%241%2C214.3%20million","SEC 10-K same $1,214.3m")</f>
+        <v/>
+      </c>
+      <c r="I5" s="645">
+        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results#:~:text=GAAP%20Revenue%20of%20%241%2C214.3%20million","Verbatim: GAAP Revenue of $1,214.3 million → click")</f>
+        <v/>
+      </c>
+      <c r="J5" s="645">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm#:~:text=We%20generated%20revenue%20of%20%241%2C214.3%20million","Verbatim: We generated revenue of $1,214.3 million' (10-K) → click")</f>
+        <v/>
+      </c>
+      <c r="K5" s="643" t="inlineStr">
+        <is>
+          <t>10% growth: N/A — MODEL CONST (no link)</t>
         </is>
       </c>
     </row>
@@ -5479,10 +5478,9 @@
           <t>High profitability on direct services. Highly reasonable for a SaaS company, which historically scales digital infrastructure with minimal incremental cost per user.</t>
         </is>
       </c>
-      <c r="E6" s="645" t="inlineStr">
-        <is>
-          <t>IN EQ: software median GM=80% → C6=0.80 (Aleph × Benchmarkit)</t>
-        </is>
+      <c r="E6" s="645">
+        <f>HYPERLINK("https://www.getaleph.com/answers/saas-gross-margin-2026#:~:text=The%202025%20median%20software%20gross%20margin%20is%2080%25","IN EQ: software median GM=80% → C6=0.80 (Aleph × Benchmarkit)")</f>
+        <v/>
       </c>
       <c r="F6" s="646" t="inlineStr">
         <is>
@@ -5495,13 +5493,12 @@
         </is>
       </c>
       <c r="H6" s="593" t="n"/>
-      <c r="I6" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "median software gross margin is 80"</t>
-        </is>
-      </c>
-      <c r="J6" s="652" t="n"/>
-      <c r="K6" s="652" t="n"/>
+      <c r="I6" s="645">
+        <f>HYPERLINK("https://www.getaleph.com/answers/saas-gross-margin-2026#:~:text=The%202025%20median%20software%20gross%20margin%20is%2080%25","Verbatim: The 2025 median software gross margin is 80% → click")</f>
+        <v/>
+      </c>
+      <c r="J6" s="651" t="n"/>
+      <c r="K6" s="651" t="n"/>
     </row>
     <row r="7" ht="96" customHeight="1" s="244">
       <c r="B7" s="607" t="inlineStr">
@@ -5517,10 +5514,9 @@
           <t>Immediate headcount reduction for human SDRs. Set to 18% to match published US B2B SaaS net SDR headcount decline of 18% YoY (Ctrl+F: down 18%).</t>
         </is>
       </c>
-      <c r="E7" s="645" t="inlineStr">
-        <is>
-          <t>IN EQ: C7=18% = US B2B SaaS net SDR headcount down 18% YoY (Digital Applied / Bridge Group)</t>
-        </is>
+      <c r="E7" s="645">
+        <f>HYPERLINK("https://www.digitalapplied.com/blog/ai-sdr-statistics-2026-outbound-sales-data-points#:~:text=down%2018%25%20YoY","IN EQ: C7=18% = US B2B SaaS net SDR headcount down 18% YoY (Digital Applied / Bridge Group)")</f>
+        <v/>
       </c>
       <c r="F7" s="646" t="inlineStr">
         <is>
@@ -5533,13 +5529,12 @@
         </is>
       </c>
       <c r="H7" s="593" t="n"/>
-      <c r="I7" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "down 18%"</t>
-        </is>
-      </c>
-      <c r="J7" s="652" t="n"/>
-      <c r="K7" s="652" t="n"/>
+      <c r="I7" s="645">
+        <f>HYPERLINK("https://www.digitalapplied.com/blog/ai-sdr-statistics-2026-outbound-sales-data-points#:~:text=down%2018%25%20YoY","Verbatim: down 18% YoY → click")</f>
+        <v/>
+      </c>
+      <c r="J7" s="651" t="n"/>
+      <c r="K7" s="651" t="n"/>
     </row>
     <row r="8" ht="96" customHeight="1" s="244">
       <c r="B8" s="613" t="inlineStr">
@@ -5555,10 +5550,9 @@
           <t>Reduces payouts for automated sales. Reasonable because AI agents do not collect commission checks, retaining more profit per enterprise deal directly for the company.</t>
         </is>
       </c>
-      <c r="E8" s="642" t="inlineStr">
-        <is>
-          <t>Pool mix sourced (~30% variable); C8=20% cut = MODEL CONST (20% cut not in source).</t>
-        </is>
+      <c r="E8" s="645">
+        <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep#:~:text=70%2F30%20base%2Fvariable%20split","Pool mix sourced (~30% variable); C8=20% cut = MODEL CONST (20% cut not in source).")</f>
+        <v/>
       </c>
       <c r="F8" s="643" t="inlineStr">
         <is>
@@ -5570,24 +5564,21 @@
           <t>Go to AI_Operating!D8 (Commissions)</t>
         </is>
       </c>
-      <c r="H8" s="593" t="inlineStr">
-        <is>
-          <t>Also: commission 30–35% of pay</t>
-        </is>
-      </c>
-      <c r="I8" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "70/30"</t>
-        </is>
-      </c>
-      <c r="J8" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "30–35%"</t>
-        </is>
-      </c>
-      <c r="K8" s="651" t="inlineStr">
-        <is>
-          <t>20% cut: N/A MODEL CONST</t>
+      <c r="H8" s="645">
+        <f>HYPERLINK("https://syncgtm.com/blog/how-much-do-sales-development-representatives-make-at-tech-companies#:~:text=30%E2%80%9335%25%20of%20total%20pay","Also: commission 30–35% of pay")</f>
+        <v/>
+      </c>
+      <c r="I8" s="645">
+        <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep#:~:text=70%2F30%20base%2Fvariable%20split","Verbatim: 70/30 base/variable split → click")</f>
+        <v/>
+      </c>
+      <c r="J8" s="645">
+        <f>HYPERLINK("https://syncgtm.com/blog/how-much-do-sales-development-representatives-make-at-tech-companies#:~:text=30%E2%80%9335%25%20of%20total%20pay","Verbatim: 30–35% of total pay → click")</f>
+        <v/>
+      </c>
+      <c r="K8" s="643" t="inlineStr">
+        <is>
+          <t>20% cut: N/A — MODEL CONST (no link)</t>
         </is>
       </c>
     </row>
@@ -5605,10 +5596,9 @@
           <t>AI infra $34m = 378 roles × $5–10k/mo × 12, midpoint. $/mo from published AI SDR enterprise pricing; headcount from ZI 10-K.</t>
         </is>
       </c>
-      <c r="E9" s="645" t="inlineStr">
-        <is>
-          <t>IN EQ: $5,000 and $10,000/mo AI SDR (White Space + Miniloop) + 1,513 S&amp;M HC (SEC)</t>
-        </is>
+      <c r="E9" s="645">
+        <f>HYPERLINK("https://www.whitespacesolutions.ai/content/ai-sdr-pricing-guide-2026#:~:text=%245%2C000-10%2C000%2B","IN EQ: $5,000 and $10,000/mo AI SDR (White Space + Miniloop) + 1,513 S&amp;M HC (SEC)")</f>
+        <v/>
       </c>
       <c r="F9" s="649" t="inlineStr">
         <is>
@@ -5620,25 +5610,21 @@
           <t>Go to AI_Operating!D10 (AI infrastructure)</t>
         </is>
       </c>
-      <c r="H9" s="593" t="inlineStr">
-        <is>
-          <t>Miniloop Entry $5,000 / Enterprise $10,000+</t>
-        </is>
-      </c>
-      <c r="I9" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "$5,000-10,000+" (White Space)</t>
-        </is>
-      </c>
-      <c r="J9" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "$10,000-$15,000+" (Miniloop)</t>
-        </is>
-      </c>
-      <c r="K9" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "1,513 in sales and marketing" (SEC)</t>
-        </is>
+      <c r="H9" s="645">
+        <f>HYPERLINK("https://www.miniloop.ai/blog/11x-pricing#:~:text=%2410%2C000-%2415%2C000%2B","Miniloop Entry $5,000 / Enterprise $10,000+")</f>
+        <v/>
+      </c>
+      <c r="I9" s="645">
+        <f>HYPERLINK("https://www.whitespacesolutions.ai/content/ai-sdr-pricing-guide-2026#:~:text=%245%2C000-10%2C000%2B","Verbatim: 11x.ai (Alice) $5,000-10,000+ → click")</f>
+        <v/>
+      </c>
+      <c r="J9" s="645">
+        <f>HYPERLINK("https://www.miniloop.ai/blog/11x-pricing#:~:text=%2410%2C000-%2415%2C000%2B","Verbatim: Enterprise $10,000-$15,000+ → click")</f>
+        <v/>
+      </c>
+      <c r="K9" s="645">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm#:~:text=1%2C513%20in%20sales%20and%20marketing","Verbatim: 1,513 in sales and marketing → click")</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="96" customHeight="1" s="244">
@@ -5655,10 +5641,9 @@
           <t>Caps future marketing cost increases. Reasonable because AI scales infinitely without needing proportional headcount additions, severing the link between revenue growth and human hiring.</t>
         </is>
       </c>
-      <c r="E10" s="645" t="inlineStr">
-        <is>
-          <t>IN EQ: C10=2% = Fed longer-run inflation goal of 2 percent (FOMC FAQ)</t>
-        </is>
+      <c r="E10" s="645">
+        <f>HYPERLINK("https://www.federalreserve.gov/faqs/economy_14400.htm#:~:text=inflation%20of%202%20percent%20over%20the%20longer%20run","IN EQ: C10=2% = Fed longer-run inflation goal of 2 percent (FOMC FAQ)")</f>
+        <v/>
       </c>
       <c r="F10" s="646" t="inlineStr">
         <is>
@@ -5675,13 +5660,12 @@
           <t>FOMC Statement on Longer-Run Goals (PDF)</t>
         </is>
       </c>
-      <c r="I10" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "2 percent"</t>
-        </is>
-      </c>
-      <c r="J10" s="652" t="n"/>
-      <c r="K10" s="652" t="n"/>
+      <c r="I10" s="645">
+        <f>HYPERLINK("https://www.federalreserve.gov/faqs/economy_14400.htm#:~:text=inflation%20of%202%20percent%20over%20the%20longer%20run","Verbatim: inflation of 2 percent over the longer run → click")</f>
+        <v/>
+      </c>
+      <c r="J10" s="651" t="n"/>
+      <c r="K10" s="651" t="n"/>
     </row>
     <row r="11" ht="96" customHeight="1" s="244">
       <c r="B11" s="607" t="inlineStr">
@@ -5697,10 +5681,9 @@
           <t>General administrative overhead costs. Reasonable for a public-to-private SaaS company, maintaining standard corporate expenses without relying on unrealistic operational magic outside of sales.</t>
         </is>
       </c>
-      <c r="E11" s="645" t="inlineStr">
-        <is>
-          <t>IN EQ: C11=18% = Blossom Street 2025 public SaaS median G&amp;A 18% of revenue</t>
-        </is>
+      <c r="E11" s="645">
+        <f>HYPERLINK("https://blossomstreetventures.medium.com/what-should-saas-spend-on-cogs-s-m-r-d-and-g-a-the-data-from-57-public-cos-8e88eabe99ca#:~:text=G%26A%20was%2018%25","IN EQ: C11=18% = Blossom Street 2025 public SaaS median G&amp;A 18% of revenue")</f>
+        <v/>
       </c>
       <c r="F11" s="643" t="inlineStr">
         <is>
@@ -5712,22 +5695,19 @@
           <t>Go to AI_Operating!D12 (G&amp;A)</t>
         </is>
       </c>
-      <c r="H11" s="593" t="inlineStr">
-        <is>
-          <t>Table MEDIAN G&amp;A as % of Revenue = 18%</t>
-        </is>
-      </c>
-      <c r="I11" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "G&amp;A was 18%"</t>
-        </is>
-      </c>
-      <c r="J11" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND table MEDIAN 18% G&amp;A</t>
-        </is>
-      </c>
-      <c r="K11" s="652" t="n"/>
+      <c r="H11" s="645">
+        <f>HYPERLINK("https://www.blossomstreetventures.com/saas-metric/2025-annual-percent-of-revenue#:~:text=MEDIAN","Table MEDIAN G&amp;A as % of Revenue = 18%")</f>
+        <v/>
+      </c>
+      <c r="I11" s="645">
+        <f>HYPERLINK("https://blossomstreetventures.medium.com/what-should-saas-spend-on-cogs-s-m-r-d-and-g-a-the-data-from-57-public-cos-8e88eabe99ca#:~:text=G%26A%20was%2018%25","Verbatim: G&amp;A was 18% → click")</f>
+        <v/>
+      </c>
+      <c r="J11" s="645">
+        <f>HYPERLINK("https://www.blossomstreetventures.com/saas-metric/2025-annual-percent-of-revenue#:~:text=MEDIAN","Verbatim table: 'MEDIAN' (G&amp;A col 18%) → click")</f>
+        <v/>
+      </c>
+      <c r="K11" s="651" t="n"/>
     </row>
     <row r="12" ht="96" customHeight="1" s="244">
       <c r="B12" s="613" t="inlineStr">
@@ -5759,13 +5739,13 @@
         </is>
       </c>
       <c r="H12" s="593" t="n"/>
-      <c r="I12" s="651" t="inlineStr">
-        <is>
-          <t>5% CapEx cut: N/A MODEL CONST</t>
-        </is>
-      </c>
-      <c r="J12" s="652" t="n"/>
-      <c r="K12" s="652" t="n"/>
+      <c r="I12" s="643" t="inlineStr">
+        <is>
+          <t>5% CapEx cut: N/A — MODEL CONST (no link)</t>
+        </is>
+      </c>
+      <c r="J12" s="651" t="n"/>
+      <c r="K12" s="651" t="n"/>
     </row>
     <row r="13" ht="96" customHeight="1" s="244">
       <c r="B13" s="607" t="inlineStr">
@@ -5797,13 +5777,13 @@
         </is>
       </c>
       <c r="H13" s="593" t="n"/>
-      <c r="I13" s="651" t="inlineStr">
-        <is>
-          <t>10% WC improve: N/A MODEL CONST</t>
-        </is>
-      </c>
-      <c r="J13" s="652" t="n"/>
-      <c r="K13" s="652" t="n"/>
+      <c r="I13" s="643" t="inlineStr">
+        <is>
+          <t>10% WC improve: N/A — MODEL CONST (no link)</t>
+        </is>
+      </c>
+      <c r="J13" s="651" t="n"/>
+      <c r="K13" s="651" t="n"/>
     </row>
     <row r="14" ht="96" customHeight="1" s="244">
       <c r="B14" s="613" t="inlineStr">
@@ -5819,10 +5799,9 @@
           <t>The foundational secured lending interest rate. Reasonable and historically accurate for the macroeconomic environment, properly reflecting actual institutional baseline borrowing costs.</t>
         </is>
       </c>
-      <c r="E14" s="645" t="inlineStr">
-        <is>
-          <t>IN EQ: C14=4.30% = SOFR 2024 calendar-year Lowest (Global-Rates summary of NY Fed)</t>
-        </is>
+      <c r="E14" s="645">
+        <f>HYPERLINK("https://www.global-rates.com/en/interest-rates/sofr/historical/2024/#:~:text=4.30","IN EQ: C14=4.30% = SOFR 2024 calendar-year Lowest (Global-Rates summary of NY Fed)")</f>
+        <v/>
       </c>
       <c r="F14" s="643" t="inlineStr">
         <is>
@@ -5839,13 +5818,12 @@
           <t>NY Fed SOFR publisher</t>
         </is>
       </c>
-      <c r="I14" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "4.30"</t>
-        </is>
-      </c>
-      <c r="J14" s="652" t="n"/>
-      <c r="K14" s="652" t="n"/>
+      <c r="I14" s="645">
+        <f>HYPERLINK("https://www.global-rates.com/en/interest-rates/sofr/historical/2024/#:~:text=4.30","Verbatim: 4.30' (SOFR 2024 Lowest) → click")</f>
+        <v/>
+      </c>
+      <c r="J14" s="651" t="n"/>
+      <c r="K14" s="651" t="n"/>
     </row>
     <row r="15" ht="96" customHeight="1" s="244">
       <c r="B15" s="607" t="inlineStr">
@@ -5861,10 +5839,9 @@
           <t>The risk premium for senior debt. Reasonable for a standard LBO, reflecting typical syndicated commercial bank pricing for secured corporate borrowing.</t>
         </is>
       </c>
-      <c r="E15" s="645" t="inlineStr">
-        <is>
-          <t>IN EQ: C15=+400bps = floor of senior Term Loan A SOFR+400-500 bps (CT Acquisitions)</t>
-        </is>
+      <c r="E15" s="645">
+        <f>HYPERLINK("https://ctacquisitions.com/acquisition-financing/#:~:text=SOFR%20%2B%20400-500%20bps","IN EQ: C15=+400bps = floor of senior Term Loan A SOFR+400-500 bps (CT Acquisitions)")</f>
+        <v/>
       </c>
       <c r="F15" s="643" t="inlineStr">
         <is>
@@ -5881,13 +5858,12 @@
           <t>Also: senior debt SOFR plus 400 to 500</t>
         </is>
       </c>
-      <c r="I15" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "400-500"</t>
-        </is>
-      </c>
-      <c r="J15" s="652" t="n"/>
-      <c r="K15" s="652" t="n"/>
+      <c r="I15" s="645">
+        <f>HYPERLINK("https://ctacquisitions.com/acquisition-financing/#:~:text=SOFR%20%2B%20400-500%20bps","Verbatim: SOFR + 400-500 bps → click")</f>
+        <v/>
+      </c>
+      <c r="J15" s="651" t="n"/>
+      <c r="K15" s="651" t="n"/>
     </row>
     <row r="16" ht="96" customHeight="1" s="244">
       <c r="B16" s="613" t="inlineStr">
@@ -5903,10 +5879,9 @@
           <t>The risk premium for riskier debt. Reasonable, as Term Loan B is usually held by institutional investors requiring higher yields for slightly higher risk.</t>
         </is>
       </c>
-      <c r="E16" s="645" t="inlineStr">
-        <is>
-          <t>IN EQ: TLB SOFR+300-500 bps → C16=+500bps = upper bound</t>
-        </is>
+      <c r="E16" s="645">
+        <f>HYPERLINK("https://ibinterviewquestions.com/guides/valuation-investment-banking/lbo-debt-structures-senior-subordinated-mezzanine#:~:text=SOFR%20%2B%20300-500%20basis%20points","IN EQ: TLB SOFR+300-500 bps → C16=+500bps = upper bound")</f>
+        <v/>
       </c>
       <c r="F16" s="646" t="inlineStr">
         <is>
@@ -5923,13 +5898,12 @@
           <t>Table: Term Loan B | SOFR + 300-500 bps | 1% annual</t>
         </is>
       </c>
-      <c r="I16" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "300-500"</t>
-        </is>
-      </c>
-      <c r="J16" s="652" t="n"/>
-      <c r="K16" s="652" t="n"/>
+      <c r="I16" s="645">
+        <f>HYPERLINK("https://ibinterviewquestions.com/guides/valuation-investment-banking/lbo-debt-structures-senior-subordinated-mezzanine#:~:text=SOFR%20%2B%20300-500%20basis%20points","Verbatim: SOFR + 300-500 basis points → click")</f>
+        <v/>
+      </c>
+      <c r="J16" s="651" t="n"/>
+      <c r="K16" s="651" t="n"/>
     </row>
     <row r="17" ht="96" customHeight="1" s="244">
       <c r="B17" s="607" t="inlineStr">
@@ -5945,10 +5919,9 @@
           <t>Required annual principal repayment. Highly reasonable and standard market practice for leveraged loans, forcing a tiny minimum debt reduction each year.</t>
         </is>
       </c>
-      <c r="E17" s="645" t="inlineStr">
-        <is>
-          <t>IN EQ: ~1%/yr TLB amort → C17=1%</t>
-        </is>
+      <c r="E17" s="645">
+        <f>HYPERLINK("https://clearvaluelending.com/glossary/term-loan-b#:~:text=minimal%20amortization%20%281%25%20annually%29","IN EQ: ~1%/yr TLB amort → C17=1%")</f>
+        <v/>
       </c>
       <c r="F17" s="646" t="inlineStr">
         <is>
@@ -5965,13 +5938,12 @@
           <t>ClearValue: "minimal amortization (1% annually)"</t>
         </is>
       </c>
-      <c r="I17" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "1% annually"</t>
-        </is>
-      </c>
-      <c r="J17" s="652" t="n"/>
-      <c r="K17" s="652" t="n"/>
+      <c r="I17" s="645">
+        <f>HYPERLINK("https://clearvaluelending.com/glossary/term-loan-b#:~:text=minimal%20amortization%20%281%25%20annually%29","Verbatim: minimal amortization (1% annually) → click")</f>
+        <v/>
+      </c>
+      <c r="J17" s="651" t="n"/>
+      <c r="K17" s="651" t="n"/>
     </row>
     <row r="18" ht="96" customHeight="1" s="244">
       <c r="B18" s="613" t="inlineStr">
@@ -5987,10 +5959,9 @@
           <t>Dedicates all excess cash to debt. Reasonable and standard for maximizing LBO returns, ensuring every free dollar generated immediately aggressively reduces outstanding leverage.</t>
         </is>
       </c>
-      <c r="E18" s="645" t="inlineStr">
-        <is>
-          <t>IN EQ: C18=100% = upper bound of ECF sweep 50-100%; models often use 100%</t>
-        </is>
+      <c r="E18" s="645">
+        <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/#:~:text=50-100%25%20of%20annual%20excess%20free%20cash%20flow","IN EQ: C18=100% = upper bound of ECF sweep 50-100%; models often use 100%")</f>
+        <v/>
       </c>
       <c r="F18" s="643" t="inlineStr">
         <is>
@@ -6002,18 +5973,19 @@
           <t>Go to Debt_Sweep_AI!E5 (Total paydown)</t>
         </is>
       </c>
-      <c r="H18" s="593" t="n"/>
-      <c r="I18" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "50-100%"</t>
-        </is>
-      </c>
-      <c r="J18" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "modeled at 100%"</t>
-        </is>
-      </c>
-      <c r="K18" s="652" t="n"/>
+      <c r="H18" s="645">
+        <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/#:~:text=typically%20modeled%20at%20100%25","Verbatim: typically modeled at 100% → click")</f>
+        <v/>
+      </c>
+      <c r="I18" s="645">
+        <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/#:~:text=50-100%25%20of%20annual%20excess%20free%20cash%20flow","Verbatim: 50-100% of annual excess free cash flow → click")</f>
+        <v/>
+      </c>
+      <c r="J18" s="645">
+        <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/#:~:text=typically%20modeled%20at%20100%25","Verbatim: typically modeled at 100% → click")</f>
+        <v/>
+      </c>
+      <c r="K18" s="651" t="n"/>
     </row>
     <row r="19" ht="96" customHeight="1" s="244">
       <c r="B19" s="607" t="inlineStr">
@@ -6029,10 +6001,9 @@
           <t>Corporate income tax obligation. Perfectly reasonable because it strictly matches the current standard U.S. federal statutory corporate tax rate without aggressive tax-dodging assumptions.</t>
         </is>
       </c>
-      <c r="E19" s="645" t="inlineStr">
-        <is>
-          <t>IN EQ: US federal CIT=21% → C19=0.21 (PwC)</t>
-        </is>
+      <c r="E19" s="645">
+        <f>HYPERLINK("https://taxsummaries.pwc.com/united-states/corporate/taxes-on-corporate-income#:~:text=flat%20rate%20of%2021%25","IN EQ: US federal CIT=21% → C19=0.21 (PwC)")</f>
+        <v/>
       </c>
       <c r="F19" s="646" t="inlineStr">
         <is>
@@ -6049,13 +6020,12 @@
           <t>Trading Economics: 21 percent</t>
         </is>
       </c>
-      <c r="I19" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "flat rate of 21%"</t>
-        </is>
-      </c>
-      <c r="J19" s="652" t="n"/>
-      <c r="K19" s="652" t="n"/>
+      <c r="I19" s="645">
+        <f>HYPERLINK("https://taxsummaries.pwc.com/united-states/corporate/taxes-on-corporate-income#:~:text=flat%20rate%20of%2021%25","Verbatim: flat rate of 21% → click")</f>
+        <v/>
+      </c>
+      <c r="J19" s="651" t="n"/>
+      <c r="K19" s="651" t="n"/>
     </row>
     <row r="20" ht="96" customHeight="1" s="244">
       <c r="B20" s="613" t="inlineStr">
@@ -6071,10 +6041,9 @@
           <t>The valuation multiple upon selling. Set to 12.9x to match Aventis private SaaS EV/EBITDA 1st quartile (Ctrl+F 12.9x)—conservative lower-quartile exit, not PE median.</t>
         </is>
       </c>
-      <c r="E20" s="645" t="inlineStr">
-        <is>
-          <t>IN EQ: C20=12.9x = Aventis private SaaS EV/EBITDA 1st quartile 12.9x (was 13 round)</t>
-        </is>
+      <c r="E20" s="645">
+        <f>HYPERLINK("https://aventis-advisors.com/saas-valuation-multiples-how-much-is-my-saas-business-worth/#:~:text=12.9x","IN EQ: C20=12.9x = Aventis private SaaS EV/EBITDA 1st quartile 12.9x (was 13 round)")</f>
+        <v/>
       </c>
       <c r="F20" s="643" t="inlineStr">
         <is>
@@ -6087,13 +6056,12 @@
         </is>
       </c>
       <c r="H20" s="593" t="n"/>
-      <c r="I20" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "12.9x"</t>
-        </is>
-      </c>
-      <c r="J20" s="652" t="n"/>
-      <c r="K20" s="652" t="n"/>
+      <c r="I20" s="645">
+        <f>HYPERLINK("https://aventis-advisors.com/saas-valuation-multiples-how-much-is-my-saas-business-worth/#:~:text=12.9x","Verbatim: 12.9x → click")</f>
+        <v/>
+      </c>
+      <c r="J20" s="651" t="n"/>
+      <c r="K20" s="651" t="n"/>
     </row>
     <row r="21" ht="96" customHeight="1" s="244">
       <c r="B21" s="607" t="inlineStr">
@@ -6109,10 +6077,9 @@
           <t>This is historical assumptions without AI. Total initial sales spend is reasonable, representing roughly 35% of FY24 revenue, perfectly aligning with standard SaaS benchmarks.</t>
         </is>
       </c>
-      <c r="E21" s="645" t="inlineStr">
-        <is>
-          <t>IN EQ: Rev $1,214.3m; S&amp;M $414.1m (34.1%) → model 35%→$425m</t>
-        </is>
+      <c r="E21" s="645">
+        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results#:~:text=%241%2C214.3","IN EQ: Rev $1,214.3m; S&amp;M $414.1m (34.1%) → model 35%→$425m")</f>
+        <v/>
       </c>
       <c r="F21" s="646" t="inlineStr">
         <is>
@@ -6124,25 +6091,21 @@
           <t>Go to AI_Operating!C9 (S&amp;M human FY24A)</t>
         </is>
       </c>
-      <c r="H21" s="593" t="inlineStr">
-        <is>
-          <t>SEC 10-K Sales and marketing $414.1</t>
-        </is>
-      </c>
-      <c r="I21" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "$1,214.3"</t>
-        </is>
-      </c>
-      <c r="J21" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "414.1"</t>
-        </is>
-      </c>
-      <c r="K21" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "414.1" (10-K)</t>
-        </is>
+      <c r="H21" s="645">
+        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results#:~:text=414.1","SEC 10-K Sales and marketing $414.1")</f>
+        <v/>
+      </c>
+      <c r="I21" s="645">
+        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results#:~:text=%241%2C214.3","Verbatim: $1,214.3 → click")</f>
+        <v/>
+      </c>
+      <c r="J21" s="645">
+        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results#:~:text=414.1","Verbatim: 414.1 → click")</f>
+        <v/>
+      </c>
+      <c r="K21" s="645">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm#:~:text=%24414.1","Verbatim: $414.1' (10-K) → click")</f>
+        <v/>
       </c>
     </row>
     <row r="22" ht="96" customHeight="1" s="244">
@@ -6159,10 +6122,9 @@
           <t>This is historical assumptions without AI. The fixed salary portion is reasonable, representing 75% of S&amp;M, accurately reflecting that human software sales floors are base-salary heavy.</t>
         </is>
       </c>
-      <c r="E22" s="642" t="inlineStr">
-        <is>
-          <t>IN EQ: ~70% base OTE → model 75%×$425m=$318.8m</t>
-        </is>
+      <c r="E22" s="645">
+        <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep#:~:text=70%2F30%20base%2Fvariable%20split","IN EQ: ~70% base OTE → model 75%×$425m=$318.8m")</f>
+        <v/>
       </c>
       <c r="F22" s="646" t="inlineStr">
         <is>
@@ -6175,17 +6137,16 @@
         </is>
       </c>
       <c r="H22" s="593" t="n"/>
-      <c r="I22" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "70/30"</t>
-        </is>
-      </c>
-      <c r="J22" s="651" t="inlineStr">
-        <is>
-          <t>$318.8 / 75%: MODEL carve</t>
-        </is>
-      </c>
-      <c r="K22" s="652" t="n"/>
+      <c r="I22" s="645">
+        <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep#:~:text=70%2F30%20base%2Fvariable%20split","Verbatim: 70/30 base/variable split → click")</f>
+        <v/>
+      </c>
+      <c r="J22" s="643" t="inlineStr">
+        <is>
+          <t>$318.8 / 75%: MODEL carve (no link)</t>
+        </is>
+      </c>
+      <c r="K22" s="651" t="n"/>
     </row>
     <row r="23" ht="96" customHeight="1" s="244">
       <c r="B23" s="607" t="inlineStr">
@@ -6201,10 +6162,9 @@
           <t>This is historical assumptions without AI. The variable payout is reasonable, calculating exactly to the remaining 25% of the budget, representing standard quota-based enterprise sales incentives.</t>
         </is>
       </c>
-      <c r="E23" s="642" t="inlineStr">
-        <is>
-          <t>IN EQ: residual 25%×$425m=$106.2m (near sourced ~30–35% variable)</t>
-        </is>
+      <c r="E23" s="645">
+        <f>HYPERLINK("https://syncgtm.com/blog/how-much-do-sales-development-representatives-make-at-tech-companies#:~:text=30%E2%80%9335%25%20of%20total%20pay","IN EQ: residual 25%×$425m=$106.2m (near sourced ~30–35% variable)")</f>
+        <v/>
       </c>
       <c r="F23" s="646" t="inlineStr">
         <is>
@@ -6221,17 +6181,16 @@
           <t>70/30 pay article</t>
         </is>
       </c>
-      <c r="I23" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "30–35%"</t>
-        </is>
-      </c>
-      <c r="J23" s="651" t="inlineStr">
-        <is>
-          <t>$106.2 / 25%: MODEL carve</t>
-        </is>
-      </c>
-      <c r="K23" s="652" t="n"/>
+      <c r="I23" s="645">
+        <f>HYPERLINK("https://syncgtm.com/blog/how-much-do-sales-development-representatives-make-at-tech-companies#:~:text=30%E2%80%9335%25%20of%20total%20pay","Verbatim: 30–35% of total pay → click")</f>
+        <v/>
+      </c>
+      <c r="J23" s="643" t="inlineStr">
+        <is>
+          <t>$106.2 / 25%: MODEL carve (no link)</t>
+        </is>
+      </c>
+      <c r="K23" s="651" t="n"/>
     </row>
     <row r="24" ht="96" customHeight="1" s="244">
       <c r="B24" s="613" t="inlineStr">
@@ -6247,10 +6206,9 @@
           <t>This is historical assumptions without AI. Normal hardware and capitalized software spending is reasonable for asset-light tech companies investing heavily in code rather than factories.</t>
         </is>
       </c>
-      <c r="E24" s="645" t="inlineStr">
-        <is>
-          <t>IN EQ band: SaaS CapEx 1–3% of rev (SaaSDB) → C24=2% = midpoint of that band</t>
-        </is>
+      <c r="E24" s="645">
+        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/#:~:text=Most%20pure-play%20SaaS%20companies%20report%20CapEx%20of","IN EQ band: SaaS CapEx 1–3% of rev (SaaSDB) → C24=2% = midpoint of that band")</f>
+        <v/>
       </c>
       <c r="F24" s="646" t="inlineStr">
         <is>
@@ -6263,17 +6221,16 @@
         </is>
       </c>
       <c r="H24" s="593" t="n"/>
-      <c r="I24" s="645" t="inlineStr">
-        <is>
-          <t>CLICK → FIND "CapEx of 1" (en-dash 1–3%)</t>
-        </is>
-      </c>
-      <c r="J24" s="651" t="inlineStr">
-        <is>
-          <t>2%: MODEL midpoint of 1–3% band</t>
-        </is>
-      </c>
-      <c r="K24" s="652" t="n"/>
+      <c r="I24" s="645">
+        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/#:~:text=Most%20pure-play%20SaaS%20companies%20report%20CapEx%20of","Verbatim: Most pure-play SaaS companies report CapEx of 1–3% of revenue → click")</f>
+        <v/>
+      </c>
+      <c r="J24" s="643" t="inlineStr">
+        <is>
+          <t>2%: MODEL midpoint of 1–3% band (no link)</t>
+        </is>
+      </c>
+      <c r="K24" s="651" t="n"/>
     </row>
     <row r="25" ht="96" customHeight="1" s="244">
       <c r="B25" s="607" t="inlineStr">
@@ -6305,13 +6262,13 @@
         </is>
       </c>
       <c r="H25" s="593" t="n"/>
-      <c r="I25" s="651" t="inlineStr">
-        <is>
-          <t>2% WC plug: N/A MODEL CONST</t>
-        </is>
-      </c>
-      <c r="J25" s="652" t="n"/>
-      <c r="K25" s="652" t="n"/>
+      <c r="I25" s="643" t="inlineStr">
+        <is>
+          <t>2% WC plug: N/A — MODEL CONST (no link)</t>
+        </is>
+      </c>
+      <c r="J25" s="651" t="n"/>
+      <c r="K25" s="651" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="618" t="inlineStr">
@@ -6351,13 +6308,13 @@
         </is>
       </c>
       <c r="H27" s="593" t="n"/>
-      <c r="I27" s="651" t="inlineStr">
-        <is>
-          <t>Uses rows 14–15 FIND links</t>
-        </is>
-      </c>
-      <c r="J27" s="652" t="n"/>
-      <c r="K27" s="652" t="n"/>
+      <c r="I27" s="643" t="inlineStr">
+        <is>
+          <t>See FIND links on rows 14–15</t>
+        </is>
+      </c>
+      <c r="J27" s="651" t="n"/>
+      <c r="K27" s="651" t="n"/>
     </row>
     <row r="28" ht="96" customHeight="1" s="244">
       <c r="B28" s="607" t="inlineStr">
@@ -6390,13 +6347,13 @@
         </is>
       </c>
       <c r="H28" s="593" t="n"/>
-      <c r="I28" s="651" t="inlineStr">
-        <is>
-          <t>Uses rows 14 &amp; 16 FIND links</t>
-        </is>
-      </c>
-      <c r="J28" s="652" t="n"/>
-      <c r="K28" s="652" t="n"/>
+      <c r="I28" s="643" t="inlineStr">
+        <is>
+          <t>See FIND links on rows 14 &amp; 16</t>
+        </is>
+      </c>
+      <c r="J28" s="651" t="n"/>
+      <c r="K28" s="651" t="n"/>
     </row>
     <row r="29" ht="72" customHeight="1" s="244">
       <c r="B29" s="618" t="inlineStr">
@@ -6452,12 +6409,12 @@
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>How FIND links work:</t>
-        </is>
-      </c>
-      <c r="C33" s="574" t="inlineStr">
-        <is>
-          <t>Blue FIND cells use Chrome Scroll-to-Text (#:~:text=...). Click → browser opens the URL and highlights the quote (same effect as Ctrl+F landing on that string). Use Chrome or Edge.</t>
+          <t>HOW TO USE VERBATIM LINKS:</t>
+        </is>
+      </c>
+      <c r="C33" s="653" t="inlineStr">
+        <is>
+          <t>Go to columns I, J, K. Blue cells are Excel HYPERLINK formulas. Click the blue verbatim text → browser opens the source and jumps to/highlights that quote. Example row 9: I9 White Space $5,000-10,000+ | J9 Miniloop $10,000-$15,000+ | K9 SEC 1,513.</t>
         </is>
       </c>
     </row>
@@ -6479,88 +6436,39 @@
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -938,7 +938,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="46">
+  <fills count="47">
     <fill>
       <patternFill/>
     </fill>
@@ -1171,6 +1171,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -1970,7 +1975,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="654">
+  <cellXfs count="662">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3154,6 +3159,24 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="46" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="36" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="115" fillId="36" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="115" fillId="46" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5337,9 +5360,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K34"/>
+  <dimension ref="A2:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
+    <col width="16" customWidth="1" style="244" min="1" max="1"/>
     <col width="26" customWidth="1" style="244" min="2" max="2"/>
     <col width="11" customWidth="1" style="244" min="3" max="3"/>
     <col width="52" customWidth="1" style="244" min="4" max="4"/>
@@ -5355,18 +5379,23 @@
     <row r="2">
       <c r="B2" s="629" t="inlineStr">
         <is>
-          <t>Assumptions Drivers — columns I/J/K are =HYPERLINK() to the verbatim quote (click the blue text). Opens source with quote highlighted in Chrome/Edge.</t>
+          <t>Assumptions Drivers — Col A = Baseline Yes/No. YES = derived from company past performance (ZI FY24 pools). NO = external source / market rate / MODEL CONST / AI thesis lever. Verbatim click-links: cols I/J/K.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>If a cell says MODEL CONST there is no link. Scroll right to columns I, J, K for Verbatim hyperlinks on every sourced row.</t>
+          <t>Baseline YES = rows 21–23 only (S&amp;M $425 / payroll $318.8 / commission $106.2 from FY24). All forward rates and AI levers = Baseline NO.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1" s="244">
+      <c r="A4" s="654" t="inlineStr">
+        <is>
+          <t>Baseline Yes/No</t>
+        </is>
+      </c>
       <c r="B4" s="606" t="inlineStr">
         <is>
           <t>Driver</t>
@@ -5419,6 +5448,11 @@
       </c>
     </row>
     <row r="5" ht="96" customHeight="1" s="244">
+      <c r="A5" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B5" s="607" t="inlineStr">
         <is>
           <t>Revenue growth</t>
@@ -5465,6 +5499,11 @@
       </c>
     </row>
     <row r="6" ht="96" customHeight="1" s="244">
+      <c r="A6" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B6" s="613" t="inlineStr">
         <is>
           <t>Gross margin</t>
@@ -5501,6 +5540,11 @@
       <c r="K6" s="651" t="n"/>
     </row>
     <row r="7" ht="96" customHeight="1" s="244">
+      <c r="A7" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B7" s="607" t="inlineStr">
         <is>
           <t>Sales payroll cut (Y1)</t>
@@ -5537,6 +5581,11 @@
       <c r="K7" s="651" t="n"/>
     </row>
     <row r="8" ht="96" customHeight="1" s="244">
+      <c r="A8" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B8" s="613" t="inlineStr">
         <is>
           <t>Variable commission cut</t>
@@ -5583,6 +5632,11 @@
       </c>
     </row>
     <row r="9" ht="96" customHeight="1" s="244">
+      <c r="A9" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B9" s="607" t="inlineStr">
         <is>
           <t>AI infrastructure ($m)</t>
@@ -5628,6 +5682,11 @@
       </c>
     </row>
     <row r="10" ht="96" customHeight="1" s="244">
+      <c r="A10" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B10" s="613" t="inlineStr">
         <is>
           <t>S&amp;M expense growth Y2+</t>
@@ -5668,6 +5727,11 @@
       <c r="K10" s="651" t="n"/>
     </row>
     <row r="11" ht="96" customHeight="1" s="244">
+      <c r="A11" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B11" s="607" t="inlineStr">
         <is>
           <t>G&amp;A % of revenue</t>
@@ -5710,6 +5774,11 @@
       <c r="K11" s="651" t="n"/>
     </row>
     <row r="12" ht="96" customHeight="1" s="244">
+      <c r="A12" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B12" s="613" t="inlineStr">
         <is>
           <t>CapEx reduction vs base</t>
@@ -5720,7 +5789,7 @@
       </c>
       <c r="D12" s="609" t="inlineStr">
         <is>
-          <t>Lowers physical equipment spending. Reasonable because firing 15% of the sales team permanently eliminates the need to purchase and refresh their laptops and hardware.</t>
+          <t>Lowers physical equipment spending. Reasonable because firing 18% of the sales team permanently eliminates the need to purchase and refresh their laptops and hardware.</t>
         </is>
       </c>
       <c r="E12" s="643" t="inlineStr">
@@ -5748,6 +5817,11 @@
       <c r="K12" s="651" t="n"/>
     </row>
     <row r="13" ht="96" customHeight="1" s="244">
+      <c r="A13" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B13" s="607" t="inlineStr">
         <is>
           <t>WC / receivables improvement</t>
@@ -5786,6 +5860,11 @@
       <c r="K13" s="651" t="n"/>
     </row>
     <row r="14" ht="96" customHeight="1" s="244">
+      <c r="A14" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B14" s="613" t="inlineStr">
         <is>
           <t>SOFR</t>
@@ -5826,6 +5905,11 @@
       <c r="K14" s="651" t="n"/>
     </row>
     <row r="15" ht="96" customHeight="1" s="244">
+      <c r="A15" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B15" s="607" t="inlineStr">
         <is>
           <t>Term Loan A spread</t>
@@ -5866,6 +5950,11 @@
       <c r="K15" s="651" t="n"/>
     </row>
     <row r="16" ht="96" customHeight="1" s="244">
+      <c r="A16" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B16" s="613" t="inlineStr">
         <is>
           <t>Term Loan B spread</t>
@@ -5906,6 +5995,11 @@
       <c r="K16" s="651" t="n"/>
     </row>
     <row r="17" ht="96" customHeight="1" s="244">
+      <c r="A17" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B17" s="607" t="inlineStr">
         <is>
           <t>Mandatory amortization</t>
@@ -5946,6 +6040,11 @@
       <c r="K17" s="651" t="n"/>
     </row>
     <row r="18" ht="96" customHeight="1" s="244">
+      <c r="A18" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B18" s="613" t="inlineStr">
         <is>
           <t>Cash sweep %</t>
@@ -5988,6 +6087,11 @@
       <c r="K18" s="651" t="n"/>
     </row>
     <row r="19" ht="96" customHeight="1" s="244">
+      <c r="A19" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B19" s="607" t="inlineStr">
         <is>
           <t>Tax rate</t>
@@ -6028,6 +6132,11 @@
       <c r="K19" s="651" t="n"/>
     </row>
     <row r="20" ht="96" customHeight="1" s="244">
+      <c r="A20" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B20" s="613" t="inlineStr">
         <is>
           <t>Exit EV/EBITDA multiple</t>
@@ -6064,6 +6173,11 @@
       <c r="K20" s="651" t="n"/>
     </row>
     <row r="21" ht="96" customHeight="1" s="244">
+      <c r="A21" s="656" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="B21" s="607" t="inlineStr">
         <is>
           <t>S&amp;M baseline ($m)</t>
@@ -6109,6 +6223,11 @@
       </c>
     </row>
     <row r="22" ht="96" customHeight="1" s="244">
+      <c r="A22" s="656" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="B22" s="613" t="inlineStr">
         <is>
           <t>Payroll baseline ($m)</t>
@@ -6149,6 +6268,11 @@
       <c r="K22" s="651" t="n"/>
     </row>
     <row r="23" ht="96" customHeight="1" s="244">
+      <c r="A23" s="656" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="B23" s="607" t="inlineStr">
         <is>
           <t>Commission baseline ($m)</t>
@@ -6193,6 +6317,11 @@
       <c r="K23" s="651" t="n"/>
     </row>
     <row r="24" ht="96" customHeight="1" s="244">
+      <c r="A24" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B24" s="613" t="inlineStr">
         <is>
           <t>CapEx base % of rev</t>
@@ -6233,6 +6362,11 @@
       <c r="K24" s="651" t="n"/>
     </row>
     <row r="25" ht="96" customHeight="1" s="244">
+      <c r="A25" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B25" s="607" t="inlineStr">
         <is>
           <t>WC base % of Δrev</t>
@@ -6278,6 +6412,11 @@
       </c>
     </row>
     <row r="27" ht="96" customHeight="1" s="244">
+      <c r="A27" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B27" s="613" t="inlineStr">
         <is>
           <t>TLA rate (SOFR+4)</t>
@@ -6317,6 +6456,11 @@
       <c r="K27" s="651" t="n"/>
     </row>
     <row r="28" ht="96" customHeight="1" s="244">
+      <c r="A28" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="B28" s="607" t="inlineStr">
         <is>
           <t>TLB rate (SOFR+5)</t>
@@ -6427,6 +6571,18 @@
       <c r="C34" s="574" t="inlineStr">
         <is>
           <t>I → White Space $5,000-10,000+ highlighted | J → Miniloop $10,000-$15,000+ highlighted | K → SEC 1,513 in sales and marketing highlighted</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Baseline legend (col A):</t>
+        </is>
+      </c>
+      <c r="C35" s="574" t="inlineStr">
+        <is>
+          <t>YES = yellow value derived from ZI past performance / FY24 S&amp;M pools. NO = external publication, market quote, MODEL CONST, or AI operating lever.</t>
         </is>
       </c>
     </row>
@@ -12728,7 +12884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M43"/>
+  <dimension ref="B2:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" style="244" min="2" max="2"/>
@@ -12743,6 +12899,7 @@
     <col width="28" customWidth="1" style="244" min="11" max="11"/>
     <col width="40" customWidth="1" style="244" min="12" max="12"/>
     <col width="70" customWidth="1" style="244" min="13" max="13"/>
+    <col width="14" customWidth="1" style="244" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -12762,7 +12919,7 @@
     <row r="4">
       <c r="B4" s="570" t="inlineStr">
         <is>
-          <t>PDF: https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.pdf</t>
+          <t>PDF: https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_DRIVER_SOURCES.pdf</t>
         </is>
       </c>
     </row>
@@ -12825,6 +12982,11 @@
       <c r="M6" s="557" t="inlineStr">
         <is>
           <t>Commentary (Why / What changed)</t>
+        </is>
+      </c>
+      <c r="N6" s="657" t="inlineStr">
+        <is>
+          <t>Baseline Yes/No</t>
         </is>
       </c>
     </row>
@@ -12887,6 +13049,11 @@
           <t>Annual growth remains stable at ten percent. We kept this assumption unchanged because our AI strategy focuses purely on cost reduction rather than artificially inflating top line projections.</t>
         </is>
       </c>
+      <c r="N7" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="78" customHeight="1" s="244">
       <c r="B8" s="571" t="n">
@@ -12947,6 +13114,11 @@
           <t>Expansion reached precisely eighty percent. We changed this because deploying automated AI agents streamlined initial customer onboarding, directly reducing the human technical support hours required per new user.</t>
         </is>
       </c>
+      <c r="N8" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="78" customHeight="1" s="244">
       <c r="B9" s="571" t="n">
@@ -12959,7 +13131,7 @@
       </c>
       <c r="D9" s="571" t="inlineStr">
         <is>
-          <t>−15% in Year 1</t>
+          <t>−18% in Year 1</t>
         </is>
       </c>
       <c r="E9" s="571" t="inlineStr">
@@ -12999,12 +13171,17 @@
       </c>
       <c r="L9" s="571" t="inlineStr">
         <is>
-          <t>Payroll_Y1 = Assumptions_Drivers!C22 × (1 − C7). Baseline payroll = C22.</t>
+          <t>Payroll_Y1 = Assumptions_Drivers!C22 × (1 − C7). C7=18%. Baseline payroll = C22.</t>
         </is>
       </c>
       <c r="M9" s="573" t="inlineStr">
         <is>
-          <t>Baseline costs dropped by fifteen percent immediately. We changed this to reflect the aggressive termination of outbound human development representatives, instantly eliminating their recurring annual base salary expenses.</t>
+          <t>Sales payroll cut 18% in Y1 — matches published US B2B SaaS net SDR headcount decline of 18% YoY (Assumptions_Drivers!C7). Synced from Drivers (was −15%).</t>
+        </is>
+      </c>
+      <c r="N9" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -13067,6 +13244,11 @@
           <t>Rates decreased significantly starting in year one. Replacing human representatives with AI meant fewer outbound deals required traditional payouts, allowing the company to retain higher profit per sale.</t>
         </is>
       </c>
+      <c r="N10" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="78" customHeight="1" s="244">
       <c r="B11" s="571" t="n">
@@ -13127,6 +13309,11 @@
           <t>A new fixed thirty-four million dollar expense was added. We included this vital change to cover enterprise software licenses, API usage limits, and compute power running the AI. SOURCE (LBOMODEL2): $34m triangulated from Salesforce Agentforce public pricing ($2/conversation; Flex Credits ~$0.10/action) and ZoomInfo 10-K S&amp;M headcount (1,513). Full math + clickable links: sheet Assumptions_Drivers (cols E–G). Primary link: https://www.salesforce.com/news/press-releases/2025/05/15/agentforce-flexible-pricing-news/</t>
         </is>
       </c>
+      <c r="N11" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="78" customHeight="1" s="244">
       <c r="B12" s="571" t="n">
@@ -13187,6 +13374,11 @@
           <t>Expense growth was permanently capped at two percent. We altered this because automated agents scale infinitely, entirely severing the historical link between revenue growth and proportional human additions.</t>
         </is>
       </c>
+      <c r="N12" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="78" customHeight="1" s="244">
       <c r="B13" s="571" t="n">
@@ -13199,7 +13391,7 @@
       </c>
       <c r="D13" s="571" t="inlineStr">
         <is>
-          <t>Locked at baseline % of revenue</t>
+          <t>18% of revenue</t>
         </is>
       </c>
       <c r="E13" s="571" t="inlineStr">
@@ -13244,7 +13436,12 @@
       </c>
       <c r="M13" s="573" t="inlineStr">
         <is>
-          <t>General overhead remained locked at baseline percentages. We avoided changing this because the value creation strategy strictly impacts the active sales floor without altering corporate finance or compensation.</t>
+          <t>G&amp;A = 18% of revenue (Assumptions_Drivers!C11 = Blossom 2025 SaaS median). Same % in AI and Base; not ZI filing ~24.3%.</t>
+        </is>
+      </c>
+      <c r="N13" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -13307,6 +13504,11 @@
           <t>Hardware spending was reduced by five percent. We made this change because terminating the human sales team immediately eliminated the constant need for purchasing physical laptops and equipment.</t>
         </is>
       </c>
+      <c r="N14" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="78" customHeight="1" s="244">
       <c r="B15" s="571" t="n">
@@ -13367,6 +13569,11 @@
           <t>Receivables collection periods improved slightly overall. Implementing automated AI billing reminders accelerated cash collections from late customers, lowering total working capital requirements and freeing extra cash for debt.</t>
         </is>
       </c>
+      <c r="N15" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="78" customHeight="1" s="244">
       <c r="B16" s="571" t="n">
@@ -13379,7 +13586,7 @@
       </c>
       <c r="D16" s="571" t="inlineStr">
         <is>
-          <t>SOFR + 4.00%</t>
+          <t>SOFR 4.30% + 4.00% (= 8.30%)</t>
         </is>
       </c>
       <c r="E16" s="571" t="inlineStr">
@@ -13425,6 +13632,11 @@
       <c r="M16" s="573" t="inlineStr">
         <is>
           <t>The interest rate remained static at SOFR plus four. This was unchanged because the macroeconomic lending environment and the base company credit profile strictly dictate senior pricing.</t>
+        </is>
+      </c>
+      <c r="N16" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -13439,7 +13651,7 @@
       </c>
       <c r="D17" s="571" t="inlineStr">
         <is>
-          <t>SOFR + 5.00%</t>
+          <t>SOFR 4.30% + 5.00% (= 9.30%)</t>
         </is>
       </c>
       <c r="E17" s="571" t="inlineStr">
@@ -13485,6 +13697,11 @@
       <c r="M17" s="573" t="inlineStr">
         <is>
           <t>Pricing was maintained exactly at SOFR plus five. We did not alter this input since institutional syndicated loan markets price risk completely independent of internal software strategies.</t>
+        </is>
+      </c>
+      <c r="N17" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -13547,6 +13764,11 @@
           <t>Principal repayment schedules were held constant at one percent. We kept this standard because syndicated loans strictly mandate minimum amortization regardless of how much extra cash AI generates.</t>
         </is>
       </c>
+      <c r="N18" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="78" customHeight="1" s="244">
       <c r="B19" s="571" t="n">
@@ -13607,6 +13829,11 @@
           <t>One hundred percent of excess cash targets debt paydown. This remained unchanged to ensure all newly generated margins from AI savings aggressively reduce leverage and maximize sponsor returns.</t>
         </is>
       </c>
+      <c r="N19" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="78" customHeight="1" s="244">
       <c r="B20" s="571" t="n">
@@ -13667,6 +13894,11 @@
           <t>The corporate tax rate remained steady at twenty one percent. We did not change this assumption because federal statutory tax obligations remain unaffected by internal operating margin improvements.</t>
         </is>
       </c>
+      <c r="N20" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="78" customHeight="1" s="244">
       <c r="B21" s="571" t="n">
@@ -13679,7 +13911,7 @@
       </c>
       <c r="D21" s="571" t="inlineStr">
         <is>
-          <t>13.0x EV / EBITDA</t>
+          <t>12.9x EV / EBITDA</t>
         </is>
       </c>
       <c r="E21" s="571" t="inlineStr">
@@ -13719,133 +13951,316 @@
       </c>
       <c r="L21" s="571" t="inlineStr">
         <is>
-          <t>Exit_EV = Y5_EBITDA × Assumptions_Drivers!C20; Exit_Equity = Exit_EV − Debt_end; MOIC / IRR from that.</t>
+          <t>Exit_EV = Y5_EBITDA × Assumptions_Drivers!C20 (12.9x); Exit_Equity = Exit_EV − Debt_end; MOIC / IRR from that.</t>
         </is>
       </c>
       <c r="M21" s="573" t="inlineStr">
         <is>
-          <t>The valuation multiple was securely locked at thirteen. We kept this exact multiple consistent across scenarios to prove equity value creation stemmed purely from AI operational improvements alone.</t>
+          <t>Exit multiple 12.9x EV/EBITDA = Aventis private SaaS 1st quartile (Assumptions_Drivers!C20). Synced from Drivers (was 13.0x).</t>
+        </is>
+      </c>
+      <c r="N21" s="655" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="618" t="inlineStr">
+        <is>
+          <t>BASELINE POOLS (must match Assumptions_Drivers)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="564" t="inlineStr">
-        <is>
-          <t>NOTE ON DCF TAB</t>
+      <c r="B23" s="564" t="n">
+        <v>16</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>S&amp;M baseline ($m)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>$425.0m</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>C21</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C21</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>ZI FY24-derived (~35%×$1,214.3m near filing $414.1m)</t>
+        </is>
+      </c>
+      <c r="N23" s="658" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="574" t="inlineStr">
-        <is>
-          <t>These AI-SDR operating assumptions are NOT the primary drivers of the DCF tab. IRR/MOIC value-creation math is on Strategy_Summary, AI_Operating, Base_Operating, Debt_Sweep_AI, and LBO!D17/J275. DCF remains a secondary WSP shell for football-field context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
+      <c r="B24" s="574" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Payroll baseline ($m)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>$318.8m</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>C22</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C22</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>75% × $425m FY24 S&amp;M carve</t>
+        </is>
+      </c>
+      <c r="N24" s="658" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>18</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Commission baseline ($m)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>$106.2m</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>C23</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C23</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>25% × $425m FY24 S&amp;M carve</t>
+        </is>
+      </c>
+      <c r="N25" s="658" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>19</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CapEx base % of rev</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>C24</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C24</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>External SaaS CapEx 1–3% midpoint</t>
+        </is>
+      </c>
+      <c r="N26" s="659" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="B27" s="564" t="inlineStr">
-        <is>
-          <t>AI Infrastructure $34m — SOURCE PACK</t>
+      <c r="B27" s="564" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>WC base % of Δrev</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C25</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>MODEL CONST plug</t>
+        </is>
+      </c>
+      <c r="N27" s="659" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="590" t="inlineStr">
-        <is>
-          <t>Go to Assumptions_Drivers (cols E–G) (in-workbook evidence)</t>
-        </is>
-      </c>
+      <c r="B28" s="590" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="590" t="inlineStr">
-        <is>
-          <t>Salesforce Agentforce pricing press release</t>
+      <c r="B29" s="660" t="inlineStr">
+        <is>
+          <t>NOTE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="590" t="inlineStr">
         <is>
-          <t>ZoomInfo FY2024 10-K (S&amp;M headcount)</t>
+          <t>This list must match Assumptions_Drivers: payroll cut −18%, exit 12.9x, AI infra $34m, G&amp;A 18%, SOFR 4.30%. Col N = Baseline Yes/No (same rule as Drivers col A).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="590" t="inlineStr">
-        <is>
-          <t>PDF: LBOMODEL2_AI_COST_SOURCES.pdf</t>
+      <c r="B31" s="590" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="618" t="inlineStr">
+        <is>
+          <t>SOURCES / VERBATIM</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="564" t="inlineStr">
-        <is>
-          <t>SOURCE MAP: open Assumptions_Drivers — columns E (link), F (~30-word justification), G (secondary link) on each driver row.</t>
+      <c r="B33" s="661" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers: Col A Baseline Yes/No | Col E source | Cols I/J/K clickable Verbatim. PDF: https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_DRIVER_SOURCES.pdf</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="593" t="inlineStr">
-        <is>
-          <t>Jump to AI infra source row (E9)</t>
-        </is>
-      </c>
+      <c r="B34" s="593" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="593" t="inlineStr">
-        <is>
-          <t>PDF: all driver sources</t>
-        </is>
-      </c>
-    </row>
+      <c r="B35" s="593" t="n"/>
+    </row>
+    <row r="36"/>
     <row r="37">
-      <c r="B37" s="564" t="inlineStr">
-        <is>
-          <t>SOURCE MAP: open Assumptions_Drivers — columns E (link), F (~30-word justification), G (secondary link) on each driver row.</t>
-        </is>
-      </c>
+      <c r="B37" s="564" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="593" t="inlineStr">
-        <is>
-          <t>Jump to AI infra source row (E9)</t>
-        </is>
-      </c>
+      <c r="B38" s="593" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="593" t="inlineStr">
-        <is>
-          <t>PDF: all driver sources</t>
-        </is>
-      </c>
-    </row>
+      <c r="B39" s="593" t="n"/>
+    </row>
+    <row r="40"/>
     <row r="41">
-      <c r="B41" s="564" t="inlineStr">
-        <is>
-          <t>SOURCE MAP: open Assumptions_Drivers — columns E (link), F (~30-word justification), G (secondary link) on each driver row.</t>
-        </is>
-      </c>
+      <c r="B41" s="564" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="593" t="inlineStr">
-        <is>
-          <t>Jump to AI infra source row (E9)</t>
-        </is>
-      </c>
+      <c r="B42" s="593" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="593" t="inlineStr">
-        <is>
-          <t>PDF: all driver sources</t>
-        </is>
-      </c>
-    </row>
+      <c r="B43" s="593" t="n"/>
+    </row>
+    <row r="44"/>
+    <row r="45"/>
   </sheetData>
   <autoFilter ref="B6:M21"/>
-  <mergeCells count="1">
-    <mergeCell ref="B24:M25"/>
-  </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId2"/>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -5379,14 +5379,14 @@
     <row r="2">
       <c r="B2" s="629" t="inlineStr">
         <is>
-          <t>Assumptions Drivers — Col A = Baseline Yes/No. YES = derived from company past performance (ZI FY24 pools). NO = external source / market rate / MODEL CONST / AI thesis lever. Verbatim click-links: cols I/J/K.</t>
+          <t>Assumptions Drivers — Col A Baseline Yes/No. Col E/H = source page link (opens page only). Cols I/J/K = plain Verbatim strings — copy into Ctrl+F on that source (no hyperlink).</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>Baseline YES = rows 21–23 only (S&amp;M $425 / payroll $318.8 / commission $106.2 from FY24). All forward rates and AI levers = Baseline NO.</t>
+          <t>How to verify: click Source (E) → open page → copy Verbatim from I/J/K → Ctrl+F → paste.</t>
         </is>
       </c>
     </row>
@@ -5433,17 +5433,17 @@
       </c>
       <c r="I4" s="641" t="inlineStr">
         <is>
-          <t>Verbatim 1 (click blue link — opens source at quote)</t>
+          <t>Verbatim 1 — copy this into Ctrl+F on the source page</t>
         </is>
       </c>
       <c r="J4" s="641" t="inlineStr">
         <is>
-          <t>Verbatim 2 (click blue link — opens source at quote)</t>
+          <t>Verbatim 2 — copy this into Ctrl+F on the source page</t>
         </is>
       </c>
       <c r="K4" s="641" t="inlineStr">
         <is>
-          <t>Verbatim 3 (click blue link — opens source at quote)</t>
+          <t>Verbatim 3 — copy this into Ctrl+F on the source page</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="E5" s="645">
-        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results#:~:text=GAAP%20Revenue%20of%20%241%2C214.3%20million","IN EQ $ base only: FY24 Rev=$1,214.3m (ZI). C5=10% = MODEL CONST (10% not in filing).")</f>
+        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results","IN EQ $ base only: FY24 Rev=$1,214.3m (ZI). C5=10% = MODEL CONST (10% not in filing).")</f>
         <v/>
       </c>
       <c r="F5" s="643" t="inlineStr">
@@ -5481,20 +5481,22 @@
         </is>
       </c>
       <c r="H5" s="645">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm#:~:text=We%20generated%20revenue%20of%20%241%2C214.3%20million","SEC 10-K same $1,214.3m")</f>
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","SEC 10-K same $1,214.3m")</f>
         <v/>
       </c>
-      <c r="I5" s="645">
-        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results#:~:text=GAAP%20Revenue%20of%20%241%2C214.3%20million","Verbatim: GAAP Revenue of $1,214.3 million → click")</f>
-        <v/>
-      </c>
-      <c r="J5" s="645">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm#:~:text=We%20generated%20revenue%20of%20%241%2C214.3%20million","Verbatim: We generated revenue of $1,214.3 million' (10-K) → click")</f>
-        <v/>
+      <c r="I5" s="643" t="inlineStr">
+        <is>
+          <t>Ctrl+F: GAAP Revenue of $1,214.3 million</t>
+        </is>
+      </c>
+      <c r="J5" s="643" t="inlineStr">
+        <is>
+          <t>Ctrl+F: We generated revenue of $1,214.3 million</t>
+        </is>
       </c>
       <c r="K5" s="643" t="inlineStr">
         <is>
-          <t>10% growth: N/A — MODEL CONST (no link)</t>
+          <t>10% growth: N/A — MODEL CONST</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5520,7 @@
         </is>
       </c>
       <c r="E6" s="645">
-        <f>HYPERLINK("https://www.getaleph.com/answers/saas-gross-margin-2026#:~:text=The%202025%20median%20software%20gross%20margin%20is%2080%25","IN EQ: software median GM=80% → C6=0.80 (Aleph × Benchmarkit)")</f>
+        <f>HYPERLINK("https://www.getaleph.com/answers/saas-gross-margin-2026","IN EQ: software median GM=80% → C6=0.80 (Aleph × Benchmarkit)")</f>
         <v/>
       </c>
       <c r="F6" s="646" t="inlineStr">
@@ -5532,9 +5534,10 @@
         </is>
       </c>
       <c r="H6" s="593" t="n"/>
-      <c r="I6" s="645">
-        <f>HYPERLINK("https://www.getaleph.com/answers/saas-gross-margin-2026#:~:text=The%202025%20median%20software%20gross%20margin%20is%2080%25","Verbatim: The 2025 median software gross margin is 80% → click")</f>
-        <v/>
+      <c r="I6" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: The 2025 median software gross margin is 80%</t>
+        </is>
       </c>
       <c r="J6" s="651" t="n"/>
       <c r="K6" s="651" t="n"/>
@@ -5559,7 +5562,7 @@
         </is>
       </c>
       <c r="E7" s="645">
-        <f>HYPERLINK("https://www.digitalapplied.com/blog/ai-sdr-statistics-2026-outbound-sales-data-points#:~:text=down%2018%25%20YoY","IN EQ: C7=18% = US B2B SaaS net SDR headcount down 18% YoY (Digital Applied / Bridge Group)")</f>
+        <f>HYPERLINK("https://www.digitalapplied.com/blog/ai-sdr-statistics-2026-outbound-sales-data-points","IN EQ: C7=18% = US B2B SaaS net SDR headcount down 18% YoY (Digital Applied / Bridge Group)")</f>
         <v/>
       </c>
       <c r="F7" s="646" t="inlineStr">
@@ -5573,9 +5576,10 @@
         </is>
       </c>
       <c r="H7" s="593" t="n"/>
-      <c r="I7" s="645">
-        <f>HYPERLINK("https://www.digitalapplied.com/blog/ai-sdr-statistics-2026-outbound-sales-data-points#:~:text=down%2018%25%20YoY","Verbatim: down 18% YoY → click")</f>
-        <v/>
+      <c r="I7" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: down 18% YoY</t>
+        </is>
       </c>
       <c r="J7" s="651" t="n"/>
       <c r="K7" s="651" t="n"/>
@@ -5600,7 +5604,7 @@
         </is>
       </c>
       <c r="E8" s="645">
-        <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep#:~:text=70%2F30%20base%2Fvariable%20split","Pool mix sourced (~30% variable); C8=20% cut = MODEL CONST (20% cut not in source).")</f>
+        <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep","Pool mix sourced (~30% variable); C8=20% cut = MODEL CONST (20% cut not in source).")</f>
         <v/>
       </c>
       <c r="F8" s="643" t="inlineStr">
@@ -5614,20 +5618,22 @@
         </is>
       </c>
       <c r="H8" s="645">
-        <f>HYPERLINK("https://syncgtm.com/blog/how-much-do-sales-development-representatives-make-at-tech-companies#:~:text=30%E2%80%9335%25%20of%20total%20pay","Also: commission 30–35% of pay")</f>
+        <f>HYPERLINK("https://syncgtm.com/blog/how-much-do-sales-development-representatives-make-at-tech-companies","Also: commission 30–35% of pay")</f>
         <v/>
       </c>
-      <c r="I8" s="645">
-        <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep#:~:text=70%2F30%20base%2Fvariable%20split","Verbatim: 70/30 base/variable split → click")</f>
-        <v/>
-      </c>
-      <c r="J8" s="645">
-        <f>HYPERLINK("https://syncgtm.com/blog/how-much-do-sales-development-representatives-make-at-tech-companies#:~:text=30%E2%80%9335%25%20of%20total%20pay","Verbatim: 30–35% of total pay → click")</f>
-        <v/>
+      <c r="I8" s="643" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 70/30 base/variable split</t>
+        </is>
+      </c>
+      <c r="J8" s="643" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 30–35% of total pay</t>
+        </is>
       </c>
       <c r="K8" s="643" t="inlineStr">
         <is>
-          <t>20% cut: N/A — MODEL CONST (no link)</t>
+          <t>20% cut: N/A — MODEL CONST</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5657,7 @@
         </is>
       </c>
       <c r="E9" s="645">
-        <f>HYPERLINK("https://www.whitespacesolutions.ai/content/ai-sdr-pricing-guide-2026#:~:text=%245%2C000-10%2C000%2B","IN EQ: $5,000 and $10,000/mo AI SDR (White Space + Miniloop) + 1,513 S&amp;M HC (SEC)")</f>
+        <f>HYPERLINK("https://www.whitespacesolutions.ai/content/ai-sdr-pricing-guide-2026","IN EQ: $5,000 and $10,000/mo AI SDR (White Space + Miniloop) + 1,513 S&amp;M HC (SEC)")</f>
         <v/>
       </c>
       <c r="F9" s="649" t="inlineStr">
@@ -5665,20 +5671,23 @@
         </is>
       </c>
       <c r="H9" s="645">
-        <f>HYPERLINK("https://www.miniloop.ai/blog/11x-pricing#:~:text=%2410%2C000-%2415%2C000%2B","Miniloop Entry $5,000 / Enterprise $10,000+")</f>
+        <f>HYPERLINK("https://www.miniloop.ai/blog/11x-pricing","Miniloop Entry $5,000 / Enterprise $10,000+")</f>
         <v/>
       </c>
-      <c r="I9" s="645">
-        <f>HYPERLINK("https://www.whitespacesolutions.ai/content/ai-sdr-pricing-guide-2026#:~:text=%245%2C000-10%2C000%2B","Verbatim: 11x.ai (Alice) $5,000-10,000+ → click")</f>
-        <v/>
-      </c>
-      <c r="J9" s="645">
-        <f>HYPERLINK("https://www.miniloop.ai/blog/11x-pricing#:~:text=%2410%2C000-%2415%2C000%2B","Verbatim: Enterprise $10,000-$15,000+ → click")</f>
-        <v/>
-      </c>
-      <c r="K9" s="645">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm#:~:text=1%2C513%20in%20sales%20and%20marketing","Verbatim: 1,513 in sales and marketing → click")</f>
-        <v/>
+      <c r="I9" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: $5,000-10,000+</t>
+        </is>
+      </c>
+      <c r="J9" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: $10,000-$15,000+</t>
+        </is>
+      </c>
+      <c r="K9" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 1,513 in sales and marketing</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="96" customHeight="1" s="244">
@@ -5701,7 +5710,7 @@
         </is>
       </c>
       <c r="E10" s="645">
-        <f>HYPERLINK("https://www.federalreserve.gov/faqs/economy_14400.htm#:~:text=inflation%20of%202%20percent%20over%20the%20longer%20run","IN EQ: C10=2% = Fed longer-run inflation goal of 2 percent (FOMC FAQ)")</f>
+        <f>HYPERLINK("https://www.federalreserve.gov/faqs/economy_14400.htm","IN EQ: C10=2% = Fed longer-run inflation goal of 2 percent (FOMC FAQ)")</f>
         <v/>
       </c>
       <c r="F10" s="646" t="inlineStr">
@@ -5719,9 +5728,10 @@
           <t>FOMC Statement on Longer-Run Goals (PDF)</t>
         </is>
       </c>
-      <c r="I10" s="645">
-        <f>HYPERLINK("https://www.federalreserve.gov/faqs/economy_14400.htm#:~:text=inflation%20of%202%20percent%20over%20the%20longer%20run","Verbatim: inflation of 2 percent over the longer run → click")</f>
-        <v/>
+      <c r="I10" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: inflation of 2 percent over the longer run</t>
+        </is>
       </c>
       <c r="J10" s="651" t="n"/>
       <c r="K10" s="651" t="n"/>
@@ -5746,7 +5756,7 @@
         </is>
       </c>
       <c r="E11" s="645">
-        <f>HYPERLINK("https://blossomstreetventures.medium.com/what-should-saas-spend-on-cogs-s-m-r-d-and-g-a-the-data-from-57-public-cos-8e88eabe99ca#:~:text=G%26A%20was%2018%25","IN EQ: C11=18% = Blossom Street 2025 public SaaS median G&amp;A 18% of revenue")</f>
+        <f>HYPERLINK("https://blossomstreetventures.medium.com/what-should-saas-spend-on-cogs-s-m-r-d-and-g-a-the-data-from-57-public-cos-8e88eabe99ca","IN EQ: C11=18% = Blossom Street 2025 public SaaS median G&amp;A 18% of revenue")</f>
         <v/>
       </c>
       <c r="F11" s="643" t="inlineStr">
@@ -5760,16 +5770,18 @@
         </is>
       </c>
       <c r="H11" s="645">
-        <f>HYPERLINK("https://www.blossomstreetventures.com/saas-metric/2025-annual-percent-of-revenue#:~:text=MEDIAN","Table MEDIAN G&amp;A as % of Revenue = 18%")</f>
+        <f>HYPERLINK("https://www.blossomstreetventures.com/saas-metric/2025-annual-percent-of-revenue","Table MEDIAN G&amp;A as % of Revenue = 18%")</f>
         <v/>
       </c>
-      <c r="I11" s="645">
-        <f>HYPERLINK("https://blossomstreetventures.medium.com/what-should-saas-spend-on-cogs-s-m-r-d-and-g-a-the-data-from-57-public-cos-8e88eabe99ca#:~:text=G%26A%20was%2018%25","Verbatim: G&amp;A was 18% → click")</f>
-        <v/>
-      </c>
-      <c r="J11" s="645">
-        <f>HYPERLINK("https://www.blossomstreetventures.com/saas-metric/2025-annual-percent-of-revenue#:~:text=MEDIAN","Verbatim table: 'MEDIAN' (G&amp;A col 18%) → click")</f>
-        <v/>
+      <c r="I11" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: G&amp;A was 18%</t>
+        </is>
+      </c>
+      <c r="J11" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: MEDIAN</t>
+        </is>
       </c>
       <c r="K11" s="651" t="n"/>
     </row>
@@ -5810,7 +5822,7 @@
       <c r="H12" s="593" t="n"/>
       <c r="I12" s="643" t="inlineStr">
         <is>
-          <t>5% CapEx cut: N/A — MODEL CONST (no link)</t>
+          <t>5% CapEx cut: N/A — MODEL CONST</t>
         </is>
       </c>
       <c r="J12" s="651" t="n"/>
@@ -5853,7 +5865,7 @@
       <c r="H13" s="593" t="n"/>
       <c r="I13" s="643" t="inlineStr">
         <is>
-          <t>10% WC improve: N/A — MODEL CONST (no link)</t>
+          <t>10% WC improve: N/A — MODEL CONST</t>
         </is>
       </c>
       <c r="J13" s="651" t="n"/>
@@ -5879,7 +5891,7 @@
         </is>
       </c>
       <c r="E14" s="645">
-        <f>HYPERLINK("https://www.global-rates.com/en/interest-rates/sofr/historical/2024/#:~:text=4.30","IN EQ: C14=4.30% = SOFR 2024 calendar-year Lowest (Global-Rates summary of NY Fed)")</f>
+        <f>HYPERLINK("https://www.global-rates.com/en/interest-rates/sofr/historical/2024/","IN EQ: C14=4.30% = SOFR 2024 calendar-year Lowest (Global-Rates summary of NY Fed)")</f>
         <v/>
       </c>
       <c r="F14" s="643" t="inlineStr">
@@ -5897,9 +5909,10 @@
           <t>NY Fed SOFR publisher</t>
         </is>
       </c>
-      <c r="I14" s="645">
-        <f>HYPERLINK("https://www.global-rates.com/en/interest-rates/sofr/historical/2024/#:~:text=4.30","Verbatim: 4.30' (SOFR 2024 Lowest) → click")</f>
-        <v/>
+      <c r="I14" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 4.30</t>
+        </is>
       </c>
       <c r="J14" s="651" t="n"/>
       <c r="K14" s="651" t="n"/>
@@ -5924,7 +5937,7 @@
         </is>
       </c>
       <c r="E15" s="645">
-        <f>HYPERLINK("https://ctacquisitions.com/acquisition-financing/#:~:text=SOFR%20%2B%20400-500%20bps","IN EQ: C15=+400bps = floor of senior Term Loan A SOFR+400-500 bps (CT Acquisitions)")</f>
+        <f>HYPERLINK("https://ctacquisitions.com/acquisition-financing/","IN EQ: C15=+400bps = floor of senior Term Loan A SOFR+400-500 bps (CT Acquisitions)")</f>
         <v/>
       </c>
       <c r="F15" s="643" t="inlineStr">
@@ -5942,9 +5955,10 @@
           <t>Also: senior debt SOFR plus 400 to 500</t>
         </is>
       </c>
-      <c r="I15" s="645">
-        <f>HYPERLINK("https://ctacquisitions.com/acquisition-financing/#:~:text=SOFR%20%2B%20400-500%20bps","Verbatim: SOFR + 400-500 bps → click")</f>
-        <v/>
+      <c r="I15" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: SOFR + 400-500 bps</t>
+        </is>
       </c>
       <c r="J15" s="651" t="n"/>
       <c r="K15" s="651" t="n"/>
@@ -5969,7 +5983,7 @@
         </is>
       </c>
       <c r="E16" s="645">
-        <f>HYPERLINK("https://ibinterviewquestions.com/guides/valuation-investment-banking/lbo-debt-structures-senior-subordinated-mezzanine#:~:text=SOFR%20%2B%20300-500%20basis%20points","IN EQ: TLB SOFR+300-500 bps → C16=+500bps = upper bound")</f>
+        <f>HYPERLINK("https://ibinterviewquestions.com/guides/valuation-investment-banking/lbo-debt-structures-senior-subordinated-mezzanine","IN EQ: TLB SOFR+300-500 bps → C16=+500bps = upper bound")</f>
         <v/>
       </c>
       <c r="F16" s="646" t="inlineStr">
@@ -5987,9 +6001,10 @@
           <t>Table: Term Loan B | SOFR + 300-500 bps | 1% annual</t>
         </is>
       </c>
-      <c r="I16" s="645">
-        <f>HYPERLINK("https://ibinterviewquestions.com/guides/valuation-investment-banking/lbo-debt-structures-senior-subordinated-mezzanine#:~:text=SOFR%20%2B%20300-500%20basis%20points","Verbatim: SOFR + 300-500 basis points → click")</f>
-        <v/>
+      <c r="I16" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: SOFR + 300-500 basis points</t>
+        </is>
       </c>
       <c r="J16" s="651" t="n"/>
       <c r="K16" s="651" t="n"/>
@@ -6014,7 +6029,7 @@
         </is>
       </c>
       <c r="E17" s="645">
-        <f>HYPERLINK("https://clearvaluelending.com/glossary/term-loan-b#:~:text=minimal%20amortization%20%281%25%20annually%29","IN EQ: ~1%/yr TLB amort → C17=1%")</f>
+        <f>HYPERLINK("https://clearvaluelending.com/glossary/term-loan-b","IN EQ: ~1%/yr TLB amort → C17=1%")</f>
         <v/>
       </c>
       <c r="F17" s="646" t="inlineStr">
@@ -6032,9 +6047,10 @@
           <t>ClearValue: "minimal amortization (1% annually)"</t>
         </is>
       </c>
-      <c r="I17" s="645">
-        <f>HYPERLINK("https://clearvaluelending.com/glossary/term-loan-b#:~:text=minimal%20amortization%20%281%25%20annually%29","Verbatim: minimal amortization (1% annually) → click")</f>
-        <v/>
+      <c r="I17" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: minimal amortization (1% annually)</t>
+        </is>
       </c>
       <c r="J17" s="651" t="n"/>
       <c r="K17" s="651" t="n"/>
@@ -6059,7 +6075,7 @@
         </is>
       </c>
       <c r="E18" s="645">
-        <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/#:~:text=50-100%25%20of%20annual%20excess%20free%20cash%20flow","IN EQ: C18=100% = upper bound of ECF sweep 50-100%; models often use 100%")</f>
+        <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/","IN EQ: C18=100% = upper bound of ECF sweep 50-100%; models often use 100%")</f>
         <v/>
       </c>
       <c r="F18" s="643" t="inlineStr">
@@ -6073,16 +6089,18 @@
         </is>
       </c>
       <c r="H18" s="645">
-        <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/#:~:text=typically%20modeled%20at%20100%25","Verbatim: typically modeled at 100% → click")</f>
+        <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/","Also: typically modeled at 100%")</f>
         <v/>
       </c>
-      <c r="I18" s="645">
-        <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/#:~:text=50-100%25%20of%20annual%20excess%20free%20cash%20flow","Verbatim: 50-100% of annual excess free cash flow → click")</f>
-        <v/>
-      </c>
-      <c r="J18" s="645">
-        <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/#:~:text=typically%20modeled%20at%20100%25","Verbatim: typically modeled at 100% → click")</f>
-        <v/>
+      <c r="I18" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 50-100% of annual excess free cash flow</t>
+        </is>
+      </c>
+      <c r="J18" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: typically modeled at 100%</t>
+        </is>
       </c>
       <c r="K18" s="651" t="n"/>
     </row>
@@ -6106,7 +6124,7 @@
         </is>
       </c>
       <c r="E19" s="645">
-        <f>HYPERLINK("https://taxsummaries.pwc.com/united-states/corporate/taxes-on-corporate-income#:~:text=flat%20rate%20of%2021%25","IN EQ: US federal CIT=21% → C19=0.21 (PwC)")</f>
+        <f>HYPERLINK("https://taxsummaries.pwc.com/united-states/corporate/taxes-on-corporate-income","IN EQ: US federal CIT=21% → C19=0.21 (PwC)")</f>
         <v/>
       </c>
       <c r="F19" s="646" t="inlineStr">
@@ -6124,9 +6142,10 @@
           <t>Trading Economics: 21 percent</t>
         </is>
       </c>
-      <c r="I19" s="645">
-        <f>HYPERLINK("https://taxsummaries.pwc.com/united-states/corporate/taxes-on-corporate-income#:~:text=flat%20rate%20of%2021%25","Verbatim: flat rate of 21% → click")</f>
-        <v/>
+      <c r="I19" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: flat rate of 21%</t>
+        </is>
       </c>
       <c r="J19" s="651" t="n"/>
       <c r="K19" s="651" t="n"/>
@@ -6151,7 +6170,7 @@
         </is>
       </c>
       <c r="E20" s="645">
-        <f>HYPERLINK("https://aventis-advisors.com/saas-valuation-multiples-how-much-is-my-saas-business-worth/#:~:text=12.9x","IN EQ: C20=12.9x = Aventis private SaaS EV/EBITDA 1st quartile 12.9x (was 13 round)")</f>
+        <f>HYPERLINK("https://aventis-advisors.com/saas-valuation-multiples-how-much-is-my-saas-business-worth/","IN EQ: C20=12.9x = Aventis private SaaS EV/EBITDA 1st quartile 12.9x")</f>
         <v/>
       </c>
       <c r="F20" s="643" t="inlineStr">
@@ -6165,9 +6184,10 @@
         </is>
       </c>
       <c r="H20" s="593" t="n"/>
-      <c r="I20" s="645">
-        <f>HYPERLINK("https://aventis-advisors.com/saas-valuation-multiples-how-much-is-my-saas-business-worth/#:~:text=12.9x","Verbatim: 12.9x → click")</f>
-        <v/>
+      <c r="I20" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 12.9x</t>
+        </is>
       </c>
       <c r="J20" s="651" t="n"/>
       <c r="K20" s="651" t="n"/>
@@ -6192,7 +6212,7 @@
         </is>
       </c>
       <c r="E21" s="645">
-        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results#:~:text=%241%2C214.3","IN EQ: Rev $1,214.3m; S&amp;M $414.1m (34.1%) → model 35%→$425m")</f>
+        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results","IN EQ: Rev $1,214.3m; S&amp;M $414.1m (34.1%) → model 35%→$425m")</f>
         <v/>
       </c>
       <c r="F21" s="646" t="inlineStr">
@@ -6206,20 +6226,23 @@
         </is>
       </c>
       <c r="H21" s="645">
-        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results#:~:text=414.1","SEC 10-K Sales and marketing $414.1")</f>
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","SEC 10-K Sales and marketing $414.1")</f>
         <v/>
       </c>
-      <c r="I21" s="645">
-        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results#:~:text=%241%2C214.3","Verbatim: $1,214.3 → click")</f>
-        <v/>
-      </c>
-      <c r="J21" s="645">
-        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results#:~:text=414.1","Verbatim: 414.1 → click")</f>
-        <v/>
-      </c>
-      <c r="K21" s="645">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm#:~:text=%24414.1","Verbatim: $414.1' (10-K) → click")</f>
-        <v/>
+      <c r="I21" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: $1,214.3</t>
+        </is>
+      </c>
+      <c r="J21" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 414.1</t>
+        </is>
+      </c>
+      <c r="K21" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: $414.1</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="96" customHeight="1" s="244">
@@ -6242,7 +6265,7 @@
         </is>
       </c>
       <c r="E22" s="645">
-        <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep#:~:text=70%2F30%20base%2Fvariable%20split","IN EQ: ~70% base OTE → model 75%×$425m=$318.8m")</f>
+        <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep","IN EQ: ~70% base OTE → model 75%×$425m=$318.8m")</f>
         <v/>
       </c>
       <c r="F22" s="646" t="inlineStr">
@@ -6256,13 +6279,14 @@
         </is>
       </c>
       <c r="H22" s="593" t="n"/>
-      <c r="I22" s="645">
-        <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep#:~:text=70%2F30%20base%2Fvariable%20split","Verbatim: 70/30 base/variable split → click")</f>
-        <v/>
-      </c>
-      <c r="J22" s="643" t="inlineStr">
-        <is>
-          <t>$318.8 / 75%: MODEL carve (no link)</t>
+      <c r="I22" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 70/30 base/variable split</t>
+        </is>
+      </c>
+      <c r="J22" s="647" t="inlineStr">
+        <is>
+          <t>$318.8 / 75%: MODEL carve</t>
         </is>
       </c>
       <c r="K22" s="651" t="n"/>
@@ -6287,7 +6311,7 @@
         </is>
       </c>
       <c r="E23" s="645">
-        <f>HYPERLINK("https://syncgtm.com/blog/how-much-do-sales-development-representatives-make-at-tech-companies#:~:text=30%E2%80%9335%25%20of%20total%20pay","IN EQ: residual 25%×$425m=$106.2m (near sourced ~30–35% variable)")</f>
+        <f>HYPERLINK("https://syncgtm.com/blog/how-much-do-sales-development-representatives-make-at-tech-companies","IN EQ: residual 25%×$425m=$106.2m (near sourced ~30–35% variable)")</f>
         <v/>
       </c>
       <c r="F23" s="646" t="inlineStr">
@@ -6305,13 +6329,14 @@
           <t>70/30 pay article</t>
         </is>
       </c>
-      <c r="I23" s="645">
-        <f>HYPERLINK("https://syncgtm.com/blog/how-much-do-sales-development-representatives-make-at-tech-companies#:~:text=30%E2%80%9335%25%20of%20total%20pay","Verbatim: 30–35% of total pay → click")</f>
-        <v/>
-      </c>
-      <c r="J23" s="643" t="inlineStr">
-        <is>
-          <t>$106.2 / 25%: MODEL carve (no link)</t>
+      <c r="I23" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 30–35% of total pay</t>
+        </is>
+      </c>
+      <c r="J23" s="647" t="inlineStr">
+        <is>
+          <t>$106.2 / 25%: MODEL carve</t>
         </is>
       </c>
       <c r="K23" s="651" t="n"/>
@@ -6336,7 +6361,7 @@
         </is>
       </c>
       <c r="E24" s="645">
-        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/#:~:text=Most%20pure-play%20SaaS%20companies%20report%20CapEx%20of","IN EQ band: SaaS CapEx 1–3% of rev (SaaSDB) → C24=2% = midpoint of that band")</f>
+        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/","IN EQ band: SaaS CapEx 1–3% of rev (SaaSDB) → C24=2% = midpoint of that band")</f>
         <v/>
       </c>
       <c r="F24" s="646" t="inlineStr">
@@ -6350,16 +6375,21 @@
         </is>
       </c>
       <c r="H24" s="593" t="n"/>
-      <c r="I24" s="645">
-        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/#:~:text=Most%20pure-play%20SaaS%20companies%20report%20CapEx%20of","Verbatim: Most pure-play SaaS companies report CapEx of 1–3% of revenue → click")</f>
-        <v/>
-      </c>
-      <c r="J24" s="643" t="inlineStr">
-        <is>
-          <t>2%: MODEL midpoint of 1–3% band (no link)</t>
-        </is>
-      </c>
-      <c r="K24" s="651" t="n"/>
+      <c r="I24" s="647" t="inlineStr">
+        <is>
+          <t>Ctrl+F: CapEx of 1</t>
+        </is>
+      </c>
+      <c r="J24" s="647" t="inlineStr">
+        <is>
+          <t>Tip: page uses en-dash 1–3%; or Ctrl+F: Most pure-play SaaS companies report CapEx of</t>
+        </is>
+      </c>
+      <c r="K24" s="647" t="inlineStr">
+        <is>
+          <t>2%: MODEL midpoint of 1–3% band</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="96" customHeight="1" s="244">
       <c r="A25" s="655" t="inlineStr">
@@ -6398,7 +6428,7 @@
       <c r="H25" s="593" t="n"/>
       <c r="I25" s="643" t="inlineStr">
         <is>
-          <t>2% WC plug: N/A — MODEL CONST (no link)</t>
+          <t>2% WC plug: N/A — MODEL CONST</t>
         </is>
       </c>
       <c r="J25" s="651" t="n"/>
@@ -6447,9 +6477,9 @@
         </is>
       </c>
       <c r="H27" s="593" t="n"/>
-      <c r="I27" s="643" t="inlineStr">
-        <is>
-          <t>See FIND links on rows 14–15</t>
+      <c r="I27" s="647" t="inlineStr">
+        <is>
+          <t>See Ctrl+F strings on rows 14–15</t>
         </is>
       </c>
       <c r="J27" s="651" t="n"/>
@@ -6491,9 +6521,9 @@
         </is>
       </c>
       <c r="H28" s="593" t="n"/>
-      <c r="I28" s="643" t="inlineStr">
-        <is>
-          <t>See FIND links on rows 14 &amp; 16</t>
+      <c r="I28" s="647" t="inlineStr">
+        <is>
+          <t>See Ctrl+F strings on rows 14 &amp; 16</t>
         </is>
       </c>
       <c r="J28" s="651" t="n"/>
@@ -6553,12 +6583,12 @@
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>HOW TO USE VERBATIM LINKS:</t>
+          <t>HOW TO USE VERBATIM (no auto-highlight):</t>
         </is>
       </c>
       <c r="C33" s="653" t="inlineStr">
         <is>
-          <t>Go to columns I, J, K. Blue cells are Excel HYPERLINK formulas. Click the blue verbatim text → browser opens the source and jumps to/highlights that quote. Example row 9: I9 White Space $5,000-10,000+ | J9 Miniloop $10,000-$15,000+ | K9 SEC 1,513.</t>
+          <t>1) Click Source link in column E (opens the page). 2) Copy the string from column I (or J/K). 3) Ctrl+F on the page and paste. Example row 9: I9 copy $5,000-10,000+ | J9 copy $10,000-$15,000+ | K9 copy 1,513 in sales and marketing</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N45"/>
+  <dimension ref="B2:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" style="244" min="2" max="2"/>
@@ -14198,7 +14228,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="590" t="n"/>
+      <c r="B28" s="590" t="inlineStr">
+        <is>
+          <t>#'Assumptions_Drivers'!E9</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="660" t="inlineStr">
@@ -14215,7 +14249,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="590" t="n"/>
+      <c r="B31" s="590" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_AI_COST_SOURCES.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="618" t="inlineStr">
@@ -14232,33 +14270,53 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="593" t="n"/>
+      <c r="B34" s="593" t="inlineStr">
+        <is>
+          <t>#'Assumptions_Drivers'!E9</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="B35" s="593" t="n"/>
-    </row>
-    <row r="36"/>
+      <c r="B35" s="593" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_AI_COST_SOURCES.pdf</t>
+        </is>
+      </c>
+    </row>
     <row r="37">
       <c r="B37" s="564" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="593" t="n"/>
+      <c r="B38" s="593" t="inlineStr">
+        <is>
+          <t>#'Assumptions_Drivers'!E9</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="B39" s="593" t="n"/>
-    </row>
-    <row r="40"/>
+      <c r="B39" s="593" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_AI_COST_SOURCES.pdf</t>
+        </is>
+      </c>
+    </row>
     <row r="41">
       <c r="B41" s="564" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="593" t="n"/>
+      <c r="B42" s="593" t="inlineStr">
+        <is>
+          <t>#'Assumptions_Drivers'!E9</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="B43" s="593" t="n"/>
-    </row>
-    <row r="44"/>
-    <row r="45"/>
+      <c r="B43" s="593" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_AI_COST_SOURCES.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B6:M21"/>
   <hyperlinks>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -1179,7 +1179,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -1643,6 +1643,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1975,7 +1989,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="662">
+  <cellXfs count="665">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3177,6 +3191,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="35" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="35" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5368,7 +5391,7 @@
     <col width="11" customWidth="1" style="244" min="3" max="3"/>
     <col width="52" customWidth="1" style="244" min="4" max="4"/>
     <col width="42" customWidth="1" style="244" min="5" max="5"/>
-    <col width="48" customWidth="1" style="244" min="6" max="6"/>
+    <col width="44" customWidth="1" style="244" min="6" max="6"/>
     <col width="34" customWidth="1" style="244" min="7" max="7"/>
     <col width="38" customWidth="1" style="244" min="8" max="8"/>
     <col width="48" customWidth="1" style="244" min="9" max="9"/>
@@ -5416,9 +5439,9 @@
           <t>Source — ONLY if number appears in EQ (click)</t>
         </is>
       </c>
-      <c r="F4" s="606" t="inlineStr">
-        <is>
-          <t>EQUATION: SOURCED inputs vs MODEL CONST (no fake links)</t>
+      <c r="F4" s="663" t="inlineStr">
+        <is>
+          <t>Source justification (≤30 words): Source says X. Does X go into the math?</t>
         </is>
       </c>
       <c r="G4" s="606" t="inlineStr">
@@ -5470,9 +5493,9 @@
         <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results","IN EQ $ base only: FY24 Rev=$1,214.3m (ZI). C5=10% = MODEL CONST (10% not in filing).")</f>
         <v/>
       </c>
-      <c r="F5" s="643" t="inlineStr">
-        <is>
-          <t>EQ: Y1_Rev=1214.3×(1+0.10)=$1,335.73m. SOURCED $: 1,214.3. MODEL CONST: 0.10 (filing prints −2%, not +10%).</t>
+      <c r="F5" s="664" t="inlineStr">
+        <is>
+          <t>ZoomInfo says FY24 sales were $1,214.3m. That sales base is in the math. The +10% growth rate is our choice, not from a source.</t>
         </is>
       </c>
       <c r="G5" s="612" t="inlineStr">
@@ -5523,9 +5546,9 @@
         <f>HYPERLINK("https://www.getaleph.com/answers/saas-gross-margin-2026","IN EQ: software median GM=80% → C6=0.80 (Aleph × Benchmarkit)")</f>
         <v/>
       </c>
-      <c r="F6" s="646" t="inlineStr">
-        <is>
-          <t>EQ: COGS=Rev×(1−0.80). Y1: 1335.73×0.20=$267.15m. SOURCED: 80% = 2025 median software gross margin.</t>
+      <c r="F6" s="664" t="inlineStr">
+        <is>
+          <t>Aleph says the 2025 software median gross margin is 80%. We use that 80% in the COGS math.</t>
         </is>
       </c>
       <c r="G6" s="612" t="inlineStr">
@@ -5565,9 +5588,9 @@
         <f>HYPERLINK("https://www.digitalapplied.com/blog/ai-sdr-statistics-2026-outbound-sales-data-points","IN EQ: C7=18% = US B2B SaaS net SDR headcount down 18% YoY (Digital Applied / Bridge Group)")</f>
         <v/>
       </c>
-      <c r="F7" s="646" t="inlineStr">
-        <is>
-          <t>EQ: Payroll_Y1=318.8×(1−0.18)=$261.416m. SOURCED: 18% YoY SDR HC decline. SOURCED $: 318.8 from row22. (Was 15% midpoint — replaced so yellow equals findable text.)</t>
+      <c r="F7" s="664" t="inlineStr">
+        <is>
+          <t>Digital Applied says U.S. B2B SaaS SDR headcount fell 18% YoY. We use that 18% as the Year 1 payroll cut.</t>
         </is>
       </c>
       <c r="G7" s="612" t="inlineStr">
@@ -5607,9 +5630,9 @@
         <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep","Pool mix sourced (~30% variable); C8=20% cut = MODEL CONST (20% cut not in source).")</f>
         <v/>
       </c>
-      <c r="F8" s="643" t="inlineStr">
-        <is>
-          <t>EQ: Commission_AI=106.2×(1−0.20)=$84.96m. SOURCED mix: 70/30 base/variable. MODEL CONST: 0.20 cut.</t>
+      <c r="F8" s="664" t="inlineStr">
+        <is>
+          <t>SyncGTM says SDR pay is about 70/30 base/variable. That mix is context only. The 20% cut is our choice and goes into the math.</t>
         </is>
       </c>
       <c r="G8" s="612" t="inlineStr">
@@ -5660,9 +5683,9 @@
         <f>HYPERLINK("https://www.whitespacesolutions.ai/content/ai-sdr-pricing-guide-2026","IN EQ: $5,000 and $10,000/mo AI SDR (White Space + Miniloop) + 1,513 S&amp;M HC (SEC)")</f>
         <v/>
       </c>
-      <c r="F9" s="649" t="inlineStr">
-        <is>
-          <t>EQ: Roles=0.25×1,513=378; Low=378×$5,000×12=$22.68m; High=378×$10,000×12=$45.36m; C9=avg=$34.0m. MODEL CONST: 0.25 outbound share. NOT in EQ: 11x Growth $3,750.</t>
+      <c r="F9" s="664" t="inlineStr">
+        <is>
+          <t>White Space/Miniloop say ~$5k–$10k+/mo. ZoomInfo’s 10-K says 1,513 S&amp;M staff. Those go into the $34m math. The 25% role share is our choice.</t>
         </is>
       </c>
       <c r="G9" s="612" t="inlineStr">
@@ -5713,9 +5736,9 @@
         <f>HYPERLINK("https://www.federalreserve.gov/faqs/economy_14400.htm","IN EQ: C10=2% = Fed longer-run inflation goal of 2 percent (FOMC FAQ)")</f>
         <v/>
       </c>
-      <c r="F10" s="646" t="inlineStr">
-        <is>
-          <t>EQ: Payroll_t=Payroll_{t−1}×(1.02). SOURCED: 2 percent longer-run inflation target.</t>
+      <c r="F10" s="664" t="inlineStr">
+        <is>
+          <t>The Fed says longer-run inflation is 2%. We use that 2% to grow S&amp;M costs after Year 1.</t>
         </is>
       </c>
       <c r="G10" s="612" t="inlineStr">
@@ -5759,9 +5782,9 @@
         <f>HYPERLINK("https://blossomstreetventures.medium.com/what-should-saas-spend-on-cogs-s-m-r-d-and-g-a-the-data-from-57-public-cos-8e88eabe99ca","IN EQ: C11=18% = Blossom Street 2025 public SaaS median G&amp;A 18% of revenue")</f>
         <v/>
       </c>
-      <c r="F11" s="643" t="inlineStr">
-        <is>
-          <t>EQ: G&amp;A=Rev×0.18. SOURCED: G&amp;A was 18% in 2025 (medians). NOT in EQ: ZI filing ~24.3%.</t>
+      <c r="F11" s="664" t="inlineStr">
+        <is>
+          <t>Blossom Street says 2025 public SaaS median G&amp;A is 18% of sales. We use that 18% in the G&amp;A math.</t>
         </is>
       </c>
       <c r="G11" s="612" t="inlineStr">
@@ -5809,9 +5832,9 @@
           <t>C12=5% CapEx cut = MODEL CONST (no source prints 5%).</t>
         </is>
       </c>
-      <c r="F12" s="643" t="inlineStr">
-        <is>
-          <t>EQ: CapEx_AI=Rev×0.02×(1−0.05)=Rev×0.019. MODEL CONST: 0.05.</t>
+      <c r="F12" s="664" t="inlineStr">
+        <is>
+          <t>No source says a 5% CapEx cut. The 5% is our choice and still goes into the CapEx math.</t>
         </is>
       </c>
       <c r="G12" s="612" t="inlineStr">
@@ -5852,9 +5875,9 @@
           <t>C13=10% WC improvement = MODEL CONST (no source equals 10%).</t>
         </is>
       </c>
-      <c r="F13" s="643" t="inlineStr">
-        <is>
-          <t>EQ: ΔNWC_AI=ΔRev×0.02×0.90. MODEL CONST: 0.10. Removed prior ~80 DSO link (did not equal 10%).</t>
+      <c r="F13" s="664" t="inlineStr">
+        <is>
+          <t>No source says a 10% working-capital gain. The 10% is our choice and still goes into the WC math.</t>
         </is>
       </c>
       <c r="G13" s="612" t="inlineStr">
@@ -5894,9 +5917,9 @@
         <f>HYPERLINK("https://www.global-rates.com/en/interest-rates/sofr/historical/2024/","IN EQ: C14=4.30% = SOFR 2024 calendar-year Lowest (Global-Rates summary of NY Fed)")</f>
         <v/>
       </c>
-      <c r="F14" s="643" t="inlineStr">
-        <is>
-          <t>EQ: rates use C14. SOURCED: Lowest SOFR in 2024 = 4.30%. NOT used: latest FRED ~3.62%.</t>
+      <c r="F14" s="664" t="inlineStr">
+        <is>
+          <t>Global-Rates shows the lowest 2024 SOFR print was 4.30%. We use that 4.30% in the interest math.</t>
         </is>
       </c>
       <c r="G14" s="612" t="inlineStr">
@@ -5940,9 +5963,9 @@
         <f>HYPERLINK("https://ctacquisitions.com/acquisition-financing/","IN EQ: C15=+400bps = floor of senior Term Loan A SOFR+400-500 bps (CT Acquisitions)")</f>
         <v/>
       </c>
-      <c r="F15" s="643" t="inlineStr">
-        <is>
-          <t>EQ: TLA_rate=4.30%+4.00%=8.30%. SOURCED: SOFR + 400-500 bps on Senior term loan A.</t>
+      <c r="F15" s="664" t="inlineStr">
+        <is>
+          <t>CT Acquisitions lists senior Term Loan A at SOFR + 400–500 bps. We use +400 bps from that range in the rate math.</t>
         </is>
       </c>
       <c r="G15" s="612" t="inlineStr">
@@ -5986,9 +6009,9 @@
         <f>HYPERLINK("https://ibinterviewquestions.com/guides/valuation-investment-banking/lbo-debt-structures-senior-subordinated-mezzanine","IN EQ: TLB SOFR+300-500 bps → C16=+500bps = upper bound")</f>
         <v/>
       </c>
-      <c r="F16" s="646" t="inlineStr">
-        <is>
-          <t>EQ: TLB_rate=4.30%+5.00%=9.30%. SOURCED: SOFR + 300-500 basis points for TLB.</t>
+      <c r="F16" s="664" t="inlineStr">
+        <is>
+          <t>LBO debt guides list Term Loan B at SOFR + 300–500 bps. We use +500 bps from that range in the rate math.</t>
         </is>
       </c>
       <c r="G16" s="612" t="inlineStr">
@@ -6032,9 +6055,9 @@
         <f>HYPERLINK("https://clearvaluelending.com/glossary/term-loan-b","IN EQ: ~1%/yr TLB amort → C17=1%")</f>
         <v/>
       </c>
-      <c r="F17" s="646" t="inlineStr">
-        <is>
-          <t>EQ: Mandatory≈915.5×0.01=$9.155m/yr. SOURCED: 1% annual amortization.</t>
+      <c r="F17" s="664" t="inlineStr">
+        <is>
+          <t>ClearValue says Term Loan B amortizes about 1% per year. We use that 1% in the debt paydown math.</t>
         </is>
       </c>
       <c r="G17" s="612" t="inlineStr">
@@ -6078,9 +6101,9 @@
         <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/","IN EQ: C18=100% = upper bound of ECF sweep 50-100%; models often use 100%")</f>
         <v/>
       </c>
-      <c r="F18" s="643" t="inlineStr">
-        <is>
-          <t>EQ: Sweep=1.00×max(0,FCF−Mandatory). SOURCED: typically 50-100%; typically modeled at 100%.</t>
+      <c r="F18" s="664" t="inlineStr">
+        <is>
+          <t>Ryan O’Connell says excess-cash sweeps are often 50–100% and models often use 100%. We use that 100% in the sweep math.</t>
         </is>
       </c>
       <c r="G18" s="612" t="inlineStr">
@@ -6127,9 +6150,9 @@
         <f>HYPERLINK("https://taxsummaries.pwc.com/united-states/corporate/taxes-on-corporate-income","IN EQ: US federal CIT=21% → C19=0.21 (PwC)")</f>
         <v/>
       </c>
-      <c r="F19" s="646" t="inlineStr">
-        <is>
-          <t>EQ: Tax=EBT×0.21. SOURCED: flat rate of 21%.</t>
+      <c r="F19" s="664" t="inlineStr">
+        <is>
+          <t>PwC says the U.S. federal corporate tax rate is a flat 21%. We use that 21% in the tax math.</t>
         </is>
       </c>
       <c r="G19" s="612" t="inlineStr">
@@ -6173,9 +6196,9 @@
         <f>HYPERLINK("https://aventis-advisors.com/saas-valuation-multiples-how-much-is-my-saas-business-worth/","IN EQ: C20=12.9x = Aventis private SaaS EV/EBITDA 1st quartile 12.9x")</f>
         <v/>
       </c>
-      <c r="F20" s="643" t="inlineStr">
-        <is>
-          <t>EQ: Exit_EV=Y5_EBITDA×12.9. SOURCED: table 1st quartile EV/EBITDA = 12.9x. Text also ~12.8x.</t>
+      <c r="F20" s="664" t="inlineStr">
+        <is>
+          <t>Aventis shows private SaaS EV/EBITDA first quartile at 12.9x. We use that 12.9x as the exit multiple.</t>
         </is>
       </c>
       <c r="G20" s="612" t="inlineStr">
@@ -6215,9 +6238,9 @@
         <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results","IN EQ: Rev $1,214.3m; S&amp;M $414.1m (34.1%) → model 35%→$425m")</f>
         <v/>
       </c>
-      <c r="F21" s="646" t="inlineStr">
-        <is>
-          <t>EQ: 0.35×1214.3=$425.0m=C21. SOURCED: 1,214.3 and 414.1. MODEL ROUND: 35% near 34.1%.</t>
+      <c r="F21" s="664" t="inlineStr">
+        <is>
+          <t>ZoomInfo says FY24 S&amp;M was $414.1m. That exact figure is not the driver. We use $425m (~35% of sales) in the math.</t>
         </is>
       </c>
       <c r="G21" s="612" t="inlineStr">
@@ -6268,9 +6291,9 @@
         <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep","IN EQ: ~70% base OTE → model 75%×$425m=$318.8m")</f>
         <v/>
       </c>
-      <c r="F22" s="646" t="inlineStr">
-        <is>
-          <t>EQ: C22=0.75×425=$318.8m. SOURCED mix: 70/30. MODEL: 75% of S&amp;M pool.</t>
+      <c r="F22" s="664" t="inlineStr">
+        <is>
+          <t>SyncGTM says pay is about 70% base. That 70% is not the driver. We use $318.8m (75% of S&amp;M) as a model carve in the math.</t>
         </is>
       </c>
       <c r="G22" s="612" t="inlineStr">
@@ -6314,9 +6337,9 @@
         <f>HYPERLINK("https://syncgtm.com/blog/how-much-do-sales-development-representatives-make-at-tech-companies","IN EQ: residual 25%×$425m=$106.2m (near sourced ~30–35% variable)")</f>
         <v/>
       </c>
-      <c r="F23" s="646" t="inlineStr">
-        <is>
-          <t>EQ: C23=0.25×425=$106.2m. SOURCED: 30–35% variable. MODEL: 25% of S&amp;M as commission carve.</t>
+      <c r="F23" s="664" t="inlineStr">
+        <is>
+          <t>SyncGTM says commission is about 30–35% of pay. That band is not the driver. We use $106.2m (25% of S&amp;M) as a model carve.</t>
         </is>
       </c>
       <c r="G23" s="612" t="inlineStr">
@@ -6364,9 +6387,9 @@
         <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/","IN EQ band: SaaS CapEx 1–3% of rev (SaaSDB) → C24=2% = midpoint of that band")</f>
         <v/>
       </c>
-      <c r="F24" s="646" t="inlineStr">
-        <is>
-          <t>EQ: CapEx=Rev×0.02. SOURCED band: CapEx of 1–3% of revenue. MODEL midpoint: 2%. NOTE: page uses en-dash 1–3% (Ctrl+F '1-3%' with hyphen may miss).</t>
+      <c r="F24" s="664" t="inlineStr">
+        <is>
+          <t>SaaSDB says pure-play SaaS CapEx is often 1–3% of sales. We use 2%, the midpoint of that band, in the CapEx math.</t>
         </is>
       </c>
       <c r="G24" s="612" t="inlineStr">
@@ -6415,9 +6438,9 @@
           <t>C25=2% ΔNWC/ΔRev = MODEL CONST (no source equals 2%).</t>
         </is>
       </c>
-      <c r="F25" s="643" t="inlineStr">
-        <is>
-          <t>EQ: ΔNWC=ΔRev×0.02. MODEL CONST: 0.02.</t>
+      <c r="F25" s="664" t="inlineStr">
+        <is>
+          <t>No source says a 2% WC plug. The 2% is our choice and still goes into the working-capital math.</t>
         </is>
       </c>
       <c r="G25" s="612" t="inlineStr">
@@ -6466,9 +6489,9 @@
           <t>EQ only: C27=C14+C15 (see rows 14–15 Verbatim)</t>
         </is>
       </c>
-      <c r="F27" s="646" t="inlineStr">
-        <is>
-          <t>EQ: 4.30%+4.00%=8.30%. Component Ctrl+F strings on rows 14 and 15.</t>
+      <c r="F27" s="664" t="inlineStr">
+        <is>
+          <t>No new source. This cell only adds SOFR (row 14) and the TLA spread (row 15). Both already go into the rate math.</t>
         </is>
       </c>
       <c r="G27" s="612" t="inlineStr">
@@ -6510,9 +6533,9 @@
           <t>EQ only: C28=C14+C16 (see rows 14 &amp; 16 Verbatim)</t>
         </is>
       </c>
-      <c r="F28" s="646" t="inlineStr">
-        <is>
-          <t>EQ: 4.30%+5.00%=9.30%. Component Ctrl+F strings on rows 14 and 16.</t>
+      <c r="F28" s="664" t="inlineStr">
+        <is>
+          <t>No new source. This cell only adds SOFR (row 14) and the TLB spread (row 16). Both already go into the rate math.</t>
         </is>
       </c>
       <c r="G28" s="612" t="inlineStr">

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -1989,7 +1989,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="665">
+  <cellXfs count="676">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3200,6 +3200,39 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="46" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="116" fillId="36" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="40" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="36" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="37" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="43" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="36" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="45" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="116" fillId="36" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="116" fillId="36" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5402,14 +5435,14 @@
     <row r="2">
       <c r="B2" s="629" t="inlineStr">
         <is>
-          <t>Assumptions Drivers — Col A Baseline Yes/No. Col E/H = source page link (opens page only). Cols I/J/K = plain Verbatim strings — copy into Ctrl+F on that source (no hyperlink).</t>
+          <t>Assumptions Drivers — Col A Baseline Yes/No. Col E/H = source page link. Cols I/J/K = plain Verbatim Ctrl+F strings. Converse pass: driver must match sourced figure or a justified gap; else driver was reset to the source.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>How to verify: click Source (E) → open page → copy Verbatim from I/J/K → Ctrl+F → paste.</t>
+          <t>How to verify: click Source (E) → open page → copy Verbatim from I/J/K → Ctrl+F → paste. Converse fixes: rev −2% (was +10%); S&amp;M growth 0% (was Fed +2%); S&amp;M $414.1; 70/30 mix; cuts 18%/18%; AI $24.5m via 18%×1,513; CapEx/WC cuts → 0.</t>
         </is>
       </c>
     </row>
@@ -5471,78 +5504,78 @@
       </c>
     </row>
     <row r="5" ht="96" customHeight="1" s="244">
-      <c r="A5" s="655" t="inlineStr">
+      <c r="A5" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B5" s="607" t="inlineStr">
+      <c r="B5" s="664" t="inlineStr">
         <is>
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="C5" s="608" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D5" s="609" t="inlineStr">
-        <is>
-          <t>Assumes steady top-line expansion. Reasonable for a mature enterprise software company, avoiding aggressive hypergrowth assumptions while maintaining a healthy, realistic sales trajectory.</t>
-        </is>
-      </c>
-      <c r="E5" s="645">
-        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results","IN EQ $ base only: FY24 Rev=$1,214.3m (ZI). C5=10% = MODEL CONST (10% not in filing).")</f>
+      <c r="C5" s="666" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="D5" s="667" t="inlineStr">
+        <is>
+          <t>Was +10% with no page printing +10%. ZoomInfo FY24 results print a 2% revenue decline, so the driver is now −2% to match that source.</t>
+        </is>
+      </c>
+      <c r="E5" s="668">
+        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results","IN EQ: C5=−2% = ZI FY24 GAAP revenue decrease of 2% YoY")</f>
         <v/>
       </c>
       <c r="F5" s="664" t="inlineStr">
         <is>
-          <t>ZoomInfo says FY24 sales were $1,214.3m. That sales base is in the math. The +10% growth rate is our choice, not from a source.</t>
-        </is>
-      </c>
-      <c r="G5" s="612" t="inlineStr">
+          <t>ZoomInfo says FY24 GAAP revenue fell 2% YoY. We use that −2% as the revenue growth driver.</t>
+        </is>
+      </c>
+      <c r="G5" s="664" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D5 (Revenue)</t>
         </is>
       </c>
-      <c r="H5" s="645">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","SEC 10-K same $1,214.3m")</f>
+      <c r="H5" s="668">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","SEC 10-K same FY24 revenue")</f>
         <v/>
       </c>
-      <c r="I5" s="643" t="inlineStr">
+      <c r="I5" s="669" t="inlineStr">
+        <is>
+          <t>Ctrl+F: a decrease of 2% year-over-year</t>
+        </is>
+      </c>
+      <c r="J5" s="669" t="inlineStr">
         <is>
           <t>Ctrl+F: GAAP Revenue of $1,214.3 million</t>
         </is>
       </c>
-      <c r="J5" s="643" t="inlineStr">
+      <c r="K5" s="669" t="inlineStr">
         <is>
           <t>Ctrl+F: We generated revenue of $1,214.3 million</t>
         </is>
       </c>
-      <c r="K5" s="643" t="inlineStr">
-        <is>
-          <t>10% growth: N/A — MODEL CONST</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="96" customHeight="1" s="244">
-      <c r="A6" s="655" t="inlineStr">
+      <c r="A6" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B6" s="613" t="inlineStr">
+      <c r="B6" s="670" t="inlineStr">
         <is>
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="C6" s="644" t="n">
+      <c r="C6" s="666" t="n">
         <v>0.8</v>
       </c>
-      <c r="D6" s="609" t="inlineStr">
-        <is>
-          <t>High profitability on direct services. Highly reasonable for a SaaS company, which historically scales digital infrastructure with minimal incremental cost per user.</t>
-        </is>
-      </c>
-      <c r="E6" s="645">
+      <c r="D6" s="667" t="inlineStr">
+        <is>
+          <t>Uses the 2025 software median gross margin of 80%. ZoomInfo’s own GAAP GM is higher (~84%), but this model uses the cited Aleph median.</t>
+        </is>
+      </c>
+      <c r="E6" s="668">
         <f>HYPERLINK("https://www.getaleph.com/answers/saas-gross-margin-2026","IN EQ: software median GM=80% → C6=0.80 (Aleph × Benchmarkit)")</f>
         <v/>
       </c>
@@ -5551,41 +5584,45 @@
           <t>Aleph says the 2025 software median gross margin is 80%. We use that 80% in the COGS math.</t>
         </is>
       </c>
-      <c r="G6" s="612" t="inlineStr">
+      <c r="G6" s="664" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D6 (COGS)</t>
         </is>
       </c>
       <c r="H6" s="593" t="n"/>
-      <c r="I6" s="647" t="inlineStr">
+      <c r="I6" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: The 2025 median software gross margin is 80%</t>
         </is>
       </c>
       <c r="J6" s="651" t="n"/>
-      <c r="K6" s="651" t="n"/>
+      <c r="K6" s="672" t="inlineStr">
+        <is>
+          <t>ZI GAAP GM ~84% not used — Aleph median is the driver</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="96" customHeight="1" s="244">
-      <c r="A7" s="655" t="inlineStr">
+      <c r="A7" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B7" s="607" t="inlineStr">
+      <c r="B7" s="664" t="inlineStr">
         <is>
           <t>Sales payroll cut (Y1)</t>
         </is>
       </c>
-      <c r="C7" s="644" t="n">
+      <c r="C7" s="666" t="n">
         <v>0.18</v>
       </c>
-      <c r="D7" s="609" t="inlineStr">
-        <is>
-          <t>Immediate headcount reduction for human SDRs. Set to 18% to match published US B2B SaaS net SDR headcount decline of 18% YoY (Ctrl+F: down 18%).</t>
-        </is>
-      </c>
-      <c r="E7" s="645">
-        <f>HYPERLINK("https://www.digitalapplied.com/blog/ai-sdr-statistics-2026-outbound-sales-data-points","IN EQ: C7=18% = US B2B SaaS net SDR headcount down 18% YoY (Digital Applied / Bridge Group)")</f>
+      <c r="D7" s="667" t="inlineStr">
+        <is>
+          <t>Matches published US B2B SaaS net SDR headcount decline of 18% YoY.</t>
+        </is>
+      </c>
+      <c r="E7" s="668">
+        <f>HYPERLINK("https://www.digitalapplied.com/blog/ai-sdr-statistics-2026-outbound-sales-data-points","IN EQ: C7=18% = US B2B SaaS net SDR headcount down 18% YoY")</f>
         <v/>
       </c>
       <c r="F7" s="664" t="inlineStr">
@@ -5593,13 +5630,13 @@
           <t>Digital Applied says U.S. B2B SaaS SDR headcount fell 18% YoY. We use that 18% as the Year 1 payroll cut.</t>
         </is>
       </c>
-      <c r="G7" s="612" t="inlineStr">
+      <c r="G7" s="664" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D7 (Sales payroll)</t>
         </is>
       </c>
       <c r="H7" s="593" t="n"/>
-      <c r="I7" s="647" t="inlineStr">
+      <c r="I7" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: down 18% YoY</t>
         </is>
@@ -5608,313 +5645,322 @@
       <c r="K7" s="651" t="n"/>
     </row>
     <row r="8" ht="96" customHeight="1" s="244">
-      <c r="A8" s="655" t="inlineStr">
+      <c r="A8" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B8" s="613" t="inlineStr">
+      <c r="B8" s="670" t="inlineStr">
         <is>
           <t>Variable commission cut</t>
         </is>
       </c>
-      <c r="C8" s="608" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D8" s="609" t="inlineStr">
-        <is>
-          <t>Reduces payouts for automated sales. Reasonable because AI agents do not collect commission checks, retaining more profit per enterprise deal directly for the company.</t>
-        </is>
-      </c>
-      <c r="E8" s="645">
-        <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep","Pool mix sourced (~30% variable); C8=20% cut = MODEL CONST (20% cut not in source).")</f>
+      <c r="C8" s="666" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D8" s="667" t="inlineStr">
+        <is>
+          <t>Was an unsourced 20% cut. Now 18% to match the same SDR headcount decline used for payroll.</t>
+        </is>
+      </c>
+      <c r="E8" s="668">
+        <f>HYPERLINK("https://www.digitalapplied.com/blog/ai-sdr-statistics-2026-outbound-sales-data-points","IN EQ: C8=18% cut = same SDR HC down 18% YoY (Digital Applied)")</f>
         <v/>
       </c>
       <c r="F8" s="664" t="inlineStr">
         <is>
-          <t>SyncGTM says SDR pay is about 70/30 base/variable. That mix is context only. The 20% cut is our choice and goes into the math.</t>
-        </is>
-      </c>
-      <c r="G8" s="612" t="inlineStr">
+          <t>Digital Applied says SDR headcount fell 18% YoY. We use that same 18% as the commission cut.</t>
+        </is>
+      </c>
+      <c r="G8" s="664" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D8 (Commissions)</t>
         </is>
       </c>
-      <c r="H8" s="645">
-        <f>HYPERLINK("https://syncgtm.com/blog/how-much-do-sales-development-representatives-make-at-tech-companies","Also: commission 30–35% of pay")</f>
+      <c r="H8" s="668">
+        <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep","Pay mix context only: 70/30 base/variable")</f>
         <v/>
       </c>
-      <c r="I8" s="643" t="inlineStr">
+      <c r="I8" s="669" t="inlineStr">
+        <is>
+          <t>Ctrl+F: down 18% YoY</t>
+        </is>
+      </c>
+      <c r="J8" s="669" t="inlineStr">
         <is>
           <t>Ctrl+F: 70/30 base/variable split</t>
         </is>
       </c>
-      <c r="J8" s="643" t="inlineStr">
-        <is>
-          <t>Ctrl+F: 30–35% of total pay</t>
-        </is>
-      </c>
-      <c r="K8" s="643" t="inlineStr">
-        <is>
-          <t>20% cut: N/A — MODEL CONST</t>
+      <c r="K8" s="669" t="inlineStr">
+        <is>
+          <t>Prior 20% cut removed — no source equaled 20%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="96" customHeight="1" s="244">
-      <c r="A9" s="655" t="inlineStr">
+      <c r="A9" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B9" s="607" t="inlineStr">
+      <c r="B9" s="664" t="inlineStr">
         <is>
           <t>AI infrastructure ($m)</t>
         </is>
       </c>
-      <c r="C9" s="648" t="n">
-        <v>34</v>
-      </c>
-      <c r="D9" s="609" t="inlineStr">
-        <is>
-          <t>AI infra $34m = 378 roles × $5–10k/mo × 12, midpoint. $/mo from published AI SDR enterprise pricing; headcount from ZI 10-K.</t>
-        </is>
-      </c>
-      <c r="E9" s="645">
-        <f>HYPERLINK("https://www.whitespacesolutions.ai/content/ai-sdr-pricing-guide-2026","IN EQ: $5,000 and $10,000/mo AI SDR (White Space + Miniloop) + 1,513 S&amp;M HC (SEC)")</f>
+      <c r="C9" s="673" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D9" s="667" t="inlineStr">
+        <is>
+          <t>AI $24.5m = 18%×1,513 roles × $5–10k/mo × 12, midpoint. Role share now uses the same sourced 18% SDR decline (was unsourced 25%).</t>
+        </is>
+      </c>
+      <c r="E9" s="668">
+        <f>HYPERLINK("https://www.whitespacesolutions.ai/content/ai-sdr-pricing-guide-2026","IN EQ: $5k/$10k/mo + 1,513 HC; roles=18% (same 18% as C7) → $24.5m")</f>
         <v/>
       </c>
       <c r="F9" s="664" t="inlineStr">
         <is>
-          <t>White Space/Miniloop say ~$5k–$10k+/mo. ZoomInfo’s 10-K says 1,513 S&amp;M staff. Those go into the $34m math. The 25% role share is our choice.</t>
-        </is>
-      </c>
-      <c r="G9" s="612" t="inlineStr">
+          <t>White Space/Miniloop say ~$5k–$10k+/mo. ZoomInfo’s 10-K says 1,513 S&amp;M staff. Roles use the sourced 18% (not 25%). Those build the $24.5m cost.</t>
+        </is>
+      </c>
+      <c r="G9" s="664" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D10 (AI infrastructure)</t>
         </is>
       </c>
-      <c r="H9" s="645">
-        <f>HYPERLINK("https://www.miniloop.ai/blog/11x-pricing","Miniloop Entry $5,000 / Enterprise $10,000+")</f>
+      <c r="H9" s="668">
+        <f>HYPERLINK("https://www.miniloop.ai/blog/11x-pricing","Miniloop Enterprise $10,000+")</f>
         <v/>
       </c>
-      <c r="I9" s="647" t="inlineStr">
+      <c r="I9" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: $5,000-10,000+</t>
         </is>
       </c>
-      <c r="J9" s="647" t="inlineStr">
+      <c r="J9" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: $10,000-$15,000+</t>
         </is>
       </c>
-      <c r="K9" s="647" t="inlineStr">
+      <c r="K9" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: 1,513 in sales and marketing</t>
         </is>
       </c>
     </row>
     <row r="10" ht="96" customHeight="1" s="244">
-      <c r="A10" s="655" t="inlineStr">
+      <c r="A10" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B10" s="613" t="inlineStr">
+      <c r="B10" s="670" t="inlineStr">
         <is>
           <t>S&amp;M expense growth Y2+</t>
         </is>
       </c>
-      <c r="C10" s="644" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D10" s="609" t="inlineStr">
-        <is>
-          <t>Caps future marketing cost increases. Reasonable because AI scales infinitely without needing proportional headcount additions, severing the link between revenue growth and human hiring.</t>
-        </is>
-      </c>
-      <c r="E10" s="645">
-        <f>HYPERLINK("https://www.federalreserve.gov/faqs/economy_14400.htm","IN EQ: C10=2% = Fed longer-run inflation goal of 2 percent (FOMC FAQ)")</f>
+      <c r="C10" s="666" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="667" t="inlineStr">
+        <is>
+          <t>Was Fed +2% expense inflation, which contradicted sourced revenue −2%. After the Y1 cut, AI holds S&amp;M dollars flat (no headcount adds).</t>
+        </is>
+      </c>
+      <c r="E10" s="671" t="inlineStr">
+        <is>
+          <t>C10=0% S&amp;M growth Y2+ — Fed +2% removed (contradicted rev −2%). Flat after Y1 cut.</t>
+        </is>
+      </c>
+      <c r="F10" s="664" t="inlineStr">
+        <is>
+          <t>No source supports growing S&amp;M while revenue falls 2%. After the Y1 cut, we hold S&amp;M flat at 0% growth.</t>
+        </is>
+      </c>
+      <c r="G10" s="664" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!E7 (payroll Y2+)</t>
+        </is>
+      </c>
+      <c r="H10" s="664" t="inlineStr">
+        <is>
+          <t>FOMC Statement on Longer-Run Goals (PDF)</t>
+        </is>
+      </c>
+      <c r="I10" s="671" t="inlineStr">
+        <is>
+          <t>0% S&amp;M growth Y2+: prior Fed +2% removed as contradictory</t>
+        </is>
+      </c>
+      <c r="J10" s="651" t="n"/>
+      <c r="K10" s="672" t="inlineStr">
+        <is>
+          <t>See row 5: revenue −2% from ZoomInfo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="96" customHeight="1" s="244">
+      <c r="A11" s="665" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="B11" s="664" t="inlineStr">
+        <is>
+          <t>G&amp;A % of revenue</t>
+        </is>
+      </c>
+      <c r="C11" s="666" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D11" s="667" t="inlineStr">
+        <is>
+          <t>Post-LBO target at the public SaaS median (18%). ZoomInfo’s own FY24 G&amp;A is higher (~24%) and is not used.</t>
+        </is>
+      </c>
+      <c r="E11" s="668">
+        <f>HYPERLINK("https://blossomstreetventures.medium.com/what-should-saas-spend-on-cogs-s-m-r-d-and-g-a-the-data-from-57-public-cos-8e88eabe99ca","IN EQ: C11=18% = Blossom Street 2025 public SaaS median G&amp;A")</f>
         <v/>
       </c>
-      <c r="F10" s="664" t="inlineStr">
-        <is>
-          <t>The Fed says longer-run inflation is 2%. We use that 2% to grow S&amp;M costs after Year 1.</t>
-        </is>
-      </c>
-      <c r="G10" s="612" t="inlineStr">
-        <is>
-          <t>Go to AI_Operating!E7 (payroll Y2+)</t>
-        </is>
-      </c>
-      <c r="H10" s="593" t="inlineStr">
-        <is>
-          <t>FOMC Statement on Longer-Run Goals (PDF)</t>
-        </is>
-      </c>
-      <c r="I10" s="647" t="inlineStr">
-        <is>
-          <t>Ctrl+F: inflation of 2 percent over the longer run</t>
-        </is>
-      </c>
-      <c r="J10" s="651" t="n"/>
-      <c r="K10" s="651" t="n"/>
-    </row>
-    <row r="11" ht="96" customHeight="1" s="244">
-      <c r="A11" s="655" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="B11" s="607" t="inlineStr">
-        <is>
-          <t>G&amp;A % of revenue</t>
-        </is>
-      </c>
-      <c r="C11" s="644" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D11" s="609" t="inlineStr">
-        <is>
-          <t>General administrative overhead costs. Reasonable for a public-to-private SaaS company, maintaining standard corporate expenses without relying on unrealistic operational magic outside of sales.</t>
-        </is>
-      </c>
-      <c r="E11" s="645">
-        <f>HYPERLINK("https://blossomstreetventures.medium.com/what-should-saas-spend-on-cogs-s-m-r-d-and-g-a-the-data-from-57-public-cos-8e88eabe99ca","IN EQ: C11=18% = Blossom Street 2025 public SaaS median G&amp;A 18% of revenue")</f>
-        <v/>
-      </c>
       <c r="F11" s="664" t="inlineStr">
         <is>
           <t>Blossom Street says 2025 public SaaS median G&amp;A is 18% of sales. We use that 18% in the G&amp;A math.</t>
         </is>
       </c>
-      <c r="G11" s="612" t="inlineStr">
+      <c r="G11" s="664" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D12 (G&amp;A)</t>
         </is>
       </c>
-      <c r="H11" s="645">
+      <c r="H11" s="668">
         <f>HYPERLINK("https://www.blossomstreetventures.com/saas-metric/2025-annual-percent-of-revenue","Table MEDIAN G&amp;A as % of Revenue = 18%")</f>
         <v/>
       </c>
-      <c r="I11" s="647" t="inlineStr">
+      <c r="I11" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: G&amp;A was 18%</t>
         </is>
       </c>
-      <c r="J11" s="647" t="inlineStr">
+      <c r="J11" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: MEDIAN</t>
         </is>
       </c>
-      <c r="K11" s="651" t="n"/>
+      <c r="K11" s="672" t="inlineStr">
+        <is>
+          <t>ZI own ~24% G&amp;A not used — median is the driver</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="96" customHeight="1" s="244">
-      <c r="A12" s="655" t="inlineStr">
+      <c r="A12" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B12" s="613" t="inlineStr">
+      <c r="B12" s="670" t="inlineStr">
         <is>
           <t>CapEx reduction vs base</t>
         </is>
       </c>
-      <c r="C12" s="608" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D12" s="609" t="inlineStr">
-        <is>
-          <t>Lowers physical equipment spending. Reasonable because firing 18% of the sales team permanently eliminates the need to purchase and refresh their laptops and hardware.</t>
-        </is>
-      </c>
-      <c r="E12" s="643" t="inlineStr">
-        <is>
-          <t>C12=5% CapEx cut = MODEL CONST (no source prints 5%).</t>
+      <c r="C12" s="666" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="667" t="inlineStr">
+        <is>
+          <t>No source printed a 5% CapEx cut, so the cut is set to 0% (no AI CapEx discount).</t>
+        </is>
+      </c>
+      <c r="E12" s="669" t="inlineStr">
+        <is>
+          <t>C12=0% CapEx cut — no source printed a cut, so none is applied.</t>
         </is>
       </c>
       <c r="F12" s="664" t="inlineStr">
         <is>
-          <t>No source says a 5% CapEx cut. The 5% is our choice and still goes into the CapEx math.</t>
-        </is>
-      </c>
-      <c r="G12" s="612" t="inlineStr">
+          <t>No source says a CapEx cut. The cut is 0%, so CapEx uses the base rate only.</t>
+        </is>
+      </c>
+      <c r="G12" s="664" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D19 (CapEx)</t>
         </is>
       </c>
       <c r="H12" s="593" t="n"/>
-      <c r="I12" s="643" t="inlineStr">
-        <is>
-          <t>5% CapEx cut: N/A — MODEL CONST</t>
+      <c r="I12" s="669" t="inlineStr">
+        <is>
+          <t>0% CapEx cut: no source claimed a cut</t>
         </is>
       </c>
       <c r="J12" s="651" t="n"/>
       <c r="K12" s="651" t="n"/>
     </row>
     <row r="13" ht="96" customHeight="1" s="244">
-      <c r="A13" s="655" t="inlineStr">
+      <c r="A13" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B13" s="607" t="inlineStr">
+      <c r="B13" s="664" t="inlineStr">
         <is>
           <t>WC / receivables improvement</t>
         </is>
       </c>
-      <c r="C13" s="608" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D13" s="609" t="inlineStr">
-        <is>
-          <t>Speeds up cash collection from clients. Reasonable because automated AI billing systems can aggressively follow up on late invoices, freeing up cash for debt paydown.</t>
-        </is>
-      </c>
-      <c r="E13" s="643" t="inlineStr">
-        <is>
-          <t>C13=10% WC improvement = MODEL CONST (no source equals 10%).</t>
+      <c r="C13" s="666" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="667" t="inlineStr">
+        <is>
+          <t>No source printed a 10% WC improvement, so the improvement is set to 0%.</t>
+        </is>
+      </c>
+      <c r="E13" s="669" t="inlineStr">
+        <is>
+          <t>C13=0% WC improve — no source printed 10%, so none is applied.</t>
         </is>
       </c>
       <c r="F13" s="664" t="inlineStr">
         <is>
-          <t>No source says a 10% working-capital gain. The 10% is our choice and still goes into the WC math.</t>
-        </is>
-      </c>
-      <c r="G13" s="612" t="inlineStr">
+          <t>No source says a WC improvement. The improvement is 0%, so WC uses the base plug only.</t>
+        </is>
+      </c>
+      <c r="G13" s="664" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D20 (ΔNWC)</t>
         </is>
       </c>
       <c r="H13" s="593" t="n"/>
-      <c r="I13" s="643" t="inlineStr">
-        <is>
-          <t>10% WC improve: N/A — MODEL CONST</t>
+      <c r="I13" s="669" t="inlineStr">
+        <is>
+          <t>0% WC improve: no source claimed 10%</t>
         </is>
       </c>
       <c r="J13" s="651" t="n"/>
       <c r="K13" s="651" t="n"/>
     </row>
     <row r="14" ht="96" customHeight="1" s="244">
-      <c r="A14" s="655" t="inlineStr">
+      <c r="A14" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B14" s="613" t="inlineStr">
+      <c r="B14" s="670" t="inlineStr">
         <is>
           <t>SOFR</t>
         </is>
       </c>
-      <c r="C14" s="644" t="n">
+      <c r="C14" s="666" t="n">
         <v>0.043</v>
       </c>
-      <c r="D14" s="609" t="inlineStr">
-        <is>
-          <t>The foundational secured lending interest rate. Reasonable and historically accurate for the macroeconomic environment, properly reflecting actual institutional baseline borrowing costs.</t>
-        </is>
-      </c>
-      <c r="E14" s="645">
-        <f>HYPERLINK("https://www.global-rates.com/en/interest-rates/sofr/historical/2024/","IN EQ: C14=4.30% = SOFR 2024 calendar-year Lowest (Global-Rates summary of NY Fed)")</f>
+      <c r="D14" s="667" t="inlineStr">
+        <is>
+          <t>Uses the sourced 2024 calendar-year lowest SOFR print of 4.30%.</t>
+        </is>
+      </c>
+      <c r="E14" s="668">
+        <f>HYPERLINK("https://www.global-rates.com/en/interest-rates/sofr/historical/2024/","IN EQ: C14=4.30% = SOFR 2024 calendar-year Lowest")</f>
         <v/>
       </c>
       <c r="F14" s="664" t="inlineStr">
@@ -5922,45 +5968,49 @@
           <t>Global-Rates shows the lowest 2024 SOFR print was 4.30%. We use that 4.30% in the interest math.</t>
         </is>
       </c>
-      <c r="G14" s="612" t="inlineStr">
+      <c r="G14" s="664" t="inlineStr">
         <is>
           <t>Go to Debt_Sweep_AI!C12 (TLA rate uses SOFR)</t>
         </is>
       </c>
-      <c r="H14" s="593" t="inlineStr">
+      <c r="H14" s="664" t="inlineStr">
         <is>
           <t>NY Fed SOFR publisher</t>
         </is>
       </c>
-      <c r="I14" s="647" t="inlineStr">
+      <c r="I14" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: 4.30</t>
         </is>
       </c>
       <c r="J14" s="651" t="n"/>
-      <c r="K14" s="651" t="n"/>
+      <c r="K14" s="672" t="inlineStr">
+        <is>
+          <t>Uses Lowest print (sourced), not Average</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="96" customHeight="1" s="244">
-      <c r="A15" s="655" t="inlineStr">
+      <c r="A15" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B15" s="607" t="inlineStr">
+      <c r="B15" s="664" t="inlineStr">
         <is>
           <t>Term Loan A spread</t>
         </is>
       </c>
-      <c r="C15" s="644" t="n">
+      <c r="C15" s="666" t="n">
         <v>0.04</v>
       </c>
-      <c r="D15" s="609" t="inlineStr">
-        <is>
-          <t>The risk premium for senior debt. Reasonable for a standard LBO, reflecting typical syndicated commercial bank pricing for secured corporate borrowing.</t>
-        </is>
-      </c>
-      <c r="E15" s="645">
-        <f>HYPERLINK("https://ctacquisitions.com/acquisition-financing/","IN EQ: C15=+400bps = floor of senior Term Loan A SOFR+400-500 bps (CT Acquisitions)")</f>
+      <c r="D15" s="667" t="inlineStr">
+        <is>
+          <t>Floor of the sourced senior Term Loan A SOFR+400–500 bps band.</t>
+        </is>
+      </c>
+      <c r="E15" s="668">
+        <f>HYPERLINK("https://ctacquisitions.com/acquisition-financing/","IN EQ: C15=+400bps = floor of senior TLA SOFR+400-500 bps")</f>
         <v/>
       </c>
       <c r="F15" s="664" t="inlineStr">
@@ -5968,17 +6018,17 @@
           <t>CT Acquisitions lists senior Term Loan A at SOFR + 400–500 bps. We use +400 bps from that range in the rate math.</t>
         </is>
       </c>
-      <c r="G15" s="612" t="inlineStr">
+      <c r="G15" s="664" t="inlineStr">
         <is>
           <t>Go to Assumptions_Drivers!C27 (TLA rate)</t>
         </is>
       </c>
-      <c r="H15" s="593" t="inlineStr">
+      <c r="H15" s="664" t="inlineStr">
         <is>
           <t>Also: senior debt SOFR plus 400 to 500</t>
         </is>
       </c>
-      <c r="I15" s="647" t="inlineStr">
+      <c r="I15" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: SOFR + 400-500 bps</t>
         </is>
@@ -5987,25 +6037,25 @@
       <c r="K15" s="651" t="n"/>
     </row>
     <row r="16" ht="96" customHeight="1" s="244">
-      <c r="A16" s="655" t="inlineStr">
+      <c r="A16" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B16" s="613" t="inlineStr">
+      <c r="B16" s="670" t="inlineStr">
         <is>
           <t>Term Loan B spread</t>
         </is>
       </c>
-      <c r="C16" s="644" t="n">
+      <c r="C16" s="666" t="n">
         <v>0.05</v>
       </c>
-      <c r="D16" s="609" t="inlineStr">
-        <is>
-          <t>The risk premium for riskier debt. Reasonable, as Term Loan B is usually held by institutional investors requiring higher yields for slightly higher risk.</t>
-        </is>
-      </c>
-      <c r="E16" s="645">
+      <c r="D16" s="667" t="inlineStr">
+        <is>
+          <t>Upper bound of the sourced TLB SOFR+300–500 bps band (conservative).</t>
+        </is>
+      </c>
+      <c r="E16" s="668">
         <f>HYPERLINK("https://ibinterviewquestions.com/guides/valuation-investment-banking/lbo-debt-structures-senior-subordinated-mezzanine","IN EQ: TLB SOFR+300-500 bps → C16=+500bps = upper bound")</f>
         <v/>
       </c>
@@ -6014,17 +6064,17 @@
           <t>LBO debt guides list Term Loan B at SOFR + 300–500 bps. We use +500 bps from that range in the rate math.</t>
         </is>
       </c>
-      <c r="G16" s="612" t="inlineStr">
+      <c r="G16" s="664" t="inlineStr">
         <is>
           <t>Go to Assumptions_Drivers!C28 (TLB rate)</t>
         </is>
       </c>
-      <c r="H16" s="593" t="inlineStr">
+      <c r="H16" s="664" t="inlineStr">
         <is>
           <t>Table: Term Loan B | SOFR + 300-500 bps | 1% annual</t>
         </is>
       </c>
-      <c r="I16" s="647" t="inlineStr">
+      <c r="I16" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: SOFR + 300-500 basis points</t>
         </is>
@@ -6033,25 +6083,25 @@
       <c r="K16" s="651" t="n"/>
     </row>
     <row r="17" ht="96" customHeight="1" s="244">
-      <c r="A17" s="655" t="inlineStr">
+      <c r="A17" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B17" s="607" t="inlineStr">
+      <c r="B17" s="664" t="inlineStr">
         <is>
           <t>Mandatory amortization</t>
         </is>
       </c>
-      <c r="C17" s="644" t="n">
+      <c r="C17" s="666" t="n">
         <v>0.01</v>
       </c>
-      <c r="D17" s="609" t="inlineStr">
-        <is>
-          <t>Required annual principal repayment. Highly reasonable and standard market practice for leveraged loans, forcing a tiny minimum debt reduction each year.</t>
-        </is>
-      </c>
-      <c r="E17" s="645">
+      <c r="D17" s="667" t="inlineStr">
+        <is>
+          <t>Standard ~1%/year TLB amortization.</t>
+        </is>
+      </c>
+      <c r="E17" s="668">
         <f>HYPERLINK("https://clearvaluelending.com/glossary/term-loan-b","IN EQ: ~1%/yr TLB amort → C17=1%")</f>
         <v/>
       </c>
@@ -6060,17 +6110,17 @@
           <t>ClearValue says Term Loan B amortizes about 1% per year. We use that 1% in the debt paydown math.</t>
         </is>
       </c>
-      <c r="G17" s="612" t="inlineStr">
+      <c r="G17" s="664" t="inlineStr">
         <is>
           <t>Go to Debt_Sweep_AI!D5 (Mandatory 1%)</t>
         </is>
       </c>
-      <c r="H17" s="593" t="inlineStr">
+      <c r="H17" s="664" t="inlineStr">
         <is>
           <t>ClearValue: "minimal amortization (1% annually)"</t>
         </is>
       </c>
-      <c r="I17" s="647" t="inlineStr">
+      <c r="I17" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: minimal amortization (1% annually)</t>
         </is>
@@ -6079,26 +6129,26 @@
       <c r="K17" s="651" t="n"/>
     </row>
     <row r="18" ht="96" customHeight="1" s="244">
-      <c r="A18" s="655" t="inlineStr">
+      <c r="A18" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B18" s="613" t="inlineStr">
+      <c r="B18" s="670" t="inlineStr">
         <is>
           <t>Cash sweep %</t>
         </is>
       </c>
-      <c r="C18" s="644" t="n">
+      <c r="C18" s="666" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="609" t="inlineStr">
-        <is>
-          <t>Dedicates all excess cash to debt. Reasonable and standard for maximizing LBO returns, ensuring every free dollar generated immediately aggressively reduces outstanding leverage.</t>
-        </is>
-      </c>
-      <c r="E18" s="645">
-        <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/","IN EQ: C18=100% = upper bound of ECF sweep 50-100%; models often use 100%")</f>
+      <c r="D18" s="667" t="inlineStr">
+        <is>
+          <t>Uses the upper end of the sourced 50–100% excess-cash sweep range.</t>
+        </is>
+      </c>
+      <c r="E18" s="668">
+        <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/","IN EQ: C18=100% = upper bound of ECF sweep 50-100%")</f>
         <v/>
       </c>
       <c r="F18" s="664" t="inlineStr">
@@ -6106,21 +6156,21 @@
           <t>Ryan O’Connell says excess-cash sweeps are often 50–100% and models often use 100%. We use that 100% in the sweep math.</t>
         </is>
       </c>
-      <c r="G18" s="612" t="inlineStr">
+      <c r="G18" s="664" t="inlineStr">
         <is>
           <t>Go to Debt_Sweep_AI!E5 (Total paydown)</t>
         </is>
       </c>
-      <c r="H18" s="645">
+      <c r="H18" s="668">
         <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/","Also: typically modeled at 100%")</f>
         <v/>
       </c>
-      <c r="I18" s="647" t="inlineStr">
+      <c r="I18" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: 50-100% of annual excess free cash flow</t>
         </is>
       </c>
-      <c r="J18" s="647" t="inlineStr">
+      <c r="J18" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: typically modeled at 100%</t>
         </is>
@@ -6128,25 +6178,25 @@
       <c r="K18" s="651" t="n"/>
     </row>
     <row r="19" ht="96" customHeight="1" s="244">
-      <c r="A19" s="655" t="inlineStr">
+      <c r="A19" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B19" s="607" t="inlineStr">
+      <c r="B19" s="664" t="inlineStr">
         <is>
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="C19" s="644" t="n">
+      <c r="C19" s="666" t="n">
         <v>0.21</v>
       </c>
-      <c r="D19" s="609" t="inlineStr">
-        <is>
-          <t>Corporate income tax obligation. Perfectly reasonable because it strictly matches the current standard U.S. federal statutory corporate tax rate without aggressive tax-dodging assumptions.</t>
-        </is>
-      </c>
-      <c r="E19" s="645">
+      <c r="D19" s="667" t="inlineStr">
+        <is>
+          <t>Matches the U.S. federal corporate tax rate of 21%.</t>
+        </is>
+      </c>
+      <c r="E19" s="668">
         <f>HYPERLINK("https://taxsummaries.pwc.com/united-states/corporate/taxes-on-corporate-income","IN EQ: US federal CIT=21% → C19=0.21 (PwC)")</f>
         <v/>
       </c>
@@ -6155,17 +6205,17 @@
           <t>PwC says the U.S. federal corporate tax rate is a flat 21%. We use that 21% in the tax math.</t>
         </is>
       </c>
-      <c r="G19" s="612" t="inlineStr">
+      <c r="G19" s="664" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D18 (Net income)</t>
         </is>
       </c>
-      <c r="H19" s="593" t="inlineStr">
+      <c r="H19" s="664" t="inlineStr">
         <is>
           <t>Trading Economics: 21 percent</t>
         </is>
       </c>
-      <c r="I19" s="647" t="inlineStr">
+      <c r="I19" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: flat rate of 21%</t>
         </is>
@@ -6174,26 +6224,26 @@
       <c r="K19" s="651" t="n"/>
     </row>
     <row r="20" ht="96" customHeight="1" s="244">
-      <c r="A20" s="655" t="inlineStr">
+      <c r="A20" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B20" s="613" t="inlineStr">
+      <c r="B20" s="670" t="inlineStr">
         <is>
           <t>Exit EV/EBITDA multiple</t>
         </is>
       </c>
-      <c r="C20" s="648" t="n">
+      <c r="C20" s="673" t="n">
         <v>12.9</v>
       </c>
-      <c r="D20" s="609" t="inlineStr">
-        <is>
-          <t>The valuation multiple upon selling. Set to 12.9x to match Aventis private SaaS EV/EBITDA 1st quartile (Ctrl+F 12.9x)—conservative lower-quartile exit, not PE median.</t>
-        </is>
-      </c>
-      <c r="E20" s="645">
-        <f>HYPERLINK("https://aventis-advisors.com/saas-valuation-multiples-how-much-is-my-saas-business-worth/","IN EQ: C20=12.9x = Aventis private SaaS EV/EBITDA 1st quartile 12.9x")</f>
+      <c r="D20" s="667" t="inlineStr">
+        <is>
+          <t>Matches Aventis private SaaS EV/EBITDA first quartile of 12.9x.</t>
+        </is>
+      </c>
+      <c r="E20" s="668">
+        <f>HYPERLINK("https://aventis-advisors.com/saas-valuation-multiples-how-much-is-my-saas-business-worth/","IN EQ: C20=12.9x = Aventis private SaaS EV/EBITDA 1st quartile")</f>
         <v/>
       </c>
       <c r="F20" s="664" t="inlineStr">
@@ -6201,13 +6251,13 @@
           <t>Aventis shows private SaaS EV/EBITDA first quartile at 12.9x. We use that 12.9x as the exit multiple.</t>
         </is>
       </c>
-      <c r="G20" s="612" t="inlineStr">
+      <c r="G20" s="664" t="inlineStr">
         <is>
           <t>Go to LBO!D17 (Exit multiple)</t>
         </is>
       </c>
       <c r="H20" s="593" t="n"/>
-      <c r="I20" s="647" t="inlineStr">
+      <c r="I20" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: 12.9x</t>
         </is>
@@ -6216,175 +6266,182 @@
       <c r="K20" s="651" t="n"/>
     </row>
     <row r="21" ht="96" customHeight="1" s="244">
-      <c r="A21" s="656" t="inlineStr">
+      <c r="A21" s="671" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="B21" s="607" t="inlineStr">
+      <c r="B21" s="664" t="inlineStr">
         <is>
           <t>S&amp;M baseline ($m)</t>
         </is>
       </c>
-      <c r="C21" s="650" t="n">
-        <v>425</v>
-      </c>
-      <c r="D21" s="609" t="inlineStr">
-        <is>
-          <t>This is historical assumptions without AI. Total initial sales spend is reasonable, representing roughly 35% of FY24 revenue, perfectly aligning with standard SaaS benchmarks.</t>
-        </is>
-      </c>
-      <c r="E21" s="645">
-        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results","IN EQ: Rev $1,214.3m; S&amp;M $414.1m (34.1%) → model 35%→$425m")</f>
+      <c r="C21" s="674" t="n">
+        <v>414.1</v>
+      </c>
+      <c r="D21" s="667" t="inlineStr">
+        <is>
+          <t>Was a rounded $425m (~35% of sales). Now the exact ZoomInfo FY24 S&amp;M of $414.1m.</t>
+        </is>
+      </c>
+      <c r="E21" s="668">
+        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results","IN EQ: C21=$414.1m = ZI FY24 Sales and marketing")</f>
         <v/>
       </c>
       <c r="F21" s="664" t="inlineStr">
         <is>
-          <t>ZoomInfo says FY24 S&amp;M was $414.1m. That exact figure is not the driver. We use $425m (~35% of sales) in the math.</t>
-        </is>
-      </c>
-      <c r="G21" s="612" t="inlineStr">
+          <t>ZoomInfo says FY24 S&amp;M was $414.1m. We use that $414.1m as the S&amp;M baseline in the math.</t>
+        </is>
+      </c>
+      <c r="G21" s="664" t="inlineStr">
         <is>
           <t>Go to AI_Operating!C9 (S&amp;M human FY24A)</t>
         </is>
       </c>
-      <c r="H21" s="645">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","SEC 10-K Sales and marketing $414.1")</f>
+      <c r="H21" s="668">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","SEC 10-K")</f>
         <v/>
       </c>
-      <c r="I21" s="647" t="inlineStr">
-        <is>
-          <t>Ctrl+F: $1,214.3</t>
-        </is>
-      </c>
-      <c r="J21" s="647" t="inlineStr">
+      <c r="I21" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: 414.1</t>
         </is>
       </c>
-      <c r="K21" s="647" t="inlineStr">
+      <c r="J21" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: $414.1</t>
         </is>
       </c>
+      <c r="K21" s="671" t="inlineStr">
+        <is>
+          <t>Ctrl+F: Sales and marketing</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="96" customHeight="1" s="244">
-      <c r="A22" s="656" t="inlineStr">
+      <c r="A22" s="671" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="B22" s="613" t="inlineStr">
+      <c r="B22" s="670" t="inlineStr">
         <is>
           <t>Payroll baseline ($m)</t>
         </is>
       </c>
-      <c r="C22" s="614" t="n">
-        <v>318.8</v>
-      </c>
-      <c r="D22" s="609" t="inlineStr">
-        <is>
-          <t>This is historical assumptions without AI. The fixed salary portion is reasonable, representing 75% of S&amp;M, accurately reflecting that human software sales floors are base-salary heavy.</t>
-        </is>
-      </c>
-      <c r="E22" s="645">
-        <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep","IN EQ: ~70% base OTE → model 75%×$425m=$318.8m")</f>
+      <c r="C22" s="674" t="n">
+        <v>289.9</v>
+      </c>
+      <c r="D22" s="667" t="inlineStr">
+        <is>
+          <t>Was 75% of $425m. Now 70% of $414.1m = $289.9m to match SyncGTM’s ~70% base mix.</t>
+        </is>
+      </c>
+      <c r="E22" s="668">
+        <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep","IN EQ: ~70% base × $414.1m S&amp;M → C22=$289.9m")</f>
         <v/>
       </c>
       <c r="F22" s="664" t="inlineStr">
         <is>
-          <t>SyncGTM says pay is about 70% base. That 70% is not the driver. We use $318.8m (75% of S&amp;M) as a model carve in the math.</t>
-        </is>
-      </c>
-      <c r="G22" s="612" t="inlineStr">
+          <t>SyncGTM says pay is about 70% base. We use 70% of $414.1m = $289.9m as payroll in the math.</t>
+        </is>
+      </c>
+      <c r="G22" s="664" t="inlineStr">
         <is>
           <t>Go to AI_Operating!C7 (Payroll FY24A)</t>
         </is>
       </c>
       <c r="H22" s="593" t="n"/>
-      <c r="I22" s="647" t="inlineStr">
+      <c r="I22" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: 70/30 base/variable split</t>
         </is>
       </c>
-      <c r="J22" s="647" t="inlineStr">
-        <is>
-          <t>$318.8 / 75%: MODEL carve</t>
-        </is>
-      </c>
-      <c r="K22" s="651" t="n"/>
+      <c r="J22" s="671" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 414.1 (on ZI results for S&amp;M pool)</t>
+        </is>
+      </c>
+      <c r="K22" s="672" t="inlineStr">
+        <is>
+          <t>$289.9m = 70% × $414.1m</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="96" customHeight="1" s="244">
-      <c r="A23" s="656" t="inlineStr">
+      <c r="A23" s="671" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="B23" s="607" t="inlineStr">
+      <c r="B23" s="664" t="inlineStr">
         <is>
           <t>Commission baseline ($m)</t>
         </is>
       </c>
-      <c r="C23" s="614" t="n">
-        <v>106.2</v>
-      </c>
-      <c r="D23" s="609" t="inlineStr">
-        <is>
-          <t>This is historical assumptions without AI. The variable payout is reasonable, calculating exactly to the remaining 25% of the budget, representing standard quota-based enterprise sales incentives.</t>
-        </is>
-      </c>
-      <c r="E23" s="645">
-        <f>HYPERLINK("https://syncgtm.com/blog/how-much-do-sales-development-representatives-make-at-tech-companies","IN EQ: residual 25%×$425m=$106.2m (near sourced ~30–35% variable)")</f>
+      <c r="C23" s="674" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="D23" s="667" t="inlineStr">
+        <is>
+          <t>Was 25% of $425m. Now 30% of $414.1m = $124.2m to match SyncGTM’s ~30% variable mix.</t>
+        </is>
+      </c>
+      <c r="E23" s="668">
+        <f>HYPERLINK("https://syncgtm.com/blog/how-much-do-sales-development-representatives-make-at-tech-companies","IN EQ: ~30% variable × $414.1m → C23=$124.2m")</f>
         <v/>
       </c>
       <c r="F23" s="664" t="inlineStr">
         <is>
-          <t>SyncGTM says commission is about 30–35% of pay. That band is not the driver. We use $106.2m (25% of S&amp;M) as a model carve.</t>
-        </is>
-      </c>
-      <c r="G23" s="612" t="inlineStr">
+          <t>SyncGTM says commission is about 30–35% of pay. We use 30% of $414.1m = $124.2m in the math.</t>
+        </is>
+      </c>
+      <c r="G23" s="664" t="inlineStr">
         <is>
           <t>Go to AI_Operating!C8 (Commissions FY24A)</t>
         </is>
       </c>
-      <c r="H23" s="593" t="inlineStr">
-        <is>
-          <t>70/30 pay article</t>
-        </is>
-      </c>
-      <c r="I23" s="647" t="inlineStr">
+      <c r="H23" s="675">
+        <f>HYPERLINK("https://syncgtm.com/blog/how-to-pay-sales-development-rep","70/30 pay article")</f>
+        <v/>
+      </c>
+      <c r="I23" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: 30–35% of total pay</t>
         </is>
       </c>
-      <c r="J23" s="647" t="inlineStr">
-        <is>
-          <t>$106.2 / 25%: MODEL carve</t>
-        </is>
-      </c>
-      <c r="K23" s="651" t="n"/>
+      <c r="J23" s="671" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 70/30 base/variable split</t>
+        </is>
+      </c>
+      <c r="K23" s="672" t="inlineStr">
+        <is>
+          <t>$124.2m = 30% × $414.1m</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="96" customHeight="1" s="244">
-      <c r="A24" s="655" t="inlineStr">
+      <c r="A24" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B24" s="613" t="inlineStr">
+      <c r="B24" s="670" t="inlineStr">
         <is>
           <t>CapEx base % of rev</t>
         </is>
       </c>
-      <c r="C24" s="644" t="n">
+      <c r="C24" s="666" t="n">
         <v>0.02</v>
       </c>
-      <c r="D24" s="609" t="inlineStr">
-        <is>
-          <t>This is historical assumptions without AI. Normal hardware and capitalized software spending is reasonable for asset-light tech companies investing heavily in code rather than factories.</t>
-        </is>
-      </c>
-      <c r="E24" s="645">
-        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/","IN EQ band: SaaS CapEx 1–3% of rev (SaaSDB) → C24=2% = midpoint of that band")</f>
+      <c r="D24" s="667" t="inlineStr">
+        <is>
+          <t>Midpoint of the sourced pure-play SaaS CapEx band of 1–3% of revenue.</t>
+        </is>
+      </c>
+      <c r="E24" s="668">
+        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/","IN EQ band: SaaS CapEx 1–3% of rev → C24=2% midpoint")</f>
         <v/>
       </c>
       <c r="F24" s="664" t="inlineStr">
@@ -6392,66 +6449,66 @@
           <t>SaaSDB says pure-play SaaS CapEx is often 1–3% of sales. We use 2%, the midpoint of that band, in the CapEx math.</t>
         </is>
       </c>
-      <c r="G24" s="612" t="inlineStr">
+      <c r="G24" s="664" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D19 (CapEx)</t>
         </is>
       </c>
       <c r="H24" s="593" t="n"/>
-      <c r="I24" s="647" t="inlineStr">
+      <c r="I24" s="671" t="inlineStr">
         <is>
           <t>Ctrl+F: CapEx of 1</t>
         </is>
       </c>
-      <c r="J24" s="647" t="inlineStr">
+      <c r="J24" s="671" t="inlineStr">
         <is>
           <t>Tip: page uses en-dash 1–3%; or Ctrl+F: Most pure-play SaaS companies report CapEx of</t>
         </is>
       </c>
-      <c r="K24" s="647" t="inlineStr">
+      <c r="K24" s="671" t="inlineStr">
         <is>
           <t>2%: MODEL midpoint of 1–3% band</t>
         </is>
       </c>
     </row>
     <row r="25" ht="96" customHeight="1" s="244">
-      <c r="A25" s="655" t="inlineStr">
+      <c r="A25" s="665" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B25" s="607" t="inlineStr">
+      <c r="B25" s="664" t="inlineStr">
         <is>
           <t>WC base % of Δrev</t>
         </is>
       </c>
-      <c r="C25" s="608" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D25" s="609" t="inlineStr">
-        <is>
-          <t>This is historical assumptions without AI. Normal working capital needs are reasonable, showing that as revenue grows, a small percentage of cash gets tied up in daily operations.</t>
-        </is>
-      </c>
-      <c r="E25" s="643" t="inlineStr">
-        <is>
-          <t>C25=2% ΔNWC/ΔRev = MODEL CONST (no source equals 2%).</t>
+      <c r="C25" s="666" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="667" t="inlineStr">
+        <is>
+          <t>Was an unsourced 2% ΔNWC/ΔRev plug. No page equals 2%, so the plug is set to 0%.</t>
+        </is>
+      </c>
+      <c r="E25" s="669" t="inlineStr">
+        <is>
+          <t>C25=0% ΔNWC/ΔRev — no source printed 2%, so the plug is zero.</t>
         </is>
       </c>
       <c r="F25" s="664" t="inlineStr">
         <is>
-          <t>No source says a 2% WC plug. The 2% is our choice and still goes into the working-capital math.</t>
-        </is>
-      </c>
-      <c r="G25" s="612" t="inlineStr">
+          <t>No source says a 2% WC plug. The plug is 0%, so ΔNWC is zero in the forecast.</t>
+        </is>
+      </c>
+      <c r="G25" s="664" t="inlineStr">
         <is>
           <t>Go to AI_Operating!D20 (ΔNWC)</t>
         </is>
       </c>
       <c r="H25" s="593" t="n"/>
-      <c r="I25" s="643" t="inlineStr">
-        <is>
-          <t>2% WC plug: N/A — MODEL CONST</t>
+      <c r="I25" s="669" t="inlineStr">
+        <is>
+          <t>0% WC plug: no source equaled 2%</t>
         </is>
       </c>
       <c r="J25" s="651" t="n"/>
@@ -6555,17 +6612,14 @@
     <row r="29" ht="72" customHeight="1" s="244">
       <c r="B29" s="618" t="inlineStr">
         <is>
-          <t>AI $34m IN-EQ sources + Ctrl+F:</t>
+          <t>AI $24.5m IN-EQ sources + Ctrl+F:</t>
         </is>
       </c>
       <c r="C29" s="620" t="inlineStr">
         <is>
-          <t>White Space Ctrl+F $5,000-10,000 | Miniloop Ctrl+F $10,000-$15,000 | SEC Ctrl+F 1,513 in sales | MODEL CONST 25% outbound | NOT in EQ: 11x $3,750</t>
-        </is>
-      </c>
-      <c r="D29" s="621" t="n"/>
-      <c r="E29" s="621" t="n"/>
-      <c r="F29" s="622" t="n"/>
+          <t>White Space Ctrl+F $5,000-10,000+ | Miniloop Ctrl+F $10,000-$15,000+ | SEC Ctrl+F 1,513 in sales | roles=18% of HC (same 18% as payroll cut)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="618" t="inlineStr">
@@ -6640,8 +6694,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C29:F29"/>
+  <mergeCells count="1">
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <hyperlinks>
@@ -12445,11 +12498,11 @@
     <row r="16">
       <c r="B16" s="575" t="inlineStr">
         <is>
-          <t>S&amp;M baseline (35% of rev)</t>
+          <t>S&amp;M baseline (ZI FY24 S&amp;M $414.1m)</t>
         </is>
       </c>
       <c r="C16" s="567" t="n">
-        <v>425</v>
+        <v>414.1</v>
       </c>
       <c r="D16" s="591" t="inlineStr">
         <is>
@@ -12544,14 +12597,12 @@
           <t>Exit multiple</t>
         </is>
       </c>
-      <c r="C22" s="602" t="inlineStr">
-        <is>
-          <t>13.0x</t>
-        </is>
+      <c r="C22" s="602" t="n">
+        <v>12.9</v>
       </c>
       <c r="D22" s="591" t="inlineStr">
         <is>
-          <t>Mid of 12–14x software band</t>
+          <t>Aventis private SaaS EV/EBITDA 1st quartile 12.9x</t>
         </is>
       </c>
     </row>
@@ -12565,14 +12616,14 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>Y1: cut S&amp;M 15% vs baseline $425m; add $34m AI software/compute cost</t>
+          <t>Y1: cut payroll &amp; commissions 18% vs baseline $414.1m S&amp;M; add $24.5m AI software/compute cost</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>Y2–Y5: S&amp;M grows only 2%/yr (AI scales without headcount)</t>
+          <t>Y2–Y5: S&amp;M held flat at 0%/yr after Y1 cut (AI scales without headcount; no Fed +2% vs −2% rev)</t>
         </is>
       </c>
     </row>
@@ -12624,13 +12675,13 @@
         </is>
       </c>
       <c r="C31" s="624" t="n">
-        <v>0.1085118998600017</v>
+        <v>0.1174882648439431</v>
       </c>
       <c r="D31" s="624" t="n">
-        <v>0.1882716226673465</v>
+        <v>0.1463334408379282</v>
       </c>
       <c r="E31" s="624" t="n">
-        <v>0.07975972280734472</v>
+        <v>0.02884517599398503</v>
       </c>
       <c r="F31" s="625" t="inlineStr">
         <is>
@@ -12645,13 +12696,13 @@
         </is>
       </c>
       <c r="C32" s="626" t="n">
-        <v>-422.7456147574727</v>
+        <v>-332.9819649180587</v>
       </c>
       <c r="D32" s="626" t="n">
-        <v>374.8516133159746</v>
+        <v>-44.53020497820842</v>
       </c>
       <c r="E32" s="626" t="n">
-        <v>797.5972280734472</v>
+        <v>288.4517599398503</v>
       </c>
       <c r="F32" s="625" t="inlineStr">
         <is>
@@ -12666,13 +12717,13 @@
         </is>
       </c>
       <c r="C33" s="626" t="n">
-        <v>212.2104606600003</v>
+        <v>128.9587643962689</v>
       </c>
       <c r="D33" s="626" t="n">
-        <v>477.3963076296004</v>
+        <v>139.2103663511489</v>
       </c>
       <c r="E33" s="626" t="n">
-        <v>265.1858469696001</v>
+        <v>10.25160195488002</v>
       </c>
       <c r="F33" s="625" t="inlineStr">
         <is>
@@ -12687,13 +12738,13 @@
         </is>
       </c>
       <c r="C34" s="626" t="n">
-        <v>2758.735988580003</v>
+        <v>1663.568060711868</v>
       </c>
       <c r="D34" s="626" t="n">
-        <v>6206.151999184804</v>
+        <v>1795.813725929821</v>
       </c>
       <c r="E34" s="626" t="n">
-        <v>3447.416010604801</v>
+        <v>132.2456652179521</v>
       </c>
       <c r="F34" s="625" t="inlineStr">
         <is>
@@ -12708,17 +12759,17 @@
         </is>
       </c>
       <c r="C35" s="626" t="n">
-        <v>557.1124750633038</v>
+        <v>714.8120820308267</v>
       </c>
       <c r="D35" s="626" t="n">
-        <v>0</v>
+        <v>572.4246974503579</v>
       </c>
       <c r="E35" s="626" t="n">
-        <v>-557.1124750633038</v>
+        <v>-142.3873845804687</v>
       </c>
       <c r="F35" s="625" t="inlineStr">
         <is>
-          <t>Remaining debt at exit; AI case $0.0m vs Base $557.1m.</t>
+          <t>Remaining debt at exit; AI case $572.4m vs Base $714.8m.</t>
         </is>
       </c>
     </row>
@@ -12729,17 +12780,17 @@
         </is>
       </c>
       <c r="C36" s="626" t="n">
-        <v>2180.4024674507</v>
+        <v>948.7559786810417</v>
       </c>
       <c r="D36" s="626" t="n">
-        <v>6291.958085621143</v>
+        <v>1223.389028479462</v>
       </c>
       <c r="E36" s="626" t="n">
-        <v>4111.555618170443</v>
+        <v>274.6330497984208</v>
       </c>
       <c r="F36" s="625" t="inlineStr">
         <is>
-          <t>Total equity payout; AI strategy changed final payout by $4,111.6m to $6,292.0m (exit 12.9x).</t>
+          <t>Total equity payout; AI strategy changed final payout by $274.6m to $1,223.4m (exit 12.9x).</t>
         </is>
       </c>
     </row>
@@ -12750,17 +12801,17 @@
         </is>
       </c>
       <c r="C37" s="627" t="n">
-        <v>1.16518721058838</v>
+        <v>0.5070065498600007</v>
       </c>
       <c r="D37" s="627" t="n">
-        <v>3.362365068085611</v>
+        <v>0.6537679491919968</v>
       </c>
       <c r="E37" s="627" t="n">
-        <v>2.19717785749723</v>
+        <v>0.1467613993319961</v>
       </c>
       <c r="F37" s="625" t="inlineStr">
         <is>
-          <t>Multiple on Invested Capital; AI improved gross cash return from 1.17x to 3.36x.</t>
+          <t>Multiple on Invested Capital; AI improved gross cash return from 0.51x to 0.65x.</t>
         </is>
       </c>
     </row>
@@ -12771,17 +12822,17 @@
         </is>
       </c>
       <c r="C38" s="624" t="n">
-        <v>0.03104861170671052</v>
+        <v>-0.1270231762544919</v>
       </c>
       <c r="D38" s="624" t="n">
-        <v>0.2744681102428927</v>
+        <v>-0.08148823147841401</v>
       </c>
       <c r="E38" s="624" t="n">
-        <v>0.2434194985361822</v>
+        <v>0.04553494477607785</v>
       </c>
       <c r="F38" s="625" t="inlineStr">
         <is>
-          <t>5-year IRR; AI boosted return by 24.3 percentage points to 27.4% (AI infra $34m; payroll cut 18%; exit 12.9x).</t>
+          <t>5-year IRR; AI boosted return by 4.6 percentage points to -8.1% (AI infra $24.5m; payroll/commission cut 18%; rev -2%; exit 12.9x).</t>
         </is>
       </c>
     </row>
@@ -12802,14 +12853,14 @@
     <row r="41">
       <c r="B41" s="569" t="inlineStr">
         <is>
-          <t>AI case IRR 27.4% − Base IRR 3.1% = 24.3 percentage points of IRR</t>
+          <t>AI case IRR -8.1% − Base IRR -12.7% = 4.6 percentage points of IRR</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="569" t="inlineStr">
         <is>
-          <t>Y2 AI EBITDA margin 19.5% vs FY24 baseline 15.1% = 441 bps (target ≥500: NO)</t>
+          <t>Y2 AI EBITDA margin 14.6% vs FY24 baseline 15.1% = -45 bps (target ≥500: NO)</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13105,7 @@
       </c>
       <c r="D7" s="571" t="inlineStr">
         <is>
-          <t>10% per year (unchanged by AI)</t>
+          <t>-2% per year (unchanged by AI)</t>
         </is>
       </c>
       <c r="E7" s="571" t="inlineStr">
@@ -13249,7 +13300,7 @@
       </c>
       <c r="D10" s="571" t="inlineStr">
         <is>
-          <t>−20% of baseline commission pool from Y1</t>
+          <t>−18% of baseline commission pool from Y1</t>
         </is>
       </c>
       <c r="E10" s="571" t="inlineStr">
@@ -13314,7 +13365,7 @@
       </c>
       <c r="D11" s="571" t="inlineStr">
         <is>
-          <t>$34 million fixed / year</t>
+          <t>$24.5 million fixed / year</t>
         </is>
       </c>
       <c r="E11" s="571" t="inlineStr">
@@ -13379,7 +13430,7 @@
       </c>
       <c r="D12" s="571" t="inlineStr">
         <is>
-          <t>2% per year from Year 2</t>
+          <t>0% per year from Year 2</t>
         </is>
       </c>
       <c r="E12" s="571" t="inlineStr">
@@ -13509,7 +13560,7 @@
       </c>
       <c r="D14" s="571" t="inlineStr">
         <is>
-          <t>−5% vs baseline CapEx rate</t>
+          <t>−0% vs baseline CapEx rate (no sourced cut)</t>
         </is>
       </c>
       <c r="E14" s="571" t="inlineStr">
@@ -13574,7 +13625,7 @@
       </c>
       <c r="D15" s="571" t="inlineStr">
         <is>
-          <t>Receivables / WC requirement −10% vs base</t>
+          <t>WC improve 0% vs base (no sourced improve)</t>
         </is>
       </c>
       <c r="E15" s="571" t="inlineStr">
@@ -14036,7 +14087,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>$425.0m</t>
+          <t>$414.1m</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -14081,7 +14132,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>$318.8m</t>
+          <t>$289.9m</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -14126,7 +14177,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>$106.2m</t>
+          <t>$124.2m</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -14216,7 +14267,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -14267,7 +14318,7 @@
     <row r="30">
       <c r="B30" s="590" t="inlineStr">
         <is>
-          <t>This list must match Assumptions_Drivers: payroll cut −18%, exit 12.9x, AI infra $34m, G&amp;A 18%, SOFR 4.30%. Col N = Baseline Yes/No (same rule as Drivers col A).</t>
+          <t>This list must match Assumptions_Drivers: rev -2%, payroll/commission cut −18%, AI $24.5m, S&amp;M $414.1m, exit 12.9x, CapEx/WC cuts 0% (unsourced removed).</t>
         </is>
       </c>
     </row>
@@ -14454,22 +14505,22 @@
         <v>2025</v>
       </c>
       <c r="C5" s="626" t="n">
-        <v>106.533319</v>
+        <v>75.80021219999996</v>
       </c>
       <c r="D5" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E5" s="626" t="n">
-        <v>106.533319</v>
+        <v>75.80021219999996</v>
       </c>
       <c r="F5" s="626" t="n">
-        <v>808.966681</v>
+        <v>839.6997878000001</v>
       </c>
       <c r="G5" s="626" t="n">
-        <v>877.5180999999999</v>
+        <v>877.3051</v>
       </c>
       <c r="H5" s="626" t="n">
-        <v>68.5514189999999</v>
+        <v>37.60531219999996</v>
       </c>
     </row>
     <row r="6">
@@ -14477,22 +14528,22 @@
         <v>2026</v>
       </c>
       <c r="C6" s="626" t="n">
-        <v>155.5010311268301</v>
+        <v>72.27273176995408</v>
       </c>
       <c r="D6" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E6" s="626" t="n">
-        <v>155.5010311268301</v>
+        <v>72.27273176995408</v>
       </c>
       <c r="F6" s="626" t="n">
-        <v>653.4656498731698</v>
+        <v>767.4270560300459</v>
       </c>
       <c r="G6" s="626" t="n">
-        <v>824.8037622999997</v>
+        <v>838.2602713</v>
       </c>
       <c r="H6" s="626" t="n">
-        <v>171.3381124268299</v>
+        <v>70.83321526995405</v>
       </c>
     </row>
     <row r="7">
@@ -14500,22 +14551,22 @@
         <v>2027</v>
       </c>
       <c r="C7" s="626" t="n">
-        <v>212.3276965378165</v>
+        <v>68.68390845498992</v>
       </c>
       <c r="D7" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E7" s="626" t="n">
-        <v>212.3276965378165</v>
+        <v>68.68390845498992</v>
       </c>
       <c r="F7" s="626" t="n">
-        <v>441.1379533353534</v>
+        <v>698.743147575056</v>
       </c>
       <c r="G7" s="626" t="n">
-        <v>754.9762005708997</v>
+        <v>798.2485648578999</v>
       </c>
       <c r="H7" s="626" t="n">
-        <v>313.8382472355463</v>
+        <v>99.50541728284384</v>
       </c>
     </row>
     <row r="8">
@@ -14523,22 +14574,22 @@
         <v>2028</v>
       </c>
       <c r="C8" s="626" t="n">
-        <v>278.1336741716516</v>
+        <v>65.02632092200611</v>
       </c>
       <c r="D8" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E8" s="626" t="n">
-        <v>278.1336741716516</v>
+        <v>65.02632092200611</v>
       </c>
       <c r="F8" s="626" t="n">
-        <v>163.0042791637017</v>
+        <v>633.7168266530499</v>
       </c>
       <c r="G8" s="626" t="n">
-        <v>665.9609770683334</v>
+        <v>757.1442529603054</v>
       </c>
       <c r="H8" s="626" t="n">
-        <v>502.9566979046317</v>
+        <v>123.4274263072555</v>
       </c>
     </row>
     <row r="9">
@@ -14546,22 +14597,22 @@
         <v>2029</v>
       </c>
       <c r="C9" s="626" t="n">
-        <v>355.725762314317</v>
+        <v>61.29212920269194</v>
       </c>
       <c r="D9" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E9" s="626" t="n">
-        <v>163.0042791637017</v>
+        <v>61.29212920269194</v>
       </c>
       <c r="F9" s="626" t="n">
-        <v>0</v>
+        <v>572.4246974503579</v>
       </c>
       <c r="G9" s="626" t="n">
-        <v>557.1124750633038</v>
+        <v>714.8120820308267</v>
       </c>
       <c r="H9" s="626" t="n">
-        <v>557.1124750633038</v>
+        <v>142.3873845804687</v>
       </c>
     </row>
     <row r="11">
@@ -14678,19 +14729,19 @@
         <v>1214.3</v>
       </c>
       <c r="D5" s="626" t="n">
-        <v>1335.73</v>
+        <v>1190.014</v>
       </c>
       <c r="E5" s="626" t="n">
-        <v>1469.303</v>
+        <v>1166.21372</v>
       </c>
       <c r="F5" s="626" t="n">
-        <v>1616.2333</v>
+        <v>1142.8894456</v>
       </c>
       <c r="G5" s="626" t="n">
-        <v>1777.85663</v>
+        <v>1120.031656688</v>
       </c>
       <c r="H5" s="626" t="n">
-        <v>1955.642293000001</v>
+        <v>1097.63102355424</v>
       </c>
     </row>
     <row r="6">
@@ -14703,19 +14754,19 @@
         <v>242.8599999999999</v>
       </c>
       <c r="D6" s="626" t="n">
-        <v>267.146</v>
+        <v>238.0027999999999</v>
       </c>
       <c r="E6" s="626" t="n">
-        <v>293.8606</v>
+        <v>233.2427439999999</v>
       </c>
       <c r="F6" s="626" t="n">
-        <v>323.24666</v>
+        <v>228.57788912</v>
       </c>
       <c r="G6" s="626" t="n">
-        <v>355.571326</v>
+        <v>224.0063313376</v>
       </c>
       <c r="H6" s="626" t="n">
-        <v>391.1284586</v>
+        <v>219.526204710848</v>
       </c>
     </row>
     <row r="7">
@@ -14725,22 +14776,22 @@
         </is>
       </c>
       <c r="C7" s="582" t="n">
-        <v>318.8</v>
+        <v>289.9</v>
       </c>
       <c r="D7" s="626" t="n">
-        <v>350.68</v>
+        <v>284.102</v>
       </c>
       <c r="E7" s="626" t="n">
-        <v>385.748</v>
+        <v>278.41996</v>
       </c>
       <c r="F7" s="626" t="n">
-        <v>424.3228000000001</v>
+        <v>272.8515608</v>
       </c>
       <c r="G7" s="626" t="n">
-        <v>466.7550800000001</v>
+        <v>267.394529584</v>
       </c>
       <c r="H7" s="626" t="n">
-        <v>513.4305880000002</v>
+        <v>262.04663899232</v>
       </c>
     </row>
     <row r="8">
@@ -14750,22 +14801,22 @@
         </is>
       </c>
       <c r="C8" s="582" t="n">
-        <v>106.2</v>
+        <v>124.2</v>
       </c>
       <c r="D8" s="626" t="n">
-        <v>116.82</v>
+        <v>121.716</v>
       </c>
       <c r="E8" s="626" t="n">
-        <v>128.502</v>
+        <v>119.28168</v>
       </c>
       <c r="F8" s="626" t="n">
-        <v>141.3522</v>
+        <v>116.8960464</v>
       </c>
       <c r="G8" s="626" t="n">
-        <v>155.48742</v>
+        <v>114.558125472</v>
       </c>
       <c r="H8" s="626" t="n">
-        <v>171.0361620000001</v>
+        <v>112.26696296256</v>
       </c>
     </row>
     <row r="9">
@@ -14775,22 +14826,22 @@
         </is>
       </c>
       <c r="C9" s="582" t="n">
-        <v>425</v>
+        <v>414.1</v>
       </c>
       <c r="D9" s="626" t="n">
-        <v>467.5</v>
+        <v>405.818</v>
       </c>
       <c r="E9" s="626" t="n">
-        <v>514.25</v>
+        <v>397.70164</v>
       </c>
       <c r="F9" s="626" t="n">
-        <v>565.6750000000002</v>
+        <v>389.7476072</v>
       </c>
       <c r="G9" s="626" t="n">
-        <v>622.2425000000002</v>
+        <v>381.952655056</v>
       </c>
       <c r="H9" s="626" t="n">
-        <v>684.4667500000003</v>
+        <v>374.31360195488</v>
       </c>
     </row>
     <row r="10">
@@ -14828,19 +14879,19 @@
         <v>196.1</v>
       </c>
       <c r="D11" s="626" t="n">
-        <v>215.71</v>
+        <v>192.178</v>
       </c>
       <c r="E11" s="626" t="n">
-        <v>237.281</v>
+        <v>188.33444</v>
       </c>
       <c r="F11" s="626" t="n">
-        <v>261.0091</v>
+        <v>184.5677512</v>
       </c>
       <c r="G11" s="626" t="n">
-        <v>287.11001</v>
+        <v>180.876396176</v>
       </c>
       <c r="H11" s="626" t="n">
-        <v>315.8210110000001</v>
+        <v>177.25886825248</v>
       </c>
     </row>
     <row r="12">
@@ -14853,19 +14904,19 @@
         <v>218.574</v>
       </c>
       <c r="D12" s="626" t="n">
-        <v>240.4314</v>
+        <v>214.20252</v>
       </c>
       <c r="E12" s="626" t="n">
-        <v>264.47454</v>
+        <v>209.9184696</v>
       </c>
       <c r="F12" s="626" t="n">
-        <v>290.921994</v>
+        <v>205.720100208</v>
       </c>
       <c r="G12" s="626" t="n">
-        <v>320.0141934000001</v>
+        <v>201.60569820384</v>
       </c>
       <c r="H12" s="626" t="n">
-        <v>352.0156127400001</v>
+        <v>197.5735842397632</v>
       </c>
     </row>
     <row r="13">
@@ -14878,19 +14929,19 @@
         <v>183.1</v>
       </c>
       <c r="D13" s="626" t="n">
-        <v>144.9426000000001</v>
+        <v>139.81268</v>
       </c>
       <c r="E13" s="626" t="n">
-        <v>159.4368600000001</v>
+        <v>137.0164264000001</v>
       </c>
       <c r="F13" s="626" t="n">
-        <v>175.380546</v>
+        <v>134.2760978720001</v>
       </c>
       <c r="G13" s="626" t="n">
-        <v>192.9186006000002</v>
+        <v>131.5905759145601</v>
       </c>
       <c r="H13" s="626" t="n">
-        <v>212.2104606600003</v>
+        <v>128.9587643962689</v>
       </c>
     </row>
     <row r="14">
@@ -14903,19 +14954,19 @@
         <v>0.150786461335749</v>
       </c>
       <c r="D14" s="624" t="n">
-        <v>0.1085118998600017</v>
+        <v>0.117488264843943</v>
       </c>
       <c r="E14" s="624" t="n">
-        <v>0.1085118998600017</v>
+        <v>0.1174882648439431</v>
       </c>
       <c r="F14" s="624" t="n">
-        <v>0.1085118998600016</v>
+        <v>0.1174882648439431</v>
       </c>
       <c r="G14" s="624" t="n">
-        <v>0.1085118998600017</v>
+        <v>0.1174882648439431</v>
       </c>
       <c r="H14" s="624" t="n">
-        <v>0.1085118998600017</v>
+        <v>0.1174882648439431</v>
       </c>
     </row>
     <row r="15">
@@ -14928,19 +14979,19 @@
         <v>85.7</v>
       </c>
       <c r="D15" s="626" t="n">
-        <v>94.27</v>
+        <v>83.98599999999999</v>
       </c>
       <c r="E15" s="626" t="n">
-        <v>103.697</v>
+        <v>82.30628</v>
       </c>
       <c r="F15" s="626" t="n">
-        <v>114.0667</v>
+        <v>80.6601544</v>
       </c>
       <c r="G15" s="626" t="n">
-        <v>125.47337</v>
+        <v>79.046951312</v>
       </c>
       <c r="H15" s="626" t="n">
-        <v>138.020707</v>
+        <v>77.46601228576</v>
       </c>
     </row>
     <row r="16">
@@ -14953,19 +15004,19 @@
         <v>97.40000000000001</v>
       </c>
       <c r="D16" s="626" t="n">
-        <v>50.67260000000009</v>
+        <v>55.82667999999998</v>
       </c>
       <c r="E16" s="626" t="n">
-        <v>55.73986000000014</v>
+        <v>54.71014640000011</v>
       </c>
       <c r="F16" s="626" t="n">
-        <v>61.31384600000001</v>
+        <v>53.61594347200013</v>
       </c>
       <c r="G16" s="626" t="n">
-        <v>67.44523060000019</v>
+        <v>52.54362460256013</v>
       </c>
       <c r="H16" s="626" t="n">
-        <v>74.18975366000021</v>
+        <v>51.49275211050886</v>
       </c>
     </row>
     <row r="17">
@@ -14978,16 +15029,16 @@
         <v>77.8175</v>
       </c>
       <c r="E17" s="626" t="n">
-        <v>74.66500229999998</v>
+        <v>74.6473233</v>
       </c>
       <c r="F17" s="626" t="n">
-        <v>70.28971227089997</v>
+        <v>71.4066025179</v>
       </c>
       <c r="G17" s="626" t="n">
-        <v>64.49402464738468</v>
+        <v>68.08563088320568</v>
       </c>
       <c r="H17" s="626" t="n">
-        <v>57.10576109667166</v>
+        <v>64.67397299570534</v>
       </c>
     </row>
     <row r="18">
@@ -14997,19 +15048,19 @@
         </is>
       </c>
       <c r="D18" s="626" t="n">
-        <v>-27.14489999999991</v>
+        <v>-21.99082000000001</v>
       </c>
       <c r="E18" s="626" t="n">
-        <v>-18.92514229999985</v>
+        <v>-19.93717689999988</v>
       </c>
       <c r="F18" s="626" t="n">
-        <v>-8.975866270899957</v>
+        <v>-17.79065904589987</v>
       </c>
       <c r="G18" s="626" t="n">
-        <v>2.331452702566253</v>
+        <v>-15.54200628064555</v>
       </c>
       <c r="H18" s="626" t="n">
-        <v>13.49635412502955</v>
+        <v>-13.18122088519648</v>
       </c>
     </row>
     <row r="19">
@@ -15019,19 +15070,19 @@
         </is>
       </c>
       <c r="D19" s="626" t="n">
-        <v>26.7146</v>
+        <v>23.80028</v>
       </c>
       <c r="E19" s="626" t="n">
-        <v>29.38606</v>
+        <v>23.3242744</v>
       </c>
       <c r="F19" s="626" t="n">
-        <v>32.32466600000001</v>
+        <v>22.857788912</v>
       </c>
       <c r="G19" s="626" t="n">
-        <v>35.55713260000001</v>
+        <v>22.40063313376</v>
       </c>
       <c r="H19" s="626" t="n">
-        <v>39.11284586000001</v>
+        <v>21.9526204710848</v>
       </c>
     </row>
     <row r="20">
@@ -15041,19 +15092,19 @@
         </is>
       </c>
       <c r="D20" s="626" t="n">
-        <v>2.428600000000001</v>
+        <v>-0</v>
       </c>
       <c r="E20" s="626" t="n">
-        <v>2.671460000000002</v>
+        <v>-0</v>
       </c>
       <c r="F20" s="626" t="n">
-        <v>2.938606000000004</v>
+        <v>-0</v>
       </c>
       <c r="G20" s="626" t="n">
-        <v>3.232466600000003</v>
+        <v>-0</v>
       </c>
       <c r="H20" s="626" t="n">
-        <v>3.555713260000002</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="21">
@@ -15063,19 +15114,19 @@
         </is>
       </c>
       <c r="D21" s="626" t="n">
-        <v>37.98190000000008</v>
+        <v>38.19489999999998</v>
       </c>
       <c r="E21" s="626" t="n">
-        <v>52.71433770000015</v>
+        <v>39.04482870000012</v>
       </c>
       <c r="F21" s="626" t="n">
-        <v>69.82756172910005</v>
+        <v>40.01170644210012</v>
       </c>
       <c r="G21" s="626" t="n">
-        <v>89.01522350256627</v>
+        <v>41.10431189759445</v>
       </c>
       <c r="H21" s="626" t="n">
-        <v>108.8485020050296</v>
+        <v>42.33217092947872</v>
       </c>
     </row>
     <row r="22">
@@ -15107,19 +15158,19 @@
         </is>
       </c>
       <c r="D23" s="626" t="n">
-        <v>37.98190000000008</v>
+        <v>38.19489999999998</v>
       </c>
       <c r="E23" s="626" t="n">
-        <v>52.71433770000015</v>
+        <v>39.04482870000012</v>
       </c>
       <c r="F23" s="626" t="n">
-        <v>69.82756172910005</v>
+        <v>40.01170644210012</v>
       </c>
       <c r="G23" s="626" t="n">
-        <v>89.01522350256627</v>
+        <v>41.10431189759445</v>
       </c>
       <c r="H23" s="626" t="n">
-        <v>108.8485020050296</v>
+        <v>42.33217092947872</v>
       </c>
     </row>
     <row r="24">
@@ -15132,19 +15183,19 @@
         <v>1329.9</v>
       </c>
       <c r="D24" s="626" t="n">
-        <v>877.5180999999999</v>
+        <v>877.3051</v>
       </c>
       <c r="E24" s="626" t="n">
-        <v>824.8037622999997</v>
+        <v>838.2602713</v>
       </c>
       <c r="F24" s="626" t="n">
-        <v>754.9762005708997</v>
+        <v>798.2485648578999</v>
       </c>
       <c r="G24" s="626" t="n">
-        <v>665.9609770683334</v>
+        <v>757.1442529603054</v>
       </c>
       <c r="H24" s="626" t="n">
-        <v>557.1124750633038</v>
+        <v>714.8120820308267</v>
       </c>
     </row>
   </sheetData>
@@ -15232,19 +15283,19 @@
         <v>1214.3</v>
       </c>
       <c r="D5" s="626" t="n">
-        <v>1335.73</v>
+        <v>1190.014</v>
       </c>
       <c r="E5" s="626" t="n">
-        <v>1469.303</v>
+        <v>1166.21372</v>
       </c>
       <c r="F5" s="626" t="n">
-        <v>1616.2333</v>
+        <v>1142.8894456</v>
       </c>
       <c r="G5" s="626" t="n">
-        <v>1777.85663</v>
+        <v>1120.031656688</v>
       </c>
       <c r="H5" s="626" t="n">
-        <v>1955.642293000001</v>
+        <v>1097.63102355424</v>
       </c>
     </row>
     <row r="6">
@@ -15257,19 +15308,19 @@
         <v>242.8599999999999</v>
       </c>
       <c r="D6" s="626" t="n">
-        <v>267.146</v>
+        <v>238.0027999999999</v>
       </c>
       <c r="E6" s="626" t="n">
-        <v>293.8606</v>
+        <v>233.2427439999999</v>
       </c>
       <c r="F6" s="626" t="n">
-        <v>323.24666</v>
+        <v>228.57788912</v>
       </c>
       <c r="G6" s="626" t="n">
-        <v>355.571326</v>
+        <v>224.0063313376</v>
       </c>
       <c r="H6" s="626" t="n">
-        <v>391.1284586</v>
+        <v>219.526204710848</v>
       </c>
     </row>
     <row r="7">
@@ -15279,22 +15330,22 @@
         </is>
       </c>
       <c r="C7" s="582" t="n">
-        <v>318.8</v>
+        <v>289.9</v>
       </c>
       <c r="D7" s="626" t="n">
-        <v>261.4160000000001</v>
+        <v>237.718</v>
       </c>
       <c r="E7" s="626" t="n">
-        <v>266.6443200000001</v>
+        <v>237.718</v>
       </c>
       <c r="F7" s="626" t="n">
-        <v>271.9772064000001</v>
+        <v>237.718</v>
       </c>
       <c r="G7" s="626" t="n">
-        <v>277.4167505280001</v>
+        <v>237.718</v>
       </c>
       <c r="H7" s="626" t="n">
-        <v>282.9650855385601</v>
+        <v>237.718</v>
       </c>
     </row>
     <row r="8">
@@ -15304,22 +15355,22 @@
         </is>
       </c>
       <c r="C8" s="582" t="n">
-        <v>106.2</v>
+        <v>124.2</v>
       </c>
       <c r="D8" s="626" t="n">
-        <v>84.96000000000001</v>
+        <v>101.844</v>
       </c>
       <c r="E8" s="626" t="n">
-        <v>86.65920000000001</v>
+        <v>101.844</v>
       </c>
       <c r="F8" s="626" t="n">
-        <v>88.39238400000002</v>
+        <v>101.844</v>
       </c>
       <c r="G8" s="626" t="n">
-        <v>90.16023168000002</v>
+        <v>101.844</v>
       </c>
       <c r="H8" s="626" t="n">
-        <v>91.96343631360003</v>
+        <v>101.844</v>
       </c>
     </row>
     <row r="9">
@@ -15329,22 +15380,22 @@
         </is>
       </c>
       <c r="C9" s="582" t="n">
-        <v>425</v>
+        <v>414.1</v>
       </c>
       <c r="D9" s="626" t="n">
-        <v>346.3760000000001</v>
+        <v>339.562</v>
       </c>
       <c r="E9" s="626" t="n">
-        <v>353.30352</v>
+        <v>339.562</v>
       </c>
       <c r="F9" s="626" t="n">
-        <v>360.3695904000001</v>
+        <v>339.562</v>
       </c>
       <c r="G9" s="626" t="n">
-        <v>367.5769822080001</v>
+        <v>339.562</v>
       </c>
       <c r="H9" s="626" t="n">
-        <v>374.9285218521601</v>
+        <v>339.562</v>
       </c>
     </row>
     <row r="10">
@@ -15357,19 +15408,19 @@
         <v>0</v>
       </c>
       <c r="D10" s="626" t="n">
-        <v>34</v>
+        <v>24.5</v>
       </c>
       <c r="E10" s="626" t="n">
-        <v>34</v>
+        <v>24.5</v>
       </c>
       <c r="F10" s="626" t="n">
-        <v>34</v>
+        <v>24.5</v>
       </c>
       <c r="G10" s="626" t="n">
-        <v>34</v>
+        <v>24.5</v>
       </c>
       <c r="H10" s="626" t="n">
-        <v>34</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="11">
@@ -15382,19 +15433,19 @@
         <v>196.1</v>
       </c>
       <c r="D11" s="626" t="n">
-        <v>215.71</v>
+        <v>192.178</v>
       </c>
       <c r="E11" s="626" t="n">
-        <v>237.281</v>
+        <v>188.33444</v>
       </c>
       <c r="F11" s="626" t="n">
-        <v>261.0091</v>
+        <v>184.5677512</v>
       </c>
       <c r="G11" s="626" t="n">
-        <v>287.11001</v>
+        <v>180.876396176</v>
       </c>
       <c r="H11" s="626" t="n">
-        <v>315.8210110000001</v>
+        <v>177.25886825248</v>
       </c>
     </row>
     <row r="12">
@@ -15407,19 +15458,19 @@
         <v>218.574</v>
       </c>
       <c r="D12" s="626" t="n">
-        <v>240.4314</v>
+        <v>214.20252</v>
       </c>
       <c r="E12" s="626" t="n">
-        <v>264.47454</v>
+        <v>209.9184696</v>
       </c>
       <c r="F12" s="626" t="n">
-        <v>290.921994</v>
+        <v>205.720100208</v>
       </c>
       <c r="G12" s="626" t="n">
-        <v>320.0141934000001</v>
+        <v>201.60569820384</v>
       </c>
       <c r="H12" s="626" t="n">
-        <v>352.0156127400001</v>
+        <v>197.5735842397632</v>
       </c>
     </row>
     <row r="13">
@@ -15432,19 +15483,19 @@
         <v>183.1</v>
       </c>
       <c r="D13" s="626" t="n">
-        <v>232.0666</v>
+        <v>181.5686799999999</v>
       </c>
       <c r="E13" s="626" t="n">
-        <v>286.38334</v>
+        <v>170.6560664000001</v>
       </c>
       <c r="F13" s="626" t="n">
-        <v>346.6859556000002</v>
+        <v>159.9617050720001</v>
       </c>
       <c r="G13" s="626" t="n">
-        <v>413.5841183920002</v>
+        <v>149.4812309705601</v>
       </c>
       <c r="H13" s="626" t="n">
-        <v>487.7486888078406</v>
+        <v>139.2103663511489</v>
       </c>
     </row>
     <row r="14">
@@ -15457,19 +15508,19 @@
         <v>0.150786461335749</v>
       </c>
       <c r="D14" s="624" t="n">
-        <v>0.1737376565623292</v>
+        <v>0.1525769276663972</v>
       </c>
       <c r="E14" s="624" t="n">
-        <v>0.1949110156312211</v>
+        <v>0.1463334408379282</v>
       </c>
       <c r="F14" s="624" t="n">
-        <v>0.2145024209066848</v>
+        <v>0.1399625359109188</v>
       </c>
       <c r="G14" s="624" t="n">
-        <v>0.2326307484040488</v>
+        <v>0.1334616125160114</v>
       </c>
       <c r="H14" s="624" t="n">
-        <v>0.2494058808984044</v>
+        <v>0.1268280172150853</v>
       </c>
     </row>
     <row r="15">
@@ -15482,19 +15533,19 @@
         <v>85.7</v>
       </c>
       <c r="D15" s="626" t="n">
-        <v>94.27</v>
+        <v>83.98599999999999</v>
       </c>
       <c r="E15" s="626" t="n">
-        <v>103.697</v>
+        <v>82.30628</v>
       </c>
       <c r="F15" s="626" t="n">
-        <v>114.0667</v>
+        <v>80.6601544</v>
       </c>
       <c r="G15" s="626" t="n">
-        <v>125.47337</v>
+        <v>79.046951312</v>
       </c>
       <c r="H15" s="626" t="n">
-        <v>138.020707</v>
+        <v>77.46601228576</v>
       </c>
     </row>
     <row r="16">
@@ -15507,19 +15558,19 @@
         <v>97.40000000000001</v>
       </c>
       <c r="D16" s="626" t="n">
-        <v>137.7966</v>
+        <v>97.58267999999995</v>
       </c>
       <c r="E16" s="626" t="n">
-        <v>182.68634</v>
+        <v>88.3497864000001</v>
       </c>
       <c r="F16" s="626" t="n">
-        <v>232.6192556000001</v>
+        <v>79.30155067200006</v>
       </c>
       <c r="G16" s="626" t="n">
-        <v>288.1107483920001</v>
+        <v>70.43427965856014</v>
       </c>
       <c r="H16" s="626" t="n">
-        <v>349.7279818078405</v>
+        <v>61.74435406538888</v>
       </c>
     </row>
     <row r="17">
@@ -15532,16 +15583,16 @@
         <v>77.8175</v>
       </c>
       <c r="E17" s="626" t="n">
-        <v>68.348123043</v>
+        <v>71.5260823874</v>
       </c>
       <c r="F17" s="626" t="n">
-        <v>54.7607640501295</v>
+        <v>65.52744565049382</v>
       </c>
       <c r="G17" s="626" t="n">
-        <v>35.9867231453002</v>
+        <v>59.82668124872964</v>
       </c>
       <c r="H17" s="626" t="n">
-        <v>10.02482647488497</v>
+        <v>54.42949661220314</v>
       </c>
     </row>
     <row r="18">
@@ -15551,19 +15602,19 @@
         </is>
       </c>
       <c r="D18" s="626" t="n">
-        <v>47.38348900000001</v>
+        <v>15.61449219999997</v>
       </c>
       <c r="E18" s="626" t="n">
-        <v>90.32719139603003</v>
+        <v>13.29072616995408</v>
       </c>
       <c r="F18" s="626" t="n">
-        <v>140.5082083243978</v>
+        <v>10.88154296698993</v>
       </c>
       <c r="G18" s="626" t="n">
-        <v>199.1779799448929</v>
+        <v>8.380002743766095</v>
       </c>
       <c r="H18" s="626" t="n">
-        <v>268.3654927130348</v>
+        <v>5.778737388016733</v>
       </c>
     </row>
     <row r="19">
@@ -15573,19 +15624,19 @@
         </is>
       </c>
       <c r="D19" s="626" t="n">
-        <v>25.37887</v>
+        <v>23.80028</v>
       </c>
       <c r="E19" s="626" t="n">
-        <v>27.916757</v>
+        <v>23.3242744</v>
       </c>
       <c r="F19" s="626" t="n">
-        <v>30.70843270000001</v>
+        <v>22.857788912</v>
       </c>
       <c r="G19" s="626" t="n">
-        <v>33.77927597000001</v>
+        <v>22.40063313376</v>
       </c>
       <c r="H19" s="626" t="n">
-        <v>37.15720356700001</v>
+        <v>21.9526204710848</v>
       </c>
     </row>
     <row r="20">
@@ -15595,19 +15646,19 @@
         </is>
       </c>
       <c r="D20" s="626" t="n">
-        <v>2.185740000000001</v>
+        <v>-0</v>
       </c>
       <c r="E20" s="626" t="n">
-        <v>2.404314000000002</v>
+        <v>-0</v>
       </c>
       <c r="F20" s="626" t="n">
-        <v>2.644745400000004</v>
+        <v>-0</v>
       </c>
       <c r="G20" s="626" t="n">
-        <v>2.909219940000003</v>
+        <v>-0</v>
       </c>
       <c r="H20" s="626" t="n">
-        <v>3.200141934000002</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="21">
@@ -15617,19 +15668,19 @@
         </is>
       </c>
       <c r="D21" s="626" t="n">
-        <v>114.088879</v>
+        <v>75.80021219999996</v>
       </c>
       <c r="E21" s="626" t="n">
-        <v>163.70312039603</v>
+        <v>72.27273176995408</v>
       </c>
       <c r="F21" s="626" t="n">
-        <v>221.2217302243978</v>
+        <v>68.68390845498992</v>
       </c>
       <c r="G21" s="626" t="n">
-        <v>287.9628540348929</v>
+        <v>65.02632092200611</v>
       </c>
       <c r="H21" s="626" t="n">
-        <v>366.0288542120349</v>
+        <v>61.29212920269194</v>
       </c>
     </row>
     <row r="22">
@@ -15661,19 +15712,19 @@
         </is>
       </c>
       <c r="D23" s="626" t="n">
-        <v>114.088879</v>
+        <v>75.80021219999996</v>
       </c>
       <c r="E23" s="626" t="n">
-        <v>163.70312039603</v>
+        <v>72.27273176995408</v>
       </c>
       <c r="F23" s="626" t="n">
-        <v>221.2217302243978</v>
+        <v>68.68390845498992</v>
       </c>
       <c r="G23" s="626" t="n">
-        <v>287.9628540348929</v>
+        <v>65.02632092200611</v>
       </c>
       <c r="H23" s="626" t="n">
-        <v>128.5234163446792</v>
+        <v>61.29212920269194</v>
       </c>
     </row>
     <row r="24">
@@ -15686,19 +15737,19 @@
         <v>1329.9</v>
       </c>
       <c r="D24" s="626" t="n">
-        <v>801.411121</v>
+        <v>839.6997878000001</v>
       </c>
       <c r="E24" s="626" t="n">
-        <v>637.7080006039699</v>
+        <v>767.4270560300459</v>
       </c>
       <c r="F24" s="626" t="n">
-        <v>416.4862703795721</v>
+        <v>698.743147575056</v>
       </c>
       <c r="G24" s="626" t="n">
-        <v>128.5234163446792</v>
+        <v>633.7168266530499</v>
       </c>
       <c r="H24" s="626" t="n">
-        <v>0</v>
+        <v>572.4246974503579</v>
       </c>
     </row>
   </sheetData>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -5442,7 +5442,7 @@
     <row r="3" ht="48" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>How to verify: click Source (E) → open page → copy Verbatim from I/J/K → Ctrl+F → paste. Converse fixes: rev −2% (was +10%); S&amp;M growth 0% (was Fed +2%); S&amp;M $414.1; 70/30 mix; cuts 18%/18%; AI $24.5m via 18%×1,513; CapEx/WC cuts → 0.</t>
+          <t>How to verify: click Source (E) → open page → copy Verbatim from I/J/K → Ctrl+F → paste. Overpessimism fix: rev +5% (mature CAGR; FY24 −2% outlier). S&amp;M +2% Fed restored. S&amp;M $414.1; 70/30; cuts 18%/18%; AI $24.5m; CapEx/WC cuts 0.</t>
         </is>
       </c>
     </row>
@@ -5515,20 +5515,20 @@
         </is>
       </c>
       <c r="C5" s="666" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D5" s="667" t="inlineStr">
         <is>
-          <t>Was +10% with no page printing +10%. ZoomInfo FY24 results print a 2% revenue decline, so the driver is now −2% to match that source.</t>
+          <t>FY24 −2% was the only revenue decline in CY2019–CY2025 (outlier). FY25 recovered +3% ($1,249.5m). Mature CAGR CY2022 $1,098m → CY2025 $1,249.5m ≈ 4.4%, rounded to 5% forward.</t>
         </is>
       </c>
       <c r="E5" s="668">
-        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results","IN EQ: C5=−2% = ZI FY24 GAAP revenue decrease of 2% YoY")</f>
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm","IN EQ: C5=+5% ≈ mature CAGR CY2022→CY2025 (~4.4%). FY24 −2% = outlier; FY25 +3% recovery.")</f>
         <v/>
       </c>
       <c r="F5" s="664" t="inlineStr">
         <is>
-          <t>ZoomInfo says FY24 GAAP revenue fell 2% YoY. We use that −2% as the revenue growth driver.</t>
+          <t>FY24 −2% was an outlier (only decline). FY25 rose 3% to $1,249.5m. CAGR 2022–2025 ≈4.4%; we use 5% forward.</t>
         </is>
       </c>
       <c r="G5" s="664" t="inlineStr">
@@ -5537,22 +5537,22 @@
         </is>
       </c>
       <c r="H5" s="668">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","SEC 10-K same FY24 revenue")</f>
+        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results","FY24 −2% outlier: decrease of 2% YoY")</f>
         <v/>
       </c>
       <c r="I5" s="669" t="inlineStr">
         <is>
-          <t>Ctrl+F: a decrease of 2% year-over-year</t>
+          <t>Ctrl+F: increase of $35.2 million, or 3%</t>
         </is>
       </c>
       <c r="J5" s="669" t="inlineStr">
         <is>
-          <t>Ctrl+F: GAAP Revenue of $1,214.3 million</t>
+          <t>Ctrl+F: revenue of $1,249.5 million</t>
         </is>
       </c>
       <c r="K5" s="669" t="inlineStr">
         <is>
-          <t>Ctrl+F: We generated revenue of $1,214.3 million</t>
+          <t>Ctrl+F: a decrease of 2% year-over-year (FY24 outlier)</t>
         </is>
       </c>
     </row>
@@ -5762,21 +5762,20 @@
         </is>
       </c>
       <c r="C10" s="666" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D10" s="667" t="inlineStr">
         <is>
-          <t>Was Fed +2% expense inflation, which contradicted sourced revenue −2%. After the Y1 cut, AI holds S&amp;M dollars flat (no headcount adds).</t>
-        </is>
-      </c>
-      <c r="E10" s="671" t="inlineStr">
-        <is>
-          <t>C10=0% S&amp;M growth Y2+ — Fed +2% removed (contradicted rev −2%). Flat after Y1 cut.</t>
-        </is>
+          <t>After the Y1 headcount cut, AI keeps S&amp;M growing only at ~inflation (2%), not with revenue. Restored now that forward revenue is positive again.</t>
+        </is>
+      </c>
+      <c r="E10" s="668">
+        <f>HYPERLINK("https://www.federalreserve.gov/faqs/economy_14400.htm","IN EQ: C10=2% = Fed longer-run inflation goal of 2 percent")</f>
+        <v/>
       </c>
       <c r="F10" s="664" t="inlineStr">
         <is>
-          <t>No source supports growing S&amp;M while revenue falls 2%. After the Y1 cut, we hold S&amp;M flat at 0% growth.</t>
+          <t>The Fed says longer-run inflation is 2%. We use that 2% to grow S&amp;M costs after Year 1.</t>
         </is>
       </c>
       <c r="G10" s="664" t="inlineStr">
@@ -5791,13 +5790,13 @@
       </c>
       <c r="I10" s="671" t="inlineStr">
         <is>
-          <t>0% S&amp;M growth Y2+: prior Fed +2% removed as contradictory</t>
+          <t>Ctrl+F: inflation of 2 percent over the longer run</t>
         </is>
       </c>
       <c r="J10" s="651" t="n"/>
       <c r="K10" s="672" t="inlineStr">
         <is>
-          <t>See row 5: revenue −2% from ZoomInfo</t>
+          <t>Valid with +5% revenue (row 5); not used when rev was −2%</t>
         </is>
       </c>
     </row>
@@ -12623,7 +12622,7 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>Y2–Y5: S&amp;M held flat at 0%/yr after Y1 cut (AI scales without headcount; no Fed +2% vs −2% rev)</t>
+          <t>Y2–Y5: S&amp;M grows only 2%/yr after Y1 cut (AI scales without headcount; Fed inflation)</t>
         </is>
       </c>
     </row>
@@ -12675,13 +12674,13 @@
         </is>
       </c>
       <c r="C31" s="624" t="n">
-        <v>0.1174882648439431</v>
+        <v>0.117488264843943</v>
       </c>
       <c r="D31" s="624" t="n">
-        <v>0.1463334408379282</v>
+        <v>0.1814964828611728</v>
       </c>
       <c r="E31" s="624" t="n">
-        <v>0.02884517599398503</v>
+        <v>0.06400821801722981</v>
       </c>
       <c r="F31" s="625" t="inlineStr">
         <is>
@@ -12696,13 +12695,13 @@
         </is>
       </c>
       <c r="C32" s="626" t="n">
-        <v>-332.9819649180587</v>
+        <v>-332.9819649180596</v>
       </c>
       <c r="D32" s="626" t="n">
-        <v>-44.53020497820842</v>
+        <v>307.1002152542385</v>
       </c>
       <c r="E32" s="626" t="n">
-        <v>288.4517599398503</v>
+        <v>640.0821801722981</v>
       </c>
       <c r="F32" s="625" t="inlineStr">
         <is>
@@ -12717,13 +12716,13 @@
         </is>
       </c>
       <c r="C33" s="626" t="n">
-        <v>128.9587643962689</v>
+        <v>182.0819853956252</v>
       </c>
       <c r="D33" s="626" t="n">
-        <v>139.2103663511489</v>
+        <v>318.5373513129553</v>
       </c>
       <c r="E33" s="626" t="n">
-        <v>10.25160195488002</v>
+        <v>136.45536591733</v>
       </c>
       <c r="F33" s="625" t="inlineStr">
         <is>
@@ -12738,13 +12737,13 @@
         </is>
       </c>
       <c r="C34" s="626" t="n">
-        <v>1663.568060711868</v>
+        <v>2348.857611603566</v>
       </c>
       <c r="D34" s="626" t="n">
-        <v>1795.813725929821</v>
+        <v>4109.131831937123</v>
       </c>
       <c r="E34" s="626" t="n">
-        <v>132.2456652179521</v>
+        <v>1760.274220333557</v>
       </c>
       <c r="F34" s="625" t="inlineStr">
         <is>
@@ -12759,17 +12758,17 @@
         </is>
       </c>
       <c r="C35" s="626" t="n">
-        <v>714.8120820308267</v>
+        <v>574.8877051518325</v>
       </c>
       <c r="D35" s="626" t="n">
-        <v>572.4246974503579</v>
+        <v>112.7770612693652</v>
       </c>
       <c r="E35" s="626" t="n">
-        <v>-142.3873845804687</v>
+        <v>-462.1106438824673</v>
       </c>
       <c r="F35" s="625" t="inlineStr">
         <is>
-          <t>Remaining debt at exit; AI case $572.4m vs Base $714.8m.</t>
+          <t>Remaining debt at exit; AI case $112.8m vs Base $574.9m.</t>
         </is>
       </c>
     </row>
@@ -12780,17 +12779,17 @@
         </is>
       </c>
       <c r="C36" s="626" t="n">
-        <v>948.7559786810417</v>
+        <v>1773.969906451733</v>
       </c>
       <c r="D36" s="626" t="n">
-        <v>1223.389028479462</v>
+        <v>3996.354770667758</v>
       </c>
       <c r="E36" s="626" t="n">
-        <v>274.6330497984208</v>
+        <v>2222.384864216025</v>
       </c>
       <c r="F36" s="625" t="inlineStr">
         <is>
-          <t>Total equity payout; AI strategy changed final payout by $274.6m to $1,223.4m (exit 12.9x).</t>
+          <t>Total equity payout; AI strategy changed final payout by $2,222.4m to $3,996.4m (exit 12.9x).</t>
         </is>
       </c>
     </row>
@@ -12801,17 +12800,17 @@
         </is>
       </c>
       <c r="C37" s="627" t="n">
-        <v>0.5070065498600007</v>
+        <v>0.9479933534394431</v>
       </c>
       <c r="D37" s="627" t="n">
-        <v>0.6537679491919968</v>
+        <v>2.135615574311956</v>
       </c>
       <c r="E37" s="627" t="n">
-        <v>0.1467613993319961</v>
+        <v>1.187622220872513</v>
       </c>
       <c r="F37" s="625" t="inlineStr">
         <is>
-          <t>Multiple on Invested Capital; AI improved gross cash return from 0.51x to 0.65x.</t>
+          <t>Multiple on Invested Capital; AI improved gross cash return from 0.95x to 2.14x.</t>
         </is>
       </c>
     </row>
@@ -12822,17 +12821,17 @@
         </is>
       </c>
       <c r="C38" s="624" t="n">
-        <v>-0.1270231762544919</v>
+        <v>-0.01062471232081792</v>
       </c>
       <c r="D38" s="624" t="n">
-        <v>-0.08148823147841401</v>
+        <v>0.1638703804018492</v>
       </c>
       <c r="E38" s="624" t="n">
-        <v>0.04553494477607785</v>
+        <v>0.1744950927226671</v>
       </c>
       <c r="F38" s="625" t="inlineStr">
         <is>
-          <t>5-year IRR; AI boosted return by 4.6 percentage points to -8.1% (AI infra $24.5m; payroll/commission cut 18%; rev -2%; exit 12.9x).</t>
+          <t>5-year IRR; AI boosted return by 17.4 percentage points to 16.4% (AI infra $24.5m; payroll/commission cut 18%; rev 5%; exit 12.9x).</t>
         </is>
       </c>
     </row>
@@ -12853,14 +12852,14 @@
     <row r="41">
       <c r="B41" s="569" t="inlineStr">
         <is>
-          <t>AI case IRR -8.1% − Base IRR -12.7% = 4.6 percentage points of IRR</t>
+          <t>AI case IRR 16.4% − Base IRR -1.1% = 17.4 percentage points of IRR</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="569" t="inlineStr">
         <is>
-          <t>Y2 AI EBITDA margin 14.6% vs FY24 baseline 15.1% = -45 bps (target ≥500: NO)</t>
+          <t>Y2 AI EBITDA margin 18.1% vs FY24 baseline 15.1% = 307 bps (target ≥500: NO)</t>
         </is>
       </c>
     </row>
@@ -13105,7 +13104,7 @@
       </c>
       <c r="D7" s="571" t="inlineStr">
         <is>
-          <t>-2% per year (unchanged by AI)</t>
+          <t>5% per year (unchanged by AI)</t>
         </is>
       </c>
       <c r="E7" s="571" t="inlineStr">
@@ -13430,7 +13429,7 @@
       </c>
       <c r="D12" s="571" t="inlineStr">
         <is>
-          <t>0% per year from Year 2</t>
+          <t>2% per year from Year 2</t>
         </is>
       </c>
       <c r="E12" s="571" t="inlineStr">
@@ -14318,7 +14317,7 @@
     <row r="30">
       <c r="B30" s="590" t="inlineStr">
         <is>
-          <t>This list must match Assumptions_Drivers: rev -2%, payroll/commission cut −18%, AI $24.5m, S&amp;M $414.1m, exit 12.9x, CapEx/WC cuts 0% (unsourced removed).</t>
+          <t>This list must match Assumptions_Drivers: rev 5%, payroll/commission cut −18%, AI $24.5m, S&amp;M $414.1m, exit 12.9x, CapEx/WC cuts 0% (unsourced removed).</t>
         </is>
       </c>
     </row>
@@ -14505,22 +14504,22 @@
         <v>2025</v>
       </c>
       <c r="C5" s="626" t="n">
-        <v>75.80021219999996</v>
+        <v>106.1491420000001</v>
       </c>
       <c r="D5" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E5" s="626" t="n">
-        <v>75.80021219999996</v>
+        <v>106.1491420000001</v>
       </c>
       <c r="F5" s="626" t="n">
-        <v>839.6997878000001</v>
+        <v>809.3508579999999</v>
       </c>
       <c r="G5" s="626" t="n">
-        <v>877.3051</v>
+        <v>869.0184999999998</v>
       </c>
       <c r="H5" s="626" t="n">
-        <v>37.60531219999996</v>
+        <v>59.66764199999989</v>
       </c>
     </row>
     <row r="6">
@@ -14528,22 +14527,22 @@
         <v>2026</v>
       </c>
       <c r="C6" s="626" t="n">
-        <v>72.27273176995408</v>
+        <v>130.5059589909402</v>
       </c>
       <c r="D6" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E6" s="626" t="n">
-        <v>72.27273176995408</v>
+        <v>130.5059589909402</v>
       </c>
       <c r="F6" s="626" t="n">
-        <v>767.4270560300459</v>
+        <v>678.8448990090596</v>
       </c>
       <c r="G6" s="626" t="n">
-        <v>838.2602713</v>
+        <v>812.4640854999998</v>
       </c>
       <c r="H6" s="626" t="n">
-        <v>70.83321526995405</v>
+        <v>133.6191864909401</v>
       </c>
     </row>
     <row r="7">
@@ -14551,22 +14550,22 @@
         <v>2027</v>
       </c>
       <c r="C7" s="626" t="n">
-        <v>68.68390845498992</v>
+        <v>157.4906357474761</v>
       </c>
       <c r="D7" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E7" s="626" t="n">
-        <v>68.68390845498992</v>
+        <v>157.4906357474761</v>
       </c>
       <c r="F7" s="626" t="n">
-        <v>698.743147575056</v>
+        <v>521.3542632615836</v>
       </c>
       <c r="G7" s="626" t="n">
-        <v>798.2485648578999</v>
+        <v>744.6899570964996</v>
       </c>
       <c r="H7" s="626" t="n">
-        <v>99.50541728284384</v>
+        <v>223.335693834916</v>
       </c>
     </row>
     <row r="8">
@@ -14574,22 +14573,22 @@
         <v>2028</v>
       </c>
       <c r="C8" s="626" t="n">
-        <v>65.02632092200611</v>
+        <v>187.3302392459731</v>
       </c>
       <c r="D8" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E8" s="626" t="n">
-        <v>65.02632092200611</v>
+        <v>187.3302392459731</v>
       </c>
       <c r="F8" s="626" t="n">
-        <v>633.7168266530499</v>
+        <v>334.0240240156105</v>
       </c>
       <c r="G8" s="626" t="n">
-        <v>757.1442529603054</v>
+        <v>665.6150688061919</v>
       </c>
       <c r="H8" s="626" t="n">
-        <v>123.4274263072555</v>
+        <v>331.5910447905814</v>
       </c>
     </row>
     <row r="9">
@@ -14597,22 +14596,22 @@
         <v>2029</v>
       </c>
       <c r="C9" s="626" t="n">
-        <v>61.29212920269194</v>
+        <v>221.2469627462453</v>
       </c>
       <c r="D9" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E9" s="626" t="n">
-        <v>61.29212920269194</v>
+        <v>221.2469627462453</v>
       </c>
       <c r="F9" s="626" t="n">
-        <v>572.4246974503579</v>
+        <v>112.7770612693652</v>
       </c>
       <c r="G9" s="626" t="n">
-        <v>714.8120820308267</v>
+        <v>574.8877051518325</v>
       </c>
       <c r="H9" s="626" t="n">
-        <v>142.3873845804687</v>
+        <v>462.1106438824673</v>
       </c>
     </row>
     <row r="11">
@@ -14729,19 +14728,19 @@
         <v>1214.3</v>
       </c>
       <c r="D5" s="626" t="n">
-        <v>1190.014</v>
+        <v>1275.015</v>
       </c>
       <c r="E5" s="626" t="n">
-        <v>1166.21372</v>
+        <v>1338.76575</v>
       </c>
       <c r="F5" s="626" t="n">
-        <v>1142.8894456</v>
+        <v>1405.7040375</v>
       </c>
       <c r="G5" s="626" t="n">
-        <v>1120.031656688</v>
+        <v>1475.989239375</v>
       </c>
       <c r="H5" s="626" t="n">
-        <v>1097.63102355424</v>
+        <v>1549.788701343751</v>
       </c>
     </row>
     <row r="6">
@@ -14754,19 +14753,19 @@
         <v>242.8599999999999</v>
       </c>
       <c r="D6" s="626" t="n">
-        <v>238.0027999999999</v>
+        <v>255.003</v>
       </c>
       <c r="E6" s="626" t="n">
-        <v>233.2427439999999</v>
+        <v>267.75315</v>
       </c>
       <c r="F6" s="626" t="n">
-        <v>228.57788912</v>
+        <v>281.1408075</v>
       </c>
       <c r="G6" s="626" t="n">
-        <v>224.0063313376</v>
+        <v>295.197847875</v>
       </c>
       <c r="H6" s="626" t="n">
-        <v>219.526204710848</v>
+        <v>309.9577402687501</v>
       </c>
     </row>
     <row r="7">
@@ -14779,19 +14778,19 @@
         <v>289.9</v>
       </c>
       <c r="D7" s="626" t="n">
-        <v>284.102</v>
+        <v>304.395</v>
       </c>
       <c r="E7" s="626" t="n">
-        <v>278.41996</v>
+        <v>319.6147500000001</v>
       </c>
       <c r="F7" s="626" t="n">
-        <v>272.8515608</v>
+        <v>335.5954875000001</v>
       </c>
       <c r="G7" s="626" t="n">
-        <v>267.394529584</v>
+        <v>352.3752618750001</v>
       </c>
       <c r="H7" s="626" t="n">
-        <v>262.04663899232</v>
+        <v>369.9940249687501</v>
       </c>
     </row>
     <row r="8">
@@ -14804,19 +14803,19 @@
         <v>124.2</v>
       </c>
       <c r="D8" s="626" t="n">
-        <v>121.716</v>
+        <v>130.41</v>
       </c>
       <c r="E8" s="626" t="n">
-        <v>119.28168</v>
+        <v>136.9305</v>
       </c>
       <c r="F8" s="626" t="n">
-        <v>116.8960464</v>
+        <v>143.777025</v>
       </c>
       <c r="G8" s="626" t="n">
-        <v>114.558125472</v>
+        <v>150.96587625</v>
       </c>
       <c r="H8" s="626" t="n">
-        <v>112.26696296256</v>
+        <v>158.5141700625001</v>
       </c>
     </row>
     <row r="9">
@@ -14829,19 +14828,19 @@
         <v>414.1</v>
       </c>
       <c r="D9" s="626" t="n">
-        <v>405.818</v>
+        <v>434.8050000000001</v>
       </c>
       <c r="E9" s="626" t="n">
-        <v>397.70164</v>
+        <v>456.5452500000001</v>
       </c>
       <c r="F9" s="626" t="n">
-        <v>389.7476072</v>
+        <v>479.3725125000001</v>
       </c>
       <c r="G9" s="626" t="n">
-        <v>381.952655056</v>
+        <v>503.3411381250002</v>
       </c>
       <c r="H9" s="626" t="n">
-        <v>374.31360195488</v>
+        <v>528.5081950312501</v>
       </c>
     </row>
     <row r="10">
@@ -14879,19 +14878,19 @@
         <v>196.1</v>
       </c>
       <c r="D11" s="626" t="n">
-        <v>192.178</v>
+        <v>205.905</v>
       </c>
       <c r="E11" s="626" t="n">
-        <v>188.33444</v>
+        <v>216.20025</v>
       </c>
       <c r="F11" s="626" t="n">
-        <v>184.5677512</v>
+        <v>227.0102625</v>
       </c>
       <c r="G11" s="626" t="n">
-        <v>180.876396176</v>
+        <v>238.360775625</v>
       </c>
       <c r="H11" s="626" t="n">
-        <v>177.25886825248</v>
+        <v>250.2788144062501</v>
       </c>
     </row>
     <row r="12">
@@ -14904,19 +14903,19 @@
         <v>218.574</v>
       </c>
       <c r="D12" s="626" t="n">
-        <v>214.20252</v>
+        <v>229.5027</v>
       </c>
       <c r="E12" s="626" t="n">
-        <v>209.9184696</v>
+        <v>240.977835</v>
       </c>
       <c r="F12" s="626" t="n">
-        <v>205.720100208</v>
+        <v>253.0267267500001</v>
       </c>
       <c r="G12" s="626" t="n">
-        <v>201.60569820384</v>
+        <v>265.6780630875</v>
       </c>
       <c r="H12" s="626" t="n">
-        <v>197.5735842397632</v>
+        <v>278.9619662418751</v>
       </c>
     </row>
     <row r="13">
@@ -14929,19 +14928,19 @@
         <v>183.1</v>
       </c>
       <c r="D13" s="626" t="n">
-        <v>139.81268</v>
+        <v>149.7993000000001</v>
       </c>
       <c r="E13" s="626" t="n">
-        <v>137.0164264000001</v>
+        <v>157.2892650000001</v>
       </c>
       <c r="F13" s="626" t="n">
-        <v>134.2760978720001</v>
+        <v>165.1537282500002</v>
       </c>
       <c r="G13" s="626" t="n">
-        <v>131.5905759145601</v>
+        <v>173.4114146625001</v>
       </c>
       <c r="H13" s="626" t="n">
-        <v>128.9587643962689</v>
+        <v>182.0819853956252</v>
       </c>
     </row>
     <row r="14">
@@ -14954,10 +14953,10 @@
         <v>0.150786461335749</v>
       </c>
       <c r="D14" s="624" t="n">
+        <v>0.1174882648439431</v>
+      </c>
+      <c r="E14" s="624" t="n">
         <v>0.117488264843943</v>
-      </c>
-      <c r="E14" s="624" t="n">
-        <v>0.1174882648439431</v>
       </c>
       <c r="F14" s="624" t="n">
         <v>0.1174882648439431</v>
@@ -14979,19 +14978,19 @@
         <v>85.7</v>
       </c>
       <c r="D15" s="626" t="n">
-        <v>83.98599999999999</v>
+        <v>89.985</v>
       </c>
       <c r="E15" s="626" t="n">
-        <v>82.30628</v>
+        <v>94.48425000000002</v>
       </c>
       <c r="F15" s="626" t="n">
-        <v>80.6601544</v>
+        <v>99.20846250000002</v>
       </c>
       <c r="G15" s="626" t="n">
-        <v>79.046951312</v>
+        <v>104.168885625</v>
       </c>
       <c r="H15" s="626" t="n">
-        <v>77.46601228576</v>
+        <v>109.37732990625</v>
       </c>
     </row>
     <row r="16">
@@ -15004,19 +15003,19 @@
         <v>97.40000000000001</v>
       </c>
       <c r="D16" s="626" t="n">
-        <v>55.82667999999998</v>
+        <v>59.81430000000013</v>
       </c>
       <c r="E16" s="626" t="n">
-        <v>54.71014640000011</v>
+        <v>62.80501500000004</v>
       </c>
       <c r="F16" s="626" t="n">
-        <v>53.61594347200013</v>
+        <v>65.9452657500002</v>
       </c>
       <c r="G16" s="626" t="n">
-        <v>52.54362460256013</v>
+        <v>69.24252903750012</v>
       </c>
       <c r="H16" s="626" t="n">
-        <v>51.49275211050886</v>
+        <v>72.70465548937518</v>
       </c>
     </row>
     <row r="17">
@@ -15029,16 +15028,16 @@
         <v>77.8175</v>
       </c>
       <c r="E17" s="626" t="n">
-        <v>74.6473233</v>
+        <v>73.95953549999999</v>
       </c>
       <c r="F17" s="626" t="n">
-        <v>71.4066025179</v>
+        <v>69.26551909649999</v>
       </c>
       <c r="G17" s="626" t="n">
-        <v>68.08563088320568</v>
+        <v>63.64026643900946</v>
       </c>
       <c r="H17" s="626" t="n">
-        <v>64.67397299570534</v>
+        <v>57.07705071091392</v>
       </c>
     </row>
     <row r="18">
@@ -15048,19 +15047,19 @@
         </is>
       </c>
       <c r="D18" s="626" t="n">
-        <v>-21.99082000000001</v>
+        <v>-18.00319999999986</v>
       </c>
       <c r="E18" s="626" t="n">
-        <v>-19.93717689999988</v>
+        <v>-11.15452049999995</v>
       </c>
       <c r="F18" s="626" t="n">
-        <v>-17.79065904589987</v>
+        <v>-3.320253346499783</v>
       </c>
       <c r="G18" s="626" t="n">
-        <v>-15.54200628064555</v>
+        <v>4.425787452807622</v>
       </c>
       <c r="H18" s="626" t="n">
-        <v>-13.18122088519648</v>
+        <v>12.3458077749844</v>
       </c>
     </row>
     <row r="19">
@@ -15070,19 +15069,19 @@
         </is>
       </c>
       <c r="D19" s="626" t="n">
-        <v>23.80028</v>
+        <v>25.5003</v>
       </c>
       <c r="E19" s="626" t="n">
-        <v>23.3242744</v>
+        <v>26.77531500000001</v>
       </c>
       <c r="F19" s="626" t="n">
-        <v>22.857788912</v>
+        <v>28.11408075000001</v>
       </c>
       <c r="G19" s="626" t="n">
-        <v>22.40063313376</v>
+        <v>29.51978478750001</v>
       </c>
       <c r="H19" s="626" t="n">
-        <v>21.9526204710848</v>
+        <v>30.99577402687501</v>
       </c>
     </row>
     <row r="20">
@@ -15092,19 +15091,19 @@
         </is>
       </c>
       <c r="D20" s="626" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E20" s="626" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F20" s="626" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G20" s="626" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H20" s="626" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -15114,19 +15113,19 @@
         </is>
       </c>
       <c r="D21" s="626" t="n">
-        <v>38.19489999999998</v>
+        <v>46.48150000000013</v>
       </c>
       <c r="E21" s="626" t="n">
-        <v>39.04482870000012</v>
+        <v>56.55441450000006</v>
       </c>
       <c r="F21" s="626" t="n">
-        <v>40.01170644210012</v>
+        <v>67.77412840350024</v>
       </c>
       <c r="G21" s="626" t="n">
-        <v>41.10431189759445</v>
+        <v>79.07488829030763</v>
       </c>
       <c r="H21" s="626" t="n">
-        <v>42.33217092947872</v>
+        <v>90.72736365435942</v>
       </c>
     </row>
     <row r="22">
@@ -15158,19 +15157,19 @@
         </is>
       </c>
       <c r="D23" s="626" t="n">
-        <v>38.19489999999998</v>
+        <v>46.48150000000013</v>
       </c>
       <c r="E23" s="626" t="n">
-        <v>39.04482870000012</v>
+        <v>56.55441450000006</v>
       </c>
       <c r="F23" s="626" t="n">
-        <v>40.01170644210012</v>
+        <v>67.77412840350024</v>
       </c>
       <c r="G23" s="626" t="n">
-        <v>41.10431189759445</v>
+        <v>79.07488829030763</v>
       </c>
       <c r="H23" s="626" t="n">
-        <v>42.33217092947872</v>
+        <v>90.72736365435942</v>
       </c>
     </row>
     <row r="24">
@@ -15183,19 +15182,19 @@
         <v>1329.9</v>
       </c>
       <c r="D24" s="626" t="n">
-        <v>877.3051</v>
+        <v>869.0184999999998</v>
       </c>
       <c r="E24" s="626" t="n">
-        <v>838.2602713</v>
+        <v>812.4640854999998</v>
       </c>
       <c r="F24" s="626" t="n">
-        <v>798.2485648578999</v>
+        <v>744.6899570964996</v>
       </c>
       <c r="G24" s="626" t="n">
-        <v>757.1442529603054</v>
+        <v>665.6150688061919</v>
       </c>
       <c r="H24" s="626" t="n">
-        <v>714.8120820308267</v>
+        <v>574.8877051518325</v>
       </c>
     </row>
   </sheetData>
@@ -15283,19 +15282,19 @@
         <v>1214.3</v>
       </c>
       <c r="D5" s="626" t="n">
-        <v>1190.014</v>
+        <v>1275.015</v>
       </c>
       <c r="E5" s="626" t="n">
-        <v>1166.21372</v>
+        <v>1338.76575</v>
       </c>
       <c r="F5" s="626" t="n">
-        <v>1142.8894456</v>
+        <v>1405.7040375</v>
       </c>
       <c r="G5" s="626" t="n">
-        <v>1120.031656688</v>
+        <v>1475.989239375</v>
       </c>
       <c r="H5" s="626" t="n">
-        <v>1097.63102355424</v>
+        <v>1549.788701343751</v>
       </c>
     </row>
     <row r="6">
@@ -15308,19 +15307,19 @@
         <v>242.8599999999999</v>
       </c>
       <c r="D6" s="626" t="n">
-        <v>238.0027999999999</v>
+        <v>255.003</v>
       </c>
       <c r="E6" s="626" t="n">
-        <v>233.2427439999999</v>
+        <v>267.75315</v>
       </c>
       <c r="F6" s="626" t="n">
-        <v>228.57788912</v>
+        <v>281.1408075</v>
       </c>
       <c r="G6" s="626" t="n">
-        <v>224.0063313376</v>
+        <v>295.197847875</v>
       </c>
       <c r="H6" s="626" t="n">
-        <v>219.526204710848</v>
+        <v>309.9577402687501</v>
       </c>
     </row>
     <row r="7">
@@ -15336,16 +15335,16 @@
         <v>237.718</v>
       </c>
       <c r="E7" s="626" t="n">
-        <v>237.718</v>
+        <v>242.47236</v>
       </c>
       <c r="F7" s="626" t="n">
-        <v>237.718</v>
+        <v>247.3218072</v>
       </c>
       <c r="G7" s="626" t="n">
-        <v>237.718</v>
+        <v>252.268243344</v>
       </c>
       <c r="H7" s="626" t="n">
-        <v>237.718</v>
+        <v>257.31360821088</v>
       </c>
     </row>
     <row r="8">
@@ -15361,16 +15360,16 @@
         <v>101.844</v>
       </c>
       <c r="E8" s="626" t="n">
-        <v>101.844</v>
+        <v>103.88088</v>
       </c>
       <c r="F8" s="626" t="n">
-        <v>101.844</v>
+        <v>105.9584976</v>
       </c>
       <c r="G8" s="626" t="n">
-        <v>101.844</v>
+        <v>108.077667552</v>
       </c>
       <c r="H8" s="626" t="n">
-        <v>101.844</v>
+        <v>110.23922090304</v>
       </c>
     </row>
     <row r="9">
@@ -15386,16 +15385,16 @@
         <v>339.562</v>
       </c>
       <c r="E9" s="626" t="n">
-        <v>339.562</v>
+        <v>346.35324</v>
       </c>
       <c r="F9" s="626" t="n">
-        <v>339.562</v>
+        <v>353.2803048</v>
       </c>
       <c r="G9" s="626" t="n">
-        <v>339.562</v>
+        <v>360.345910896</v>
       </c>
       <c r="H9" s="626" t="n">
-        <v>339.562</v>
+        <v>367.55282911392</v>
       </c>
     </row>
     <row r="10">
@@ -15433,19 +15432,19 @@
         <v>196.1</v>
       </c>
       <c r="D11" s="626" t="n">
-        <v>192.178</v>
+        <v>205.905</v>
       </c>
       <c r="E11" s="626" t="n">
-        <v>188.33444</v>
+        <v>216.20025</v>
       </c>
       <c r="F11" s="626" t="n">
-        <v>184.5677512</v>
+        <v>227.0102625</v>
       </c>
       <c r="G11" s="626" t="n">
-        <v>180.876396176</v>
+        <v>238.360775625</v>
       </c>
       <c r="H11" s="626" t="n">
-        <v>177.25886825248</v>
+        <v>250.2788144062501</v>
       </c>
     </row>
     <row r="12">
@@ -15458,19 +15457,19 @@
         <v>218.574</v>
       </c>
       <c r="D12" s="626" t="n">
-        <v>214.20252</v>
+        <v>229.5027</v>
       </c>
       <c r="E12" s="626" t="n">
-        <v>209.9184696</v>
+        <v>240.977835</v>
       </c>
       <c r="F12" s="626" t="n">
-        <v>205.720100208</v>
+        <v>253.0267267500001</v>
       </c>
       <c r="G12" s="626" t="n">
-        <v>201.60569820384</v>
+        <v>265.6780630875</v>
       </c>
       <c r="H12" s="626" t="n">
-        <v>197.5735842397632</v>
+        <v>278.9619662418751</v>
       </c>
     </row>
     <row r="13">
@@ -15483,19 +15482,19 @@
         <v>183.1</v>
       </c>
       <c r="D13" s="626" t="n">
-        <v>181.5686799999999</v>
+        <v>220.5423000000002</v>
       </c>
       <c r="E13" s="626" t="n">
-        <v>170.6560664000001</v>
+        <v>242.9812750000003</v>
       </c>
       <c r="F13" s="626" t="n">
-        <v>159.9617050720001</v>
+        <v>266.7459359500002</v>
       </c>
       <c r="G13" s="626" t="n">
-        <v>149.4812309705601</v>
+        <v>291.9066418915002</v>
       </c>
       <c r="H13" s="626" t="n">
-        <v>139.2103663511489</v>
+        <v>318.5373513129553</v>
       </c>
     </row>
     <row r="14">
@@ -15508,19 +15507,19 @@
         <v>0.150786461335749</v>
       </c>
       <c r="D14" s="624" t="n">
-        <v>0.1525769276663972</v>
+        <v>0.1729723179727299</v>
       </c>
       <c r="E14" s="624" t="n">
-        <v>0.1463334408379282</v>
+        <v>0.1814964828611728</v>
       </c>
       <c r="F14" s="624" t="n">
-        <v>0.1399625359109188</v>
+        <v>0.1897596711925217</v>
       </c>
       <c r="G14" s="624" t="n">
-        <v>0.1334616125160114</v>
+        <v>0.1977701693916864</v>
       </c>
       <c r="H14" s="624" t="n">
-        <v>0.1268280172150853</v>
+        <v>0.2055359876070629</v>
       </c>
     </row>
     <row r="15">
@@ -15533,19 +15532,19 @@
         <v>85.7</v>
       </c>
       <c r="D15" s="626" t="n">
-        <v>83.98599999999999</v>
+        <v>89.985</v>
       </c>
       <c r="E15" s="626" t="n">
-        <v>82.30628</v>
+        <v>94.48425000000002</v>
       </c>
       <c r="F15" s="626" t="n">
-        <v>80.6601544</v>
+        <v>99.20846250000002</v>
       </c>
       <c r="G15" s="626" t="n">
-        <v>79.046951312</v>
+        <v>104.168885625</v>
       </c>
       <c r="H15" s="626" t="n">
-        <v>77.46601228576</v>
+        <v>109.37732990625</v>
       </c>
     </row>
     <row r="16">
@@ -15558,19 +15557,19 @@
         <v>97.40000000000001</v>
       </c>
       <c r="D16" s="626" t="n">
-        <v>97.58267999999995</v>
+        <v>130.5573000000002</v>
       </c>
       <c r="E16" s="626" t="n">
-        <v>88.3497864000001</v>
+        <v>148.4970250000002</v>
       </c>
       <c r="F16" s="626" t="n">
-        <v>79.30155067200006</v>
+        <v>167.5374734500002</v>
       </c>
       <c r="G16" s="626" t="n">
-        <v>70.43427965856014</v>
+        <v>187.7377562665001</v>
       </c>
       <c r="H16" s="626" t="n">
-        <v>61.74435406538888</v>
+        <v>209.1600214067052</v>
       </c>
     </row>
     <row r="17">
@@ -15583,16 +15582,16 @@
         <v>77.8175</v>
       </c>
       <c r="E17" s="626" t="n">
-        <v>71.5260823874</v>
+        <v>69.00712121399999</v>
       </c>
       <c r="F17" s="626" t="n">
-        <v>65.52744565049382</v>
+        <v>58.17512661775195</v>
       </c>
       <c r="G17" s="626" t="n">
-        <v>59.82668124872964</v>
+        <v>45.10340385071143</v>
       </c>
       <c r="H17" s="626" t="n">
-        <v>54.42949661220314</v>
+        <v>28.31773423345177</v>
       </c>
     </row>
     <row r="18">
@@ -15602,19 +15601,19 @@
         </is>
       </c>
       <c r="D18" s="626" t="n">
-        <v>15.61449219999997</v>
+        <v>41.66444200000014</v>
       </c>
       <c r="E18" s="626" t="n">
-        <v>13.29072616995408</v>
+        <v>62.79702399094019</v>
       </c>
       <c r="F18" s="626" t="n">
-        <v>10.88154296698993</v>
+        <v>86.39625399747612</v>
       </c>
       <c r="G18" s="626" t="n">
-        <v>8.380002743766095</v>
+        <v>112.6811384084731</v>
       </c>
       <c r="H18" s="626" t="n">
-        <v>5.778737388016733</v>
+        <v>142.8654068668702</v>
       </c>
     </row>
     <row r="19">
@@ -15624,19 +15623,19 @@
         </is>
       </c>
       <c r="D19" s="626" t="n">
-        <v>23.80028</v>
+        <v>25.5003</v>
       </c>
       <c r="E19" s="626" t="n">
-        <v>23.3242744</v>
+        <v>26.77531500000001</v>
       </c>
       <c r="F19" s="626" t="n">
-        <v>22.857788912</v>
+        <v>28.11408075000001</v>
       </c>
       <c r="G19" s="626" t="n">
-        <v>22.40063313376</v>
+        <v>29.51978478750001</v>
       </c>
       <c r="H19" s="626" t="n">
-        <v>21.9526204710848</v>
+        <v>30.99577402687501</v>
       </c>
     </row>
     <row r="20">
@@ -15646,19 +15645,19 @@
         </is>
       </c>
       <c r="D20" s="626" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E20" s="626" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F20" s="626" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G20" s="626" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H20" s="626" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -15668,19 +15667,19 @@
         </is>
       </c>
       <c r="D21" s="626" t="n">
-        <v>75.80021219999996</v>
+        <v>106.1491420000001</v>
       </c>
       <c r="E21" s="626" t="n">
-        <v>72.27273176995408</v>
+        <v>130.5059589909402</v>
       </c>
       <c r="F21" s="626" t="n">
-        <v>68.68390845498992</v>
+        <v>157.4906357474761</v>
       </c>
       <c r="G21" s="626" t="n">
-        <v>65.02632092200611</v>
+        <v>187.3302392459731</v>
       </c>
       <c r="H21" s="626" t="n">
-        <v>61.29212920269194</v>
+        <v>221.2469627462453</v>
       </c>
     </row>
     <row r="22">
@@ -15712,19 +15711,19 @@
         </is>
       </c>
       <c r="D23" s="626" t="n">
-        <v>75.80021219999996</v>
+        <v>106.1491420000001</v>
       </c>
       <c r="E23" s="626" t="n">
-        <v>72.27273176995408</v>
+        <v>130.5059589909402</v>
       </c>
       <c r="F23" s="626" t="n">
-        <v>68.68390845498992</v>
+        <v>157.4906357474761</v>
       </c>
       <c r="G23" s="626" t="n">
-        <v>65.02632092200611</v>
+        <v>187.3302392459731</v>
       </c>
       <c r="H23" s="626" t="n">
-        <v>61.29212920269194</v>
+        <v>221.2469627462453</v>
       </c>
     </row>
     <row r="24">
@@ -15737,19 +15736,19 @@
         <v>1329.9</v>
       </c>
       <c r="D24" s="626" t="n">
-        <v>839.6997878000001</v>
+        <v>809.3508579999999</v>
       </c>
       <c r="E24" s="626" t="n">
-        <v>767.4270560300459</v>
+        <v>678.8448990090596</v>
       </c>
       <c r="F24" s="626" t="n">
-        <v>698.743147575056</v>
+        <v>521.3542632615836</v>
       </c>
       <c r="G24" s="626" t="n">
-        <v>633.7168266530499</v>
+        <v>334.0240240156105</v>
       </c>
       <c r="H24" s="626" t="n">
-        <v>572.4246974503579</v>
+        <v>112.7770612693652</v>
       </c>
     </row>
   </sheetData>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -1989,7 +1989,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="676">
+  <cellXfs count="677">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3233,6 +3233,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="37" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5442,7 +5445,7 @@
     <row r="3" ht="48" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>How to verify: click Source (E) → open page → copy Verbatim from I/J/K → Ctrl+F → paste. Overpessimism fix: rev +5% (mature CAGR; FY24 −2% outlier). S&amp;M +2% Fed restored. S&amp;M $414.1; 70/30; cuts 18%/18%; AI $24.5m; CapEx/WC cuts 0.</t>
+          <t>How to verify: click Source (E) → open page → copy Verbatim from I/J/K → Ctrl+F → paste. Overpessimism fix: rev +5% (mature CAGR; FY24 −2% outlier). S&amp;M +2% Fed restored. S&amp;M $414.1; 70/30; cuts 18%/18%; AI $24.5m; CapEx cut 8% (HC-linked); WC 0.</t>
         </is>
       </c>
     </row>
@@ -5865,21 +5868,20 @@
         </is>
       </c>
       <c r="C12" s="666" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="D12" s="667" t="inlineStr">
         <is>
-          <t>No source printed a 5% CapEx cut, so the cut is set to 0% (no AI CapEx discount).</t>
-        </is>
-      </c>
-      <c r="E12" s="669" t="inlineStr">
-        <is>
-          <t>C12=0% CapEx cut — no source printed a cut, so none is applied.</t>
-        </is>
+          <t>SaaS CapEx is primarily laptops/office gear (SaaSDB). Replacing 18% of S&amp;M SDRs with AI removes that gear. S&amp;M is 1,513/3,508≈43% of ZI HC → CapEx cut ≈18%×43%≈8%.</t>
+        </is>
+      </c>
+      <c r="E12" s="676">
+        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/","IN EQ: C12=8% ≈ 18% SDR cut × S&amp;M 43% of HC; SaaS CapEx primarily laptops/office gear")</f>
+        <v/>
       </c>
       <c r="F12" s="664" t="inlineStr">
         <is>
-          <t>No source says a CapEx cut. The cut is 0%, so CapEx uses the base rate only.</t>
+          <t>SaaSDB says SaaS CapEx is mainly laptops and office gear. 18%×(1,513/3,508 S&amp;M share)≈8% CapEx cut when those SDRs become AI.</t>
         </is>
       </c>
       <c r="G12" s="664" t="inlineStr">
@@ -5887,14 +5889,25 @@
           <t>Go to AI_Operating!D19 (CapEx)</t>
         </is>
       </c>
-      <c r="H12" s="593" t="n"/>
+      <c r="H12" s="675">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","ZI 10-K: 1,513 S&amp;M / 3,508 employees")</f>
+        <v/>
+      </c>
       <c r="I12" s="669" t="inlineStr">
         <is>
-          <t>0% CapEx cut: no source claimed a cut</t>
-        </is>
-      </c>
-      <c r="J12" s="651" t="n"/>
-      <c r="K12" s="651" t="n"/>
+          <t>Ctrl+F: primarily laptops, office equipment</t>
+        </is>
+      </c>
+      <c r="J12" s="672" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 1,513 in sales and marketing</t>
+        </is>
+      </c>
+      <c r="K12" s="672" t="inlineStr">
+        <is>
+          <t>Ctrl+F: had 3,508 employees</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="96" customHeight="1" s="244">
       <c r="A13" s="665" t="inlineStr">
@@ -12761,14 +12774,14 @@
         <v>574.8877051518325</v>
       </c>
       <c r="D35" s="626" t="n">
-        <v>112.7770612693652</v>
+        <v>99.92925784902985</v>
       </c>
       <c r="E35" s="626" t="n">
-        <v>-462.1106438824673</v>
+        <v>-474.9584473028027</v>
       </c>
       <c r="F35" s="625" t="inlineStr">
         <is>
-          <t>Remaining debt at exit; AI case $112.8m vs Base $574.9m.</t>
+          <t>Remaining debt at exit; AI case $99.9m vs Base $574.9m.</t>
         </is>
       </c>
     </row>
@@ -12782,14 +12795,14 @@
         <v>1773.969906451733</v>
       </c>
       <c r="D36" s="626" t="n">
-        <v>3996.354770667758</v>
+        <v>4009.202574088093</v>
       </c>
       <c r="E36" s="626" t="n">
-        <v>2222.384864216025</v>
+        <v>2235.23266763636</v>
       </c>
       <c r="F36" s="625" t="inlineStr">
         <is>
-          <t>Total equity payout; AI strategy changed final payout by $2,222.4m to $3,996.4m (exit 12.9x).</t>
+          <t>Total equity payout; AI strategy changed final payout by $2,235.2m to $4,009.2m (exit 12.9x).</t>
         </is>
       </c>
     </row>
@@ -12803,10 +12816,10 @@
         <v>0.9479933534394431</v>
       </c>
       <c r="D37" s="627" t="n">
-        <v>2.135615574311956</v>
+        <v>2.142481323389478</v>
       </c>
       <c r="E37" s="627" t="n">
-        <v>1.187622220872513</v>
+        <v>1.194487969950035</v>
       </c>
       <c r="F37" s="625" t="inlineStr">
         <is>
@@ -12824,14 +12837,14 @@
         <v>-0.01062471232081792</v>
       </c>
       <c r="D38" s="624" t="n">
-        <v>0.1638703804018492</v>
+        <v>0.1646177607845645</v>
       </c>
       <c r="E38" s="624" t="n">
-        <v>0.1744950927226671</v>
+        <v>0.1752424731053824</v>
       </c>
       <c r="F38" s="625" t="inlineStr">
         <is>
-          <t>5-year IRR; AI boosted return by 17.4 percentage points to 16.4% (AI infra $24.5m; payroll/commission cut 18%; rev 5%; exit 12.9x).</t>
+          <t>5-year IRR; AI boosted return by 17.5 percentage points to 16.5% (AI infra $24.5m; payroll/commission cut 18%; rev 5%; exit 12.9x).</t>
         </is>
       </c>
     </row>
@@ -12852,7 +12865,7 @@
     <row r="41">
       <c r="B41" s="569" t="inlineStr">
         <is>
-          <t>AI case IRR 16.4% − Base IRR -1.1% = 17.4 percentage points of IRR</t>
+          <t>AI case IRR 16.5% − Base IRR -1.1% = 17.5 percentage points of IRR</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13572,7 @@
       </c>
       <c r="D14" s="571" t="inlineStr">
         <is>
-          <t>−0% vs baseline CapEx rate (no sourced cut)</t>
+          <t>−8% vs baseline CapEx (18% SDR cut × ~43% S&amp;M share of HC)</t>
         </is>
       </c>
       <c r="E14" s="571" t="inlineStr">
@@ -14317,7 +14330,7 @@
     <row r="30">
       <c r="B30" s="590" t="inlineStr">
         <is>
-          <t>This list must match Assumptions_Drivers: rev 5%, payroll/commission cut −18%, AI $24.5m, S&amp;M $414.1m, exit 12.9x, CapEx/WC cuts 0% (unsourced removed).</t>
+          <t>This list must match Assumptions_Drivers: rev 5%, payroll/commission cut −18%, AI $24.5m, S&amp;M $414.1m, exit 12.9x, CapEx cut 8% (HC-linked); WC improve/plug 0%.</t>
         </is>
       </c>
     </row>
@@ -14504,22 +14517,22 @@
         <v>2025</v>
       </c>
       <c r="C5" s="626" t="n">
-        <v>106.1491420000001</v>
+        <v>108.1891660000001</v>
       </c>
       <c r="D5" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E5" s="626" t="n">
-        <v>106.1491420000001</v>
+        <v>108.1891660000001</v>
       </c>
       <c r="F5" s="626" t="n">
-        <v>809.3508579999999</v>
+        <v>807.3108339999999</v>
       </c>
       <c r="G5" s="626" t="n">
         <v>869.0184999999998</v>
       </c>
       <c r="H5" s="626" t="n">
-        <v>59.66764199999989</v>
+        <v>61.7076659999999</v>
       </c>
     </row>
     <row r="6">
@@ -14527,22 +14540,22 @@
         <v>2026</v>
       </c>
       <c r="C6" s="626" t="n">
-        <v>130.5059589909402</v>
+        <v>132.7817485646202</v>
       </c>
       <c r="D6" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E6" s="626" t="n">
-        <v>130.5059589909402</v>
+        <v>132.7817485646202</v>
       </c>
       <c r="F6" s="626" t="n">
-        <v>678.8448990090596</v>
+        <v>674.5290854353797</v>
       </c>
       <c r="G6" s="626" t="n">
         <v>812.4640854999998</v>
       </c>
       <c r="H6" s="626" t="n">
-        <v>133.6191864909401</v>
+        <v>137.9350000646201</v>
       </c>
     </row>
     <row r="7">
@@ -14550,22 +14563,22 @@
         <v>2027</v>
       </c>
       <c r="C7" s="626" t="n">
-        <v>157.4906357474761</v>
+        <v>160.0227501035023</v>
       </c>
       <c r="D7" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E7" s="626" t="n">
-        <v>157.4906357474761</v>
+        <v>160.0227501035023</v>
       </c>
       <c r="F7" s="626" t="n">
-        <v>521.3542632615836</v>
+        <v>514.5063353318774</v>
       </c>
       <c r="G7" s="626" t="n">
         <v>744.6899570964996</v>
       </c>
       <c r="H7" s="626" t="n">
-        <v>223.335693834916</v>
+        <v>230.1836217646222</v>
       </c>
     </row>
     <row r="8">
@@ -14573,22 +14586,22 @@
         <v>2028</v>
       </c>
       <c r="C8" s="626" t="n">
-        <v>187.3302392459731</v>
+        <v>190.1408406633239</v>
       </c>
       <c r="D8" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E8" s="626" t="n">
-        <v>187.3302392459731</v>
+        <v>190.1408406633239</v>
       </c>
       <c r="F8" s="626" t="n">
-        <v>334.0240240156105</v>
+        <v>324.3654946685534</v>
       </c>
       <c r="G8" s="626" t="n">
         <v>665.6150688061919</v>
       </c>
       <c r="H8" s="626" t="n">
-        <v>331.5910447905814</v>
+        <v>341.2495741376384</v>
       </c>
     </row>
     <row r="9">
@@ -14596,22 +14609,22 @@
         <v>2029</v>
       </c>
       <c r="C9" s="626" t="n">
-        <v>221.2469627462453</v>
+        <v>224.4362368195235</v>
       </c>
       <c r="D9" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E9" s="626" t="n">
-        <v>221.2469627462453</v>
+        <v>224.4362368195235</v>
       </c>
       <c r="F9" s="626" t="n">
-        <v>112.7770612693652</v>
+        <v>99.92925784902985</v>
       </c>
       <c r="G9" s="626" t="n">
         <v>574.8877051518325</v>
       </c>
       <c r="H9" s="626" t="n">
-        <v>462.1106438824673</v>
+        <v>474.9584473028027</v>
       </c>
     </row>
     <row r="11">
@@ -15582,16 +15595,16 @@
         <v>77.8175</v>
       </c>
       <c r="E17" s="626" t="n">
-        <v>69.00712121399999</v>
+        <v>68.83779922199999</v>
       </c>
       <c r="F17" s="626" t="n">
-        <v>58.17512661775195</v>
+        <v>57.8169140911365</v>
       </c>
       <c r="G17" s="626" t="n">
-        <v>45.10340385071143</v>
+        <v>44.53502583254582</v>
       </c>
       <c r="H17" s="626" t="n">
-        <v>28.31773423345177</v>
+        <v>27.41949100417546</v>
       </c>
     </row>
     <row r="18">
@@ -15604,16 +15617,16 @@
         <v>41.66444200000014</v>
       </c>
       <c r="E18" s="626" t="n">
-        <v>62.79702399094019</v>
+        <v>62.9307883646202</v>
       </c>
       <c r="F18" s="626" t="n">
-        <v>86.39625399747612</v>
+        <v>86.67924189350231</v>
       </c>
       <c r="G18" s="626" t="n">
-        <v>112.6811384084731</v>
+        <v>113.1301570428239</v>
       </c>
       <c r="H18" s="626" t="n">
-        <v>142.8654068668702</v>
+        <v>143.5750190179985</v>
       </c>
     </row>
     <row r="19">
@@ -15623,19 +15636,19 @@
         </is>
       </c>
       <c r="D19" s="626" t="n">
-        <v>25.5003</v>
+        <v>23.460276</v>
       </c>
       <c r="E19" s="626" t="n">
-        <v>26.77531500000001</v>
+        <v>24.63328980000001</v>
       </c>
       <c r="F19" s="626" t="n">
-        <v>28.11408075000001</v>
+        <v>25.86495429000001</v>
       </c>
       <c r="G19" s="626" t="n">
-        <v>29.51978478750001</v>
+        <v>27.15820200450001</v>
       </c>
       <c r="H19" s="626" t="n">
-        <v>30.99577402687501</v>
+        <v>28.51611210472501</v>
       </c>
     </row>
     <row r="20">
@@ -15667,19 +15680,19 @@
         </is>
       </c>
       <c r="D21" s="626" t="n">
-        <v>106.1491420000001</v>
+        <v>108.1891660000001</v>
       </c>
       <c r="E21" s="626" t="n">
-        <v>130.5059589909402</v>
+        <v>132.7817485646202</v>
       </c>
       <c r="F21" s="626" t="n">
-        <v>157.4906357474761</v>
+        <v>160.0227501035023</v>
       </c>
       <c r="G21" s="626" t="n">
-        <v>187.3302392459731</v>
+        <v>190.1408406633239</v>
       </c>
       <c r="H21" s="626" t="n">
-        <v>221.2469627462453</v>
+        <v>224.4362368195235</v>
       </c>
     </row>
     <row r="22">
@@ -15711,19 +15724,19 @@
         </is>
       </c>
       <c r="D23" s="626" t="n">
-        <v>106.1491420000001</v>
+        <v>108.1891660000001</v>
       </c>
       <c r="E23" s="626" t="n">
-        <v>130.5059589909402</v>
+        <v>132.7817485646202</v>
       </c>
       <c r="F23" s="626" t="n">
-        <v>157.4906357474761</v>
+        <v>160.0227501035023</v>
       </c>
       <c r="G23" s="626" t="n">
-        <v>187.3302392459731</v>
+        <v>190.1408406633239</v>
       </c>
       <c r="H23" s="626" t="n">
-        <v>221.2469627462453</v>
+        <v>224.4362368195235</v>
       </c>
     </row>
     <row r="24">
@@ -15736,19 +15749,19 @@
         <v>1329.9</v>
       </c>
       <c r="D24" s="626" t="n">
-        <v>809.3508579999999</v>
+        <v>807.3108339999999</v>
       </c>
       <c r="E24" s="626" t="n">
-        <v>678.8448990090596</v>
+        <v>674.5290854353797</v>
       </c>
       <c r="F24" s="626" t="n">
-        <v>521.3542632615836</v>
+        <v>514.5063353318774</v>
       </c>
       <c r="G24" s="626" t="n">
-        <v>334.0240240156105</v>
+        <v>324.3654946685534</v>
       </c>
       <c r="H24" s="626" t="n">
-        <v>112.7770612693652</v>
+        <v>99.92925784902985</v>
       </c>
     </row>
   </sheetData>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -5445,7 +5445,7 @@
     <row r="3" ht="48" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>How to verify: click Source (E) → open page → copy Verbatim from I/J/K → Ctrl+F → paste. Overpessimism fix: rev +5% (mature CAGR; FY24 −2% outlier). S&amp;M +2% Fed restored. S&amp;M $414.1; 70/30; cuts 18%/18%; AI $24.5m; CapEx cut 8% (HC-linked); WC 0.</t>
+          <t>How to verify: click Source (E) → open page → copy Verbatim from I/J/K → Ctrl+F → paste. Overpessimism fix: rev +5% (mature CAGR; FY24 −2% outlier). S&amp;M +2% Fed restored. S&amp;M $414.1; 70/30; cuts 18%/18%; AI $24.5m; CapEx 8%; WC base 2.5% / improve 10%.</t>
         </is>
       </c>
     </row>
@@ -5921,21 +5921,20 @@
         </is>
       </c>
       <c r="C13" s="666" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D13" s="667" t="inlineStr">
         <is>
-          <t>No source printed a 10% WC improvement, so the improvement is set to 0%.</t>
-        </is>
-      </c>
-      <c r="E13" s="669" t="inlineStr">
-        <is>
-          <t>C13=0% WC improve — no source printed 10%, so none is applied.</t>
-        </is>
+          <t>AI/AR automation shortens collections. Conservative: ~6 DSO days cut (Global PayEx) on a 59-day B2B SaaS median (Fairview) → ≈10%. Below 20–40% automation headlines.</t>
+        </is>
+      </c>
+      <c r="E13" s="676">
+        <f>HYPERLINK("https://getfairview.com/blog/working-capital-management-saas","IN EQ: C13=10% ≈ 6 DSO days / 59-day B2B SaaS median (conservative AR-automation cut)")</f>
+        <v/>
       </c>
       <c r="F13" s="664" t="inlineStr">
         <is>
-          <t>No source says a WC improvement. The improvement is 0%, so WC uses the base plug only.</t>
+          <t>Fairview says median B2B SaaS DSO is 59 days. Global PayEx shows ~6-day DSO cuts. 6/59≈10% WC improvement in the AI case.</t>
         </is>
       </c>
       <c r="G13" s="664" t="inlineStr">
@@ -5943,14 +5942,25 @@
           <t>Go to AI_Operating!D20 (ΔNWC)</t>
         </is>
       </c>
-      <c r="H13" s="593" t="n"/>
+      <c r="H13" s="675">
+        <f>HYPERLINK("https://globalpayex.com/resources/blogs/fortune-500-cfo-ar-automation-dso-reduction/","Global PayEx: DSO reduced by 6 days (AR automation)")</f>
+        <v/>
+      </c>
       <c r="I13" s="669" t="inlineStr">
         <is>
-          <t>0% WC improve: no source claimed 10%</t>
-        </is>
-      </c>
-      <c r="J13" s="651" t="n"/>
-      <c r="K13" s="651" t="n"/>
+          <t>Ctrl+F: Median B2B SaaS DSO is 59 days</t>
+        </is>
+      </c>
+      <c r="J13" s="672" t="inlineStr">
+        <is>
+          <t>Ctrl+F: reduced DSO by 6 days</t>
+        </is>
+      </c>
+      <c r="K13" s="672" t="inlineStr">
+        <is>
+          <t>Ctrl+F: Cut DSO 20%+ (headline; we use conservative 10%)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="96" customHeight="1" s="244">
       <c r="A14" s="665" t="inlineStr">
@@ -6495,21 +6505,20 @@
         </is>
       </c>
       <c r="C25" s="666" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="D25" s="667" t="inlineStr">
         <is>
-          <t>Was an unsourced 2% ΔNWC/ΔRev plug. No page equals 2%, so the plug is set to 0%.</t>
-        </is>
-      </c>
-      <c r="E25" s="669" t="inlineStr">
-        <is>
-          <t>C25=0% ΔNWC/ΔRev — no source printed 2%, so the plug is zero.</t>
-        </is>
+          <t>Growth still ties up some NWC (receivables). VeloraAI SaaS/Software NWC is 0–5% of sales; we use the 2.5% midpoint as ΔNWC/ΔRev (conservative vs assuming negative SaaS NWC).</t>
+        </is>
+      </c>
+      <c r="E25" s="676">
+        <f>HYPERLINK("https://veloraailabs.com/blog/working-capital-schedule-excel","IN EQ: C25=2.5% = midpoint of SaaS/Software NWC % of Sales band 0–5% (VeloraAI)")</f>
+        <v/>
       </c>
       <c r="F25" s="664" t="inlineStr">
         <is>
-          <t>No source says a 2% WC plug. The plug is 0%, so ΔNWC is zero in the forecast.</t>
+          <t>VeloraAI says SaaS/Software NWC is 0–5% of sales. We use 2.5%, the midpoint, as the ΔNWC / Δrevenue plug.</t>
         </is>
       </c>
       <c r="G25" s="664" t="inlineStr">
@@ -6517,14 +6526,25 @@
           <t>Go to AI_Operating!D20 (ΔNWC)</t>
         </is>
       </c>
-      <c r="H25" s="593" t="n"/>
+      <c r="H25" s="675">
+        <f>HYPERLINK("https://getfairview.com/blog/working-capital-management-saas","Fairview: SaaS WC levers center on DSO")</f>
+        <v/>
+      </c>
       <c r="I25" s="669" t="inlineStr">
         <is>
-          <t>0% WC plug: no source equaled 2%</t>
-        </is>
-      </c>
-      <c r="J25" s="651" t="n"/>
-      <c r="K25" s="651" t="n"/>
+          <t>Ctrl+F: SaaS / Software</t>
+        </is>
+      </c>
+      <c r="J25" s="672" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 0-5%</t>
+        </is>
+      </c>
+      <c r="K25" s="672" t="inlineStr">
+        <is>
+          <t>Ctrl+F: NWC % of Sales</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="618" t="inlineStr">
@@ -12771,17 +12791,17 @@
         </is>
       </c>
       <c r="C35" s="626" t="n">
-        <v>574.8877051518325</v>
+        <v>584.486394566851</v>
       </c>
       <c r="D35" s="626" t="n">
-        <v>99.92925784902985</v>
+        <v>108.532697639433</v>
       </c>
       <c r="E35" s="626" t="n">
-        <v>-474.9584473028027</v>
+        <v>-475.953696927418</v>
       </c>
       <c r="F35" s="625" t="inlineStr">
         <is>
-          <t>Remaining debt at exit; AI case $99.9m vs Base $574.9m.</t>
+          <t>Remaining debt at exit; AI case $108.5m vs Base $584.5m.</t>
         </is>
       </c>
     </row>
@@ -12792,17 +12812,17 @@
         </is>
       </c>
       <c r="C36" s="626" t="n">
-        <v>1773.969906451733</v>
+        <v>1764.371217036715</v>
       </c>
       <c r="D36" s="626" t="n">
-        <v>4009.202574088093</v>
+        <v>4000.59913429769</v>
       </c>
       <c r="E36" s="626" t="n">
-        <v>2235.23266763636</v>
+        <v>2236.227917260975</v>
       </c>
       <c r="F36" s="625" t="inlineStr">
         <is>
-          <t>Total equity payout; AI strategy changed final payout by $2,235.2m to $4,009.2m (exit 12.9x).</t>
+          <t>Total equity payout; AI strategy changed final payout by $2,236.2m to $4,000.6m (exit 12.9x).</t>
         </is>
       </c>
     </row>
@@ -12813,17 +12833,17 @@
         </is>
       </c>
       <c r="C37" s="627" t="n">
-        <v>0.9479933534394431</v>
+        <v>0.9428639012801515</v>
       </c>
       <c r="D37" s="627" t="n">
-        <v>2.142481323389478</v>
+        <v>2.13788372356078</v>
       </c>
       <c r="E37" s="627" t="n">
-        <v>1.194487969950035</v>
+        <v>1.195019822280629</v>
       </c>
       <c r="F37" s="625" t="inlineStr">
         <is>
-          <t>Multiple on Invested Capital; AI improved gross cash return from 0.95x to 2.14x.</t>
+          <t>Multiple on Invested Capital; AI improved gross cash return from 0.94x to 2.14x.</t>
         </is>
       </c>
     </row>
@@ -12834,17 +12854,17 @@
         </is>
       </c>
       <c r="C38" s="624" t="n">
-        <v>-0.01062471232081792</v>
+        <v>-0.01169770991337527</v>
       </c>
       <c r="D38" s="624" t="n">
-        <v>0.1646177607845645</v>
+        <v>0.1641174951927608</v>
       </c>
       <c r="E38" s="624" t="n">
-        <v>0.1752424731053824</v>
+        <v>0.175815205106136</v>
       </c>
       <c r="F38" s="625" t="inlineStr">
         <is>
-          <t>5-year IRR; AI boosted return by 17.5 percentage points to 16.5% (AI infra $24.5m; payroll/commission cut 18%; rev 5%; exit 12.9x).</t>
+          <t>5-year IRR; AI boosted return by 17.6 percentage points to 16.4% (AI infra $24.5m; payroll/commission cut 18%; rev 5%; exit 12.9x).</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12885,7 @@
     <row r="41">
       <c r="B41" s="569" t="inlineStr">
         <is>
-          <t>AI case IRR 16.5% − Base IRR -1.1% = 17.5 percentage points of IRR</t>
+          <t>AI case IRR 16.4% − Base IRR -1.2% = 17.6 percentage points of IRR</t>
         </is>
       </c>
     </row>
@@ -13637,7 +13657,7 @@
       </c>
       <c r="D15" s="571" t="inlineStr">
         <is>
-          <t>WC improve 0% vs base (no sourced improve)</t>
+          <t>WC / receivables improve 10% vs base (≈6 DSO days / 59-day median)</t>
         </is>
       </c>
       <c r="E15" s="571" t="inlineStr">
@@ -14279,7 +14299,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -14330,7 +14350,7 @@
     <row r="30">
       <c r="B30" s="590" t="inlineStr">
         <is>
-          <t>This list must match Assumptions_Drivers: rev 5%, payroll/commission cut −18%, AI $24.5m, S&amp;M $414.1m, exit 12.9x, CapEx cut 8% (HC-linked); WC improve/plug 0%.</t>
+          <t>This list must match Assumptions_Drivers: rev 5%, payroll/commission cut −18%, AI $24.5m, S&amp;M $414.1m, exit 12.9x, CapEx cut 8%; WC base 2.5% of Δrev; WC improve 10%.</t>
         </is>
       </c>
     </row>
@@ -14517,22 +14537,22 @@
         <v>2025</v>
       </c>
       <c r="C5" s="626" t="n">
-        <v>108.1891660000001</v>
+        <v>106.8230785000001</v>
       </c>
       <c r="D5" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E5" s="626" t="n">
-        <v>108.1891660000001</v>
+        <v>106.8230785000001</v>
       </c>
       <c r="F5" s="626" t="n">
-        <v>807.3108339999999</v>
+        <v>808.6769214999998</v>
       </c>
       <c r="G5" s="626" t="n">
-        <v>869.0184999999998</v>
+        <v>870.5363749999998</v>
       </c>
       <c r="H5" s="626" t="n">
-        <v>61.7076659999999</v>
+        <v>61.85945349999997</v>
       </c>
     </row>
     <row r="6">
@@ -14540,22 +14560,22 @@
         <v>2026</v>
       </c>
       <c r="C6" s="626" t="n">
-        <v>132.7817485646202</v>
+        <v>131.2577823322452</v>
       </c>
       <c r="D6" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E6" s="626" t="n">
-        <v>132.7817485646202</v>
+        <v>131.2577823322452</v>
       </c>
       <c r="F6" s="626" t="n">
-        <v>674.5290854353797</v>
+        <v>677.4191391677547</v>
       </c>
       <c r="G6" s="626" t="n">
-        <v>812.4640854999998</v>
+        <v>815.7017128749998</v>
       </c>
       <c r="H6" s="626" t="n">
-        <v>137.9350000646201</v>
+        <v>138.2825737072451</v>
       </c>
     </row>
     <row r="7">
@@ -14563,22 +14583,22 @@
         <v>2027</v>
       </c>
       <c r="C7" s="626" t="n">
-        <v>160.0227501035023</v>
+        <v>158.3271378115205</v>
       </c>
       <c r="D7" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E7" s="626" t="n">
-        <v>160.0227501035023</v>
+        <v>158.3271378115205</v>
       </c>
       <c r="F7" s="626" t="n">
-        <v>514.5063353318774</v>
+        <v>519.0920013562342</v>
       </c>
       <c r="G7" s="626" t="n">
-        <v>744.6899570964996</v>
+        <v>749.8697647311245</v>
       </c>
       <c r="H7" s="626" t="n">
-        <v>230.1836217646222</v>
+        <v>230.7777633748904</v>
       </c>
     </row>
     <row r="8">
@@ -14586,22 +14606,22 @@
         <v>2028</v>
       </c>
       <c r="C8" s="626" t="n">
-        <v>190.1408406633239</v>
+        <v>188.2587414999194</v>
       </c>
       <c r="D8" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E8" s="626" t="n">
-        <v>190.1408406633239</v>
+        <v>188.2587414999194</v>
       </c>
       <c r="F8" s="626" t="n">
-        <v>324.3654946685534</v>
+        <v>330.8332598563148</v>
       </c>
       <c r="G8" s="626" t="n">
-        <v>665.6150688061919</v>
+        <v>672.8916464742942</v>
       </c>
       <c r="H8" s="626" t="n">
-        <v>341.2495741376384</v>
+        <v>342.0583866179794</v>
       </c>
     </row>
     <row r="9">
@@ -14609,22 +14629,22 @@
         <v>2029</v>
       </c>
       <c r="C9" s="626" t="n">
-        <v>224.4362368195235</v>
+        <v>222.3005622168818</v>
       </c>
       <c r="D9" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E9" s="626" t="n">
-        <v>224.4362368195235</v>
+        <v>222.3005622168818</v>
       </c>
       <c r="F9" s="626" t="n">
-        <v>99.92925784902985</v>
+        <v>108.532697639433</v>
       </c>
       <c r="G9" s="626" t="n">
-        <v>574.8877051518325</v>
+        <v>584.486394566851</v>
       </c>
       <c r="H9" s="626" t="n">
-        <v>474.9584473028027</v>
+        <v>475.953696927418</v>
       </c>
     </row>
     <row r="11">
@@ -15041,16 +15061,16 @@
         <v>77.8175</v>
       </c>
       <c r="E17" s="626" t="n">
-        <v>73.95953549999999</v>
+        <v>74.08551912499999</v>
       </c>
       <c r="F17" s="626" t="n">
-        <v>69.26551909649999</v>
+        <v>69.53424216862498</v>
       </c>
       <c r="G17" s="626" t="n">
-        <v>63.64026643900946</v>
+        <v>64.07019047268334</v>
       </c>
       <c r="H17" s="626" t="n">
-        <v>57.07705071091392</v>
+        <v>57.68100665736642</v>
       </c>
     </row>
     <row r="18">
@@ -15063,16 +15083,16 @@
         <v>-18.00319999999986</v>
       </c>
       <c r="E18" s="626" t="n">
-        <v>-11.15452049999995</v>
+        <v>-11.28050412499995</v>
       </c>
       <c r="F18" s="626" t="n">
-        <v>-3.320253346499783</v>
+        <v>-3.588976418624782</v>
       </c>
       <c r="G18" s="626" t="n">
-        <v>4.425787452807622</v>
+        <v>4.086147466205259</v>
       </c>
       <c r="H18" s="626" t="n">
-        <v>12.3458077749844</v>
+        <v>11.86868257728693</v>
       </c>
     </row>
     <row r="19">
@@ -15104,19 +15124,19 @@
         </is>
       </c>
       <c r="D20" s="626" t="n">
-        <v>0</v>
+        <v>1.517875000000004</v>
       </c>
       <c r="E20" s="626" t="n">
-        <v>0</v>
+        <v>1.593768750000004</v>
       </c>
       <c r="F20" s="626" t="n">
-        <v>0</v>
+        <v>1.673457187500003</v>
       </c>
       <c r="G20" s="626" t="n">
-        <v>0</v>
+        <v>1.757130046875</v>
       </c>
       <c r="H20" s="626" t="n">
-        <v>0</v>
+        <v>1.844986549218754</v>
       </c>
     </row>
     <row r="21">
@@ -15126,19 +15146,19 @@
         </is>
       </c>
       <c r="D21" s="626" t="n">
-        <v>46.48150000000013</v>
+        <v>44.96362500000013</v>
       </c>
       <c r="E21" s="626" t="n">
-        <v>56.55441450000006</v>
+        <v>54.83466212500006</v>
       </c>
       <c r="F21" s="626" t="n">
-        <v>67.77412840350024</v>
+        <v>65.83194814387524</v>
       </c>
       <c r="G21" s="626" t="n">
-        <v>79.07488829030763</v>
+        <v>76.97811825683027</v>
       </c>
       <c r="H21" s="626" t="n">
-        <v>90.72736365435942</v>
+        <v>88.40525190744319</v>
       </c>
     </row>
     <row r="22">
@@ -15170,19 +15190,19 @@
         </is>
       </c>
       <c r="D23" s="626" t="n">
-        <v>46.48150000000013</v>
+        <v>44.96362500000013</v>
       </c>
       <c r="E23" s="626" t="n">
-        <v>56.55441450000006</v>
+        <v>54.83466212500006</v>
       </c>
       <c r="F23" s="626" t="n">
-        <v>67.77412840350024</v>
+        <v>65.83194814387524</v>
       </c>
       <c r="G23" s="626" t="n">
-        <v>79.07488829030763</v>
+        <v>76.97811825683027</v>
       </c>
       <c r="H23" s="626" t="n">
-        <v>90.72736365435942</v>
+        <v>88.40525190744319</v>
       </c>
     </row>
     <row r="24">
@@ -15195,19 +15215,19 @@
         <v>1329.9</v>
       </c>
       <c r="D24" s="626" t="n">
-        <v>869.0184999999998</v>
+        <v>870.5363749999998</v>
       </c>
       <c r="E24" s="626" t="n">
-        <v>812.4640854999998</v>
+        <v>815.7017128749998</v>
       </c>
       <c r="F24" s="626" t="n">
-        <v>744.6899570964996</v>
+        <v>749.8697647311245</v>
       </c>
       <c r="G24" s="626" t="n">
-        <v>665.6150688061919</v>
+        <v>672.8916464742942</v>
       </c>
       <c r="H24" s="626" t="n">
-        <v>574.8877051518325</v>
+        <v>584.486394566851</v>
       </c>
     </row>
   </sheetData>
@@ -15595,16 +15615,16 @@
         <v>77.8175</v>
       </c>
       <c r="E17" s="626" t="n">
-        <v>68.83779922199999</v>
+        <v>68.95118448449999</v>
       </c>
       <c r="F17" s="626" t="n">
-        <v>57.8169140911365</v>
+        <v>58.05678855092363</v>
       </c>
       <c r="G17" s="626" t="n">
-        <v>44.53502583254582</v>
+        <v>44.91563611256743</v>
       </c>
       <c r="H17" s="626" t="n">
-        <v>27.41949100417546</v>
+        <v>28.02099316663728</v>
       </c>
     </row>
     <row r="18">
@@ -15617,16 +15637,16 @@
         <v>41.66444200000014</v>
       </c>
       <c r="E18" s="626" t="n">
-        <v>62.9307883646202</v>
+        <v>62.8412140072452</v>
       </c>
       <c r="F18" s="626" t="n">
-        <v>86.67924189350231</v>
+        <v>86.48974107027047</v>
       </c>
       <c r="G18" s="626" t="n">
-        <v>113.1301570428239</v>
+        <v>112.8294749216068</v>
       </c>
       <c r="H18" s="626" t="n">
-        <v>143.5750190179985</v>
+        <v>143.0998323096537</v>
       </c>
     </row>
     <row r="19">
@@ -15658,19 +15678,19 @@
         </is>
       </c>
       <c r="D20" s="626" t="n">
-        <v>0</v>
+        <v>1.366087500000003</v>
       </c>
       <c r="E20" s="626" t="n">
-        <v>0</v>
+        <v>1.434391875000004</v>
       </c>
       <c r="F20" s="626" t="n">
-        <v>0</v>
+        <v>1.506111468750003</v>
       </c>
       <c r="G20" s="626" t="n">
-        <v>0</v>
+        <v>1.5814170421875</v>
       </c>
       <c r="H20" s="626" t="n">
-        <v>0</v>
+        <v>1.660487894296879</v>
       </c>
     </row>
     <row r="21">
@@ -15680,19 +15700,19 @@
         </is>
       </c>
       <c r="D21" s="626" t="n">
-        <v>108.1891660000001</v>
+        <v>106.8230785000001</v>
       </c>
       <c r="E21" s="626" t="n">
-        <v>132.7817485646202</v>
+        <v>131.2577823322452</v>
       </c>
       <c r="F21" s="626" t="n">
-        <v>160.0227501035023</v>
+        <v>158.3271378115205</v>
       </c>
       <c r="G21" s="626" t="n">
-        <v>190.1408406633239</v>
+        <v>188.2587414999194</v>
       </c>
       <c r="H21" s="626" t="n">
-        <v>224.4362368195235</v>
+        <v>222.3005622168818</v>
       </c>
     </row>
     <row r="22">
@@ -15724,19 +15744,19 @@
         </is>
       </c>
       <c r="D23" s="626" t="n">
-        <v>108.1891660000001</v>
+        <v>106.8230785000001</v>
       </c>
       <c r="E23" s="626" t="n">
-        <v>132.7817485646202</v>
+        <v>131.2577823322452</v>
       </c>
       <c r="F23" s="626" t="n">
-        <v>160.0227501035023</v>
+        <v>158.3271378115205</v>
       </c>
       <c r="G23" s="626" t="n">
-        <v>190.1408406633239</v>
+        <v>188.2587414999194</v>
       </c>
       <c r="H23" s="626" t="n">
-        <v>224.4362368195235</v>
+        <v>222.3005622168818</v>
       </c>
     </row>
     <row r="24">
@@ -15749,19 +15769,19 @@
         <v>1329.9</v>
       </c>
       <c r="D24" s="626" t="n">
-        <v>807.3108339999999</v>
+        <v>808.6769214999998</v>
       </c>
       <c r="E24" s="626" t="n">
-        <v>674.5290854353797</v>
+        <v>677.4191391677547</v>
       </c>
       <c r="F24" s="626" t="n">
-        <v>514.5063353318774</v>
+        <v>519.0920013562342</v>
       </c>
       <c r="G24" s="626" t="n">
-        <v>324.3654946685534</v>
+        <v>330.8332598563148</v>
       </c>
       <c r="H24" s="626" t="n">
-        <v>99.92925784902985</v>
+        <v>108.532697639433</v>
       </c>
     </row>
   </sheetData>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -1989,7 +1989,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="677">
+  <cellXfs count="678">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3236,6 +3236,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="37" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="36" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5445,7 +5448,7 @@
     <row r="3" ht="48" customHeight="1" s="244">
       <c r="B3" s="605" t="inlineStr">
         <is>
-          <t>How to verify: click Source (E) → open page → copy Verbatim from I/J/K → Ctrl+F → paste. Overpessimism fix: rev +5% (mature CAGR; FY24 −2% outlier). S&amp;M +2% Fed restored. S&amp;M $414.1; 70/30; cuts 18%/18%; AI $24.5m; CapEx 8%; WC base 2.5% / improve 10%.</t>
+          <t>How to verify: click Source (E) → open page → copy Verbatim from I/J/K → Ctrl+F → paste. Overpessimism fix: rev +5% (mature CAGR; FY24 −2% outlier). S&amp;M +2% Fed restored. S&amp;M $414.1; AI $24.5m; CapEx 8%; ΔNWC=ΔAR(16.2%×[1−10% AI])−ΔDR(39%).</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5920,7 @@
       </c>
       <c r="B13" s="664" t="inlineStr">
         <is>
-          <t>WC / receivables improvement</t>
+          <t>AR / receivables improvement (DSO)</t>
         </is>
       </c>
       <c r="C13" s="666" t="n">
@@ -5925,16 +5928,16 @@
       </c>
       <c r="D13" s="667" t="inlineStr">
         <is>
-          <t>AI/AR automation shortens collections. Conservative: ~6 DSO days cut (Global PayEx) on a 59-day B2B SaaS median (Fairview) → ≈10%. Below 20–40% automation headlines.</t>
+          <t>6/59 DSO days ≈10% faster collections → ~10% lower AR if sales steady. That frees cash trapped in AR; it is NOT the same as a 10% cut to total NWC (NWC also reflects deferred revenue and other liabilities).</t>
         </is>
       </c>
       <c r="E13" s="676">
-        <f>HYPERLINK("https://getfairview.com/blog/working-capital-management-saas","IN EQ: C13=10% ≈ 6 DSO days / 59-day B2B SaaS median (conservative AR-automation cut)")</f>
+        <f>HYPERLINK("https://getfairview.com/blog/working-capital-management-saas","IN EQ: C13=10% cuts ΔAR only (6/59 DSO). NWC% change ≠10% once deferred revenue is netted.")</f>
         <v/>
       </c>
       <c r="F13" s="664" t="inlineStr">
         <is>
-          <t>Fairview says median B2B SaaS DSO is 59 days. Global PayEx shows ~6-day DSO cuts. 6/59≈10% WC improvement in the AI case.</t>
+          <t>6/59≈10% DSO cut → ~10% less AR. That frees AR cash. It is not a 10% cut to total NWC (deferred revenue still nets in).</t>
         </is>
       </c>
       <c r="G13" s="664" t="inlineStr">
@@ -5958,7 +5961,7 @@
       </c>
       <c r="K13" s="672" t="inlineStr">
         <is>
-          <t>Ctrl+F: Cut DSO 20%+ (headline; we use conservative 10%)</t>
+          <t>20–40% headlines often measure overdue/FTE — not calendar DSO; we keep 10%</t>
         </is>
       </c>
     </row>
@@ -6501,24 +6504,24 @@
       </c>
       <c r="B25" s="664" t="inlineStr">
         <is>
-          <t>WC base % of Δrev</t>
+          <t>AR intensity (DSO÷365)</t>
         </is>
       </c>
       <c r="C25" s="666" t="n">
-        <v>0.025</v>
+        <v>0.1616438356164384</v>
       </c>
       <c r="D25" s="667" t="inlineStr">
         <is>
-          <t>Growth still ties up some NWC (receivables). VeloraAI SaaS/Software NWC is 0–5% of sales; we use the 2.5% midpoint as ΔNWC/ΔRev (conservative vs assuming negative SaaS NWC).</t>
+          <t>AR ≈ (DSO/365)×Revenue. Fairview median B2B SaaS DSO is 59 days → 59/365≈16.2% of Δrev builds AR if DSO is unchanged. This is the gross AR leg — not net NWC.</t>
         </is>
       </c>
       <c r="E25" s="676">
-        <f>HYPERLINK("https://veloraailabs.com/blog/working-capital-schedule-excel","IN EQ: C25=2.5% = midpoint of SaaS/Software NWC % of Sales band 0–5% (VeloraAI)")</f>
+        <f>HYPERLINK("https://getfairview.com/blog/working-capital-management-saas","IN EQ: C25=59/365≈16.2% AR intensity; ΔAR=ΔRev×C25 before the 10% AI cut on row 13")</f>
         <v/>
       </c>
       <c r="F25" s="664" t="inlineStr">
         <is>
-          <t>VeloraAI says SaaS/Software NWC is 0–5% of sales. We use 2.5%, the midpoint, as the ΔNWC / Δrevenue plug.</t>
+          <t>Fairview median DSO is 59 days. AR intensity = 59/365≈16.2% of Δrevenue. That is the AR leg of ΔNWC, not net NWC.</t>
         </is>
       </c>
       <c r="G25" s="664" t="inlineStr">
@@ -6527,29 +6530,75 @@
         </is>
       </c>
       <c r="H25" s="675">
-        <f>HYPERLINK("https://getfairview.com/blog/working-capital-management-saas","Fairview: SaaS WC levers center on DSO")</f>
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","ZI FY24 AR $246.1m (~20% of sales; we use median DSO 16.2%)")</f>
         <v/>
       </c>
       <c r="I25" s="669" t="inlineStr">
         <is>
-          <t>Ctrl+F: SaaS / Software</t>
+          <t>Ctrl+F: Median B2B SaaS DSO is 59 days</t>
         </is>
       </c>
       <c r="J25" s="672" t="inlineStr">
         <is>
-          <t>Ctrl+F: 0-5%</t>
+          <t>Ctrl+F: Accounts receivable</t>
         </is>
       </c>
       <c r="K25" s="672" t="inlineStr">
         <is>
-          <t>Ctrl+F: NWC % of Sales</t>
+          <t>EQ: ΔAR_base=ΔRev×16.2%; ΔAR_AI=ΔRev×16.2%×(1−10%)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="618" t="inlineStr">
-        <is>
-          <t>Computed rates (SOFR + spreads) — still sourced on the same row</t>
+      <c r="A26" s="664" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="B26" s="664" t="inlineStr">
+        <is>
+          <t>Deferred revenue % of rev</t>
+        </is>
+      </c>
+      <c r="C26" s="677" t="n">
+        <v>0.3901836448982953</v>
+      </c>
+      <c r="D26" s="664" t="inlineStr">
+        <is>
+          <t>ZI FY24 unearned revenue current $473.8m / $1,214.3m sales ≈39%. As sales grow, deferred revenue typically rises too — a cash source that nets against AR in NWC.</t>
+        </is>
+      </c>
+      <c r="E26" s="675">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","IN EQ: C26≈39% = ZI FY24 unearned revenue current $473.8m / revenue $1,214.3m")</f>
+        <v/>
+      </c>
+      <c r="F26" s="664" t="inlineStr">
+        <is>
+          <t>ZoomInfo FY24 unearned revenue was $473.8m on $1,214.3m sales (~39%). ΔDeferred≈39% of Δrev and reduces ΔNWC (cash source).</t>
+        </is>
+      </c>
+      <c r="G26" s="664" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D20 (ΔNWC)</t>
+        </is>
+      </c>
+      <c r="H26" s="675">
+        <f>HYPERLINK("https://markets.financialcontent.com/stocks/article/bizwire-2025-2-25-zoominfo-announces-fourth-quarter-and-full-year-2024-financial-results","FY24 results balance sheet: Unearned revenue")</f>
+        <v/>
+      </c>
+      <c r="I26" s="664" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 473.8</t>
+        </is>
+      </c>
+      <c r="J26" s="664" t="inlineStr">
+        <is>
+          <t>Ctrl+F: Unearned revenue</t>
+        </is>
+      </c>
+      <c r="K26" s="664" t="inlineStr">
+        <is>
+          <t>EQ: ΔNWC≈ΔAR−ΔDeferred; AI cuts only ΔAR by 10%</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6619,7 @@
       </c>
       <c r="D27" s="609" t="inlineStr">
         <is>
-          <t>Total Term Loan A interest. Mathematically correct and reasonable for the total borrowing cost demanded by senior lenders in this specific rate environment.</t>
+          <t>Total Term Loan A interest. Sum of sourced SOFR + TLA spread.</t>
         </is>
       </c>
       <c r="E27" s="647" t="inlineStr">
@@ -6614,7 +6663,7 @@
       </c>
       <c r="D28" s="609" t="inlineStr">
         <is>
-          <t>Total Term Loan B interest. Mathematically correct and perfectly reasonable, pricing the institutional debt risk appropriately above the safer Term Loan A.</t>
+          <t>Total Term Loan B interest. Sum of sourced SOFR + TLB spread.</t>
         </is>
       </c>
       <c r="E28" s="647" t="inlineStr">
@@ -12791,17 +12840,17 @@
         </is>
       </c>
       <c r="C35" s="626" t="n">
-        <v>584.486394566851</v>
+        <v>487.1403992212673</v>
       </c>
       <c r="D35" s="626" t="n">
-        <v>108.532697639433</v>
+        <v>6.360467200663038</v>
       </c>
       <c r="E35" s="626" t="n">
-        <v>-475.953696927418</v>
+        <v>-480.7799320206043</v>
       </c>
       <c r="F35" s="625" t="inlineStr">
         <is>
-          <t>Remaining debt at exit; AI case $108.5m vs Base $584.5m.</t>
+          <t>Remaining debt at exit; AI case $6.4m vs Base $487.1m.</t>
         </is>
       </c>
     </row>
@@ -12812,17 +12861,17 @@
         </is>
       </c>
       <c r="C36" s="626" t="n">
-        <v>1764.371217036715</v>
+        <v>1861.717212382298</v>
       </c>
       <c r="D36" s="626" t="n">
-        <v>4000.59913429769</v>
+        <v>4102.77136473646</v>
       </c>
       <c r="E36" s="626" t="n">
-        <v>2236.227917260975</v>
+        <v>2241.054152354161</v>
       </c>
       <c r="F36" s="625" t="inlineStr">
         <is>
-          <t>Total equity payout; AI strategy changed final payout by $2,236.2m to $4,000.6m (exit 12.9x).</t>
+          <t>Total equity payout; AI strategy changed final payout by $2,241.1m to $4,102.8m (exit 12.9x).</t>
         </is>
       </c>
     </row>
@@ -12833,17 +12882,17 @@
         </is>
       </c>
       <c r="C37" s="627" t="n">
-        <v>0.9428639012801515</v>
+        <v>0.9948847141676397</v>
       </c>
       <c r="D37" s="627" t="n">
-        <v>2.13788372356078</v>
+        <v>2.192483632504992</v>
       </c>
       <c r="E37" s="627" t="n">
-        <v>1.195019822280629</v>
+        <v>1.197598918337353</v>
       </c>
       <c r="F37" s="625" t="inlineStr">
         <is>
-          <t>Multiple on Invested Capital; AI improved gross cash return from 0.94x to 2.14x.</t>
+          <t>Multiple on Invested Capital; AI improved gross cash return from 0.99x to 2.19x.</t>
         </is>
       </c>
     </row>
@@ -12854,17 +12903,17 @@
         </is>
       </c>
       <c r="C38" s="624" t="n">
-        <v>-0.01169770991337527</v>
+        <v>-0.001025156906170403</v>
       </c>
       <c r="D38" s="624" t="n">
-        <v>0.1641174951927608</v>
+        <v>0.1700037992226664</v>
       </c>
       <c r="E38" s="624" t="n">
-        <v>0.175815205106136</v>
+        <v>0.1710289561288368</v>
       </c>
       <c r="F38" s="625" t="inlineStr">
         <is>
-          <t>5-year IRR; AI boosted return by 17.6 percentage points to 16.4% (AI infra $24.5m; payroll/commission cut 18%; rev 5%; exit 12.9x).</t>
+          <t>5-year IRR; AI boosted return by 17.1 percentage points to 17.0% (AI infra $24.5m; payroll/commission cut 18%; rev 5%; exit 12.9x).</t>
         </is>
       </c>
     </row>
@@ -12885,7 +12934,7 @@
     <row r="41">
       <c r="B41" s="569" t="inlineStr">
         <is>
-          <t>AI case IRR 16.4% − Base IRR -1.2% = 17.6 percentage points of IRR</t>
+          <t>AI case IRR 17.0% − Base IRR -0.1% = 17.1 percentage points of IRR</t>
         </is>
       </c>
     </row>
@@ -12896,10 +12945,24 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NWC math: ΔNWC≈ΔAR−ΔDeferred. AR intensity 59/365≈16.2%; ZI deferred 39.0% of sales. AI cuts ΔAR by 10% only (not 10% of total NWC).</t>
+        </is>
+      </c>
+    </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>See AI_Operating, Base_Operating, Debt_Sweep_AI, LBO, Assumptions_Drivers, 00_Assumptions_List</t>
+          <t>FCF impact Y1: AI ΔNWC -14.9m vs Base -13.9m (AI FCF +1.0m from lower ΔAR). Illustrative stock: 10%×FY24 AR $246.1m ≈ $24.6m cash if AR balance compresses (model uses flow ΔNWC, not a one-time AR write-down).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deferred revenue: ZI FY24 unearned $473.8m &gt; AR $246.1m → structural cash source. 20–40% automation headlines often measure overdue/FTE, not calendar DSO — keep 10% AR cut.</t>
         </is>
       </c>
     </row>
@@ -13657,7 +13720,7 @@
       </c>
       <c r="D15" s="571" t="inlineStr">
         <is>
-          <t>WC / receivables improve 10% vs base (≈6 DSO days / 59-day median)</t>
+          <t>AR improve 10% (6/59 DSO→AR); frees AR cash — not 10% of total NWC</t>
         </is>
       </c>
       <c r="E15" s="571" t="inlineStr">
@@ -14299,7 +14362,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>AR 16.2% / DR 39.0% (net -22.9%)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -14350,7 +14413,7 @@
     <row r="30">
       <c r="B30" s="590" t="inlineStr">
         <is>
-          <t>This list must match Assumptions_Drivers: rev 5%, payroll/commission cut −18%, AI $24.5m, S&amp;M $414.1m, exit 12.9x, CapEx cut 8%; WC base 2.5% of Δrev; WC improve 10%.</t>
+          <t>This list must match Assumptions_Drivers: rev 5%, payroll/commission cut −18%, AI $24.5m, S&amp;M $414.1m, exit 12.9x, CapEx 8%; ΔNWC=ΔAR(59/365)−ΔDR(39%); AI cuts ΔAR 10% only.</t>
         </is>
       </c>
     </row>
@@ -14537,22 +14600,22 @@
         <v>2025</v>
       </c>
       <c r="C5" s="626" t="n">
-        <v>106.8230785000001</v>
+        <v>123.0463810684933</v>
       </c>
       <c r="D5" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E5" s="626" t="n">
-        <v>106.8230785000001</v>
+        <v>123.0463810684933</v>
       </c>
       <c r="F5" s="626" t="n">
-        <v>808.6769214999998</v>
+        <v>792.4536189315066</v>
       </c>
       <c r="G5" s="626" t="n">
-        <v>870.5363749999998</v>
+        <v>855.1427054794518</v>
       </c>
       <c r="H5" s="626" t="n">
-        <v>61.85945349999997</v>
+        <v>62.68908654794518</v>
       </c>
     </row>
     <row r="6">
@@ -14560,22 +14623,22 @@
         <v>2026</v>
       </c>
       <c r="C6" s="626" t="n">
-        <v>131.2577823322452</v>
+        <v>149.3560119785791</v>
       </c>
       <c r="D6" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E6" s="626" t="n">
-        <v>131.2577823322452</v>
+        <v>149.3560119785791</v>
       </c>
       <c r="F6" s="626" t="n">
-        <v>677.4191391677547</v>
+        <v>643.0976069529275</v>
       </c>
       <c r="G6" s="626" t="n">
-        <v>815.7017128749998</v>
+        <v>782.867015787671</v>
       </c>
       <c r="H6" s="626" t="n">
-        <v>138.2825737072451</v>
+        <v>139.7694088347434</v>
       </c>
     </row>
     <row r="7">
@@ -14583,22 +14646,22 @@
         <v>2027</v>
       </c>
       <c r="C7" s="626" t="n">
-        <v>158.3271378115205</v>
+        <v>178.4637917606104</v>
       </c>
       <c r="D7" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E7" s="626" t="n">
-        <v>158.3271378115205</v>
+        <v>178.4637917606104</v>
       </c>
       <c r="F7" s="626" t="n">
-        <v>519.0920013562342</v>
+        <v>464.6338151923171</v>
       </c>
       <c r="G7" s="626" t="n">
-        <v>749.8697647311245</v>
+        <v>697.3382671391433</v>
       </c>
       <c r="H7" s="626" t="n">
-        <v>230.7777633748904</v>
+        <v>232.7044519468262</v>
       </c>
     </row>
     <row r="8">
@@ -14606,22 +14669,22 @@
         <v>2028</v>
       </c>
       <c r="C8" s="626" t="n">
-        <v>188.2587414999194</v>
+        <v>210.6100654025392</v>
       </c>
       <c r="D8" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E8" s="626" t="n">
-        <v>188.2587414999194</v>
+        <v>210.6100654025392</v>
       </c>
       <c r="F8" s="626" t="n">
-        <v>330.8332598563148</v>
+        <v>254.0237497897778</v>
       </c>
       <c r="G8" s="626" t="n">
-        <v>672.8916464742942</v>
+        <v>599.0955619064824</v>
       </c>
       <c r="H8" s="626" t="n">
-        <v>342.0583866179794</v>
+        <v>345.0718121167046</v>
       </c>
     </row>
     <row r="9">
@@ -14629,22 +14692,22 @@
         <v>2029</v>
       </c>
       <c r="C9" s="626" t="n">
-        <v>222.3005622168818</v>
+        <v>247.6632825891148</v>
       </c>
       <c r="D9" s="626" t="n">
         <v>9.154999999999999</v>
       </c>
       <c r="E9" s="626" t="n">
-        <v>222.3005622168818</v>
+        <v>247.6632825891148</v>
       </c>
       <c r="F9" s="626" t="n">
-        <v>108.532697639433</v>
+        <v>6.360467200663038</v>
       </c>
       <c r="G9" s="626" t="n">
-        <v>584.486394566851</v>
+        <v>487.1403992212673</v>
       </c>
       <c r="H9" s="626" t="n">
-        <v>475.953696927418</v>
+        <v>480.7799320206043</v>
       </c>
     </row>
     <row r="11">
@@ -15061,16 +15124,16 @@
         <v>77.8175</v>
       </c>
       <c r="E17" s="626" t="n">
-        <v>74.08551912499999</v>
+        <v>72.8078445547945</v>
       </c>
       <c r="F17" s="626" t="n">
-        <v>69.53424216862498</v>
+        <v>66.80896231037669</v>
       </c>
       <c r="G17" s="626" t="n">
-        <v>64.07019047268334</v>
+        <v>59.71007617254889</v>
       </c>
       <c r="H17" s="626" t="n">
-        <v>57.68100665736642</v>
+        <v>51.55593163823804</v>
       </c>
     </row>
     <row r="18">
@@ -15083,16 +15146,16 @@
         <v>-18.00319999999986</v>
       </c>
       <c r="E18" s="626" t="n">
-        <v>-11.28050412499995</v>
+        <v>-10.00282955479446</v>
       </c>
       <c r="F18" s="626" t="n">
-        <v>-3.588976418624782</v>
+        <v>-0.8636965603764821</v>
       </c>
       <c r="G18" s="626" t="n">
-        <v>4.086147466205259</v>
+        <v>7.530637763311473</v>
       </c>
       <c r="H18" s="626" t="n">
-        <v>11.86868257728693</v>
+        <v>16.70749184239834</v>
       </c>
     </row>
     <row r="19">
@@ -15124,19 +15187,19 @@
         </is>
       </c>
       <c r="D20" s="626" t="n">
-        <v>1.517875000000004</v>
+        <v>-13.87579452054798</v>
       </c>
       <c r="E20" s="626" t="n">
-        <v>1.593768750000004</v>
+        <v>-14.56958424657538</v>
       </c>
       <c r="F20" s="626" t="n">
-        <v>1.673457187500003</v>
+        <v>-15.29806345890414</v>
       </c>
       <c r="G20" s="626" t="n">
-        <v>1.757130046875</v>
+        <v>-16.06296663184931</v>
       </c>
       <c r="H20" s="626" t="n">
-        <v>1.844986549218754</v>
+        <v>-16.86611496344182</v>
       </c>
     </row>
     <row r="21">
@@ -15146,19 +15209,19 @@
         </is>
       </c>
       <c r="D21" s="626" t="n">
-        <v>44.96362500000013</v>
+        <v>60.35729452054811</v>
       </c>
       <c r="E21" s="626" t="n">
-        <v>54.83466212500006</v>
+        <v>72.27568969178093</v>
       </c>
       <c r="F21" s="626" t="n">
-        <v>65.83194814387524</v>
+        <v>85.52874864852767</v>
       </c>
       <c r="G21" s="626" t="n">
-        <v>76.97811825683027</v>
+        <v>98.2427052326608</v>
       </c>
       <c r="H21" s="626" t="n">
-        <v>88.40525190744319</v>
+        <v>111.9551626852152</v>
       </c>
     </row>
     <row r="22">
@@ -15190,19 +15253,19 @@
         </is>
       </c>
       <c r="D23" s="626" t="n">
-        <v>44.96362500000013</v>
+        <v>60.35729452054811</v>
       </c>
       <c r="E23" s="626" t="n">
-        <v>54.83466212500006</v>
+        <v>72.27568969178093</v>
       </c>
       <c r="F23" s="626" t="n">
-        <v>65.83194814387524</v>
+        <v>85.52874864852767</v>
       </c>
       <c r="G23" s="626" t="n">
-        <v>76.97811825683027</v>
+        <v>98.2427052326608</v>
       </c>
       <c r="H23" s="626" t="n">
-        <v>88.40525190744319</v>
+        <v>111.9551626852152</v>
       </c>
     </row>
     <row r="24">
@@ -15215,19 +15278,19 @@
         <v>1329.9</v>
       </c>
       <c r="D24" s="626" t="n">
-        <v>870.5363749999998</v>
+        <v>855.1427054794518</v>
       </c>
       <c r="E24" s="626" t="n">
-        <v>815.7017128749998</v>
+        <v>782.867015787671</v>
       </c>
       <c r="F24" s="626" t="n">
-        <v>749.8697647311245</v>
+        <v>697.3382671391433</v>
       </c>
       <c r="G24" s="626" t="n">
-        <v>672.8916464742942</v>
+        <v>599.0955619064824</v>
       </c>
       <c r="H24" s="626" t="n">
-        <v>584.486394566851</v>
+        <v>487.1403992212673</v>
       </c>
     </row>
   </sheetData>
@@ -15615,16 +15678,16 @@
         <v>77.8175</v>
       </c>
       <c r="E17" s="626" t="n">
-        <v>68.95118448449999</v>
+        <v>67.60465037131506</v>
       </c>
       <c r="F17" s="626" t="n">
-        <v>58.05678855092363</v>
+        <v>55.20810137709298</v>
       </c>
       <c r="G17" s="626" t="n">
-        <v>44.91563611256743</v>
+        <v>40.39560666096232</v>
       </c>
       <c r="H17" s="626" t="n">
-        <v>28.02099316663728</v>
+        <v>20.87770873044934</v>
       </c>
     </row>
     <row r="18">
@@ -15637,16 +15700,16 @@
         <v>41.66444200000014</v>
       </c>
       <c r="E18" s="626" t="n">
-        <v>62.8412140072452</v>
+        <v>63.90497595666129</v>
       </c>
       <c r="F18" s="626" t="n">
-        <v>86.48974107027047</v>
+        <v>88.74020393759669</v>
       </c>
       <c r="G18" s="626" t="n">
-        <v>112.8294749216068</v>
+        <v>116.4002981883749</v>
       </c>
       <c r="H18" s="626" t="n">
-        <v>143.0998323096537</v>
+        <v>148.7430270142421</v>
       </c>
     </row>
     <row r="19">
@@ -15678,19 +15741,19 @@
         </is>
       </c>
       <c r="D20" s="626" t="n">
-        <v>1.366087500000003</v>
+        <v>-14.85721506849319</v>
       </c>
       <c r="E20" s="626" t="n">
-        <v>1.434391875000004</v>
+        <v>-15.60007582191784</v>
       </c>
       <c r="F20" s="626" t="n">
-        <v>1.506111468750003</v>
+        <v>-16.38007961301373</v>
       </c>
       <c r="G20" s="626" t="n">
-        <v>1.5814170421875</v>
+        <v>-17.19908359366438</v>
       </c>
       <c r="H20" s="626" t="n">
-        <v>1.660487894296879</v>
+        <v>-18.05903777334764</v>
       </c>
     </row>
     <row r="21">
@@ -15700,19 +15763,19 @@
         </is>
       </c>
       <c r="D21" s="626" t="n">
-        <v>106.8230785000001</v>
+        <v>123.0463810684933</v>
       </c>
       <c r="E21" s="626" t="n">
-        <v>131.2577823322452</v>
+        <v>149.3560119785791</v>
       </c>
       <c r="F21" s="626" t="n">
-        <v>158.3271378115205</v>
+        <v>178.4637917606104</v>
       </c>
       <c r="G21" s="626" t="n">
-        <v>188.2587414999194</v>
+        <v>210.6100654025392</v>
       </c>
       <c r="H21" s="626" t="n">
-        <v>222.3005622168818</v>
+        <v>247.6632825891148</v>
       </c>
     </row>
     <row r="22">
@@ -15744,19 +15807,19 @@
         </is>
       </c>
       <c r="D23" s="626" t="n">
-        <v>106.8230785000001</v>
+        <v>123.0463810684933</v>
       </c>
       <c r="E23" s="626" t="n">
-        <v>131.2577823322452</v>
+        <v>149.3560119785791</v>
       </c>
       <c r="F23" s="626" t="n">
-        <v>158.3271378115205</v>
+        <v>178.4637917606104</v>
       </c>
       <c r="G23" s="626" t="n">
-        <v>188.2587414999194</v>
+        <v>210.6100654025392</v>
       </c>
       <c r="H23" s="626" t="n">
-        <v>222.3005622168818</v>
+        <v>247.6632825891148</v>
       </c>
     </row>
     <row r="24">
@@ -15769,19 +15832,19 @@
         <v>1329.9</v>
       </c>
       <c r="D24" s="626" t="n">
-        <v>808.6769214999998</v>
+        <v>792.4536189315066</v>
       </c>
       <c r="E24" s="626" t="n">
-        <v>677.4191391677547</v>
+        <v>643.0976069529275</v>
       </c>
       <c r="F24" s="626" t="n">
-        <v>519.0920013562342</v>
+        <v>464.6338151923171</v>
       </c>
       <c r="G24" s="626" t="n">
-        <v>330.8332598563148</v>
+        <v>254.0237497897778</v>
       </c>
       <c r="H24" s="626" t="n">
-        <v>108.532697639433</v>
+        <v>6.360467200663038</v>
       </c>
     </row>
   </sheetData>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -12966,6 +12966,13 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FIX: earlier drafts applied 10% to all ΔNWC (ΔRev×WCbase×0.9). Workbook now applies 10% to ΔAR only; deferred revenue uncapped by C13.</t>
+        </is>
+      </c>
+    </row>
     <row r="48">
       <c r="B48" s="564" t="inlineStr">
         <is>
@@ -13083,7 +13090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N43"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" style="244" min="2" max="2"/>
@@ -13101,6 +13108,7 @@
     <col width="14" customWidth="1" style="244" min="14" max="14"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -13122,6 +13130,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="557" t="inlineStr">
         <is>
@@ -13715,12 +13724,12 @@
       </c>
       <c r="C15" s="571" t="inlineStr">
         <is>
-          <t>Working Capital</t>
+          <t>AR / receivables improvement (DSO)</t>
         </is>
       </c>
       <c r="D15" s="571" t="inlineStr">
         <is>
-          <t>AR improve 10% (6/59 DSO→AR); frees AR cash — not 10% of total NWC</t>
+          <t>10% of AR only (6/59 DSO) — NOT 10% of total NWC</t>
         </is>
       </c>
       <c r="E15" s="571" t="inlineStr">
@@ -13760,12 +13769,12 @@
       </c>
       <c r="L15" s="571" t="inlineStr">
         <is>
-          <t>ΔNWC_AI = ΔRevenue_t × Assumptions_Drivers!C25 × (1 − C13).</t>
+          <t>ΔNWC ≈ ΔAR − ΔDeferred. ΔAR_AI = ΔRev × Assumptions_Drivers!C25 × (1 − C13); ΔDeferred = ΔRev × C26. C13 cuts Accounts Receivable only — it does not scale the entire NWC by 10%.</t>
         </is>
       </c>
       <c r="M15" s="573" t="inlineStr">
         <is>
-          <t>Receivables collection periods improved slightly overall. Implementing automated AI billing reminders accelerated cash collections from late customers, lowering total working capital requirements and freeing extra cash for debt.</t>
+          <t>Prior wrong math was ΔNWC_AI = ΔRev × WC_base × (1−C13), which cut all NWC 10%. Fixed: 10% applies only to the AR leg; deferred revenue is unchanged by C13.</t>
         </is>
       </c>
       <c r="N15" s="655" t="inlineStr">
@@ -14357,12 +14366,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>WC base % of Δrev</t>
+          <t>AR intensity + Deferred rev % (NWC)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AR 16.2% / DR 39.0% (net -22.9%)</t>
+          <t>AR 16.2% (C25) / Deferred 39.0% (C26); net ΔNWC rate ≈ −22.9% of Δrev</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -14377,12 +14386,22 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C25 / C26</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Go to Assumptions_Drivers!C25</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>AI_Operating!D20:H20 (ΔNWC)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>ΔNWC_Base = ΔRev × (C25 − C26); ΔNWC_AI = ΔRev × (C25 × (1 − C13) − C26). C13 does not multiply the whole (C25−C26) net.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -14413,7 +14432,7 @@
     <row r="30">
       <c r="B30" s="590" t="inlineStr">
         <is>
-          <t>This list must match Assumptions_Drivers: rev 5%, payroll/commission cut −18%, AI $24.5m, S&amp;M $414.1m, exit 12.9x, CapEx 8%; ΔNWC=ΔAR(59/365)−ΔDR(39%); AI cuts ΔAR 10% only.</t>
+          <t>NWC FIX: C13=10% cuts AR only (not entire NWC). ΔNWC≈ΔAR(C25)−ΔDeferred(C26). Old formula ΔRev×WCbase×(1−C13) removed from ops.</t>
         </is>
       </c>
     </row>
@@ -14452,6 +14471,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="564" t="n"/>
     </row>
@@ -14469,6 +14489,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="B41" s="564" t="n"/>
     </row>
@@ -14486,6 +14507,12 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
   </sheetData>
   <autoFilter ref="B6:M21"/>
   <hyperlinks>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -1989,7 +1989,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="678">
+  <cellXfs count="679">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3240,6 +3240,9 @@
     </xf>
     <xf numFmtId="173" fontId="0" fillId="36" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="187">
@@ -13090,7 +13093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="B2:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" style="244" min="2" max="2"/>
@@ -13108,7 +13111,6 @@
     <col width="14" customWidth="1" style="244" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
         <is>
@@ -13130,7 +13132,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" s="557" t="inlineStr">
         <is>
@@ -14471,7 +14472,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="B37" s="564" t="n"/>
     </row>
@@ -14489,7 +14489,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="B41" s="564" t="n"/>
     </row>
@@ -14507,12 +14506,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
   </sheetData>
   <autoFilter ref="B6:M21"/>
   <hyperlinks>
@@ -14568,7 +14561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H12"/>
+  <dimension ref="B2:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -14740,7 +14733,7 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>TLA initial / TLB initial / Notes initial</t>
+          <t>TLA initial / TLB initial / Senior Notes initial</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -14756,7 +14749,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>TLA rate / TLB rate</t>
+          <t>TLA rate / TLB rate / Notes rate (SOFR+3.5%)</t>
         </is>
       </c>
       <c r="C12" s="581" t="n">
@@ -14764,6 +14757,16 @@
       </c>
       <c r="D12" s="581" t="n">
         <v>0.093</v>
+      </c>
+      <c r="E12" s="581" t="n">
+        <v>0.078</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="678" t="inlineStr">
+        <is>
+          <t>Notes rate was blank under the $183.1m tranche — display only. Interest math already used SOFR+3.5%=7.80% on Notes; TLA=SOFR+4%, TLB=SOFR+5%.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -1989,7 +1989,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="679">
+  <cellXfs count="680">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3243,6 +3243,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="187">
@@ -14561,7 +14564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H13"/>
+  <dimension ref="B2:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -14730,6 +14733,7 @@
         <v>480.7799320206043</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
@@ -14762,13 +14766,15 @@
         <v>0.078</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="678" t="inlineStr">
-        <is>
-          <t>Notes rate was blank under the $183.1m tranche — display only. Interest math already used SOFR+3.5%=7.80% on Notes; TLA=SOFR+4%, TLB=SOFR+5%.</t>
-        </is>
-      </c>
-    </row>
+    <row r="13" ht="36" customHeight="1" s="244">
+      <c r="B13" s="679" t="inlineStr">
+        <is>
+          <t>Those five figures: 457.75 = Term Loan A principal; 274.65 = Term Loan B principal; 183.1 = Senior Notes principal; 8.3% = TLA interest rate; 9.3% = TLB interest rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -1989,7 +1989,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="680">
+  <cellXfs count="682">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3245,6 +3245,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="119" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -14564,8 +14570,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" style="244" min="2" max="2"/>
+    <col width="36" customWidth="1" style="244" min="3" max="3"/>
+    <col width="36" customWidth="1" style="244" min="4" max="4"/>
+    <col width="36" customWidth="1" style="244" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="563" t="inlineStr">
@@ -14733,48 +14745,72 @@
         <v>480.7799320206043</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TLA initial / TLB initial / Senior Notes initial</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>457.75</v>
-      </c>
-      <c r="D11" t="n">
-        <v>274.65</v>
-      </c>
-      <c r="E11" t="n">
-        <v>183.1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TLA rate / TLB rate / Notes rate (SOFR+3.5%)</t>
-        </is>
-      </c>
-      <c r="C12" s="581" t="n">
-        <v>0.08299999999999999</v>
-      </c>
-      <c r="D12" s="581" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="E12" s="581" t="n">
-        <v>0.078</v>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" s="244">
-      <c r="B13" s="679" t="inlineStr">
-        <is>
-          <t>Those five figures: 457.75 = Term Loan A principal; 274.65 = Term Loan B principal; 183.1 = Senior Notes principal; 8.3% = TLA interest rate; 9.3% = TLB interest rate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15"/>
+    <row r="11" ht="55" customHeight="1" s="244">
+      <c r="B11" s="680" t="inlineStr">
+        <is>
+          <t>Principals — three different loans (not TLA pieces)</t>
+        </is>
+      </c>
+      <c r="C11" s="664" t="inlineStr">
+        <is>
+          <t>457.75 = Term Loan A principal ($m). Senior bank loan, paid first, 2.5× EBITDA. Safest debt stack here.</t>
+        </is>
+      </c>
+      <c r="D11" s="664" t="inlineStr">
+        <is>
+          <t>274.65 = Term Loan B principal ($m). Institutional loan below TLA, 1.5× EBITDA. Riskier than TLA, safer than Notes.</t>
+        </is>
+      </c>
+      <c r="E11" s="664" t="inlineStr">
+        <is>
+          <t>183.1 = Senior Notes principal ($m). Bond-style tranche, 1.0× EBITDA. Junior to TLA and TLB in repayment priority.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="55" customHeight="1" s="244">
+      <c r="B12" s="680" t="inlineStr">
+        <is>
+          <t>Rates — one interest rate per loan above</t>
+        </is>
+      </c>
+      <c r="C12" s="681" t="inlineStr">
+        <is>
+          <t>8.3% = TLA interest rate (SOFR+4.0%). Lowest spread of the loans because TLA is the senior bank piece.</t>
+        </is>
+      </c>
+      <c r="D12" s="681" t="inlineStr">
+        <is>
+          <t>9.3% = TLB interest rate (SOFR+5.0%). Higher than TLA because TLB lenders sit behind the bank loan.</t>
+        </is>
+      </c>
+      <c r="E12" s="681" t="inlineStr">
+        <is>
+          <t>7.8% = Notes interest rate (SOFR+3.5%). Rate charged on the $183.1m Notes principal in the cell above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="55" customHeight="1" s="244">
+      <c r="B13" s="680" t="inlineStr">
+        <is>
+          <t>How they differ: columns are separate debt instruments (TLA, TLB, Notes), not slices of one TLA. Left is most senior; right is most junior. Row above = dollars owed; row rates = annual interest on that column only.</t>
+        </is>
+      </c>
+      <c r="C13" s="664" t="inlineStr">
+        <is>
+          <t>TLA vs others: TLA is the bank term loan — first claim on cash for interest and paydown.</t>
+        </is>
+      </c>
+      <c r="D13" s="664" t="inlineStr">
+        <is>
+          <t>TLB vs others: TLB is the next loan — usually higher rate and paid after TLA.</t>
+        </is>
+      </c>
+      <c r="E13" s="664" t="inlineStr">
+        <is>
+          <t>Notes vs others: Notes are the third stack — smallest dollars here; not a TLA sub-tranche.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -14792,7 +14792,7 @@
     <row r="13" ht="55" customHeight="1" s="244">
       <c r="B13" s="680" t="inlineStr">
         <is>
-          <t>How they differ: columns are separate debt instruments (TLA, TLB, Notes), not slices of one TLA. Left is most senior; right is most junior. Row above = dollars owed; row rates = annual interest on that column only.</t>
+          <t>How they differ: each column is a separate loan (TLA, TLB, Notes), not pieces of one TLA. Left=most senior; right=most junior.</t>
         </is>
       </c>
       <c r="C13" s="664" t="inlineStr">

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -153,7 +153,7 @@
     <numFmt numFmtId="245" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
     <numFmt numFmtId="246" formatCode="###0&quot;E&quot;_)"/>
   </numFmts>
-  <fonts count="123">
+  <fonts count="124">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -937,6 +937,11 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="47">
     <fill>
@@ -1989,7 +1994,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="682">
+  <cellXfs count="688">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3252,6 +3257,20 @@
     </xf>
     <xf numFmtId="10" fontId="119" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="111" fillId="35" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="105" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="34" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="115" fillId="34" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="187">
@@ -3707,6 +3726,68 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Initial debt by tranche</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Debt_Sweep_AI'!C16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Debt_Sweep_AI'!$B$17:$B$19</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Debt_Sweep_AI'!$C$17:$C$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+          <showCatName val="1"/>
+          <showPercent val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -4802,6 +4883,33 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>1</col>
@@ -14570,7 +14678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H13"/>
+  <dimension ref="B2:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="244" min="2" max="2"/>
@@ -14811,8 +14919,69 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="682" t="inlineStr">
+        <is>
+          <t>Debt stacks — labels &amp; amounts only</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="683" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C16" s="683" t="inlineStr">
+        <is>
+          <t>Amount ($m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="684" t="inlineStr">
+        <is>
+          <t>Term Loan A principal</t>
+        </is>
+      </c>
+      <c r="C17" s="685" t="n">
+        <v>457.75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="684" t="inlineStr">
+        <is>
+          <t>Term Loan B principal</t>
+        </is>
+      </c>
+      <c r="C18" s="685" t="n">
+        <v>274.65</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="684" t="inlineStr">
+        <is>
+          <t>Senior Notes principal</t>
+        </is>
+      </c>
+      <c r="C19" s="685" t="n">
+        <v>183.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="686" t="inlineStr">
+        <is>
+          <t>Total debt</t>
+        </is>
+      </c>
+      <c r="C20" s="687" t="n">
+        <v>915.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -153,7 +153,7 @@
     <numFmt numFmtId="245" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
     <numFmt numFmtId="246" formatCode="###0&quot;E&quot;_)"/>
   </numFmts>
-  <fonts count="124">
+  <fonts count="128">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -942,6 +942,28 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="47">
     <fill>
@@ -1184,7 +1206,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="44">
     <border>
       <left/>
       <right/>
@@ -1662,6 +1684,21 @@
         <color rgb="00D0D0D0"/>
       </bottom>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1994,7 +2031,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="688">
+  <cellXfs count="698">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3272,6 +3309,30 @@
     <xf numFmtId="4" fontId="115" fillId="34" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="125" fillId="35" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="37" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="126" fillId="37" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="36" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="126" fillId="36" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="115" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="187">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3727,6 +3788,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -3737,21 +3799,22 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Initial debt by tranche</a:t>
+              <a:t>Initial debt by tranche ($m)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
     </title>
     <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Debt_Sweep_AI'!C16</f>
+              <f>'Debt_Sweep_AI'!C15</f>
             </strRef>
           </tx>
           <spPr>
@@ -3761,22 +3824,59 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Debt_Sweep_AI'!$B$17:$B$19</f>
+              <f>'Debt_Sweep_AI'!$B$16:$B$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Debt_Sweep_AI'!$C$17:$C$19</f>
+              <f>'Debt_Sweep_AI'!$C$16:$C$18</f>
             </numRef>
           </val>
         </ser>
         <dLbls>
           <showVal val="1"/>
-          <showCatName val="1"/>
-          <showPercent val="1"/>
         </dLbls>
-        <firstSliceAng val="0"/>
-      </pieChart>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>$ millions</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
     </plotArea>
     <legend>
       <legendPos val="r"/>
@@ -4887,10 +4987,10 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="2880000"/>
+    <ext cx="5400000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -14678,11 +14778,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H20"/>
+  <dimension ref="B2:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="244" min="2" max="2"/>
-    <col width="36" customWidth="1" style="244" min="3" max="3"/>
+    <col width="16" customWidth="1" style="244" min="3" max="3"/>
     <col width="36" customWidth="1" style="244" min="4" max="4"/>
     <col width="36" customWidth="1" style="244" min="5" max="5"/>
   </cols>
@@ -14919,67 +15019,237 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="B15" s="682" t="inlineStr">
-        <is>
-          <t>Debt stacks — labels &amp; amounts only</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="683" t="inlineStr">
+    <row r="14" ht="22" customHeight="1" s="244">
+      <c r="B14" s="688" t="inlineStr">
+        <is>
+          <t>▼ SCROLL HERE — TOTAL DEBT TABLE + CHART (labels &amp; numbers only)</t>
+        </is>
+      </c>
+      <c r="E14" s="689" t="n"/>
+      <c r="F14" s="689" t="n"/>
+      <c r="G14" s="689" t="n"/>
+      <c r="H14" s="689" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1" s="244">
+      <c r="B15" s="690" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C16" s="683" t="inlineStr">
+      <c r="C15" s="690" t="inlineStr">
         <is>
           <t>Amount ($m)</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="684" t="inlineStr">
+      <c r="D15" s="689" t="n"/>
+      <c r="E15" s="689" t="n"/>
+      <c r="F15" s="689" t="n"/>
+      <c r="G15" s="689" t="n"/>
+      <c r="H15" s="689" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" s="244">
+      <c r="B16" s="691" t="inlineStr">
         <is>
           <t>Term Loan A principal</t>
         </is>
       </c>
-      <c r="C17" s="685" t="n">
+      <c r="C16" s="692" t="n">
         <v>457.75</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="684" t="inlineStr">
+      <c r="D16" s="689" t="n"/>
+      <c r="E16" s="689" t="n"/>
+      <c r="F16" s="689" t="n"/>
+      <c r="G16" s="689" t="n"/>
+      <c r="H16" s="689" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1" s="244">
+      <c r="B17" s="691" t="inlineStr">
         <is>
           <t>Term Loan B principal</t>
         </is>
       </c>
-      <c r="C18" s="685" t="n">
+      <c r="C17" s="692" t="n">
         <v>274.65</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="684" t="inlineStr">
+      <c r="D17" s="689" t="n"/>
+      <c r="E17" s="689" t="n"/>
+      <c r="F17" s="689" t="n"/>
+      <c r="G17" s="689" t="n"/>
+      <c r="H17" s="689" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" s="244">
+      <c r="B18" s="691" t="inlineStr">
         <is>
           <t>Senior Notes principal</t>
         </is>
       </c>
-      <c r="C19" s="685" t="n">
+      <c r="C18" s="692" t="n">
         <v>183.1</v>
       </c>
+      <c r="D18" s="689" t="n"/>
+      <c r="E18" s="689" t="n"/>
+      <c r="F18" s="689" t="n"/>
+      <c r="G18" s="689" t="n"/>
+      <c r="H18" s="689" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1" s="244">
+      <c r="B19" s="693" t="inlineStr">
+        <is>
+          <t>TOTAL DEBT</t>
+        </is>
+      </c>
+      <c r="C19" s="694" t="n">
+        <v>915.5</v>
+      </c>
+      <c r="D19" s="689" t="n"/>
+      <c r="E19" s="689" t="n"/>
+      <c r="F19" s="689" t="n"/>
+      <c r="G19" s="689" t="n"/>
+      <c r="H19" s="689" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="686" t="inlineStr">
-        <is>
-          <t>Total debt</t>
-        </is>
-      </c>
-      <c r="C20" s="687" t="n">
-        <v>915.5</v>
-      </c>
+      <c r="B20" s="695" t="n"/>
+      <c r="C20" s="696" t="n"/>
+      <c r="D20" s="689" t="n"/>
+      <c r="E20" s="689" t="n"/>
+      <c r="F20" s="689" t="n"/>
+      <c r="G20" s="689" t="n"/>
+      <c r="H20" s="689" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="697" t="inlineStr">
+        <is>
+          <t>Total debt = 457.75 + 274.65 + 183.10 = 915.50</t>
+        </is>
+      </c>
+      <c r="C21" s="689" t="n"/>
+      <c r="D21" s="689" t="n"/>
+      <c r="E21" s="689" t="n"/>
+      <c r="F21" s="689" t="n"/>
+      <c r="G21" s="689" t="n"/>
+      <c r="H21" s="689" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="689" t="n"/>
+      <c r="C22" s="689" t="n"/>
+      <c r="D22" s="689" t="n"/>
+      <c r="E22" s="689" t="n"/>
+      <c r="F22" s="689" t="n"/>
+      <c r="G22" s="689" t="n"/>
+      <c r="H22" s="689" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="689" t="n"/>
+      <c r="C23" s="689" t="n"/>
+      <c r="D23" s="689" t="n"/>
+      <c r="E23" s="689" t="n"/>
+      <c r="F23" s="689" t="n"/>
+      <c r="G23" s="689" t="n"/>
+      <c r="H23" s="689" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="689" t="n"/>
+      <c r="C24" s="689" t="n"/>
+      <c r="D24" s="689" t="n"/>
+      <c r="E24" s="689" t="n"/>
+      <c r="F24" s="689" t="n"/>
+      <c r="G24" s="689" t="n"/>
+      <c r="H24" s="689" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="689" t="n"/>
+      <c r="C25" s="689" t="n"/>
+      <c r="D25" s="689" t="n"/>
+      <c r="E25" s="689" t="n"/>
+      <c r="F25" s="689" t="n"/>
+      <c r="G25" s="689" t="n"/>
+      <c r="H25" s="689" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="689" t="n"/>
+      <c r="C26" s="689" t="n"/>
+      <c r="D26" s="689" t="n"/>
+      <c r="E26" s="689" t="n"/>
+      <c r="F26" s="689" t="n"/>
+      <c r="G26" s="689" t="n"/>
+      <c r="H26" s="689" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="689" t="n"/>
+      <c r="C27" s="689" t="n"/>
+      <c r="D27" s="689" t="n"/>
+      <c r="E27" s="689" t="n"/>
+      <c r="F27" s="689" t="n"/>
+      <c r="G27" s="689" t="n"/>
+      <c r="H27" s="689" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="689" t="n"/>
+      <c r="C28" s="689" t="n"/>
+      <c r="D28" s="689" t="n"/>
+      <c r="E28" s="689" t="n"/>
+      <c r="F28" s="689" t="n"/>
+      <c r="G28" s="689" t="n"/>
+      <c r="H28" s="689" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="689" t="n"/>
+      <c r="C29" s="689" t="n"/>
+      <c r="D29" s="689" t="n"/>
+      <c r="E29" s="689" t="n"/>
+      <c r="F29" s="689" t="n"/>
+      <c r="G29" s="689" t="n"/>
+      <c r="H29" s="689" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="689" t="n"/>
+      <c r="C30" s="689" t="n"/>
+      <c r="D30" s="689" t="n"/>
+      <c r="E30" s="689" t="n"/>
+      <c r="F30" s="689" t="n"/>
+      <c r="G30" s="689" t="n"/>
+      <c r="H30" s="689" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="689" t="n"/>
+      <c r="C31" s="689" t="n"/>
+      <c r="D31" s="689" t="n"/>
+      <c r="E31" s="689" t="n"/>
+      <c r="F31" s="689" t="n"/>
+      <c r="G31" s="689" t="n"/>
+      <c r="H31" s="689" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="689" t="n"/>
+      <c r="C32" s="689" t="n"/>
+      <c r="D32" s="689" t="n"/>
+      <c r="E32" s="689" t="n"/>
+      <c r="F32" s="689" t="n"/>
+      <c r="G32" s="689" t="n"/>
+      <c r="H32" s="689" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="689" t="n"/>
+      <c r="C33" s="689" t="n"/>
+      <c r="D33" s="689" t="n"/>
+      <c r="E33" s="689" t="n"/>
+      <c r="F33" s="689" t="n"/>
+      <c r="G33" s="689" t="n"/>
+      <c r="H33" s="689" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="689" t="n"/>
+      <c r="C34" s="689" t="n"/>
+      <c r="D34" s="689" t="n"/>
+      <c r="E34" s="689" t="n"/>
+      <c r="F34" s="689" t="n"/>
+      <c r="G34" s="689" t="n"/>
+      <c r="H34" s="689" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B14:D14"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL2.xlsx
@@ -153,7 +153,7 @@
     <numFmt numFmtId="245" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
     <numFmt numFmtId="246" formatCode="###0&quot;E&quot;_)"/>
   </numFmts>
-  <fonts count="128">
+  <fonts count="129">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -964,6 +964,12 @@
       <i val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="47">
     <fill>
@@ -2031,7 +2037,7 @@
     <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="698">
+  <cellXfs count="707">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3333,6 +3339,31 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="127" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="128" fillId="35" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="37" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="123" fillId="37" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="36" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="123" fillId="36" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="126" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="187">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3814,7 +3845,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Debt_Sweep_AI'!C15</f>
+              <f>'Debt_Sweep_AI'!G11</f>
             </strRef>
           </tx>
           <spPr>
@@ -3824,12 +3855,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Debt_Sweep_AI'!$B$16:$B$18</f>
+              <f>'Debt_Sweep_AI'!$F$12:$F$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Debt_Sweep_AI'!$C$16:$C$18</f>
+              <f>'Debt_Sweep_AI'!$G$12:$G$14</f>
             </numRef>
           </val>
         </ser>
@@ -4985,12 +5016,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>8</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3600000"/>
+    <ext cx="4320000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -14778,13 +14809,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H34"/>
+  <dimension ref="B2:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="244" min="2" max="2"/>
     <col width="16" customWidth="1" style="244" min="3" max="3"/>
     <col width="36" customWidth="1" style="244" min="4" max="4"/>
     <col width="36" customWidth="1" style="244" min="5" max="5"/>
+    <col width="26" customWidth="1" style="244" min="6" max="6"/>
+    <col width="14" customWidth="1" style="244" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -14953,6 +14986,7 @@
         <v>480.7799320206043</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="55" customHeight="1" s="244">
       <c r="B11" s="680" t="inlineStr">
         <is>
@@ -14974,6 +15008,18 @@
           <t>183.1 = Senior Notes principal ($m). Bond-style tranche, 1.0× EBITDA. Junior to TLA and TLB in repayment priority.</t>
         </is>
       </c>
+      <c r="F11" s="698" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="G11" s="698" t="inlineStr">
+        <is>
+          <t>Amount ($m)</t>
+        </is>
+      </c>
+      <c r="H11" s="689" t="n"/>
+      <c r="I11" s="689" t="n"/>
     </row>
     <row r="12" ht="55" customHeight="1" s="244">
       <c r="B12" s="680" t="inlineStr">
@@ -14996,6 +15042,16 @@
           <t>7.8% = Notes interest rate (SOFR+3.5%). Rate charged on the $183.1m Notes principal in the cell above.</t>
         </is>
       </c>
+      <c r="F12" s="699" t="inlineStr">
+        <is>
+          <t>Term Loan A principal</t>
+        </is>
+      </c>
+      <c r="G12" s="700" t="n">
+        <v>457.75</v>
+      </c>
+      <c r="H12" s="689" t="n"/>
+      <c r="I12" s="689" t="n"/>
     </row>
     <row r="13" ht="55" customHeight="1" s="244">
       <c r="B13" s="680" t="inlineStr">
@@ -15018,94 +15074,92 @@
           <t>Notes vs others: Notes are the third stack — smallest dollars here; not a TLA sub-tranche.</t>
         </is>
       </c>
+      <c r="F13" s="699" t="inlineStr">
+        <is>
+          <t>Term Loan B principal</t>
+        </is>
+      </c>
+      <c r="G13" s="700" t="n">
+        <v>274.65</v>
+      </c>
+      <c r="H13" s="689" t="n"/>
+      <c r="I13" s="689" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1" s="244">
-      <c r="B14" s="688" t="inlineStr">
-        <is>
-          <t>▼ SCROLL HERE — TOTAL DEBT TABLE + CHART (labels &amp; numbers only)</t>
-        </is>
-      </c>
+      <c r="B14" s="688" t="n"/>
+      <c r="C14" s="689" t="n"/>
+      <c r="D14" s="689" t="n"/>
       <c r="E14" s="689" t="n"/>
-      <c r="F14" s="689" t="n"/>
-      <c r="G14" s="689" t="n"/>
+      <c r="F14" s="699" t="inlineStr">
+        <is>
+          <t>Senior Notes principal</t>
+        </is>
+      </c>
+      <c r="G14" s="700" t="n">
+        <v>183.1</v>
+      </c>
       <c r="H14" s="689" t="n"/>
+      <c r="I14" s="689" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="244">
-      <c r="B15" s="690" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="C15" s="690" t="inlineStr">
-        <is>
-          <t>Amount ($m)</t>
-        </is>
-      </c>
+      <c r="B15" s="701" t="n"/>
+      <c r="C15" s="701" t="n"/>
       <c r="D15" s="689" t="n"/>
       <c r="E15" s="689" t="n"/>
-      <c r="F15" s="689" t="n"/>
-      <c r="G15" s="689" t="n"/>
+      <c r="F15" s="702" t="inlineStr">
+        <is>
+          <t>TOTAL DEBT</t>
+        </is>
+      </c>
+      <c r="G15" s="703" t="n">
+        <v>915.5</v>
+      </c>
       <c r="H15" s="689" t="n"/>
+      <c r="I15" s="689" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="244">
-      <c r="B16" s="691" t="inlineStr">
-        <is>
-          <t>Term Loan A principal</t>
-        </is>
-      </c>
-      <c r="C16" s="692" t="n">
-        <v>457.75</v>
-      </c>
+      <c r="B16" s="704" t="n"/>
+      <c r="C16" s="705" t="n"/>
       <c r="D16" s="689" t="n"/>
       <c r="E16" s="689" t="n"/>
-      <c r="F16" s="689" t="n"/>
+      <c r="F16" s="706" t="inlineStr">
+        <is>
+          <t>Total debt = 457.75 + 274.65 + 183.10 = 915.50</t>
+        </is>
+      </c>
       <c r="G16" s="689" t="n"/>
       <c r="H16" s="689" t="n"/>
+      <c r="I16" s="689" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="244">
-      <c r="B17" s="691" t="inlineStr">
-        <is>
-          <t>Term Loan B principal</t>
-        </is>
-      </c>
-      <c r="C17" s="692" t="n">
-        <v>274.65</v>
-      </c>
+      <c r="B17" s="704" t="n"/>
+      <c r="C17" s="705" t="n"/>
       <c r="D17" s="689" t="n"/>
       <c r="E17" s="689" t="n"/>
       <c r="F17" s="689" t="n"/>
       <c r="G17" s="689" t="n"/>
       <c r="H17" s="689" t="n"/>
+      <c r="I17" s="689" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="244">
-      <c r="B18" s="691" t="inlineStr">
-        <is>
-          <t>Senior Notes principal</t>
-        </is>
-      </c>
-      <c r="C18" s="692" t="n">
-        <v>183.1</v>
-      </c>
+      <c r="B18" s="704" t="n"/>
+      <c r="C18" s="705" t="n"/>
       <c r="D18" s="689" t="n"/>
       <c r="E18" s="689" t="n"/>
       <c r="F18" s="689" t="n"/>
       <c r="G18" s="689" t="n"/>
       <c r="H18" s="689" t="n"/>
+      <c r="I18" s="689" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="244">
-      <c r="B19" s="693" t="inlineStr">
-        <is>
-          <t>TOTAL DEBT</t>
-        </is>
-      </c>
-      <c r="C19" s="694" t="n">
-        <v>915.5</v>
-      </c>
+      <c r="B19" s="704" t="n"/>
+      <c r="C19" s="705" t="n"/>
       <c r="D19" s="689" t="n"/>
       <c r="E19" s="689" t="n"/>
       <c r="F19" s="689" t="n"/>
       <c r="G19" s="689" t="n"/>
       <c r="H19" s="689" t="n"/>
+      <c r="I19" s="689" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="695" t="n"/>
@@ -15115,19 +15169,17 @@
       <c r="F20" s="689" t="n"/>
       <c r="G20" s="689" t="n"/>
       <c r="H20" s="689" t="n"/>
+      <c r="I20" s="689" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="697" t="inlineStr">
-        <is>
-          <t>Total debt = 457.75 + 274.65 + 183.10 = 915.50</t>
-        </is>
-      </c>
+      <c r="B21" s="697" t="n"/>
       <c r="C21" s="689" t="n"/>
       <c r="D21" s="689" t="n"/>
       <c r="E21" s="689" t="n"/>
       <c r="F21" s="689" t="n"/>
       <c r="G21" s="689" t="n"/>
       <c r="H21" s="689" t="n"/>
+      <c r="I21" s="689" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="689" t="n"/>
@@ -15137,6 +15189,7 @@
       <c r="F22" s="689" t="n"/>
       <c r="G22" s="689" t="n"/>
       <c r="H22" s="689" t="n"/>
+      <c r="I22" s="689" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="689" t="n"/>
@@ -15146,6 +15199,7 @@
       <c r="F23" s="689" t="n"/>
       <c r="G23" s="689" t="n"/>
       <c r="H23" s="689" t="n"/>
+      <c r="I23" s="689" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="689" t="n"/>
@@ -15155,6 +15209,7 @@
       <c r="F24" s="689" t="n"/>
       <c r="G24" s="689" t="n"/>
       <c r="H24" s="689" t="n"/>
+      <c r="I24" s="689" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="689" t="n"/>
@@ -15164,6 +15219,7 @@
       <c r="F25" s="689" t="n"/>
       <c r="G25" s="689" t="n"/>
       <c r="H25" s="689" t="n"/>
+      <c r="I25" s="689" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="689" t="n"/>
@@ -15173,6 +15229,7 @@
       <c r="F26" s="689" t="n"/>
       <c r="G26" s="689" t="n"/>
       <c r="H26" s="689" t="n"/>
+      <c r="I26" s="689" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="689" t="n"/>
@@ -15182,6 +15239,7 @@
       <c r="F27" s="689" t="n"/>
       <c r="G27" s="689" t="n"/>
       <c r="H27" s="689" t="n"/>
+      <c r="I27" s="689" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="689" t="n"/>
@@ -15191,6 +15249,7 @@
       <c r="F28" s="689" t="n"/>
       <c r="G28" s="689" t="n"/>
       <c r="H28" s="689" t="n"/>
+      <c r="I28" s="689" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="689" t="n"/>
@@ -15200,6 +15259,7 @@
       <c r="F29" s="689" t="n"/>
       <c r="G29" s="689" t="n"/>
       <c r="H29" s="689" t="n"/>
+      <c r="I29" s="689" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="689" t="n"/>
@@ -15247,9 +15307,6 @@
       <c r="H34" s="689" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B14:D14"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
